--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>384741577.16</v>
+        <v>1580000000</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2481,10 +2481,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>628398583.83</v>
+        <v>1823657006.67</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>106804261.82</v>
+        <v>438608000</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2496,16 +2496,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2745965.83</v>
+        <v>2653790.16</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>8633652.529999999</v>
+        <v>8343840.94</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>183648282.38</v>
+        <v>515070033.3</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2518,11 +2518,17 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>197601342.62</v>
-      </c>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
+        <v>1540000000</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>147816672.25</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>27279175.53</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>24810710</v>
+      </c>
       <c r="F36" s="6" t="n"/>
       <c r="G36" s="6" t="n">
         <v>29986046.5</v>
@@ -2531,26 +2537,32 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>254643655.12</v>
+        <v>1796948870.28</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>54854132.71</v>
-      </c>
-      <c r="K36" s="9" t="n"/>
-      <c r="L36" s="9" t="n"/>
-      <c r="M36" s="9" t="n"/>
+        <v>427504000</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>47162206.4</v>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>9261586.119999999</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>8799940.630000001</v>
+      </c>
       <c r="N36" s="9" t="n"/>
       <c r="O36" s="9" t="n">
-        <v>9091275.08</v>
+        <v>8586780.689999999</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>77203759.31999999</v>
+        <v>514572865.37</v>
       </c>
       <c r="R36" s="10" t="n">
-        <v>0.2825</v>
+        <v>0.2787214839144412</v>
       </c>
     </row>
   </sheetData>
@@ -4038,7 +4050,7 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>185276153.9</v>
+        <v>760864800</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>11377652.1</v>
@@ -4081,11 +4093,17 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>95156902.55</v>
-      </c>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
+        <v>741602400</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>9775548.310000001</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>7350913</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>38474226.51</v>
+      </c>
       <c r="F36" s="6" t="n"/>
       <c r="G36" s="6" t="n">
         <v>8471978</v>
@@ -4093,9 +4111,15 @@
       <c r="H36" s="11" t="n">
         <v>0.4816</v>
       </c>
-      <c r="I36" s="11" t="n"/>
-      <c r="J36" s="11" t="n"/>
-      <c r="K36" s="11" t="n"/>
+      <c r="I36" s="11" t="n">
+        <v>0.3584000000000001</v>
+      </c>
+      <c r="J36" s="11" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="K36" s="11" t="n">
+        <v>0.2603</v>
+      </c>
       <c r="L36" s="11" t="n"/>
       <c r="M36" s="11" t="n">
         <v>0.2825</v>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -2529,7 +2529,9 @@
       <c r="E36" s="6" t="n">
         <v>24810710</v>
       </c>
-      <c r="F36" s="6" t="n"/>
+      <c r="F36" s="6" t="n">
+        <v>10391420.59</v>
+      </c>
       <c r="G36" s="6" t="n">
         <v>29986046.5</v>
       </c>
@@ -2537,7 +2539,7 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1796948870.28</v>
+        <v>1807340290.87</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>427504000</v>
@@ -2551,7 +2553,9 @@
       <c r="M36" s="9" t="n">
         <v>8799940.630000001</v>
       </c>
-      <c r="N36" s="9" t="n"/>
+      <c r="N36" s="9" t="n">
+        <v>2975679.03</v>
+      </c>
       <c r="O36" s="9" t="n">
         <v>8586780.689999999</v>
       </c>
@@ -2559,10 +2563,10 @@
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>514572865.37</v>
+        <v>517548544.4</v>
       </c>
       <c r="R36" s="10" t="n">
-        <v>0.2787214839144412</v>
+        <v>0.3000842795719814</v>
       </c>
     </row>
   </sheetData>
@@ -4104,7 +4108,9 @@
       <c r="E36" s="6" t="n">
         <v>38474226.51</v>
       </c>
-      <c r="F36" s="6" t="n"/>
+      <c r="F36" s="6" t="n">
+        <v>8029436.38</v>
+      </c>
       <c r="G36" s="6" t="n">
         <v>8471978</v>
       </c>
@@ -4120,7 +4126,9 @@
       <c r="K36" s="11" t="n">
         <v>0.2603</v>
       </c>
-      <c r="L36" s="11" t="n"/>
+      <c r="L36" s="11" t="n">
+        <v>0.7726999999999999</v>
+      </c>
       <c r="M36" s="11" t="n">
         <v>0.2825</v>
       </c>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily volume'!$A$2:$R$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Parlay share'!$A$2:$M$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily volume'!$A$2:$R$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Parlay share'!$A$2:$M$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2569,8 +2569,66 @@
         <v>0.3000842795719814</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1719953645.86</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>161563894</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>32818984.23</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>20593115</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>10350317.52</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>36280620</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>12713214</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>1994273790.61</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>477459132.09</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>49969403.31</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>10372615.86</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>7004156.33</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>2925245.08</v>
+      </c>
+      <c r="O37" s="9" t="n">
+        <v>10253763.24</v>
+      </c>
+      <c r="P37" s="9" t="n">
+        <v>5644731.29</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>563629047.2</v>
+      </c>
+      <c r="R37" s="10" t="n">
+        <v>0.3158320960096582</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R36"/>
+  <autoFilter ref="A2:R37"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -2586,7 +2644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4133,15 +4191,58 @@
         <v>0.2825</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>828260877.7</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>12490106.43</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>6837334</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>42248270.23</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>9179481.23</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>11868618</v>
+      </c>
+      <c r="H37" s="11" t="n">
+        <v>0.4816</v>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="J37" s="11" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <v>0.2615</v>
+      </c>
+      <c r="L37" s="11" t="n">
+        <v>0.8869</v>
+      </c>
+      <c r="M37" s="11" t="n">
+        <v>0.3271</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>Kalshi = its KXMVE multi-event parlay engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample of the public feed scaled to the daily total. Its % is of its WHOLE-EXCHANGE volume (matching its main column) - ~48% by contracts / ~11% by $. Sample-based, so it moves less day to day; not folded into the Daily tab's blended Combo %. Rothera runs no on-exchange parlay product and is omitted here.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M36"/>
+  <autoFilter ref="A2:M37"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -4172,7 +4273,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-04 from unified_sports_volume.csv</t>
+          <t>Generated 2026-09-05 from unified_sports_volume.csv</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily volume'!$A$2:$R$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Parlay share'!$A$2:$M$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily volume'!$A$2:$R$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Parlay share'!$A$2:$M$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1719953645.86</v>
+        <v>1721050019.04</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2597,10 +2597,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1994273790.61</v>
+        <v>1995370163.79</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>477459132.09</v>
+        <v>477763485.29</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2612,23 +2612,81 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2925245.08</v>
+        <v>2925215.83</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>10253763.24</v>
+        <v>10253660.7</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>563629047.2</v>
+        <v>563933268.61</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2342612096.54</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>172439695.17</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>50137129.16</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>52782942</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>17867253.73</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>30304593</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>20531449</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>2686675158.6</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>650309118</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>46814559.69</v>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>18023125.75</v>
+      </c>
+      <c r="M38" s="9" t="n">
+        <v>15883449.41</v>
+      </c>
+      <c r="N38" s="9" t="n">
+        <v>5016245.58</v>
+      </c>
+      <c r="O38" s="9" t="n">
+        <v>8508038.390000001</v>
+      </c>
+      <c r="P38" s="9" t="n">
+        <v>9731632.92</v>
+      </c>
+      <c r="Q38" s="9" t="n">
+        <v>754286169.73</v>
+      </c>
+      <c r="R38" s="10" t="n">
+        <v>0.3730201375328469</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R37"/>
+  <autoFilter ref="A2:R38"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -2644,7 +2702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4198,7 +4256,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>828260877.7</v>
+        <v>828788847.17</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>12490106.43</v>
@@ -4234,15 +4292,58 @@
         <v>0.3271</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>1128108281.21</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>18169819.03</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>24913497</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>52326936.92</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>14441124.55</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>10824093</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <v>0.4816</v>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="J38" s="11" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="K38" s="11" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="L38" s="11" t="n">
+        <v>0.8081999999999999</v>
+      </c>
+      <c r="M38" s="11" t="n">
+        <v>0.3572</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>Kalshi = its KXMVE multi-event parlay engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample of the public feed scaled to the daily total. Its % is of its WHOLE-EXCHANGE volume (matching its main column) - ~48% by contracts / ~11% by $. Sample-based, so it moves less day to day; not folded into the Daily tab's blended Combo %. Rothera runs no on-exchange parlay product and is omitted here.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M37"/>
+  <autoFilter ref="A2:M38"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -4273,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-05 from unified_sports_volume.csv</t>
+          <t>Generated 2026-09-06 from unified_sports_volume.csv</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -7,13 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Daily volume" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Parlay share" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sports volume" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Total exchange" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Parlay share" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily volume'!$A$2:$R$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Parlay share'!$A$2:$M$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,7 +47,7 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -477,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -616,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1410000000</v>
+        <v>1226348301.09</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -635,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1587962094.58</v>
+        <v>1404310395.67</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>391416000</v>
+        <v>290712233.4</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -648,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>597930.11</v>
+        <v>524812.1800000001</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>10664366.25</v>
+        <v>9360273.49</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>456136202.99</v>
+        <v>354055225.7</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -670,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1240000000</v>
+        <v>1019790521.49</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -689,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1423404909.51</v>
+        <v>1203195431</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>344224000</v>
+        <v>223745816.63</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -702,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>621319.9</v>
+        <v>516298.92</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>11116379.04</v>
+        <v>9237390.460000001</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>411519804.72</v>
+        <v>289057611.79</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -724,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>826100000</v>
+        <v>766399762</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -743,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>942142547.04</v>
+        <v>882442309.04</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>229325360</v>
+        <v>197400001.9</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -756,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>398283.4</v>
+        <v>374709.28</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5739032.4</v>
+        <v>5399343.04</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>271777958.18</v>
+        <v>239489336.6</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -778,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1150000000</v>
+        <v>983748421.3200001</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -799,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1334638149.02</v>
+        <v>1168386570.34</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>319240000</v>
+        <v>236058435.39</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -814,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>362261.57</v>
+        <v>324586.19</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>8212604.46</v>
+        <v>7358489.61</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>389928450.59</v>
+        <v>305855095.76</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -836,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1300000000</v>
+        <v>1097580318.95</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -857,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1505080037.58</v>
+        <v>1302660356.53</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>360880000</v>
+        <v>250948122.31</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -872,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>822855.03</v>
+        <v>709925.6800000001</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>8917132.41</v>
+        <v>7693337.29</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>439320718.7</v>
+        <v>328052116.54</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -894,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1180000000</v>
+        <v>1011514178.87</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -915,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1402173119.51</v>
+        <v>1233687298.38</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>327568000</v>
+        <v>229522489.57</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -930,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1460836.55</v>
+        <v>1255741.5</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>9783240.49</v>
+        <v>8409716.380000001</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>408821533.7</v>
+        <v>309197404.1</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -952,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1160000000</v>
+        <v>961933487.02</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -973,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1343607161.54</v>
+        <v>1145540648.56</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>322016000</v>
+        <v>214888229.88</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -988,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>962747.51</v>
+        <v>814778.05</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>8094646.96</v>
+        <v>6850540.39</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>389725239.67</v>
+        <v>281205393.52</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1010,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1290000000</v>
+        <v>1073038713.76</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1031,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1494665897.48</v>
+        <v>1277704611.24</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>358104000</v>
+        <v>240123237.17</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1046,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2779825.18</v>
+        <v>2353400.13</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>8941548.68</v>
+        <v>7569915.52</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>433525851.74</v>
+        <v>313747030.7</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1068,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1170000000</v>
+        <v>960754930.92</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1089,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1394673317.12</v>
+        <v>1185428248.04</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>324792000</v>
+        <v>212543726.02</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1104,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2933210.13</v>
+        <v>2490144.51</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>10518020.08</v>
+        <v>8929257.99</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>410458570.91</v>
+        <v>296178469.23</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1126,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>861600000</v>
+        <v>686488587.74</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1147,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>988511691.03</v>
+        <v>813400278.77</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>239180160</v>
+        <v>150986874.89</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1162,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>2270938.56</v>
+        <v>1897060.47</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>4172455.9</v>
+        <v>3485519.72</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>285505514.36</v>
+        <v>196251414.98</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1184,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1180000000</v>
+        <v>970895177.89</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1205,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1339556654.24</v>
+        <v>1130451832.13</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>327568000</v>
+        <v>227536176.85</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1220,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>3016973.98</v>
+        <v>2642012.55</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>6295526.18</v>
+        <v>5513093.35</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>387723048.6</v>
+        <v>286533831.19</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1242,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1300000000</v>
+        <v>1042720983.61</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1263,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1501484190.07</v>
+        <v>1244205173.68</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>360880000</v>
+        <v>230879117.13</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1278,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>3398793</v>
+        <v>2865649.45</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>8333200.03</v>
+        <v>7026032.49</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>437525064.47</v>
+        <v>305683870.5</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1300,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1220000000</v>
+        <v>1046511668.87</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1321,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1442047099.81</v>
+        <v>1268558768.68</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>338672000</v>
+        <v>238375725.51</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1336,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>4351928.21</v>
+        <v>3737679.55</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>9126364.98</v>
+        <v>7838233.09</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>418041029.99</v>
+        <v>315842374.95</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1358,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1200000000</v>
+        <v>1026507894.75</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1379,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1402143879.03</v>
+        <v>1228651773.78</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>333120000</v>
+        <v>246149823.25</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1394,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3991051.15</v>
+        <v>3558650.45</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>8453164.18</v>
+        <v>7537326.75</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>403888269.48</v>
+        <v>315569854.61</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1416,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1500000000</v>
+        <v>1275197725.87</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1437,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1742721477.25</v>
+        <v>1517919203.12</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>416400000</v>
+        <v>295667968.4</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1452,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4926894.39</v>
+        <v>4271142.9</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>11052215.46</v>
+        <v>9581206.310000001</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>501623105.73</v>
+        <v>378764313.5</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1474,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1400000000</v>
+        <v>1123162110.77</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1495,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1652175161.33</v>
+        <v>1375337272.1</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>388640000</v>
+        <v>251871816.77</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1510,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>4127549.32</v>
+        <v>3520463.22</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>13196617.46</v>
+        <v>11255639.31</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>480407123.62</v>
+        <v>341090876.14</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1532,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>926400000</v>
+        <v>780468036.02</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1553,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>1087816845.53</v>
+        <v>941884881.55</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>257168640</v>
+        <v>182876983.93</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1568,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>3290649.79</v>
+        <v>2893225.33</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>5662876.63</v>
+        <v>4978949.19</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>315734009.35</v>
+        <v>240361001.38</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1590,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>1160000000</v>
+        <v>925190752.63</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1611,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1338003383.82</v>
+        <v>1103194136.45</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>322016000</v>
+        <v>208930058.54</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1626,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3637816.9</v>
+        <v>3099127.65</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>7299548.29</v>
+        <v>6218628.53</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>385453875.2</v>
+        <v>270748324.73</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1648,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1370000000</v>
+        <v>1099235509.23</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1669,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1585300293.82</v>
+        <v>1314535803.05</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>380312000</v>
+        <v>244612818.63</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1684,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>4357451.88</v>
+        <v>3671151</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>9151899.65</v>
+        <v>7710470.83</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>457293772.23</v>
+        <v>319466861.16</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1706,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>1190000000</v>
+        <v>967567863.75</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1727,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1413321005.58</v>
+        <v>1190888869.33</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>330344000</v>
+        <v>210526920.69</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1742,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3954335.84</v>
+        <v>3281796.18</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>9080706.52</v>
+        <v>7536291.6</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>405843923.03</v>
+        <v>283809889.14</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1764,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1260000000</v>
+        <v>1003048142.35</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1785,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1455156688.06</v>
+        <v>1198204830.41</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>349776000</v>
+        <v>222078381.47</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1800,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>4683619.92</v>
+        <v>3890999.55</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>7626528.18</v>
+        <v>6335872.31</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>410790643.03</v>
+        <v>281009748.26</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1822,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1680000000</v>
+        <v>1362246646.22</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1843,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1952216755.12</v>
+        <v>1634463401.34</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>466368000</v>
+        <v>306752950.06</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1858,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>7292030.85</v>
+        <v>6136465.49</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>12204614.9</v>
+        <v>10270554.21</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>550716777.25</v>
+        <v>388012101.25</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1880,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1480000000</v>
+        <v>1156848829.83</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1901,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1732499967.65</v>
+        <v>1409348797.48</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>410848000</v>
+        <v>247783486.21</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1916,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>4661314.97</v>
+        <v>3795191.26</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>12195295.41</v>
+        <v>9929275.09</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>492177835.15</v>
+        <v>325981177.34</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1938,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>1120000000</v>
+        <v>870234303.1799999</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1959,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1289104212.37</v>
+        <v>1039338515.55</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>310912000</v>
+        <v>193417623.28</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1974,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3901805.72</v>
+        <v>3256064.62</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>6811497.3</v>
+        <v>5684208.02</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>364527114.66</v>
+        <v>245259707.55</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1996,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1320000000</v>
+        <v>1002162415.6</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2017,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1527337407.96</v>
+        <v>1209499823.56</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>366432000</v>
+        <v>216979327.6</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2032,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>3577500.59</v>
+        <v>2934170.27</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>8458913.27</v>
+        <v>6937774.34</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>432568818.94</v>
+        <v>280951677.29</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2054,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1420000000</v>
+        <v>1105872460</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2075,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1665854899.65</v>
+        <v>1351727359.65</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>394192000</v>
+        <v>242452076.24</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2090,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>3228105.93</v>
+        <v>2693171.11</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>10504510.02</v>
+        <v>8763790.130000001</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>476781094.95</v>
+        <v>322765516.48</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2112,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>1190000000</v>
+        <v>932777126.6900001</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2133,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1393947814.45</v>
+        <v>1136724941.14</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>330344000</v>
+        <v>196501497.97</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2148,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>3640510.96</v>
+        <v>2927838.11</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>8178728.19</v>
+        <v>6577645.92</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>395611580.51</v>
+        <v>259455323.36</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2170,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1490000000</v>
+        <v>1161937950.78</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2191,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1682836484.07</v>
+        <v>1354774434.85</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>413624000</v>
+        <v>252320947.82</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2206,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>5186852.71</v>
+        <v>4229055.32</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>5570098.34</v>
+        <v>4541531.32</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>475222669.68</v>
+        <v>311933253.09</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2228,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1930000000</v>
+        <v>1439894997.32</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2249,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>2230056666.03</v>
+        <v>1739951663.35</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>535768000</v>
+        <v>284684023.21</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2264,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>5320793.3</v>
+        <v>4066960.53</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>7821426.22</v>
+        <v>5978325.02</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>629735408.38</v>
+        <v>375554497.62</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2286,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1700000000</v>
+        <v>1319471126.18</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2307,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1959763084.12</v>
+        <v>1579234210.3</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>471920000</v>
+        <v>283287864.82</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2322,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3750230.46</v>
+        <v>3050704.66</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>9143248.68</v>
+        <v>7437769.93</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>554564843.66</v>
+        <v>363527703.93</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2344,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1400000000</v>
+        <v>1096650095.4</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2365,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1586041026.11</v>
+        <v>1282691121.51</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>388640000</v>
+        <v>243300304.72</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2380,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1996993.35</v>
+        <v>1660372.72</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>8660854.789999999</v>
+        <v>7200948.89</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>449152739.67</v>
+        <v>302016517.86</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2402,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1520000000</v>
+        <v>1141713194.51</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2423,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1743891113.95</v>
+        <v>1365604308.46</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>421952000</v>
+        <v>239505889.8</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2438,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1629086.86</v>
+        <v>1298241.07</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>11585152.88</v>
+        <v>9232363.02</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>492426614.48</v>
+        <v>307296868.64</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2460,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1580000000</v>
+        <v>1192398704.86</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2481,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1823657006.67</v>
+        <v>1436055711.53</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>438608000</v>
+        <v>253455797.87</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2496,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2653790.16</v>
+        <v>2144828.4</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>8343840.94</v>
+        <v>6743602.9</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>515070033.3</v>
+        <v>327808631.37</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2518,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1540000000</v>
+        <v>1226269672.23</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2539,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1807340290.87</v>
+        <v>1493609963.1</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>427504000</v>
+        <v>272681676.9</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2554,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2975679.03</v>
+        <v>2511016.2</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>8586780.689999999</v>
+        <v>7245924.46</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>517548544.4</v>
+        <v>360920702.24</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2576,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1721050019.04</v>
+        <v>1172274619.91</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2597,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1995370163.79</v>
+        <v>1446594764.66</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>477763485.29</v>
+        <v>244007566.85</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2612,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2925215.83</v>
+        <v>2343656.88</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>10253660.7</v>
+        <v>8215141.66</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>563933268.61</v>
+        <v>327557272.18</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2633,9 +2635,7 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
-        <v>2342612096.54</v>
-      </c>
+      <c r="B38" s="5" t="n"/>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
       </c>
@@ -2655,11 +2655,9 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2686675158.6</v>
-      </c>
-      <c r="J38" s="8" t="n">
-        <v>650309118</v>
-      </c>
+        <v>344063062.06</v>
+      </c>
+      <c r="J38" s="8" t="n"/>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
       </c>
@@ -2670,23 +2668,77 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>5016245.58</v>
+        <v>5461948.41</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>8508038.390000001</v>
+        <v>9263993.560000001</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>754286169.73</v>
+        <v>105178709.74</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="6" t="n">
+        <v>131412975.25</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>32056055.97</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>35925674</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>21673332.38</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>32407752</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>33293997</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>286769786.6</v>
+      </c>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="9" t="n">
+        <v>38038258.86</v>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>13010644.31</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>11501420.69</v>
+      </c>
+      <c r="N39" s="9" t="n">
+        <v>7323631.12</v>
+      </c>
+      <c r="O39" s="9" t="n">
+        <v>10950896.56</v>
+      </c>
+      <c r="P39" s="9" t="n">
+        <v>16077465.82</v>
+      </c>
+      <c r="Q39" s="9" t="n">
+        <v>96902317.34999999</v>
+      </c>
+      <c r="R39" s="10" t="n">
+        <v>0.3654745795652588</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R38"/>
+  <autoFilter ref="A2:R39"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -2702,7 +2754,2159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:Q39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contracts traded  (one-sided, $1 face)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Notional $  (~ USD changed hands)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Kalshi</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Polymarket US</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Novig</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>DKeX</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>UDX</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Crypto.com</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Rothera</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Kalshi</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Polymarket US</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Novig</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>DKeX</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>UDX</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>Crypto.com</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>Rothera</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>1410000000</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>134802912.52</v>
+      </c>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n">
+        <v>983501</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>2081593.92</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>37483644</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>4563661</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>1589915312.44</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>391416000</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>51252892</v>
+      </c>
+      <c r="L3" s="9" t="n"/>
+      <c r="M3" s="9" t="n">
+        <v>436176.76</v>
+      </c>
+      <c r="N3" s="9" t="n">
+        <v>597732.41</v>
+      </c>
+      <c r="O3" s="9" t="n">
+        <v>10763477.26</v>
+      </c>
+      <c r="P3" s="9" t="n">
+        <v>2079977.15</v>
+      </c>
+      <c r="Q3" s="9" t="n">
+        <v>456546255.58</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1240000000</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>135833286.22</v>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n">
+        <v>1048537</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>2149081.97</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>38952253</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>7899184</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>1425882342.19</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>344224000</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>51599931.62</v>
+      </c>
+      <c r="L4" s="9" t="n"/>
+      <c r="M4" s="9" t="n">
+        <v>484971.88</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>621241.21</v>
+      </c>
+      <c r="O4" s="9" t="n">
+        <v>11260037.98</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>3993660.15</v>
+      </c>
+      <c r="Q4" s="9" t="n">
+        <v>412183842.84</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>826100000</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>87736455.39</v>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n">
+        <v>361422</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1380684.94</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>20405362</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>9274058</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>945257982.33</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>229325360</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>32367279.06</v>
+      </c>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n">
+        <v>165403.4</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>398141.79</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>5884200.74</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>4439328.3</v>
+      </c>
+      <c r="Q5" s="9" t="n">
+        <v>272579713.29</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1150000000</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>122647218.83</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>17996650.04</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>472924</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1239940.57</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>28486561</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>16628972</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>1337472266.44</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>319240000</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>48161416.36</v>
+      </c>
+      <c r="L6" s="9" t="n">
+        <v>6356251.37</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>222905.14</v>
+      </c>
+      <c r="N6" s="9" t="n">
+        <v>362287.47</v>
+      </c>
+      <c r="O6" s="9" t="n">
+        <v>8323241.01</v>
+      </c>
+      <c r="P6" s="9" t="n">
+        <v>8118311.67</v>
+      </c>
+      <c r="Q6" s="9" t="n">
+        <v>390784413.02</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>127635575.93</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>20682990.79</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>605580</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>2819039.99</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>30864670</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>25854868</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>1508462724.71</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>360880000</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>48492980.6</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>7561907.44</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>292548.17</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>822533.66</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>9005629.640000001</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>13080537.68</v>
+      </c>
+      <c r="Q7" s="9" t="n">
+        <v>440136137.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1180000000</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>142486082.56</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>18363859.9</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>655143</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>5010366.56</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>34132045</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>23846968</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>1404494465.02</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>327568000</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>50721504.22</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>7229157.84</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>314539.43</v>
+      </c>
+      <c r="N8" s="9" t="n">
+        <v>1460046.62</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>9946253.73</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>12037420</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>409276921.85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1160000000</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>119155726.68</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>15826632.35</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>614652</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>3319144.65</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>28308461</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>18491780</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>1345716396.68</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>322016000</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>45150709.09</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>4663406.57</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>280061.26</v>
+      </c>
+      <c r="N9" s="9" t="n">
+        <v>962433.0699999999</v>
+      </c>
+      <c r="O9" s="9" t="n">
+        <v>8208439.79</v>
+      </c>
+      <c r="P9" s="9" t="n">
+        <v>8928506.67</v>
+      </c>
+      <c r="Q9" s="9" t="n">
+        <v>390209556.44</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1290000000</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>119826023.15</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>20822561.28</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>1178183</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>9583995.710000001</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>31048172</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>23442223</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>1495901158.14</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>358104000</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>44119482.44</v>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>7466670.66</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>545929.65</v>
+      </c>
+      <c r="N10" s="9" t="n">
+        <v>2778971.06</v>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>9002713.9</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>11733055.02</v>
+      </c>
+      <c r="Q10" s="9" t="n">
+        <v>433750822.73</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1170000000</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>126747740.75</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>18043033.81</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>936332</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>9966584.189999999</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>36116656</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>34090206</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>1395900552.75</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>324792000</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>48633763.9</v>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>6159576.07</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>391311.2</v>
+      </c>
+      <c r="N11" s="9" t="n">
+        <v>2932449.05</v>
+      </c>
+      <c r="O11" s="9" t="n">
+        <v>10626534.78</v>
+      </c>
+      <c r="P11" s="9" t="n">
+        <v>17177521.22</v>
+      </c>
+      <c r="Q11" s="9" t="n">
+        <v>410713156.22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>861600000</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>77414257.48</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>16189968.12</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>315621</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>7862717.9</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>14896086</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>11570724</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>989849374.5</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>239180160</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>28257376.93</v>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>5783341.08</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>146839.93</v>
+      </c>
+      <c r="N12" s="9" t="n">
+        <v>2270517.48</v>
+      </c>
+      <c r="O12" s="9" t="n">
+        <v>4301543.57</v>
+      </c>
+      <c r="P12" s="9" t="n">
+        <v>5899079.07</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>285838858.06</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1180000000</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>88962184</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>20926301.85</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>737122</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>10423439.05</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>22104454</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>20000913</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>1343154413.9</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>327568000</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>32891944.15</v>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>8237000.57</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>342568.77</v>
+      </c>
+      <c r="N13" s="9" t="n">
+        <v>3012908.88</v>
+      </c>
+      <c r="O13" s="9" t="n">
+        <v>6389321.75</v>
+      </c>
+      <c r="P13" s="9" t="n">
+        <v>9798821.01</v>
+      </c>
+      <c r="Q13" s="9" t="n">
+        <v>388240565.14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>115992580.3</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>22182572.72</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>957673</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>11663866.53</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>28925281</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>24439775</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>1504161748.55</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>360880000</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>44498190.03</v>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>8739413.83</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>463531.04</v>
+      </c>
+      <c r="N14" s="9" t="n">
+        <v>3398429.19</v>
+      </c>
+      <c r="O14" s="9" t="n">
+        <v>8427781.550000001</v>
+      </c>
+      <c r="P14" s="9" t="n">
+        <v>11851028.97</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>438258374.61</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1220000000</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>131352520.44</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>19980748.26</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>839703</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>15012128.02</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>31735376</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>24750783</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>1443671258.72</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>338672000</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>47657304.2</v>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>6578982.54</v>
+      </c>
+      <c r="M15" s="9" t="n">
+        <v>401500.01</v>
+      </c>
+      <c r="N15" s="9" t="n">
+        <v>4351229.76</v>
+      </c>
+      <c r="O15" s="9" t="n">
+        <v>9198423.59</v>
+      </c>
+      <c r="P15" s="9" t="n">
+        <v>11585255.98</v>
+      </c>
+      <c r="Q15" s="9" t="n">
+        <v>418444696.08</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1200000000</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>123254387.3</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>21714770.99</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1294705</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>13855386.15</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>29755699</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>13982284</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>1403857232.44</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>333120000</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>45100146.59</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>6848767.95</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>598777.14</v>
+      </c>
+      <c r="N16" s="9" t="n">
+        <v>3990201.72</v>
+      </c>
+      <c r="O16" s="9" t="n">
+        <v>8569320.26</v>
+      </c>
+      <c r="P16" s="9" t="n">
+        <v>6068522.46</v>
+      </c>
+      <c r="Q16" s="9" t="n">
+        <v>404295736.12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>135734087.98</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>26328429.67</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>2039246</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>17116844.44</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>38789476</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>23809525</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>1743817609.09</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>416400000</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>49047089.99</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>8232801.42</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>899431.51</v>
+      </c>
+      <c r="N17" s="9" t="n">
+        <v>4926149.54</v>
+      </c>
+      <c r="O17" s="9" t="n">
+        <v>11163433.78</v>
+      </c>
+      <c r="P17" s="9" t="n">
+        <v>11193826.09</v>
+      </c>
+      <c r="Q17" s="9" t="n">
+        <v>501862732.34</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1400000000</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>147219414.75</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>20291070.01</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1359591</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>14195115.2</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>45793344</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>24504254</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>1653362788.96</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>388640000</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>57064827.84</v>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>5253664.07</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>644960.33</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <v>4126757.68</v>
+      </c>
+      <c r="O18" s="9" t="n">
+        <v>13312891.88</v>
+      </c>
+      <c r="P18" s="9" t="n">
+        <v>11617145.57</v>
+      </c>
+      <c r="Q18" s="9" t="n">
+        <v>480660247.37</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>926400000</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>101346609.5</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>17248459.41</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1210622</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>11337468.16</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>19897635</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>11943453</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>1089384247.07</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>257168640</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>37038769.64</v>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>6582665.07</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>587784.12</v>
+      </c>
+      <c r="N19" s="9" t="n">
+        <v>3288970.22</v>
+      </c>
+      <c r="O19" s="9" t="n">
+        <v>5772252.5</v>
+      </c>
+      <c r="P19" s="9" t="n">
+        <v>5588473.52</v>
+      </c>
+      <c r="Q19" s="9" t="n">
+        <v>316027555.06</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1160000000</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>105672875.16</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>20729166.99</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>557181</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>12627740.01</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>25712157</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>14893199</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>1340192319.16</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>322016000</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>38155857.92</v>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>7373273.33</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>262338.04</v>
+      </c>
+      <c r="N20" s="9" t="n">
+        <v>3635012.06</v>
+      </c>
+      <c r="O20" s="9" t="n">
+        <v>7401482.81</v>
+      </c>
+      <c r="P20" s="9" t="n">
+        <v>6942822.13</v>
+      </c>
+      <c r="Q20" s="9" t="n">
+        <v>385786786.29</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>1370000000</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>124084423.03</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>23043283.69</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1450093</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>15105978.17</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>32106553</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>21675050</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>1587465380.89</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>380312000</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>44959266.73</v>
+      </c>
+      <c r="L21" s="9" t="n">
+        <v>7699311.71</v>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>691813.04</v>
+      </c>
+      <c r="N21" s="9" t="n">
+        <v>4356201.81</v>
+      </c>
+      <c r="O21" s="9" t="n">
+        <v>9258759.859999999</v>
+      </c>
+      <c r="P21" s="9" t="n">
+        <v>10509589.79</v>
+      </c>
+      <c r="Q21" s="9" t="n">
+        <v>457786942.94</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1190000000</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>133614522.35</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>19460265.91</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>895848</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>13770677.81</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>32240466</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>25089021</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>1415070801.07</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>330344000</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>44531856.81</v>
+      </c>
+      <c r="L22" s="9" t="n">
+        <v>5997303.28</v>
+      </c>
+      <c r="M22" s="9" t="n">
+        <v>426029.96</v>
+      </c>
+      <c r="N22" s="9" t="n">
+        <v>3953306.49</v>
+      </c>
+      <c r="O22" s="9" t="n">
+        <v>9255640.52</v>
+      </c>
+      <c r="P22" s="9" t="n">
+        <v>11732475.1</v>
+      </c>
+      <c r="Q22" s="9" t="n">
+        <v>406240612.16</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>1260000000</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>119176847.25</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>22591885.42</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1198992</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>16590934.97</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>28572335</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>9902841</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>1458033835.64</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>349776000</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>35238750.52</v>
+      </c>
+      <c r="L23" s="9" t="n">
+        <v>9390952.41</v>
+      </c>
+      <c r="M23" s="9" t="n">
+        <v>577229.27</v>
+      </c>
+      <c r="N23" s="9" t="n">
+        <v>4682007.62</v>
+      </c>
+      <c r="O23" s="9" t="n">
+        <v>8063191.77</v>
+      </c>
+      <c r="P23" s="9" t="n">
+        <v>3733039.67</v>
+      </c>
+      <c r="Q23" s="9" t="n">
+        <v>411461171.27</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1680000000</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>147197041.73</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>34454101.03</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>1122513</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>25849266.6</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>44528557</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>21274756</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>1954426235.36</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>466368000</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>43368591.4</v>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>11415691.98</v>
+      </c>
+      <c r="M24" s="9" t="n">
+        <v>545961.96</v>
+      </c>
+      <c r="N24" s="9" t="n">
+        <v>7290541.98</v>
+      </c>
+      <c r="O24" s="9" t="n">
+        <v>12558859.76</v>
+      </c>
+      <c r="P24" s="9" t="n">
+        <v>9679849.300000001</v>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>551227496.37</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>1480000000</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>145329668.29</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>25659770.52</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>1532660</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>16408150.57</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>44263912</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>21410910</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>1734605071.38</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>410848000</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>45347988.13</v>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>8441476.460000001</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>678289.72</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>4660735.14</v>
+      </c>
+      <c r="O25" s="9" t="n">
+        <v>12573164.11</v>
+      </c>
+      <c r="P25" s="9" t="n">
+        <v>10164913.41</v>
+      </c>
+      <c r="Q25" s="9" t="n">
+        <v>492714566.97</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>1120000000</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>98117953.89</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>21651553.57</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>525316</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>13798244.33</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>25729394</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>12004100</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>1291826561.79</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>310912000</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>31546614.61</v>
+      </c>
+      <c r="L26" s="9" t="n">
+        <v>6064427.21</v>
+      </c>
+      <c r="M26" s="9" t="n">
+        <v>240533.84</v>
+      </c>
+      <c r="N26" s="9" t="n">
+        <v>3901201.2</v>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>7274515.54</v>
+      </c>
+      <c r="P26" s="9" t="n">
+        <v>5301039.25</v>
+      </c>
+      <c r="Q26" s="9" t="n">
+        <v>365240331.65</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1320000000</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>122647932.15</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>25712632.31</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>689662</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>12631632.8</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>31326910</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>16941298</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>1529950067.26</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>366432000</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>38758367.74</v>
+      </c>
+      <c r="L27" s="9" t="n">
+        <v>7634695.65</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>345067.73</v>
+      </c>
+      <c r="N27" s="9" t="n">
+        <v>3577476.75</v>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>8872272.810000001</v>
+      </c>
+      <c r="P27" s="9" t="n">
+        <v>7686001.99</v>
+      </c>
+      <c r="Q27" s="9" t="n">
+        <v>433305882.68</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1420000000</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>146914840.72</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>26242191.02</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>2557592</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>11278878.58</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>38474611</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>23226558</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>1668694671.32</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>394192000</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>47966998.93</v>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>9260973.609999999</v>
+      </c>
+      <c r="M28" s="9" t="n">
+        <v>1170559.87</v>
+      </c>
+      <c r="N28" s="9" t="n">
+        <v>3227798.28</v>
+      </c>
+      <c r="O28" s="9" t="n">
+        <v>11010694.22</v>
+      </c>
+      <c r="P28" s="9" t="n">
+        <v>10719319.3</v>
+      </c>
+      <c r="Q28" s="9" t="n">
+        <v>477548344.21</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>1190000000</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>111275220.48</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>18973251.97</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>9547705</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>12827436.18</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>30358401</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>23537141</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>1396519155.63</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>330344000</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>33561811.06</v>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>6610438.95</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>3504492.28</v>
+      </c>
+      <c r="N29" s="9" t="n">
+        <v>3640235.79</v>
+      </c>
+      <c r="O29" s="9" t="n">
+        <v>8615263.130000001</v>
+      </c>
+      <c r="P29" s="9" t="n">
+        <v>10035145.32</v>
+      </c>
+      <c r="Q29" s="9" t="n">
+        <v>396311386.54</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>1490000000</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>98118727.63</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>28162072.11</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>14809135</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>18367442.31</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>21799182</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>15601449</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>1686858008.05</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>413624000</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>30240724.05</v>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>9490626.810000001</v>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>5547393.25</v>
+      </c>
+      <c r="N30" s="9" t="n">
+        <v>5188369.11</v>
+      </c>
+      <c r="O30" s="9" t="n">
+        <v>6157754.61</v>
+      </c>
+      <c r="P30" s="9" t="n">
+        <v>6248721.69</v>
+      </c>
+      <c r="Q30" s="9" t="n">
+        <v>476497589.52</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>1930000000</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>165005629.65</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>34918943.24</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>28273980</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>18842311.25</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>29109748</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>26623498</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>2232774110.14</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>535768000</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>46829617.02</v>
+      </c>
+      <c r="L31" s="9" t="n">
+        <v>11632838.68</v>
+      </c>
+      <c r="M31" s="9" t="n">
+        <v>10477277.08</v>
+      </c>
+      <c r="N31" s="9" t="n">
+        <v>5320843.96</v>
+      </c>
+      <c r="O31" s="9" t="n">
+        <v>8220245.64</v>
+      </c>
+      <c r="P31" s="9" t="n">
+        <v>12259956.04</v>
+      </c>
+      <c r="Q31" s="9" t="n">
+        <v>630508778.4299999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>1700000000</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>153283200.98</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>25897044.82</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>4910082</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>13252847.35</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>33872270</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>31086830</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>1962302275.15</v>
+      </c>
+      <c r="J32" s="8" t="n">
+        <v>471920000</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>46033156.99</v>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>7924109.45</v>
+      </c>
+      <c r="M32" s="9" t="n">
+        <v>1721674.99</v>
+      </c>
+      <c r="N32" s="9" t="n">
+        <v>3750171.98</v>
+      </c>
+      <c r="O32" s="9" t="n">
+        <v>9584871.42</v>
+      </c>
+      <c r="P32" s="9" t="n">
+        <v>14340728.19</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>555274713.02</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>1400000000</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>113668391.39</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>24833122.69</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>15463</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>7051751.21</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>32256260</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>11845545</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>1589670533.29</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>388640000</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>36835334.14</v>
+      </c>
+      <c r="L33" s="9" t="n">
+        <v>8164954.36</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>7580.34</v>
+      </c>
+      <c r="N33" s="9" t="n">
+        <v>1997237.73</v>
+      </c>
+      <c r="O33" s="9" t="n">
+        <v>9135804.35</v>
+      </c>
+      <c r="P33" s="9" t="n">
+        <v>5454763.56</v>
+      </c>
+      <c r="Q33" s="9" t="n">
+        <v>450235674.48</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>1520000000</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>111712158.6</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>30033982.35</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>17941206</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>5769286.27</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>42760798</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>19024989</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>1747242420.22</v>
+      </c>
+      <c r="J34" s="8" t="n">
+        <v>421952000</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>33675810.27</v>
+      </c>
+      <c r="L34" s="9" t="n">
+        <v>8422284.43</v>
+      </c>
+      <c r="M34" s="9" t="n">
+        <v>7000711.88</v>
+      </c>
+      <c r="N34" s="9" t="n">
+        <v>1629230.19</v>
+      </c>
+      <c r="O34" s="9" t="n">
+        <v>12075528.88</v>
+      </c>
+      <c r="P34" s="9" t="n">
+        <v>8660771.18</v>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>493416336.83</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>1580000000</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>133200326.87</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>26868942.32</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>21144810</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>9396009.67</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>30959003</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>25133206</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>1826702297.86</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>438608000</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>39150985.29</v>
+      </c>
+      <c r="L35" s="9" t="n">
+        <v>6948205.54</v>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>7686788.4</v>
+      </c>
+      <c r="N35" s="9" t="n">
+        <v>2654002.85</v>
+      </c>
+      <c r="O35" s="9" t="n">
+        <v>8744699.619999999</v>
+      </c>
+      <c r="P35" s="9" t="n">
+        <v>12178807.65</v>
+      </c>
+      <c r="Q35" s="9" t="n">
+        <v>515971489.35</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>1540000000</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>148468892.52</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>27279175.53</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>24810710</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>10391420.59</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>31438450.5</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>28258944</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>1810647593.14</v>
+      </c>
+      <c r="J36" s="8" t="n">
+        <v>427504000</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>47297561.25</v>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>9261586.119999999</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>8799940.630000001</v>
+      </c>
+      <c r="N36" s="9" t="n">
+        <v>2976367.39</v>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>9004772.539999999</v>
+      </c>
+      <c r="P36" s="9" t="n">
+        <v>13771335.88</v>
+      </c>
+      <c r="Q36" s="9" t="n">
+        <v>518615563.81</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1523154175.75</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>162404936.11</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>32818984.23</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>20593115</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>10350317.52</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>38546740</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>14064111</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>1801932379.61</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>422827599.19</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>50100849.41</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>10372615.86</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>7004156.33</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>2931559.34</v>
+      </c>
+      <c r="O37" s="9" t="n">
+        <v>10917738.06</v>
+      </c>
+      <c r="P37" s="9" t="n">
+        <v>6213562.76</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>510368080.94</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="6" t="n">
+        <v>173014888.85</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>50137129.16</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>52782942</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>17867253.73</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>31935868</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>21111711</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>346849792.74</v>
+      </c>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="9" t="n">
+        <v>46914612.74</v>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>18023125.75</v>
+      </c>
+      <c r="M38" s="9" t="n">
+        <v>15883449.41</v>
+      </c>
+      <c r="N38" s="9" t="n">
+        <v>5459538.21</v>
+      </c>
+      <c r="O38" s="9" t="n">
+        <v>9758359.859999999</v>
+      </c>
+      <c r="P38" s="9" t="n">
+        <v>9944728.02</v>
+      </c>
+      <c r="Q38" s="9" t="n">
+        <v>105983813.98</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="6" t="n">
+        <v>132077170.89</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>32056055.97</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>35925674</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>21673332.38</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>34863515</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>33781884</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>290377632.24</v>
+      </c>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="9" t="n">
+        <v>38188228.54</v>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>13010644.31</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>11501420.69</v>
+      </c>
+      <c r="N39" s="9" t="n">
+        <v>7315628</v>
+      </c>
+      <c r="O39" s="9" t="n">
+        <v>11767849.17</v>
+      </c>
+      <c r="P39" s="9" t="n">
+        <v>16230447.81</v>
+      </c>
+      <c r="Q39" s="9" t="n">
+        <v>98014218.51000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:Q39"/>
+  <mergeCells count="2">
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2728,7 +4932,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Combo / parlay share of that venue</t>
+          <t>Combo / parlay share of that venue's sports book</t>
         </is>
       </c>
     </row>
@@ -2822,7 +5026,7 @@
         <v>15122319</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5537</v>
       </c>
       <c r="I3" s="11" t="n"/>
       <c r="J3" s="11" t="n">
@@ -2861,7 +5065,7 @@
         <v>13414300</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5855</v>
       </c>
       <c r="I4" s="11" t="n"/>
       <c r="J4" s="11" t="n">
@@ -2900,7 +5104,7 @@
         <v>5593903</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5191</v>
       </c>
       <c r="I5" s="11" t="n"/>
       <c r="J5" s="11" t="n">
@@ -2941,7 +5145,7 @@
         <v>10388004</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5629</v>
       </c>
       <c r="I6" s="11" t="n">
         <v>0.3931</v>
@@ -2984,7 +5188,7 @@
         <v>11554341</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5704</v>
       </c>
       <c r="I7" s="11" t="n">
         <v>0.3082</v>
@@ -3027,7 +5231,7 @@
         <v>11900005</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5618</v>
       </c>
       <c r="I8" s="11" t="n">
         <v>0.3006</v>
@@ -3070,7 +5274,7 @@
         <v>9881154</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5807</v>
       </c>
       <c r="I9" s="11" t="n">
         <v>0.3517</v>
@@ -3113,7 +5317,7 @@
         <v>12561820</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5789</v>
       </c>
       <c r="I10" s="11" t="n">
         <v>0.3298</v>
@@ -3156,7 +5360,7 @@
         <v>12447288</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5864</v>
       </c>
       <c r="I11" s="11" t="n">
         <v>0.3287</v>
@@ -3199,7 +5403,7 @@
         <v>5158036</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6043999999999999</v>
       </c>
       <c r="I12" s="11" t="n">
         <v>0.3621</v>
@@ -3242,7 +5446,7 @@
         <v>9937864</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5853</v>
       </c>
       <c r="I13" s="11" t="n">
         <v>0.3335</v>
@@ -3285,7 +5489,7 @@
         <v>11483868</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6004</v>
       </c>
       <c r="I14" s="11" t="n">
         <v>0.3297</v>
@@ -3328,7 +5532,7 @@
         <v>11876717</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5614</v>
       </c>
       <c r="I15" s="11" t="n">
         <v>0.3308</v>
@@ -3371,7 +5575,7 @@
         <v>10105691</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5629</v>
       </c>
       <c r="I16" s="11" t="n">
         <v>0.3907</v>
@@ -3414,7 +5618,7 @@
         <v>15529922</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5665</v>
       </c>
       <c r="I17" s="11" t="n">
         <v>0.3994</v>
@@ -3457,7 +5661,7 @@
         <v>16183161</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6003000000000001</v>
       </c>
       <c r="I18" s="11" t="n">
         <v>0.3354</v>
@@ -3500,7 +5704,7 @@
         <v>5512796</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5716</v>
       </c>
       <c r="I19" s="11" t="n">
         <v>0.3486</v>
@@ -3543,7 +5747,7 @@
         <v>9370589</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6038</v>
       </c>
       <c r="I20" s="11" t="n">
         <v>0.344</v>
@@ -3586,7 +5790,7 @@
         <v>12363246</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6002000000000001</v>
       </c>
       <c r="I21" s="11" t="n">
         <v>0.3256</v>
@@ -3629,7 +5833,7 @@
         <v>9845111</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5922999999999999</v>
       </c>
       <c r="I22" s="11" t="n">
         <v>0.2813</v>
@@ -3672,7 +5876,7 @@
         <v>9562382</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6049</v>
       </c>
       <c r="I23" s="11" t="n">
         <v>0.3146</v>
@@ -3715,7 +5919,7 @@
         <v>16160186</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.5939</v>
       </c>
       <c r="I24" s="11" t="n">
         <v>0.3856</v>
@@ -3758,7 +5962,7 @@
         <v>15568073</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6161</v>
       </c>
       <c r="I25" s="11" t="n">
         <v>0.3765</v>
@@ -3801,7 +6005,7 @@
         <v>7232750</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6198</v>
       </c>
       <c r="I26" s="11" t="n">
         <v>0.3647</v>
@@ -3844,7 +6048,7 @@
         <v>11383349</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6343</v>
       </c>
       <c r="I27" s="11" t="n">
         <v>0.3861</v>
@@ -3887,7 +6091,7 @@
         <v>13381960</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6183</v>
       </c>
       <c r="I28" s="11" t="n">
         <v>0.3211</v>
@@ -3930,7 +6134,7 @@
         <v>9008514</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="I29" s="11" t="n">
         <v>0.3433</v>
@@ -3973,7 +6177,7 @@
         <v>7506867</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6175</v>
       </c>
       <c r="I30" s="11" t="n">
         <v>0.3898</v>
@@ -4016,7 +6220,7 @@
         <v>11160815</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6455</v>
       </c>
       <c r="I31" s="11" t="n">
         <v>0.3762</v>
@@ -4059,7 +6263,7 @@
         <v>12728635</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6204</v>
       </c>
       <c r="I32" s="11" t="n">
         <v>0.3658</v>
@@ -4102,7 +6306,7 @@
         <v>9774024</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6148</v>
       </c>
       <c r="I33" s="11" t="n">
         <v>0.4301</v>
@@ -4145,7 +6349,7 @@
         <v>12995978</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6411</v>
       </c>
       <c r="I34" s="11" t="n">
         <v>0.474</v>
@@ -4188,7 +6392,7 @@
         <v>10158090</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6381</v>
       </c>
       <c r="I35" s="11" t="n">
         <v>0.4234000000000001</v>
@@ -4231,7 +6435,7 @@
         <v>8471978</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6048</v>
       </c>
       <c r="I36" s="11" t="n">
         <v>0.3584000000000001</v>
@@ -4256,7 +6460,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>828788847.17</v>
+        <v>733490124.87</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>12490106.43</v>
@@ -4274,7 +6478,7 @@
         <v>11868618</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>0.4816</v>
+        <v>0.6257</v>
       </c>
       <c r="I37" s="11" t="n">
         <v>0.3806</v>
@@ -4298,9 +6502,7 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B38" s="6" t="n">
-        <v>1128108281.21</v>
-      </c>
+      <c r="B38" s="6" t="n"/>
       <c r="C38" s="6" t="n">
         <v>18169819.03</v>
       </c>
@@ -4316,9 +6518,7 @@
       <c r="G38" s="6" t="n">
         <v>10824093</v>
       </c>
-      <c r="H38" s="11" t="n">
-        <v>0.4816</v>
-      </c>
+      <c r="H38" s="11" t="n"/>
       <c r="I38" s="11" t="n">
         <v>0.3624</v>
       </c>
@@ -4335,15 +6535,54 @@
         <v>0.3572</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>Kalshi = its KXMVE multi-event parlay engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample of the public feed scaled to the daily total. Its % is of its WHOLE-EXCHANGE volume (matching its main column) - ~48% by contracts / ~11% by $. Sample-based, so it moves less day to day; not folded into the Daily tab's blended Combo %. Rothera runs no on-exchange parlay product and is omitted here.</t>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n">
+        <v>10625376.42</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>15329162</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>40590069.68</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>13770949.4</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>12319196</v>
+      </c>
+      <c r="H39" s="11" t="n"/>
+      <c r="I39" s="11" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="J39" s="11" t="n">
+        <v>0.4267</v>
+      </c>
+      <c r="K39" s="11" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="L39" s="11" t="n">
+        <v>0.6354</v>
+      </c>
+      <c r="M39" s="11" t="n">
+        <v>0.3801</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M38"/>
+  <autoFilter ref="A2:M39"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -4352,29 +6591,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="92" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>Sports prediction-market volume - daily</t>
+          <t>US prediction-market volume - daily, 7 regulated exchanges</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-06 from unified_sports_volume.csv</t>
+          <t>Generated 2026-09-07. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>
@@ -4384,101 +6623,97 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>One comparable metric for all seven venues: contracts traded, one-sided</t>
+          <t>One comparable metric: contracts traded, one-sided (a buy matched with a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(a buy matched with a sell counts once), each contract a $1-max-payout</t>
+          <t>sell counts once), each a $1-max-payout instrument. 'Notional $' re-weights</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>instrument. 'Notional $' re-weights each contract by its traded price</t>
+          <t>each contract by its traded price (~ the dollars that changed hands).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>(~ the dollars that changed hands, roughly 1/3 of the contract count).</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>TAB 'Sports volume'  - each venue's sports book only. Apples-to-apples on sports.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kalshi   = WHOLE exchange, every category (daily total from DeFi Rate; the</t>
+          <t xml:space="preserve">  Kalshi = single-leg sports + its sports parlay engine.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">           last ~2-3 days are projected - see the 'source' column upstream).</t>
+          <t xml:space="preserve">  Polymarket US / Crypto.com / Rothera = sports filtered out of a wider book.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Polymarket US = sports, symbol-prefix filtered.</t>
+          <t xml:space="preserve">  Novig / DKeX / UDX = sports-only exchanges (their sports IS their whole book).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Novig / DKeX / UDX = 100% sports, from their CFTC Part-16 daily reports.</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Crypto.com = Nadex / CDNA 'EVENTS' book - Crypto.com's own prediction market</t>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TAB 'Total exchange'  - each venue's WHOLE book, every category (sports, crypto,</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">           plus FanDuel Predicts (all its sports flow clears there), minus a</t>
+          <t xml:space="preserve">  politics, economics, ...). Apples-to-apples on total platform activity.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">           ~0.2% non-sports tail. Notional $ uses the cross-venue avg price.</t>
+          <t xml:space="preserve">  Kalshi total from DeFi Rate (last ~2 days projected). Polymarket = all QCX.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rothera  = the CFTC exchange behind Robinhood's prediction market (Part-16</t>
+          <t xml:space="preserve">  Crypto.com = the whole Nadex/CDNA book (events + fx/commodity/crypto binaries).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">           daily report). Prefix-filtered to sports (MLB-heavy); a small</t>
+          <t xml:space="preserve">  Rothera = sports + its US-macro / elections markets.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">           US-macro / elections tail is dropped.</t>
+          <t xml:space="preserve">  Novig / DKeX / UDX total == their sports figure (sports-only exchanges).</t>
         </is>
       </c>
     </row>
@@ -4486,75 +6721,26 @@
       <c r="A19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Combos: tracked per-venue on the 'Parlay share' tab. Novig / DKeX /</t>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>TAB 'Parlay share'  - per-venue combo/parlay volume and % of that venue's sports book.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Polymarket US / UDX / Crypto.com from their combo product line</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">        (% of that venue's book). Kalshi = its KXMVE multi-event parlay</t>
+          <t>UDX and Crypto.com have no usable price column - their Notional $ is estimated</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">        engine (leg-checked ~100% sports legs), from a ~3M-trade sample</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        scaled to the daily total, as a % of its WHOLE-EXCHANGE volume</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        (matching its main column) - ~48% by contracts / ~11% by $. The</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Daily tab's blended Combo % is the five report-based venues only;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Rothera has no on-exchange parlay product.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>All seven US CFTC sports-prediction venues are covered.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>with the day's contract-weighted average price across the venues that report one.</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226348301.09</v>
+        <v>1226349065.69</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404310395.67</v>
+        <v>1404311160.27</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290712233.4</v>
+        <v>290712357.9</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524812.1800000001</v>
+        <v>524812.08</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360273.49</v>
+        <v>9360271.630000001</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354055225.7</v>
+        <v>354055348.24</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019790521.49</v>
+        <v>1019791784.21</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203195431</v>
+        <v>1203196693.72</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223745816.63</v>
+        <v>223745991.8</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516298.92</v>
+        <v>516298.68</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237390.460000001</v>
+        <v>9237386.220000001</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289057611.79</v>
+        <v>289057782.49</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766399762</v>
+        <v>766400758.2</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882442309.04</v>
+        <v>882443305.24</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197400001.9</v>
+        <v>197400445.99</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374709.28</v>
+        <v>374709.56</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399343.04</v>
+        <v>5399347.05</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239489336.6</v>
+        <v>239489784.98</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983748421.3200001</v>
+        <v>983749291.22</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168386570.34</v>
+        <v>1168387440.24</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236058435.39</v>
+        <v>236058651.18</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324586.19</v>
+        <v>324586.17</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358489.61</v>
+        <v>7358489.32</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305855095.76</v>
+        <v>305855311.24</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097580318.95</v>
+        <v>1097584373.29</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302660356.53</v>
+        <v>1302664410.87</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250948122.31</v>
+        <v>250949776.33</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709925.6800000001</v>
+        <v>709927.08</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693337.29</v>
+        <v>7693352.53</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328052116.54</v>
+        <v>328053787.2</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011514178.87</v>
+        <v>1011515724.09</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233687298.38</v>
+        <v>1233688843.6</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229522489.57</v>
+        <v>229523163.57</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255741.5</v>
+        <v>1255742.7</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409716.380000001</v>
+        <v>8409724.43</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309197404.1</v>
+        <v>309198087.35</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961933487.02</v>
+        <v>961934760.5599999</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145540648.56</v>
+        <v>1145541922.1</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214888229.88</v>
+        <v>214888631.7</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814778.05</v>
+        <v>814778.3199999999</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850540.39</v>
+        <v>6850542.63</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281205393.52</v>
+        <v>281205797.84</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073038713.76</v>
+        <v>1073041912.66</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277704611.24</v>
+        <v>1277707810.14</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240123237.17</v>
+        <v>240123982.18</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353400.13</v>
+        <v>2353399.81</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569915.52</v>
+        <v>7569914.51</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313747030.7</v>
+        <v>313747774.39</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960754930.92</v>
+        <v>960755772.36</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185428248.04</v>
+        <v>1185429089.48</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212543726.02</v>
+        <v>212543924.4</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490144.51</v>
+        <v>2490144.41</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929257.99</v>
+        <v>8929257.619999999</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296178469.23</v>
+        <v>296178667.13</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686488587.74</v>
+        <v>686491037.87</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813400278.77</v>
+        <v>813402728.9</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150986874.89</v>
+        <v>150987576.69</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897060.47</v>
+        <v>1897061.57</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485519.72</v>
+        <v>3485521.74</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196251414.98</v>
+        <v>196252119.9</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970895177.89</v>
+        <v>970898610.01</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130451832.13</v>
+        <v>1130455264.25</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227536176.85</v>
+        <v>227537789.85</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642012.55</v>
+        <v>2642019.6</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513093.35</v>
+        <v>5513108.06</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286533831.19</v>
+        <v>286535465.96</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042720983.61</v>
+        <v>1042722691.8</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244205173.68</v>
+        <v>1244206881.87</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230879117.13</v>
+        <v>230880141.16</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865649.45</v>
+        <v>2865655.3</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026032.49</v>
+        <v>7026046.84</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305683870.5</v>
+        <v>305684914.74</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046511668.87</v>
+        <v>1046512903.29</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268558768.68</v>
+        <v>1268560003.1</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238375725.51</v>
+        <v>238375967.85</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737679.55</v>
+        <v>3737678.75</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838233.09</v>
+        <v>7838231.42</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315842374.95</v>
+        <v>315842614.82</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026507894.75</v>
+        <v>1026509230.11</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228651773.78</v>
+        <v>1228653109.14</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246149823.25</v>
+        <v>246150132.87</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558650.45</v>
+        <v>3558650.06</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537326.75</v>
+        <v>7537325.92</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315569854.61</v>
+        <v>315570163.01</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275197725.87</v>
+        <v>1275202312.3</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517919203.12</v>
+        <v>1517923789.55</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295667968.4</v>
+        <v>295668395.47</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271142.9</v>
+        <v>4271134.51</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581206.310000001</v>
+        <v>9581187.48</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378764313.5</v>
+        <v>378764713.34</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123162110.77</v>
+        <v>1123165604.25</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375337272.1</v>
+        <v>1375340765.58</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251871816.77</v>
+        <v>251873332.44</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520463.22</v>
+        <v>3520470.22</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255639.31</v>
+        <v>11255661.71</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341090876.14</v>
+        <v>341092421.21</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780468036.02</v>
+        <v>780472551.89</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941884881.55</v>
+        <v>941889397.42</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182876983.93</v>
+        <v>182878296.39</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893225.33</v>
+        <v>2893227.32</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978949.19</v>
+        <v>4978952.62</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240361001.38</v>
+        <v>240362319.26</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925190752.63</v>
+        <v>925196477.27</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103194136.45</v>
+        <v>1103199861.09</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208930058.54</v>
+        <v>208931948.3</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099127.65</v>
+        <v>3099133.4</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218628.53</v>
+        <v>6218640.06</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270748324.73</v>
+        <v>270750231.77</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099235509.23</v>
+        <v>1099239543.2</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314535803.05</v>
+        <v>1314539837.02</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244612818.63</v>
+        <v>244614998.21</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671151</v>
+        <v>3671165.29</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710470.83</v>
+        <v>7710500.84</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319466861.16</v>
+        <v>319469085.04</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967567863.75</v>
+        <v>967573101.1799999</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190888869.33</v>
+        <v>1190894106.76</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210526920.69</v>
+        <v>210527933.59</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281796.18</v>
+        <v>3281793.35</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536291.6</v>
+        <v>7536285.11</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283809889.14</v>
+        <v>283810892.72</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003048142.35</v>
+        <v>1003053368.32</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198204830.41</v>
+        <v>1198210056.38</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222078381.47</v>
+        <v>222081575.1</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3890999.55</v>
+        <v>3891027.83</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335872.31</v>
+        <v>6335918.36</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281009748.26</v>
+        <v>281013016.22</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362246646.22</v>
+        <v>1362253416.36</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634463401.34</v>
+        <v>1634470171.48</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306752950.06</v>
+        <v>306754734.38</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136465.49</v>
+        <v>6136468.41</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270554.21</v>
+        <v>10270559.1</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388012101.25</v>
+        <v>388013893.39</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156848829.83</v>
+        <v>1156855385.09</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409348797.48</v>
+        <v>1409355352.74</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247783486.21</v>
+        <v>247785242.3</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795191.26</v>
+        <v>3795194.18</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929275.09</v>
+        <v>9929282.720000001</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325981177.34</v>
+        <v>325982943.97</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870234303.1799999</v>
+        <v>870241470.6900001</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039338515.55</v>
+        <v>1039345683.06</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193417623.28</v>
+        <v>193419842.54</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256064.62</v>
+        <v>3256071.89</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684208.02</v>
+        <v>5684220.72</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245259707.55</v>
+        <v>245261946.78</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002162415.6</v>
+        <v>1002174640.46</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209499823.56</v>
+        <v>1209512048.42</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>216979327.6</v>
+        <v>216983860.91</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934170.27</v>
+        <v>2934188.6</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937774.34</v>
+        <v>6937817.69</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280951677.29</v>
+        <v>280956272.28</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105872460</v>
+        <v>1105897442.3</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351727359.65</v>
+        <v>1351752341.95</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242452076.24</v>
+        <v>242461169.05</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693171.11</v>
+        <v>2693198.16</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8763790.130000001</v>
+        <v>8763878.17</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322765516.48</v>
+        <v>322774724.38</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932777126.6900001</v>
+        <v>932792254.42</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136724941.14</v>
+        <v>1136740068.87</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196501497.97</v>
+        <v>196507493.81</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927838.11</v>
+        <v>2927867.9</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577645.92</v>
+        <v>6577712.84</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259455323.36</v>
+        <v>259461415.9</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1161937950.78</v>
+        <v>1161965591.17</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354774434.85</v>
+        <v>1354802075.24</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252320947.82</v>
+        <v>252334221.71</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229055.32</v>
+        <v>4229151.71</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541531.32</v>
+        <v>4541634.83</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311933253.09</v>
+        <v>311946726.88</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439894997.32</v>
+        <v>1439936873.53</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1739951663.35</v>
+        <v>1739993539.56</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284684023.21</v>
+        <v>284698738.36</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4066960.53</v>
+        <v>4067023.69</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978325.02</v>
+        <v>5978417.86</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375554497.62</v>
+        <v>375569368.77</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319471126.18</v>
+        <v>1319619795.01</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579234210.3</v>
+        <v>1579382879.13</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283287864.82</v>
+        <v>283347224.81</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050704.66</v>
+        <v>3050921.86</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7437769.93</v>
+        <v>7438299.47</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363527703.93</v>
+        <v>363587810.66</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096650095.4</v>
+        <v>1096905074.29</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1282691121.51</v>
+        <v>1282946100.4</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243300304.72</v>
+        <v>243398809.77</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660372.72</v>
+        <v>1660590.55</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7200948.89</v>
+        <v>7201893.64</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302016517.86</v>
+        <v>302116185.49</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1141713194.51</v>
+        <v>1141995936.6</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1365604308.46</v>
+        <v>1365887050.55</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239505889.8</v>
+        <v>239622450.68</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298241.07</v>
+        <v>1298472.6</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9232363.02</v>
+        <v>9234009.52</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307296868.64</v>
+        <v>307415307.54</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192398704.86</v>
+        <v>1192713713.87</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436055711.53</v>
+        <v>1436370720.54</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253455797.87</v>
+        <v>253585262.84</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2144828.4</v>
+        <v>2145215.4</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6743602.9</v>
+        <v>6744819.69</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327808631.37</v>
+        <v>327939700.13</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226269672.23</v>
+        <v>1226786729.91</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1493609963.1</v>
+        <v>1494127020.78</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272681676.9</v>
+        <v>272903711.42</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511016.2</v>
+        <v>2511710.21</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7245924.46</v>
+        <v>7247927.12</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>360920702.24</v>
+        <v>361145433.43</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1172274619.91</v>
+        <v>1324835906.41</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1446594764.66</v>
+        <v>1599156051.16</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>244007566.85</v>
+        <v>276866413.12</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2343656.88</v>
+        <v>2332415.96</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8215141.66</v>
+        <v>8175739.23</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>327557272.18</v>
+        <v>360365475.1</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2635,7 +2635,9 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n"/>
+      <c r="B38" s="5" t="n">
+        <v>1803304137.56</v>
+      </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
       </c>
@@ -2655,9 +2657,11 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>344063062.06</v>
-      </c>
-      <c r="J38" s="8" t="n"/>
+        <v>2147367199.62</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>365996657.83</v>
+      </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
       </c>
@@ -2668,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>5461948.41</v>
+        <v>3885058.95</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>9263993.560000001</v>
+        <v>6589436.3</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>105178709.74</v>
+        <v>466923920.86</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2693,12 +2697,8 @@
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
       </c>
-      <c r="D39" s="6" t="n">
-        <v>32056055.97</v>
-      </c>
-      <c r="E39" s="6" t="n">
-        <v>35925674</v>
-      </c>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
       <c r="F39" s="6" t="n">
         <v>21673332.38</v>
       </c>
@@ -2709,36 +2709,70 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>286769786.6</v>
+        <v>218788056.63</v>
       </c>
       <c r="J39" s="8" t="n"/>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
       </c>
-      <c r="L39" s="9" t="n">
-        <v>13010644.31</v>
-      </c>
-      <c r="M39" s="9" t="n">
-        <v>11501420.69</v>
-      </c>
+      <c r="L39" s="9" t="n"/>
+      <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n">
-        <v>7323631.12</v>
+        <v>7120937.7</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>10950896.56</v>
+        <v>10647812.66</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>96902317.34999999</v>
+        <v>71884475.04000001</v>
       </c>
       <c r="R39" s="10" t="n">
-        <v>0.3654745795652588</v>
+        <v>0.3594880079566298</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n">
+        <v>19529310</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>36648697</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>56178007</v>
+      </c>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="9" t="n"/>
+      <c r="L40" s="9" t="n"/>
+      <c r="M40" s="9" t="n"/>
+      <c r="N40" s="9" t="n"/>
+      <c r="O40" s="9" t="n">
+        <v>9844830.470000001</v>
+      </c>
+      <c r="P40" s="9" t="n">
+        <v>18474805.77</v>
+      </c>
+      <c r="Q40" s="9" t="n">
+        <v>28319636.24</v>
+      </c>
+      <c r="R40" s="10" t="n">
+        <v>0.3616</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R39"/>
+  <autoFilter ref="A2:R40"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -2754,7 +2788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4740,7 +4774,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1523154175.75</v>
+        <v>1721050019.04</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>162404936.11</v>
@@ -4761,10 +4795,10 @@
         <v>14064111</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1801932379.61</v>
+        <v>1999828222.9</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>422827599.19</v>
+        <v>477763485.29</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>50100849.41</v>
@@ -4776,16 +4810,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2931559.34</v>
+        <v>2925644.45</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>10917738.06</v>
+        <v>10895709.78</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>6213562.76</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>510368080.94</v>
+        <v>565276023.87</v>
       </c>
     </row>
     <row r="38">
@@ -4794,7 +4828,9 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n"/>
+      <c r="B38" s="5" t="n">
+        <v>2342612096.54</v>
+      </c>
       <c r="C38" s="6" t="n">
         <v>173014888.85</v>
       </c>
@@ -4814,9 +4850,11 @@
         <v>21111711</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>346849792.74</v>
-      </c>
-      <c r="J38" s="8" t="n"/>
+        <v>2689461889.28</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>650309118</v>
+      </c>
       <c r="K38" s="9" t="n">
         <v>46914612.74</v>
       </c>
@@ -4827,16 +4865,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>5459538.21</v>
+        <v>5016169.45</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>9758359.859999999</v>
+        <v>8965884.060000001</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9944728.02</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>105983813.98</v>
+        <v>755057087.4299999</v>
       </c>
     </row>
     <row r="39">
@@ -4849,12 +4887,8 @@
       <c r="C39" s="6" t="n">
         <v>132077170.89</v>
       </c>
-      <c r="D39" s="6" t="n">
-        <v>32056055.97</v>
-      </c>
-      <c r="E39" s="6" t="n">
-        <v>35925674</v>
-      </c>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
       <c r="F39" s="6" t="n">
         <v>21673332.38</v>
       </c>
@@ -4865,33 +4899,64 @@
         <v>33781884</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>290377632.24</v>
+        <v>222395902.27</v>
       </c>
       <c r="J39" s="8" t="n"/>
       <c r="K39" s="9" t="n">
         <v>38188228.54</v>
       </c>
-      <c r="L39" s="9" t="n">
-        <v>13010644.31</v>
-      </c>
-      <c r="M39" s="9" t="n">
-        <v>11501420.69</v>
-      </c>
+      <c r="L39" s="9" t="n"/>
+      <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n">
-        <v>7315628</v>
+        <v>7111062.23</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>11767849.17</v>
+        <v>11438786.63</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16230447.81</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>98014218.51000001</v>
+        <v>72968525.2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n">
+        <v>21831205</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>37074913</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>58906118</v>
+      </c>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="9" t="n"/>
+      <c r="L40" s="9" t="n"/>
+      <c r="M40" s="9" t="n"/>
+      <c r="N40" s="9" t="n"/>
+      <c r="O40" s="9" t="n">
+        <v>10966998.92</v>
+      </c>
+      <c r="P40" s="9" t="n">
+        <v>18624740.64</v>
+      </c>
+      <c r="Q40" s="9" t="n">
+        <v>29591739.56</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q39"/>
+  <autoFilter ref="A2:Q40"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -4906,7 +4971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6134,7 +6199,7 @@
         <v>9008514</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.6143</v>
       </c>
       <c r="I29" s="11" t="n">
         <v>0.3433</v>
@@ -6306,7 +6371,7 @@
         <v>9774024</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.6148</v>
+        <v>0.6146</v>
       </c>
       <c r="I33" s="11" t="n">
         <v>0.4301</v>
@@ -6349,7 +6414,7 @@
         <v>12995978</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.6411</v>
+        <v>0.6409999999999999</v>
       </c>
       <c r="I34" s="11" t="n">
         <v>0.474</v>
@@ -6392,7 +6457,7 @@
         <v>10158090</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>0.6381</v>
+        <v>0.6379</v>
       </c>
       <c r="I35" s="11" t="n">
         <v>0.4234000000000001</v>
@@ -6435,7 +6500,7 @@
         <v>8471978</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>0.6048</v>
+        <v>0.6045</v>
       </c>
       <c r="I36" s="11" t="n">
         <v>0.3584000000000001</v>
@@ -6460,7 +6525,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>733490124.87</v>
+        <v>828788847.17</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>12490106.43</v>
@@ -6478,7 +6543,7 @@
         <v>11868618</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>0.6257</v>
+        <v>0.6256</v>
       </c>
       <c r="I37" s="11" t="n">
         <v>0.3806</v>
@@ -6502,7 +6567,9 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="B38" s="6" t="n"/>
+      <c r="B38" s="6" t="n">
+        <v>1128108281.21</v>
+      </c>
       <c r="C38" s="6" t="n">
         <v>18169819.03</v>
       </c>
@@ -6518,7 +6585,9 @@
       <c r="G38" s="6" t="n">
         <v>10824093</v>
       </c>
-      <c r="H38" s="11" t="n"/>
+      <c r="H38" s="11" t="n">
+        <v>0.6256</v>
+      </c>
       <c r="I38" s="11" t="n">
         <v>0.3624</v>
       </c>
@@ -6542,12 +6611,8 @@
         </is>
       </c>
       <c r="B39" s="6" t="n"/>
-      <c r="C39" s="6" t="n">
-        <v>10625376.42</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>15329162</v>
-      </c>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
       <c r="E39" s="6" t="n">
         <v>40590069.68</v>
       </c>
@@ -6558,12 +6623,8 @@
         <v>12319196</v>
       </c>
       <c r="H39" s="11" t="n"/>
-      <c r="I39" s="11" t="n">
-        <v>0.3315</v>
-      </c>
-      <c r="J39" s="11" t="n">
-        <v>0.4267</v>
-      </c>
+      <c r="I39" s="11" t="n"/>
+      <c r="J39" s="11" t="n"/>
       <c r="K39" s="11" t="n">
         <v>0.3089</v>
       </c>
@@ -6574,15 +6635,38 @@
         <v>0.3801</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n">
+        <v>7061846</v>
+      </c>
+      <c r="H40" s="11" t="n"/>
+      <c r="I40" s="11" t="n"/>
+      <c r="J40" s="11" t="n"/>
+      <c r="K40" s="11" t="n"/>
+      <c r="L40" s="11" t="n"/>
+      <c r="M40" s="11" t="n">
+        <v>0.3616</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M39"/>
+  <autoFilter ref="A2:M40"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -6613,7 +6697,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-07. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-08. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226349065.69</v>
+        <v>1226353070.77</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404311160.27</v>
+        <v>1404315165.35</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290712357.9</v>
+        <v>290712981.02</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524812.08</v>
+        <v>524811.49</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360271.630000001</v>
+        <v>9360261.119999999</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354055348.24</v>
+        <v>354055960.26</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019791784.21</v>
+        <v>1019792212.92</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203196693.72</v>
+        <v>1203197122.43</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223745991.8</v>
+        <v>223746099.06</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516298.68</v>
+        <v>516298.69</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237386.220000001</v>
+        <v>9237386.359999999</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289057782.49</v>
+        <v>289057889.9</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766400758.2</v>
+        <v>766402786.92</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882443305.24</v>
+        <v>882445333.96</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197400445.99</v>
+        <v>197400643.75</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374709.56</v>
+        <v>374708.99</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399347.05</v>
+        <v>5399338.9</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239489784.98</v>
+        <v>239489974.02</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983749291.22</v>
+        <v>983751912.77</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168387440.24</v>
+        <v>1168390061.79</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236058651.18</v>
+        <v>236059184.52</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324586.17</v>
+        <v>324586.01</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358489.32</v>
+        <v>7358485.54</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305855311.24</v>
+        <v>305855840.64</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097584373.29</v>
+        <v>1097585048.9</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302664410.87</v>
+        <v>1302665086.48</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250949776.33</v>
+        <v>250949962.1</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.08</v>
+        <v>709927.12</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693352.53</v>
+        <v>7693352.9</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328053787.2</v>
+        <v>328053973.38</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011515724.09</v>
+        <v>1011516655.42</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233688843.6</v>
+        <v>1233689774.93</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229523163.57</v>
+        <v>229523345.51</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255742.7</v>
+        <v>1255742.48</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409724.43</v>
+        <v>8409722.98</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309198087.35</v>
+        <v>309198267.63</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961934760.5599999</v>
+        <v>961936352.87</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145541922.1</v>
+        <v>1145543514.41</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214888631.7</v>
+        <v>214888992.59</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814778.3199999999</v>
+        <v>814778.23</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850542.63</v>
+        <v>6850541.87</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281205797.84</v>
+        <v>281206157.89</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073041912.66</v>
+        <v>1073042377.16</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277707810.14</v>
+        <v>1277708274.64</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240123982.18</v>
+        <v>240124122.2</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353399.81</v>
+        <v>2353400.02</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569914.51</v>
+        <v>7569915.16</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313747774.39</v>
+        <v>313747915.25</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960755772.36</v>
+        <v>960757131.67</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185429089.48</v>
+        <v>1185430448.79</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212543924.4</v>
+        <v>212544246.04</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490144.41</v>
+        <v>2490144.25</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929257.619999999</v>
+        <v>8929257.060000001</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296178667.13</v>
+        <v>296178988.05</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686491037.87</v>
+        <v>686496966.51</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813402728.9</v>
+        <v>813408657.54</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150987576.69</v>
+        <v>150989093.95</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897061.57</v>
+        <v>1897062.43</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485521.74</v>
+        <v>3485523.33</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196252119.9</v>
+        <v>196253639.61</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970898610.01</v>
+        <v>970900741.67</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130455264.25</v>
+        <v>1130457395.91</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227537789.85</v>
+        <v>227538499.62</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642019.6</v>
+        <v>2642021.21</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513108.06</v>
+        <v>5513111.42</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286535465.96</v>
+        <v>286536180.7</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042722691.8</v>
+        <v>1042724135.71</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244206881.87</v>
+        <v>1244208325.78</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230880141.16</v>
+        <v>230880571.22</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865655.3</v>
+        <v>2865656.03</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026046.84</v>
+        <v>7026048.63</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305684914.74</v>
+        <v>305685347.32</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046512903.29</v>
+        <v>1046513802.52</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268560003.1</v>
+        <v>1268560902.33</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238375967.85</v>
+        <v>238376164.75</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737678.75</v>
+        <v>3737678.42</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838231.42</v>
+        <v>7838230.72</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315842614.82</v>
+        <v>315842810.69</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026509230.11</v>
+        <v>1026509626.14</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228653109.14</v>
+        <v>1228653505.17</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246150132.87</v>
+        <v>246150307.62</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558650.06</v>
+        <v>3558650.92</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537325.92</v>
+        <v>7537327.73</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315570163.01</v>
+        <v>315570340.43</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275202312.3</v>
+        <v>1275204867.01</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517923789.55</v>
+        <v>1517926344.26</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295668395.47</v>
+        <v>295669350.26</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271134.51</v>
+        <v>4271138.22</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581187.48</v>
+        <v>9581195.810000001</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378764713.34</v>
+        <v>378765680.17</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123165604.25</v>
+        <v>1123168983.61</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375340765.58</v>
+        <v>1375344144.94</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251873332.44</v>
+        <v>251874997.72</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520470.22</v>
+        <v>3520479.15</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255661.71</v>
+        <v>11255690.24</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341092421.21</v>
+        <v>341094123.95</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780472551.89</v>
+        <v>780476664.11</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941889397.42</v>
+        <v>941893509.64</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182878296.39</v>
+        <v>182880100.72</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893227.32</v>
+        <v>2893236.72</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978952.62</v>
+        <v>4978968.78</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240362319.26</v>
+        <v>240364149.15</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925196477.27</v>
+        <v>925199775.08</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103199861.09</v>
+        <v>1103203158.9</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208931948.3</v>
+        <v>208933201.56</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099133.4</v>
+        <v>3099138.66</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218640.06</v>
+        <v>6218650.62</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270750231.77</v>
+        <v>270751500.85</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099239543.2</v>
+        <v>1099240505.37</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314539837.02</v>
+        <v>1314540799.19</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244614998.21</v>
+        <v>244615253.13</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671165.29</v>
+        <v>3671165.54</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710500.84</v>
+        <v>7710501.37</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319469085.04</v>
+        <v>319469340.74</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967573101.1799999</v>
+        <v>967574032.29</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190894106.76</v>
+        <v>1190895037.87</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210527933.59</v>
+        <v>210528248.04</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281793.35</v>
+        <v>3281794.46</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536285.11</v>
+        <v>7536287.66</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283810892.72</v>
+        <v>283811210.84</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003053368.32</v>
+        <v>1003057899.1</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198210056.38</v>
+        <v>1198214587.16</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222081575.1</v>
+        <v>222082751.86</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891027.83</v>
+        <v>3891029.47</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335918.36</v>
+        <v>6335921.03</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281013016.22</v>
+        <v>281014197.29</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362253416.36</v>
+        <v>1362263709.68</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634470171.48</v>
+        <v>1634480464.8</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306754734.38</v>
+        <v>306755630.89</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136468.41</v>
+        <v>6136442.86</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270559.1</v>
+        <v>10270516.35</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388013893.39</v>
+        <v>388014721.6</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156855385.09</v>
+        <v>1156860555.87</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409355352.74</v>
+        <v>1409360523.52</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247785242.3</v>
+        <v>247786768.7</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795194.18</v>
+        <v>3795198.19</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929282.720000001</v>
+        <v>9929293.220000001</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325982943.97</v>
+        <v>325984484.9</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870241470.6900001</v>
+        <v>870246255.6</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039345683.06</v>
+        <v>1039350467.97</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193419842.54</v>
+        <v>193421303.36</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256071.89</v>
+        <v>3256076.46</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684220.72</v>
+        <v>5684228.7</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245261946.78</v>
+        <v>245263420.15</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002174640.46</v>
+        <v>1002183197.46</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209512048.42</v>
+        <v>1209520605.42</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>216983860.91</v>
+        <v>216986369.33</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934188.6</v>
+        <v>2934194.24</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937817.69</v>
+        <v>6937831.02</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280956272.28</v>
+        <v>280958799.66</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105897442.3</v>
+        <v>1105909190.88</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351752341.95</v>
+        <v>1351764090.53</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242461169.05</v>
+        <v>242468482.61</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693198.16</v>
+        <v>2693237.16</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8763878.17</v>
+        <v>8764005.08</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322774724.38</v>
+        <v>322782203.85</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932792254.42</v>
+        <v>932799791.8</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136740068.87</v>
+        <v>1136747606.25</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196507493.81</v>
+        <v>196510120.76</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927867.9</v>
+        <v>2927878.51</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577712.84</v>
+        <v>6577736.69</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259461415.9</v>
+        <v>259464077.33</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1161965591.17</v>
+        <v>1161974488.21</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354802075.24</v>
+        <v>1354810972.28</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252334221.71</v>
+        <v>252336352.78</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229151.71</v>
+        <v>4229152.86</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541634.83</v>
+        <v>4541636.07</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311946726.88</v>
+        <v>311948860.34</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439936873.53</v>
+        <v>1439944318.71</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1739993539.56</v>
+        <v>1740000984.74</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284698738.36</v>
+        <v>284702071.79</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067023.69</v>
+        <v>4067042.9</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978417.86</v>
+        <v>5978446.1</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375569368.77</v>
+        <v>375572749.65</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319619795.01</v>
+        <v>1319636516.95</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579382879.13</v>
+        <v>1579399601.07</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283347224.81</v>
+        <v>283351526.13</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050921.86</v>
+        <v>3050925.76</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438299.47</v>
+        <v>7438308.99</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363587810.66</v>
+        <v>363592125.4</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096905074.29</v>
+        <v>1096931638.3</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1282946100.4</v>
+        <v>1282972664.41</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243398809.77</v>
+        <v>243408571.03</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660590.55</v>
+        <v>1660610.41</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7201893.64</v>
+        <v>7201979.73</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302116185.49</v>
+        <v>302126052.7</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1141995936.6</v>
+        <v>1142030728.75</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1365887050.55</v>
+        <v>1365921842.7</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239622450.68</v>
+        <v>239631865.31</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298472.6</v>
+        <v>1298479.53</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234009.52</v>
+        <v>9234058.789999999</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307415307.54</v>
+        <v>307424778.37</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192713713.87</v>
+        <v>1192752106.86</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436370720.54</v>
+        <v>1436409113.53</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253585262.84</v>
+        <v>253599282.05</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145215.4</v>
+        <v>2145250.73</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6744819.69</v>
+        <v>6744930.75</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327939700.13</v>
+        <v>327953865.73</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226786729.91</v>
+        <v>1226818236.7</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494127020.78</v>
+        <v>1494158527.57</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272903711.42</v>
+        <v>272913172.56</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511710.21</v>
+        <v>2511723.4</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7247927.12</v>
+        <v>7247965.19</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361145433.43</v>
+        <v>361154945.83</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1324835906.41</v>
+        <v>1324942127.61</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1599156051.16</v>
+        <v>1599262272.36</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>276866413.12</v>
+        <v>276886114.61</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2332415.96</v>
+        <v>2332387.72</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8175739.23</v>
+        <v>8175640.27</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>360365475.1</v>
+        <v>360385049.39</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1803304137.56</v>
+        <v>1803595209.86</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2147367199.62</v>
+        <v>2147658271.92</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>365996657.83</v>
+        <v>366053774.61</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3885058.95</v>
+        <v>3885006.41</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6589436.3</v>
+        <v>6589347.19</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>466923920.86</v>
+        <v>466980895.98</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2693,12 +2693,18 @@
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n"/>
+      <c r="B39" s="5" t="n">
+        <v>1365818247.29</v>
+      </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
       </c>
-      <c r="D39" s="6" t="n"/>
-      <c r="E39" s="6" t="n"/>
+      <c r="D39" s="6" t="n">
+        <v>32056055.97</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>35925674</v>
+      </c>
       <c r="F39" s="6" t="n">
         <v>21673332.38</v>
       </c>
@@ -2709,28 +2715,34 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>218788056.63</v>
-      </c>
-      <c r="J39" s="8" t="n"/>
+        <v>1652588033.89</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>283596356.72</v>
+      </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
       </c>
-      <c r="L39" s="9" t="n"/>
-      <c r="M39" s="9" t="n"/>
+      <c r="L39" s="9" t="n">
+        <v>13010644.31</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>11501420.69</v>
+      </c>
       <c r="N39" s="9" t="n">
-        <v>7120937.7</v>
+        <v>4911210.63</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>10647812.66</v>
+        <v>7343646.71</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>71884475.04000001</v>
+        <v>374479003.74</v>
       </c>
       <c r="R39" s="10" t="n">
-        <v>0.3594880079566298</v>
+        <v>0.3654745795652588</v>
       </c>
     </row>
     <row r="40">
@@ -2739,7 +2751,9 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n"/>
+      <c r="B40" s="5" t="n">
+        <v>796671717.37</v>
+      </c>
       <c r="C40" s="6" t="n"/>
       <c r="D40" s="6" t="n"/>
       <c r="E40" s="6" t="n"/>
@@ -2751,21 +2765,23 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>56178007</v>
-      </c>
-      <c r="J40" s="8" t="n"/>
+        <v>852849724.37</v>
+      </c>
+      <c r="J40" s="8" t="n">
+        <v>169453212.18</v>
+      </c>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
       <c r="M40" s="9" t="n"/>
       <c r="N40" s="9" t="n"/>
       <c r="O40" s="9" t="n">
-        <v>9844830.470000001</v>
+        <v>4404193.7</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>28319636.24</v>
+        <v>192332211.65</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3616</v>
@@ -4774,7 +4790,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1721050019.04</v>
+        <v>1721154057.84</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>162404936.11</v>
@@ -4795,10 +4811,10 @@
         <v>14064111</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1999828222.9</v>
+        <v>1999932261.7</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>477763485.29</v>
+        <v>477792366.46</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>50100849.41</v>
@@ -4810,16 +4826,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2925644.45</v>
+        <v>2925641.65</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>10895709.78</v>
+        <v>10895699.37</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>6213562.76</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>565276023.87</v>
+        <v>565304891.84</v>
       </c>
     </row>
     <row r="38">
@@ -4829,7 +4845,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>2342612096.54</v>
+        <v>2342944004.46</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>173014888.85</v>
@@ -4850,10 +4866,10 @@
         <v>21111711</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2689461889.28</v>
+        <v>2689793797.2</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>650309118</v>
+        <v>650401255.64</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46914612.74</v>
@@ -4865,16 +4881,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>5016169.45</v>
+        <v>5016162.38</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>8965884.060000001</v>
+        <v>8965871.42</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9944728.02</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>755057087.4299999</v>
+        <v>755149205.36</v>
       </c>
     </row>
     <row r="39">
@@ -4883,12 +4899,18 @@
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n"/>
+      <c r="B39" s="5" t="n">
+        <v>1774253810.49</v>
+      </c>
       <c r="C39" s="6" t="n">
         <v>132077170.89</v>
       </c>
-      <c r="D39" s="6" t="n"/>
-      <c r="E39" s="6" t="n"/>
+      <c r="D39" s="6" t="n">
+        <v>32056055.97</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>35925674</v>
+      </c>
       <c r="F39" s="6" t="n">
         <v>21673332.38</v>
       </c>
@@ -4899,25 +4921,31 @@
         <v>33781884</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>222395902.27</v>
-      </c>
-      <c r="J39" s="8" t="n"/>
+        <v>2064631442.73</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>492532857.79</v>
+      </c>
       <c r="K39" s="9" t="n">
         <v>38188228.54</v>
       </c>
-      <c r="L39" s="9" t="n"/>
-      <c r="M39" s="9" t="n"/>
+      <c r="L39" s="9" t="n">
+        <v>13010644.31</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>11501420.69</v>
+      </c>
       <c r="N39" s="9" t="n">
-        <v>7111062.23</v>
+        <v>6167797.35</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>11438786.63</v>
+        <v>9921459.779999999</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16230447.81</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>72968525.2</v>
+        <v>587552856.27</v>
       </c>
     </row>
     <row r="40">
@@ -4926,7 +4954,9 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n"/>
+      <c r="B40" s="5" t="n">
+        <v>1034909171.16</v>
+      </c>
       <c r="C40" s="6" t="n"/>
       <c r="D40" s="6" t="n"/>
       <c r="E40" s="6" t="n"/>
@@ -4938,21 +4968,23 @@
         <v>37074913</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>58906118</v>
-      </c>
-      <c r="J40" s="8" t="n"/>
+        <v>1093815289.16</v>
+      </c>
+      <c r="J40" s="8" t="n">
+        <v>287290785.91</v>
+      </c>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
       <c r="M40" s="9" t="n"/>
       <c r="N40" s="9" t="n"/>
       <c r="O40" s="9" t="n">
-        <v>10966998.92</v>
+        <v>6230040.79</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18624740.64</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>29591739.56</v>
+        <v>312145567.34</v>
       </c>
     </row>
   </sheetData>
@@ -6285,7 +6317,7 @@
         <v>11160815</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.6455</v>
+        <v>0.6454000000000001</v>
       </c>
       <c r="I31" s="11" t="n">
         <v>0.3762</v>
@@ -6414,7 +6446,7 @@
         <v>12995978</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.6409999999999999</v>
+        <v>0.6409</v>
       </c>
       <c r="I34" s="11" t="n">
         <v>0.474</v>
@@ -6525,7 +6557,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>828788847.17</v>
+        <v>828838948.09</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>12490106.43</v>
@@ -6568,7 +6600,7 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>1128108281.21</v>
+        <v>1128268114.79</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>18169819.03</v>
@@ -6610,9 +6642,15 @@
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="6" t="n"/>
+      <c r="B39" s="6" t="n">
+        <v>854409664.98</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>10625376.42</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>15329162</v>
+      </c>
       <c r="E39" s="6" t="n">
         <v>40590069.68</v>
       </c>
@@ -6622,9 +6660,15 @@
       <c r="G39" s="6" t="n">
         <v>12319196</v>
       </c>
-      <c r="H39" s="11" t="n"/>
-      <c r="I39" s="11" t="n"/>
-      <c r="J39" s="11" t="n"/>
+      <c r="H39" s="11" t="n">
+        <v>0.6256</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="J39" s="11" t="n">
+        <v>0.4267</v>
+      </c>
       <c r="K39" s="11" t="n">
         <v>0.3089</v>
       </c>
@@ -6641,7 +6685,9 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n"/>
+      <c r="B40" s="6" t="n">
+        <v>498370860.46</v>
+      </c>
       <c r="C40" s="6" t="n"/>
       <c r="D40" s="6" t="n"/>
       <c r="E40" s="6" t="n"/>
@@ -6649,7 +6695,9 @@
       <c r="G40" s="6" t="n">
         <v>7061846</v>
       </c>
-      <c r="H40" s="11" t="n"/>
+      <c r="H40" s="11" t="n">
+        <v>0.6256</v>
+      </c>
       <c r="I40" s="11" t="n"/>
       <c r="J40" s="11" t="n"/>
       <c r="K40" s="11" t="n"/>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226353070.77</v>
+        <v>1226353348.67</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404315165.35</v>
+        <v>1404315443.25</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290712981.02</v>
+        <v>290713047.44</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524811.49</v>
+        <v>524811.48</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360261.119999999</v>
+        <v>9360261.02</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354055960.26</v>
+        <v>354056026.57</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019792212.92</v>
+        <v>1019792252.01</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203197122.43</v>
+        <v>1203197161.52</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223746099.06</v>
+        <v>223746101.58</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516298.69</v>
+        <v>516298.68</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237386.359999999</v>
+        <v>9237386.140000001</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289057889.9</v>
+        <v>289057892.18</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766402786.92</v>
+        <v>766402797.5</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882445333.96</v>
+        <v>882445344.54</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197400643.75</v>
+        <v>197400652.42</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374708.99</v>
+        <v>374709</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399338.9</v>
+        <v>5399339.04</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239489974.02</v>
+        <v>239489982.84</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983751912.77</v>
+        <v>983752003.36</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168390061.79</v>
+        <v>1168390152.38</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236059184.52</v>
+        <v>236059264.37</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324586.01</v>
+        <v>324586.07</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358485.54</v>
+        <v>7358486.93</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305855840.64</v>
+        <v>305855921.94</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097585048.9</v>
+        <v>1097585141.3</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302665086.48</v>
+        <v>1302665178.88</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250949962.1</v>
+        <v>250949984.77</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -877,13 +877,13 @@
         <v>709927.12</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693352.9</v>
+        <v>7693352.89</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328053973.38</v>
+        <v>328053996.03</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011516655.42</v>
+        <v>1011516743.17</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233689774.93</v>
+        <v>1233689862.68</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229523345.51</v>
+        <v>229523390.53</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255742.48</v>
+        <v>1255742.58</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409722.98</v>
+        <v>8409723.630000001</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309198267.63</v>
+        <v>309198313.4</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961936352.87</v>
+        <v>961936856.71</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145543514.41</v>
+        <v>1145544018.25</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214888992.59</v>
+        <v>214889140.39</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814778.23</v>
+        <v>814778.3</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850541.87</v>
+        <v>6850542.48</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281206157.89</v>
+        <v>281206306.37</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073042377.16</v>
+        <v>1073042410.25</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277708274.64</v>
+        <v>1277708307.73</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240124122.2</v>
+        <v>240124138.25</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353400.02</v>
+        <v>2353400.08</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569915.16</v>
+        <v>7569915.36</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313747915.25</v>
+        <v>313747931.56</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960757131.67</v>
+        <v>960757189.34</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185430448.79</v>
+        <v>1185430506.46</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212544246.04</v>
+        <v>212544272.79</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490144.25</v>
+        <v>2490144.36</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929257.060000001</v>
+        <v>8929257.439999999</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296178988.05</v>
+        <v>296179015.3</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686496966.51</v>
+        <v>686497250.42</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813408657.54</v>
+        <v>813408941.45</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150989093.95</v>
+        <v>150989214.29</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897062.43</v>
+        <v>1897062.95</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485523.33</v>
+        <v>3485524.27</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196253639.61</v>
+        <v>196253761.41</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970900741.67</v>
+        <v>970901719.45</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130457395.91</v>
+        <v>1130458373.69</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227538499.62</v>
+        <v>227538817.25</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642021.21</v>
+        <v>2642021.87</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513111.42</v>
+        <v>5513112.8</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286536180.7</v>
+        <v>286536500.37</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042724135.71</v>
+        <v>1042724928.37</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244208325.78</v>
+        <v>1244209118.44</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230880571.22</v>
+        <v>230880999.81</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865656.03</v>
+        <v>2865658.3</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026048.63</v>
+        <v>7026054.19</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305685347.32</v>
+        <v>305685783.73</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046513802.52</v>
+        <v>1046514293.1</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268560902.33</v>
+        <v>1268561392.91</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238376164.75</v>
+        <v>238376378.25</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737678.42</v>
+        <v>3737679.54</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838230.72</v>
+        <v>7838233.07</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315842810.69</v>
+        <v>315843027.67</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026509626.14</v>
+        <v>1026510534.92</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228653505.17</v>
+        <v>1228654413.95</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246150307.62</v>
+        <v>246150550.03</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558650.92</v>
+        <v>3558651.02</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537327.73</v>
+        <v>7537327.95</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315570340.43</v>
+        <v>315570583.16</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275204867.01</v>
+        <v>1275205093.48</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517926344.26</v>
+        <v>1517926570.73</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295669350.26</v>
+        <v>295669462.22</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271138.22</v>
+        <v>4271138.87</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581195.810000001</v>
+        <v>9581197.27</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378765680.17</v>
+        <v>378765794.24</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123168983.61</v>
+        <v>1123171618.54</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375344144.94</v>
+        <v>1375346779.87</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251874997.72</v>
+        <v>251875488.24</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520479.15</v>
+        <v>3520477.39</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255690.24</v>
+        <v>11255684.62</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341094123.95</v>
+        <v>341094607.09</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780476664.11</v>
+        <v>780477175.9299999</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941893509.64</v>
+        <v>941894021.46</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182880100.72</v>
+        <v>182880313.01</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893236.72</v>
+        <v>2893237.74</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978968.78</v>
+        <v>4978970.53</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240364149.15</v>
+        <v>240364364.21</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925199775.08</v>
+        <v>925201063.09</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103203158.9</v>
+        <v>1103204446.91</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208933201.56</v>
+        <v>208933402.78</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099138.66</v>
+        <v>3099137.3</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218650.62</v>
+        <v>6218647.89</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270751500.85</v>
+        <v>270751697.98</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099240505.37</v>
+        <v>1099240990.42</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314540799.19</v>
+        <v>1314541284.24</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244615253.13</v>
+        <v>244615379.2</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671165.54</v>
+        <v>3671165.64</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710501.37</v>
+        <v>7710501.57</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319469340.74</v>
+        <v>319469467.12</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967574032.29</v>
+        <v>967574176.67</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190895037.87</v>
+        <v>1190895182.25</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210528248.04</v>
+        <v>210528289.45</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281794.46</v>
+        <v>3281794.55</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536287.66</v>
+        <v>7536287.85</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283811210.84</v>
+        <v>283811252.52</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003057899.1</v>
+        <v>1003059057.88</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198214587.16</v>
+        <v>1198215745.94</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222082751.86</v>
+        <v>222083203.46</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891029.47</v>
+        <v>3891032.06</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335921.03</v>
+        <v>6335925.24</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281014197.29</v>
+        <v>281014655.68</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362263709.68</v>
+        <v>1362266377.1</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634480464.8</v>
+        <v>1634483132.22</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306755630.89</v>
+        <v>306756178.76</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136442.86</v>
+        <v>6136441.45</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270516.35</v>
+        <v>10270513.99</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388014721.6</v>
+        <v>388015265.7</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156860555.87</v>
+        <v>1156863207.12</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409360523.52</v>
+        <v>1409363174.77</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247786768.7</v>
+        <v>247787674.62</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795198.19</v>
+        <v>3795201.75</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929293.220000001</v>
+        <v>9929302.529999999</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325984484.9</v>
+        <v>325985403.68</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870246255.6</v>
+        <v>870248325.6</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039350467.97</v>
+        <v>1039352537.97</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193421303.36</v>
+        <v>193421651.77</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256076.46</v>
+        <v>3256074.53</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684228.7</v>
+        <v>5684225.33</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245263420.15</v>
+        <v>245263763.26</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002183197.46</v>
+        <v>1002186012.35</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209520605.42</v>
+        <v>1209523420.31</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>216986369.33</v>
+        <v>216986913.98</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934194.24</v>
+        <v>2934193.05</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937831.02</v>
+        <v>6937828.22</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280958799.66</v>
+        <v>280959340.34</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105909190.88</v>
+        <v>1105912739.23</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351764090.53</v>
+        <v>1351767638.88</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242468482.61</v>
+        <v>242468859.05</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693237.16</v>
+        <v>2693233.09</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764005.08</v>
+        <v>8763991.83</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322782203.85</v>
+        <v>322782562.97</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932799791.8</v>
+        <v>932801186.3099999</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136747606.25</v>
+        <v>1136749000.76</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196510120.76</v>
+        <v>196510682.68</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927878.51</v>
+        <v>2927881.37</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577736.69</v>
+        <v>6577743.1</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259464077.33</v>
+        <v>259464648.51</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1161974488.21</v>
+        <v>1161975710.32</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354810972.28</v>
+        <v>1354812194.39</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252336352.78</v>
+        <v>252336630.91</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229152.86</v>
+        <v>4229152.81</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541636.07</v>
+        <v>4541636.02</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311948860.34</v>
+        <v>311949138.37</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439944318.71</v>
+        <v>1439945897.59</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740000984.74</v>
+        <v>1740002563.62</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284702071.79</v>
+        <v>284702664.45</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067042.9</v>
+        <v>4067045.7</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978446.1</v>
+        <v>5978450.22</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375572749.65</v>
+        <v>375573349.23</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319636516.95</v>
+        <v>1319638099.04</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579399601.07</v>
+        <v>1579401183.16</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283351526.13</v>
+        <v>283352108.3</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050925.76</v>
+        <v>3050927.65</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438308.99</v>
+        <v>7438313.58</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363592125.4</v>
+        <v>363592714.05</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096931638.3</v>
+        <v>1096935076.33</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1282972664.41</v>
+        <v>1282976102.44</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243408571.03</v>
+        <v>243410086.36</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660610.41</v>
+        <v>1660614.4</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7201979.73</v>
+        <v>7201997.06</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302126052.7</v>
+        <v>302127589.35</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142030728.75</v>
+        <v>1142039953.47</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1365921842.7</v>
+        <v>1365931067.42</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239631865.31</v>
+        <v>239636489.52</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298479.53</v>
+        <v>1298490.67</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234058.789999999</v>
+        <v>9234138.039999999</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307424778.37</v>
+        <v>307429492.97</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192752106.86</v>
+        <v>1192759750.85</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436409113.53</v>
+        <v>1436416757.52</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253599282.05</v>
+        <v>253601824.97</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145250.73</v>
+        <v>2145256.09</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6744930.75</v>
+        <v>6744947.62</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327953865.73</v>
+        <v>327956430.88</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226818236.7</v>
+        <v>1226832512.97</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494158527.57</v>
+        <v>1494172803.84</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272913172.56</v>
+        <v>272917904.78</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511723.4</v>
+        <v>2511732.56</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7247965.19</v>
+        <v>7247991.62</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361154945.83</v>
+        <v>361159713.65</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1324942127.61</v>
+        <v>1324957522.53</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1599262272.36</v>
+        <v>1599277667.28</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>276886114.61</v>
+        <v>276890020.47</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2332387.72</v>
+        <v>2332390.63</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8175640.27</v>
+        <v>8175650.47</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>360385049.39</v>
+        <v>360388968.37</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1803595209.86</v>
+        <v>1803638026.28</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2147658271.92</v>
+        <v>2147701088.34</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>366053774.61</v>
+        <v>366063610.14</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3885006.41</v>
+        <v>3885010.88</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6589347.19</v>
+        <v>6589354.77</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>466980895.98</v>
+        <v>466990743.57</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1365818247.29</v>
+        <v>1366056856.17</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1652588033.89</v>
+        <v>1652826642.77</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283596356.72</v>
+        <v>283639203.64</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4911210.63</v>
+        <v>4911058.5</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7343646.71</v>
+        <v>7343419.23</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374479003.74</v>
+        <v>374521471.05</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,12 +2752,18 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>796671717.37</v>
+        <v>1020262394.89</v>
       </c>
       <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
+      <c r="D40" s="6" t="n">
+        <v>29680306.46</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>23736200</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>15433876.01</v>
+      </c>
       <c r="G40" s="6" t="n">
         <v>19529310</v>
       </c>
@@ -2765,26 +2771,32 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>852849724.37</v>
+        <v>1145290784.36</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>169453212.18</v>
+        <v>217012725.67</v>
       </c>
       <c r="K40" s="9" t="n"/>
-      <c r="L40" s="9" t="n"/>
-      <c r="M40" s="9" t="n"/>
-      <c r="N40" s="9" t="n"/>
+      <c r="L40" s="9" t="n">
+        <v>10696701.66</v>
+      </c>
+      <c r="M40" s="9" t="n">
+        <v>8293832.56</v>
+      </c>
+      <c r="N40" s="9" t="n">
+        <v>3537319</v>
+      </c>
       <c r="O40" s="9" t="n">
-        <v>4404193.7</v>
+        <v>4475959.2</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>192332211.65</v>
+        <v>262491343.87</v>
       </c>
       <c r="R40" s="10" t="n">
-        <v>0.3616</v>
+        <v>0.4057164260172154</v>
       </c>
     </row>
   </sheetData>
@@ -4790,7 +4802,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1721154057.84</v>
+        <v>1721166006.77</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>162404936.11</v>
@@ -4811,10 +4823,10 @@
         <v>14064111</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1999932261.7</v>
+        <v>1999944210.63</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>477792366.46</v>
+        <v>477795683.48</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>50100849.41</v>
@@ -4826,16 +4838,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2925641.65</v>
+        <v>2925641.33</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>10895699.37</v>
+        <v>10895698.18</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>6213562.76</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>565304891.84</v>
+        <v>565308207.35</v>
       </c>
     </row>
     <row r="38">
@@ -4845,7 +4857,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>2342944004.46</v>
+        <v>2342988666.85</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>173014888.85</v>
@@ -4866,10 +4878,10 @@
         <v>21111711</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2689793797.2</v>
+        <v>2689838459.59</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>650401255.64</v>
+        <v>650413653.92</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46914612.74</v>
@@ -4881,16 +4893,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>5016162.38</v>
+        <v>5016161.43</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>8965871.42</v>
+        <v>8965869.720000001</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9944728.02</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>755149205.36</v>
+        <v>755161600.99</v>
       </c>
     </row>
     <row r="39">
@@ -4900,7 +4912,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1774253810.49</v>
+        <v>1774555473.8</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>132077170.89</v>
@@ -4921,10 +4933,10 @@
         <v>33781884</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>2064631442.73</v>
+        <v>2064933106.04</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>492532857.79</v>
+        <v>492616599.53</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38188228.54</v>
@@ -4936,16 +4948,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>6167797.35</v>
+        <v>6167774.63</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>9921459.779999999</v>
+        <v>9921423.23</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16230447.81</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>587552856.27</v>
+        <v>587636538.74</v>
       </c>
     </row>
     <row r="40">
@@ -4955,12 +4967,18 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1034909171.16</v>
+        <v>1325356414.99</v>
       </c>
       <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
+      <c r="D40" s="6" t="n">
+        <v>29680306.46</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>23736200</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>15433876.01</v>
+      </c>
       <c r="G40" s="6" t="n">
         <v>21831205</v>
       </c>
@@ -4968,23 +4986,29 @@
         <v>37074913</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1093815289.16</v>
+        <v>1453112915.46</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>287290785.91</v>
+        <v>367918940.8</v>
       </c>
       <c r="K40" s="9" t="n"/>
-      <c r="L40" s="9" t="n"/>
-      <c r="M40" s="9" t="n"/>
-      <c r="N40" s="9" t="n"/>
+      <c r="L40" s="9" t="n">
+        <v>10696701.66</v>
+      </c>
+      <c r="M40" s="9" t="n">
+        <v>8293832.56</v>
+      </c>
+      <c r="N40" s="9" t="n">
+        <v>4420647.93</v>
+      </c>
       <c r="O40" s="9" t="n">
-        <v>6230040.79</v>
+        <v>6253002.89</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18624740.64</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>312145567.34</v>
+        <v>416207866.48</v>
       </c>
     </row>
   </sheetData>
@@ -6557,7 +6581,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>828838948.09</v>
+        <v>828844702.22</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>12490106.43</v>
@@ -6600,7 +6624,7 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>1128268114.79</v>
+        <v>1128289622.41</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>18169819.03</v>
@@ -6643,7 +6667,7 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>854409664.98</v>
+        <v>854554933.96</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>10625376.42</v>
@@ -6686,22 +6710,34 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>498370860.46</v>
-      </c>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
+        <v>638238635.2</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>10495613.05</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>8464581</v>
+      </c>
       <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
+      <c r="F40" s="6" t="n">
+        <v>9836630.27</v>
+      </c>
       <c r="G40" s="6" t="n">
         <v>7061846</v>
       </c>
       <c r="H40" s="11" t="n">
         <v>0.6256</v>
       </c>
-      <c r="I40" s="11" t="n"/>
-      <c r="J40" s="11" t="n"/>
+      <c r="I40" s="11" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="J40" s="11" t="n">
+        <v>0.3566</v>
+      </c>
       <c r="K40" s="11" t="n"/>
-      <c r="L40" s="11" t="n"/>
+      <c r="L40" s="11" t="n">
+        <v>0.6373</v>
+      </c>
       <c r="M40" s="11" t="n">
         <v>0.3616</v>
       </c>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967574176.67</v>
+        <v>967574196.67</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190895182.25</v>
+        <v>1190895202.25</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210528289.45</v>
+        <v>210528293.4</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281794.55</v>
+        <v>3281794.54</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536287.85</v>
+        <v>7536287.83</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283811252.52</v>
+        <v>283811256.44</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002186012.35</v>
+        <v>1002188396.99</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209523420.31</v>
+        <v>1209525804.95</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>216986913.98</v>
+        <v>216987119.2</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934193.05</v>
+        <v>2934189.28</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937828.22</v>
+        <v>6937819.3</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280959340.34</v>
+        <v>280959532.86</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105912739.23</v>
+        <v>1105912832.74</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351767638.88</v>
+        <v>1351767732.39</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242468859.05</v>
+        <v>242468859.99</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693233.09</v>
+        <v>2693232.91</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8763991.83</v>
+        <v>8763991.220000001</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322782562.97</v>
+        <v>322782563.12</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932801186.3099999</v>
+        <v>932802223.75</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136749000.76</v>
+        <v>1136750038.2</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196510682.68</v>
+        <v>196510738.69</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927881.37</v>
+        <v>2927879.25</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577743.1</v>
+        <v>6577738.35</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259464648.51</v>
+        <v>259464697.65</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1161975710.32</v>
+        <v>1161975758.78</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354812194.39</v>
+        <v>1354812242.85</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252336630.91</v>
+        <v>252336632.79</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229152.81</v>
+        <v>4229152.68</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541636.02</v>
+        <v>4541635.88</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311949138.37</v>
+        <v>311949139.99</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439945897.59</v>
+        <v>1439947270.33</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740002563.62</v>
+        <v>1740003936.36</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284702664.45</v>
+        <v>284702803.78</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067045.7</v>
+        <v>4067043.95</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978450.22</v>
+        <v>5978447.65</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375573349.23</v>
+        <v>375573484.24</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319638099.04</v>
+        <v>1319638223.09</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579401183.16</v>
+        <v>1579401307.21</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283352108.3</v>
+        <v>283352128.09</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050927.65</v>
+        <v>3050927.57</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438313.58</v>
+        <v>7438313.4</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363592714.05</v>
+        <v>363592733.58</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096935076.33</v>
+        <v>1096935470.06</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1282976102.44</v>
+        <v>1282976496.17</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243410086.36</v>
+        <v>243410104.26</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660614.4</v>
+        <v>1660613.98</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7201997.06</v>
+        <v>7201995.22</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302127589.35</v>
+        <v>302127604.99</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142039953.47</v>
+        <v>1142040559</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1365931067.42</v>
+        <v>1365931672.95</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239636489.52</v>
+        <v>239636555.58</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298490.67</v>
+        <v>1298490.37</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234138.039999999</v>
+        <v>9234135.85</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307429492.97</v>
+        <v>307429556.54</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192759750.85</v>
+        <v>1192762654.16</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436416757.52</v>
+        <v>1436419660.83</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253601824.97</v>
+        <v>253602160.57</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145256.09</v>
+        <v>2145253.89</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6744947.62</v>
+        <v>6744940.7</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327956430.88</v>
+        <v>327956757.36</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226832512.97</v>
+        <v>1226832842.73</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494172803.84</v>
+        <v>1494173133.6</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272917904.78</v>
+        <v>272917934.25</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511732.56</v>
+        <v>2511732.2</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7247991.62</v>
+        <v>7247990.59</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361159713.65</v>
+        <v>361159741.72</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1324957522.53</v>
+        <v>1324960789.23</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1599277667.28</v>
+        <v>1599280933.98</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>276890020.47</v>
+        <v>276890357.01</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2332390.63</v>
+        <v>2332387.97</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8175650.47</v>
+        <v>8175641.13</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>360388968.37</v>
+        <v>360389292.9</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1803638026.28</v>
+        <v>1803648216.5</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2147701088.34</v>
+        <v>2147711278.56</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>366063610.14</v>
+        <v>366065069.7</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3885010.88</v>
+        <v>3885004.45</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6589354.77</v>
+        <v>6589343.86</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>466990743.57</v>
+        <v>466992185.78</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1366056856.17</v>
+        <v>1366096806.76</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1652826642.77</v>
+        <v>1652866593.36</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283639203.64</v>
+        <v>283647354.82</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4911058.5</v>
+        <v>4911046.28</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7343419.23</v>
+        <v>7343400.96</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374521471.05</v>
+        <v>374529591.73</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,9 +2752,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1020262394.89</v>
-      </c>
-      <c r="C40" s="6" t="n"/>
+        <v>1020459078.68</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>184348327.32</v>
+      </c>
       <c r="D40" s="6" t="n">
         <v>29680306.46</v>
       </c>
@@ -2771,12 +2773,14 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1145290784.36</v>
+        <v>1329835795.47</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>217012725.67</v>
-      </c>
-      <c r="K40" s="9" t="n"/>
+        <v>217049872.89</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>52663233.49</v>
+      </c>
       <c r="L40" s="9" t="n">
         <v>10696701.66</v>
       </c>
@@ -2784,19 +2788,19 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3537319</v>
+        <v>3661328.55</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4475959.2</v>
+        <v>4632875.13</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>262491343.87</v>
+        <v>315472650.05</v>
       </c>
       <c r="R40" s="10" t="n">
-        <v>0.4057164260172154</v>
+        <v>0.3156022523452979</v>
       </c>
     </row>
   </sheetData>
@@ -4802,7 +4806,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1721166006.77</v>
+        <v>1721169117.05</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>162404936.11</v>
@@ -4823,10 +4827,10 @@
         <v>14064111</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1999944210.63</v>
+        <v>1999947320.91</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>477795683.48</v>
+        <v>477796546.89</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>50100849.41</v>
@@ -4838,16 +4842,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2925641.33</v>
+        <v>2925641.25</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>10895698.18</v>
+        <v>10895697.87</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>6213562.76</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>565308207.35</v>
+        <v>565309070.36</v>
       </c>
     </row>
     <row r="38">
@@ -4857,7 +4861,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>2342988666.85</v>
+        <v>2343000361.6</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>173014888.85</v>
@@ -4878,10 +4882,10 @@
         <v>21111711</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2689838459.59</v>
+        <v>2689850154.34</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>650413653.92</v>
+        <v>650416900.38</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46914612.74</v>
@@ -4893,16 +4897,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>5016161.43</v>
+        <v>5016161.18</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>8965869.720000001</v>
+        <v>8965869.279999999</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9944728.02</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>755161600.99</v>
+        <v>755164846.76</v>
       </c>
     </row>
     <row r="39">
@@ -4912,7 +4916,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1774555473.8</v>
+        <v>1774606202.55</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>132077170.89</v>
@@ -4933,10 +4937,10 @@
         <v>33781884</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>2064933106.04</v>
+        <v>2064983834.79</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>492616599.53</v>
+        <v>492630681.83</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38188228.54</v>
@@ -4948,16 +4952,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>6167774.63</v>
+        <v>6167770.81</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>9921423.23</v>
+        <v>9921417.08</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16230447.81</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>587636538.74</v>
+        <v>587650611.0700001</v>
       </c>
     </row>
     <row r="40">
@@ -4967,9 +4971,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1325356414.99</v>
-      </c>
-      <c r="C40" s="6" t="n"/>
+        <v>1325611041.26</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>185485243.71</v>
+      </c>
       <c r="D40" s="6" t="n">
         <v>29680306.46</v>
       </c>
@@ -4986,12 +4992,14 @@
         <v>37074913</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1453112915.46</v>
+        <v>1638852785.44</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>367918940.8</v>
-      </c>
-      <c r="K40" s="9" t="n"/>
+        <v>367989625.05</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>52881481.78</v>
+      </c>
       <c r="L40" s="9" t="n">
         <v>10696701.66</v>
       </c>
@@ -4999,16 +5007,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>4420647.93</v>
+        <v>4418254.43</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>6253002.89</v>
+        <v>6249617.28</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18624740.64</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>416207866.48</v>
+        <v>469154253.4</v>
       </c>
     </row>
   </sheetData>
@@ -6581,7 +6589,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>828844702.22</v>
+        <v>828846200.01</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>12490106.43</v>
@@ -6624,7 +6632,7 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>1128289622.41</v>
+        <v>1128295254.13</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>18169819.03</v>
@@ -6667,7 +6675,7 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>854554933.96</v>
+        <v>854579362.9</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>10625376.42</v>
@@ -6710,7 +6718,7 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>638238635.2</v>
+        <v>638361253.03</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>10495613.05</v>
@@ -6718,7 +6726,9 @@
       <c r="D40" s="6" t="n">
         <v>8464581</v>
       </c>
-      <c r="E40" s="6" t="n"/>
+      <c r="E40" s="6" t="n">
+        <v>50215867.66</v>
+      </c>
       <c r="F40" s="6" t="n">
         <v>9836630.27</v>
       </c>
@@ -6734,7 +6744,9 @@
       <c r="J40" s="11" t="n">
         <v>0.3566</v>
       </c>
-      <c r="K40" s="11" t="n"/>
+      <c r="K40" s="11" t="n">
+        <v>0.2724</v>
+      </c>
       <c r="L40" s="11" t="n">
         <v>0.6373</v>
       </c>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R40"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226353348.67</v>
+        <v>1226353811.27</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404315443.25</v>
+        <v>1404315905.85</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290713047.44</v>
+        <v>290713240.46</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524811.48</v>
+        <v>524811.6</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360261.02</v>
+        <v>9360263.1</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354056026.57</v>
+        <v>354056221.79</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019792252.01</v>
+        <v>1019794241.7</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203197161.52</v>
+        <v>1203199151.21</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223746101.58</v>
+        <v>223746567.14</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516298.68</v>
+        <v>516298.66</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237386.140000001</v>
+        <v>9237385.73</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289057892.18</v>
+        <v>289058357.3</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766402797.5</v>
+        <v>766403333.45</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882445344.54</v>
+        <v>882445880.49</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197400652.42</v>
+        <v>197400801.4</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374709</v>
+        <v>374709.01</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399339.04</v>
+        <v>5399339.12</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239489982.84</v>
+        <v>239490131.9</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983752003.36</v>
+        <v>983755258.27</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168390152.38</v>
+        <v>1168393407.29</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236059264.37</v>
+        <v>236059954.66</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324586.07</v>
+        <v>324585.89</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358486.93</v>
+        <v>7358482.93</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305855921.94</v>
+        <v>305856608.06</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097585141.3</v>
+        <v>1097585702.11</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302665178.88</v>
+        <v>1302665739.69</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250949984.77</v>
+        <v>250950088.42</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.12</v>
+        <v>709927.03</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693352.89</v>
+        <v>7693351.98</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328053996.03</v>
+        <v>328054098.7</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011516743.17</v>
+        <v>1011519239.61</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233689862.68</v>
+        <v>1233692359.12</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229523390.53</v>
+        <v>229524286.15</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255742.58</v>
+        <v>1255743.71</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409723.630000001</v>
+        <v>8409731.210000001</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309198313.4</v>
+        <v>309199217.73</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961936856.71</v>
+        <v>961937757.6799999</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145544018.25</v>
+        <v>1145544919.22</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214889140.39</v>
+        <v>214889305.22</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814778.3</v>
+        <v>814778.13</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850542.48</v>
+        <v>6850541.07</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281206306.37</v>
+        <v>281206469.62</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073042410.25</v>
+        <v>1073043651.93</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277708307.73</v>
+        <v>1277709549.41</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240124138.25</v>
+        <v>240124392.77</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353400.08</v>
+        <v>2353399.69</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569915.36</v>
+        <v>7569914.1</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313747931.56</v>
+        <v>313748184.44</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960757189.34</v>
+        <v>960758292.38</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185430506.46</v>
+        <v>1185431609.5</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212544272.79</v>
+        <v>212544683.62</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490144.36</v>
+        <v>2490145.54</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929257.439999999</v>
+        <v>8929261.68</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296179015.3</v>
+        <v>296179431.55</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686497250.42</v>
+        <v>686500475.6799999</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813408941.45</v>
+        <v>813412166.71</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150989214.29</v>
+        <v>150989880.86</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897062.95</v>
+        <v>1897061.84</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485524.27</v>
+        <v>3485522.24</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196253761.41</v>
+        <v>196254424.83</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970901719.45</v>
+        <v>970904184.11</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130458373.69</v>
+        <v>1130460838.35</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227538817.25</v>
+        <v>227539607.6</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642021.87</v>
+        <v>2642023.44</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513112.8</v>
+        <v>5513116.08</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286536500.37</v>
+        <v>286537295.57</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042724928.37</v>
+        <v>1042725681.49</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244209118.44</v>
+        <v>1244209871.56</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230880999.81</v>
+        <v>230881448.75</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865658.3</v>
+        <v>2865660.85</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026054.19</v>
+        <v>7026060.46</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305685783.73</v>
+        <v>305686241.5</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046514293.1</v>
+        <v>1046517788.39</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268561392.91</v>
+        <v>1268564888.2</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238376378.25</v>
+        <v>238378233.45</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737679.54</v>
+        <v>3737691.64</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838233.07</v>
+        <v>7838258.45</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315843027.67</v>
+        <v>315844920.34</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026510534.92</v>
+        <v>1026514411.78</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228654413.95</v>
+        <v>1228658290.81</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246150550.03</v>
+        <v>246152380.11</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558651.02</v>
+        <v>3558660.77</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537327.95</v>
+        <v>7537348.6</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315570583.16</v>
+        <v>315572443.65</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275205093.48</v>
+        <v>1275206788.52</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517926570.73</v>
+        <v>1517928265.77</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295669462.22</v>
+        <v>295670042.55</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271138.87</v>
+        <v>4271140.71</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581197.27</v>
+        <v>9581201.4</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378765794.24</v>
+        <v>378766380.54</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123171618.54</v>
+        <v>1123173544.79</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375346779.87</v>
+        <v>1375348706.12</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251875488.24</v>
+        <v>251876360.49</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520477.39</v>
+        <v>3520481.65</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255684.62</v>
+        <v>11255698.22</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341094607.09</v>
+        <v>341095497.2</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780477175.9299999</v>
+        <v>780481128.11</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941894021.46</v>
+        <v>941897973.64</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182880313.01</v>
+        <v>182881669.79</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893237.74</v>
+        <v>2893242.07</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978970.53</v>
+        <v>4978977.99</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240364364.21</v>
+        <v>240365732.78</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925201063.09</v>
+        <v>925203351.02</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103204446.91</v>
+        <v>1103206734.84</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208933402.78</v>
+        <v>208934470.39</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099137.3</v>
+        <v>3099143.3</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218647.89</v>
+        <v>6218659.93</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270751697.98</v>
+        <v>270752783.62</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099240990.42</v>
+        <v>1099247443.05</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314541284.24</v>
+        <v>1314547736.87</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244615379.2</v>
+        <v>244617883.89</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671165.64</v>
+        <v>3671176.8</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710501.57</v>
+        <v>7710525.01</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319469467.12</v>
+        <v>319472006.4</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967574196.67</v>
+        <v>967576583.75</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190895202.25</v>
+        <v>1190897589.33</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210528293.4</v>
+        <v>210529070</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281794.54</v>
+        <v>3281797.04</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536287.83</v>
+        <v>7536293.57</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283811256.44</v>
+        <v>283812041.27</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003059057.88</v>
+        <v>1003061264.37</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198215745.94</v>
+        <v>1198217952.43</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222083203.46</v>
+        <v>222083512.6</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891032.06</v>
+        <v>3891029.06</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335925.24</v>
+        <v>6335920.36</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281014655.68</v>
+        <v>281014956.96</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362266377.1</v>
+        <v>1362268693.98</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634483132.22</v>
+        <v>1634485449.1</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306756178.76</v>
+        <v>306756790.47</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136441.45</v>
+        <v>6136442.47</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270513.99</v>
+        <v>10270515.69</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388015265.7</v>
+        <v>388015880.13</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156863207.12</v>
+        <v>1156868660.21</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409363174.77</v>
+        <v>1409368627.86</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247787674.62</v>
+        <v>247790781.5</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795201.75</v>
+        <v>3795224.18</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929302.529999999</v>
+        <v>9929361.220000001</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325985403.68</v>
+        <v>325988591.68</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870248325.6</v>
+        <v>870256138.75</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039352537.97</v>
+        <v>1039360351.12</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193421651.77</v>
+        <v>193423273.33</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256074.53</v>
+        <v>3256071.47</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684225.33</v>
+        <v>5684219.98</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245263763.26</v>
+        <v>245265376.42</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002188396.99</v>
+        <v>1002192351.53</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209525804.95</v>
+        <v>1209529759.49</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>216987119.2</v>
+        <v>216988270.67</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934189.28</v>
+        <v>2934191.8</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937819.3</v>
+        <v>6937825.26</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280959532.86</v>
+        <v>280960692.81</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105912832.74</v>
+        <v>1105914869.63</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351767732.39</v>
+        <v>1351769769.28</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242468859.99</v>
+        <v>242469275.97</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693232.91</v>
+        <v>2693232.3</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8763991.220000001</v>
+        <v>8763989.24</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322782563.12</v>
+        <v>322782976.51</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932802223.75</v>
+        <v>932806048.83</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136750038.2</v>
+        <v>1136753863.28</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196510738.69</v>
+        <v>196511755.98</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927879.25</v>
+        <v>2927880.94</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577738.35</v>
+        <v>6577742.14</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259464697.65</v>
+        <v>259465720.42</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1161975758.78</v>
+        <v>1161982257.38</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354812242.85</v>
+        <v>1354818741.45</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252336632.79</v>
+        <v>252339419.63</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229152.68</v>
+        <v>4229170.69</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541635.88</v>
+        <v>4541655.21</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311949139.99</v>
+        <v>311951964.16</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439947270.33</v>
+        <v>1439957902.56</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740003936.36</v>
+        <v>1740014568.59</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284702803.78</v>
+        <v>284705788.64</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067043.95</v>
+        <v>4067051.63</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978447.65</v>
+        <v>5978458.93</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375573484.24</v>
+        <v>375576488.06</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319638223.09</v>
+        <v>1319652399.84</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579401307.21</v>
+        <v>1579415483.96</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283352128.09</v>
+        <v>283357457.5</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050927.57</v>
+        <v>3050945.42</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438313.4</v>
+        <v>7438356.91</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363592733.58</v>
+        <v>363598124.35</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096935470.06</v>
+        <v>1096953830.87</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1282976496.17</v>
+        <v>1282994856.98</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243410104.26</v>
+        <v>243414382.41</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660613.98</v>
+        <v>1660613.72</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7201995.22</v>
+        <v>7201994.1</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302127604.99</v>
+        <v>302131881.76</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142040559</v>
+        <v>1142061170.97</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1365931672.95</v>
+        <v>1365952284.92</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239636555.58</v>
+        <v>239644335.92</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298490.37</v>
+        <v>1298504.11</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234135.85</v>
+        <v>9234233.550000001</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307429556.54</v>
+        <v>307437448.31</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192762654.16</v>
+        <v>1192779804.33</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436419660.83</v>
+        <v>1436436811</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253602160.57</v>
+        <v>253608485.26</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145253.89</v>
+        <v>2145270.09</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6744940.7</v>
+        <v>6744991.62</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327956757.36</v>
+        <v>327963149.17</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226832842.73</v>
+        <v>1226859378.66</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494173133.6</v>
+        <v>1494199669.53</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272917934.25</v>
+        <v>272927191.83</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511732.2</v>
+        <v>2511752.53</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7247990.59</v>
+        <v>7248049.24</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361159741.72</v>
+        <v>361169078.28</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1324960789.23</v>
+        <v>1348502893.28</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1599280933.98</v>
+        <v>1622823038.03</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>276890357.01</v>
+        <v>278401437.86</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2332387.97</v>
+        <v>2307474.03</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8175641.13</v>
+        <v>8088311.14</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>360389292.9</v>
+        <v>361788129.82</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1803648216.5</v>
+        <v>1778159400.97</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2147711278.56</v>
+        <v>2122222463.03</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>366065069.7</v>
+        <v>364453603.31</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3885004.45</v>
+        <v>3918866.54</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6589343.86</v>
+        <v>6646777.24</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>466992185.78</v>
+        <v>465472014.86</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1366096806.76</v>
+        <v>1363993961.08</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1652866593.36</v>
+        <v>1650763747.68</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283647354.82</v>
+        <v>283551493.33</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4911046.28</v>
+        <v>4916212.95</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7343400.96</v>
+        <v>7351126.59</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374529591.73</v>
+        <v>374446622.55</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1020459078.68</v>
+        <v>1037409706.05</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1329835795.47</v>
+        <v>1346786422.84</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>217049872.89</v>
+        <v>218246754.03</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,23 +2788,77 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3661328.55</v>
+        <v>3628100.52</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4632875.13</v>
+        <v>4590829.92</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>315472650.05</v>
+        <v>316594257.95</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>1048783428.16</v>
+      </c>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n">
+        <v>30068575.81</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>17272330</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>15345833.96</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>25006540</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>35555460</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>1172032167.93</v>
+      </c>
+      <c r="J41" s="8" t="n">
+        <v>221785565.55</v>
+      </c>
+      <c r="K41" s="9" t="n"/>
+      <c r="L41" s="9" t="n">
+        <v>8900667.25</v>
+      </c>
+      <c r="M41" s="9" t="n">
+        <v>5234399.4</v>
+      </c>
+      <c r="N41" s="9" t="n">
+        <v>3429852.52</v>
+      </c>
+      <c r="O41" s="9" t="n">
+        <v>5589057.22</v>
+      </c>
+      <c r="P41" s="9" t="n">
+        <v>17014125.22</v>
+      </c>
+      <c r="Q41" s="9" t="n">
+        <v>261953667.16</v>
+      </c>
+      <c r="R41" s="10" t="n">
+        <v>0.4468039425501122</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R40"/>
+  <autoFilter ref="A2:R41"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -2820,7 +2874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4806,7 +4860,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1721169117.05</v>
+        <v>1770000000</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>162404936.11</v>
@@ -4827,10 +4881,10 @@
         <v>14064111</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1999947320.91</v>
+        <v>2048778203.86</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>477796546.89</v>
+        <v>491352000</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>50100849.41</v>
@@ -4842,16 +4896,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2925641.25</v>
+        <v>2924361.97</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>10895697.87</v>
+        <v>10890933.57</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>6213562.76</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>565309070.36</v>
+        <v>578858479.9</v>
       </c>
     </row>
     <row r="38">
@@ -4861,7 +4915,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>2343000361.6</v>
+        <v>2290000000</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>173014888.85</v>
@@ -4882,10 +4936,10 @@
         <v>21111711</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2689850154.34</v>
+        <v>2636849792.74</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>650416900.38</v>
+        <v>635704000</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46914612.74</v>
@@ -4897,16 +4951,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>5016161.18</v>
+        <v>5017312.78</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>8965869.279999999</v>
+        <v>8967927.640000001</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9944728.02</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>755164846.76</v>
+        <v>740455156.33</v>
       </c>
     </row>
     <row r="39">
@@ -4916,7 +4970,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1774606202.55</v>
+        <v>1770000000</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>132077170.89</v>
@@ -4937,10 +4991,10 @@
         <v>33781884</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>2064983834.79</v>
+        <v>2060377632.24</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>492630681.83</v>
+        <v>491352000</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38188228.54</v>
@@ -4952,16 +5006,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>6167770.81</v>
+        <v>6168118.49</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>9921417.08</v>
+        <v>9921976.369999999</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16230447.81</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>587650611.0700001</v>
+        <v>586372836.21</v>
       </c>
     </row>
     <row r="40">
@@ -4971,7 +5025,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1325611041.26</v>
+        <v>1360000000</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>185485243.71</v>
@@ -4992,10 +5046,10 @@
         <v>37074913</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1638852785.44</v>
+        <v>1673241744.18</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>367989625.05</v>
+        <v>377536000</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52881481.78</v>
@@ -5007,20 +5061,71 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>4418254.43</v>
+        <v>4415441.67</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>6249617.28</v>
+        <v>6245638.64</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18624740.64</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>469154253.4</v>
+        <v>478693836.95</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>1365929642.25</v>
+      </c>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n">
+        <v>30068575.81</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>17272330</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>15345833.96</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>26927787</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>36473569</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>1492017738.02</v>
+      </c>
+      <c r="J41" s="8" t="n">
+        <v>379182068.69</v>
+      </c>
+      <c r="K41" s="9" t="n"/>
+      <c r="L41" s="9" t="n">
+        <v>8900667.25</v>
+      </c>
+      <c r="M41" s="9" t="n">
+        <v>5234399.4</v>
+      </c>
+      <c r="N41" s="9" t="n">
+        <v>4347249.58</v>
+      </c>
+      <c r="O41" s="9" t="n">
+        <v>7628246.93</v>
+      </c>
+      <c r="P41" s="9" t="n">
+        <v>17374100.29</v>
+      </c>
+      <c r="Q41" s="9" t="n">
+        <v>422666732.15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q40"/>
+  <autoFilter ref="A2:Q41"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -5035,7 +5140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5747,7 +5852,7 @@
         <v>15529922</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.5665</v>
+        <v>0.5664</v>
       </c>
       <c r="I17" s="11" t="n">
         <v>0.3994</v>
@@ -5790,7 +5895,7 @@
         <v>16183161</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.6003000000000001</v>
+        <v>0.6002000000000001</v>
       </c>
       <c r="I18" s="11" t="n">
         <v>0.3354</v>
@@ -6589,7 +6694,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>828846200.01</v>
+        <v>852361200</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>12490106.43</v>
@@ -6607,7 +6712,7 @@
         <v>11868618</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>0.6256</v>
+        <v>0.6321</v>
       </c>
       <c r="I37" s="11" t="n">
         <v>0.3806</v>
@@ -6632,7 +6737,7 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>1128295254.13</v>
+        <v>1102772400</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>18169819.03</v>
@@ -6650,7 +6755,7 @@
         <v>10824093</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>0.6256</v>
+        <v>0.6202000000000001</v>
       </c>
       <c r="I38" s="11" t="n">
         <v>0.3624</v>
@@ -6675,7 +6780,7 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>854579362.9</v>
+        <v>852361200</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>10625376.42</v>
@@ -6693,7 +6798,7 @@
         <v>12319196</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>0.6256</v>
+        <v>0.6249</v>
       </c>
       <c r="I39" s="11" t="n">
         <v>0.3315</v>
@@ -6718,7 +6823,7 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>638361253.03</v>
+        <v>654921600</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>10495613.05</v>
@@ -6736,7 +6841,7 @@
         <v>7061846</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>0.6256</v>
+        <v>0.6313</v>
       </c>
       <c r="I40" s="11" t="n">
         <v>0.3536</v>
@@ -6754,15 +6859,54 @@
         <v>0.3616</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>657777078.52</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>12213347.32</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>7654521</v>
+      </c>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n">
+        <v>10065487.41</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>9247924</v>
+      </c>
+      <c r="H41" s="11" t="n">
+        <v>0.6272</v>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>0.4061999999999999</v>
+      </c>
+      <c r="J41" s="11" t="n">
+        <v>0.4432</v>
+      </c>
+      <c r="K41" s="11" t="n"/>
+      <c r="L41" s="11" t="n">
+        <v>0.6559</v>
+      </c>
+      <c r="M41" s="11" t="n">
+        <v>0.3698</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M40"/>
+  <autoFilter ref="A2:M41"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -6793,7 +6937,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-08. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-09. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226353811.27</v>
+        <v>1226353824.68</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404315905.85</v>
+        <v>1404315919.26</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290713240.46</v>
+        <v>290713241.4</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -653,13 +653,13 @@
         <v>524811.6</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360263.1</v>
+        <v>9360263.029999999</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354056221.79</v>
+        <v>354056222.66</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983755258.27</v>
+        <v>983755333</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168393407.29</v>
+        <v>1168393482.02</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236059954.66</v>
+        <v>236059990.15</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324585.89</v>
+        <v>324585.91</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358482.93</v>
+        <v>7358483.33</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305856608.06</v>
+        <v>305856643.96</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097585702.11</v>
+        <v>1097585809.41</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302665739.69</v>
+        <v>1302665846.99</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250950088.42</v>
+        <v>250950095.93</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.03</v>
+        <v>709926.99</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693351.98</v>
+        <v>7693351.51</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328054098.7</v>
+        <v>328054105.69</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011519239.61</v>
+        <v>1011520113.11</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233692359.12</v>
+        <v>1233693232.62</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229524286.15</v>
+        <v>229524374.05</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255743.71</v>
+        <v>1255743.16</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409731.210000001</v>
+        <v>8409727.529999999</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309199217.73</v>
+        <v>309199301.4</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073043651.93</v>
+        <v>1073043987.23</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277709549.41</v>
+        <v>1277709884.71</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240124392.77</v>
+        <v>240124416.24</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353399.69</v>
+        <v>2353399.23</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569914.1</v>
+        <v>7569912.63</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313748184.44</v>
+        <v>313748205.98</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686500475.6799999</v>
+        <v>686500880.05</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813412166.71</v>
+        <v>813412571.08</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150989880.86</v>
+        <v>150989909.12</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897061.84</v>
+        <v>1897061.15</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485522.24</v>
+        <v>3485520.97</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196254424.83</v>
+        <v>196254451.14</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970904184.11</v>
+        <v>970905587.85</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130460838.35</v>
+        <v>1130462242.09</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227539607.6</v>
+        <v>227540097.17</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642023.44</v>
+        <v>2642024.71</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513116.08</v>
+        <v>5513118.73</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286537295.57</v>
+        <v>286537789.06</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042725681.49</v>
+        <v>1042725778.39</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244209871.56</v>
+        <v>1244209968.46</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230881448.75</v>
+        <v>230881491.39</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865660.85</v>
+        <v>2865661.03</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026060.46</v>
+        <v>7026060.9</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305686241.5</v>
+        <v>305686284.77</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046517788.39</v>
+        <v>1046517812.32</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268564888.2</v>
+        <v>1268564912.13</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238378233.45</v>
+        <v>238378237.23</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737691.64</v>
+        <v>3737691.61</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838258.45</v>
+        <v>7838258.39</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315844920.34</v>
+        <v>315844924.03</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026514411.78</v>
+        <v>1026514460.66</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228658290.81</v>
+        <v>1228658339.69</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246152380.11</v>
+        <v>246152401.61</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558660.77</v>
+        <v>3558660.88</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537348.6</v>
+        <v>7537348.83</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315572443.65</v>
+        <v>315572465.47</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275206788.52</v>
+        <v>1275207157.27</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517928265.77</v>
+        <v>1517928634.52</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295670042.55</v>
+        <v>295670168.79</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271140.71</v>
+        <v>4271141.11</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581201.4</v>
+        <v>9581202.300000001</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378766380.54</v>
+        <v>378766508.08</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123173544.79</v>
+        <v>1123173594.95</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375348706.12</v>
+        <v>1375348756.28</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251876360.49</v>
+        <v>251876380.56</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520481.65</v>
+        <v>3520481.73</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255698.22</v>
+        <v>11255698.49</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341095497.2</v>
+        <v>341095517.62</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780481128.11</v>
+        <v>780481352.11</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941897973.64</v>
+        <v>941898197.64</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182881669.79</v>
+        <v>182881767.56</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893242.07</v>
+        <v>2893242.57</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978977.99</v>
+        <v>4978978.86</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240365732.78</v>
+        <v>240365831.93</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925203351.02</v>
+        <v>925203581.79</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103206734.84</v>
+        <v>1103206965.61</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208934470.39</v>
+        <v>208934524.99</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099143.3</v>
+        <v>3099143.27</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218659.93</v>
+        <v>6218659.88</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270752783.62</v>
+        <v>270752838.15</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099247443.05</v>
+        <v>1099247673.38</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314547736.87</v>
+        <v>1314547967.2</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244617883.89</v>
+        <v>244617950.34</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671176.8</v>
+        <v>3671176.93</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710525.01</v>
+        <v>7710525.27</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319472006.4</v>
+        <v>319472073.24</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967576583.75</v>
+        <v>967576658.33</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190897589.33</v>
+        <v>1190897663.91</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210529070</v>
+        <v>210529104.15</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281797.04</v>
+        <v>3281797.23</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536293.57</v>
+        <v>7536294.02</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283812041.27</v>
+        <v>283812076.07</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003061264.37</v>
+        <v>1003061316.64</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198217952.43</v>
+        <v>1198218004.7</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222083512.6</v>
+        <v>222083526.67</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891029.06</v>
+        <v>3891029.09</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335920.36</v>
+        <v>6335920.41</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281014956.96</v>
+        <v>281014971.09</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362268693.98</v>
+        <v>1362268845.18</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634485449.1</v>
+        <v>1634485600.3</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306756790.47</v>
+        <v>306756849.21</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136442.47</v>
+        <v>6136442.85</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270515.69</v>
+        <v>10270516.32</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388015880.13</v>
+        <v>388015939.88</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156868660.21</v>
+        <v>1156869259.79</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409368627.86</v>
+        <v>1409369227.44</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247790781.5</v>
+        <v>247790965.73</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795224.18</v>
+        <v>3795224.73</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929361.220000001</v>
+        <v>9929362.66</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325988591.68</v>
+        <v>325988777.91</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870256138.75</v>
+        <v>870256143.75</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039360351.12</v>
+        <v>1039360356.12</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193423273.33</v>
+        <v>193423273.93</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1979,13 +1979,13 @@
         <v>3256071.47</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684219.98</v>
+        <v>5684219.97</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245265376.42</v>
+        <v>245265376.99</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002192351.53</v>
+        <v>1002192402.78</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209529759.49</v>
+        <v>1209529810.74</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>216988270.67</v>
+        <v>216988295.06</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934191.8</v>
+        <v>2934191.94</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937825.26</v>
+        <v>6937825.58</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280960692.81</v>
+        <v>280960717.65</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105914869.63</v>
+        <v>1105916624.63</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351769769.28</v>
+        <v>1351771524.28</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242469275.97</v>
+        <v>242470925.59</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693232.3</v>
+        <v>2693242.94</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8763989.24</v>
+        <v>8764023.880000001</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322782976.51</v>
+        <v>322784671.41</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932806048.83</v>
+        <v>932806287.76</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136753863.28</v>
+        <v>1136754102.21</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196511755.98</v>
+        <v>196511848.32</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927880.94</v>
+        <v>2927881.38</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577742.14</v>
+        <v>6577743.14</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259465720.42</v>
+        <v>259465814.2</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1161982257.38</v>
+        <v>1161982743.92</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354818741.45</v>
+        <v>1354819227.99</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252339419.63</v>
+        <v>252339558.48</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229170.69</v>
+        <v>4229171.06</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541655.21</v>
+        <v>4541655.62</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311951964.16</v>
+        <v>311952103.79</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439957902.56</v>
+        <v>1439958245.9</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740014568.59</v>
+        <v>1740014911.93</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284705788.64</v>
+        <v>284705883.7</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067051.63</v>
+        <v>4067051.86</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978458.93</v>
+        <v>5978459.28</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375576488.06</v>
+        <v>375576583.7</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319652399.84</v>
+        <v>1319653972.29</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579415483.96</v>
+        <v>1579417056.41</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283357457.5</v>
+        <v>283358020.27</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050945.42</v>
+        <v>3050947.16</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438356.91</v>
+        <v>7438361.14</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363598124.35</v>
+        <v>363598693.09</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096953830.87</v>
+        <v>1096954616.23</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1282994856.98</v>
+        <v>1282995642.34</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243414382.41</v>
+        <v>243414722.2</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660613.72</v>
+        <v>1660614.6</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7201994.1</v>
+        <v>7201997.91</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302131881.76</v>
+        <v>302132226.23</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142061170.97</v>
+        <v>1142062265.35</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1365952284.92</v>
+        <v>1365953379.3</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239644335.92</v>
+        <v>239644699.22</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298504.11</v>
+        <v>1298504.62</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234233.550000001</v>
+        <v>9234237.189999999</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307437448.31</v>
+        <v>307437815.76</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192779804.33</v>
+        <v>1192781715.89</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436436811</v>
+        <v>1436438722.56</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253608485.26</v>
+        <v>253610054.34</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145270.09</v>
+        <v>2145277.7</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6744991.62</v>
+        <v>6745015.57</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327963149.17</v>
+        <v>327964749.81</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226859378.66</v>
+        <v>1226860529.44</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494199669.53</v>
+        <v>1494200820.31</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272927191.83</v>
+        <v>272927744.95</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511752.53</v>
+        <v>2511754.49</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248049.24</v>
+        <v>7248054.91</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361169078.28</v>
+        <v>361169639.03</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348502893.28</v>
+        <v>1348504100.19</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622823038.03</v>
+        <v>1622824244.94</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278401437.86</v>
+        <v>278401814.92</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307474.03</v>
+        <v>2307474.74</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088311.14</v>
+        <v>8088313.63</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361788129.82</v>
+        <v>361788510.08</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778159400.97</v>
+        <v>1778162499.5</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122222463.03</v>
+        <v>2122225561.56</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364453603.31</v>
+        <v>364455132.67</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3918866.54</v>
+        <v>3918873.86</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6646777.24</v>
+        <v>6646789.65</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465472014.86</v>
+        <v>465473563.95</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1363993961.08</v>
+        <v>1363998848.73</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1650763747.68</v>
+        <v>1650768635.33</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283551493.33</v>
+        <v>283553580.22</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4916212.95</v>
+        <v>4916226.23</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7351126.59</v>
+        <v>7351146.45</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374446622.55</v>
+        <v>374448742.57</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1037409706.05</v>
+        <v>1037417563.81</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1346786422.84</v>
+        <v>1346794280.6</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218246754.03</v>
+        <v>218250616.18</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3628100.52</v>
+        <v>3628124.23</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4590829.92</v>
+        <v>4590859.92</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316594257.95</v>
+        <v>316598173.81</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1048783428.16</v>
+        <v>1048928677.83</v>
       </c>
       <c r="C41" s="6" t="n"/>
       <c r="D41" s="6" t="n">
@@ -2829,10 +2829,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1172032167.93</v>
+        <v>1172177417.6</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>221785565.55</v>
+        <v>221815486.88</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n">
@@ -2842,16 +2842,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3429852.52</v>
+        <v>3429818.04</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5589057.22</v>
+        <v>5589001.05</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>261953667.16</v>
+        <v>261983497.84</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.4468039425501122</v>
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1365929642.25</v>
+        <v>1366115446.49</v>
       </c>
       <c r="C41" s="6" t="n"/>
       <c r="D41" s="6" t="n">
@@ -5099,10 +5099,10 @@
         <v>36473569</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1492017738.02</v>
+        <v>1492203542.26</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>379182068.69</v>
+        <v>379233647.95</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n">
@@ -5112,16 +5112,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>4347249.58</v>
+        <v>4347238.4</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>7628246.93</v>
+        <v>7628227.32</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17374100.29</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>422666732.15</v>
+        <v>422718280.61</v>
       </c>
     </row>
   </sheetData>
@@ -6866,7 +6866,7 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>657777078.52</v>
+        <v>657866554.41</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>12213347.32</v>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226353824.68</v>
+        <v>1226355221.39</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404315919.26</v>
+        <v>1404317315.97</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290713241.4</v>
+        <v>290713672.08</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524811.6</v>
+        <v>524811.72</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360263.029999999</v>
+        <v>9360265.17</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354056222.66</v>
+        <v>354056655.59</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019794241.7</v>
+        <v>1019795144.48</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203199151.21</v>
+        <v>1203200053.99</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223746567.14</v>
+        <v>223746802.03</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516298.66</v>
+        <v>516298.69</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237385.73</v>
+        <v>9237386.32</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289058357.3</v>
+        <v>289058592.82</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766403333.45</v>
+        <v>766406464.95</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882445880.49</v>
+        <v>882449011.99</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197400801.4</v>
+        <v>197401466.43</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374709.01</v>
+        <v>374708.71</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399339.12</v>
+        <v>5399334.85</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239490131.9</v>
+        <v>239490792.37</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983755333</v>
+        <v>983759220.62</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168393482.02</v>
+        <v>1168397369.64</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236059990.15</v>
+        <v>236062007.59</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324585.91</v>
+        <v>324587</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358483.33</v>
+        <v>7358508</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305856643.96</v>
+        <v>305858687.16</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097585809.41</v>
+        <v>1097587146.58</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302665846.99</v>
+        <v>1302667184.16</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250950095.93</v>
+        <v>250950792.74</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709926.99</v>
+        <v>709927.79</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693351.51</v>
+        <v>7693360.18</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328054105.69</v>
+        <v>328054811.97</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011520113.11</v>
+        <v>1011520512.51</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233693232.62</v>
+        <v>1233693632.02</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229524374.05</v>
+        <v>229524540.76</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255743.16</v>
+        <v>1255743.44</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409727.529999999</v>
+        <v>8409729.4</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309199301.4</v>
+        <v>309199470.26</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961937757.6799999</v>
+        <v>961939006.3099999</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145544919.22</v>
+        <v>1145546167.85</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214889305.22</v>
+        <v>214889667.58</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814778.13</v>
+        <v>814778.3</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850541.07</v>
+        <v>6850542.47</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281206469.62</v>
+        <v>281206833.54</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073043987.23</v>
+        <v>1073046088.26</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277709884.71</v>
+        <v>1277711985.74</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240124416.24</v>
+        <v>240125120.68</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353399.23</v>
+        <v>2353400.69</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569912.63</v>
+        <v>7569917.33</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313748205.98</v>
+        <v>313748916.58</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960758292.38</v>
+        <v>960760309.86</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185431609.5</v>
+        <v>1185433626.98</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212544683.62</v>
+        <v>212545363.6</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490145.54</v>
+        <v>2490147.08</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929261.68</v>
+        <v>8929267.199999999</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296179431.55</v>
+        <v>296180118.58</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686500880.05</v>
+        <v>686502406.12</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813412571.08</v>
+        <v>813414097.15</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150989909.12</v>
+        <v>150990336.34</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897061.15</v>
+        <v>1897061.73</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485520.97</v>
+        <v>3485522.05</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196254451.14</v>
+        <v>196254880.02</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970905587.85</v>
+        <v>970906842.2</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130462242.09</v>
+        <v>1130463496.44</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227540097.17</v>
+        <v>227540769.07</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642024.71</v>
+        <v>2642028.07</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513118.73</v>
+        <v>5513125.74</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286537789.06</v>
+        <v>286538471.33</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042725778.39</v>
+        <v>1042728399.49</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244209968.46</v>
+        <v>1244212589.56</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230881491.39</v>
+        <v>230882677.5</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865661.03</v>
+        <v>2865666.29</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026060.9</v>
+        <v>7026073.78</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305686284.77</v>
+        <v>305687489.01</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046517812.32</v>
+        <v>1046519927.38</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268564912.13</v>
+        <v>1268567027.19</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238378237.23</v>
+        <v>238379113.16</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737691.61</v>
+        <v>3737695.91</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838258.39</v>
+        <v>7838267.39</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315844924.03</v>
+        <v>315845813.26</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026514460.66</v>
+        <v>1026516698.6</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228658339.69</v>
+        <v>1228660577.63</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246152401.61</v>
+        <v>246153611.44</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558660.88</v>
+        <v>3558668.3</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537348.83</v>
+        <v>7537364.55</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315572465.47</v>
+        <v>315573698.45</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275207157.27</v>
+        <v>1275209987.96</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517928634.52</v>
+        <v>1517931465.21</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295670168.79</v>
+        <v>295671351.97</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271141.11</v>
+        <v>4271146.69</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581202.300000001</v>
+        <v>9581214.82</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378766508.08</v>
+        <v>378767709.36</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123173594.95</v>
+        <v>1123183253.17</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375348756.28</v>
+        <v>1375358414.5</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251876380.56</v>
+        <v>251880308.02</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520481.73</v>
+        <v>3520498.26</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255698.49</v>
+        <v>11255751.34</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341095517.62</v>
+        <v>341099514.45</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780481352.11</v>
+        <v>780489943.36</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941898197.64</v>
+        <v>941906788.89</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182881767.56</v>
+        <v>182885240.09</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893242.57</v>
+        <v>2893258.5</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978978.86</v>
+        <v>4979006.27</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240365831.93</v>
+        <v>240369347.8</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925203581.79</v>
+        <v>925205422.29</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103206965.61</v>
+        <v>1103208806.11</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208934524.99</v>
+        <v>208935400.05</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099143.27</v>
+        <v>3099148.29</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218659.88</v>
+        <v>6218669.95</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270752838.15</v>
+        <v>270753728.3</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099247673.38</v>
+        <v>1099248824.83</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314547967.2</v>
+        <v>1314549118.65</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244617950.34</v>
+        <v>244618546.65</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671176.93</v>
+        <v>3671180.7</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710525.27</v>
+        <v>7710533.19</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319472073.24</v>
+        <v>319472681.24</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967576658.33</v>
+        <v>967578907.9400001</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190897663.91</v>
+        <v>1190899913.52</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210529104.15</v>
+        <v>210529939.29</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281797.23</v>
+        <v>3281800.83</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536294.02</v>
+        <v>7536302.27</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283812076.07</v>
+        <v>283812923.06</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003061316.64</v>
+        <v>1003066448.36</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198218004.7</v>
+        <v>1198223136.42</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222083526.67</v>
+        <v>222084385.85</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891029.09</v>
+        <v>3891024.14</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335920.41</v>
+        <v>6335912.35</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281014971.09</v>
+        <v>281015817.27</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362268845.18</v>
+        <v>1362270566.61</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634485600.3</v>
+        <v>1634487321.73</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306756849.21</v>
+        <v>306757553.3</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136442.85</v>
+        <v>6136447.73</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270516.32</v>
+        <v>10270524.49</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388015939.88</v>
+        <v>388016657.02</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156869259.79</v>
+        <v>1156874177.6</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409369227.44</v>
+        <v>1409374145.25</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247790965.73</v>
+        <v>247792661.95</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795224.73</v>
+        <v>3795231.53</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929362.66</v>
+        <v>9929380.43</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325988777.91</v>
+        <v>325990498.69</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870256143.75</v>
+        <v>870261061.91</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039360356.12</v>
+        <v>1039365274.28</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193423273.93</v>
+        <v>193424135.7</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256071.47</v>
+        <v>3256067.35</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684219.97</v>
+        <v>5684212.78</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245265376.99</v>
+        <v>245266227.46</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002192402.78</v>
+        <v>1002201934.62</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209529810.74</v>
+        <v>1209539342.58</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>216988295.06</v>
+        <v>216989809.2</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934191.94</v>
+        <v>2934184.36</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937825.58</v>
+        <v>6937807.66</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280960717.65</v>
+        <v>280962206.3</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105916624.63</v>
+        <v>1105921808.35</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351771524.28</v>
+        <v>1351776708</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242470925.59</v>
+        <v>242472365.57</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693242.94</v>
+        <v>2693244.69</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764023.880000001</v>
+        <v>8764029.57</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322784671.41</v>
+        <v>322786118.83</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932806287.76</v>
+        <v>932812084.74</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136754102.21</v>
+        <v>1136759899.19</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196511848.32</v>
+        <v>196514841.97</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927881.38</v>
+        <v>2927900.95</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577743.14</v>
+        <v>6577787.09</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259465814.2</v>
+        <v>259468871.37</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1161982743.92</v>
+        <v>1161988043.71</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354819227.99</v>
+        <v>1354824527.78</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252339558.48</v>
+        <v>252341754.38</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229171.06</v>
+        <v>4229184.67</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541655.62</v>
+        <v>4541670.23</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311952103.79</v>
+        <v>311954327.91</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439958245.9</v>
+        <v>1439965256.89</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740014911.93</v>
+        <v>1740021922.92</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284705883.7</v>
+        <v>284708258.94</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067051.86</v>
+        <v>4067061.45</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978459.28</v>
+        <v>5978473.38</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375576583.7</v>
+        <v>375578982.63</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319653972.29</v>
+        <v>1319674535.76</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579417056.41</v>
+        <v>1579437619.88</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283358020.27</v>
+        <v>283364443.3</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050947.16</v>
+        <v>3050961.75</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438361.14</v>
+        <v>7438396.72</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363598693.09</v>
+        <v>363605166.29</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096954616.23</v>
+        <v>1096967806.98</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1282995642.34</v>
+        <v>1283008833.09</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243414722.2</v>
+        <v>243418195.06</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660614.6</v>
+        <v>1660616.67</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7201997.91</v>
+        <v>7202006.91</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302132226.23</v>
+        <v>302135710.17</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142062265.35</v>
+        <v>1142078180.69</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1365953379.3</v>
+        <v>1365969294.64</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239644699.22</v>
+        <v>239648900.82</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298504.62</v>
+        <v>1298507.33</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234237.189999999</v>
+        <v>9234256.460000001</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307437815.76</v>
+        <v>307442039.34</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192781715.89</v>
+        <v>1192800876.99</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436438722.56</v>
+        <v>1436457883.66</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253610054.34</v>
+        <v>253615502.47</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145277.7</v>
+        <v>2145284.92</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745015.57</v>
+        <v>6745038.25</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327964749.81</v>
+        <v>327970227.84</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226860529.44</v>
+        <v>1226883296.02</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494200820.31</v>
+        <v>1494223586.89</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272927744.95</v>
+        <v>272936846.09</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511754.49</v>
+        <v>2511780.21</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248054.91</v>
+        <v>7248129.12</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361169639.03</v>
+        <v>361178840.1</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348504100.19</v>
+        <v>1348527326.36</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622824244.94</v>
+        <v>1622847471.11</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278401814.92</v>
+        <v>278409409.25</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307474.74</v>
+        <v>2307490.61</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088313.63</v>
+        <v>8088369.25</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361788510.08</v>
+        <v>361796175.89</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778162499.5</v>
+        <v>1778194422.31</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122225561.56</v>
+        <v>2122257484.37</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364455132.67</v>
+        <v>364467833.48</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3918873.86</v>
+        <v>3918922.95</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6646789.65</v>
+        <v>6646872.92</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465473563.95</v>
+        <v>465486397.13</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1363998848.73</v>
+        <v>1364095211.89</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1650768635.33</v>
+        <v>1650864998.49</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283553580.22</v>
+        <v>283593120.97</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4916226.23</v>
+        <v>4916466.23</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7351146.45</v>
+        <v>7351505.32</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374448742.57</v>
+        <v>374488882.2</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1037417563.81</v>
+        <v>1037598689.64</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1346794280.6</v>
+        <v>1346975406.43</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218250616.18</v>
+        <v>218311513.12</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3628124.23</v>
+        <v>3628339.72</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4590859.92</v>
+        <v>4591132.59</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316598173.81</v>
+        <v>316659558.91</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,9 +2810,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1048928677.83</v>
-      </c>
-      <c r="C41" s="6" t="n"/>
+        <v>1142879355.12</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>155233679.84</v>
+      </c>
       <c r="D41" s="6" t="n">
         <v>30068575.81</v>
       </c>
@@ -2829,12 +2831,14 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1172177417.6</v>
+        <v>1421361774.73</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>221815486.88</v>
-      </c>
-      <c r="K41" s="9" t="n"/>
+        <v>227960732.84</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>45723993.31</v>
+      </c>
       <c r="L41" s="9" t="n">
         <v>8900667.25</v>
       </c>
@@ -2842,23 +2846,77 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3429818.04</v>
+        <v>3387327.19</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5589001.05</v>
+        <v>5519760.81</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>261983497.84</v>
+        <v>313741006.02</v>
       </c>
       <c r="R41" s="10" t="n">
-        <v>0.4468039425501122</v>
+        <v>0.3586814200401954</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>1285208873.67</v>
+      </c>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n">
+        <v>36982193.7</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>34479215</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>12699402.55</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>33261296</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>55348498</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>1457979478.92</v>
+      </c>
+      <c r="J42" s="8" t="n">
+        <v>266151290.41</v>
+      </c>
+      <c r="K42" s="9" t="n"/>
+      <c r="L42" s="9" t="n">
+        <v>13379956.09</v>
+      </c>
+      <c r="M42" s="9" t="n">
+        <v>9926271.91</v>
+      </c>
+      <c r="N42" s="9" t="n">
+        <v>2843196.41</v>
+      </c>
+      <c r="O42" s="9" t="n">
+        <v>7446680.82</v>
+      </c>
+      <c r="P42" s="9" t="n">
+        <v>26671269.08</v>
+      </c>
+      <c r="Q42" s="9" t="n">
+        <v>326418664.73</v>
+      </c>
+      <c r="R42" s="10" t="n">
+        <v>0.4221353362955425</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R41"/>
+  <autoFilter ref="A2:R42"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -2874,7 +2932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5080,9 +5138,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1366115446.49</v>
-      </c>
-      <c r="C41" s="6" t="n"/>
+        <v>1560000000</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>156390621.69</v>
+      </c>
       <c r="D41" s="6" t="n">
         <v>30068575.81</v>
       </c>
@@ -5099,12 +5159,14 @@
         <v>36473569</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1492203542.26</v>
+        <v>1842478717.46</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>379233647.95</v>
-      </c>
-      <c r="K41" s="9" t="n"/>
+        <v>433056000</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>45961726.06</v>
+      </c>
       <c r="L41" s="9" t="n">
         <v>8900667.25</v>
       </c>
@@ -5112,20 +5174,71 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>4347238.4</v>
+        <v>4351982.42</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>7628227.32</v>
+        <v>7636551.78</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17374100.29</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>422718280.61</v>
+        <v>522515427.2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>1679626074.74</v>
+      </c>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n">
+        <v>36982193.7</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>34479215</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>12699402.55</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>35774746</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>56166007</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>1855727638.99</v>
+      </c>
+      <c r="J42" s="8" t="n">
+        <v>466264198.35</v>
+      </c>
+      <c r="K42" s="9" t="n"/>
+      <c r="L42" s="9" t="n">
+        <v>13379956.09</v>
+      </c>
+      <c r="M42" s="9" t="n">
+        <v>9926271.91</v>
+      </c>
+      <c r="N42" s="9" t="n">
+        <v>3629726.05</v>
+      </c>
+      <c r="O42" s="9" t="n">
+        <v>10225089.48</v>
+      </c>
+      <c r="P42" s="9" t="n">
+        <v>26976320.04</v>
+      </c>
+      <c r="Q42" s="9" t="n">
+        <v>530401561.92</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q41"/>
+  <autoFilter ref="A2:Q42"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -5140,7 +5253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6497,7 +6610,7 @@
         <v>12728635</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>0.6204</v>
+        <v>0.6203</v>
       </c>
       <c r="I32" s="11" t="n">
         <v>0.3658</v>
@@ -6841,7 +6954,7 @@
         <v>7061846</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>0.6313</v>
+        <v>0.6312</v>
       </c>
       <c r="I40" s="11" t="n">
         <v>0.3536</v>
@@ -6866,7 +6979,7 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>657866554.41</v>
+        <v>751233600</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>12213347.32</v>
@@ -6874,7 +6987,9 @@
       <c r="D41" s="6" t="n">
         <v>7654521</v>
       </c>
-      <c r="E41" s="6" t="n"/>
+      <c r="E41" s="6" t="n">
+        <v>47959054.65</v>
+      </c>
       <c r="F41" s="6" t="n">
         <v>10065487.41</v>
       </c>
@@ -6882,7 +6997,7 @@
         <v>9247924</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>0.6272</v>
+        <v>0.6573</v>
       </c>
       <c r="I41" s="11" t="n">
         <v>0.4061999999999999</v>
@@ -6890,7 +7005,9 @@
       <c r="J41" s="11" t="n">
         <v>0.4432</v>
       </c>
-      <c r="K41" s="11" t="n"/>
+      <c r="K41" s="11" t="n">
+        <v>0.3089</v>
+      </c>
       <c r="L41" s="11" t="n">
         <v>0.6559</v>
       </c>
@@ -6898,15 +7015,54 @@
         <v>0.3698</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>808840732.55</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>13331547.8</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>14834012</v>
+      </c>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n">
+        <v>6213065.03</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>15189926</v>
+      </c>
+      <c r="H42" s="11" t="n">
+        <v>0.6293</v>
+      </c>
+      <c r="I42" s="11" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="J42" s="11" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="K42" s="11" t="n"/>
+      <c r="L42" s="11" t="n">
+        <v>0.4892</v>
+      </c>
+      <c r="M42" s="11" t="n">
+        <v>0.4567</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M41"/>
+  <autoFilter ref="A2:M42"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -6937,7 +7093,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-09. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-10. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766406464.95</v>
+        <v>766406465.95</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882449011.99</v>
+        <v>882449012.99</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197401466.43</v>
+        <v>197401466.8</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -767,7 +767,7 @@
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239490792.37</v>
+        <v>239490792.74</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983759220.62</v>
+        <v>983759222.62</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168397369.64</v>
+        <v>1168397371.64</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236062007.59</v>
+        <v>236062008.96</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -819,13 +819,13 @@
         <v>324587</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358508</v>
+        <v>7358508.02</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305858687.16</v>
+        <v>305858688.55</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097587146.58</v>
+        <v>1097587155.58</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302667184.16</v>
+        <v>1302667193.16</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250950792.74</v>
+        <v>250950796.96</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -877,13 +877,13 @@
         <v>709927.79</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693360.18</v>
+        <v>7693360.23</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328054811.97</v>
+        <v>328054816.24</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011520512.51</v>
+        <v>1011520522.51</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233693632.02</v>
+        <v>1233693642.02</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229524540.76</v>
+        <v>229524545.36</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255743.44</v>
+        <v>1255743.45</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409729.4</v>
+        <v>8409729.460000001</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309199470.26</v>
+        <v>309199474.93</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961939006.3099999</v>
+        <v>961939026.3099999</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145546167.85</v>
+        <v>1145546187.85</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214889667.58</v>
+        <v>214889674.48</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -993,13 +993,13 @@
         <v>814778.3</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850542.47</v>
+        <v>6850542.52</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281206833.54</v>
+        <v>281206840.5</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960760309.86</v>
+        <v>960760389.64</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185433626.98</v>
+        <v>1185433706.76</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212545363.6</v>
+        <v>212545394.72</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490147.08</v>
+        <v>2490147.18</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929267.199999999</v>
+        <v>8929267.550000001</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296180118.58</v>
+        <v>296180150.15</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686502406.12</v>
+        <v>686502416.12</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813414097.15</v>
+        <v>813414107.15</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150990336.34</v>
+        <v>150990338.24</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1167,13 +1167,13 @@
         <v>1897061.73</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485522.05</v>
+        <v>3485522.04</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196254880.02</v>
+        <v>196254881.91</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046519927.38</v>
+        <v>1046520444.38</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268567027.19</v>
+        <v>1268567544.19</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238379113.16</v>
+        <v>238379190.81</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737695.91</v>
+        <v>3737695.28</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838267.39</v>
+        <v>7838266.07</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315845813.26</v>
+        <v>315845888.96</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026516698.6</v>
+        <v>1026516711.6</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228660577.63</v>
+        <v>1228660590.63</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246153611.44</v>
+        <v>246153613.09</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558668.3</v>
+        <v>3558668.28</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537364.55</v>
+        <v>7537364.5</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315573698.45</v>
+        <v>315573700.04</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275209987.96</v>
+        <v>1275210269</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517931465.21</v>
+        <v>1517931746.25</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295671351.97</v>
+        <v>295671421.72</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1457,13 +1457,13 @@
         <v>4271146.69</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581214.82</v>
+        <v>9581214.810000001</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378767709.36</v>
+        <v>378767779.1</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123183253.17</v>
+        <v>1123184587.2</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375358414.5</v>
+        <v>1375359748.53</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251880308.02</v>
+        <v>251880657.76</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520498.26</v>
+        <v>3520498.46</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255751.34</v>
+        <v>11255751.99</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341099514.45</v>
+        <v>341099865.05</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780489943.36</v>
+        <v>780491807.51</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941906788.89</v>
+        <v>941908653.04</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182885240.09</v>
+        <v>182885658.84</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893258.5</v>
+        <v>2893257.8</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4979006.27</v>
+        <v>4979005.05</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240369347.8</v>
+        <v>240369764.62</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925205422.29</v>
+        <v>925205491.0700001</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103208806.11</v>
+        <v>1103208874.89</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208935400.05</v>
+        <v>208935415.85</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099148.29</v>
+        <v>3099148.28</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218669.95</v>
+        <v>6218669.92</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270753728.3</v>
+        <v>270753744.06</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099248824.83</v>
+        <v>1099248998.09</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314549118.65</v>
+        <v>1314549291.91</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244618546.65</v>
+        <v>244618586.5</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671180.7</v>
+        <v>3671180.67</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710533.19</v>
+        <v>7710533.14</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319472681.24</v>
+        <v>319472721.01</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967578907.9400001</v>
+        <v>967578919.9400001</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190899913.52</v>
+        <v>1190899925.52</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210529939.29</v>
+        <v>210529942.06</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1753,7 +1753,7 @@
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283812923.06</v>
+        <v>283812925.83</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003066448.36</v>
+        <v>1003066466.36</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198223136.42</v>
+        <v>1198223154.42</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222084385.85</v>
+        <v>222084389.45</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891024.14</v>
+        <v>3891024.13</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335912.35</v>
+        <v>6335912.33</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281015817.27</v>
+        <v>281015820.85</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362270566.61</v>
+        <v>1362271000.88</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634487321.73</v>
+        <v>1634487756</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306757553.3</v>
+        <v>306757603.5</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136447.73</v>
+        <v>6136446.85</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270524.49</v>
+        <v>10270523.03</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388016657.02</v>
+        <v>388016704.88</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156874177.6</v>
+        <v>1156875800.15</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409374145.25</v>
+        <v>1409375767.8</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247792661.95</v>
+        <v>247793098.33</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795231.53</v>
+        <v>3795232.27</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929380.43</v>
+        <v>9929382.369999999</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325990498.69</v>
+        <v>325990937.75</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002201934.62</v>
+        <v>1002203801.62</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209539342.58</v>
+        <v>1209541209.58</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>216989809.2</v>
+        <v>216990051.91</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934184.36</v>
+        <v>2934182.29</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937807.66</v>
+        <v>6937802.77</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280962206.3</v>
+        <v>280962442.06</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105921808.35</v>
+        <v>1105922775.04</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351776708</v>
+        <v>1351777674.69</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242472365.57</v>
+        <v>242472513.08</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693244.69</v>
+        <v>2693243.97</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764029.57</v>
+        <v>8764027.23</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322786118.83</v>
+        <v>322786263.28</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932812084.74</v>
+        <v>932812373.74</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136759899.19</v>
+        <v>1136760188.19</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196514841.97</v>
+        <v>196514882.43</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927900.95</v>
+        <v>2927900.65</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577787.09</v>
+        <v>6577786.42</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259468871.37</v>
+        <v>259468910.86</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1161988043.71</v>
+        <v>1161988230.22</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354824527.78</v>
+        <v>1354824714.29</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252341754.38</v>
+        <v>252341790.98</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229184.67</v>
+        <v>4229184.58</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541670.23</v>
+        <v>4541670.14</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311954327.91</v>
+        <v>311954364.33</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439965256.89</v>
+        <v>1439965383.62</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740021922.92</v>
+        <v>1740022049.65</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284708258.94</v>
+        <v>284708274</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067061.45</v>
+        <v>4067061.32</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978473.38</v>
+        <v>5978473.17</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375578982.63</v>
+        <v>375578997.35</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319674535.76</v>
+        <v>1319675252.13</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579437619.88</v>
+        <v>1579438336.25</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283364443.3</v>
+        <v>283364502.44</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050961.75</v>
+        <v>3050960.84</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438396.72</v>
+        <v>7438394.49</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363605166.29</v>
+        <v>363605222.29</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096967806.98</v>
+        <v>1096968161.64</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283008833.09</v>
+        <v>1283009187.75</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243418195.06</v>
+        <v>243418286.29</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660616.67</v>
+        <v>1660616.72</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202006.91</v>
+        <v>7202007.1</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302135710.17</v>
+        <v>302135801.63</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142078180.69</v>
+        <v>1142079314.33</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1365969294.64</v>
+        <v>1365970428.28</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239648900.82</v>
+        <v>239649187.65</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298507.33</v>
+        <v>1298507.46</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234256.460000001</v>
+        <v>9234257.439999999</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307442039.34</v>
+        <v>307442327.3</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192800876.99</v>
+        <v>1192802384.99</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436457883.66</v>
+        <v>1436459391.66</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253615502.47</v>
+        <v>253615902.17</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145284.92</v>
+        <v>2145285.29</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745038.25</v>
+        <v>6745039.43</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327970227.84</v>
+        <v>327970629.09</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226883296.02</v>
+        <v>1226885672.79</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494223586.89</v>
+        <v>1494225963.66</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272936846.09</v>
+        <v>272937752.95</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511780.21</v>
+        <v>2511782.59</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248129.12</v>
+        <v>7248135.98</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361178840.1</v>
+        <v>361179756.19</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348527326.36</v>
+        <v>1348528088.63</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622847471.11</v>
+        <v>1622848233.38</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278409409.25</v>
+        <v>278409667.02</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307490.61</v>
+        <v>2307491.18</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088369.25</v>
+        <v>8088371.27</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361796175.89</v>
+        <v>361796436.26</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778194422.31</v>
+        <v>1778195398.27</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122257484.37</v>
+        <v>2122258460.33</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364467833.48</v>
+        <v>364468378.04</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3918922.95</v>
+        <v>3918925.8</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6646872.92</v>
+        <v>6646877.75</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465486397.13</v>
+        <v>465486949.36</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364095211.89</v>
+        <v>1364101298.6</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1650864998.49</v>
+        <v>1650871085.2</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283593120.97</v>
+        <v>283596040.84</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4916466.23</v>
+        <v>4916487.12</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7351505.32</v>
+        <v>7351536.56</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374488882.2</v>
+        <v>374491854.2</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1037598689.64</v>
+        <v>1037609194.13</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1346975406.43</v>
+        <v>1346985910.92</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218311513.12</v>
+        <v>218317046.39</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3628339.72</v>
+        <v>3628375.76</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4591132.59</v>
+        <v>4591178.2</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316659558.91</v>
+        <v>316665173.83</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1142879355.12</v>
+        <v>1142898332.89</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1421361774.73</v>
+        <v>1421380752.5</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>227960732.84</v>
+        <v>227965252.08</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3387327.19</v>
+        <v>3387330.86</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5519760.81</v>
+        <v>5519766.79</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>313741006.02</v>
+        <v>313745534.9</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1285208873.67</v>
+        <v>1285319982.97</v>
       </c>
       <c r="C42" s="6" t="n"/>
       <c r="D42" s="6" t="n">
@@ -2887,10 +2887,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1457979478.92</v>
+        <v>1458090588.22</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>266151290.41</v>
+        <v>266173108.82</v>
       </c>
       <c r="K42" s="9" t="n"/>
       <c r="L42" s="9" t="n">
@@ -2900,16 +2900,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2843196.41</v>
+        <v>2843168.92</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7446680.82</v>
+        <v>7446608.81</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>326418664.73</v>
+        <v>326440383.63</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.4221353362955425</v>
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1679626074.74</v>
+        <v>1679762914.42</v>
       </c>
       <c r="C42" s="6" t="n"/>
       <c r="D42" s="6" t="n">
@@ -5212,10 +5212,10 @@
         <v>56166007</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1855727638.99</v>
+        <v>1855864478.67</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>466264198.35</v>
+        <v>466302185.04</v>
       </c>
       <c r="K42" s="9" t="n"/>
       <c r="L42" s="9" t="n">
@@ -5225,16 +5225,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>3629726.05</v>
+        <v>3629718.15</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>10225089.48</v>
+        <v>10225067.22</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26976320.04</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>530401561.92</v>
+        <v>530439518.44</v>
       </c>
     </row>
   </sheetData>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>808840732.55</v>
+        <v>808906629.0700001</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>13331547.8</v>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226355221.39</v>
+        <v>1226356139.32</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404317315.97</v>
+        <v>1404318233.9</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290713672.08</v>
+        <v>290713845.16</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524811.72</v>
+        <v>524811.63</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360265.17</v>
+        <v>9360263.58</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354056655.59</v>
+        <v>354056827</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019795144.48</v>
+        <v>1019796762.15</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203200053.99</v>
+        <v>1203201671.66</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223746802.03</v>
+        <v>223746932.49</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516298.69</v>
+        <v>516298.21</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237386.32</v>
+        <v>9237377.779999999</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289058592.82</v>
+        <v>289058714.26</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766406465.95</v>
+        <v>766406536.08</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882449012.99</v>
+        <v>882449083.12</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197401466.8</v>
+        <v>197401499.15</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374708.71</v>
+        <v>374708.73</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399334.85</v>
+        <v>5399335.16</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239490792.74</v>
+        <v>239490825.42</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983759222.62</v>
+        <v>983759487.78</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168397371.64</v>
+        <v>1168397636.8</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236062008.96</v>
+        <v>236062105.8</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324587</v>
+        <v>324587.03</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358508.02</v>
+        <v>7358508.7</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305858688.55</v>
+        <v>305858786.1</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097587155.58</v>
+        <v>1097587673.77</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302667193.16</v>
+        <v>1302667711.35</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250950796.96</v>
+        <v>250950831.81</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.79</v>
+        <v>709927.58</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693360.23</v>
+        <v>7693357.93</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328054816.24</v>
+        <v>328054848.58</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011520522.51</v>
+        <v>1011521623.45</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233693642.02</v>
+        <v>1233694742.96</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229524545.36</v>
+        <v>229525448.1</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255743.45</v>
+        <v>1255746.08</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409729.460000001</v>
+        <v>8409747.060000001</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309199474.93</v>
+        <v>309200397.89</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961939026.3099999</v>
+        <v>961939751.03</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145546187.85</v>
+        <v>1145546912.57</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214889674.48</v>
+        <v>214889945.11</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814778.3</v>
+        <v>814778.58</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850542.52</v>
+        <v>6850544.84</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281206840.5</v>
+        <v>281207113.73</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073046088.26</v>
+        <v>1073046768.36</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277711985.74</v>
+        <v>1277712665.84</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240125120.68</v>
+        <v>240125278.98</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353400.69</v>
+        <v>2353400.62</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569917.33</v>
+        <v>7569917.11</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313748916.58</v>
+        <v>313749074.6</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960760389.64</v>
+        <v>960761125.99</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185433706.76</v>
+        <v>1185434443.11</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212545394.72</v>
+        <v>212545774.99</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490147.18</v>
+        <v>2490148.9</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929267.550000001</v>
+        <v>8929273.710000001</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296180150.15</v>
+        <v>296180538.29</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686502416.12</v>
+        <v>686503350.9</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813414107.15</v>
+        <v>813415041.9299999</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150990338.24</v>
+        <v>150990755.37</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897061.73</v>
+        <v>1897063.63</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485522.04</v>
+        <v>3485525.54</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196254881.91</v>
+        <v>196255304.44</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970906842.2</v>
+        <v>970907334.3099999</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130463496.44</v>
+        <v>1130463988.55</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227540769.07</v>
+        <v>227540890.05</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642028.07</v>
+        <v>2642028.04</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513125.74</v>
+        <v>5513125.66</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286538471.33</v>
+        <v>286538592.2</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042728399.49</v>
+        <v>1042728700.46</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244212589.56</v>
+        <v>1244212890.53</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230882677.5</v>
+        <v>230882769.76</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865666.29</v>
+        <v>2865666.46</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026073.78</v>
+        <v>7026074.22</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305687489.01</v>
+        <v>305687581.88</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046520444.38</v>
+        <v>1046522868.23</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268567544.19</v>
+        <v>1268569968.04</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238379190.81</v>
+        <v>238379561.6</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737695.28</v>
+        <v>3737692.42</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838266.07</v>
+        <v>7838260.08</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315845888.96</v>
+        <v>315846250.9</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026516711.6</v>
+        <v>1026517344.04</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228660590.63</v>
+        <v>1228661223.07</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246153613.09</v>
+        <v>246154020.5</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558668.28</v>
+        <v>3558671.14</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537364.5</v>
+        <v>7537370.57</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315573700.04</v>
+        <v>315574116.37</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275210269</v>
+        <v>1275212922.59</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517931746.25</v>
+        <v>1517934399.84</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295671421.72</v>
+        <v>295672253.91</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271146.69</v>
+        <v>4271148.68</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581214.810000001</v>
+        <v>9581219.27</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378767779.1</v>
+        <v>378768617.74</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123184587.2</v>
+        <v>1123189412.99</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375359748.53</v>
+        <v>1375364574.32</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251880657.76</v>
+        <v>251883669.46</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520498.46</v>
+        <v>3520518.04</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255751.99</v>
+        <v>11255814.59</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341099865.05</v>
+        <v>341102958.93</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780491807.51</v>
+        <v>780493646.95</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941908653.04</v>
+        <v>941910492.48</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182885658.84</v>
+        <v>182886808.12</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893257.8</v>
+        <v>2893266.26</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4979005.05</v>
+        <v>4979019.61</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240369764.62</v>
+        <v>240370936.92</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925205491.0700001</v>
+        <v>925209703.76</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103208874.89</v>
+        <v>1103213087.58</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208935415.85</v>
+        <v>208936450.31</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099148.28</v>
+        <v>3099148.29</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218669.92</v>
+        <v>6218669.94</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270753744.06</v>
+        <v>270754778.54</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099248998.09</v>
+        <v>1099253491.31</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314549291.91</v>
+        <v>1314553785.13</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244618586.5</v>
+        <v>244619837.59</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671180.67</v>
+        <v>3671182.57</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710533.14</v>
+        <v>7710537.12</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319472721.01</v>
+        <v>319473977.98</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967578919.9400001</v>
+        <v>967580843.71</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190899925.52</v>
+        <v>1190901849.29</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210529942.06</v>
+        <v>210530668.01</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281800.83</v>
+        <v>3281804.04</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536302.27</v>
+        <v>7536309.65</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283812925.83</v>
+        <v>283813662.38</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003066466.36</v>
+        <v>1003067287.81</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198223154.42</v>
+        <v>1198223975.87</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222084389.45</v>
+        <v>222084703.64</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891024.13</v>
+        <v>3891025.88</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335912.33</v>
+        <v>6335915.18</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281015820.85</v>
+        <v>281016139.63</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362271000.88</v>
+        <v>1362275308.88</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634487756</v>
+        <v>1634492064</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306757603.5</v>
+        <v>306759543.49</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136446.85</v>
+        <v>6136462</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270523.03</v>
+        <v>10270548.38</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388016704.88</v>
+        <v>388018685.37</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156875800.15</v>
+        <v>1156881181.61</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409375767.8</v>
+        <v>1409381149.26</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247793098.33</v>
+        <v>247794400.83</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795232.27</v>
+        <v>3795232.97</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929382.369999999</v>
+        <v>9929384.210000001</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325990937.75</v>
+        <v>325992242.79</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870261061.91</v>
+        <v>870268692.91</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039365274.28</v>
+        <v>1039372905.28</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193424135.7</v>
+        <v>193425813.16</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256067.35</v>
+        <v>3256065.65</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684212.78</v>
+        <v>5684209.82</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245266227.46</v>
+        <v>245267900.26</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002203801.62</v>
+        <v>1002218062.44</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209541209.58</v>
+        <v>1209555470.4</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>216990051.91</v>
+        <v>216992548.28</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934182.29</v>
+        <v>2934173.46</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937802.77</v>
+        <v>6937781.88</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280962442.06</v>
+        <v>280964908.7</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105922775.04</v>
+        <v>1105931068.75</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351777674.69</v>
+        <v>1351785968.4</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242472513.08</v>
+        <v>242474160.28</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693243.97</v>
+        <v>2693241.09</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764027.23</v>
+        <v>8764017.85</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322786263.28</v>
+        <v>322787898.21</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932812373.74</v>
+        <v>932821797.2</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136760188.19</v>
+        <v>1136769611.65</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196514882.43</v>
+        <v>196518485.91</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927900.65</v>
+        <v>2927917.66</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577786.42</v>
+        <v>6577824.65</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259468910.86</v>
+        <v>259472569.58</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1161988230.22</v>
+        <v>1161996524.21</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354824714.29</v>
+        <v>1354833008.28</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252341790.98</v>
+        <v>252343621.78</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229184.58</v>
+        <v>4229183.48</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541670.14</v>
+        <v>4541668.95</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311954364.33</v>
+        <v>311956192.84</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439965383.62</v>
+        <v>1439971081.63</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740022049.65</v>
+        <v>1740027747.66</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284708274</v>
+        <v>284710378.16</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067061.32</v>
+        <v>4067071.04</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978473.17</v>
+        <v>5978487.47</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375578997.35</v>
+        <v>375581125.54</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319675252.13</v>
+        <v>1319683463.06</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579438336.25</v>
+        <v>1579446547.18</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283364502.44</v>
+        <v>283367272.44</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050960.84</v>
+        <v>3050968.44</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438394.49</v>
+        <v>7438413.03</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363605222.29</v>
+        <v>363608018.42</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096968161.64</v>
+        <v>1096971334.04</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283009187.75</v>
+        <v>1283012360.15</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243418286.29</v>
+        <v>243419590.78</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660616.72</v>
+        <v>1660619.87</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202007.1</v>
+        <v>7202020.79</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302135801.63</v>
+        <v>302137122.97</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142079314.33</v>
+        <v>1142088309.67</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1365970428.28</v>
+        <v>1365979423.62</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239649187.65</v>
+        <v>239651704.02</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298507.46</v>
+        <v>1298509.62</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234257.439999999</v>
+        <v>9234272.73</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307442327.3</v>
+        <v>307444861.11</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192802384.99</v>
+        <v>1192810903.06</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436459391.66</v>
+        <v>1436467909.73</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253615902.17</v>
+        <v>253618930.81</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145285.29</v>
+        <v>2145292.58</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745039.43</v>
+        <v>6745062.34</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327970629.09</v>
+        <v>327973687.92</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226885672.79</v>
+        <v>1226893555.18</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494225963.66</v>
+        <v>1494233846.05</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272937752.95</v>
+        <v>272940065.37</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511782.59</v>
+        <v>2511785.5</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248135.98</v>
+        <v>7248144.37</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361179756.19</v>
+        <v>361182079.92</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348528088.63</v>
+        <v>1348545732.33</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622848233.38</v>
+        <v>1622865877.08</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278409667.02</v>
+        <v>278414263.58</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307491.18</v>
+        <v>2307495.54</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088371.27</v>
+        <v>8088386.53</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361796436.26</v>
+        <v>361801052.44</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778195398.27</v>
+        <v>1778221660.06</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122258460.33</v>
+        <v>2122284722.12</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364468378.04</v>
+        <v>364477119.18</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3918925.8</v>
+        <v>3918951.48</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6646877.75</v>
+        <v>6646921.31</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465486949.36</v>
+        <v>465495759.74</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364101298.6</v>
+        <v>1364162952.26</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1650871085.2</v>
+        <v>1650932738.86</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283596040.84</v>
+        <v>283619638.86</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4916487.12</v>
+        <v>4916617.58</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7351536.56</v>
+        <v>7351731.64</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374491854.2</v>
+        <v>374515777.76</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1037609194.13</v>
+        <v>1037704889.71</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1346985910.92</v>
+        <v>1347081606.5</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218317046.39</v>
+        <v>218350489.46</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3628375.76</v>
+        <v>3628504.51</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4591178.2</v>
+        <v>4591341.11</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316665173.83</v>
+        <v>316698908.56</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1142898332.89</v>
+        <v>1143111126.84</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1421380752.5</v>
+        <v>1421593546.45</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>227965252.08</v>
+        <v>228040636.42</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3387330.86</v>
+        <v>3387646.54</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5519766.79</v>
+        <v>5520281.2</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>313745534.9</v>
+        <v>313821749.34</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,9 +2868,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1285319982.97</v>
-      </c>
-      <c r="C42" s="6" t="n"/>
+        <v>1338824453.76</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>202803300.35</v>
+      </c>
       <c r="D42" s="6" t="n">
         <v>36982193.7</v>
       </c>
@@ -2887,12 +2889,14 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1458090588.22</v>
+        <v>1714398359.36</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>266173108.82</v>
-      </c>
-      <c r="K42" s="9" t="n"/>
+        <v>269710714.63</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>59467972.27</v>
+      </c>
       <c r="L42" s="9" t="n">
         <v>13379956.09</v>
       </c>
@@ -2900,23 +2904,77 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2843168.92</v>
+        <v>2885967.59</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7446608.81</v>
+        <v>7558703.79</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>326440383.63</v>
+        <v>389600855.35</v>
       </c>
       <c r="R42" s="10" t="n">
-        <v>0.4221353362955425</v>
+        <v>0.3748043859905762</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>1030603566.63</v>
+      </c>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n">
+        <v>31660988.96</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>41803224</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>12387810.53</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>33785000</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>48290841</v>
+      </c>
+      <c r="I43" s="7" t="n">
+        <v>1198531431.12</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>210602244.46</v>
+      </c>
+      <c r="K43" s="9" t="n"/>
+      <c r="L43" s="9" t="n">
+        <v>8080178.7</v>
+      </c>
+      <c r="M43" s="9" t="n">
+        <v>10508877.38</v>
+      </c>
+      <c r="N43" s="9" t="n">
+        <v>2703549.64</v>
+      </c>
+      <c r="O43" s="9" t="n">
+        <v>7373330.78</v>
+      </c>
+      <c r="P43" s="9" t="n">
+        <v>22302595.9</v>
+      </c>
+      <c r="Q43" s="9" t="n">
+        <v>261570776.87</v>
+      </c>
+      <c r="R43" s="10" t="n">
+        <v>0.4394700544002308</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R42"/>
+  <autoFilter ref="A2:R43"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -2932,7 +2990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5193,9 +5251,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1679762914.42</v>
-      </c>
-      <c r="C42" s="6" t="n"/>
+        <v>1790000000</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>203922586.92</v>
+      </c>
       <c r="D42" s="6" t="n">
         <v>36982193.7</v>
       </c>
@@ -5212,12 +5272,14 @@
         <v>56166007</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1855864478.67</v>
+        <v>2170024151.17</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>466302185.04</v>
-      </c>
-      <c r="K42" s="9" t="n"/>
+        <v>496904000</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>59745247.93</v>
+      </c>
       <c r="L42" s="9" t="n">
         <v>13379956.09</v>
       </c>
@@ -5225,20 +5287,71 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>3629718.15</v>
+        <v>3633037.73</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>10225067.22</v>
+        <v>10234418.62</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26976320.04</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>530439518.44</v>
+        <v>620799252.3099999</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>1348571137.83</v>
+      </c>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n">
+        <v>31660988.96</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>41803224</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>12387810.53</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>37360842</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>49898532</v>
+      </c>
+      <c r="I43" s="7" t="n">
+        <v>1521682535.32</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>374363347.86</v>
+      </c>
+      <c r="K43" s="9" t="n"/>
+      <c r="L43" s="9" t="n">
+        <v>8080178.7</v>
+      </c>
+      <c r="M43" s="9" t="n">
+        <v>10508877.38</v>
+      </c>
+      <c r="N43" s="9" t="n">
+        <v>3500592.09</v>
+      </c>
+      <c r="O43" s="9" t="n">
+        <v>10557561.23</v>
+      </c>
+      <c r="P43" s="9" t="n">
+        <v>22991971.37</v>
+      </c>
+      <c r="Q43" s="9" t="n">
+        <v>430002528.63</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q42"/>
+  <autoFilter ref="A2:Q43"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -5253,7 +5366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6352,7 +6465,7 @@
         <v>7232750</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.6198</v>
+        <v>0.6197</v>
       </c>
       <c r="I26" s="11" t="n">
         <v>0.3647</v>
@@ -6911,7 +7024,7 @@
         <v>12319196</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>0.6249</v>
+        <v>0.6248</v>
       </c>
       <c r="I39" s="11" t="n">
         <v>0.3315</v>
@@ -6954,7 +7067,7 @@
         <v>7061846</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>0.6312</v>
+        <v>0.6311</v>
       </c>
       <c r="I40" s="11" t="n">
         <v>0.3536</v>
@@ -6997,7 +7110,7 @@
         <v>9247924</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>0.6573</v>
+        <v>0.6572</v>
       </c>
       <c r="I41" s="11" t="n">
         <v>0.4061999999999999</v>
@@ -7022,7 +7135,7 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>808906629.0700001</v>
+        <v>861992400</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>13331547.8</v>
@@ -7030,7 +7143,9 @@
       <c r="D42" s="6" t="n">
         <v>14834012</v>
       </c>
-      <c r="E42" s="6" t="n"/>
+      <c r="E42" s="6" t="n">
+        <v>70453371.34999999</v>
+      </c>
       <c r="F42" s="6" t="n">
         <v>6213065.03</v>
       </c>
@@ -7038,7 +7153,7 @@
         <v>15189926</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>0.6293</v>
+        <v>0.6437999999999999</v>
       </c>
       <c r="I42" s="11" t="n">
         <v>0.3605</v>
@@ -7046,7 +7161,9 @@
       <c r="J42" s="11" t="n">
         <v>0.4302</v>
       </c>
-      <c r="K42" s="11" t="n"/>
+      <c r="K42" s="11" t="n">
+        <v>0.3474</v>
+      </c>
       <c r="L42" s="11" t="n">
         <v>0.4892</v>
       </c>
@@ -7054,15 +7171,54 @@
         <v>0.4567</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>649417917.13</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>10973579.3</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>22453189</v>
+      </c>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n">
+        <v>5738340.25</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>13411796</v>
+      </c>
+      <c r="H43" s="11" t="n">
+        <v>0.6301</v>
+      </c>
+      <c r="I43" s="11" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="J43" s="11" t="n">
+        <v>0.5371</v>
+      </c>
+      <c r="K43" s="11" t="n"/>
+      <c r="L43" s="11" t="n">
+        <v>0.4632</v>
+      </c>
+      <c r="M43" s="11" t="n">
+        <v>0.397</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M42"/>
+  <autoFilter ref="A2:M43"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -7093,7 +7249,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-10. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-11. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026517344.04</v>
+        <v>1026517381.04</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228661223.07</v>
+        <v>1228661260.07</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246154020.5</v>
+        <v>246154024.74</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558671.14</v>
+        <v>3558671.08</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537370.57</v>
+        <v>7537370.44</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315574116.37</v>
+        <v>315574120.42</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275212922.59</v>
+        <v>1275214012.59</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517934399.84</v>
+        <v>1517935489.84</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295672253.91</v>
+        <v>295672417.41</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271148.68</v>
+        <v>4271147.41</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581219.27</v>
+        <v>9581216.42</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378768617.74</v>
+        <v>378768777.12</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780493646.95</v>
+        <v>780493687.48</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941910492.48</v>
+        <v>941910533.01</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182886808.12</v>
+        <v>182886832.44</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893266.26</v>
+        <v>2893266.43</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4979019.61</v>
+        <v>4979019.91</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240370936.92</v>
+        <v>240370961.71</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967580843.71</v>
+        <v>967580890.71</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190901849.29</v>
+        <v>1190901896.29</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210530668.01</v>
+        <v>210530677.41</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281804.04</v>
+        <v>3281804.02</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536309.65</v>
+        <v>7536309.6</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283813662.38</v>
+        <v>283813671.7</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156881181.61</v>
+        <v>1156881190.12</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409381149.26</v>
+        <v>1409381157.77</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247794400.83</v>
+        <v>247794405.68</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795232.97</v>
+        <v>3795233</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929384.210000001</v>
+        <v>9929384.300000001</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325992242.79</v>
+        <v>325992247.77</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870268692.91</v>
+        <v>870268733.4400001</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039372905.28</v>
+        <v>1039372945.81</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193425813.16</v>
+        <v>193425825.72</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256065.65</v>
+        <v>3256065.69</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684209.82</v>
+        <v>5684209.89</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245267900.26</v>
+        <v>245267912.93</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002218062.44</v>
+        <v>1002218105.74</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209555470.4</v>
+        <v>1209555513.7</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>216992548.28</v>
+        <v>216992579.89</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934173.46</v>
+        <v>2934173.69</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937781.88</v>
+        <v>6937782.44</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280964908.7</v>
+        <v>280964941.1</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105931068.75</v>
+        <v>1105931180.2</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351785968.4</v>
+        <v>1351786079.85</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242474160.28</v>
+        <v>242474174.8</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693241.09</v>
+        <v>2693240.98</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764017.85</v>
+        <v>8764017.51</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322787898.21</v>
+        <v>322787912.29</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932821797.2</v>
+        <v>932821952.72</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136769611.65</v>
+        <v>1136769767.17</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196518485.91</v>
+        <v>196518593</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927917.66</v>
+        <v>2927918.5</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577824.65</v>
+        <v>6577826.53</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259472569.58</v>
+        <v>259472679.39</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1161996524.21</v>
+        <v>1161996710.19</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354833008.28</v>
+        <v>1354833194.26</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252343621.78</v>
+        <v>252343653.81</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229183.48</v>
+        <v>4229183.33</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541668.95</v>
+        <v>4541668.79</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311956192.84</v>
+        <v>311956224.56</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439971081.63</v>
+        <v>1439972339.68</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740027747.66</v>
+        <v>1740029005.71</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284710378.16</v>
+        <v>284710603.9</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067071.04</v>
+        <v>4067070.53</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978487.47</v>
+        <v>5978486.72</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375581125.54</v>
+        <v>375581350.02</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319683463.06</v>
+        <v>1319683728.82</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579446547.18</v>
+        <v>1579446812.94</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283367272.44</v>
+        <v>283367334.5</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2327,13 +2327,13 @@
         <v>3050968.44</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438413.03</v>
+        <v>7438413.05</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363608018.42</v>
+        <v>363608080.51</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096971334.04</v>
+        <v>1096972160.74</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283012360.15</v>
+        <v>1283013186.85</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243419590.78</v>
+        <v>243419667.44</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660619.87</v>
+        <v>1660619.2</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202020.79</v>
+        <v>7202017.89</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302137122.97</v>
+        <v>302137196.06</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142088309.67</v>
+        <v>1142088504.36</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1365979423.62</v>
+        <v>1365979618.31</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239651704.02</v>
+        <v>239651815.03</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298509.62</v>
+        <v>1298509.91</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234272.73</v>
+        <v>9234274.82</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307444861.11</v>
+        <v>307444974.5</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192810903.06</v>
+        <v>1192811832.06</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436467909.73</v>
+        <v>1436468838.73</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253618930.81</v>
+        <v>253619121.11</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145292.58</v>
+        <v>2145292.43</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745062.34</v>
+        <v>6745061.88</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327973687.92</v>
+        <v>327973877.62</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226893555.18</v>
+        <v>1226895263.88</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494233846.05</v>
+        <v>1494235554.75</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272940065.37</v>
+        <v>272940320.42</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511785.5</v>
+        <v>2511784.37</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248144.37</v>
+        <v>7248141.11</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361182079.92</v>
+        <v>361182330.58</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348545732.33</v>
+        <v>1348547550.9</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622865877.08</v>
+        <v>1622867695.65</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278414263.58</v>
+        <v>278414872.3</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307495.54</v>
+        <v>2307496.87</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088386.53</v>
+        <v>8088391.21</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361801052.44</v>
+        <v>361801667.17</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778221660.06</v>
+        <v>1778223268.44</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122284722.12</v>
+        <v>2122286330.5</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364477119.18</v>
+        <v>364477517.42</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3918951.48</v>
+        <v>3918951.87</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6646921.31</v>
+        <v>6646921.97</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465495759.74</v>
+        <v>465496159.03</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364162952.26</v>
+        <v>1364170892.38</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1650932738.86</v>
+        <v>1650940678.98</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283619638.86</v>
+        <v>283621733.75</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4916617.58</v>
+        <v>4916621.57</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7351731.64</v>
+        <v>7351737.6</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374515777.76</v>
+        <v>374517882.6</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1037704889.71</v>
+        <v>1037714269.08</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347081606.5</v>
+        <v>1347090985.87</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218350489.46</v>
+        <v>218354391.11</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3628504.51</v>
+        <v>3628524.47</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4591341.11</v>
+        <v>4591366.36</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316698908.56</v>
+        <v>316702855.42</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143111126.84</v>
+        <v>1143124037.75</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1421593546.45</v>
+        <v>1421606457.36</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228040636.42</v>
+        <v>228044013.64</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3387646.54</v>
+        <v>3387652.4</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5520281.2</v>
+        <v>5520290.74</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>313821749.34</v>
+        <v>313825141.96</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1338824453.76</v>
+        <v>1338835374.35</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1714398359.36</v>
+        <v>1714409279.95</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269710714.63</v>
+        <v>269713270.07</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2885967.59</v>
+        <v>2885968.15</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7558703.79</v>
+        <v>7558705.26</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389600855.35</v>
+        <v>389603412.82</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1030603566.63</v>
+        <v>1030919079.2</v>
       </c>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6" t="n">
@@ -2945,10 +2945,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1198531431.12</v>
+        <v>1198846943.69</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>210602244.46</v>
+        <v>210663009.85</v>
       </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n">
@@ -2958,16 +2958,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2703549.64</v>
+        <v>2703462.67</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>7373330.78</v>
+        <v>7373093.58</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>261570776.87</v>
+        <v>261631218.08</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.4394700544002308</v>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1348571137.83</v>
+        <v>1348976782.37</v>
       </c>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6" t="n">
@@ -5325,10 +5325,10 @@
         <v>49898532</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1521682535.32</v>
+        <v>1522088179.86</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>374363347.86</v>
+        <v>374475954.78</v>
       </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n">
@@ -5338,16 +5338,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>3500592.09</v>
+        <v>3500575.08</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>10557561.23</v>
+        <v>10557509.93</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22991971.37</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>430002528.63</v>
+        <v>430115067.24</v>
       </c>
     </row>
   </sheetData>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>649417917.13</v>
+        <v>649613259.3200001</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>10973579.3</v>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226356139.32</v>
+        <v>1226356260.49</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404318233.9</v>
+        <v>1404318355.07</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290713845.16</v>
+        <v>290713901.32</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524811.63</v>
+        <v>524811.67</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360263.58</v>
+        <v>9360264.279999999</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354056827</v>
+        <v>354056883.89</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019796762.15</v>
+        <v>1019798054.79</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203201671.66</v>
+        <v>1203202964.3</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223746932.49</v>
+        <v>223747156.83</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516298.21</v>
+        <v>516298.05</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237377.779999999</v>
+        <v>9237374.93</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289058714.26</v>
+        <v>289058935.59</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766406536.08</v>
+        <v>766407132.25</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882449083.12</v>
+        <v>882449679.29</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197401499.15</v>
+        <v>197401672.88</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374708.73</v>
+        <v>374708.75</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399335.16</v>
+        <v>5399335.43</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239490825.42</v>
+        <v>239490999.44</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983759487.78</v>
+        <v>983759737.24</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168397636.8</v>
+        <v>1168397886.26</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236062105.8</v>
+        <v>236062231.3</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324587.03</v>
+        <v>324587.09</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358508.7</v>
+        <v>7358510.18</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305858786.1</v>
+        <v>305858913.15</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097587673.77</v>
+        <v>1097587917.65</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302667711.35</v>
+        <v>1302667955.23</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250950831.81</v>
+        <v>250950917.59</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.58</v>
+        <v>709927.64</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693357.93</v>
+        <v>7693358.51</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328054848.58</v>
+        <v>328054935</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011521623.45</v>
+        <v>1011522572.39</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233694742.96</v>
+        <v>1233695691.9</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229525448.1</v>
+        <v>229525528.93</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255746.08</v>
+        <v>1255745.42</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409747.060000001</v>
+        <v>8409742.65</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309200397.89</v>
+        <v>309200473.66</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961939751.03</v>
+        <v>961941096.4</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145546912.57</v>
+        <v>1145548257.94</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214889945.11</v>
+        <v>214890219.72</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814778.58</v>
+        <v>814778.41</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850544.84</v>
+        <v>6850543.44</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281207113.73</v>
+        <v>281207386.78</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073046768.36</v>
+        <v>1073046826.61</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277712665.84</v>
+        <v>1277712724.09</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240125278.98</v>
+        <v>240125311.63</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353400.62</v>
+        <v>2353400.77</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569917.11</v>
+        <v>7569917.57</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313749074.6</v>
+        <v>313749107.85</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960761125.99</v>
+        <v>960761994.58</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185434443.11</v>
+        <v>1185435311.7</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212545774.99</v>
+        <v>212546032.98</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490148.9</v>
+        <v>2490149.25</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929273.710000001</v>
+        <v>8929274.99</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296180538.29</v>
+        <v>296180797.93</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686503350.9</v>
+        <v>686505447.34</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813415041.9299999</v>
+        <v>813417138.37</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150990755.37</v>
+        <v>150991011.62</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897063.63</v>
+        <v>1897061.15</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485525.54</v>
+        <v>3485520.98</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196255304.44</v>
+        <v>196255553.65</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970907334.3099999</v>
+        <v>970907759.97</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130463988.55</v>
+        <v>1130464414.21</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227540890.05</v>
+        <v>227541107.58</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642028.04</v>
+        <v>2642029.08</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513125.66</v>
+        <v>5513127.84</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286538592.2</v>
+        <v>286538812.94</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042728700.46</v>
+        <v>1042728928.36</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244212890.53</v>
+        <v>1244213118.43</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230882769.76</v>
+        <v>230882946.88</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865666.46</v>
+        <v>2865667.64</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026074.22</v>
+        <v>7026077.09</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305687581.88</v>
+        <v>305687763.05</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046522868.23</v>
+        <v>1046523922.89</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268569968.04</v>
+        <v>1268571022.7</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238379561.6</v>
+        <v>238380138.95</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737692.42</v>
+        <v>3737696.29</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838260.08</v>
+        <v>7838268.19</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315846250.9</v>
+        <v>315846840.22</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026517381.04</v>
+        <v>1026519167.03</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228661260.07</v>
+        <v>1228663046.06</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246154024.74</v>
+        <v>246154558.54</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558671.08</v>
+        <v>3558671.96</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537370.44</v>
+        <v>7537372.3</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315574120.42</v>
+        <v>315574656.96</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275214012.59</v>
+        <v>1275217669.22</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517935489.84</v>
+        <v>1517939146.47</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295672417.41</v>
+        <v>295672939.68</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271147.41</v>
+        <v>4271142.84</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581216.42</v>
+        <v>9581206.18</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378768777.12</v>
+        <v>378769284.58</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123189412.99</v>
+        <v>1123194322.67</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375364574.32</v>
+        <v>1375369484</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251883669.46</v>
+        <v>251884237.27</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520518.04</v>
+        <v>3520511.03</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255814.59</v>
+        <v>11255792.17</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341102958.93</v>
+        <v>341103497.31</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780493687.48</v>
+        <v>780497628.33</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941910533.01</v>
+        <v>941914473.86</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182886832.44</v>
+        <v>182887072.69</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893266.43</v>
+        <v>2893256.9</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4979019.91</v>
+        <v>4979003.52</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240370961.71</v>
+        <v>240371176.05</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925209703.76</v>
+        <v>925211512.74</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103213087.58</v>
+        <v>1103214896.56</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208936450.31</v>
+        <v>208937010.05</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099148.29</v>
+        <v>3099149.66</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218669.94</v>
+        <v>6218672.69</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270754778.54</v>
+        <v>270755342.41</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099253491.31</v>
+        <v>1099256266.78</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314553785.13</v>
+        <v>1314556560.6</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244619837.59</v>
+        <v>244620182.41</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671182.57</v>
+        <v>3671178.64</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710537.12</v>
+        <v>7710528.87</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319473977.98</v>
+        <v>319474310.62</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967580890.71</v>
+        <v>967581973.59</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190901896.29</v>
+        <v>1190902979.17</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210530677.41</v>
+        <v>210530920.28</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281804.02</v>
+        <v>3281803.84</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536309.6</v>
+        <v>7536309.18</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283813671.7</v>
+        <v>283813913.97</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003067287.81</v>
+        <v>1003068485.45</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198223975.87</v>
+        <v>1198225173.51</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222084703.64</v>
+        <v>222085222.08</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891025.88</v>
+        <v>3891029.29</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335915.18</v>
+        <v>6335920.74</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281016139.63</v>
+        <v>281016667.04</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362275308.88</v>
+        <v>1362277225.12</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634492064</v>
+        <v>1634493980.24</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306759543.49</v>
+        <v>306759965.52</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136462</v>
+        <v>6136461.46</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270548.38</v>
+        <v>10270547.47</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388018685.37</v>
+        <v>388019105.95</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156881190.12</v>
+        <v>1156884485.97</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409381157.77</v>
+        <v>1409384453.62</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247794405.68</v>
+        <v>247795278.08</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795233</v>
+        <v>3795234.34</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929384.300000001</v>
+        <v>9929387.800000001</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325992247.77</v>
+        <v>325993125</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870268733.4400001</v>
+        <v>870273336.45</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039372945.81</v>
+        <v>1039377548.82</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193425825.72</v>
+        <v>193426566.2</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256065.69</v>
+        <v>3256060.93</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684209.89</v>
+        <v>5684201.57</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245267912.93</v>
+        <v>245268640.33</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002218105.74</v>
+        <v>1002220277.97</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209555513.7</v>
+        <v>1209557685.93</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>216992579.89</v>
+        <v>216993137.62</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934173.69</v>
+        <v>2934174.27</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937782.44</v>
+        <v>6937783.8</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280964941.1</v>
+        <v>280965500.76</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105931180.2</v>
+        <v>1105940184.56</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351786079.85</v>
+        <v>1351795084.21</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242474174.8</v>
+        <v>242476536.99</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693240.98</v>
+        <v>2693242.82</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764017.51</v>
+        <v>8764023.48</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322787912.29</v>
+        <v>322790282.28</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932821952.72</v>
+        <v>932826063.37</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136769767.17</v>
+        <v>1136773877.82</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196518593</v>
+        <v>196520550.55</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927918.5</v>
+        <v>2927930.44</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577826.53</v>
+        <v>6577853.35</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259472679.39</v>
+        <v>259474675.7</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1161996710.19</v>
+        <v>1162002889.39</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354833194.26</v>
+        <v>1354839373.46</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252343653.81</v>
+        <v>252345489.82</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229183.33</v>
+        <v>4229189.09</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541668.79</v>
+        <v>4541674.98</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311956224.56</v>
+        <v>311958072.52</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439972339.68</v>
+        <v>1439981869.84</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740029005.71</v>
+        <v>1740038535.87</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284710603.9</v>
+        <v>284712996.22</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067070.53</v>
+        <v>4067074.26</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978486.72</v>
+        <v>5978492.21</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375581350.02</v>
+        <v>375583751.55</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319683728.82</v>
+        <v>1319688925.81</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579446812.94</v>
+        <v>1579452009.93</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283367334.5</v>
+        <v>283368428.51</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050968.44</v>
+        <v>3050967.56</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438413.05</v>
+        <v>7438410.89</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363608080.51</v>
+        <v>363609171.48</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096972160.74</v>
+        <v>1096975075.98</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283013186.85</v>
+        <v>1283016102.09</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243419667.44</v>
+        <v>243420441.55</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660619.2</v>
+        <v>1660619.7</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202017.89</v>
+        <v>7202020.04</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302137196.06</v>
+        <v>302137972.82</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142088504.36</v>
+        <v>1142093307.64</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1365979618.31</v>
+        <v>1365984421.59</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239651815.03</v>
+        <v>239652597.44</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298509.91</v>
+        <v>1298508.6</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234274.82</v>
+        <v>9234265.539999999</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307444974.5</v>
+        <v>307445746.32</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192811832.06</v>
+        <v>1192816957.34</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436468838.73</v>
+        <v>1436473964.01</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253619121.11</v>
+        <v>253620184.05</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145292.43</v>
+        <v>2145291.71</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745061.88</v>
+        <v>6745059.61</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327973877.62</v>
+        <v>327974937.57</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226895263.88</v>
+        <v>1226905179.21</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494235554.75</v>
+        <v>1494245470.08</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272940320.42</v>
+        <v>272942896.04</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511784.37</v>
+        <v>2511785.65</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248141.11</v>
+        <v>7248144.81</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361182330.58</v>
+        <v>361184911.17</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348547550.9</v>
+        <v>1348557247.97</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622867695.65</v>
+        <v>1622877392.72</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278414872.3</v>
+        <v>278417655.79</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307496.87</v>
+        <v>2307500.96</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088391.21</v>
+        <v>8088405.52</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361801667.17</v>
+        <v>361804469.05</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778223268.44</v>
+        <v>1778240146.32</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122286330.5</v>
+        <v>2122303208.38</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364477517.42</v>
+        <v>364483626.34</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3918951.87</v>
+        <v>3918972.6</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6646921.97</v>
+        <v>6646957.14</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465496159.03</v>
+        <v>465502323.85</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364170892.38</v>
+        <v>1364231261.46</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1650940678.98</v>
+        <v>1651001048.06</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283621733.75</v>
+        <v>283646812.16</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4916621.57</v>
+        <v>4916776.07</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7351737.6</v>
+        <v>7351968.61</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374517882.6</v>
+        <v>374543346.52</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1037714269.08</v>
+        <v>1037801087.23</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347090985.87</v>
+        <v>1347177804.02</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218354391.11</v>
+        <v>218387803.3</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3628524.47</v>
+        <v>3628677.38</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4591366.36</v>
+        <v>4591559.86</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316702855.42</v>
+        <v>316736614.02</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143124037.75</v>
+        <v>1143278602.96</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1421606457.36</v>
+        <v>1421761022.57</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228044013.64</v>
+        <v>228101985.02</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3387652.4</v>
+        <v>3387917.35</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5520290.74</v>
+        <v>5520722.49</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>313825141.96</v>
+        <v>313883810.04</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1338835374.35</v>
+        <v>1339029466.87</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1714409279.95</v>
+        <v>1714603372.47</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269713270.07</v>
+        <v>269789989.31</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2885968.15</v>
+        <v>2886216.34</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7558705.26</v>
+        <v>7559355.3</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389603412.82</v>
+        <v>389681030.3</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1030919079.2</v>
+        <v>1171639970.58</v>
       </c>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6" t="n">
@@ -2945,10 +2945,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1198846943.69</v>
+        <v>1339567835.07</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>210663009.85</v>
+        <v>219850592.75</v>
       </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n">
@@ -2958,23 +2958,81 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2703462.67</v>
+        <v>2497323.3</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>7373093.58</v>
+        <v>6810894.25</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>261631218.08</v>
+        <v>270050462.28</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.4394700544002308</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>1123382910.46</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>118878392.5</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>36482666.67</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>28674442</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>24382549.1</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>32471001</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>37871164</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>1402143125.73</v>
+      </c>
+      <c r="J44" s="8" t="n">
+        <v>229923649.58</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>32561198.02</v>
+      </c>
+      <c r="L44" s="9" t="n">
+        <v>11549732.06</v>
+      </c>
+      <c r="M44" s="9" t="n">
+        <v>9720707.050000001</v>
+      </c>
+      <c r="N44" s="9" t="n">
+        <v>5461593.82</v>
+      </c>
+      <c r="O44" s="9" t="n">
+        <v>7273374.81</v>
+      </c>
+      <c r="P44" s="9" t="n">
+        <v>17584216.39</v>
+      </c>
+      <c r="Q44" s="9" t="n">
+        <v>314074471.72</v>
+      </c>
+      <c r="R44" s="10" t="n">
+        <v>0.3923339612110134</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R43"/>
+  <autoFilter ref="A2:R44"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -2990,7 +3048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5306,7 +5364,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1348976782.37</v>
+        <v>1640000000</v>
       </c>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6" t="n">
@@ -5325,10 +5383,10 @@
         <v>49898532</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1522088179.86</v>
+        <v>1813111397.49</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>374475954.78</v>
+        <v>455264000</v>
       </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n">
@@ -5338,20 +5396,75 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>3500575.08</v>
+        <v>3490389.08</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>10557509.93</v>
+        <v>10526789.58</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22991971.37</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>430115067.24</v>
+        <v>510862206.11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>1492836859.81</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>120197775.42</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>36482666.67</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>28674442</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>24382549.1</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>35686711</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>43834004</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>1782095008</v>
+      </c>
+      <c r="J44" s="8" t="n">
+        <v>414411512.28</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>32887256.58</v>
+      </c>
+      <c r="L44" s="9" t="n">
+        <v>11549732.06</v>
+      </c>
+      <c r="M44" s="9" t="n">
+        <v>9720707.050000001</v>
+      </c>
+      <c r="N44" s="9" t="n">
+        <v>6917206.24</v>
+      </c>
+      <c r="O44" s="9" t="n">
+        <v>10124139.97</v>
+      </c>
+      <c r="P44" s="9" t="n">
+        <v>19960813.73</v>
+      </c>
+      <c r="Q44" s="9" t="n">
+        <v>505571367.9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q43"/>
+  <autoFilter ref="A2:Q44"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -5366,7 +5479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6895,7 +7008,7 @@
         <v>8471978</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>0.6045</v>
+        <v>0.6043999999999999</v>
       </c>
       <c r="I36" s="11" t="n">
         <v>0.3584000000000001</v>
@@ -6981,7 +7094,7 @@
         <v>10824093</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>0.6202000000000001</v>
+        <v>0.6201</v>
       </c>
       <c r="I38" s="11" t="n">
         <v>0.3624</v>
@@ -7110,7 +7223,7 @@
         <v>9247924</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>0.6572</v>
+        <v>0.6570999999999999</v>
       </c>
       <c r="I41" s="11" t="n">
         <v>0.4061999999999999</v>
@@ -7153,7 +7266,7 @@
         <v>15189926</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>0.6437999999999999</v>
+        <v>0.6437</v>
       </c>
       <c r="I42" s="11" t="n">
         <v>0.3605</v>
@@ -7178,7 +7291,7 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>649613259.3200001</v>
+        <v>789758400</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>10973579.3</v>
@@ -7194,7 +7307,7 @@
         <v>13411796</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>0.6301</v>
+        <v>0.6740999999999999</v>
       </c>
       <c r="I43" s="11" t="n">
         <v>0.3466</v>
@@ -7210,15 +7323,58 @@
         <v>0.397</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>718890518.21</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>14687824.44</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>11713221</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>36985227.39</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>19074195.33</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>12049458</v>
+      </c>
+      <c r="H44" s="11" t="n">
+        <v>0.6399</v>
+      </c>
+      <c r="I44" s="11" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="J44" s="11" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="K44" s="11" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="L44" s="11" t="n">
+        <v>0.7823</v>
+      </c>
+      <c r="M44" s="11" t="n">
+        <v>0.3711</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M43"/>
+  <autoFilter ref="A2:M44"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -7249,7 +7405,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-11. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-12. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R44"/>
+  <dimension ref="A1:R45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226356260.49</v>
+        <v>1226358213.97</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404318355.07</v>
+        <v>1404320308.55</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290713901.32</v>
+        <v>290715227.52</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524811.67</v>
+        <v>524812.9399999999</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360264.279999999</v>
+        <v>9360286.949999999</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354056883.89</v>
+        <v>354058234.04</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019798054.79</v>
+        <v>1019798188.9</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203202964.3</v>
+        <v>1203203098.41</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223747156.83</v>
+        <v>223747203.46</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516298.05</v>
+        <v>516298.08</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237374.93</v>
+        <v>9237375.41</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289058935.59</v>
+        <v>289058982.73</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766407132.25</v>
+        <v>766407609.51</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882449679.29</v>
+        <v>882450156.55</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197401672.88</v>
+        <v>197402013.09</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374708.75</v>
+        <v>374709.09</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399335.43</v>
+        <v>5399340.3</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239490999.44</v>
+        <v>239491344.86</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983759737.24</v>
+        <v>983760597.38</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168397886.26</v>
+        <v>1168398746.4</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236062231.3</v>
+        <v>236062536.37</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324587.09</v>
+        <v>324587.18</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358510.18</v>
+        <v>7358512.16</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305858913.15</v>
+        <v>305859220.28</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097587917.65</v>
+        <v>1097588506.89</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302667955.23</v>
+        <v>1302668544.47</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250950917.59</v>
+        <v>250950975.68</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.64</v>
+        <v>709927.4300000001</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693358.51</v>
+        <v>7693356.34</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328054935</v>
+        <v>328054990.71</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011522572.39</v>
+        <v>1011522847.81</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233695691.9</v>
+        <v>1233695967.32</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229525528.93</v>
+        <v>229525586.89</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255745.42</v>
+        <v>1255745.37</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409742.65</v>
+        <v>8409742.34</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309200473.66</v>
+        <v>309200531.26</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961941096.4</v>
+        <v>961941272.58</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145548257.94</v>
+        <v>1145548434.12</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214890219.72</v>
+        <v>214890233.74</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814778.41</v>
+        <v>814778.33</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850543.44</v>
+        <v>6850542.71</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281207386.78</v>
+        <v>281207399.98</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073046826.61</v>
+        <v>1073047706.97</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277712724.09</v>
+        <v>1277713604.45</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240125311.63</v>
+        <v>240125905.28</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353400.77</v>
+        <v>2353403.69</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569917.57</v>
+        <v>7569926.98</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313749107.85</v>
+        <v>313749713.83</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960761994.58</v>
+        <v>960763029.54</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185435311.7</v>
+        <v>1185436346.66</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212546032.98</v>
+        <v>212546399.61</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490149.25</v>
+        <v>2490150.2</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929274.99</v>
+        <v>8929278.380000001</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296180797.93</v>
+        <v>296181168.89</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686505447.34</v>
+        <v>686506271.8200001</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813417138.37</v>
+        <v>813417962.85</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150991011.62</v>
+        <v>150991199.88</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897061.15</v>
+        <v>1897061.05</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485520.98</v>
+        <v>3485520.79</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196255553.65</v>
+        <v>196255741.61</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970907759.97</v>
+        <v>970909146.39</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130464414.21</v>
+        <v>1130465800.63</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227541107.58</v>
+        <v>227541227.44</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642029.08</v>
+        <v>2642026.88</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513127.84</v>
+        <v>5513123.25</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286538812.94</v>
+        <v>286538926.02</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042728928.36</v>
+        <v>1042729835.63</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244213118.43</v>
+        <v>1244214025.7</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230882946.88</v>
+        <v>230883198.37</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865667.64</v>
+        <v>2865667.91</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026077.09</v>
+        <v>7026077.77</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305687763.05</v>
+        <v>305688015.5</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046523922.89</v>
+        <v>1046525276.67</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268571022.7</v>
+        <v>1268572376.48</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238380138.95</v>
+        <v>238380579.06</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737696.29</v>
+        <v>3737697.55</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838268.19</v>
+        <v>7838270.84</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315846840.22</v>
+        <v>315847284.25</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026519167.03</v>
+        <v>1026522650.84</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228663046.06</v>
+        <v>1228666529.87</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246154558.54</v>
+        <v>246155780.23</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558671.96</v>
+        <v>3558675.78</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537372.3</v>
+        <v>7537380.39</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315574656.96</v>
+        <v>315575890.56</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275217669.22</v>
+        <v>1275220008.67</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517939146.47</v>
+        <v>1517941485.92</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295672939.68</v>
+        <v>295673580.12</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271142.84</v>
+        <v>4271143.51</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581206.18</v>
+        <v>9581207.67</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378769284.58</v>
+        <v>378769927.17</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123194322.67</v>
+        <v>1123198389.23</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375369484</v>
+        <v>1375373550.56</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251884237.27</v>
+        <v>251885526.51</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520511.03</v>
+        <v>3520514.06</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255792.17</v>
+        <v>11255801.85</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341103497.31</v>
+        <v>341104799.26</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780497628.33</v>
+        <v>780500282.12</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941914473.86</v>
+        <v>941917127.65</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182887072.69</v>
+        <v>182887914.84</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893256.9</v>
+        <v>2893258.96</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4979003.52</v>
+        <v>4979007.05</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240371176.05</v>
+        <v>240372023.78</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925211512.74</v>
+        <v>925214808.84</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103214896.56</v>
+        <v>1103218192.66</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208937010.05</v>
+        <v>208938214.09</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099149.66</v>
+        <v>3099154.34</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218672.69</v>
+        <v>6218682.09</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270755342.41</v>
+        <v>270756560.53</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099256266.78</v>
+        <v>1099259048.39</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314556560.6</v>
+        <v>1314559342.21</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244620182.41</v>
+        <v>244621142.32</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671178.64</v>
+        <v>3671182.02</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710528.87</v>
+        <v>7710535.97</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319474310.62</v>
+        <v>319475281.01</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967581973.59</v>
+        <v>967584555.54</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190902979.17</v>
+        <v>1190905561.12</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210530920.28</v>
+        <v>210531559.34</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281803.84</v>
+        <v>3281804.12</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536309.18</v>
+        <v>7536309.84</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283813913.97</v>
+        <v>283814553.97</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003068485.45</v>
+        <v>1003071287.01</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198225173.51</v>
+        <v>1198227975.07</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222085222.08</v>
+        <v>222086143.04</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891029.29</v>
+        <v>3891033.08</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335920.74</v>
+        <v>6335926.91</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281016667.04</v>
+        <v>281017597.97</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362277225.12</v>
+        <v>1362279412.5</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634493980.24</v>
+        <v>1634496167.62</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306759965.52</v>
+        <v>306760289.7</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136461.46</v>
+        <v>6136458.24</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270547.47</v>
+        <v>10270542.08</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388019105.95</v>
+        <v>388019421.52</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156884485.97</v>
+        <v>1156887121.22</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409384453.62</v>
+        <v>1409387088.87</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247795278.08</v>
+        <v>247795627.2</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795234.34</v>
+        <v>3795231.18</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929387.800000001</v>
+        <v>9929379.52</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325993125</v>
+        <v>325993462.68</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870273336.45</v>
+        <v>870282582.33</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039377548.82</v>
+        <v>1039386794.7</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193426566.2</v>
+        <v>193428584.87</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256060.93</v>
+        <v>3256058.68</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684201.57</v>
+        <v>5684197.65</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245268640.33</v>
+        <v>245270652.83</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002220277.97</v>
+        <v>1002227966.8</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209557685.93</v>
+        <v>1209565374.76</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>216993137.62</v>
+        <v>216994393.49</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934174.27</v>
+        <v>2934168.53</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937783.8</v>
+        <v>6937770.23</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280965500.76</v>
+        <v>280966737.33</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105940184.56</v>
+        <v>1105952105.87</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351795084.21</v>
+        <v>1351807005.52</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242476536.99</v>
+        <v>242480925.07</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693242.82</v>
+        <v>2693256.15</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764023.48</v>
+        <v>8764066.869999999</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322790282.28</v>
+        <v>322794727.09</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932826063.37</v>
+        <v>932831655.38</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136773877.82</v>
+        <v>1136779469.83</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196520550.55</v>
+        <v>196522128.09</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927930.44</v>
+        <v>2927933.97</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577853.35</v>
+        <v>6577861.28</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259474675.7</v>
+        <v>259476264.7</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1162002889.39</v>
+        <v>1162008025.78</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354839373.46</v>
+        <v>1354844509.85</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252345489.82</v>
+        <v>252346920.37</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229189.09</v>
+        <v>4229192.55</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541674.98</v>
+        <v>4541678.69</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311958072.52</v>
+        <v>311959510.24</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439981869.84</v>
+        <v>1439987633.9</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740038535.87</v>
+        <v>1740044299.93</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284712996.22</v>
+        <v>284714629.19</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067074.26</v>
+        <v>4067078.59</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978492.21</v>
+        <v>5978498.57</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375583751.55</v>
+        <v>375585395.21</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319688925.81</v>
+        <v>1319701714.81</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579452009.93</v>
+        <v>1579464798.93</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283368428.51</v>
+        <v>283370986.15</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050967.56</v>
+        <v>3050964.22</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438410.89</v>
+        <v>7438402.75</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363609171.48</v>
+        <v>363611717.64</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096975075.98</v>
+        <v>1096982338</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283016102.09</v>
+        <v>1283023364.11</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243420441.55</v>
+        <v>243422798.78</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660619.7</v>
+        <v>1660623.36</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202020.04</v>
+        <v>7202035.93</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302137972.82</v>
+        <v>302140349.61</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142093307.64</v>
+        <v>1142099684.96</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1365984421.59</v>
+        <v>1365990798.91</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239652597.44</v>
+        <v>239654757.11</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298508.6</v>
+        <v>1298511.77</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234265.539999999</v>
+        <v>9234288.060000001</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307445746.32</v>
+        <v>307447931.68</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192816957.34</v>
+        <v>1192823425.01</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436473964.01</v>
+        <v>1436480431.68</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253620184.05</v>
+        <v>253622663.44</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145291.71</v>
+        <v>2145298.45</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745059.61</v>
+        <v>6745080.8</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327974937.57</v>
+        <v>327977444.89</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226905179.21</v>
+        <v>1226910166.41</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494245470.08</v>
+        <v>1494250457.28</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272942896.04</v>
+        <v>272944944.77</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511785.65</v>
+        <v>2511791.67</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248144.81</v>
+        <v>7248162.2</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361184911.17</v>
+        <v>361186983.32</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348557247.97</v>
+        <v>1348576284.37</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622877392.72</v>
+        <v>1622896429.12</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278417655.79</v>
+        <v>278424181.54</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307500.96</v>
+        <v>2307515.94</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088405.52</v>
+        <v>8088458.04</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361804469.05</v>
+        <v>361811062.3</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778240146.32</v>
+        <v>1778272159.84</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122303208.38</v>
+        <v>2122335221.9</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364483626.34</v>
+        <v>364498323.55</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3918972.6</v>
+        <v>3919038.72</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6646957.14</v>
+        <v>6647069.28</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465502323.85</v>
+        <v>465517199.32</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364231261.46</v>
+        <v>1364338723.72</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1651001048.06</v>
+        <v>1651108510.32</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283646812.16</v>
+        <v>283692009.94</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4916776.07</v>
+        <v>4917058.6</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7351968.61</v>
+        <v>7352391.09</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374543346.52</v>
+        <v>374589249.31</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1037801087.23</v>
+        <v>1037973174.56</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347177804.02</v>
+        <v>1347349891.35</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218387803.3</v>
+        <v>218456127.31</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3628677.38</v>
+        <v>3629005.07</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4591559.86</v>
+        <v>4591974.5</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316736614.02</v>
+        <v>316805680.36</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143278602.96</v>
+        <v>1143533255</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1421761022.57</v>
+        <v>1422015674.61</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228101985.02</v>
+        <v>228204454.15</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3387917.35</v>
+        <v>3388431.03</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5520722.49</v>
+        <v>5521559.55</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>313883810.04</v>
+        <v>313987629.91</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339029466.87</v>
+        <v>1339297798.67</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1714603372.47</v>
+        <v>1714871704.27</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269789989.31</v>
+        <v>269890822.47</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2886216.34</v>
+        <v>2886519.57</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7559355.3</v>
+        <v>7560149.49</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389681030.3</v>
+        <v>389782960.87</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1171639970.58</v>
+        <v>1172169834.71</v>
       </c>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6" t="n">
@@ -2945,10 +2945,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1339567835.07</v>
+        <v>1340097699.2</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>219850592.75</v>
+        <v>220062654.22</v>
       </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n">
@@ -2958,16 +2958,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2497323.3</v>
+        <v>2498330.88</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>6810894.25</v>
+        <v>6813642.21</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>270050462.28</v>
+        <v>270266279.28</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.4394700544002308</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1123382910.46</v>
+        <v>1224515303.34</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>118878392.5</v>
@@ -3001,10 +3001,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1402143125.73</v>
+        <v>1503275518.61</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>229923649.58</v>
+        <v>236802034.31</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>32561198.02</v>
@@ -3016,23 +3016,77 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5461593.82</v>
+        <v>5195674.53</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>7273374.81</v>
+        <v>6919241.8</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>314074471.72</v>
+        <v>320332804.16</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3923339612110134</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>1962527154.87</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>151695056.58</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>66142107.86</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>93309716</v>
+      </c>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="n">
+        <v>79898997</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>32146387</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>2385719419.31</v>
+      </c>
+      <c r="J45" s="8" t="n">
+        <v>392922162.99</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>38969011.58</v>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>23893066.65</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>28343613.08</v>
+      </c>
+      <c r="N45" s="9" t="n"/>
+      <c r="O45" s="9" t="n">
+        <v>17318221.84</v>
+      </c>
+      <c r="P45" s="9" t="n">
+        <v>15662019.12</v>
+      </c>
+      <c r="Q45" s="9" t="n">
+        <v>517108095.26</v>
+      </c>
+      <c r="R45" s="10" t="n">
+        <v>0.3664440983125071</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R44"/>
+  <autoFilter ref="A2:R45"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3048,7 +3102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5415,7 +5469,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1492836859.81</v>
+        <v>1700000000</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>120197775.42</v>
@@ -5436,10 +5490,10 @@
         <v>43834004</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1782095008</v>
+        <v>1989258148.19</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>414411512.28</v>
+        <v>471920000</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>32887256.58</v>
@@ -5451,20 +5505,71 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>6917206.24</v>
+        <v>6901247.9</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>10124139.97</v>
+        <v>10100783.08</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>19960813.73</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>505571367.9</v>
+        <v>563040540.4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>2628291138.41</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>152527110.31</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>66142107.86</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>93309716</v>
+      </c>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="n">
+        <v>82937759</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>34419473</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>3057627304.58</v>
+      </c>
+      <c r="J45" s="8" t="n">
+        <v>729613620.02</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>39087094.48</v>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>23893066.65</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>28343613.08</v>
+      </c>
+      <c r="N45" s="9" t="n"/>
+      <c r="O45" s="9" t="n">
+        <v>23348429.55</v>
+      </c>
+      <c r="P45" s="9" t="n">
+        <v>16489733.2</v>
+      </c>
+      <c r="Q45" s="9" t="n">
+        <v>860775556.98</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q44"/>
+  <autoFilter ref="A2:Q45"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -5479,7 +5584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6621,7 +6726,7 @@
         <v>11383349</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.6343</v>
+        <v>0.6342</v>
       </c>
       <c r="I27" s="11" t="n">
         <v>0.3861</v>
@@ -7051,7 +7156,7 @@
         <v>11868618</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>0.6321</v>
+        <v>0.632</v>
       </c>
       <c r="I37" s="11" t="n">
         <v>0.3806</v>
@@ -7137,7 +7242,7 @@
         <v>12319196</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>0.6248</v>
+        <v>0.6247</v>
       </c>
       <c r="I39" s="11" t="n">
         <v>0.3315</v>
@@ -7180,7 +7285,7 @@
         <v>7061846</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>0.6311</v>
+        <v>0.631</v>
       </c>
       <c r="I40" s="11" t="n">
         <v>0.3536</v>
@@ -7223,7 +7328,7 @@
         <v>9247924</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>0.6570999999999999</v>
+        <v>0.6568999999999999</v>
       </c>
       <c r="I41" s="11" t="n">
         <v>0.4061999999999999</v>
@@ -7266,7 +7371,7 @@
         <v>15189926</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>0.6437</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="I42" s="11" t="n">
         <v>0.3605</v>
@@ -7307,7 +7412,7 @@
         <v>13411796</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>0.6740999999999999</v>
+        <v>0.6738</v>
       </c>
       <c r="I43" s="11" t="n">
         <v>0.3466</v>
@@ -7330,7 +7435,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>718890518.21</v>
+        <v>818652000</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>14687824.44</v>
@@ -7348,7 +7453,7 @@
         <v>12049458</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>0.6399</v>
+        <v>0.6686</v>
       </c>
       <c r="I44" s="11" t="n">
         <v>0.4026</v>
@@ -7366,15 +7471,54 @@
         <v>0.3711</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>1265679880.61</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>25784306.09</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>42363201</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>53274388.26</v>
+      </c>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="n">
+        <v>21875177</v>
+      </c>
+      <c r="H45" s="11" t="n">
+        <v>0.6448999999999999</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>0.3898</v>
+      </c>
+      <c r="J45" s="11" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="K45" s="11" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="L45" s="11" t="n"/>
+      <c r="M45" s="11" t="n">
+        <v>0.2738</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M44"/>
+  <autoFilter ref="A2:M45"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -7405,7 +7549,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-12. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-13. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:R46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226358213.97</v>
+        <v>1226359047.97</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404320308.55</v>
+        <v>1404321142.55</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290715227.52</v>
+        <v>290715347.52</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524812.9399999999</v>
+        <v>524812.8</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360286.949999999</v>
+        <v>9360284.49</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354058234.04</v>
+        <v>354058351.45</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019798188.9</v>
+        <v>1019798550.38</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203203098.41</v>
+        <v>1203203459.89</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223747203.46</v>
+        <v>223747291.29</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -707,13 +707,13 @@
         <v>516298.08</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237375.41</v>
+        <v>9237375.439999999</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289058982.73</v>
+        <v>289059070.59</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766407609.51</v>
+        <v>766408358.99</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882450156.55</v>
+        <v>882450906.03</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197402013.09</v>
+        <v>197402127.89</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374709.09</v>
+        <v>374708.95</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399340.3</v>
+        <v>5399338.25</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239491344.86</v>
+        <v>239491457.47</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983760597.38</v>
+        <v>983762949.55</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168398746.4</v>
+        <v>1168401098.57</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236062536.37</v>
+        <v>236064404.4</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324587.18</v>
+        <v>324588.54</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358512.16</v>
+        <v>7358543.06</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305859220.28</v>
+        <v>305861120.57</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097588506.89</v>
+        <v>1097588708.03</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302668544.47</v>
+        <v>1302668745.61</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250950975.68</v>
+        <v>250951038.92</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.4300000001</v>
+        <v>709927.46</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693356.34</v>
+        <v>7693356.64</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328054990.71</v>
+        <v>328055054.28</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011522847.81</v>
+        <v>1011523877.55</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233695967.32</v>
+        <v>1233696997.06</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229525586.89</v>
+        <v>229525913.28</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255745.37</v>
+        <v>1255745.66</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409742.34</v>
+        <v>8409744.25</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309200531.26</v>
+        <v>309200859.85</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961941272.58</v>
+        <v>961942323.58</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145548434.12</v>
+        <v>1145549485.12</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214890233.74</v>
+        <v>214890608.89</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814778.33</v>
+        <v>814778.6800000001</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850542.71</v>
+        <v>6850545.65</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281207399.98</v>
+        <v>281207778.41</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073047706.97</v>
+        <v>1073048473.57</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277713604.45</v>
+        <v>1277714371.05</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240125905.28</v>
+        <v>240126105.36</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353403.69</v>
+        <v>2353403.78</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569926.98</v>
+        <v>7569927.27</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313749713.83</v>
+        <v>313749914.29</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960763029.54</v>
+        <v>960775761.9</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185436346.66</v>
+        <v>1185449079.02</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212546399.61</v>
+        <v>212551689.99</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490150.2</v>
+        <v>2490168.64</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929278.380000001</v>
+        <v>8929344.52</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296181168.89</v>
+        <v>296186543.85</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686506271.8200001</v>
+        <v>686510814.01</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813417962.85</v>
+        <v>813422505.04</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150991199.88</v>
+        <v>150992614.67</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897061.05</v>
+        <v>1897064.22</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485520.79</v>
+        <v>3485526.61</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196255741.61</v>
+        <v>196257165.4</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970909146.39</v>
+        <v>970910492.75</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130465800.63</v>
+        <v>1130467146.99</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227541227.44</v>
+        <v>227541652.15</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642026.88</v>
+        <v>2642027.67</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513123.25</v>
+        <v>5513124.9</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286538926.02</v>
+        <v>286539353.17</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042729835.63</v>
+        <v>1042731307.08</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244214025.7</v>
+        <v>1244215497.15</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230883198.37</v>
+        <v>230883759.96</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865667.91</v>
+        <v>2865669.85</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026077.77</v>
+        <v>7026082.52</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305688015.5</v>
+        <v>305688583.78</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046525276.67</v>
+        <v>1046531651.65</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268572376.48</v>
+        <v>1268578751.46</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238380579.06</v>
+        <v>238383400.24</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737697.55</v>
+        <v>3737712.71</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838270.84</v>
+        <v>7838302.63</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315847284.25</v>
+        <v>315850152.38</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026522650.84</v>
+        <v>1026526753.33</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228666529.87</v>
+        <v>1228670632.36</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246155780.23</v>
+        <v>246156789.24</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558675.78</v>
+        <v>3558675.26</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537380.39</v>
+        <v>7537379.28</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315575890.56</v>
+        <v>315576897.94</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275220008.67</v>
+        <v>1275233774.87</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517941485.92</v>
+        <v>1517955252.12</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295673580.12</v>
+        <v>295676822.44</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271143.51</v>
+        <v>4271141.25</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581207.67</v>
+        <v>9581202.609999999</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378769927.17</v>
+        <v>378773162.18</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123198389.23</v>
+        <v>1123210816.15</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375373550.56</v>
+        <v>1375385977.48</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251885526.51</v>
+        <v>251891900.23</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520514.06</v>
+        <v>3520549.57</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255801.85</v>
+        <v>11255915.39</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341104799.26</v>
+        <v>341111322.03</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780500282.12</v>
+        <v>780514859.41</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941917127.65</v>
+        <v>941931704.9400001</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182887914.84</v>
+        <v>182890873.33</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893258.96</v>
+        <v>2893249.48</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4979007.05</v>
+        <v>4978990.74</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240372023.78</v>
+        <v>240374956.48</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925214808.84</v>
+        <v>925223184.05</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103218192.66</v>
+        <v>1103226567.87</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208938214.09</v>
+        <v>208939531.88</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099154.34</v>
+        <v>3099145.6</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218682.09</v>
+        <v>6218664.54</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270756560.53</v>
+        <v>270757852.03</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099259048.39</v>
+        <v>1099263517.88</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314559342.21</v>
+        <v>1314563811.7</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244621142.32</v>
+        <v>244622568.78</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671182.02</v>
+        <v>3671186.07</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710535.97</v>
+        <v>7710544.49</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319475281.01</v>
+        <v>319476720.04</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967584555.54</v>
+        <v>967592674.75</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190905561.12</v>
+        <v>1190913680.33</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210531559.34</v>
+        <v>210534002.06</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281804.12</v>
+        <v>3281810.23</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536309.84</v>
+        <v>7536323.86</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283814553.97</v>
+        <v>283817016.81</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003071287.01</v>
+        <v>1003078424.37</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198227975.07</v>
+        <v>1198235112.43</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222086143.04</v>
+        <v>222088374.38</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891033.08</v>
+        <v>3891041.09</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335926.91</v>
+        <v>6335939.95</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281017597.97</v>
+        <v>281019850.36</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362279412.5</v>
+        <v>1362286346.21</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634496167.62</v>
+        <v>1634503101.33</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306760289.7</v>
+        <v>306762584.8</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136458.24</v>
+        <v>6136468.96</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270542.08</v>
+        <v>10270560.02</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388019421.52</v>
+        <v>388021745.27</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156887121.22</v>
+        <v>1156893098.04</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409387088.87</v>
+        <v>1409393065.69</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247795627.2</v>
+        <v>247797745.47</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795231.18</v>
+        <v>3795240.12</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929379.52</v>
+        <v>9929402.92</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325993462.68</v>
+        <v>325995613.29</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870282582.33</v>
+        <v>870293078.5</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039386794.7</v>
+        <v>1039397290.87</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193428584.87</v>
+        <v>193431819.39</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256058.68</v>
+        <v>3256069.12</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684197.65</v>
+        <v>5684215.87</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245270652.83</v>
+        <v>245273916.01</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002227966.8</v>
+        <v>1002261643.14</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209565374.76</v>
+        <v>1209599051.1</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>216994393.49</v>
+        <v>216999992.87</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934168.53</v>
+        <v>2934144.47</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937770.23</v>
+        <v>6937713.33</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280966737.33</v>
+        <v>280972255.75</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105952105.87</v>
+        <v>1105960743.67</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351807005.52</v>
+        <v>1351815643.32</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242480925.07</v>
+        <v>242482900.58</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693256.15</v>
+        <v>2693255.4</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764066.869999999</v>
+        <v>8764064.42</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322794727.09</v>
+        <v>322796699.39</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932831655.38</v>
+        <v>932835414.99</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136779469.83</v>
+        <v>1136783229.44</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196522128.09</v>
+        <v>196523247.42</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927933.97</v>
+        <v>2927937.03</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577861.28</v>
+        <v>6577868.15</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259476264.7</v>
+        <v>259477393.96</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1162008025.78</v>
+        <v>1162023256.99</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354844509.85</v>
+        <v>1354859741.06</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252346920.37</v>
+        <v>252350382.04</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229192.55</v>
+        <v>4229191.92</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541678.69</v>
+        <v>4541678.01</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311959510.24</v>
+        <v>311962970.6</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439987633.9</v>
+        <v>1439998288.31</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740044299.93</v>
+        <v>1740054954.34</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284714629.19</v>
+        <v>284717205.62</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067078.59</v>
+        <v>4067081.67</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978498.57</v>
+        <v>5978503.09</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375585395.21</v>
+        <v>375587979.24</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319701714.81</v>
+        <v>1319725505.19</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579464798.93</v>
+        <v>1579488589.31</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283370986.15</v>
+        <v>283376917.32</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050964.22</v>
+        <v>3050968.15</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438402.75</v>
+        <v>7438412.32</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363611717.64</v>
+        <v>363617662.3</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096982338</v>
+        <v>1096994942.9</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283023364.11</v>
+        <v>1283035969.01</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243422798.78</v>
+        <v>243425475.44</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660623.36</v>
+        <v>1660621.71</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202035.93</v>
+        <v>7202028.77</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302140349.61</v>
+        <v>302143017.45</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142099684.96</v>
+        <v>1142111662.52</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1365990798.91</v>
+        <v>1366002776.47</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239654757.11</v>
+        <v>239658182.52</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298511.77</v>
+        <v>1298514.96</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234288.060000001</v>
+        <v>9234310.75</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307447931.68</v>
+        <v>307451382.97</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192823425.01</v>
+        <v>1192843449.73</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436480431.68</v>
+        <v>1436500456.4</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253622663.44</v>
+        <v>253629810.84</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145298.45</v>
+        <v>2145315.76</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745080.8</v>
+        <v>6745135.24</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327977444.89</v>
+        <v>327984664.05</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226910166.41</v>
+        <v>1226934158.15</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494250457.28</v>
+        <v>1494274449.02</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272944944.77</v>
+        <v>272957328.24</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511791.67</v>
+        <v>2511838.73</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248162.2</v>
+        <v>7248297.99</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361186983.32</v>
+        <v>361199549.65</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348576284.37</v>
+        <v>1348607805.31</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622896429.12</v>
+        <v>1622927950.06</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278424181.54</v>
+        <v>278431696.7</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307515.94</v>
+        <v>2307519.14</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088458.04</v>
+        <v>8088469.26</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361811062.3</v>
+        <v>361818591.9</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778272159.84</v>
+        <v>1778305042.65</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122335221.9</v>
+        <v>2122368104.71</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364498323.55</v>
+        <v>364509733.66</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3919038.72</v>
+        <v>3919074.88</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6647069.28</v>
+        <v>6647130.61</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465517199.32</v>
+        <v>465528706.92</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364338723.72</v>
+        <v>1364384947.33</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1651108510.32</v>
+        <v>1651154733.93</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283692009.94</v>
+        <v>283707729.19</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4917058.6</v>
+        <v>4917129.61</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7352391.09</v>
+        <v>7352497.26</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374589249.31</v>
+        <v>374605145.74</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1037973174.56</v>
+        <v>1038042768.21</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347349891.35</v>
+        <v>1347419485</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218456127.31</v>
+        <v>218477105.39</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3629005.07</v>
+        <v>3629059.34</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4591974.5</v>
+        <v>4592043.16</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316805680.36</v>
+        <v>316826781.36</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143533255</v>
+        <v>1143641265.48</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1422015674.61</v>
+        <v>1422123685.09</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228204454.15</v>
+        <v>228239624.36</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3388431.03</v>
+        <v>3388556.76</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5521559.55</v>
+        <v>5521764.43</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>313987629.91</v>
+        <v>314023130.73</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339297798.67</v>
+        <v>1339459979.89</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1714871704.27</v>
+        <v>1715033885.49</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269890822.47</v>
+        <v>269948269.25</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2886519.57</v>
+        <v>2886676.18</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7560149.49</v>
+        <v>7560559.68</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389782960.87</v>
+        <v>389840974.46</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1172169834.71</v>
+        <v>1172325800.18</v>
       </c>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6" t="n">
@@ -2945,10 +2945,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1340097699.2</v>
+        <v>1340253664.67</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>220062654.22</v>
+        <v>220117832.27</v>
       </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n">
@@ -2958,16 +2958,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2498330.88</v>
+        <v>2498557.97</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>6813642.21</v>
+        <v>6814261.56</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>270266279.28</v>
+        <v>270322303.79</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.4394700544002308</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1224515303.34</v>
+        <v>1224919187.44</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>118878392.5</v>
@@ -3001,10 +3001,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1503275518.61</v>
+        <v>1503679402.71</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236802034.31</v>
+        <v>236940003.82</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>32561198.02</v>
@@ -3016,16 +3016,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5195674.53</v>
+        <v>5196549.27</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6919241.8</v>
+        <v>6920406.72</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>320332804.16</v>
+        <v>320472813.33</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3923339612110134</v>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1962527154.87</v>
+        <v>1838797795.92</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>151695056.58</v>
@@ -3057,10 +3057,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2385719419.31</v>
+        <v>2261990060.36</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>392922162.99</v>
+        <v>385208796.42</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>38969011.58</v>
@@ -3073,20 +3073,62 @@
       </c>
       <c r="N45" s="9" t="n"/>
       <c r="O45" s="9" t="n">
-        <v>17318221.84</v>
+        <v>18017772.04</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>517108095.26</v>
+        <v>510094278.89</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0.3664440983125071</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>1668253682.4</v>
+      </c>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n">
+        <v>98924928</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>64959415</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>1832138025.4</v>
+      </c>
+      <c r="J46" s="8" t="n">
+        <v>339249028.27</v>
+      </c>
+      <c r="K46" s="9" t="n"/>
+      <c r="L46" s="9" t="n"/>
+      <c r="M46" s="9" t="n"/>
+      <c r="N46" s="9" t="n"/>
+      <c r="O46" s="9" t="n">
+        <v>21229253.66</v>
+      </c>
+      <c r="P46" s="9" t="n">
+        <v>32697873.72</v>
+      </c>
+      <c r="Q46" s="9" t="n">
+        <v>393176155.65</v>
+      </c>
+      <c r="R46" s="10" t="n">
+        <v>0.247</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R45"/>
+  <autoFilter ref="A2:R46"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3102,7 +3144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5524,7 +5566,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>2628291138.41</v>
+        <v>2370000000</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>152527110.31</v>
@@ -5543,10 +5585,10 @@
         <v>34419473</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>3057627304.58</v>
+        <v>2799336166.17</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>729613620.02</v>
+        <v>657912000</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>39087094.48</v>
@@ -5559,17 +5601,56 @@
       </c>
       <c r="N45" s="9" t="n"/>
       <c r="O45" s="9" t="n">
-        <v>23348429.55</v>
+        <v>23379323.68</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>16489733.2</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>860775556.98</v>
+        <v>789104831.09</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>2234233434.52</v>
+      </c>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n">
+        <v>101814088</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>66113614</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>2402161136.52</v>
+      </c>
+      <c r="J46" s="8" t="n">
+        <v>620223201.42</v>
+      </c>
+      <c r="K46" s="9" t="n"/>
+      <c r="L46" s="9" t="n"/>
+      <c r="M46" s="9" t="n"/>
+      <c r="N46" s="9" t="n"/>
+      <c r="O46" s="9" t="n">
+        <v>28915978.17</v>
+      </c>
+      <c r="P46" s="9" t="n">
+        <v>33092919.58</v>
+      </c>
+      <c r="Q46" s="9" t="n">
+        <v>682232099.17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q45"/>
+  <autoFilter ref="A2:Q46"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -5584,7 +5665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6511,7 +6592,7 @@
         <v>9845111</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.5922999999999999</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="I22" s="11" t="n">
         <v>0.2813</v>
@@ -7285,7 +7366,7 @@
         <v>7061846</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>0.631</v>
+        <v>0.6309</v>
       </c>
       <c r="I40" s="11" t="n">
         <v>0.3536</v>
@@ -7371,7 +7452,7 @@
         <v>15189926</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.6435</v>
       </c>
       <c r="I42" s="11" t="n">
         <v>0.3605</v>
@@ -7412,7 +7493,7 @@
         <v>13411796</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>0.6738</v>
+        <v>0.6737000000000001</v>
       </c>
       <c r="I43" s="11" t="n">
         <v>0.3466</v>
@@ -7453,7 +7534,7 @@
         <v>12049458</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>0.6686</v>
+        <v>0.6683</v>
       </c>
       <c r="I44" s="11" t="n">
         <v>0.4026</v>
@@ -7478,7 +7559,7 @@
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>1265679880.61</v>
+        <v>1141297200</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>25784306.09</v>
@@ -7494,7 +7575,7 @@
         <v>21875177</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>0.6448999999999999</v>
+        <v>0.6207</v>
       </c>
       <c r="I45" s="11" t="n">
         <v>0.3898</v>
@@ -7510,15 +7591,42 @@
         <v>0.2738</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>1075917452.73</v>
+      </c>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n">
+        <v>24436069</v>
+      </c>
+      <c r="H46" s="11" t="n">
+        <v>0.6448999999999999</v>
+      </c>
+      <c r="I46" s="11" t="n"/>
+      <c r="J46" s="11" t="n"/>
+      <c r="K46" s="11" t="n"/>
+      <c r="L46" s="11" t="n"/>
+      <c r="M46" s="11" t="n">
+        <v>0.247</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M45"/>
+  <autoFilter ref="A2:M46"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -7549,7 +7657,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-13. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-14. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226359047.97</v>
+        <v>1226360067.97</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404321142.55</v>
+        <v>1404322162.55</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290715347.52</v>
+        <v>290715362.32</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524812.8</v>
+        <v>524812.4300000001</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360284.49</v>
+        <v>9360277.9</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354058351.45</v>
+        <v>354058359.28</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983762949.55</v>
+        <v>983762958.55</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168401098.57</v>
+        <v>1168401107.57</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236064404.4</v>
+        <v>236064404.85</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -819,13 +819,13 @@
         <v>324588.54</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358543.06</v>
+        <v>7358543.01</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305861120.57</v>
+        <v>305861120.98</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097588708.03</v>
+        <v>1097588734.61</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302668745.61</v>
+        <v>1302668772.19</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250951038.92</v>
+        <v>250951048.49</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.46</v>
+        <v>709927.47</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693356.64</v>
+        <v>7693356.71</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328055054.28</v>
+        <v>328055063.93</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011523877.55</v>
+        <v>1011523900.96</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233696997.06</v>
+        <v>1233697020.47</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229525913.28</v>
+        <v>229525927.09</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255745.66</v>
+        <v>1255745.69</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409744.25</v>
+        <v>8409744.48</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309200859.85</v>
+        <v>309200873.92</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961942323.58</v>
+        <v>961942863.58</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145549485.12</v>
+        <v>1145550025.12</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214890608.89</v>
+        <v>214890645.49</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814778.6800000001</v>
+        <v>814778.39</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850545.65</v>
+        <v>6850543.24</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281207778.41</v>
+        <v>281207812.32</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073048473.57</v>
+        <v>1073048493.36</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277714371.05</v>
+        <v>1277714390.84</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240126105.36</v>
+        <v>240126115</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353403.78</v>
+        <v>2353403.82</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569927.27</v>
+        <v>7569927.39</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313749914.29</v>
+        <v>313749924.09</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960775761.9</v>
+        <v>960775832.9</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185449079.02</v>
+        <v>1185449150.02</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212551689.99</v>
+        <v>212551716.25</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490168.64</v>
+        <v>2490168.72</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929344.52</v>
+        <v>8929344.779999999</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296186543.85</v>
+        <v>296186570.45</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686510814.01</v>
+        <v>686510854.01</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813422505.04</v>
+        <v>813422545.04</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150992614.67</v>
+        <v>150992619.37</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897064.22</v>
+        <v>1897064.17</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485526.61</v>
+        <v>3485526.52</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196257165.4</v>
+        <v>196257169.96</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970910492.75</v>
+        <v>970910497.75</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130467146.99</v>
+        <v>1130467151.99</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227541652.15</v>
+        <v>227541653.05</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1231,7 +1231,7 @@
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286539353.17</v>
+        <v>286539354.06</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042731307.08</v>
+        <v>1042731401.84</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244215497.15</v>
+        <v>1244215591.91</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230883759.96</v>
+        <v>230883764.92</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865669.85</v>
+        <v>2865669.68</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026082.52</v>
+        <v>7026082.09</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305688583.78</v>
+        <v>305688588.12</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026526753.33</v>
+        <v>1026526817.68</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228670632.36</v>
+        <v>1228670696.71</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246156789.24</v>
+        <v>246156816.98</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558675.26</v>
+        <v>3558675.39</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537379.28</v>
+        <v>7537379.56</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315576897.94</v>
+        <v>315576926.09</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275233774.87</v>
+        <v>1275234525.36</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517955252.12</v>
+        <v>1517956002.61</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295676822.44</v>
+        <v>295676875.73</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271141.25</v>
+        <v>4271139.68</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581202.609999999</v>
+        <v>9581199.09</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378773162.18</v>
+        <v>378773210.38</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123210816.15</v>
+        <v>1123210846.3</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375385977.48</v>
+        <v>1375386007.63</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251891900.23</v>
+        <v>251891908.69</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520549.57</v>
+        <v>3520549.58</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255915.39</v>
+        <v>11255915.43</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341111322.03</v>
+        <v>341111330.54</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780514859.41</v>
+        <v>780514869.3099999</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941931704.9400001</v>
+        <v>941931714.84</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182890873.33</v>
+        <v>182890879.16</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893249.48</v>
+        <v>2893249.52</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978990.74</v>
+        <v>4978990.82</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240374956.48</v>
+        <v>240374962.43</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925223184.05</v>
+        <v>925223391.5</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103226567.87</v>
+        <v>1103226775.32</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208939531.88</v>
+        <v>208939590.71</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099145.6</v>
+        <v>3099145.69</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218664.54</v>
+        <v>6218664.73</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270757852.03</v>
+        <v>270757911.14</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099263517.88</v>
+        <v>1099263918.03</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314563811.7</v>
+        <v>1314564211.85</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244622568.78</v>
+        <v>244622733.6</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671186.07</v>
+        <v>3671186.88</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710544.49</v>
+        <v>7710546.18</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319476720.04</v>
+        <v>319476887.36</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967592674.75</v>
+        <v>967592732.75</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190913680.33</v>
+        <v>1190913738.33</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210534002.06</v>
+        <v>210534020.29</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281810.23</v>
+        <v>3281810.28</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536323.86</v>
+        <v>7536323.98</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283817016.81</v>
+        <v>283817035.22</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003078424.37</v>
+        <v>1003078471.09</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198235112.43</v>
+        <v>1198235159.15</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222088374.38</v>
+        <v>222088390.79</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891041.09</v>
+        <v>3891041.17</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335939.95</v>
+        <v>6335940.08</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281019850.36</v>
+        <v>281019866.97</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362286346.21</v>
+        <v>1362286573.21</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634503101.33</v>
+        <v>1634503328.33</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306762584.8</v>
+        <v>306762675.26</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136468.96</v>
+        <v>6136469.56</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270560.02</v>
+        <v>10270561.03</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388021745.27</v>
+        <v>388021837.35</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156893098.04</v>
+        <v>1156894195.57</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409393065.69</v>
+        <v>1409394163.22</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247797745.47</v>
+        <v>247797783.75</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795240.12</v>
+        <v>3795237.5</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929402.92</v>
+        <v>9929396.060000001</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325995613.29</v>
+        <v>325995642.09</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870293078.5</v>
+        <v>870295671.52</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039397290.87</v>
+        <v>1039399883.89</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193431819.39</v>
+        <v>193432340.98</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256069.12</v>
+        <v>3256067.87</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684215.87</v>
+        <v>5684213.7</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245273916.01</v>
+        <v>245274434.19</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002261643.14</v>
+        <v>1002262367.19</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209599051.1</v>
+        <v>1209599775.15</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>216999992.87</v>
+        <v>217000193.54</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934144.47</v>
+        <v>2934144.82</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937713.33</v>
+        <v>6937714.17</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280972255.75</v>
+        <v>280972457.6</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105960743.67</v>
+        <v>1105961013.05</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351815643.32</v>
+        <v>1351815912.7</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242482900.58</v>
+        <v>242482959.62</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693255.4</v>
+        <v>2693255.35</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764064.42</v>
+        <v>8764064.27</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322796699.39</v>
+        <v>322796758.24</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932835414.99</v>
+        <v>932837759.46</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136783229.44</v>
+        <v>1136785573.91</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196523247.42</v>
+        <v>196523461.12</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927937.03</v>
+        <v>2927933.26</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577868.15</v>
+        <v>6577859.69</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259477393.96</v>
+        <v>259477595.43</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1162023256.99</v>
+        <v>1162026469.66</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354859741.06</v>
+        <v>1354862953.73</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252350382.04</v>
+        <v>252351621.93</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229191.92</v>
+        <v>4229198.89</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541678.01</v>
+        <v>4541685.51</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311962970.6</v>
+        <v>311964224.96</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439998288.31</v>
+        <v>1439998479.4</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740054954.34</v>
+        <v>1740055145.43</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284717205.62</v>
+        <v>284717249.52</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067081.67</v>
+        <v>4067081.7</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978503.09</v>
+        <v>5978503.13</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375587979.24</v>
+        <v>375588023.21</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319725505.19</v>
+        <v>1319725757.93</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579488589.31</v>
+        <v>1579488842.05</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283376917.32</v>
+        <v>283376974.1</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050968.15</v>
+        <v>3050968.13</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438412.32</v>
+        <v>7438412.29</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363617662.3</v>
+        <v>363617719.04</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096994942.9</v>
+        <v>1096995535.19</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283035969.01</v>
+        <v>1283036561.3</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243425475.44</v>
+        <v>243425712.05</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660621.71</v>
+        <v>1660622.26</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202028.77</v>
+        <v>7202031.15</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302143017.45</v>
+        <v>302143257</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142111662.52</v>
+        <v>1142118984.5</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1366002776.47</v>
+        <v>1366010098.45</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239658182.52</v>
+        <v>239658840.3</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298514.96</v>
+        <v>1298510.63</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234310.75</v>
+        <v>9234279.960000001</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307451382.97</v>
+        <v>307452005.63</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192843449.73</v>
+        <v>1192844672.23</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436500456.4</v>
+        <v>1436501678.9</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253629810.84</v>
+        <v>253630242.68</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145315.76</v>
+        <v>2145316.79</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745135.24</v>
+        <v>6745138.47</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327984664.05</v>
+        <v>327985100.14</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226934158.15</v>
+        <v>1226935410.62</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494274449.02</v>
+        <v>1494275701.49</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272957328.24</v>
+        <v>272957501.24</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511838.73</v>
+        <v>2511837.8</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248297.99</v>
+        <v>7248295.32</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361199549.65</v>
+        <v>361199719.04</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348607805.31</v>
+        <v>1348612791.82</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622927950.06</v>
+        <v>1622932936.57</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278431696.7</v>
+        <v>278433841.29</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307519.14</v>
+        <v>2307525.92</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088469.26</v>
+        <v>8088493.04</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361818591.9</v>
+        <v>361820767.04</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778305042.65</v>
+        <v>1778307419.94</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122368104.71</v>
+        <v>2122370482</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364509733.66</v>
+        <v>364511021.48</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3919074.88</v>
+        <v>3919081.48</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6647130.61</v>
+        <v>6647141.81</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465528706.92</v>
+        <v>465530012.54</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364384947.33</v>
+        <v>1364394887.53</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1651154733.93</v>
+        <v>1651164674.13</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283707729.19</v>
+        <v>283713767.06</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4917129.61</v>
+        <v>4917180.94</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7352497.26</v>
+        <v>7352574.02</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374605145.74</v>
+        <v>374611311.7</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1038042768.21</v>
+        <v>1038045932.72</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347419485</v>
+        <v>1347422649.51</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218477105.39</v>
+        <v>218477706.92</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3629059.34</v>
+        <v>3629057.66</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4592043.16</v>
+        <v>4592041.04</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316826781.36</v>
+        <v>316827379.1</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143641265.48</v>
+        <v>1143655074.07</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1422123685.09</v>
+        <v>1422137493.68</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228239624.36</v>
+        <v>228247036.42</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3388556.76</v>
+        <v>3388605.21</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5521764.43</v>
+        <v>5521843.39</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>314023130.73</v>
+        <v>314030670.2</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339459979.89</v>
+        <v>1339474995.46</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1715033885.49</v>
+        <v>1715048901.06</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269948269.25</v>
+        <v>269951514.51</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2886676.18</v>
+        <v>2886674.9</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7560559.68</v>
+        <v>7560556.33</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389840974.46</v>
+        <v>389844215.1</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1172325800.18</v>
+        <v>1172339049.5</v>
       </c>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6" t="n">
@@ -2945,10 +2945,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1340253664.67</v>
+        <v>1340266913.99</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>220117832.27</v>
+        <v>220121807.56</v>
       </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n">
@@ -2958,16 +2958,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2498557.97</v>
+        <v>2498570.45</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>6814261.56</v>
+        <v>6814295.58</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>270322303.79</v>
+        <v>270326325.57</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.4394700544002308</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1224919187.44</v>
+        <v>1224947180.94</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>118878392.5</v>
@@ -3001,10 +3001,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1503679402.71</v>
+        <v>1503707396.21</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236940003.82</v>
+        <v>236949831.48</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>32561198.02</v>
@@ -3016,16 +3016,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5196549.27</v>
+        <v>5196614.35</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6920406.72</v>
+        <v>6920493.38</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>320472813.33</v>
+        <v>320482792.73</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3923339612110134</v>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1838797795.92</v>
+        <v>1838839614.69</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>151695056.58</v>
@@ -3049,7 +3049,9 @@
       <c r="E45" s="6" t="n">
         <v>93309716</v>
       </c>
-      <c r="F45" s="6" t="n"/>
+      <c r="F45" s="6" t="n">
+        <v>46812451.04</v>
+      </c>
       <c r="G45" s="6" t="n">
         <v>79898997</v>
       </c>
@@ -3057,10 +3059,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2261990060.36</v>
+        <v>2308844330.17</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>385208796.42</v>
+        <v>385222268.64</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>38969011.58</v>
@@ -3071,18 +3073,20 @@
       <c r="M45" s="9" t="n">
         <v>28343613.08</v>
       </c>
-      <c r="N45" s="9" t="n"/>
+      <c r="N45" s="9" t="n">
+        <v>10556615.61</v>
+      </c>
       <c r="O45" s="9" t="n">
-        <v>18017772.04</v>
+        <v>18017920.03</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>510094278.89</v>
+        <v>520664514.71</v>
       </c>
       <c r="R45" s="10" t="n">
-        <v>0.3664440983125071</v>
+        <v>0.4083810879699633</v>
       </c>
     </row>
     <row r="46">
@@ -3092,12 +3096,18 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1668253682.4</v>
+        <v>1902619720.21</v>
       </c>
       <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
+      <c r="D46" s="6" t="n">
+        <v>69142299.48</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>137656512</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>53729151.21</v>
+      </c>
       <c r="G46" s="6" t="n">
         <v>98924928</v>
       </c>
@@ -3105,26 +3115,32 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>1832138025.4</v>
+        <v>2327032025.9</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>339249028.27</v>
+        <v>382604396.38</v>
       </c>
       <c r="K46" s="9" t="n"/>
-      <c r="L46" s="9" t="n"/>
-      <c r="M46" s="9" t="n"/>
-      <c r="N46" s="9" t="n"/>
+      <c r="L46" s="9" t="n">
+        <v>23371135.67</v>
+      </c>
+      <c r="M46" s="9" t="n">
+        <v>30010982.69</v>
+      </c>
+      <c r="N46" s="9" t="n">
+        <v>11581249.9</v>
+      </c>
       <c r="O46" s="9" t="n">
-        <v>21229253.66</v>
+        <v>21323141.85</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>393176155.65</v>
+        <v>501588780.21</v>
       </c>
       <c r="R46" s="10" t="n">
-        <v>0.247</v>
+        <v>0.5318716921548481</v>
       </c>
     </row>
   </sheetData>
@@ -5577,7 +5593,9 @@
       <c r="E45" s="6" t="n">
         <v>93309716</v>
       </c>
-      <c r="F45" s="6" t="n"/>
+      <c r="F45" s="6" t="n">
+        <v>46812451.04</v>
+      </c>
       <c r="G45" s="6" t="n">
         <v>82937759</v>
       </c>
@@ -5585,7 +5603,7 @@
         <v>34419473</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2799336166.17</v>
+        <v>2846148617.21</v>
       </c>
       <c r="J45" s="8" t="n">
         <v>657912000</v>
@@ -5599,7 +5617,9 @@
       <c r="M45" s="9" t="n">
         <v>28343613.08</v>
       </c>
-      <c r="N45" s="9" t="n"/>
+      <c r="N45" s="9" t="n">
+        <v>13195961.14</v>
+      </c>
       <c r="O45" s="9" t="n">
         <v>23379323.68</v>
       </c>
@@ -5607,7 +5627,7 @@
         <v>16489733.2</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>789104831.09</v>
+        <v>802300792.23</v>
       </c>
     </row>
     <row r="46">
@@ -5617,12 +5637,18 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>2234233434.52</v>
+        <v>2548078774.13</v>
       </c>
       <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
+      <c r="D46" s="6" t="n">
+        <v>69142299.48</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>137656512</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>53729151.21</v>
+      </c>
       <c r="G46" s="6" t="n">
         <v>101814088</v>
       </c>
@@ -5630,23 +5656,29 @@
         <v>66113614</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2402161136.52</v>
+        <v>2976534438.82</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>620223201.42</v>
+        <v>707346667.7</v>
       </c>
       <c r="K46" s="9" t="n"/>
-      <c r="L46" s="9" t="n"/>
-      <c r="M46" s="9" t="n"/>
-      <c r="N46" s="9" t="n"/>
+      <c r="L46" s="9" t="n">
+        <v>23371135.67</v>
+      </c>
+      <c r="M46" s="9" t="n">
+        <v>30010982.69</v>
+      </c>
+      <c r="N46" s="9" t="n">
+        <v>15119283.77</v>
+      </c>
       <c r="O46" s="9" t="n">
-        <v>28915978.17</v>
+        <v>28650296.04</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>33092919.58</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>682232099.17</v>
+        <v>837591285.45</v>
       </c>
     </row>
   </sheetData>
@@ -7570,7 +7602,9 @@
       <c r="E45" s="6" t="n">
         <v>53274388.26</v>
       </c>
-      <c r="F45" s="6" t="n"/>
+      <c r="F45" s="6" t="n">
+        <v>35518475.4</v>
+      </c>
       <c r="G45" s="6" t="n">
         <v>21875177</v>
       </c>
@@ -7586,7 +7620,9 @@
       <c r="K45" s="11" t="n">
         <v>0.3512</v>
       </c>
-      <c r="L45" s="11" t="n"/>
+      <c r="L45" s="11" t="n">
+        <v>0.7587</v>
+      </c>
       <c r="M45" s="11" t="n">
         <v>0.2738</v>
       </c>
@@ -7598,22 +7634,34 @@
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>1075917452.73</v>
-      </c>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
+        <v>1227052814.47</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>30527478.39</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>87962042</v>
+      </c>
       <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
+      <c r="F46" s="6" t="n">
+        <v>48256943.28</v>
+      </c>
       <c r="G46" s="6" t="n">
         <v>24436069</v>
       </c>
       <c r="H46" s="11" t="n">
         <v>0.6448999999999999</v>
       </c>
-      <c r="I46" s="11" t="n"/>
-      <c r="J46" s="11" t="n"/>
+      <c r="I46" s="11" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="J46" s="11" t="n">
+        <v>0.639</v>
+      </c>
       <c r="K46" s="11" t="n"/>
-      <c r="L46" s="11" t="n"/>
+      <c r="L46" s="11" t="n">
+        <v>0.8981999999999999</v>
+      </c>
       <c r="M46" s="11" t="n">
         <v>0.247</v>
       </c>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226360067.97</v>
+        <v>1226360088.39</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404322162.55</v>
+        <v>1404322182.97</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290715362.32</v>
+        <v>290715366.9</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -653,13 +653,13 @@
         <v>524812.4300000001</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360277.9</v>
+        <v>9360277.890000001</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354058359.28</v>
+        <v>354058363.85</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019798550.38</v>
+        <v>1019798715.57</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203203459.89</v>
+        <v>1203203625.08</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223747291.29</v>
+        <v>223747329.23</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -707,13 +707,13 @@
         <v>516298.08</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237375.439999999</v>
+        <v>9237375.380000001</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289059070.59</v>
+        <v>289059108.47</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766408358.99</v>
+        <v>766408714.64</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882450906.03</v>
+        <v>882451261.6799999</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197402127.89</v>
+        <v>197402162.67</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374708.95</v>
+        <v>374708.85</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399338.25</v>
+        <v>5399336.83</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239491457.47</v>
+        <v>239491490.72</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097588734.61</v>
+        <v>1097588833.62</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302668772.19</v>
+        <v>1302668871.2</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250951048.49</v>
+        <v>250951071.26</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.47</v>
+        <v>709927.46</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693356.71</v>
+        <v>7693356.66</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328055063.93</v>
+        <v>328055086.64</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011523900.96</v>
+        <v>1011524092.28</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233697020.47</v>
+        <v>1233697211.79</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229525927.09</v>
+        <v>229525975.24</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -941,7 +941,7 @@
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309200873.92</v>
+        <v>309200922.08</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073048493.36</v>
+        <v>1073048832.28</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277714390.84</v>
+        <v>1277714729.76</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240126115</v>
+        <v>240126171.53</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353403.82</v>
+        <v>2353403.61</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569927.39</v>
+        <v>7569926.72</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313749924.09</v>
+        <v>313749979.75</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960775832.9</v>
+        <v>960776228.9</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185449150.02</v>
+        <v>1185449546.02</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212551716.25</v>
+        <v>212551849.64</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490168.72</v>
+        <v>2490169.02</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929344.779999999</v>
+        <v>8929345.859999999</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296186570.45</v>
+        <v>296186705.22</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686510854.01</v>
+        <v>686510951.01</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813422545.04</v>
+        <v>813422642.04</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150992619.37</v>
+        <v>150992642.65</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1173,7 +1173,7 @@
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196257169.96</v>
+        <v>196257193.23</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970910497.75</v>
+        <v>970910827.75</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130467151.99</v>
+        <v>1130467481.99</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227541653.05</v>
+        <v>227541679.45</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642027.67</v>
+        <v>2642027.12</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513124.9</v>
+        <v>5513123.76</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286539354.06</v>
+        <v>286539378.79</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042731401.84</v>
+        <v>1042731531.26</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244215591.91</v>
+        <v>1244215721.33</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230883764.92</v>
+        <v>230883812.81</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865669.68</v>
+        <v>2865669.83</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026082.09</v>
+        <v>7026082.47</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305688588.12</v>
+        <v>305688636.55</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046531651.65</v>
+        <v>1046532073.87</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268578751.46</v>
+        <v>1268579173.68</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238383400.24</v>
+        <v>238383498.58</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737712.71</v>
+        <v>3737712.63</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838302.63</v>
+        <v>7838302.46</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315850152.38</v>
+        <v>315850250.46</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026526817.68</v>
+        <v>1026526859.68</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228670696.71</v>
+        <v>1228670738.71</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246156816.98</v>
+        <v>246156826.31</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558675.39</v>
+        <v>3558675.37</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537379.56</v>
+        <v>7537379.52</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315576926.09</v>
+        <v>315576935.37</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275234525.36</v>
+        <v>1275234589.56</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517956002.61</v>
+        <v>1517956066.81</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295676875.73</v>
+        <v>295676886.15</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271139.68</v>
+        <v>4271139.62</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581199.09</v>
+        <v>9581198.939999999</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378773210.38</v>
+        <v>378773220.59</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123210846.3</v>
+        <v>1123211110.07</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375386007.63</v>
+        <v>1375386271.4</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251891908.69</v>
+        <v>251892009.06</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520549.58</v>
+        <v>3520549.96</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255915.43</v>
+        <v>11255916.63</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341111330.54</v>
+        <v>341111432.49</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780514869.3099999</v>
+        <v>780514888.38</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941931714.84</v>
+        <v>941931733.91</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182890879.16</v>
+        <v>182890884.11</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1579,7 +1579,7 @@
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240374962.43</v>
+        <v>240374967.38</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925223391.5</v>
+        <v>925223588.2</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103226775.32</v>
+        <v>1103226972.02</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208939590.71</v>
+        <v>208939609.52</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099145.69</v>
+        <v>3099145.34</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218664.73</v>
+        <v>6218664.03</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270757911.14</v>
+        <v>270757928.9</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099263918.03</v>
+        <v>1099263923.03</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314564211.85</v>
+        <v>1314564216.85</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244622733.6</v>
+        <v>244622737.95</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671186.88</v>
+        <v>3671186.92</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710546.18</v>
+        <v>7710546.26</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319476887.36</v>
+        <v>319476891.83</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967592732.75</v>
+        <v>967592842.47</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190913738.33</v>
+        <v>1190913848.05</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210534020.29</v>
+        <v>210534058.08</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281810.28</v>
+        <v>3281810.42</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536323.98</v>
+        <v>7536324.3</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283817035.22</v>
+        <v>283817073.47</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003078471.09</v>
+        <v>1003078500.6</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198235159.15</v>
+        <v>1198235188.66</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222088390.79</v>
+        <v>222088395.52</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891041.17</v>
+        <v>3891041.14</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335940.08</v>
+        <v>6335940.03</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281019866.97</v>
+        <v>281019871.62</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362286573.21</v>
+        <v>1362287134.62</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634503328.33</v>
+        <v>1634503889.74</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306762675.26</v>
+        <v>306762685.55</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136469.56</v>
+        <v>6136467.53</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270561.03</v>
+        <v>10270557.63</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388021837.35</v>
+        <v>388021842.21</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156894195.57</v>
+        <v>1156894339.57</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409394163.22</v>
+        <v>1409394307.22</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247797783.75</v>
+        <v>247797809.91</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795237.5</v>
+        <v>3795237.41</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929396.060000001</v>
+        <v>9929395.84</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325995642.09</v>
+        <v>325995667.94</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870295671.52</v>
+        <v>870296411.08</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039399883.89</v>
+        <v>1039400623.45</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193432340.98</v>
+        <v>193432449.79</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256067.87</v>
+        <v>3256066.97</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684213.7</v>
+        <v>5684212.12</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245274434.19</v>
+        <v>245274540.51</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002262367.19</v>
+        <v>1002262868.89</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209599775.15</v>
+        <v>1209600276.85</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>217000193.54</v>
+        <v>217000311.73</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934144.82</v>
+        <v>2934144.84</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937714.17</v>
+        <v>6937714.21</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280972457.6</v>
+        <v>280972575.85</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105961013.05</v>
+        <v>1105961332.18</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351815912.7</v>
+        <v>1351816231.83</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242482959.62</v>
+        <v>242483011.96</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693255.35</v>
+        <v>2693255.15</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764064.27</v>
+        <v>8764063.6</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322796758.24</v>
+        <v>322796809.7</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932837759.46</v>
+        <v>932840040</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136785573.91</v>
+        <v>1136787854.45</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196523461.12</v>
+        <v>196523677.75</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927933.26</v>
+        <v>2927929.7</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577859.69</v>
+        <v>6577851.69</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259477595.43</v>
+        <v>259477800.51</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1162026469.66</v>
+        <v>1162026561.98</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354862953.73</v>
+        <v>1354863046.05</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252351621.93</v>
+        <v>252351659.12</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229198.89</v>
+        <v>4229199.12</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541685.51</v>
+        <v>4541685.75</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311964224.96</v>
+        <v>311964262.61</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439998479.4</v>
+        <v>1439999350.39</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740055145.43</v>
+        <v>1740056016.42</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284717249.52</v>
+        <v>284717574.18</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067081.7</v>
+        <v>4067083.22</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978503.13</v>
+        <v>5978505.37</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375588023.21</v>
+        <v>375588351.63</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319725757.93</v>
+        <v>1319726537.97</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579488842.05</v>
+        <v>1579489622.09</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283376974.1</v>
+        <v>283377339.55</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050968.13</v>
+        <v>3050969.74</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438412.29</v>
+        <v>7438416.2</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363617719.04</v>
+        <v>363618090.01</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096995535.19</v>
+        <v>1096995658.4</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283036561.3</v>
+        <v>1283036684.51</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243425712.05</v>
+        <v>243425732.96</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660622.26</v>
+        <v>1660622.22</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202031.15</v>
+        <v>7202030.95</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302143257</v>
+        <v>302143277.66</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142118984.5</v>
+        <v>1142119113.11</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1366010098.45</v>
+        <v>1366010227.06</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239658840.3</v>
+        <v>239658853.09</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298510.63</v>
+        <v>1298510.56</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234279.960000001</v>
+        <v>9234279.449999999</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307452005.63</v>
+        <v>307452017.84</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192844672.23</v>
+        <v>1192845018.21</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436501678.9</v>
+        <v>1436502024.88</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253630242.68</v>
+        <v>253630471.11</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145316.79</v>
+        <v>2145317.8</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745138.47</v>
+        <v>6745141.63</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327985100.14</v>
+        <v>327985332.74</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226935410.62</v>
+        <v>1226935706.02</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494275701.49</v>
+        <v>1494275996.89</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272957501.24</v>
+        <v>272957573.07</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511837.8</v>
+        <v>2511837.81</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248295.32</v>
+        <v>7248295.33</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361199719.04</v>
+        <v>361199790.88</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348612791.82</v>
+        <v>1348613742.4</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622932936.57</v>
+        <v>1622933887.15</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278433841.29</v>
+        <v>278434307.01</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307525.92</v>
+        <v>2307527.59</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088493.04</v>
+        <v>8088498.88</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361820767.04</v>
+        <v>361821240.27</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778307419.94</v>
+        <v>1778307676.58</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122370482</v>
+        <v>2122370738.64</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364511021.48</v>
+        <v>364511086.6</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3919081.48</v>
+        <v>3919081.56</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6647141.81</v>
+        <v>6647141.94</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465530012.54</v>
+        <v>465530077.86</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364394887.53</v>
+        <v>1364400925.22</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1651164674.13</v>
+        <v>1651170711.82</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283713767.06</v>
+        <v>283715770.86</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4917180.94</v>
+        <v>4917189.55</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7352574.02</v>
+        <v>7352586.88</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374611311.7</v>
+        <v>374613336.97</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1038045932.72</v>
+        <v>1038048037.61</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347422649.51</v>
+        <v>1347424754.4</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218477706.92</v>
+        <v>218478295.06</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3629057.66</v>
+        <v>3629058.75</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4592041.04</v>
+        <v>4592042.43</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316827379.1</v>
+        <v>316827969.72</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143655074.07</v>
+        <v>1143658202.59</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1422137493.68</v>
+        <v>1422140622.2</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228247036.42</v>
+        <v>228247839.13</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3388605.21</v>
+        <v>3388606.45</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5521843.39</v>
+        <v>5521845.41</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>314030670.2</v>
+        <v>314031476.18</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339474995.46</v>
+        <v>1339477795.27</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1715048901.06</v>
+        <v>1715051700.87</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269951514.51</v>
+        <v>269952368.76</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2886674.9</v>
+        <v>2886676.56</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7560556.33</v>
+        <v>7560560.67</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389844215.1</v>
+        <v>389845075.34</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1172339049.5</v>
+        <v>1172343535.55</v>
       </c>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6" t="n">
@@ -2945,10 +2945,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1340266913.99</v>
+        <v>1340271400.04</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>220121807.56</v>
+        <v>220123050.96</v>
       </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n">
@@ -2958,16 +2958,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2498570.45</v>
+        <v>2498573.69</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>6814295.58</v>
+        <v>6814304.42</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>270326325.57</v>
+        <v>270327581.05</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.4394700544002308</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1224947180.94</v>
+        <v>1224961315.84</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>118878392.5</v>
@@ -3001,10 +3001,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1503707396.21</v>
+        <v>1503721531.11</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236949831.48</v>
+        <v>236954921.87</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>32561198.02</v>
@@ -3016,16 +3016,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5196614.35</v>
+        <v>5196649.36</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6920493.38</v>
+        <v>6920540.01</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>320482792.73</v>
+        <v>320487964.77</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3923339612110134</v>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1838839614.69</v>
+        <v>1838867508.19</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>151695056.58</v>
@@ -3059,10 +3059,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2308844330.17</v>
+        <v>2308872223.67</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>385222268.64</v>
+        <v>385234510.67</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>38969011.58</v>
@@ -3074,16 +3074,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>10556615.61</v>
+        <v>10556743.29</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>18017920.03</v>
+        <v>18018137.95</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>520664514.71</v>
+        <v>520677102.34</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0.4083810879699633</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1902619720.21</v>
+        <v>1903239188.97</v>
       </c>
       <c r="C46" s="6" t="n"/>
       <c r="D46" s="6" t="n">
@@ -3115,10 +3115,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2327032025.9</v>
+        <v>2327651494.66</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>382604396.38</v>
+        <v>382714232.41</v>
       </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n">
@@ -3128,16 +3128,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>11581249.9</v>
+        <v>11580664.69</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>21323141.85</v>
+        <v>21322064.37</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>501588780.21</v>
+        <v>501696953.56</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0.5318716921548481</v>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>2548078774.13</v>
+        <v>2548893109.12</v>
       </c>
       <c r="C46" s="6" t="n"/>
       <c r="D46" s="6" t="n">
@@ -5656,10 +5656,10 @@
         <v>66113614</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2976534438.82</v>
+        <v>2977348773.81</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>707346667.7</v>
+        <v>707572727.09</v>
       </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n">
@@ -5669,16 +5669,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>15119283.77</v>
+        <v>15119224.88</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>28650296.04</v>
+        <v>28650184.44</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>33092919.58</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>837591285.45</v>
+        <v>837817174.35</v>
       </c>
     </row>
   </sheetData>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>1227052814.47</v>
+        <v>1227444965.63</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>30527478.39</v>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R46"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226360088.39</v>
+        <v>1226360709.94</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404322182.97</v>
+        <v>1404322804.52</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290715366.9</v>
+        <v>290715403.68</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524812.4300000001</v>
+        <v>524812.25</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360277.890000001</v>
+        <v>9360274.630000001</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354058363.85</v>
+        <v>354058397.18</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019798715.57</v>
+        <v>1019798856.73</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203203625.08</v>
+        <v>1203203766.24</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223747329.23</v>
+        <v>223747343.14</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516298.08</v>
+        <v>516298.04</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237375.380000001</v>
+        <v>9237374.720000001</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289059108.47</v>
+        <v>289059121.68</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766408714.64</v>
+        <v>766409057.53</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882451261.6799999</v>
+        <v>882451604.5700001</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197402162.67</v>
+        <v>197402434.93</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374708.85</v>
+        <v>374709.13</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399336.83</v>
+        <v>5399340.97</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239491490.72</v>
+        <v>239491767.41</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983762958.55</v>
+        <v>983763420.67</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168401107.57</v>
+        <v>1168401569.69</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236064404.85</v>
+        <v>236064611.36</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324588.54</v>
+        <v>324588.64</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358543.01</v>
+        <v>7358545.12</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305861120.98</v>
+        <v>305861329.69</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011524092.28</v>
+        <v>1011525363.26</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233697211.79</v>
+        <v>1233698482.77</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229525975.24</v>
+        <v>229526107.1</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255745.69</v>
+        <v>1255744.91</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409744.48</v>
+        <v>8409739.24</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309200922.08</v>
+        <v>309201047.91</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961942863.58</v>
+        <v>961943767.05</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145550025.12</v>
+        <v>1145550928.59</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214890645.49</v>
+        <v>214890661.29</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814778.39</v>
+        <v>814777.78</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850543.24</v>
+        <v>6850538.09</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281207812.32</v>
+        <v>281207822.35</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073048832.28</v>
+        <v>1073048834.28</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277714729.76</v>
+        <v>1277714731.76</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240126171.53</v>
+        <v>240126173.35</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353403.61</v>
+        <v>2353403.62</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569926.72</v>
+        <v>7569926.76</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313749979.75</v>
+        <v>313749981.61</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960776228.9</v>
+        <v>960777160.66</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185449546.02</v>
+        <v>1185450477.78</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212551849.64</v>
+        <v>212552325.31</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490169.02</v>
+        <v>2490171.14</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929345.859999999</v>
+        <v>8929353.48</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296186705.22</v>
+        <v>296187190.63</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686510951.01</v>
+        <v>686511834.17</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813422642.04</v>
+        <v>813423525.2</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150992642.65</v>
+        <v>150992992.33</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897064.17</v>
+        <v>1897065.52</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485526.52</v>
+        <v>3485529.01</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196257193.23</v>
+        <v>196257546.76</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970910827.75</v>
+        <v>970911906.72</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130467481.99</v>
+        <v>1130468560.96</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227541679.45</v>
+        <v>227541944.84</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642027.12</v>
+        <v>2642027.05</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513123.76</v>
+        <v>5513123.6</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286539378.79</v>
+        <v>286539643.94</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042731531.26</v>
+        <v>1042731574.43</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244215721.33</v>
+        <v>1244215764.5</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230883812.81</v>
+        <v>230883827.86</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865669.83</v>
+        <v>2865669.87</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026082.47</v>
+        <v>7026082.58</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305688636.55</v>
+        <v>305688651.75</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046532073.87</v>
+        <v>1046532171.23</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268579173.68</v>
+        <v>1268579271.04</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238383498.58</v>
+        <v>238383508.77</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737712.63</v>
+        <v>3737712.45</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838302.46</v>
+        <v>7838302.09</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315850250.46</v>
+        <v>315850260.12</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026526859.68</v>
+        <v>1026530017.5</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228670738.71</v>
+        <v>1228673896.53</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246156826.31</v>
+        <v>246156952.49</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558675.37</v>
+        <v>3558667.37</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537379.52</v>
+        <v>7537362.57</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315576935.37</v>
+        <v>315577036.59</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275234589.56</v>
+        <v>1275235495.08</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517956066.81</v>
+        <v>1517956972.33</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295676886.15</v>
+        <v>295676918.94</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271139.62</v>
+        <v>4271137.36</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581198.939999999</v>
+        <v>9581193.869999999</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378773220.59</v>
+        <v>378773246.05</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123211110.07</v>
+        <v>1123211345.81</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375386271.4</v>
+        <v>1375386507.14</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251892009.06</v>
+        <v>251892038.03</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520549.96</v>
+        <v>3520549.64</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255916.63</v>
+        <v>11255915.61</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341111432.49</v>
+        <v>341111460.12</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780514888.38</v>
+        <v>780515085.95</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941931733.91</v>
+        <v>941931931.48</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182890884.11</v>
+        <v>182890906.91</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893249.52</v>
+        <v>2893249.18</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978990.82</v>
+        <v>4978990.23</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240374967.38</v>
+        <v>240374989.24</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925223588.2</v>
+        <v>925223652.85</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103226972.02</v>
+        <v>1103227036.67</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208939609.52</v>
+        <v>208939633.67</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099145.34</v>
+        <v>3099145.44</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218664.03</v>
+        <v>6218664.23</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270757928.9</v>
+        <v>270757953.35</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099263923.03</v>
+        <v>1099263977.69</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314564216.85</v>
+        <v>1314564271.51</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244622737.95</v>
+        <v>244622740.43</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671186.92</v>
+        <v>3671186.79</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710546.26</v>
+        <v>7710545.99</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319476891.83</v>
+        <v>319476893.91</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967592842.47</v>
+        <v>967593940</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190913848.05</v>
+        <v>1190914945.58</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210534058.08</v>
+        <v>210534126.58</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281810.42</v>
+        <v>3281808.1</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536324.3</v>
+        <v>7536318.97</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283817073.47</v>
+        <v>283817134.32</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003078500.6</v>
+        <v>1003078883.07</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198235188.66</v>
+        <v>1198235571.13</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222088395.52</v>
+        <v>222088470.41</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891041.14</v>
+        <v>3891040.93</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335940.03</v>
+        <v>6335939.68</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281019871.62</v>
+        <v>281019945.95</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362287134.62</v>
+        <v>1362287489.01</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634503889.74</v>
+        <v>1634504244.13</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306762685.55</v>
+        <v>306762881.17</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136467.53</v>
+        <v>6136469.37</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270557.63</v>
+        <v>10270560.71</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388021842.21</v>
+        <v>388022042.75</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156894339.57</v>
+        <v>1156894498.58</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409394307.22</v>
+        <v>1409394466.23</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247797809.91</v>
+        <v>247797842.27</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795237.41</v>
+        <v>3795237.36</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929395.84</v>
+        <v>9929395.689999999</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325995667.94</v>
+        <v>325995700.1</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870296411.08</v>
+        <v>870298016.14</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039400623.45</v>
+        <v>1039402228.51</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193432449.79</v>
+        <v>193432538.86</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256066.97</v>
+        <v>3256062.98</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684212.12</v>
+        <v>5684205.15</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245274540.51</v>
+        <v>245274618.62</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002262868.89</v>
+        <v>1002264081.76</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209600276.85</v>
+        <v>1209601489.72</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>217000311.73</v>
+        <v>217000346.89</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934144.84</v>
+        <v>2934142.17</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937714.21</v>
+        <v>6937707.9</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280972575.85</v>
+        <v>280972602.03</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105961332.18</v>
+        <v>1105961756.18</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351816231.83</v>
+        <v>1351816655.83</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242483011.96</v>
+        <v>242483149.7</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693255.15</v>
+        <v>2693255.46</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764063.6</v>
+        <v>8764064.619999999</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322796809.7</v>
+        <v>322796948.78</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932840040</v>
+        <v>932840625.66</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136787854.45</v>
+        <v>1136788440.11</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196523677.75</v>
+        <v>196523804.36</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927929.7</v>
+        <v>2927929.62</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577851.69</v>
+        <v>6577851.51</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259477800.51</v>
+        <v>259477926.85</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1162026561.98</v>
+        <v>1162027186.88</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354863046.05</v>
+        <v>1354863670.95</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252351659.12</v>
+        <v>252351823.36</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229199.12</v>
+        <v>4229199.4</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541685.75</v>
+        <v>4541686.05</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311964262.61</v>
+        <v>311964427.44</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1439999350.39</v>
+        <v>1440000240.37</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740056016.42</v>
+        <v>1740056906.4</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284717574.18</v>
+        <v>284717808.25</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067083.22</v>
+        <v>4067083.69</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978505.37</v>
+        <v>5978506.06</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375588351.63</v>
+        <v>375588586.85</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319726537.97</v>
+        <v>1319729229.95</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579489622.09</v>
+        <v>1579492314.07</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283377339.55</v>
+        <v>283377951.3</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050969.74</v>
+        <v>3050969.67</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438416.2</v>
+        <v>7438416.03</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363618090.01</v>
+        <v>363618701.52</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096995658.4</v>
+        <v>1096998712.37</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283036684.51</v>
+        <v>1283039738.48</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243425732.96</v>
+        <v>243426086.53</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660622.22</v>
+        <v>1660620.15</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202030.95</v>
+        <v>7202021.98</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302143277.66</v>
+        <v>302143620.18</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142119113.11</v>
+        <v>1142122526.37</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1366010227.06</v>
+        <v>1366013640.32</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239658853.09</v>
+        <v>239659764.63</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298510.56</v>
+        <v>1298511.19</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234279.449999999</v>
+        <v>9234283.91</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307452017.84</v>
+        <v>307452934.47</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192845018.21</v>
+        <v>1192850135.45</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436502024.88</v>
+        <v>1436507142.12</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253630471.11</v>
+        <v>253631002.51</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145317.8</v>
+        <v>2145313.51</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745141.63</v>
+        <v>6745128.16</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327985332.74</v>
+        <v>327985846.39</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226935706.02</v>
+        <v>1226937347.06</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494275996.89</v>
+        <v>1494277637.93</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272957573.07</v>
+        <v>272957836.41</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511837.81</v>
+        <v>2511836.85</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248295.33</v>
+        <v>7248292.58</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361199790.88</v>
+        <v>361200050.52</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348613742.4</v>
+        <v>1348618475.53</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622933887.15</v>
+        <v>1622938620.28</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278434307.01</v>
+        <v>278435356.26</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307527.59</v>
+        <v>2307527.55</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088498.88</v>
+        <v>8088498.74</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361821240.27</v>
+        <v>361822289.34</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778307676.58</v>
+        <v>1778313505.08</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122370738.64</v>
+        <v>2122376567.14</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364511086.6</v>
+        <v>364512615.1</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3919081.56</v>
+        <v>3919083.71</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6647141.94</v>
+        <v>6647145.59</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465530077.86</v>
+        <v>465531612.17</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364400925.22</v>
+        <v>1364405852.45</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1651170711.82</v>
+        <v>1651175639.05</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283715770.86</v>
+        <v>283717815.02</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4917189.55</v>
+        <v>4917202.12</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7352586.88</v>
+        <v>7352605.68</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374613336.97</v>
+        <v>374615412.5</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1038048037.61</v>
+        <v>1038056441.43</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347424754.4</v>
+        <v>1347433158.22</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218478295.06</v>
+        <v>218481265.75</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3629058.75</v>
+        <v>3629070.45</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4592042.43</v>
+        <v>4592057.23</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316827969.72</v>
+        <v>316830966.91</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143658202.59</v>
+        <v>1143673254.92</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1422140622.2</v>
+        <v>1422155674.53</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228247839.13</v>
+        <v>228251900.4</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3388606.45</v>
+        <v>3388614.64</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5521845.41</v>
+        <v>5521858.76</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>314031476.18</v>
+        <v>314035558.98</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339477795.27</v>
+        <v>1339496529.78</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1715051700.87</v>
+        <v>1715070435.38</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269952368.76</v>
+        <v>269958993.59</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2886676.56</v>
+        <v>2886694.56</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7560560.67</v>
+        <v>7560607.83</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389845075.34</v>
+        <v>389851765.33</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1172343535.55</v>
+        <v>1172362976.46</v>
       </c>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6" t="n">
@@ -2945,10 +2945,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1340271400.04</v>
+        <v>1340290840.95</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>220123050.96</v>
+        <v>220131318.08</v>
       </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n">
@@ -2958,16 +2958,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2498573.69</v>
+        <v>2498615.29</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>6814304.42</v>
+        <v>6814417.88</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>270327581.05</v>
+        <v>270336003.23</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.4394700544002308</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1224961315.84</v>
+        <v>1224983696.83</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>118878392.5</v>
@@ -3001,10 +3001,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1503721531.11</v>
+        <v>1503743912.1</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236954921.87</v>
+        <v>236964222.21</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>32561198.02</v>
@@ -3016,16 +3016,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5196649.36</v>
+        <v>5196725.71</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6920540.01</v>
+        <v>6920641.68</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>320487964.77</v>
+        <v>320497443.12</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3923339612110134</v>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1838867508.19</v>
+        <v>1838912707.42</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>151695056.58</v>
@@ -3059,10 +3059,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2308872223.67</v>
+        <v>2308917422.9</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>385234510.67</v>
+        <v>385250966.35</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>38969011.58</v>
@@ -3074,16 +3074,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>10556743.29</v>
+        <v>10556877.64</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>18018137.95</v>
+        <v>18018367.25</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>520677102.34</v>
+        <v>520693921.67</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0.4083810879699633</v>
@@ -3096,9 +3096,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1903239188.97</v>
-      </c>
-      <c r="C46" s="6" t="n"/>
+        <v>1904220072.73</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>198191544.89</v>
+      </c>
       <c r="D46" s="6" t="n">
         <v>69142299.48</v>
       </c>
@@ -3115,12 +3117,14 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2327651494.66</v>
+        <v>2526823923.31</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>382714232.41</v>
-      </c>
-      <c r="K46" s="9" t="n"/>
+        <v>382893521.84</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>54130695.48</v>
+      </c>
       <c r="L46" s="9" t="n">
         <v>23371135.67</v>
       </c>
@@ -3128,23 +3132,77 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>11580664.69</v>
+        <v>11838220.1</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>21322064.37</v>
+        <v>21796269.71</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>501696953.56</v>
+        <v>556738699.21</v>
       </c>
       <c r="R46" s="10" t="n">
-        <v>0.5318716921548481</v>
+        <v>0.4547581192007113</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>1020882646.75</v>
+      </c>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n">
+        <v>35781373.52</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>50533838</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>17873782.49</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>25282892</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>52052630</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>1202407162.76</v>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>208838914.36</v>
+      </c>
+      <c r="K47" s="9" t="n"/>
+      <c r="L47" s="9" t="n">
+        <v>11249014.9</v>
+      </c>
+      <c r="M47" s="9" t="n">
+        <v>10674494.15</v>
+      </c>
+      <c r="N47" s="9" t="n">
+        <v>3931642.22</v>
+      </c>
+      <c r="O47" s="9" t="n">
+        <v>5561401.77</v>
+      </c>
+      <c r="P47" s="9" t="n">
+        <v>24234422.43</v>
+      </c>
+      <c r="Q47" s="9" t="n">
+        <v>264489889.82</v>
+      </c>
+      <c r="R47" s="10" t="n">
+        <v>0.5456835192724245</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R46"/>
+  <autoFilter ref="A2:R47"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3160,7 +3218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5637,9 +5695,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>2548893109.12</v>
-      </c>
-      <c r="C46" s="6" t="n"/>
+        <v>2550171048.32</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>198965031.13</v>
+      </c>
       <c r="D46" s="6" t="n">
         <v>69142299.48</v>
       </c>
@@ -5656,12 +5716,14 @@
         <v>66113614</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2977348773.81</v>
+        <v>3177591744.14</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>707572727.09</v>
-      </c>
-      <c r="K46" s="9" t="n"/>
+        <v>707927483.01</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>54231280.55</v>
+      </c>
       <c r="L46" s="9" t="n">
         <v>23371135.67</v>
       </c>
@@ -5669,20 +5731,71 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>15119224.88</v>
+        <v>15087902.72</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>28650184.44</v>
+        <v>28590830.49</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>33092919.58</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>837817174.35</v>
+        <v>892312534.71</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>1367187231.54</v>
+      </c>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n">
+        <v>35781373.52</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>50533838</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>17873782.49</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>29649287</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>55958167</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>1556983679.55</v>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>379531175.47</v>
+      </c>
+      <c r="K47" s="9" t="n"/>
+      <c r="L47" s="9" t="n">
+        <v>11249014.9</v>
+      </c>
+      <c r="M47" s="9" t="n">
+        <v>10674494.15</v>
+      </c>
+      <c r="N47" s="9" t="n">
+        <v>5055801.51</v>
+      </c>
+      <c r="O47" s="9" t="n">
+        <v>8386636.13</v>
+      </c>
+      <c r="P47" s="9" t="n">
+        <v>25513319.43</v>
+      </c>
+      <c r="Q47" s="9" t="n">
+        <v>440410441.59</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q46"/>
+  <autoFilter ref="A2:Q47"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -5697,7 +5810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7525,7 +7638,7 @@
         <v>13411796</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>0.6737000000000001</v>
+        <v>0.6736</v>
       </c>
       <c r="I43" s="11" t="n">
         <v>0.3466</v>
@@ -7609,7 +7722,7 @@
         <v>21875177</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>0.6207</v>
+        <v>0.6206</v>
       </c>
       <c r="I45" s="11" t="n">
         <v>0.3898</v>
@@ -7634,7 +7747,7 @@
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>1227444965.63</v>
+        <v>1228060370.03</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>30527478.39</v>
@@ -7642,7 +7755,9 @@
       <c r="D46" s="6" t="n">
         <v>87962042</v>
       </c>
-      <c r="E46" s="6" t="n"/>
+      <c r="E46" s="6" t="n">
+        <v>62409461.1</v>
+      </c>
       <c r="F46" s="6" t="n">
         <v>48256943.28</v>
       </c>
@@ -7658,7 +7773,9 @@
       <c r="J46" s="11" t="n">
         <v>0.639</v>
       </c>
-      <c r="K46" s="11" t="n"/>
+      <c r="K46" s="11" t="n">
+        <v>0.3149</v>
+      </c>
       <c r="L46" s="11" t="n">
         <v>0.8981999999999999</v>
       </c>
@@ -7666,15 +7783,54 @@
         <v>0.247</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>658382683.22</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>14529335.06</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>31583199</v>
+      </c>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n">
+        <v>13310527.94</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>11226252</v>
+      </c>
+      <c r="H47" s="11" t="n">
+        <v>0.6448999999999999</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="J47" s="11" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K47" s="11" t="n"/>
+      <c r="L47" s="11" t="n">
+        <v>0.7447</v>
+      </c>
+      <c r="M47" s="11" t="n">
+        <v>0.444</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M46"/>
+  <autoFilter ref="A2:M47"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -7705,7 +7861,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-14. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-15. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143673254.92</v>
+        <v>1143673284.92</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1422155674.53</v>
+        <v>1422155704.53</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228251900.4</v>
+        <v>228251901.32</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3388614.64</v>
+        <v>3388614.58</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5521858.76</v>
+        <v>5521858.66</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>314035558.98</v>
+        <v>314035559.74</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1224983696.83</v>
+        <v>1224983701.84</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>118878392.5</v>
@@ -3001,10 +3001,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1503743912.1</v>
+        <v>1503743917.11</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236964222.21</v>
+        <v>236964225.12</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>32561198.02</v>
@@ -3016,16 +3016,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5196725.71</v>
+        <v>5196725.74</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6920641.68</v>
+        <v>6920641.72</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>320497443.12</v>
+        <v>320497446.1</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3923339612110134</v>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1838912707.42</v>
+        <v>1838912773.58</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>151695056.58</v>
@@ -3059,10 +3059,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2308917422.9</v>
+        <v>2308917489.06</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>385250966.35</v>
+        <v>385250996.19</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>38969011.58</v>
@@ -3074,16 +3074,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>10556877.64</v>
+        <v>10556877.96</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>18018367.25</v>
+        <v>18018367.8</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>520693921.67</v>
+        <v>520693952.38</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0.4083810879699633</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1904220072.73</v>
+        <v>1904221320.49</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>198191544.89</v>
@@ -3117,10 +3117,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2526823923.31</v>
+        <v>2526825171.07</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>382893521.84</v>
+        <v>382893720.29</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>54130695.48</v>
@@ -3132,16 +3132,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>11838220.1</v>
+        <v>11838218.37</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>21796269.71</v>
+        <v>21796266.52</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>556738699.21</v>
+        <v>556738892.74</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0.4547581192007113</v>
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1020882646.75</v>
+        <v>1020916033.98</v>
       </c>
       <c r="C47" s="6" t="n"/>
       <c r="D47" s="6" t="n">
@@ -3173,10 +3173,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1202407162.76</v>
+        <v>1202440549.99</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>208838914.36</v>
+        <v>208845658.69</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n">
@@ -3186,16 +3186,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>3931642.22</v>
+        <v>3931632.97</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>5561401.77</v>
+        <v>5561388.69</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>264489889.82</v>
+        <v>264496611.83</v>
       </c>
       <c r="R47" s="10" t="n">
         <v>0.5456835192724245</v>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>2550171048.32</v>
+        <v>2550172694.9</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>198965031.13</v>
@@ -5716,10 +5716,10 @@
         <v>66113614</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>3177591744.14</v>
+        <v>3177593390.72</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>707927483.01</v>
+        <v>707927940.11</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>54231280.55</v>
@@ -5731,16 +5731,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>15087902.72</v>
+        <v>15087902.62</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>28590830.49</v>
+        <v>28590830.31</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>33092919.58</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>892312534.71</v>
+        <v>892312991.54</v>
       </c>
     </row>
     <row r="47">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1367187231.54</v>
+        <v>1367231931.31</v>
       </c>
       <c r="C47" s="6" t="n"/>
       <c r="D47" s="6" t="n">
@@ -5769,10 +5769,10 @@
         <v>55958167</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1556983679.55</v>
+        <v>1557028379.32</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>379531175.47</v>
+        <v>379543584.13</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n">
@@ -5782,16 +5782,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>5055801.51</v>
+        <v>5055798.73</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>8386636.13</v>
+        <v>8386631.51</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>25513319.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>440410441.59</v>
+        <v>440422842.85</v>
       </c>
     </row>
   </sheetData>
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>1228060370.03</v>
+        <v>1228061162.96</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>30527478.39</v>
@@ -7790,7 +7790,7 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>658382683.22</v>
+        <v>658404208.84</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>14529335.06</v>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766409057.53</v>
+        <v>766409116.45</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882451604.5700001</v>
+        <v>882451663.49</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197402434.93</v>
+        <v>197402474.74</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374709.13</v>
+        <v>374709.17</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399340.97</v>
+        <v>5399341.52</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239491767.41</v>
+        <v>239491807.81</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983763420.67</v>
+        <v>983763590.1799999</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168401569.69</v>
+        <v>1168401739.2</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236064611.36</v>
+        <v>236064760.12</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324588.64</v>
+        <v>324588.75</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358545.12</v>
+        <v>7358547.7</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305861329.69</v>
+        <v>305861481.14</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097588833.62</v>
+        <v>1097588846.56</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302668871.2</v>
+        <v>1302668884.14</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250951071.26</v>
+        <v>250951079.42</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.46</v>
+        <v>709927.47</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693356.66</v>
+        <v>7693356.78</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328055086.64</v>
+        <v>328055094.93</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275235495.08</v>
+        <v>1275235645.83</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517956972.33</v>
+        <v>1517957123.08</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295676918.94</v>
+        <v>295677018.54</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271137.36</v>
+        <v>4271138.08</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581193.869999999</v>
+        <v>9581195.5</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378773246.05</v>
+        <v>378773348</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099263977.69</v>
+        <v>1099263978.43</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314564271.51</v>
+        <v>1314564272.25</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244622740.43</v>
+        <v>244622740.94</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1689,13 +1689,13 @@
         <v>3671186.79</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710545.99</v>
+        <v>7710546</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319476893.91</v>
+        <v>319476894.43</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156894498.58</v>
+        <v>1156894570.44</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409394466.23</v>
+        <v>1409394538.09</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247797842.27</v>
+        <v>247797903.47</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795237.36</v>
+        <v>3795237.9</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929395.689999999</v>
+        <v>9929397.109999999</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325995700.1</v>
+        <v>325995763.26</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870298016.14</v>
+        <v>870298139.63</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039402228.51</v>
+        <v>1039402352</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193432538.86</v>
+        <v>193432635.88</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256062.98</v>
+        <v>3256063.91</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684205.15</v>
+        <v>5684206.79</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245274618.62</v>
+        <v>245274718.21</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105961756.18</v>
+        <v>1105962582.62</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351816655.83</v>
+        <v>1351817482.27</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242483149.7</v>
+        <v>242483734.07</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693255.46</v>
+        <v>2693258.81</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764064.619999999</v>
+        <v>8764075.52</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322796948.78</v>
+        <v>322797547.4</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932840625.66</v>
+        <v>932841107.64</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136788440.11</v>
+        <v>1136788922.09</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196523804.36</v>
+        <v>196524158.28</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927929.62</v>
+        <v>2927932.48</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577851.51</v>
+        <v>6577857.93</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259477926.85</v>
+        <v>259478290.04</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1162027186.88</v>
+        <v>1162027349.7</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354863670.95</v>
+        <v>1354863833.77</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252351823.36</v>
+        <v>252351940.41</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229199.4</v>
+        <v>4229200.51</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541686.05</v>
+        <v>4541687.24</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311964427.44</v>
+        <v>311964546.79</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1440000240.37</v>
+        <v>1440000377.38</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740056906.4</v>
+        <v>1740057043.41</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284717808.25</v>
+        <v>284717908.43</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067083.69</v>
+        <v>4067084.47</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978506.06</v>
+        <v>5978507.21</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375588586.85</v>
+        <v>375588688.97</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319729229.95</v>
+        <v>1319729279.45</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579492314.07</v>
+        <v>1579492363.57</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283377951.3</v>
+        <v>283377991.44</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050969.67</v>
+        <v>3050969.92</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438416.03</v>
+        <v>7438416.64</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363618701.52</v>
+        <v>363618742.52</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096998712.37</v>
+        <v>1096998732.97</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283039738.48</v>
+        <v>1283039759.08</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243426086.53</v>
+        <v>243426102.32</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660620.15</v>
+        <v>1660620.21</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202021.98</v>
+        <v>7202022.24</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302143620.18</v>
+        <v>302143636.3</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142122526.37</v>
+        <v>1142122707.98</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1366013640.32</v>
+        <v>1366013821.93</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239659764.63</v>
+        <v>239659902.51</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298511.19</v>
+        <v>1298511.61</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234283.91</v>
+        <v>9234286.93</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307452934.47</v>
+        <v>307453075.79</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226937347.06</v>
+        <v>1226937432.61</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494277637.93</v>
+        <v>1494277723.48</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272957836.41</v>
+        <v>272957902.05</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511836.85</v>
+        <v>2511837.18</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248292.58</v>
+        <v>7248293.5</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361200050.52</v>
+        <v>361200117.41</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778313505.08</v>
+        <v>1778313555.08</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122376567.14</v>
+        <v>2122376617.14</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364512615.1</v>
+        <v>364512629.1</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3919083.71</v>
+        <v>3919083.74</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6647145.59</v>
+        <v>6647145.63</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465531612.17</v>
+        <v>465531626.24</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364405852.45</v>
+        <v>1364405909.15</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1651175639.05</v>
+        <v>1651175695.75</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283717815.02</v>
+        <v>283717852.8</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4917202.12</v>
+        <v>4917202.46</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7352605.68</v>
+        <v>7352606.19</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374615412.5</v>
+        <v>374615451.12</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1038056441.43</v>
+        <v>1038057559.71</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347433158.22</v>
+        <v>1347434276.5</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218481265.75</v>
+        <v>218481819.85</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3629070.45</v>
+        <v>3629073.87</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4592057.23</v>
+        <v>4592061.56</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316830966.91</v>
+        <v>316831528.76</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143673284.92</v>
+        <v>1143675728.75</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1422155704.53</v>
+        <v>1422158148.36</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228251901.32</v>
+        <v>228253868.4</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3388614.58</v>
+        <v>3388630.43</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5521858.66</v>
+        <v>5521884.49</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>314035559.74</v>
+        <v>314037568.5</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339496529.78</v>
+        <v>1339499072.68</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1715070435.38</v>
+        <v>1715072978.28</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269958993.59</v>
+        <v>269960507.77</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2886694.56</v>
+        <v>2886701.69</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7560607.83</v>
+        <v>7560626.49</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389851765.33</v>
+        <v>389853305.29</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1172362976.46</v>
+        <v>1172363175.6</v>
       </c>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6" t="n">
@@ -2945,10 +2945,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1340290840.95</v>
+        <v>1340291040.09</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>220131318.08</v>
+        <v>220131443.27</v>
       </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n">
@@ -2958,16 +2958,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2498615.29</v>
+        <v>2498616.1</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>6814417.88</v>
+        <v>6814420.1</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>270336003.23</v>
+        <v>270336131.45</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.4394700544002308</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1224983701.84</v>
+        <v>1224983847.76</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>118878392.5</v>
@@ -3001,10 +3001,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1503743917.11</v>
+        <v>1503744063.03</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236964225.12</v>
+        <v>236964303.7</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>32561198.02</v>
@@ -3016,16 +3016,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5196725.74</v>
+        <v>5196726.54</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6920641.72</v>
+        <v>6920642.79</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>320497446.1</v>
+        <v>320497526.55</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3923339612110134</v>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1838912773.58</v>
+        <v>1838914765.05</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>151695056.58</v>
@@ -3059,10 +3059,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2308917489.06</v>
+        <v>2308919480.53</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>385250996.19</v>
+        <v>385252000.7</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>38969011.58</v>
@@ -3074,16 +3074,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>10556877.96</v>
+        <v>10556889.87</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>18018367.8</v>
+        <v>18018388.14</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>520693952.38</v>
+        <v>520694989.14</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0.4083810879699633</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1904221320.49</v>
+        <v>1904253231.77</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>198191544.89</v>
@@ -3117,10 +3117,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2526825171.07</v>
+        <v>2526857082.35</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>382893720.29</v>
+        <v>382900397.2</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>54130695.48</v>
@@ -3132,16 +3132,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>11838218.37</v>
+        <v>11838210.35</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>21796266.52</v>
+        <v>21796251.76</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>556738892.74</v>
+        <v>556745546.88</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0.4547581192007113</v>
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1020916033.98</v>
+        <v>1021193682.46</v>
       </c>
       <c r="C47" s="6" t="n"/>
       <c r="D47" s="6" t="n">
@@ -3173,10 +3173,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1202440549.99</v>
+        <v>1202718198.47</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>208845658.69</v>
+        <v>208890525.58</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n">
@@ -3186,16 +3186,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>3931632.97</v>
+        <v>3931383.16</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>5561388.69</v>
+        <v>5561035.32</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>264496611.83</v>
+        <v>264540875.54</v>
       </c>
       <c r="R47" s="10" t="n">
         <v>0.5456835192724245</v>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>2550172694.9</v>
+        <v>2550213045.8</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>198965031.13</v>
@@ -5716,10 +5716,10 @@
         <v>66113614</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>3177593390.72</v>
+        <v>3177633741.62</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>707927940.11</v>
+        <v>707939141.51</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>54231280.55</v>
@@ -5731,16 +5731,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>15087902.62</v>
+        <v>15087900.32</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>28590830.31</v>
+        <v>28590825.95</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>33092919.58</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>892312991.54</v>
+        <v>892324186.26</v>
       </c>
     </row>
     <row r="47">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1367231931.31</v>
+        <v>1367602484.72</v>
       </c>
       <c r="C47" s="6" t="n"/>
       <c r="D47" s="6" t="n">
@@ -5769,10 +5769,10 @@
         <v>55958167</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1557028379.32</v>
+        <v>1557398932.73</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>379543584.13</v>
+        <v>379646449.76</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n">
@@ -5782,16 +5782,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>5055798.73</v>
+        <v>5055775.65</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>8386631.51</v>
+        <v>8386593.23</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>25513319.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>440422842.85</v>
+        <v>440525647.12</v>
       </c>
     </row>
   </sheetData>
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>1228061162.96</v>
+        <v>1228080594.34</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>30527478.39</v>
@@ -7790,7 +7790,7 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>658404208.84</v>
+        <v>658582652.54</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>14529335.06</v>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226360709.94</v>
+        <v>1226361144.05</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404322804.52</v>
+        <v>1404323238.63</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290715403.68</v>
+        <v>290715478.15</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524812.25</v>
+        <v>524812.1899999999</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360274.630000001</v>
+        <v>9360273.67</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354058397.18</v>
+        <v>354058470.65</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019798856.73</v>
+        <v>1019800096.1</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203203766.24</v>
+        <v>1203205005.61</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223747343.14</v>
+        <v>223747425.83</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516298.04</v>
+        <v>516297.64</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237374.720000001</v>
+        <v>9237367.609999999</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289059121.68</v>
+        <v>289059196.86</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766409116.45</v>
+        <v>766409486.72</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882451663.49</v>
+        <v>882452033.76</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197402474.74</v>
+        <v>197402526.39</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374709.17</v>
+        <v>374709.09</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399341.52</v>
+        <v>5399340.39</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239491807.81</v>
+        <v>239491858.25</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983763590.1799999</v>
+        <v>983763686.27</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168401739.2</v>
+        <v>1168401835.29</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236064760.12</v>
+        <v>236064824.73</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324588.75</v>
+        <v>324588.79</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358547.7</v>
+        <v>7358548.67</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305861481.14</v>
+        <v>305861546.77</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097588846.56</v>
+        <v>1097589214.24</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302668884.14</v>
+        <v>1302669251.82</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250951079.42</v>
+        <v>250951260.78</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.47</v>
+        <v>709927.67</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693356.78</v>
+        <v>7693358.91</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328055094.93</v>
+        <v>328055278.62</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011525363.26</v>
+        <v>1011526262.43</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233698482.77</v>
+        <v>1233699381.94</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229526107.1</v>
+        <v>229526167.41</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255744.91</v>
+        <v>1255744.22</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409739.24</v>
+        <v>8409734.609999999</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309201047.91</v>
+        <v>309201102.9</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961943767.05</v>
+        <v>961944869.98</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145550928.59</v>
+        <v>1145552031.52</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214890661.29</v>
+        <v>214890748.42</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814777.78</v>
+        <v>814777.23</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850538.09</v>
+        <v>6850533.49</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281207822.35</v>
+        <v>281207904.34</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073048834.28</v>
+        <v>1073050679.76</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277714731.76</v>
+        <v>1277716577.24</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240126173.35</v>
+        <v>240126421.12</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353403.62</v>
+        <v>2353402.03</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569926.76</v>
+        <v>7569921.64</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313749981.61</v>
+        <v>313750222.67</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960777160.66</v>
+        <v>960777616.5700001</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185450477.78</v>
+        <v>1185450933.69</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212552325.31</v>
+        <v>212552579.64</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490171.14</v>
+        <v>2490172.37</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929353.48</v>
+        <v>8929357.880000001</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296187190.63</v>
+        <v>296187450.59</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686511834.17</v>
+        <v>686512372.66</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813423525.2</v>
+        <v>813424063.6900001</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150992992.33</v>
+        <v>150993223.5</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897065.52</v>
+        <v>1897066.53</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485529.01</v>
+        <v>3485530.86</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196257546.76</v>
+        <v>196257780.79</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970911906.72</v>
+        <v>970915246.6900001</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130468560.96</v>
+        <v>1130471900.93</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227541944.84</v>
+        <v>227542411.3</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642027.05</v>
+        <v>2642023.44</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513123.6</v>
+        <v>5513116.07</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286539643.94</v>
+        <v>286540099.26</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042731574.43</v>
+        <v>1042731595.8</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244215764.5</v>
+        <v>1244215785.87</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230883827.86</v>
+        <v>230883839.62</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865669.87</v>
+        <v>2865669.94</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026082.58</v>
+        <v>7026082.73</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305688651.75</v>
+        <v>305688663.73</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046532171.23</v>
+        <v>1046532400.86</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268579271.04</v>
+        <v>1268579500.67</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238383508.77</v>
+        <v>238383632.52</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737712.45</v>
+        <v>3737713.27</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838302.09</v>
+        <v>7838303.81</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315850260.12</v>
+        <v>315850386.4</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026530017.5</v>
+        <v>1026530232.06</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228673896.53</v>
+        <v>1228674111.09</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246156952.49</v>
+        <v>246157012.96</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558667.37</v>
+        <v>3558667.43</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537362.57</v>
+        <v>7537362.7</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315577036.59</v>
+        <v>315577097.25</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275235645.83</v>
+        <v>1275235677.99</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517957123.08</v>
+        <v>1517957155.24</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295677018.54</v>
+        <v>295677038.34</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271138.08</v>
+        <v>4271138.22</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581195.5</v>
+        <v>9581195.810000001</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378773348</v>
+        <v>378773368.25</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123211345.81</v>
+        <v>1123212251.73</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375386507.14</v>
+        <v>1375387413.06</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251892038.03</v>
+        <v>251892590.66</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520549.64</v>
+        <v>3520553.18</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255915.61</v>
+        <v>11255926.93</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341111460.12</v>
+        <v>341112027.6</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780515085.95</v>
+        <v>780515303.54</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941931931.48</v>
+        <v>941932149.0700001</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182890906.91</v>
+        <v>182890957.99</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893249.18</v>
+        <v>2893249.12</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978990.23</v>
+        <v>4978990.13</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240374989.24</v>
+        <v>240375040.17</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925223652.85</v>
+        <v>925224370.9299999</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103227036.67</v>
+        <v>1103227754.75</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208939633.67</v>
+        <v>208939781.33</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099145.44</v>
+        <v>3099145.1</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218664.23</v>
+        <v>6218663.55</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270757953.35</v>
+        <v>270758099.99</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099263978.43</v>
+        <v>1099264241.31</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314564272.25</v>
+        <v>1314564535.13</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244622740.94</v>
+        <v>244622801.06</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671186.79</v>
+        <v>3671186.75</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710546</v>
+        <v>7710545.9</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319476894.43</v>
+        <v>319476954.41</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967593940</v>
+        <v>967596880.24</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190914945.58</v>
+        <v>1190917885.82</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210534126.58</v>
+        <v>210534603.71</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281808.1</v>
+        <v>3281805.41</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536318.97</v>
+        <v>7536312.8</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283817134.32</v>
+        <v>283817602.59</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003078883.07</v>
+        <v>1003080732.14</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198235571.13</v>
+        <v>1198237420.2</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222088470.41</v>
+        <v>222088829.04</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891040.93</v>
+        <v>3891039.85</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335939.68</v>
+        <v>6335937.93</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281019945.95</v>
+        <v>281020301.75</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362287489.01</v>
+        <v>1362287608.99</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634504244.13</v>
+        <v>1634504364.11</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306762881.17</v>
+        <v>306762960.85</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136469.37</v>
+        <v>6136470.22</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270560.71</v>
+        <v>10270562.13</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388022042.75</v>
+        <v>388022124.69</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156894570.44</v>
+        <v>1156894814.23</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409394538.09</v>
+        <v>1409394781.88</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247797903.47</v>
+        <v>247797984.74</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795237.9</v>
+        <v>3795238.2</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929397.109999999</v>
+        <v>9929397.9</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325995763.26</v>
+        <v>325995845.63</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870298139.63</v>
+        <v>870299933.05</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039402352</v>
+        <v>1039404145.42</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193432635.88</v>
+        <v>193432998.9</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256063.91</v>
+        <v>3256063.08</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684206.79</v>
+        <v>5684205.34</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245274718.21</v>
+        <v>245275078.95</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002264081.76</v>
+        <v>1002264719.12</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209601489.72</v>
+        <v>1209602127.08</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>217000346.89</v>
+        <v>217000443.53</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934142.17</v>
+        <v>2934141.61</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937707.9</v>
+        <v>6937706.58</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280972602.03</v>
+        <v>280972696.8</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105962582.62</v>
+        <v>1105963996.73</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351817482.27</v>
+        <v>1351818896.38</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242483734.07</v>
+        <v>242483922.27</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693258.81</v>
+        <v>2693257.52</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764075.52</v>
+        <v>8764071.310000001</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322797547.4</v>
+        <v>322797730.1</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932841107.64</v>
+        <v>932844096.4</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136788922.09</v>
+        <v>1136791910.85</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196524158.28</v>
+        <v>196524670.96</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927932.48</v>
+        <v>2927930.49</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577857.93</v>
+        <v>6577853.47</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259478290.04</v>
+        <v>259478796.28</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1162027349.7</v>
+        <v>1162029739.64</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354863833.77</v>
+        <v>1354866223.71</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252351940.41</v>
+        <v>252352097.41</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229200.51</v>
+        <v>4229195.02</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541687.24</v>
+        <v>4541681.35</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311964546.79</v>
+        <v>311964692.41</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1440000377.38</v>
+        <v>1440005057.95</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740057043.41</v>
+        <v>1740061723.98</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284717908.43</v>
+        <v>284718820.17</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067084.47</v>
+        <v>4067083.37</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978507.21</v>
+        <v>5978505.6</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375588688.97</v>
+        <v>375589598</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319729279.45</v>
+        <v>1319732411.58</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579492363.57</v>
+        <v>1579495495.7</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283377991.44</v>
+        <v>283378202.78</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050969.92</v>
+        <v>3050965.51</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438416.64</v>
+        <v>7438405.9</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363618742.52</v>
+        <v>363618938.72</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1096998732.97</v>
+        <v>1097001440.62</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283039759.08</v>
+        <v>1283042466.73</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243426102.32</v>
+        <v>243427083.95</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660620.21</v>
+        <v>1660622.16</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202022.24</v>
+        <v>7202030.69</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302143636.3</v>
+        <v>302144628.33</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142122707.98</v>
+        <v>1142128807.21</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1366013821.93</v>
+        <v>1366019921.16</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239659902.51</v>
+        <v>239660821.59</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298511.61</v>
+        <v>1298509.63</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234286.93</v>
+        <v>9234272.82</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307453075.79</v>
+        <v>307453978.78</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192850135.45</v>
+        <v>1192852962.78</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436507142.12</v>
+        <v>1436509969.45</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253631002.51</v>
+        <v>253631910.11</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145313.51</v>
+        <v>2145315.28</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745128.16</v>
+        <v>6745133.7</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327985846.39</v>
+        <v>327986761.29</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226937432.61</v>
+        <v>1226940252.72</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494277723.48</v>
+        <v>1494280543.59</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272957902.05</v>
+        <v>272958698.97</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511837.18</v>
+        <v>2511838</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248293.5</v>
+        <v>7248295.88</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361200117.41</v>
+        <v>361200917.53</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348618475.53</v>
+        <v>1348620711.18</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622938620.28</v>
+        <v>1622940855.93</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278435356.26</v>
+        <v>278436127.15</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307527.55</v>
+        <v>2307529.34</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088498.74</v>
+        <v>8088505.01</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361822289.34</v>
+        <v>361823068.29</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778313555.08</v>
+        <v>1778317503.22</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122376617.14</v>
+        <v>2122380565.28</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364512629.1</v>
+        <v>364513638.36</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3919083.74</v>
+        <v>3919084.97</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6647145.63</v>
+        <v>6647147.73</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465531626.24</v>
+        <v>465532638.83</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364405909.15</v>
+        <v>1364409847.62</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1651175695.75</v>
+        <v>1651179634.22</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283717852.8</v>
+        <v>283720404.34</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4917202.46</v>
+        <v>4917224.96</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7352606.19</v>
+        <v>7352639.83</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374615451.12</v>
+        <v>374618058.81</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1038057559.71</v>
+        <v>1038061431.55</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347434276.5</v>
+        <v>1347438148.34</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218481819.85</v>
+        <v>218483322.52</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3629073.87</v>
+        <v>3629080.84</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4592061.56</v>
+        <v>4592070.37</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316831528.76</v>
+        <v>316833047.21</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143675728.75</v>
+        <v>1143682518.72</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1422158148.36</v>
+        <v>1422164938.33</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228253868.4</v>
+        <v>228257230.3</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3388630.43</v>
+        <v>3388651.12</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5521884.49</v>
+        <v>5521918.19</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>314037568.5</v>
+        <v>314040984.79</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339499072.68</v>
+        <v>1339510883.42</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1715072978.28</v>
+        <v>1715084789.02</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269960507.77</v>
+        <v>269963518.95</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2886701.69</v>
+        <v>2886704.17</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7560626.49</v>
+        <v>7560632.99</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389853305.29</v>
+        <v>389856325.46</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,9 +2926,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1172363175.6</v>
-      </c>
-      <c r="C43" s="6" t="n"/>
+        <v>1172370255.55</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>221857126.57</v>
+      </c>
       <c r="D43" s="6" t="n">
         <v>31660988.96</v>
       </c>
@@ -2945,12 +2947,14 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1340291040.09</v>
+        <v>1562155246.61</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>220131443.27</v>
-      </c>
-      <c r="K43" s="9" t="n"/>
+        <v>220133950.53</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>61180264.16</v>
+      </c>
       <c r="L43" s="9" t="n">
         <v>8080178.7</v>
       </c>
@@ -2958,19 +2962,19 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2498616.1</v>
+        <v>2632896.75</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>6814420.1</v>
+        <v>7180640.72</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>270336131.45</v>
+        <v>332019404.14</v>
       </c>
       <c r="R43" s="10" t="n">
-        <v>0.4394700544002308</v>
+        <v>0.3738082799669966</v>
       </c>
     </row>
     <row r="44">
@@ -2980,7 +2984,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1224983847.76</v>
+        <v>1224996427.88</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>118878392.5</v>
@@ -3001,10 +3005,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1503744063.03</v>
+        <v>1503756643.15</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236964303.7</v>
+        <v>236968103.03</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>32561198.02</v>
@@ -3016,16 +3020,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5196726.54</v>
+        <v>5196745.38</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6920642.79</v>
+        <v>6920667.88</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>320497526.55</v>
+        <v>320501369.81</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3923339612110134</v>
@@ -3038,7 +3042,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1838914765.05</v>
+        <v>1838936138.49</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>151695056.58</v>
@@ -3059,10 +3063,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2308919480.53</v>
+        <v>2308940853.97</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>385252000.7</v>
+        <v>385261644.59</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>38969011.58</v>
@@ -3074,16 +3078,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>10556889.87</v>
+        <v>10556993.35</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>18018388.14</v>
+        <v>18018564.75</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>520694989.14</v>
+        <v>520704913.13</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0.4083810879699633</v>
@@ -3096,7 +3100,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1904253231.77</v>
+        <v>1909056599.69</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>198191544.89</v>
@@ -3117,10 +3121,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2526857082.35</v>
+        <v>2531660450.27</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>382900397.2</v>
+        <v>383238299.37</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>54130695.48</v>
@@ -3132,16 +3136,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>11838210.35</v>
+        <v>11821939.66</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>21796251.76</v>
+        <v>21766294.52</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>556745546.88</v>
+        <v>557037221.11</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0.4547581192007113</v>
@@ -3154,9 +3158,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1021193682.46</v>
-      </c>
-      <c r="C47" s="6" t="n"/>
+        <v>1123932050.2</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>250093696.52</v>
+      </c>
       <c r="D47" s="6" t="n">
         <v>35781373.52</v>
       </c>
@@ -3173,12 +3179,14 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1202718198.47</v>
+        <v>1555550262.73</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>208890525.58</v>
-      </c>
-      <c r="K47" s="9" t="n"/>
+        <v>215562326.67</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>65852392.81</v>
+      </c>
       <c r="L47" s="9" t="n">
         <v>11249014.9</v>
       </c>
@@ -3186,23 +3194,81 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>3931383.16</v>
+        <v>3871321.83</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>5561035.32</v>
+        <v>5476077.14</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>264540875.54</v>
+        <v>336920049.93</v>
       </c>
       <c r="R47" s="10" t="n">
-        <v>0.5456835192724245</v>
+        <v>0.4207679702437824</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>1139290321.34</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>251713084.28</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>34907927.53</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>26760442</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>22486110.73</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>29324162</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>33130642</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>1537612689.88</v>
+      </c>
+      <c r="J48" s="8" t="n">
+        <v>230572300.21</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>62840730.8</v>
+      </c>
+      <c r="L48" s="9" t="n">
+        <v>9711926.279999999</v>
+      </c>
+      <c r="M48" s="9" t="n">
+        <v>7847120.41</v>
+      </c>
+      <c r="N48" s="9" t="n">
+        <v>4948739.58</v>
+      </c>
+      <c r="O48" s="9" t="n">
+        <v>6453656.79</v>
+      </c>
+      <c r="P48" s="9" t="n">
+        <v>16023075.86</v>
+      </c>
+      <c r="Q48" s="9" t="n">
+        <v>338397549.93</v>
+      </c>
+      <c r="R48" s="10" t="n">
+        <v>0.4544083188194561</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R47"/>
+  <autoFilter ref="A2:R48"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3218,7 +3284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5536,7 +5602,9 @@
       <c r="B43" s="5" t="n">
         <v>1640000000</v>
       </c>
-      <c r="C43" s="6" t="n"/>
+      <c r="C43" s="6" t="n">
+        <v>223461752.3</v>
+      </c>
       <c r="D43" s="6" t="n">
         <v>31660988.96</v>
       </c>
@@ -5553,12 +5621,14 @@
         <v>49898532</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1813111397.49</v>
+        <v>2036573149.79</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>455264000</v>
       </c>
-      <c r="K43" s="9" t="n"/>
+      <c r="K43" s="9" t="n">
+        <v>61536534.58</v>
+      </c>
       <c r="L43" s="9" t="n">
         <v>8080178.7</v>
       </c>
@@ -5566,16 +5636,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>3490389.08</v>
+        <v>3481497.74</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>10526789.58</v>
+        <v>10499973.87</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22991971.37</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>510862206.11</v>
+        <v>572363033.64</v>
       </c>
     </row>
     <row r="44">
@@ -5695,7 +5765,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>2550213045.8</v>
+        <v>2560000000</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>198965031.13</v>
@@ -5716,10 +5786,10 @@
         <v>66113614</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>3177633741.62</v>
+        <v>3187420695.82</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>707939141.51</v>
+        <v>710656000</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>54231280.55</v>
@@ -5731,16 +5801,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>15087900.32</v>
+        <v>15087342.88</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>28590825.95</v>
+        <v>28589769.62</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>33092919.58</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>892324186.26</v>
+        <v>895039430.99</v>
       </c>
     </row>
     <row r="47">
@@ -5750,9 +5820,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1367602484.72</v>
-      </c>
-      <c r="C47" s="6" t="n"/>
+        <v>1580000000</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>252221741.84</v>
+      </c>
       <c r="D47" s="6" t="n">
         <v>35781373.52</v>
       </c>
@@ -5769,12 +5841,14 @@
         <v>55958167</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1557398932.73</v>
+        <v>2022018189.85</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>379646449.76</v>
-      </c>
-      <c r="K47" s="9" t="n"/>
+        <v>438608000</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>66197336.17</v>
+      </c>
       <c r="L47" s="9" t="n">
         <v>11249014.9</v>
       </c>
@@ -5782,20 +5856,75 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>5055775.65</v>
+        <v>4999078.62</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>8386593.23</v>
+        <v>8292543.38</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>25513319.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>440525647.12</v>
+        <v>565533786.64</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>1548579111.97</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>254693199.39</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>34907927.53</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>26760442</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>22486110.73</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>33175435</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>40831654</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>1961433880.62</v>
+      </c>
+      <c r="J48" s="8" t="n">
+        <v>429885561.48</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>63291974.74</v>
+      </c>
+      <c r="L48" s="9" t="n">
+        <v>9711926.279999999</v>
+      </c>
+      <c r="M48" s="9" t="n">
+        <v>7847120.41</v>
+      </c>
+      <c r="N48" s="9" t="n">
+        <v>6234634.46</v>
+      </c>
+      <c r="O48" s="9" t="n">
+        <v>9198420.869999999</v>
+      </c>
+      <c r="P48" s="9" t="n">
+        <v>17669329.8</v>
+      </c>
+      <c r="Q48" s="9" t="n">
+        <v>543838968.03</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q47"/>
+  <autoFilter ref="A2:Q48"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -5810,7 +5939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7630,7 +7759,9 @@
       <c r="D43" s="6" t="n">
         <v>22453189</v>
       </c>
-      <c r="E43" s="6" t="n"/>
+      <c r="E43" s="6" t="n">
+        <v>75086573.58</v>
+      </c>
       <c r="F43" s="6" t="n">
         <v>5738340.25</v>
       </c>
@@ -7646,7 +7777,9 @@
       <c r="J43" s="11" t="n">
         <v>0.5371</v>
       </c>
-      <c r="K43" s="11" t="n"/>
+      <c r="K43" s="11" t="n">
+        <v>0.3384</v>
+      </c>
       <c r="L43" s="11" t="n">
         <v>0.4632</v>
       </c>
@@ -7747,7 +7880,7 @@
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>1228080594.34</v>
+        <v>1232793600</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>30527478.39</v>
@@ -7765,7 +7898,7 @@
         <v>24436069</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>0.6448999999999999</v>
+        <v>0.6457999999999999</v>
       </c>
       <c r="I46" s="11" t="n">
         <v>0.4415</v>
@@ -7790,7 +7923,7 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>658582652.54</v>
+        <v>760864800</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>14529335.06</v>
@@ -7798,7 +7931,9 @@
       <c r="D47" s="6" t="n">
         <v>31583199</v>
       </c>
-      <c r="E47" s="6" t="n"/>
+      <c r="E47" s="6" t="n">
+        <v>89069024.83</v>
+      </c>
       <c r="F47" s="6" t="n">
         <v>13310527.94</v>
       </c>
@@ -7806,7 +7941,7 @@
         <v>11226252</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>0.6448999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="I47" s="11" t="n">
         <v>0.4061</v>
@@ -7814,7 +7949,9 @@
       <c r="J47" s="11" t="n">
         <v>0.625</v>
       </c>
-      <c r="K47" s="11" t="n"/>
+      <c r="K47" s="11" t="n">
+        <v>0.3561</v>
+      </c>
       <c r="L47" s="11" t="n">
         <v>0.7447</v>
       </c>
@@ -7822,15 +7959,58 @@
         <v>0.444</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>745733757.16</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>16723415.34</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>14008880</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>102671272.38</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>19332294.14</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>13207850</v>
+      </c>
+      <c r="H48" s="11" t="n">
+        <v>0.6546</v>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>0.4791</v>
+      </c>
+      <c r="J48" s="11" t="n">
+        <v>0.5235</v>
+      </c>
+      <c r="K48" s="11" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="L48" s="11" t="n">
+        <v>0.8597</v>
+      </c>
+      <c r="M48" s="11" t="n">
+        <v>0.4504</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M47"/>
+  <autoFilter ref="A2:M48"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -7861,7 +8041,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-15. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-16. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019800096.1</v>
+        <v>1019800101.5</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203205005.61</v>
+        <v>1203205011.01</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223747425.83</v>
+        <v>223747430.8</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516297.64</v>
+        <v>516297.65</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237367.609999999</v>
+        <v>9237367.73</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289059196.86</v>
+        <v>289059201.96</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766409486.72</v>
+        <v>766409933.2</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882452033.76</v>
+        <v>882452480.24</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197402526.39</v>
+        <v>197402915.72</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374709.09</v>
+        <v>374709.52</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399340.39</v>
+        <v>5399346.58</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239491858.25</v>
+        <v>239492254.21</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983763686.27</v>
+        <v>983763697.3</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168401835.29</v>
+        <v>1168401846.32</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236064824.73</v>
+        <v>236064834.66</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324588.79</v>
+        <v>324588.8</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358548.67</v>
+        <v>7358548.85</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305861546.77</v>
+        <v>305861556.88</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960777616.5700001</v>
+        <v>960777640.1</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185450933.69</v>
+        <v>1185450957.22</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212552579.64</v>
+        <v>212552600.35</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490172.37</v>
+        <v>2490172.5</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929357.880000001</v>
+        <v>8929358.35</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296187450.59</v>
+        <v>296187471.9</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686512372.66</v>
+        <v>686512373.66</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813424063.6900001</v>
+        <v>813424064.6900001</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150993223.5</v>
+        <v>150993224.39</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897066.53</v>
+        <v>1897066.54</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485530.86</v>
+        <v>3485530.87</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196257780.79</v>
+        <v>196257781.7</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042731595.8</v>
+        <v>1042731597.94</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244215785.87</v>
+        <v>1244215788.01</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230883839.62</v>
+        <v>230883841.47</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865669.94</v>
+        <v>2865669.95</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026082.73</v>
+        <v>7026082.76</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305688663.73</v>
+        <v>305688665.62</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046532400.86</v>
+        <v>1046532401.86</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268579500.67</v>
+        <v>1268579501.67</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238383632.52</v>
+        <v>238383633.41</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737713.27</v>
+        <v>3737713.28</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838303.81</v>
+        <v>7838303.82</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315850386.4</v>
+        <v>315850387.31</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123212251.73</v>
+        <v>1123212254</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375387413.06</v>
+        <v>1375387415.33</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251892590.66</v>
+        <v>251892592.63</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520553.18</v>
+        <v>3520553.19</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255926.93</v>
+        <v>11255926.97</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341112027.6</v>
+        <v>341112029.64</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780515303.54</v>
+        <v>780515305.54</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941932149.0700001</v>
+        <v>941932151.0700001</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182890957.99</v>
+        <v>182890959.75</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893249.12</v>
+        <v>2893249.14</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978990.13</v>
+        <v>4978990.16</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240375040.17</v>
+        <v>240375041.98</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925224370.9299999</v>
+        <v>925224472.9299999</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103227754.75</v>
+        <v>1103227856.75</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208939781.33</v>
+        <v>208939866.08</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099145.1</v>
+        <v>3099145.81</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218663.55</v>
+        <v>6218664.97</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270758099.99</v>
+        <v>270758186.87</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099264241.31</v>
+        <v>1099264246.99</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314564535.13</v>
+        <v>1314564540.81</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244622801.06</v>
+        <v>244622806.01</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671186.75</v>
+        <v>3671186.79</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710545.9</v>
+        <v>7710545.99</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319476954.41</v>
+        <v>319476959.49</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967596880.24</v>
+        <v>967596891.24</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190917885.82</v>
+        <v>1190917896.82</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210534603.71</v>
+        <v>210534613.34</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281805.41</v>
+        <v>3281805.5</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536312.8</v>
+        <v>7536312.99</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283817602.59</v>
+        <v>283817612.5</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003080732.14</v>
+        <v>1003080789.3</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198237420.2</v>
+        <v>1198237477.36</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222088829.04</v>
+        <v>222088873.29</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891039.85</v>
+        <v>3891040.29</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335937.93</v>
+        <v>6335938.65</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281020301.75</v>
+        <v>281020347.16</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156894814.23</v>
+        <v>1156894960.06</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409394781.88</v>
+        <v>1409394927.71</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247797984.74</v>
+        <v>247798111.87</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795238.2</v>
+        <v>3795239.34</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929397.9</v>
+        <v>9929400.869999999</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325995845.63</v>
+        <v>325995976.86</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870299933.05</v>
+        <v>870299950.41</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039404145.42</v>
+        <v>1039404162.78</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193432998.9</v>
+        <v>193433013.8</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256063.08</v>
+        <v>3256063.23</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684205.34</v>
+        <v>5684205.6</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245275078.95</v>
+        <v>245275094.26</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002264719.12</v>
+        <v>1002264818.99</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209602127.08</v>
+        <v>1209602226.95</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>217000443.53</v>
+        <v>217000531.68</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934141.61</v>
+        <v>2934142.31</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937706.58</v>
+        <v>6937708.24</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280972696.8</v>
+        <v>280972787.32</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105963996.73</v>
+        <v>1105964021.71</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351818896.38</v>
+        <v>1351818921.36</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242483922.27</v>
+        <v>242483944.82</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693257.52</v>
+        <v>2693257.66</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764071.310000001</v>
+        <v>8764071.779999999</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322797730.1</v>
+        <v>322797753.26</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932844096.4</v>
+        <v>932844116.4</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136791910.85</v>
+        <v>1136791930.85</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196524670.96</v>
+        <v>196524689.16</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927930.49</v>
+        <v>2927930.65</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577853.47</v>
+        <v>6577853.82</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259478796.28</v>
+        <v>259478815</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1097001440.62</v>
+        <v>1097001442.8</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283042466.73</v>
+        <v>1283042468.91</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243427083.95</v>
+        <v>243427085.94</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660622.16</v>
+        <v>1660622.17</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202030.69</v>
+        <v>7202030.73</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302144628.33</v>
+        <v>302144630.36</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142128807.21</v>
+        <v>1142128813.8</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1366019921.16</v>
+        <v>1366019927.75</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239660821.59</v>
+        <v>239660827.54</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298509.63</v>
+        <v>1298509.65</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234272.82</v>
+        <v>9234272.960000001</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307453978.78</v>
+        <v>307453984.88</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192852962.78</v>
+        <v>1192852973.74</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436509969.45</v>
+        <v>1436509980.41</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253631910.11</v>
+        <v>253631920.03</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145315.28</v>
+        <v>2145315.33</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745133.7</v>
+        <v>6745133.86</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327986761.29</v>
+        <v>327986771.42</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226940252.72</v>
+        <v>1226940261.36</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494280543.59</v>
+        <v>1494280552.23</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272958698.97</v>
+        <v>272958706.92</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511838</v>
+        <v>2511838.04</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248295.88</v>
+        <v>7248296</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361200917.53</v>
+        <v>361200925.64</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348620711.18</v>
+        <v>1348621016.18</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622940855.93</v>
+        <v>1622941160.93</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278436127.15</v>
+        <v>278436386.62</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307529.34</v>
+        <v>2307530.6</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088505.01</v>
+        <v>8088509.42</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361823068.29</v>
+        <v>361823333.43</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778317503.22</v>
+        <v>1778317504.22</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122380565.28</v>
+        <v>2122380566.28</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364513638.36</v>
+        <v>364513639.24</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3919084.97</v>
+        <v>3919084.98</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6647147.73</v>
+        <v>6647147.74</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465532638.83</v>
+        <v>465532639.72</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364409847.62</v>
+        <v>1364409904.96</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1651179634.22</v>
+        <v>1651179691.56</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283720404.34</v>
+        <v>283720454.24</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4917224.96</v>
+        <v>4917225.46</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7352639.83</v>
+        <v>7352640.58</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374618058.81</v>
+        <v>374618109.95</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1038061431.55</v>
+        <v>1038061437.18</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347438148.34</v>
+        <v>1347438153.97</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218483322.52</v>
+        <v>218483327.47</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3629080.84</v>
+        <v>3629080.88</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4592070.37</v>
+        <v>4592070.42</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316833047.21</v>
+        <v>316833052.26</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339510883.42</v>
+        <v>1339510921.1</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1715084789.02</v>
+        <v>1715084826.7</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269963518.95</v>
+        <v>269963543.29</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2886704.17</v>
+        <v>2886704.29</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7560632.99</v>
+        <v>7560633.31</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389856325.46</v>
+        <v>389856350.24</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1172370255.55</v>
+        <v>1172370466.16</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>221857126.57</v>
@@ -2947,10 +2947,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1562155246.61</v>
+        <v>1562155457.22</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>220133950.53</v>
+        <v>220134141.6</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>61180264.16</v>
@@ -2962,16 +2962,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2632896.75</v>
+        <v>2632897.94</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>7180640.72</v>
+        <v>7180643.98</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>332019404.14</v>
+        <v>332019599.66</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.3738082799669966</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1224996427.88</v>
+        <v>1224996453.71</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>118878392.5</v>
@@ -3005,10 +3005,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1503756643.15</v>
+        <v>1503756668.98</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236968103.03</v>
+        <v>236968127.01</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>32561198.02</v>
@@ -3020,16 +3020,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5196745.38</v>
+        <v>5196745.69</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6920667.88</v>
+        <v>6920668.29</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>320501369.81</v>
+        <v>320501394.51</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3923339612110134</v>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1838936138.49</v>
+        <v>1838936146.5</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>151695056.58</v>
@@ -3063,10 +3063,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2308940853.97</v>
+        <v>2308940861.98</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>385261644.59</v>
+        <v>385261649.62</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>38969011.58</v>
@@ -3078,16 +3078,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>10556993.35</v>
+        <v>10556993.42</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>18018564.75</v>
+        <v>18018564.87</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>520704913.13</v>
+        <v>520704918.35</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0.4083810879699633</v>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1909056599.69</v>
+        <v>1909063527.89</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>198191544.89</v>
@@ -3121,10 +3121,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2531660450.27</v>
+        <v>2531667378.47</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>383238299.37</v>
+        <v>383241910.94</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>54130695.48</v>
@@ -3136,16 +3136,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>11821939.66</v>
+        <v>11821986.8</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>21766294.52</v>
+        <v>21766381.31</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>557037221.11</v>
+        <v>557040966.61</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0.4547581192007113</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1123932050.2</v>
+        <v>1123947290.66</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>250093696.52</v>
@@ -3179,10 +3179,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1555550262.73</v>
+        <v>1555565503.19</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>215562326.67</v>
+        <v>215568951.22</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>65852392.81</v>
@@ -3194,16 +3194,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>3871321.83</v>
+        <v>3871361.11</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>5476077.14</v>
+        <v>5476132.7</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>336920049.93</v>
+        <v>336926769.32</v>
       </c>
       <c r="R47" s="10" t="n">
         <v>0.4207679702437824</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1139290321.34</v>
+        <v>1139620016.1</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>251713084.28</v>
@@ -3237,10 +3237,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>1537612689.88</v>
+        <v>1537942384.64</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>230572300.21</v>
+        <v>230615554.39</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>62840730.8</v>
@@ -3252,16 +3252,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>4948739.58</v>
+        <v>4948296.18</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>6453656.79</v>
+        <v>6453078.55</v>
       </c>
       <c r="P48" s="9" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>338397549.93</v>
+        <v>338439782.46</v>
       </c>
       <c r="R48" s="10" t="n">
         <v>0.4544083188194561</v>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1548579111.97</v>
+        <v>1549023483.29</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>254693199.39</v>
@@ -5896,10 +5896,10 @@
         <v>40831654</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>1961433880.62</v>
+        <v>1961878251.94</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>429885561.48</v>
+        <v>430008918.96</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>63291974.74</v>
@@ -5911,16 +5911,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>6234634.46</v>
+        <v>6234636.21</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>9198420.869999999</v>
+        <v>9198423.449999999</v>
       </c>
       <c r="P48" s="9" t="n">
         <v>17669329.8</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>543838968.03</v>
+        <v>543962329.85</v>
       </c>
     </row>
   </sheetData>
@@ -7966,7 +7966,7 @@
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>745733757.16</v>
+        <v>745947748.61</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>16723415.34</v>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R48"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226361144.05</v>
+        <v>1226361202.05</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404323238.63</v>
+        <v>1404323296.63</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290715478.15</v>
+        <v>290715479.81</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524812.1899999999</v>
+        <v>524812.17</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360273.67</v>
+        <v>9360273.32</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354058470.65</v>
+        <v>354058471.94</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019800101.5</v>
+        <v>1019800254.25</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203205011.01</v>
+        <v>1203205163.76</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223747430.8</v>
+        <v>223747447.19</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516297.65</v>
+        <v>516297.61</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237367.73</v>
+        <v>9237367.060000001</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289059201.96</v>
+        <v>289059217.64</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766409933.2</v>
+        <v>766410037.92</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882452480.24</v>
+        <v>882452584.96</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197402915.72</v>
+        <v>197402935.5</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374709.52</v>
+        <v>374709.51</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399346.58</v>
+        <v>5399346.38</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239492254.21</v>
+        <v>239492273.77</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983763697.3</v>
+        <v>983765686.88</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168401846.32</v>
+        <v>1168403835.9</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236064834.66</v>
+        <v>236065045.07</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324588.8</v>
+        <v>324588.46</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358548.85</v>
+        <v>7358541.19</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305861556.88</v>
+        <v>305861759.29</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097589214.24</v>
+        <v>1097589837.49</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302669251.82</v>
+        <v>1302669875.07</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250951260.78</v>
+        <v>250951565.99</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.67</v>
+        <v>709928</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693358.91</v>
+        <v>7693362.48</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328055278.62</v>
+        <v>328055587.73</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011526262.43</v>
+        <v>1011526385.94</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233699381.94</v>
+        <v>1233699505.45</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229526167.41</v>
+        <v>229526179.85</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255744.22</v>
+        <v>1255744.14</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409734.609999999</v>
+        <v>8409734.09</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309201102.9</v>
+        <v>309201114.74</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961944869.98</v>
+        <v>961945781.22</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145552031.52</v>
+        <v>1145552942.76</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214890748.42</v>
+        <v>214890823.29</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814777.23</v>
+        <v>814776.79</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850533.49</v>
+        <v>6850529.76</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281207904.34</v>
+        <v>281207975.04</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960777640.1</v>
+        <v>960778236.1</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185450957.22</v>
+        <v>1185451553.22</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212552600.35</v>
+        <v>212552807.07</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490172.5</v>
+        <v>2490173.01</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929358.35</v>
+        <v>8929360.16</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296187471.9</v>
+        <v>296187680.94</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686512373.66</v>
+        <v>686513890.54</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813424064.6900001</v>
+        <v>813425581.5700001</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150993224.39</v>
+        <v>150993262.61</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897066.54</v>
+        <v>1897063.28</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485530.87</v>
+        <v>3485524.89</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196257781.7</v>
+        <v>196257810.67</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970915246.6900001</v>
+        <v>970916067.75</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130471900.93</v>
+        <v>1130472721.99</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227542411.3</v>
+        <v>227542471.23</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642023.44</v>
+        <v>2642022.03</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513116.07</v>
+        <v>5513113.14</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286540099.26</v>
+        <v>286540154.85</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042731597.94</v>
+        <v>1042731983.92</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244215788.01</v>
+        <v>1244216173.99</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230883841.47</v>
+        <v>230883889.47</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865669.95</v>
+        <v>2865669.5</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026082.76</v>
+        <v>7026081.65</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305688665.62</v>
+        <v>305688712.06</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046532401.86</v>
+        <v>1046532977.02</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268579501.67</v>
+        <v>1268580076.83</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238383633.41</v>
+        <v>238383739.88</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737713.28</v>
+        <v>3737712.83</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838303.82</v>
+        <v>7838302.88</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315850387.31</v>
+        <v>315850492.39</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026530232.06</v>
+        <v>1026532112.91</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228674111.09</v>
+        <v>1228675991.94</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246157012.96</v>
+        <v>246157204.12</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558667.43</v>
+        <v>3558664.02</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537362.7</v>
+        <v>7537355.48</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315577097.25</v>
+        <v>315577277.78</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275235677.99</v>
+        <v>1275236351.52</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517957155.24</v>
+        <v>1517957828.77</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295677038.34</v>
+        <v>295677142.35</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271138.22</v>
+        <v>4271137.47</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581195.810000001</v>
+        <v>9581194.119999999</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378773368.25</v>
+        <v>378773469.82</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123212254</v>
+        <v>1123212464.54</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375387415.33</v>
+        <v>1375387625.87</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251892592.63</v>
+        <v>251892628.12</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520553.19</v>
+        <v>3520553.01</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255926.97</v>
+        <v>11255926.4</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341112029.64</v>
+        <v>341112064.37</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780515305.54</v>
+        <v>780515433.72</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941932151.0700001</v>
+        <v>941932279.25</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182890959.75</v>
+        <v>182890983.85</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893249.14</v>
+        <v>2893249.03</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978990.16</v>
+        <v>4978989.97</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240375041.98</v>
+        <v>240375065.78</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925224472.9299999</v>
+        <v>925224978.41</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103227856.75</v>
+        <v>1103228362.23</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208939866.08</v>
+        <v>208940039.41</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099145.81</v>
+        <v>3099146.39</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218664.97</v>
+        <v>6218666.14</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270758186.87</v>
+        <v>270758361.95</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099264246.99</v>
+        <v>1099264250.94</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314564540.81</v>
+        <v>1314564544.76</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244622806.01</v>
+        <v>244622806.96</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1695,7 +1695,7 @@
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319476959.49</v>
+        <v>319476960.44</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967596891.24</v>
+        <v>967598832.75</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190917896.82</v>
+        <v>1190919838.33</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210534613.34</v>
+        <v>210535004.55</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281805.5</v>
+        <v>3281804.64</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536312.99</v>
+        <v>7536311.02</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283817612.5</v>
+        <v>283818000.87</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003080789.3</v>
+        <v>1003085647.23</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198237477.36</v>
+        <v>1198242335.29</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222088873.29</v>
+        <v>222089155.67</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891040.29</v>
+        <v>3891027.98</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335938.65</v>
+        <v>6335918.6</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281020347.16</v>
+        <v>281020597.18</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362287608.99</v>
+        <v>1362287973.66</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634504364.11</v>
+        <v>1634504728.78</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306762960.85</v>
+        <v>306763194.65</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136470.22</v>
+        <v>6136472.65</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270562.13</v>
+        <v>10270566.19</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388022124.69</v>
+        <v>388022364.99</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156894960.06</v>
+        <v>1156899086.48</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409394927.71</v>
+        <v>1409399054.13</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247798111.87</v>
+        <v>247798463.68</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795239.34</v>
+        <v>3795232.01</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929400.869999999</v>
+        <v>9929381.710000001</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325995976.86</v>
+        <v>325996302.19</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870299950.41</v>
+        <v>870301252.36</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039404162.78</v>
+        <v>1039405464.73</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193433013.8</v>
+        <v>193433237.04</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256063.23</v>
+        <v>3256062.08</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684205.6</v>
+        <v>5684203.58</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245275094.26</v>
+        <v>245275314.32</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002264818.99</v>
+        <v>1002266289.35</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209602226.95</v>
+        <v>1209603697.31</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>217000531.68</v>
+        <v>217000821.37</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934142.31</v>
+        <v>2934141.75</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937708.24</v>
+        <v>6937706.92</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280972787.32</v>
+        <v>280973075.12</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105964021.71</v>
+        <v>1105965582.72</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351818921.36</v>
+        <v>1351820482.37</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242483944.82</v>
+        <v>242484578.37</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693257.66</v>
+        <v>2693259.92</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764071.779999999</v>
+        <v>8764079.119999999</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322797753.26</v>
+        <v>322798396.4</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932844116.4</v>
+        <v>932845526.6</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136791930.85</v>
+        <v>1136793341.05</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196524689.16</v>
+        <v>196525044.78</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927930.65</v>
+        <v>2927931.05</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577853.82</v>
+        <v>6577854.71</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259478815</v>
+        <v>259479171.9</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1162029739.64</v>
+        <v>1162031928.44</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354866223.71</v>
+        <v>1354868412.51</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252352097.41</v>
+        <v>252352892.18</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229195.02</v>
+        <v>4229199.08</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541681.35</v>
+        <v>4541685.71</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311964692.41</v>
+        <v>311965495.6</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1440005057.95</v>
+        <v>1440006133.02</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740061723.98</v>
+        <v>1740062799.05</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284718820.17</v>
+        <v>284719171.81</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067083.37</v>
+        <v>4067084.7</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978505.6</v>
+        <v>5978507.56</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375589598</v>
+        <v>375589952.93</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319732411.58</v>
+        <v>1319733641.59</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579495495.7</v>
+        <v>1579496725.71</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283378202.78</v>
+        <v>283378656.52</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050965.51</v>
+        <v>3050966.99</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438405.9</v>
+        <v>7438409.5</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363618938.72</v>
+        <v>363619397.52</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1097001442.8</v>
+        <v>1097004720.4</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283042468.91</v>
+        <v>1283045746.51</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243427085.94</v>
+        <v>243428476.06</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660622.17</v>
+        <v>1660625.67</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202030.73</v>
+        <v>7202045.91</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302144630.36</v>
+        <v>302146039.17</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142128813.8</v>
+        <v>1142131013.09</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1366019927.75</v>
+        <v>1366022127.04</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239660827.54</v>
+        <v>239661198.66</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298509.65</v>
+        <v>1298509.1</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234272.960000001</v>
+        <v>9234269.1</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307453984.88</v>
+        <v>307454351.61</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192852973.74</v>
+        <v>1192853919.21</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436509980.41</v>
+        <v>1436510925.88</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253631920.03</v>
+        <v>253632137.79</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145315.33</v>
+        <v>2145315.34</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745133.86</v>
+        <v>6745133.9</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327986771.42</v>
+        <v>327986989.23</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226940261.36</v>
+        <v>1226941524.28</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494280552.23</v>
+        <v>1494281815.15</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272958706.92</v>
+        <v>272959013.67</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511838.04</v>
+        <v>2511838.05</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248296</v>
+        <v>7248296.03</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361200925.64</v>
+        <v>361201232.43</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348621016.18</v>
+        <v>1348627835.36</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622941160.93</v>
+        <v>1622947980.11</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278436386.62</v>
+        <v>278437421.33</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307530.6</v>
+        <v>2307527.41</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088509.42</v>
+        <v>8088498.24</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361823333.43</v>
+        <v>361824353.77</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778317504.22</v>
+        <v>1778318762.6</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122380566.28</v>
+        <v>2122381824.66</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364513639.24</v>
+        <v>364514014.12</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3919084.98</v>
+        <v>3919085.83</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6647147.74</v>
+        <v>6647149.18</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465532639.72</v>
+        <v>465533016.9</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364409904.96</v>
+        <v>1364413038.73</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1651179691.56</v>
+        <v>1651182825.33</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283720454.24</v>
+        <v>283721727.5</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4917225.46</v>
+        <v>4917233.09</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7352640.58</v>
+        <v>7352651.99</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374618109.95</v>
+        <v>374619402.25</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1038061437.18</v>
+        <v>1038064277.51</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347438153.97</v>
+        <v>1347440994.3</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218483327.47</v>
+        <v>218485207.4</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3629080.88</v>
+        <v>3629095.14</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4592070.42</v>
+        <v>4592088.46</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316833052.26</v>
+        <v>316834964.47</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143682518.72</v>
+        <v>1143685308.46</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1422164938.33</v>
+        <v>1422167728.07</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228257230.3</v>
+        <v>228258058.42</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3388651.12</v>
+        <v>3388653.47</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5521918.19</v>
+        <v>5521922.03</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>314040984.79</v>
+        <v>314041819.11</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339510921.1</v>
+        <v>1339517738.52</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1715084826.7</v>
+        <v>1715091644.12</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269963543.29</v>
+        <v>269966857.82</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2886704.29</v>
+        <v>2886717.72</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7560633.31</v>
+        <v>7560668.47</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389856350.24</v>
+        <v>389859713.36</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1172370466.16</v>
+        <v>1172377133.83</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>221857126.57</v>
@@ -2947,10 +2947,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1562155457.22</v>
+        <v>1562162124.89</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>220134141.6</v>
+        <v>220136981.03</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>61180264.16</v>
@@ -2962,16 +2962,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2632897.94</v>
+        <v>2632909.57</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>7180643.98</v>
+        <v>7180675.67</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>332019599.66</v>
+        <v>332022482.41</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.3738082799669966</v>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1224996453.71</v>
+        <v>1225003004.92</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>118878392.5</v>
+        <v>197998279.3</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>36482666.67</v>
@@ -3005,13 +3005,13 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1503756668.98</v>
+        <v>1582883106.99</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236968127.01</v>
+        <v>236971328.93</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>32561198.02</v>
+        <v>51757451.41</v>
       </c>
       <c r="L44" s="9" t="n">
         <v>11549732.06</v>
@@ -3020,19 +3020,19 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5196745.69</v>
+        <v>5234052.76</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6920668.29</v>
+        <v>6970351.28</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>320501394.51</v>
+        <v>339787839.87</v>
       </c>
       <c r="R44" s="10" t="n">
-        <v>0.3923339612110134</v>
+        <v>0.3916156197964661</v>
       </c>
     </row>
     <row r="45">
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1838936146.5</v>
+        <v>1838947578.71</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>151695056.58</v>
+        <v>306596831.13</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>66142107.86</v>
@@ -3063,13 +3063,13 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2308940861.98</v>
+        <v>2463854068.74</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>385261649.62</v>
+        <v>385266939.01</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>38969011.58</v>
+        <v>76961502.72</v>
       </c>
       <c r="L45" s="9" t="n">
         <v>23893066.65</v>
@@ -3078,19 +3078,19 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>10556993.42</v>
+        <v>10618329.66</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>18018564.87</v>
+        <v>18123252.92</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>520704918.35</v>
+        <v>558868723.16</v>
       </c>
       <c r="R45" s="10" t="n">
-        <v>0.4083810879699633</v>
+        <v>0.40067966485108</v>
       </c>
     </row>
     <row r="46">
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1909063527.89</v>
+        <v>1909112664.27</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>198191544.89</v>
+        <v>376107142.6</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>69142299.48</v>
@@ -3121,13 +3121,13 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2531667378.47</v>
+        <v>2709632112.56</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>383241910.94</v>
+        <v>383261020.27</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>54130695.48</v>
+        <v>102191529.21</v>
       </c>
       <c r="L46" s="9" t="n">
         <v>23371135.67</v>
@@ -3136,19 +3136,19 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>11821986.8</v>
+        <v>12009472.88</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>21766381.31</v>
+        <v>22111576.55</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>557040966.61</v>
+        <v>605653590.99</v>
       </c>
       <c r="R46" s="10" t="n">
-        <v>0.4547581192007113</v>
+        <v>0.442865215754716</v>
       </c>
     </row>
     <row r="47">
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1123947290.66</v>
+        <v>1124143180.65</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>250093696.52</v>
@@ -3179,10 +3179,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1555565503.19</v>
+        <v>1555761393.18</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>215568951.22</v>
+        <v>215628916.24</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>65852392.81</v>
@@ -3194,16 +3194,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>3871361.11</v>
+        <v>3871568.33</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>5476132.7</v>
+        <v>5476425.82</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>336926769.32</v>
+        <v>336987234.67</v>
       </c>
       <c r="R47" s="10" t="n">
         <v>0.4207679702437824</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1139620016.1</v>
+        <v>1314078145.15</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>251713084.28</v>
@@ -3237,10 +3237,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>1537942384.64</v>
+        <v>1712400513.69</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>230615554.39</v>
+        <v>241884601.49</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>62840730.8</v>
@@ -3252,23 +3252,81 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>4948296.18</v>
+        <v>4581033.12</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>6453078.55</v>
+        <v>5974130.38</v>
       </c>
       <c r="P48" s="9" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>338439782.46</v>
+        <v>348862618.34</v>
       </c>
       <c r="R48" s="10" t="n">
         <v>0.4544083188194561</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>1150729376.45</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>255216837.43</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>42964472.77</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>36577969</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>26458483.63</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>30577407</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>28557666</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>1571082212.28</v>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>231539145.94</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>63158844.13</v>
+      </c>
+      <c r="L49" s="9" t="n">
+        <v>12338190.77</v>
+      </c>
+      <c r="M49" s="9" t="n">
+        <v>10739760.3</v>
+      </c>
+      <c r="N49" s="9" t="n">
+        <v>5794011.54</v>
+      </c>
+      <c r="O49" s="9" t="n">
+        <v>6695994.05</v>
+      </c>
+      <c r="P49" s="9" t="n">
+        <v>13777521.12</v>
+      </c>
+      <c r="Q49" s="9" t="n">
+        <v>344043467.84</v>
+      </c>
+      <c r="R49" s="10" t="n">
+        <v>0.4715622688002217</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R48"/>
+  <autoFilter ref="A2:R49"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3284,7 +3342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5658,7 +5716,7 @@
         <v>1700000000</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>120197775.42</v>
+        <v>200060063.21</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>36482666.67</v>
@@ -5676,13 +5734,13 @@
         <v>43834004</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1989258148.19</v>
+        <v>2069120435.98</v>
       </c>
       <c r="J44" s="8" t="n">
         <v>471920000</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>32887256.58</v>
+        <v>52316511.19</v>
       </c>
       <c r="L44" s="9" t="n">
         <v>11549732.06</v>
@@ -5691,16 +5749,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>6901247.9</v>
+        <v>6862714.94</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>10100783.08</v>
+        <v>10044385.59</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>19960813.73</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>563040540.4</v>
+        <v>582374864.5599999</v>
       </c>
     </row>
     <row r="45">
@@ -5713,7 +5771,7 @@
         <v>2370000000</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>152527110.31</v>
+        <v>308253587.03</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>66142107.86</v>
@@ -5731,13 +5789,13 @@
         <v>34419473</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2846148617.21</v>
+        <v>3001875093.93</v>
       </c>
       <c r="J45" s="8" t="n">
         <v>657912000</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>39087094.48</v>
+        <v>77234060.05</v>
       </c>
       <c r="L45" s="9" t="n">
         <v>23893066.65</v>
@@ -5746,16 +5804,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>13195961.14</v>
+        <v>13102229.99</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>23379323.68</v>
+        <v>23213259.91</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>16489733.2</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>802300792.23</v>
+        <v>840187962.88</v>
       </c>
     </row>
     <row r="46">
@@ -5768,7 +5826,7 @@
         <v>2560000000</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>198965031.13</v>
+        <v>377631315.28</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>69142299.48</v>
@@ -5786,13 +5844,13 @@
         <v>66113614</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>3187420695.82</v>
+        <v>3366086979.97</v>
       </c>
       <c r="J46" s="8" t="n">
         <v>710656000</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>54231280.55</v>
+        <v>102432751.1</v>
       </c>
       <c r="L46" s="9" t="n">
         <v>23371135.67</v>
@@ -5801,16 +5859,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>15087342.88</v>
+        <v>15054396.62</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>28589769.62</v>
+        <v>28527338.1</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>33092919.58</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>895039430.99</v>
+        <v>943145523.76</v>
       </c>
     </row>
     <row r="47">
@@ -5875,7 +5933,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1549023483.29</v>
+        <v>1910000000</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>254693199.39</v>
@@ -5896,10 +5954,10 @@
         <v>40831654</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>1961878251.94</v>
+        <v>2322854768.65</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>430008918.96</v>
+        <v>530216000</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>63291974.74</v>
@@ -5911,20 +5969,75 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>6234636.21</v>
+        <v>6235831.63</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>9198423.449999999</v>
+        <v>9200187.15</v>
       </c>
       <c r="P48" s="9" t="n">
         <v>17669329.8</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>543962329.85</v>
+        <v>644172370.01</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>1577902692</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>259850875.34</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>42964472.77</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>36577969</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>26458483.63</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>35017529</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>41032470</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>2019804491.74</v>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>438025787.3</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>63886790.88</v>
+      </c>
+      <c r="L49" s="9" t="n">
+        <v>12338190.77</v>
+      </c>
+      <c r="M49" s="9" t="n">
+        <v>10739760.3</v>
+      </c>
+      <c r="N49" s="9" t="n">
+        <v>7315927.02</v>
+      </c>
+      <c r="O49" s="9" t="n">
+        <v>9682553.630000001</v>
+      </c>
+      <c r="P49" s="9" t="n">
+        <v>16498863.67</v>
+      </c>
+      <c r="Q49" s="9" t="n">
+        <v>558487873.5700001</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q48"/>
+  <autoFilter ref="A2:Q49"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -5939,7 +6052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7803,7 +7916,7 @@
         <v>11713221</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>36985227.39</v>
+        <v>67800055.73</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>19074195.33</v>
@@ -7821,7 +7934,7 @@
         <v>0.4085</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>0.3111</v>
+        <v>0.3424</v>
       </c>
       <c r="L44" s="11" t="n">
         <v>0.7823</v>
@@ -7846,7 +7959,7 @@
         <v>42363201</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>53274388.26</v>
+        <v>111953905.55</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>35518475.4</v>
@@ -7864,7 +7977,7 @@
         <v>0.454</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0.3512</v>
+        <v>0.3652</v>
       </c>
       <c r="L45" s="11" t="n">
         <v>0.7587</v>
@@ -7889,7 +8002,7 @@
         <v>87962042</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>62409461.1</v>
+        <v>134576214.47</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>48256943.28</v>
@@ -7898,7 +8011,7 @@
         <v>24436069</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>0.6457999999999999</v>
+        <v>0.6456999999999999</v>
       </c>
       <c r="I46" s="11" t="n">
         <v>0.4415</v>
@@ -7907,7 +8020,7 @@
         <v>0.639</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>0.3149</v>
+        <v>0.3578</v>
       </c>
       <c r="L46" s="11" t="n">
         <v>0.8981999999999999</v>
@@ -7941,7 +8054,7 @@
         <v>11226252</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>0.677</v>
+        <v>0.6768000000000001</v>
       </c>
       <c r="I47" s="11" t="n">
         <v>0.4061</v>
@@ -7966,7 +8079,7 @@
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>745947748.61</v>
+        <v>919779600</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>16723415.34</v>
@@ -7984,7 +8097,7 @@
         <v>13207850</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>0.6546</v>
+        <v>0.6999</v>
       </c>
       <c r="I48" s="11" t="n">
         <v>0.4791</v>
@@ -8002,15 +8115,58 @@
         <v>0.4504</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>759854820.36</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>19750670.59</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>18451428</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>110565065.63</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>24515713.9</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>11477871</v>
+      </c>
+      <c r="H49" s="11" t="n">
+        <v>0.6603</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>0.4597</v>
+      </c>
+      <c r="J49" s="11" t="n">
+        <v>0.5044</v>
+      </c>
+      <c r="K49" s="11" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="L49" s="11" t="n">
+        <v>0.9266</v>
+      </c>
+      <c r="M49" s="11" t="n">
+        <v>0.3754</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M48"/>
+  <autoFilter ref="A2:M49"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -8041,7 +8197,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-16. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-17. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019800254.25</v>
+        <v>1019800301.13</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203205163.76</v>
+        <v>1203205210.64</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223747447.19</v>
+        <v>223747449.53</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516297.61</v>
+        <v>516297.6</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237367.060000001</v>
+        <v>9237366.76</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289059217.64</v>
+        <v>289059219.67</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983765686.88</v>
+        <v>983766057.36</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168403835.9</v>
+        <v>1168404206.38</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236065045.07</v>
+        <v>236065063.82</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324588.46</v>
+        <v>324588.38</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358541.19</v>
+        <v>7358539.26</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305861759.29</v>
+        <v>305861776.02</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011526385.94</v>
+        <v>1011526531.04</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233699505.45</v>
+        <v>1233699650.55</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229526179.85</v>
+        <v>229526189.22</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255744.14</v>
+        <v>1255744.03</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409734.09</v>
+        <v>8409733.33</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309201114.74</v>
+        <v>309201123.24</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960778236.1</v>
+        <v>960778751.6799999</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185451553.22</v>
+        <v>1185452068.8</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212552807.07</v>
+        <v>212552827.69</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490173.01</v>
+        <v>2490172.06</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929360.16</v>
+        <v>8929356.77</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296187680.94</v>
+        <v>296187697.22</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099264250.94</v>
+        <v>1099264329.12</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314564544.76</v>
+        <v>1314564622.94</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244622806.96</v>
+        <v>244622811.65</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671186.79</v>
+        <v>3671186.62</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710545.99</v>
+        <v>7710545.63</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319476960.44</v>
+        <v>319476964.6</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932845526.6</v>
+        <v>932845545.6</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136793341.05</v>
+        <v>1136793360.05</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196525044.78</v>
+        <v>196525045.73</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927931.05</v>
+        <v>2927931.01</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577854.71</v>
+        <v>6577854.62</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259479171.9</v>
+        <v>259479172.72</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1162031928.44</v>
+        <v>1162031947.44</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354868412.51</v>
+        <v>1354868431.51</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252352892.18</v>
+        <v>252352892.94</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229199.08</v>
+        <v>4229199.03</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541685.71</v>
+        <v>4541685.65</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311965495.6</v>
+        <v>311965496.25</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1097004720.4</v>
+        <v>1097004798.58</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283045746.51</v>
+        <v>1283045824.69</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243428476.06</v>
+        <v>243428480.75</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660625.67</v>
+        <v>1660625.59</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202045.91</v>
+        <v>7202045.57</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302146039.17</v>
+        <v>302146043.44</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348627835.36</v>
+        <v>1348627859.36</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622947980.11</v>
+        <v>1622948004.11</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278437421.33</v>
+        <v>278437422.56</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307527.41</v>
+        <v>2307527.38</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088498.24</v>
+        <v>8088498.15</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361824353.77</v>
+        <v>361824354.88</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364413038.73</v>
+        <v>1364413044.73</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1651182825.33</v>
+        <v>1651182831.33</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283721727.5</v>
+        <v>283721727.8</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4917233.09</v>
+        <v>4917233.07</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7352651.99</v>
+        <v>7352651.97</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374619402.25</v>
+        <v>374619402.52</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1038064277.51</v>
+        <v>1038064307.51</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347440994.3</v>
+        <v>1347441024.3</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218485207.4</v>
+        <v>218485208.6</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3629095.14</v>
+        <v>3629095.07</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4592088.46</v>
+        <v>4592088.37</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316834964.47</v>
+        <v>316834965.52</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339517738.52</v>
+        <v>1339517739.91</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1715091644.12</v>
+        <v>1715091645.51</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269966857.82</v>
+        <v>269966858.79</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2907,13 +2907,13 @@
         <v>2886717.72</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7560668.47</v>
+        <v>7560668.49</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389859713.36</v>
+        <v>389859714.35</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1172377133.83</v>
+        <v>1172377140.96</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>221857126.57</v>
@@ -2947,10 +2947,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1562162124.89</v>
+        <v>1562162132.02</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>220136981.03</v>
+        <v>220136983.53</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>61180264.16</v>
@@ -2962,16 +2962,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2632909.57</v>
+        <v>2632909.58</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>7180675.67</v>
+        <v>7180675.7</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>332022482.41</v>
+        <v>332022484.94</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.3738082799669966</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1225003004.92</v>
+        <v>1225003126.96</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>197998279.3</v>
@@ -3005,10 +3005,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1582883106.99</v>
+        <v>1582883229.03</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236971328.93</v>
+        <v>236971411.89</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>51757451.41</v>
@@ -3020,16 +3020,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5234052.76</v>
+        <v>5234053.66</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6970351.28</v>
+        <v>6970352.49</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>339787839.87</v>
+        <v>339787924.95</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3916156197964661</v>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1838947578.71</v>
+        <v>1838947682.27</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>306596831.13</v>
@@ -3063,10 +3063,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2463854068.74</v>
+        <v>2463854172.3</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>385266939.01</v>
+        <v>385266999.73</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>76961502.72</v>
@@ -3078,16 +3078,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>10618329.66</v>
+        <v>10618330.41</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>18123252.92</v>
+        <v>18123254.19</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>558868723.16</v>
+        <v>558868785.9</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0.40067966485108</v>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1909112664.27</v>
+        <v>1909115698.74</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>376107142.6</v>
@@ -3121,10 +3121,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2709632112.56</v>
+        <v>2709635147.03</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>383261020.27</v>
+        <v>383262693.26</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>102191529.21</v>
@@ -3136,16 +3136,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>12009472.88</v>
+        <v>12009493.78</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>22111576.55</v>
+        <v>22111615.04</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>605653590.99</v>
+        <v>605655323.37</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0.442865215754716</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1124143180.65</v>
+        <v>1124147053.36</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>250093696.52</v>
@@ -3179,10 +3179,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1555761393.18</v>
+        <v>1555765265.89</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>215628916.24</v>
+        <v>215630898.39</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>65852392.81</v>
@@ -3194,16 +3194,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>3871568.33</v>
+        <v>3871581.84</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>5476425.82</v>
+        <v>5476444.93</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>336987234.67</v>
+        <v>336989249.44</v>
       </c>
       <c r="R47" s="10" t="n">
         <v>0.4207679702437824</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1314078145.15</v>
+        <v>1314110266.85</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>251713084.28</v>
@@ -3237,10 +3237,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>1712400513.69</v>
+        <v>1712432635.39</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>241884601.49</v>
+        <v>241897253.56</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>62840730.8</v>
@@ -3252,16 +3252,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>4581033.12</v>
+        <v>4581115.83</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>5974130.38</v>
+        <v>5974238.24</v>
       </c>
       <c r="P48" s="9" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>348862618.34</v>
+        <v>348875460.98</v>
       </c>
       <c r="R48" s="10" t="n">
         <v>0.4544083188194561</v>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>1150729376.45</v>
+        <v>1150894320.85</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>255216837.43</v>
@@ -3295,10 +3295,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>1571082212.28</v>
+        <v>1571247156.68</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>231539145.94</v>
+        <v>231566024.53</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>63158844.13</v>
@@ -3310,16 +3310,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="9" t="n">
-        <v>5794011.54</v>
+        <v>5793850.05</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>6695994.05</v>
+        <v>6695807.42</v>
       </c>
       <c r="P49" s="9" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>344043467.84</v>
+        <v>344069998.32</v>
       </c>
       <c r="R49" s="10" t="n">
         <v>0.4715622688002217</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>1577902692</v>
+        <v>1578122506.62</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>259850875.34</v>
@@ -6009,10 +6009,10 @@
         <v>41032470</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>2019804491.74</v>
+        <v>2020024306.36</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>438025787.3</v>
+        <v>438086807.84</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>63886790.88</v>
@@ -6024,16 +6024,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="9" t="n">
-        <v>7315927.02</v>
+        <v>7315930.27</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>9682553.630000001</v>
+        <v>9682557.93</v>
       </c>
       <c r="P49" s="9" t="n">
         <v>16498863.67</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>558487873.5700001</v>
+        <v>558548901.66</v>
       </c>
     </row>
   </sheetData>
@@ -8122,7 +8122,7 @@
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>759854820.36</v>
+        <v>759960674.29</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>19750670.59</v>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R49"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226361202.05</v>
+        <v>1226361286.41</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404323296.63</v>
+        <v>1404323380.99</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290715479.81</v>
+        <v>290715483.33</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524812.17</v>
+        <v>524812.15</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360273.32</v>
+        <v>9360272.84</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354058471.94</v>
+        <v>354058474.95</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019800301.13</v>
+        <v>1019800397.83</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203205210.64</v>
+        <v>1203205307.34</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223747449.53</v>
+        <v>223747452.41</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516297.6</v>
+        <v>516297.56</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237366.76</v>
+        <v>9237366.09</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289059219.67</v>
+        <v>289059221.84</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983766057.36</v>
+        <v>983766605.46</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168404206.38</v>
+        <v>1168404754.48</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236065063.82</v>
+        <v>236065194.2</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324588.38</v>
+        <v>324588.36</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358539.26</v>
+        <v>7358538.93</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305861776.02</v>
+        <v>305861906.07</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097589837.49</v>
+        <v>1097590133.51</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302669875.07</v>
+        <v>1302670171.09</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250951565.99</v>
+        <v>250951602.12</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709928</v>
+        <v>709927.92</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693362.48</v>
+        <v>7693361.56</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328055587.73</v>
+        <v>328055622.85</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011526531.04</v>
+        <v>1011526681.38</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233699650.55</v>
+        <v>1233699800.89</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229526189.22</v>
+        <v>229526214.82</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255744.03</v>
+        <v>1255743.98</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409733.33</v>
+        <v>8409732.99</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309201123.24</v>
+        <v>309201148.45</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961945781.22</v>
+        <v>961945829.2</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145552942.76</v>
+        <v>1145552990.74</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214890823.29</v>
+        <v>214890834.1</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814776.79</v>
+        <v>814776.78</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850529.76</v>
+        <v>6850529.74</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281207975.04</v>
+        <v>281207985.82</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073050679.76</v>
+        <v>1073051985.38</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277716577.24</v>
+        <v>1277717882.86</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240126421.12</v>
+        <v>240126644.66</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353402.03</v>
+        <v>2353401.28</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569921.64</v>
+        <v>7569919.22</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313750222.67</v>
+        <v>313750443.04</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960778751.6799999</v>
+        <v>960779142.62</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185452068.8</v>
+        <v>1185452459.74</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212552827.69</v>
+        <v>212552851.15</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490172.06</v>
+        <v>2490171.41</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929356.77</v>
+        <v>8929354.439999999</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296187697.22</v>
+        <v>296187717.7</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686513890.54</v>
+        <v>686516097.26</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813425581.5700001</v>
+        <v>813427788.29</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150993262.61</v>
+        <v>150993325.39</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897063.28</v>
+        <v>1897058.61</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485524.89</v>
+        <v>3485516.31</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196257810.67</v>
+        <v>196257860.21</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970916067.75</v>
+        <v>970916426.08</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130472721.99</v>
+        <v>1130473080.32</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227542471.23</v>
+        <v>227542508.37</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642022.03</v>
+        <v>2642021.52</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513113.14</v>
+        <v>5513112.08</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286540154.85</v>
+        <v>286540190.42</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042731983.92</v>
+        <v>1042732051.7</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244216173.99</v>
+        <v>1244216241.77</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230883889.47</v>
+        <v>230883898.89</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865669.5</v>
+        <v>2865669.43</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026081.65</v>
+        <v>7026081.48</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305688712.06</v>
+        <v>305688721.24</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046532977.02</v>
+        <v>1046532992.82</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268580076.83</v>
+        <v>1268580092.63</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238383739.88</v>
+        <v>238383745.94</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737712.83</v>
+        <v>3737712.85</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838302.88</v>
+        <v>7838302.93</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315850492.39</v>
+        <v>315850498.53</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026532112.91</v>
+        <v>1026532453.28</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228675991.94</v>
+        <v>1228676332.31</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246157204.12</v>
+        <v>246157208.92</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558664.02</v>
+        <v>3558663.05</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537355.48</v>
+        <v>7537353.43</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315577277.78</v>
+        <v>315577279.56</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275236351.52</v>
+        <v>1275236722.43</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517957828.77</v>
+        <v>1517958199.68</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295677142.35</v>
+        <v>295677166.01</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271137.47</v>
+        <v>4271136.66</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581194.119999999</v>
+        <v>9581192.32</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378773469.82</v>
+        <v>378773490.87</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123212464.54</v>
+        <v>1123212874.34</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375387625.87</v>
+        <v>1375388035.67</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251892628.12</v>
+        <v>251892775.73</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520553.01</v>
+        <v>3520553.51</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255926.4</v>
+        <v>11255927.98</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341112064.37</v>
+        <v>341112214.06</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780515433.72</v>
+        <v>780515840.5700001</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941932279.25</v>
+        <v>941932686.1</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182890983.85</v>
+        <v>182891069.68</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893249.03</v>
+        <v>2893248.81</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978989.97</v>
+        <v>4978989.59</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240375065.78</v>
+        <v>240375151.01</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925224978.41</v>
+        <v>925225147.36</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103228362.23</v>
+        <v>1103228531.18</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208940039.41</v>
+        <v>208940053.19</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099146.39</v>
+        <v>3099146.07</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218666.14</v>
+        <v>6218665.48</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270758361.95</v>
+        <v>270758374.75</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099264329.12</v>
+        <v>1099264442.48</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314564622.94</v>
+        <v>1314564736.3</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244622811.65</v>
+        <v>244622866.65</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671186.62</v>
+        <v>3671186.95</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710545.63</v>
+        <v>7710546.32</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319476964.6</v>
+        <v>319477020.62</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967598832.75</v>
+        <v>967599002.9299999</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190919838.33</v>
+        <v>1190920008.51</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210535004.55</v>
+        <v>210535020.24</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281804.64</v>
+        <v>3281804.34</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536311.02</v>
+        <v>7536310.33</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283818000.87</v>
+        <v>283818015.58</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003085647.23</v>
+        <v>1003086076.85</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198242335.29</v>
+        <v>1198242764.91</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222089155.67</v>
+        <v>222089315.43</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891027.98</v>
+        <v>3891028.83</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335918.6</v>
+        <v>6335919.98</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281020597.18</v>
+        <v>281020759.17</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362287973.66</v>
+        <v>1362288068.93</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634504728.78</v>
+        <v>1634504824.05</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306763194.65</v>
+        <v>306763227.44</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136472.65</v>
+        <v>6136472.81</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270566.19</v>
+        <v>10270566.48</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388022364.99</v>
+        <v>388022398.23</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156899086.48</v>
+        <v>1156899913.39</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409399054.13</v>
+        <v>1409399881.04</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247798463.68</v>
+        <v>247798550.16</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795232.01</v>
+        <v>3795230.74</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929381.710000001</v>
+        <v>9929378.380000001</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325996302.19</v>
+        <v>325996384.06</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870301252.36</v>
+        <v>870304736.7</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039405464.73</v>
+        <v>1039408949.07</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193433237.04</v>
+        <v>193434388.2</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256062.08</v>
+        <v>3256066.61</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684203.58</v>
+        <v>5684211.49</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245275314.32</v>
+        <v>245276477.93</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002266289.35</v>
+        <v>1002267138.13</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209603697.31</v>
+        <v>1209604546.09</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>217000821.37</v>
+        <v>217000890.17</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934141.75</v>
+        <v>2934140.36</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937706.92</v>
+        <v>6937703.63</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280973075.12</v>
+        <v>280973139.25</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105965582.72</v>
+        <v>1105965673.43</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351820482.37</v>
+        <v>1351820573.08</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242484578.37</v>
+        <v>242484602.24</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693259.92</v>
+        <v>2693259.94</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764079.119999999</v>
+        <v>8764079.18</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322798396.4</v>
+        <v>322798420.36</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932845545.6</v>
+        <v>932846956.12</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136793360.05</v>
+        <v>1136794770.57</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196525045.73</v>
+        <v>196525450.14</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927931.01</v>
+        <v>2927931.97</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577854.62</v>
+        <v>6577856.79</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259479172.72</v>
+        <v>259479580.27</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1162031947.44</v>
+        <v>1162032014.24</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354868431.51</v>
+        <v>1354868498.31</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252352892.94</v>
+        <v>252352898.42</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229199.03</v>
+        <v>4229198.89</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541685.65</v>
+        <v>4541685.5</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311965496.25</v>
+        <v>311965501.45</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1440006133.02</v>
+        <v>1440007101.82</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740062799.05</v>
+        <v>1740063767.85</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284719171.81</v>
+        <v>284719196.1</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067084.7</v>
+        <v>4067082.65</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978507.56</v>
+        <v>5978504.53</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375589952.93</v>
+        <v>375589972.14</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319733641.59</v>
+        <v>1319734175.49</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579496725.71</v>
+        <v>1579497259.61</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283378656.52</v>
+        <v>283378786.58</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050966.99</v>
+        <v>3050967.05</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438409.5</v>
+        <v>7438409.65</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363619397.52</v>
+        <v>363619527.8</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1097004798.58</v>
+        <v>1097007033.25</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283045824.69</v>
+        <v>1283048059.36</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243428480.75</v>
+        <v>243429907.31</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660625.59</v>
+        <v>1660630.69</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202045.57</v>
+        <v>7202067.68</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302146043.44</v>
+        <v>302147497.21</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142131013.09</v>
+        <v>1142131505.18</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1366022127.04</v>
+        <v>1366022619.13</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239661198.66</v>
+        <v>239661255.76</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298509.1</v>
+        <v>1298508.87</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234269.1</v>
+        <v>9234267.439999999</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307454351.61</v>
+        <v>307454406.81</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192853919.21</v>
+        <v>1192854224.87</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436510925.88</v>
+        <v>1436511231.54</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253632137.79</v>
+        <v>253632162.07</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145315.34</v>
+        <v>2145315.03</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745133.9</v>
+        <v>6745132.94</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327986989.23</v>
+        <v>327987012.24</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226941524.28</v>
+        <v>1226943485.4</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494281815.15</v>
+        <v>1494283776.27</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272959013.67</v>
+        <v>272959752.5</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511838.05</v>
+        <v>2511839.94</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248296.03</v>
+        <v>7248301.49</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361201232.43</v>
+        <v>361201978.62</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348627859.36</v>
+        <v>1348632008.53</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622948004.11</v>
+        <v>1622952153.28</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278437422.56</v>
+        <v>278439475.05</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307527.38</v>
+        <v>2307534.79</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088498.15</v>
+        <v>8088524.1</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361824354.88</v>
+        <v>361826440.72</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778318762.6</v>
+        <v>1778319146.33</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122381824.66</v>
+        <v>2122382208.39</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364514014.12</v>
+        <v>364514274.57</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3919085.83</v>
+        <v>3919087.35</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6647149.18</v>
+        <v>6647151.76</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465533016.9</v>
+        <v>465533281.44</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364413044.73</v>
+        <v>1364415836.23</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1651182831.33</v>
+        <v>1651185622.83</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283721727.8</v>
+        <v>283722809.18</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4917233.07</v>
+        <v>4917239.15</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7352651.97</v>
+        <v>7352661.06</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374619402.52</v>
+        <v>374620499.07</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1038064307.51</v>
+        <v>1038066873.03</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347441024.3</v>
+        <v>1347443589.82</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218485208.6</v>
+        <v>218485567.01</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3629095.07</v>
+        <v>3629092.19</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4592088.37</v>
+        <v>4592084.73</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316834965.52</v>
+        <v>316835317.41</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143685308.46</v>
+        <v>1143687896.68</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1422167728.07</v>
+        <v>1422170316.29</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228258058.42</v>
+        <v>228258619.89</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3388653.47</v>
+        <v>3388653.36</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5521922.03</v>
+        <v>5521921.85</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>314041819.11</v>
+        <v>314042380.28</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339517739.91</v>
+        <v>1339518909.07</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1715091645.51</v>
+        <v>1715092814.67</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269966858.79</v>
+        <v>269967116.7</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2886717.72</v>
+        <v>2886717.66</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7560668.49</v>
+        <v>7560668.33</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389859714.35</v>
+        <v>389859972.04</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1172377140.96</v>
+        <v>1172384024.99</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>221857126.57</v>
@@ -2947,10 +2947,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1562162132.02</v>
+        <v>1562169016.05</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>220136983.53</v>
+        <v>220138985.88</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>61180264.16</v>
@@ -2962,16 +2962,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2632909.58</v>
+        <v>2632913.98</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>7180675.7</v>
+        <v>7180687.71</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>332022484.94</v>
+        <v>332024503.71</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.3738082799669966</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1225003126.96</v>
+        <v>1225007751.11</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>197998279.3</v>
@@ -3005,10 +3005,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1582883229.03</v>
+        <v>1582887853.18</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236971411.89</v>
+        <v>236972756.23</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>51757451.41</v>
@@ -3020,16 +3020,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5234053.66</v>
+        <v>5234059.28</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6970352.49</v>
+        <v>6970359.97</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>339787924.95</v>
+        <v>339789282.39</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3916156197964661</v>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1838947682.27</v>
+        <v>1838959017.31</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>306596831.13</v>
@@ -3063,10 +3063,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2463854172.3</v>
+        <v>2463865507.34</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>385266999.73</v>
+        <v>385271090.36</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>76961502.72</v>
@@ -3078,16 +3078,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>10618330.41</v>
+        <v>10618360.84</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>18123254.19</v>
+        <v>18123306.14</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>558868785.9</v>
+        <v>558872958.91</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0.40067966485108</v>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1909115698.74</v>
+        <v>1909174759.78</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>376107142.6</v>
@@ -3121,10 +3121,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2709635147.03</v>
+        <v>2709694208.07</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>383262693.26</v>
+        <v>383288390.08</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>102191529.21</v>
@@ -3136,16 +3136,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>12009493.78</v>
+        <v>12009756.34</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>22111615.04</v>
+        <v>22112098.45</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>605655323.37</v>
+        <v>605681766.17</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0.442865215754716</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1124147053.36</v>
+        <v>1124247076.61</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>250093696.52</v>
@@ -3179,10 +3179,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1555765265.89</v>
+        <v>1555865289.14</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>215630898.39</v>
+        <v>215669229.15</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>65852392.81</v>
@@ -3194,16 +3194,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>3871581.84</v>
+        <v>3871778.75</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>5476444.93</v>
+        <v>5476723.46</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>336989249.44</v>
+        <v>337028055.65</v>
       </c>
       <c r="R47" s="10" t="n">
         <v>0.4207679702437824</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1314110266.85</v>
+        <v>1314367145.5</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>251713084.28</v>
@@ -3237,10 +3237,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>1712432635.39</v>
+        <v>1712689514.04</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>241897253.56</v>
+        <v>241979716.87</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>62840730.8</v>
@@ -3252,16 +3252,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>4581115.83</v>
+        <v>4581523.74</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>5974238.24</v>
+        <v>5974770.2</v>
       </c>
       <c r="P48" s="9" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>348875460.98</v>
+        <v>348958864.15</v>
       </c>
       <c r="R48" s="10" t="n">
         <v>0.4544083188194561</v>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>1150894320.85</v>
+        <v>1344943762.63</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>255216837.43</v>
@@ -3295,10 +3295,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>1571247156.68</v>
+        <v>1765296598.46</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>231566024.53</v>
+        <v>244098680.13</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>63158844.13</v>
@@ -3310,23 +3310,81 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="9" t="n">
-        <v>5793850.05</v>
+        <v>5329811.8</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>6695807.42</v>
+        <v>6159530.04</v>
       </c>
       <c r="P49" s="9" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>344069998.32</v>
+        <v>355602338.29</v>
       </c>
       <c r="R49" s="10" t="n">
         <v>0.4715622688002217</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>1325602926.64</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>251070477.59</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>44562231.25</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>71999654</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>24458718.91</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>31258725</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>26540371</v>
+      </c>
+      <c r="I50" s="7" t="n">
+        <v>1775493104.39</v>
+      </c>
+      <c r="J50" s="8" t="n">
+        <v>253943234.4</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>57612870.57</v>
+      </c>
+      <c r="L50" s="9" t="n">
+        <v>15178066.62</v>
+      </c>
+      <c r="M50" s="9" t="n">
+        <v>15892369.91</v>
+      </c>
+      <c r="N50" s="9" t="n">
+        <v>5059992.2</v>
+      </c>
+      <c r="O50" s="9" t="n">
+        <v>6466769.8</v>
+      </c>
+      <c r="P50" s="9" t="n">
+        <v>13158708.92</v>
+      </c>
+      <c r="Q50" s="9" t="n">
+        <v>367312012.42</v>
+      </c>
+      <c r="R50" s="10" t="n">
+        <v>0.5184969295746537</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R49"/>
+  <autoFilter ref="A2:R50"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3342,7 +3400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5988,7 +6046,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>1578122506.62</v>
+        <v>1980000000</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>259850875.34</v>
@@ -6009,10 +6067,10 @@
         <v>41032470</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>2020024306.36</v>
+        <v>2421901799.74</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>438086807.84</v>
+        <v>549648000</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>63886790.88</v>
@@ -6024,20 +6082,75 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="9" t="n">
-        <v>7315930.27</v>
+        <v>7320858.3</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>9682557.93</v>
+        <v>9689080.130000001</v>
       </c>
       <c r="P49" s="9" t="n">
         <v>16498863.67</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>558548901.66</v>
+        <v>670121544.05</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>1842530628.67</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>252909291.06</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>44562231.25</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>71999654</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>24458718.91</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>34522114</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>27100498</v>
+      </c>
+      <c r="I50" s="7" t="n">
+        <v>2298083135.89</v>
+      </c>
+      <c r="J50" s="8" t="n">
+        <v>511486502.52</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>57936471.2</v>
+      </c>
+      <c r="L50" s="9" t="n">
+        <v>15178066.62</v>
+      </c>
+      <c r="M50" s="9" t="n">
+        <v>15892369.91</v>
+      </c>
+      <c r="N50" s="9" t="n">
+        <v>6705612.83</v>
+      </c>
+      <c r="O50" s="9" t="n">
+        <v>9464597.529999999</v>
+      </c>
+      <c r="P50" s="9" t="n">
+        <v>13379834.23</v>
+      </c>
+      <c r="Q50" s="9" t="n">
+        <v>630043454.84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q49"/>
+  <autoFilter ref="A2:Q50"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -6052,7 +6165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8097,7 +8210,7 @@
         <v>13207850</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>0.6999</v>
+        <v>0.6998000000000001</v>
       </c>
       <c r="I48" s="11" t="n">
         <v>0.4791</v>
@@ -8122,7 +8235,7 @@
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>759960674.29</v>
+        <v>953488800</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>19750670.59</v>
@@ -8140,7 +8253,7 @@
         <v>11477871</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>0.6603</v>
+        <v>0.7089</v>
       </c>
       <c r="I49" s="11" t="n">
         <v>0.4597</v>
@@ -8158,15 +8271,58 @@
         <v>0.3754</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>887289049.54</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>19265583.23</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>47330737</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>118706812.51</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>21476298.84</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>12724485</v>
+      </c>
+      <c r="H50" s="11" t="n">
+        <v>0.6693000000000001</v>
+      </c>
+      <c r="I50" s="11" t="n">
+        <v>0.4323</v>
+      </c>
+      <c r="J50" s="11" t="n">
+        <v>0.6574</v>
+      </c>
+      <c r="K50" s="11" t="n">
+        <v>0.4728</v>
+      </c>
+      <c r="L50" s="11" t="n">
+        <v>0.8781</v>
+      </c>
+      <c r="M50" s="11" t="n">
+        <v>0.4071</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M49"/>
+  <autoFilter ref="A2:M50"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -8197,7 +8353,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-17. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-18. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R50"/>
+  <dimension ref="A1:R51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226361286.41</v>
+        <v>1226361361.59</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404323380.99</v>
+        <v>1404323456.17</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290715483.33</v>
+        <v>290715489.49</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524812.15</v>
+        <v>524812.13</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360272.84</v>
+        <v>9360272.49</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354058474.95</v>
+        <v>354058480.74</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019800397.83</v>
+        <v>1019800417.03</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203205307.34</v>
+        <v>1203205326.54</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223747452.41</v>
+        <v>223747458.12</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -707,13 +707,13 @@
         <v>516297.56</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237366.09</v>
+        <v>9237366.130000001</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289059221.84</v>
+        <v>289059227.59</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766410037.92</v>
+        <v>766410062.92</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882452584.96</v>
+        <v>882452609.96</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197402935.5</v>
+        <v>197402955.5</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374709.51</v>
+        <v>374709.53</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399346.38</v>
+        <v>5399346.69</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239492273.77</v>
+        <v>239492294.1</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983766605.46</v>
+        <v>983766621.12</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168404754.48</v>
+        <v>1168404770.14</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236065194.2</v>
+        <v>236065195.61</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -819,13 +819,13 @@
         <v>324588.36</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358538.93</v>
+        <v>7358538.87</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305861906.07</v>
+        <v>305861907.41</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097590133.51</v>
+        <v>1097590429.48</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302670171.09</v>
+        <v>1302670467.06</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250951602.12</v>
+        <v>250951625.59</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.92</v>
+        <v>709927.8</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693361.56</v>
+        <v>7693360.33</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328055622.85</v>
+        <v>328055644.98</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011526681.38</v>
+        <v>1011526789.07</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233699800.89</v>
+        <v>1233699908.58</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229526214.82</v>
+        <v>229526225.17</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255743.98</v>
+        <v>1255743.91</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409732.99</v>
+        <v>8409732.52</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309201148.45</v>
+        <v>309201158.26</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961945829.2</v>
+        <v>961947373.95</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145552990.74</v>
+        <v>1145554535.49</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214890834.1</v>
+        <v>214890843.72</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814776.78</v>
+        <v>814775.6800000001</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850529.74</v>
+        <v>6850520.48</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281207985.82</v>
+        <v>281207985.08</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073051985.38</v>
+        <v>1073052219.33</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277717882.86</v>
+        <v>1277718116.81</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240126644.66</v>
+        <v>240126649.34</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353401.28</v>
+        <v>2353400.87</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569919.22</v>
+        <v>7569917.91</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313750443.04</v>
+        <v>313750446</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960779142.62</v>
+        <v>960779558.38</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185452459.74</v>
+        <v>1185452875.5</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212552851.15</v>
+        <v>212552905.07</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490171.41</v>
+        <v>2490170.97</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929354.439999999</v>
+        <v>8929352.869999999</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296187717.7</v>
+        <v>296187769.62</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686516097.26</v>
+        <v>686516217.7</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813427788.29</v>
+        <v>813427908.73</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150993325.39</v>
+        <v>150993346.73</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897058.61</v>
+        <v>1897058.53</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485516.31</v>
+        <v>3485516.17</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196257860.21</v>
+        <v>196257881.33</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970916426.08</v>
+        <v>970916426.38</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130473080.32</v>
+        <v>1130473080.62</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227542508.37</v>
+        <v>227542508.38</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1225,13 +1225,13 @@
         <v>2642021.52</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513112.08</v>
+        <v>5513112.07</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286540190.42</v>
+        <v>286540190.43</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042732051.7</v>
+        <v>1042732210.82</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244216241.77</v>
+        <v>1244216400.89</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230883898.89</v>
+        <v>230883912.67</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865669.43</v>
+        <v>2865669.18</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026081.48</v>
+        <v>7026080.88</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305688721.24</v>
+        <v>305688734.17</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026532453.28</v>
+        <v>1026532454.28</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228676332.31</v>
+        <v>1228676333.31</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246157208.92</v>
+        <v>246157209.01</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1405,7 +1405,7 @@
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315577279.56</v>
+        <v>315577279.65</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275236722.43</v>
+        <v>1275236798.85</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517958199.68</v>
+        <v>1517958276.1</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295677166.01</v>
+        <v>295677177.95</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271136.66</v>
+        <v>4271136.58</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581192.32</v>
+        <v>9581192.130000001</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378773490.87</v>
+        <v>378773502.54</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123212874.34</v>
+        <v>1123212960.99</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375388035.67</v>
+        <v>1375388122.32</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251892775.73</v>
+        <v>251892783.87</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520553.51</v>
+        <v>3520553.36</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255927.98</v>
+        <v>11255927.52</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341112214.06</v>
+        <v>341112221.6</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780515840.5700001</v>
+        <v>780515856.3099999</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941932686.1</v>
+        <v>941932701.84</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182891069.68</v>
+        <v>182891071.74</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893248.81</v>
+        <v>2893248.78</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978989.59</v>
+        <v>4978989.55</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240375151.01</v>
+        <v>240375153</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925225147.36</v>
+        <v>925227082.46</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103228531.18</v>
+        <v>1103230466.28</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208940053.19</v>
+        <v>208940208.45</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099146.07</v>
+        <v>3099142.28</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218665.48</v>
+        <v>6218657.88</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270758374.75</v>
+        <v>270758518.61</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099264442.48</v>
+        <v>1099264869.6</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314564736.3</v>
+        <v>1314565163.42</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244622866.65</v>
+        <v>244622983.14</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671186.95</v>
+        <v>3671187.1</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710546.32</v>
+        <v>7710546.64</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319477020.62</v>
+        <v>319477137.58</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003086076.85</v>
+        <v>1003088411.85</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198242764.91</v>
+        <v>1198245099.91</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222089315.43</v>
+        <v>222089386.28</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891028.83</v>
+        <v>3891021.98</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335919.98</v>
+        <v>6335908.82</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281020759.17</v>
+        <v>281020812.01</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362288068.93</v>
+        <v>1362288369.79</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634504824.05</v>
+        <v>1634505124.91</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306763227.44</v>
+        <v>306763242.84</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136472.81</v>
+        <v>6136471.89</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270566.48</v>
+        <v>10270564.93</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388022398.23</v>
+        <v>388022411.16</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156899913.39</v>
+        <v>1156900459.4</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409399881.04</v>
+        <v>1409400427.05</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247798550.16</v>
+        <v>247798688.58</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795230.74</v>
+        <v>3795230.89</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929378.380000001</v>
+        <v>9929378.76</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325996384.06</v>
+        <v>325996523.01</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870304736.7</v>
+        <v>870304995.8200001</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039408949.07</v>
+        <v>1039409208.19</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193434388.2</v>
+        <v>193434393.29</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256066.61</v>
+        <v>3256065.84</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684211.49</v>
+        <v>5684210.14</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245276477.93</v>
+        <v>245276480.9</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002267138.13</v>
+        <v>1002268060.31</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209604546.09</v>
+        <v>1209605468.27</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>217000890.17</v>
+        <v>217001324.82</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934140.36</v>
+        <v>2934142.75</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937703.63</v>
+        <v>6937709.27</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280973139.25</v>
+        <v>280973581.92</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105965673.43</v>
+        <v>1105965796.43</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351820573.08</v>
+        <v>1351820696.08</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242484602.24</v>
+        <v>242484611.48</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693259.94</v>
+        <v>2693259.76</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764079.18</v>
+        <v>8764078.609999999</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322798420.36</v>
+        <v>322798428.85</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932846956.12</v>
+        <v>932847385.12</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136794770.57</v>
+        <v>1136795199.57</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196525450.14</v>
+        <v>196525553.93</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927931.97</v>
+        <v>2927932.04</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577856.79</v>
+        <v>6577856.95</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259479580.27</v>
+        <v>259479684.28</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1162032014.24</v>
+        <v>1162033775.24</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354868498.31</v>
+        <v>1354870259.31</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252352898.42</v>
+        <v>252354163.96</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229198.89</v>
+        <v>4229210.89</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541685.5</v>
+        <v>4541698.39</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311965501.45</v>
+        <v>311966791.87</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1440007101.82</v>
+        <v>1440007324.71</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740063767.85</v>
+        <v>1740063990.74</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284719196.1</v>
+        <v>284719235.36</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067082.65</v>
+        <v>4067082.55</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978504.53</v>
+        <v>5978504.39</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375589972.14</v>
+        <v>375590011.16</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319734175.49</v>
+        <v>1319734351.44</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579497259.61</v>
+        <v>1579497435.56</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283378786.58</v>
+        <v>283378872.08</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050967.05</v>
+        <v>3050967.44</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438409.65</v>
+        <v>7438410.59</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363619527.8</v>
+        <v>363619614.63</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1097007033.25</v>
+        <v>1097008099.39</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283048059.36</v>
+        <v>1283049125.5</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243429907.31</v>
+        <v>243430189.26</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660630.69</v>
+        <v>1660630.86</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202067.68</v>
+        <v>7202068.44</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302147497.21</v>
+        <v>302147780.09</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142131505.18</v>
+        <v>1142134127.09</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1366022619.13</v>
+        <v>1366025241.04</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239661255.76</v>
+        <v>239661807.03</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298508.87</v>
+        <v>1298508.7</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234267.439999999</v>
+        <v>9234266.23</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307454406.81</v>
+        <v>307454956.7</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192854224.87</v>
+        <v>1192856964.33</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436511231.54</v>
+        <v>1436513971</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253632162.07</v>
+        <v>253632520.95</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145315.03</v>
+        <v>2145313.24</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745132.94</v>
+        <v>6745127.3</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327987012.24</v>
+        <v>327987363.69</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226943485.4</v>
+        <v>1226943703.82</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494283776.27</v>
+        <v>1494283994.69</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272959752.5</v>
+        <v>272959812.74</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511839.94</v>
+        <v>2511840</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248301.49</v>
+        <v>7248301.65</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361201978.62</v>
+        <v>361202039.06</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348632008.53</v>
+        <v>1348634076.65</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622952153.28</v>
+        <v>1622954221.4</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278439475.05</v>
+        <v>278440833.28</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307534.79</v>
+        <v>2307540.68</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088524.1</v>
+        <v>8088544.75</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361826440.72</v>
+        <v>361827825.49</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778319146.33</v>
+        <v>1778319461.25</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122382208.39</v>
+        <v>2122382523.31</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364514274.57</v>
+        <v>364514398.01</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3919087.35</v>
+        <v>3919087.82</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6647151.76</v>
+        <v>6647152.55</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465533281.44</v>
+        <v>465533406.15</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364415836.23</v>
+        <v>1364417508.01</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1651185622.83</v>
+        <v>1651187294.61</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283722809.18</v>
+        <v>283723611.11</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4917239.15</v>
+        <v>4917244.89</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7352661.06</v>
+        <v>7352669.63</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374620499.07</v>
+        <v>374621315.31</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1038066873.03</v>
+        <v>1038070764.43</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347443589.82</v>
+        <v>1347447481.22</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218485567.01</v>
+        <v>218487299.15</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3629092.19</v>
+        <v>3629101.8</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4592084.73</v>
+        <v>4592096.89</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316835317.41</v>
+        <v>316837071.31</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143687896.68</v>
+        <v>1143689056.49</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1422170316.29</v>
+        <v>1422171476.1</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228258619.89</v>
+        <v>228258981.11</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3388653.36</v>
+        <v>3388654.53</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5521921.85</v>
+        <v>5521923.75</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>314042380.28</v>
+        <v>314042744.57</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339518909.07</v>
+        <v>1339522336.6</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1715092814.67</v>
+        <v>1715096242.2</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269967116.7</v>
+        <v>269967942.62</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2886717.66</v>
+        <v>2886718.02</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7560668.33</v>
+        <v>7560669.26</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389859972.04</v>
+        <v>389860799.25</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1172384024.99</v>
+        <v>1172389750.41</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>221857126.57</v>
@@ -2947,10 +2947,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1562169016.05</v>
+        <v>1562174741.47</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>220138985.88</v>
+        <v>220141553.61</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>61180264.16</v>
@@ -2962,16 +2962,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2632913.98</v>
+        <v>2632925.02</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>7180687.71</v>
+        <v>7180717.82</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>332024503.71</v>
+        <v>332027112.59</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.3738082799669966</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1225007751.11</v>
+        <v>1225009287.23</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>197998279.3</v>
@@ -3005,10 +3005,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1582887853.18</v>
+        <v>1582889389.3</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236972756.23</v>
+        <v>236973511.27</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>51757451.41</v>
@@ -3020,16 +3020,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5234059.28</v>
+        <v>5234066.08</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6970359.97</v>
+        <v>6970369.02</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>339789282.39</v>
+        <v>339790053.28</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3916156197964661</v>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1838959017.31</v>
+        <v>1838969760.7</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>306596831.13</v>
@@ -3063,10 +3063,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2463865507.34</v>
+        <v>2463876250.73</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>385271090.36</v>
+        <v>385274722.94</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>76961502.72</v>
@@ -3078,16 +3078,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>10618360.84</v>
+        <v>10618384.79</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>18123306.14</v>
+        <v>18123347.01</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>558872958.91</v>
+        <v>558876656.3099999</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0.40067966485108</v>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1909174759.78</v>
+        <v>1909254403.96</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>376107142.6</v>
@@ -3121,10 +3121,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2709694208.07</v>
+        <v>2709773852.25</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>383288390.08</v>
+        <v>383325382.69</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>102191529.21</v>
@@ -3136,16 +3136,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>12009756.34</v>
+        <v>12010159.56</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>22112098.45</v>
+        <v>22112840.85</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>605681766.17</v>
+        <v>605719904.39</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0.442865215754716</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1124247076.61</v>
+        <v>1124404374.41</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>250093696.52</v>
@@ -3179,10 +3179,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1555865289.14</v>
+        <v>1556022586.94</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>215669229.15</v>
+        <v>215735664.13</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>65852392.81</v>
@@ -3194,16 +3194,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>3871778.75</v>
+        <v>3872161.08</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>5476723.46</v>
+        <v>5477264.28</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>337028055.65</v>
+        <v>337095413.79</v>
       </c>
       <c r="R47" s="10" t="n">
         <v>0.4207679702437824</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1314367145.5</v>
+        <v>1314573734.66</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>251713084.28</v>
@@ -3237,10 +3237,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>1712689514.04</v>
+        <v>1712896103.2</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>241979716.87</v>
+        <v>242069447.35</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>62840730.8</v>
@@ -3252,16 +3252,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>4581523.74</v>
+        <v>4582168.61</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>5974770.2</v>
+        <v>5975611.18</v>
       </c>
       <c r="P48" s="9" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>348958864.15</v>
+        <v>349050080.49</v>
       </c>
       <c r="R48" s="10" t="n">
         <v>0.4544083188194561</v>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>1344943762.63</v>
+        <v>1345241260</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>255216837.43</v>
@@ -3295,10 +3295,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>1765296598.46</v>
+        <v>1765594095.83</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>244098680.13</v>
+        <v>244216134.89</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>63158844.13</v>
@@ -3310,16 +3310,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="9" t="n">
-        <v>5329811.8</v>
+        <v>5330702.65</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>6159530.04</v>
+        <v>6160559.57</v>
       </c>
       <c r="P49" s="9" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>355602338.29</v>
+        <v>355721713.44</v>
       </c>
       <c r="R49" s="10" t="n">
         <v>0.4715622688002217</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>1325602926.64</v>
+        <v>1271985227.8</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>251070477.59</v>
@@ -3353,10 +3353,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>1775493104.39</v>
+        <v>1721875405.55</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>253943234.4</v>
+        <v>250698050.06</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>57612870.57</v>
@@ -3368,23 +3368,81 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="9" t="n">
-        <v>5059992.2</v>
+        <v>5175186.61</v>
       </c>
       <c r="O50" s="9" t="n">
-        <v>6466769.8</v>
+        <v>6613990.53</v>
       </c>
       <c r="P50" s="9" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>367312012.42</v>
+        <v>364329243.22</v>
       </c>
       <c r="R50" s="10" t="n">
         <v>0.5184969295746537</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>1249115214.35</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>287468135.92</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>50305076.95</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>64394233</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>29700967.56</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>42402181</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>28011807</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>1751397615.78</v>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>242595529.2</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>59780017.61</v>
+      </c>
+      <c r="L51" s="9" t="n">
+        <v>13607705.7</v>
+      </c>
+      <c r="M51" s="9" t="n">
+        <v>13923546.06</v>
+      </c>
+      <c r="N51" s="9" t="n">
+        <v>6081989.33</v>
+      </c>
+      <c r="O51" s="9" t="n">
+        <v>8682869.07</v>
+      </c>
+      <c r="P51" s="9" t="n">
+        <v>13969238.87</v>
+      </c>
+      <c r="Q51" s="9" t="n">
+        <v>358640895.84</v>
+      </c>
+      <c r="R51" s="10" t="n">
+        <v>0.5173698555705437</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R50"/>
+  <autoFilter ref="A2:R51"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3400,7 +3458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6101,7 +6159,7 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>1842530628.67</v>
+        <v>1730000000</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>252909291.06</v>
@@ -6122,10 +6180,10 @@
         <v>27100498</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>2298083135.89</v>
+        <v>2185552507.22</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>511486502.52</v>
+        <v>480248000</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>57936471.2</v>
@@ -6137,20 +6195,75 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="9" t="n">
-        <v>6705612.83</v>
+        <v>6701161.1</v>
       </c>
       <c r="O50" s="9" t="n">
-        <v>9464597.529999999</v>
+        <v>9458314.16</v>
       </c>
       <c r="P50" s="9" t="n">
         <v>13379834.23</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>630043454.84</v>
+        <v>598794217.22</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>1729082268.83</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>289256372.11</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>50305076.95</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>64394233</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>29700967.56</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>46348921</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>28612025</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>2237699864.45</v>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>479993237.83</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>60104622.44</v>
+      </c>
+      <c r="L51" s="9" t="n">
+        <v>13607705.7</v>
+      </c>
+      <c r="M51" s="9" t="n">
+        <v>13923546.06</v>
+      </c>
+      <c r="N51" s="9" t="n">
+        <v>7994156.96</v>
+      </c>
+      <c r="O51" s="9" t="n">
+        <v>12475032.97</v>
+      </c>
+      <c r="P51" s="9" t="n">
+        <v>14189280.7</v>
+      </c>
+      <c r="Q51" s="9" t="n">
+        <v>602287582.66</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q50"/>
+  <autoFilter ref="A2:Q51"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -6165,7 +6278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8167,7 +8280,7 @@
         <v>11226252</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>0.6768000000000001</v>
+        <v>0.6767</v>
       </c>
       <c r="I47" s="11" t="n">
         <v>0.4061</v>
@@ -8210,7 +8323,7 @@
         <v>13207850</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>0.6998000000000001</v>
+        <v>0.6997</v>
       </c>
       <c r="I48" s="11" t="n">
         <v>0.4791</v>
@@ -8253,7 +8366,7 @@
         <v>11477871</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>0.7089</v>
+        <v>0.7088</v>
       </c>
       <c r="I49" s="11" t="n">
         <v>0.4597</v>
@@ -8278,7 +8391,7 @@
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>887289049.54</v>
+        <v>833098800</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>19265583.23</v>
@@ -8296,7 +8409,7 @@
         <v>12724485</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>0.6693000000000001</v>
+        <v>0.655</v>
       </c>
       <c r="I50" s="11" t="n">
         <v>0.4323</v>
@@ -8314,15 +8427,58 @@
         <v>0.4071</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="12" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>832656857.38</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>25326363.49</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>42914988</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>133190448.14</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>28212081.58</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>15736949</v>
+      </c>
+      <c r="H51" s="11" t="n">
+        <v>0.6666</v>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>0.5035000000000001</v>
+      </c>
+      <c r="J51" s="11" t="n">
+        <v>0.6664</v>
+      </c>
+      <c r="K51" s="11" t="n">
+        <v>0.4633</v>
+      </c>
+      <c r="L51" s="11" t="n">
+        <v>0.9499</v>
+      </c>
+      <c r="M51" s="11" t="n">
+        <v>0.3711</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M50"/>
+  <autoFilter ref="A2:M51"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -8353,7 +8509,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-18. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-19. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:R52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226361361.59</v>
+        <v>1226362542.07</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404323456.17</v>
+        <v>1404324636.65</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290715489.49</v>
+        <v>290715536.95</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524812.13</v>
+        <v>524811.75</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360272.49</v>
+        <v>9360265.689999999</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354058480.74</v>
+        <v>354058521.01</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019800417.03</v>
+        <v>1019800672.31</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203205326.54</v>
+        <v>1203205581.82</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223747458.12</v>
+        <v>223747519.11</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -707,13 +707,13 @@
         <v>516297.56</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237366.130000001</v>
+        <v>9237366.119999999</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289059227.59</v>
+        <v>289059288.57</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766410062.92</v>
+        <v>766410960.8</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882452609.96</v>
+        <v>882453507.84</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197402955.5</v>
+        <v>197403112.54</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374709.53</v>
+        <v>374709.39</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399346.69</v>
+        <v>5399344.69</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239492294.1</v>
+        <v>239492449</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983766621.12</v>
+        <v>983766724.58</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168404770.14</v>
+        <v>1168404873.6</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236065195.61</v>
+        <v>236065221.65</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -819,13 +819,13 @@
         <v>324588.36</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358538.87</v>
+        <v>7358538.84</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305861907.41</v>
+        <v>305861933.42</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097590429.48</v>
+        <v>1097592113.89</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302670467.06</v>
+        <v>1302672151.47</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250951625.59</v>
+        <v>250951846.91</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.8</v>
+        <v>709927.35</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693360.33</v>
+        <v>7693355.44</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328055644.98</v>
+        <v>328055860.97</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011526789.07</v>
+        <v>1011527437.08</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233699908.58</v>
+        <v>1233700556.59</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229526225.17</v>
+        <v>229526296.06</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255743.91</v>
+        <v>1255743.52</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409732.52</v>
+        <v>8409729.949999999</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309201158.26</v>
+        <v>309201226.2</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961947373.95</v>
+        <v>961948065.27</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145554535.49</v>
+        <v>1145555226.81</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214890843.72</v>
+        <v>214890955.43</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814775.6800000001</v>
+        <v>814775.51</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850520.48</v>
+        <v>6850519.03</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281207985.08</v>
+        <v>281208095.17</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073052219.33</v>
+        <v>1073052360.86</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277718116.81</v>
+        <v>1277718258.34</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240126649.34</v>
+        <v>240126689</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353400.87</v>
+        <v>2353400.91</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569917.91</v>
+        <v>7569918.03</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313750446</v>
+        <v>313750485.82</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960779558.38</v>
+        <v>960779918.1900001</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185452875.5</v>
+        <v>1185453235.31</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212552905.07</v>
+        <v>212552962.43</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490170.97</v>
+        <v>2490170.69</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929352.869999999</v>
+        <v>8929351.85</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296187769.62</v>
+        <v>296187825.67</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686516217.7</v>
+        <v>686517074.84</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813427908.73</v>
+        <v>813428765.87</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150993346.73</v>
+        <v>150993518.14</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897058.53</v>
+        <v>1897058.18</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485516.17</v>
+        <v>3485515.52</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196257881.33</v>
+        <v>196258051.75</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970916426.38</v>
+        <v>970916887.67</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130473080.62</v>
+        <v>1130473541.91</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227542508.38</v>
+        <v>227542616.4</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642021.52</v>
+        <v>2642021.44</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513112.07</v>
+        <v>5513111.9</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286540190.43</v>
+        <v>286540298.19</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042732210.82</v>
+        <v>1042733010.07</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244216400.89</v>
+        <v>1244217200.14</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230883912.67</v>
+        <v>230883953.72</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865669.18</v>
+        <v>2865667.68</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026080.88</v>
+        <v>7026077.19</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305688734.17</v>
+        <v>305688770.02</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046532992.82</v>
+        <v>1046533191.51</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268580092.63</v>
+        <v>1268580291.32</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238383745.94</v>
+        <v>238383762.2</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737712.85</v>
+        <v>3737712.45</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838302.93</v>
+        <v>7838302.08</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315850498.53</v>
+        <v>315850513.52</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026532454.28</v>
+        <v>1026533018.05</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228676333.31</v>
+        <v>1228676897.08</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246157209.01</v>
+        <v>246157315.07</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558663.05</v>
+        <v>3558662.6</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537353.43</v>
+        <v>7537352.47</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315577279.65</v>
+        <v>315577384.3</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275236798.85</v>
+        <v>1275238430.31</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517958276.1</v>
+        <v>1517959907.56</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295677177.95</v>
+        <v>295677257.25</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271136.58</v>
+        <v>4271132.74</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581192.130000001</v>
+        <v>9581183.52</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378773502.54</v>
+        <v>378773569.4</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123212960.99</v>
+        <v>1123214800.28</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375388122.32</v>
+        <v>1375389961.61</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251892783.87</v>
+        <v>251892978.51</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520553.36</v>
+        <v>3520550.54</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255927.52</v>
+        <v>11255918.5</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341112221.6</v>
+        <v>341112404.4</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780515856.3099999</v>
+        <v>780516845.49</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941932701.84</v>
+        <v>941933691.02</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182891071.74</v>
+        <v>182891179.78</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893248.78</v>
+        <v>2893246.99</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978989.55</v>
+        <v>4978986.45</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240375153</v>
+        <v>240375256.15</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925227082.46</v>
+        <v>925228555.14</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103230466.28</v>
+        <v>1103231938.96</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208940208.45</v>
+        <v>208940391.86</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099142.28</v>
+        <v>3099140.17</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218657.88</v>
+        <v>6218653.64</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270758518.61</v>
+        <v>270758695.68</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099264869.6</v>
+        <v>1099267741.82</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314565163.42</v>
+        <v>1314568035.64</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244622983.14</v>
+        <v>244623406.41</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671187.1</v>
+        <v>3671183.82</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710546.64</v>
+        <v>7710539.76</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319477137.58</v>
+        <v>319477550.69</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967599002.9299999</v>
+        <v>967600524.12</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190920008.51</v>
+        <v>1190921529.7</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210535020.24</v>
+        <v>210535261.87</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281804.34</v>
+        <v>3281802.88</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536310.33</v>
+        <v>7536306.99</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283818015.58</v>
+        <v>283818252.42</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003088411.85</v>
+        <v>1003089639.33</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198245099.91</v>
+        <v>1198246327.39</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222089386.28</v>
+        <v>222089512.93</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891021.98</v>
+        <v>3891019.66</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335908.82</v>
+        <v>6335905.05</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281020812.01</v>
+        <v>281020932.57</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362288369.79</v>
+        <v>1362288723.85</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634505124.91</v>
+        <v>1634505478.97</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306763242.84</v>
+        <v>306763295.4</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136471.89</v>
+        <v>6136471.37</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270564.93</v>
+        <v>10270564.06</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388022411.16</v>
+        <v>388022462.33</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156900459.4</v>
+        <v>1156903654.22</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409400427.05</v>
+        <v>1409403621.87</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247798688.58</v>
+        <v>247798983.94</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795230.89</v>
+        <v>3795225.5</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929378.76</v>
+        <v>9929364.66</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325996523.01</v>
+        <v>325996798.88</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870304995.8200001</v>
+        <v>870306716.37</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039409208.19</v>
+        <v>1039410928.74</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193434393.29</v>
+        <v>193434552.32</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256065.84</v>
+        <v>3256062.43</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684210.14</v>
+        <v>5684204.2</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245276480.9</v>
+        <v>245276630.58</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002268060.31</v>
+        <v>1002269124.17</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209605468.27</v>
+        <v>1209606532.13</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>217001324.82</v>
+        <v>217001495.63</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934142.75</v>
+        <v>2934141.92</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937709.27</v>
+        <v>6937707.32</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280973581.92</v>
+        <v>280973749.95</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105965796.43</v>
+        <v>1105967359.36</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351820696.08</v>
+        <v>1351822259.01</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242484611.48</v>
+        <v>242484905.2</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693259.76</v>
+        <v>2693259.07</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764078.609999999</v>
+        <v>8764076.380000001</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322798428.85</v>
+        <v>322798719.65</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932847385.12</v>
+        <v>932848424.96</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136795199.57</v>
+        <v>1136796239.41</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196525553.93</v>
+        <v>196525718.7</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927932.04</v>
+        <v>2927931.19</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577856.95</v>
+        <v>6577855.04</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259479684.28</v>
+        <v>259479846.29</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1162033775.24</v>
+        <v>1162034822.46</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354870259.31</v>
+        <v>1354871306.53</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252354163.96</v>
+        <v>252354396.92</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229210.89</v>
+        <v>4229210.77</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541698.39</v>
+        <v>4541698.26</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311966791.87</v>
+        <v>311967024.59</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1440007324.71</v>
+        <v>1440008406.28</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740063990.74</v>
+        <v>1740065072.31</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284719235.36</v>
+        <v>284719410.46</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067082.55</v>
+        <v>4067081.9</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978504.39</v>
+        <v>5978503.43</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375590011.16</v>
+        <v>375590184.65</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319734351.44</v>
+        <v>1319735513.1</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579497435.56</v>
+        <v>1579498597.22</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283378872.08</v>
+        <v>283378972.47</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050967.44</v>
+        <v>3050966</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438410.59</v>
+        <v>7438407.08</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363619614.63</v>
+        <v>363619710.06</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1097008099.39</v>
+        <v>1097009578.29</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283049125.5</v>
+        <v>1283050604.4</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243430189.26</v>
+        <v>243430437.17</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660630.86</v>
+        <v>1660630.29</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202068.44</v>
+        <v>7202065.98</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302147780.09</v>
+        <v>302148024.97</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142134127.09</v>
+        <v>1142136280.26</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1366025241.04</v>
+        <v>1366027394.21</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239661807.03</v>
+        <v>239662145.18</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298508.7</v>
+        <v>1298508.06</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234266.23</v>
+        <v>9234261.67</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307454956.7</v>
+        <v>307455289.65</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192856964.33</v>
+        <v>1192857809.79</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436513971</v>
+        <v>1436514816.46</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253632520.95</v>
+        <v>253632653.37</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145313.24</v>
+        <v>2145312.83</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745127.3</v>
+        <v>6745126.02</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327987363.69</v>
+        <v>327987494.42</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226943703.82</v>
+        <v>1226945144.43</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494283994.69</v>
+        <v>1494285435.3</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272959812.74</v>
+        <v>272960173.4</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511840</v>
+        <v>2511840.09</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248301.65</v>
+        <v>7248301.9</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361202039.06</v>
+        <v>361202400.07</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348634076.65</v>
+        <v>1348635440.3</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622954221.4</v>
+        <v>1622955585.05</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278440833.28</v>
+        <v>278441014.5</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307540.68</v>
+        <v>2307539.87</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088544.75</v>
+        <v>8088541.92</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361827825.49</v>
+        <v>361828003.08</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778319461.25</v>
+        <v>1778324391.55</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122382523.31</v>
+        <v>2122387453.61</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364514398.01</v>
+        <v>364515395.1</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3919087.82</v>
+        <v>3919087.09</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6647152.55</v>
+        <v>6647151.32</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465533406.15</v>
+        <v>465534401.28</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364417508.01</v>
+        <v>1364420972.65</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1651187294.61</v>
+        <v>1651190759.25</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283723611.11</v>
+        <v>283725311.09</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4917244.89</v>
+        <v>4917257.29</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7352669.63</v>
+        <v>7352688.18</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374621315.31</v>
+        <v>374623046.24</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1038070764.43</v>
+        <v>1038078170.81</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347447481.22</v>
+        <v>1347454887.6</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218487299.15</v>
+        <v>218489805.92</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3629101.8</v>
+        <v>3629110.79</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4592096.89</v>
+        <v>4592108.27</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316837071.31</v>
+        <v>316839598.47</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143689056.49</v>
+        <v>1143693901.54</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1422171476.1</v>
+        <v>1422176321.15</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228258981.11</v>
+        <v>228260647.09</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3388654.53</v>
+        <v>3388661.15</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5521923.75</v>
+        <v>5521934.54</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>314042744.57</v>
+        <v>314044427.96</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339522336.6</v>
+        <v>1339525723.78</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1715096242.2</v>
+        <v>1715099629.38</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269967942.62</v>
+        <v>269968937.24</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2886718.02</v>
+        <v>2886719.73</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7560669.26</v>
+        <v>7560673.74</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389860799.25</v>
+        <v>389861800.06</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1172389750.41</v>
+        <v>1172394615.29</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>221857126.57</v>
@@ -2947,10 +2947,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1562174741.47</v>
+        <v>1562179606.35</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>220141553.61</v>
+        <v>220144556.63</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>61180264.16</v>
@@ -2962,16 +2962,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2632925.02</v>
+        <v>2632941.11</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>7180717.82</v>
+        <v>7180761.7</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>332027112.59</v>
+        <v>332030175.58</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.3738082799669966</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1225009287.23</v>
+        <v>1225017980.94</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>197998279.3</v>
@@ -3005,10 +3005,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1582889389.3</v>
+        <v>1582898083.01</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236973511.27</v>
+        <v>236977500.64</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>51757451.41</v>
@@ -3020,16 +3020,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5234066.08</v>
+        <v>5234100</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6970369.02</v>
+        <v>6970414.19</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>339790053.28</v>
+        <v>339794121.75</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3916156197964661</v>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1838969760.7</v>
+        <v>1838986045.63</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>306596831.13</v>
@@ -3063,10 +3063,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2463876250.73</v>
+        <v>2463892535.66</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>385274722.94</v>
+        <v>385281822.4</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>76961502.72</v>
@@ -3078,16 +3078,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>10618384.79</v>
+        <v>10618453</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>18123347.01</v>
+        <v>18123463.44</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>558876656.3099999</v>
+        <v>558883940.41</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0.40067966485108</v>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1909254403.96</v>
+        <v>1909373745.12</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>376107142.6</v>
@@ -3121,10 +3121,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2709773852.25</v>
+        <v>2709893193.41</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>383325382.69</v>
+        <v>383374420.16</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>102191529.21</v>
@@ -3136,16 +3136,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>12010159.56</v>
+        <v>12010629.38</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>22112840.85</v>
+        <v>22113705.87</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>605719904.39</v>
+        <v>605770276.6900001</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0.442865215754716</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1124404374.41</v>
+        <v>1124604597.39</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>250093696.52</v>
@@ -3179,10 +3179,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1556022586.94</v>
+        <v>1556222809.92</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>215735664.13</v>
+        <v>215813492.31</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>65852392.81</v>
@@ -3194,16 +3194,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>3872161.08</v>
+        <v>3872568.06</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>5477264.28</v>
+        <v>5477839.97</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>337095413.79</v>
+        <v>337174224.63</v>
       </c>
       <c r="R47" s="10" t="n">
         <v>0.4207679702437824</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1314573734.66</v>
+        <v>1314866310.05</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>251713084.28</v>
@@ -3237,10 +3237,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>1712896103.2</v>
+        <v>1713188678.59</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>242069447.35</v>
+        <v>242180789.34</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>62840730.8</v>
@@ -3252,16 +3252,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>4582168.61</v>
+        <v>4582868.64</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>5975611.18</v>
+        <v>5976524.09</v>
       </c>
       <c r="P48" s="9" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>349050080.49</v>
+        <v>349163035.43</v>
       </c>
       <c r="R48" s="10" t="n">
         <v>0.4544083188194561</v>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>1345241260</v>
+        <v>1345588147.14</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>255216837.43</v>
@@ -3295,10 +3295,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>1765594095.83</v>
+        <v>1765940982.97</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>244216134.89</v>
+        <v>244352457.82</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>63158844.13</v>
@@ -3310,16 +3310,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="9" t="n">
-        <v>5330702.65</v>
+        <v>5331731.23</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>6160559.57</v>
+        <v>6161748.28</v>
       </c>
       <c r="P49" s="9" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>355721713.44</v>
+        <v>355860253.65</v>
       </c>
       <c r="R49" s="10" t="n">
         <v>0.4715622688002217</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>1271985227.8</v>
+        <v>1272437061.22</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>251070477.59</v>
@@ -3353,10 +3353,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>1721875405.55</v>
+        <v>1722327238.97</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>250698050.06</v>
+        <v>250864239.8</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>57612870.57</v>
@@ -3368,16 +3368,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="9" t="n">
-        <v>5175186.61</v>
+        <v>5176222.53</v>
       </c>
       <c r="O50" s="9" t="n">
-        <v>6613990.53</v>
+        <v>6615314.45</v>
       </c>
       <c r="P50" s="9" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>364329243.22</v>
+        <v>364497792.8</v>
       </c>
       <c r="R50" s="10" t="n">
         <v>0.5184969295746537</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>1249115214.35</v>
+        <v>1424282830.14</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>287468135.92</v>
@@ -3411,10 +3411,10 @@
         <v>28011807</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>1751397615.78</v>
+        <v>1926565231.57</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>242595529.2</v>
+        <v>254199769.81</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>59780017.61</v>
@@ -3426,23 +3426,81 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="9" t="n">
-        <v>6081989.33</v>
+        <v>5693353.51</v>
       </c>
       <c r="O51" s="9" t="n">
-        <v>8682869.07</v>
+        <v>8128038.44</v>
       </c>
       <c r="P51" s="9" t="n">
         <v>13969238.87</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>358640895.84</v>
+        <v>369301670</v>
       </c>
       <c r="R51" s="10" t="n">
         <v>0.5173698555705437</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>2084856417.15</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>438830798.95</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>87526537.66</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>73702169</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>42466402.45</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>125978923</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>20465067</v>
+      </c>
+      <c r="I52" s="7" t="n">
+        <v>2873826315.21</v>
+      </c>
+      <c r="J52" s="8" t="n">
+        <v>406361719.17</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>92879457.39</v>
+      </c>
+      <c r="L52" s="9" t="n">
+        <v>28866510.47</v>
+      </c>
+      <c r="M52" s="9" t="n">
+        <v>15738266.69</v>
+      </c>
+      <c r="N52" s="9" t="n">
+        <v>8697369.369999999</v>
+      </c>
+      <c r="O52" s="9" t="n">
+        <v>25801225.52</v>
+      </c>
+      <c r="P52" s="9" t="n">
+        <v>10232009.27</v>
+      </c>
+      <c r="Q52" s="9" t="n">
+        <v>588576557.88</v>
+      </c>
+      <c r="R52" s="10" t="n">
+        <v>0.4928123695831447</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R51"/>
+  <autoFilter ref="A2:R52"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3458,7 +3516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6214,7 +6272,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>1729082268.83</v>
+        <v>2090000000</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>289256372.11</v>
@@ -6235,10 +6293,10 @@
         <v>28612025</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>2237699864.45</v>
+        <v>2598617595.62</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>479993237.83</v>
+        <v>580184000</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>60104622.44</v>
@@ -6250,20 +6308,75 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="9" t="n">
-        <v>7994156.96</v>
+        <v>8030044.83</v>
       </c>
       <c r="O51" s="9" t="n">
-        <v>12475032.97</v>
+        <v>12531036.67</v>
       </c>
       <c r="P51" s="9" t="n">
         <v>14189280.7</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>602287582.66</v>
+        <v>702570236.41</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>2810000000</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>440017213.07</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>87526537.66</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>73702169</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>42466402.45</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>129829212</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>20804881</v>
+      </c>
+      <c r="I52" s="7" t="n">
+        <v>3604346415.18</v>
+      </c>
+      <c r="J52" s="8" t="n">
+        <v>780056000</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>93075890.23999999</v>
+      </c>
+      <c r="L52" s="9" t="n">
+        <v>28866510.47</v>
+      </c>
+      <c r="M52" s="9" t="n">
+        <v>15738266.69</v>
+      </c>
+      <c r="N52" s="9" t="n">
+        <v>11483767.21</v>
+      </c>
+      <c r="O52" s="9" t="n">
+        <v>35108423.63</v>
+      </c>
+      <c r="P52" s="9" t="n">
+        <v>10358724.77</v>
+      </c>
+      <c r="Q52" s="9" t="n">
+        <v>974687583</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q51"/>
+  <autoFilter ref="A2:Q52"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -6278,7 +6391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7334,7 +7447,7 @@
         <v>15568073</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.6161</v>
+        <v>0.616</v>
       </c>
       <c r="I25" s="11" t="n">
         <v>0.3765</v>
@@ -8022,7 +8135,7 @@
         <v>9247924</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>0.6568999999999999</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="I41" s="11" t="n">
         <v>0.4061999999999999</v>
@@ -8280,7 +8393,7 @@
         <v>11226252</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>0.6767</v>
+        <v>0.6766</v>
       </c>
       <c r="I47" s="11" t="n">
         <v>0.4061</v>
@@ -8323,7 +8436,7 @@
         <v>13207850</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>0.6997</v>
+        <v>0.6995</v>
       </c>
       <c r="I48" s="11" t="n">
         <v>0.4791</v>
@@ -8366,7 +8479,7 @@
         <v>11477871</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>0.7088</v>
+        <v>0.7086</v>
       </c>
       <c r="I49" s="11" t="n">
         <v>0.4597</v>
@@ -8409,7 +8522,7 @@
         <v>12724485</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>0.655</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="I50" s="11" t="n">
         <v>0.4323</v>
@@ -8434,7 +8547,7 @@
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>832656857.38</v>
+        <v>1006460400</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>25326363.49</v>
@@ -8452,7 +8565,7 @@
         <v>15736949</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>0.6666</v>
+        <v>0.7066</v>
       </c>
       <c r="I51" s="11" t="n">
         <v>0.5035000000000001</v>
@@ -8470,15 +8583,58 @@
         <v>0.3711</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="12" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>1353183600</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>41469933.99</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>48812989</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>208922280.31</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>41472086.49</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>38042084</v>
+      </c>
+      <c r="H52" s="11" t="n">
+        <v>0.6491</v>
+      </c>
+      <c r="I52" s="11" t="n">
+        <v>0.4738</v>
+      </c>
+      <c r="J52" s="11" t="n">
+        <v>0.6623</v>
+      </c>
+      <c r="K52" s="11" t="n">
+        <v>0.4761</v>
+      </c>
+      <c r="L52" s="11" t="n">
+        <v>0.9765999999999999</v>
+      </c>
+      <c r="M52" s="11" t="n">
+        <v>0.302</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M51"/>
+  <autoFilter ref="A2:M52"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -8509,7 +8665,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-19. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-20. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339525723.78</v>
+        <v>1339525807.37</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1715099629.38</v>
+        <v>1715099712.97</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269968937.24</v>
+        <v>269968970.51</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2886719.73</v>
+        <v>2886719.84</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7560673.74</v>
+        <v>7560674.03</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389861800.06</v>
+        <v>389861833.72</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1172394615.29</v>
+        <v>1172394617.29</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>221857126.57</v>
@@ -2947,10 +2947,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1562179606.35</v>
+        <v>1562179608.35</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>220144556.63</v>
+        <v>220144556.99</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>61180264.16</v>
@@ -2971,7 +2971,7 @@
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>332030175.58</v>
+        <v>332030175.93</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.3738082799669966</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1225017980.94</v>
+        <v>1225018035.67</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>197998279.3</v>
@@ -3005,10 +3005,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1582898083.01</v>
+        <v>1582898137.74</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236977500.64</v>
+        <v>236977519.78</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>51757451.41</v>
@@ -3020,16 +3020,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5234100</v>
+        <v>5234100.12</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6970414.19</v>
+        <v>6970414.35</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>339794121.75</v>
+        <v>339794141.16</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3916156197964661</v>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1838986045.63</v>
+        <v>1838986062.34</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>306596831.13</v>
@@ -3063,10 +3063,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2463892535.66</v>
+        <v>2463892552.37</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>385281822.4</v>
+        <v>385281823.88</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>76961502.72</v>
@@ -3078,16 +3078,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>10618453</v>
+        <v>10618452.96</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>18123463.44</v>
+        <v>18123463.36</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>558883940.41</v>
+        <v>558883941.76</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0.40067966485108</v>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1909373745.12</v>
+        <v>1909375228.94</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>376107142.6</v>
@@ -3121,10 +3121,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2709893193.41</v>
+        <v>2709894677.23</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>383374420.16</v>
+        <v>383374912.02</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>102191529.21</v>
@@ -3136,16 +3136,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>12010629.38</v>
+        <v>12010632.74</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>22113705.87</v>
+        <v>22113712.06</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>605770276.6900001</v>
+        <v>605770778.11</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0.442865215754716</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1124604597.39</v>
+        <v>1124614656.91</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>250093696.52</v>
@@ -3179,10 +3179,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1556222809.92</v>
+        <v>1556232869.44</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>215813492.31</v>
+        <v>215815448.71</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>65852392.81</v>
@@ -3194,16 +3194,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>3872568.06</v>
+        <v>3872565.43</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>5477839.97</v>
+        <v>5477836.24</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>337174224.63</v>
+        <v>337176174.67</v>
       </c>
       <c r="R47" s="10" t="n">
         <v>0.4207679702437824</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1314866310.05</v>
+        <v>1314880248.45</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>251713084.28</v>
@@ -3237,10 +3237,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>1713188678.59</v>
+        <v>1713202616.99</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>242180789.34</v>
+        <v>242185034.56</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>62840730.8</v>
@@ -3252,16 +3252,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>4582868.64</v>
+        <v>4582887.65</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>5976524.09</v>
+        <v>5976548.88</v>
       </c>
       <c r="P48" s="9" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>349163035.43</v>
+        <v>349167324.45</v>
       </c>
       <c r="R48" s="10" t="n">
         <v>0.4544083188194561</v>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>1345588147.14</v>
+        <v>1345609096.19</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>255216837.43</v>
@@ -3295,10 +3295,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>1765940982.97</v>
+        <v>1765961932.02</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>244352457.82</v>
+        <v>244360019</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>63158844.13</v>
@@ -3310,16 +3310,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="9" t="n">
-        <v>5331731.23</v>
+        <v>5331782.94</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>6161748.28</v>
+        <v>6161808.03</v>
       </c>
       <c r="P49" s="9" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>355860253.65</v>
+        <v>355867926.29</v>
       </c>
       <c r="R49" s="10" t="n">
         <v>0.4715622688002217</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>1272437061.22</v>
+        <v>1272473677.89</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>251070477.59</v>
@@ -3353,10 +3353,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>1722327238.97</v>
+        <v>1722363855.64</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>250864239.8</v>
+        <v>250878435.62</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>57612870.57</v>
@@ -3368,16 +3368,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="9" t="n">
-        <v>5176222.53</v>
+        <v>5176317.14</v>
       </c>
       <c r="O50" s="9" t="n">
-        <v>6615314.45</v>
+        <v>6615435.36</v>
       </c>
       <c r="P50" s="9" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>364497792.8</v>
+        <v>364512204.13</v>
       </c>
       <c r="R50" s="10" t="n">
         <v>0.5184969295746537</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>1424282830.14</v>
+        <v>1424366772.25</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>287468135.92</v>
@@ -3411,10 +3411,10 @@
         <v>28011807</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>1926565231.57</v>
+        <v>1926649173.68</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>254199769.81</v>
+        <v>254225570.01</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>59780017.61</v>
@@ -3426,16 +3426,16 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="9" t="n">
-        <v>5693353.51</v>
+        <v>5693509.01</v>
       </c>
       <c r="O51" s="9" t="n">
-        <v>8128038.44</v>
+        <v>8128260.43</v>
       </c>
       <c r="P51" s="9" t="n">
         <v>13969238.87</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>369301670</v>
+        <v>369327847.69</v>
       </c>
       <c r="R51" s="10" t="n">
         <v>0.5173698555705437</v>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>2084856417.15</v>
+        <v>2085015517.59</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>438830798.95</v>
@@ -3469,10 +3469,10 @@
         <v>20465067</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>2873826315.21</v>
+        <v>2873985415.65</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>406361719.17</v>
+        <v>406416243.2</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>92879457.39</v>
@@ -3484,16 +3484,16 @@
         <v>15738266.69</v>
       </c>
       <c r="N52" s="9" t="n">
-        <v>8697369.369999999</v>
+        <v>8697713.74</v>
       </c>
       <c r="O52" s="9" t="n">
-        <v>25801225.52</v>
+        <v>25802247.09</v>
       </c>
       <c r="P52" s="9" t="n">
         <v>10232009.27</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>588576557.88</v>
+        <v>588632447.84</v>
       </c>
       <c r="R52" s="10" t="n">
         <v>0.4928123695831447</v>
@@ -8608,7 +8608,7 @@
         <v>38042084</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>0.6491</v>
+        <v>0.649</v>
       </c>
       <c r="I52" s="11" t="n">
         <v>0.4738</v>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R52"/>
+  <dimension ref="A1:R53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226362542.07</v>
+        <v>1226362956.81</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404324636.65</v>
+        <v>1404325051.39</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290715536.95</v>
+        <v>290715570.41</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524811.75</v>
+        <v>524811.64</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360265.689999999</v>
+        <v>9360263.75</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354058521.01</v>
+        <v>354058552.43</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019800672.31</v>
+        <v>1019800702.49</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203205581.82</v>
+        <v>1203205612</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223747519.11</v>
+        <v>223747522.24</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516297.56</v>
+        <v>516297.55</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237366.119999999</v>
+        <v>9237365.98</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289059288.57</v>
+        <v>289059291.55</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766410960.8</v>
+        <v>766411149.46</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882453507.84</v>
+        <v>882453696.5</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197403112.54</v>
+        <v>197403208.75</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374709.39</v>
+        <v>374709.46</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399344.69</v>
+        <v>5399345.73</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239492449</v>
+        <v>239492546.32</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983766724.58</v>
+        <v>983766835.9400001</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168404873.6</v>
+        <v>1168404984.96</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236065221.65</v>
+        <v>236065236.83</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324588.36</v>
+        <v>324588.34</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358538.84</v>
+        <v>7358538.5</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305861933.42</v>
+        <v>305861948.24</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097592113.89</v>
+        <v>1097592214.3</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302672151.47</v>
+        <v>1302672251.88</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250951846.91</v>
+        <v>250951862.97</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.35</v>
+        <v>709927.33</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693355.44</v>
+        <v>7693355.22</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328055860.97</v>
+        <v>328055876.78</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011527437.08</v>
+        <v>1011527784.84</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233700556.59</v>
+        <v>1233700904.35</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229526296.06</v>
+        <v>229526393.68</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255743.52</v>
+        <v>1255743.57</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409729.949999999</v>
+        <v>8409730.25</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309201226.2</v>
+        <v>309201324.16</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961948065.27</v>
+        <v>961948549.76</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145555226.81</v>
+        <v>1145555711.3</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214890955.43</v>
+        <v>214891003.65</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814775.51</v>
+        <v>814775.3</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850519.03</v>
+        <v>6850517.26</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281208095.17</v>
+        <v>281208141.41</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073052360.86</v>
+        <v>1073052479.18</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277718258.34</v>
+        <v>1277718376.66</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240126689</v>
+        <v>240126698.78</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353400.91</v>
+        <v>2353400.76</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569918.03</v>
+        <v>7569917.55</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313750485.82</v>
+        <v>313750494.97</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960779918.1900001</v>
+        <v>960779939.2</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185453235.31</v>
+        <v>1185453256.32</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212552962.43</v>
+        <v>212552972.89</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490170.69</v>
+        <v>2490170.74</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929351.85</v>
+        <v>8929352.02</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296187825.67</v>
+        <v>296187836.34</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686517074.84</v>
+        <v>686517234.2</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813428765.87</v>
+        <v>813428925.23</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150993518.14</v>
+        <v>150993587.7</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897058.18</v>
+        <v>1897058.49</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485515.52</v>
+        <v>3485516.09</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196258051.75</v>
+        <v>196258122.18</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970916887.67</v>
+        <v>970917726.73</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130473541.91</v>
+        <v>1130474380.97</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227542616.4</v>
+        <v>227542692.71</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642021.44</v>
+        <v>2642020.14</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513111.9</v>
+        <v>5513109.2</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286540298.19</v>
+        <v>286540370.5</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042733010.07</v>
+        <v>1042733507.13</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244217200.14</v>
+        <v>1244217697.2</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230883953.72</v>
+        <v>230883959.56</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865667.68</v>
+        <v>2865666.55</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026077.19</v>
+        <v>7026074.43</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305688770.02</v>
+        <v>305688771.98</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046533191.51</v>
+        <v>1046533320.81</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268580291.32</v>
+        <v>1268580420.62</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238383762.2</v>
+        <v>238383791.66</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737712.45</v>
+        <v>3737712.41</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838302.08</v>
+        <v>7838302.01</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315850513.52</v>
+        <v>315850542.88</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026533018.05</v>
+        <v>1026533540.76</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228676897.08</v>
+        <v>1228677419.79</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246157315.07</v>
+        <v>246157420.46</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558662.6</v>
+        <v>3558662.26</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537352.47</v>
+        <v>7537351.75</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315577384.3</v>
+        <v>315577488.63</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275238430.31</v>
+        <v>1275238563.42</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517959907.56</v>
+        <v>1517960040.67</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295677257.25</v>
+        <v>295677291.2</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271132.74</v>
+        <v>4271132.75</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581183.52</v>
+        <v>9581183.539999999</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378773569.4</v>
+        <v>378773603.37</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123214800.28</v>
+        <v>1123214947.24</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375389961.61</v>
+        <v>1375390108.57</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251892978.51</v>
+        <v>251892996.64</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520550.54</v>
+        <v>3520550.35</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255918.5</v>
+        <v>11255917.87</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341112404.4</v>
+        <v>341112421.7</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780516845.49</v>
+        <v>780519684.51</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941933691.02</v>
+        <v>941936530.04</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182891179.78</v>
+        <v>182891236.98</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893246.99</v>
+        <v>2893238.68</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978986.45</v>
+        <v>4978972.16</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240375256.15</v>
+        <v>240375290.76</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925228555.14</v>
+        <v>925228616.4400001</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103231938.96</v>
+        <v>1103232000.26</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208940391.86</v>
+        <v>208940405.61</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099140.17</v>
+        <v>3099140.15</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218653.64</v>
+        <v>6218653.61</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270758695.68</v>
+        <v>270758709.38</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099267741.82</v>
+        <v>1099268146.55</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314568035.64</v>
+        <v>1314568440.37</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244623406.41</v>
+        <v>244623589.59</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671183.82</v>
+        <v>3671184.83</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710539.76</v>
+        <v>7710541.88</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319477550.69</v>
+        <v>319477737.01</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967600524.12</v>
+        <v>967600829.9299999</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190921529.7</v>
+        <v>1190921835.51</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210535261.87</v>
+        <v>210535313.9</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281802.88</v>
+        <v>3281802.63</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536306.99</v>
+        <v>7536306.42</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283818252.42</v>
+        <v>283818303.62</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003089639.33</v>
+        <v>1003092587.3</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198246327.39</v>
+        <v>1198249275.36</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222089512.93</v>
+        <v>222089714.94</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891019.66</v>
+        <v>3891012.63</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335905.05</v>
+        <v>6335893.6</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281020932.57</v>
+        <v>281021116.1</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362288723.85</v>
+        <v>1362288839.85</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634505478.97</v>
+        <v>1634505594.97</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306763295.4</v>
+        <v>306763353.05</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136471.37</v>
+        <v>6136471.87</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270564.06</v>
+        <v>10270564.89</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388022462.33</v>
+        <v>388022521.31</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156903654.22</v>
+        <v>1156904574.94</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409403621.87</v>
+        <v>1409404542.59</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247798983.94</v>
+        <v>247799030.55</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795225.5</v>
+        <v>3795223.48</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929364.66</v>
+        <v>9929359.369999999</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325996798.88</v>
+        <v>325996838.17</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870306716.37</v>
+        <v>870311652.5700001</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039410928.74</v>
+        <v>1039415864.94</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193434552.32</v>
+        <v>193435927.08</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256062.43</v>
+        <v>3256065.33</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684204.2</v>
+        <v>5684209.25</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245276630.58</v>
+        <v>245278013.29</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002269124.17</v>
+        <v>1002271713.67</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209606532.13</v>
+        <v>1209609121.63</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>217001495.63</v>
+        <v>217002066.51</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934141.92</v>
+        <v>2934141.59</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937707.32</v>
+        <v>6937706.54</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280973749.95</v>
+        <v>280974319.72</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105967359.36</v>
+        <v>1105968178.49</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351822259.01</v>
+        <v>1351823078.14</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242484905.2</v>
+        <v>242485269.66</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693259.07</v>
+        <v>2693260.53</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764076.380000001</v>
+        <v>8764081.130000001</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322798719.65</v>
+        <v>322799090.32</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932848424.96</v>
+        <v>932849708.41</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136796239.41</v>
+        <v>1136797522.86</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196525718.7</v>
+        <v>196525951</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927931.19</v>
+        <v>2927930.48</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577855.04</v>
+        <v>6577853.44</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259479846.29</v>
+        <v>259480076.28</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1162034822.46</v>
+        <v>1162035394.15</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354871306.53</v>
+        <v>1354871878.22</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252354396.92</v>
+        <v>252354442.13</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229210.77</v>
+        <v>4229209.57</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541698.26</v>
+        <v>4541696.97</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311967024.59</v>
+        <v>311967067.3</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1440008406.28</v>
+        <v>1440011463.71</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740065072.31</v>
+        <v>1740068129.74</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284719410.46</v>
+        <v>284720110.8</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067081.9</v>
+        <v>4067082.35</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978503.43</v>
+        <v>5978504.09</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375590184.65</v>
+        <v>375590886.1</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319735513.1</v>
+        <v>1319736758.13</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579498597.22</v>
+        <v>1579499842.25</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283378972.47</v>
+        <v>283379052.83</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050966</v>
+        <v>3050964.21</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438407.08</v>
+        <v>7438402.73</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363619710.06</v>
+        <v>363619784.29</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1097009578.29</v>
+        <v>1097010773.18</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283050604.4</v>
+        <v>1283051799.29</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243430437.17</v>
+        <v>243430627.18</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660630.29</v>
+        <v>1660629.78</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202065.98</v>
+        <v>7202063.73</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302148024.97</v>
+        <v>302148212.22</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142136280.26</v>
+        <v>1142137766.09</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1366027394.21</v>
+        <v>1366028880.04</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239662145.18</v>
+        <v>239662388.39</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298508.06</v>
+        <v>1298507.66</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234261.67</v>
+        <v>9234258.84</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307455289.65</v>
+        <v>307455529.63</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192857809.79</v>
+        <v>1192859316.47</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436514816.46</v>
+        <v>1436516323.14</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253632653.37</v>
+        <v>253633253.61</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145312.83</v>
+        <v>2145314.55</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745126.02</v>
+        <v>6745131.44</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327987494.42</v>
+        <v>327988101.8</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226945144.43</v>
+        <v>1226946284.86</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494285435.3</v>
+        <v>1494286575.73</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272960173.4</v>
+        <v>272960332.59</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511840.09</v>
+        <v>2511839.25</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248301.9</v>
+        <v>7248299.5</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361202400.07</v>
+        <v>361202556.02</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348635440.3</v>
+        <v>1348640208.39</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622955585.05</v>
+        <v>1622960353.14</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278441014.5</v>
+        <v>278441295</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307539.87</v>
+        <v>2307534.73</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088541.92</v>
+        <v>8088523.91</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361828003.08</v>
+        <v>361828260.43</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778324391.55</v>
+        <v>1778328115.67</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122387453.61</v>
+        <v>2122391177.73</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364515395.1</v>
+        <v>364516044.18</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3919087.09</v>
+        <v>3919085.64</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6647151.32</v>
+        <v>6647148.87</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465534401.28</v>
+        <v>465535046.46</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364420972.65</v>
+        <v>1364426641.21</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1651190759.25</v>
+        <v>1651196427.81</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283725311.09</v>
+        <v>283725983.4</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4917257.29</v>
+        <v>4917248.96</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7352688.18</v>
+        <v>7352675.72</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374623046.24</v>
+        <v>374623697.77</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1038078170.81</v>
+        <v>1038079761.61</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347454887.6</v>
+        <v>1347456478.4</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218489805.92</v>
+        <v>218490363.17</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3629110.79</v>
+        <v>3629112.95</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4592108.27</v>
+        <v>4592111</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316839598.47</v>
+        <v>316840160.6</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143693901.54</v>
+        <v>1143696049.56</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1422176321.15</v>
+        <v>1422178469.17</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228260647.09</v>
+        <v>228261114.03</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3388661.15</v>
+        <v>3388661.07</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5521934.54</v>
+        <v>5521934.41</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>314044427.96</v>
+        <v>314044894.68</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339525807.37</v>
+        <v>1339531864.58</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1715099712.97</v>
+        <v>1715105770.18</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269968970.51</v>
+        <v>269969322.97</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2886719.84</v>
+        <v>2886712.04</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7560674.03</v>
+        <v>7560653.61</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389861833.72</v>
+        <v>389862157.98</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1172394617.29</v>
+        <v>1172397330.73</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>221857126.57</v>
@@ -2947,10 +2947,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1562179608.35</v>
+        <v>1562182321.79</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>220144556.99</v>
+        <v>220144842.45</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>61180264.16</v>
@@ -2962,16 +2962,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2632941.11</v>
+        <v>2632938.73</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>7180761.7</v>
+        <v>7180755.21</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>332030175.93</v>
+        <v>332030452.52</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.3738082799669966</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1225018035.67</v>
+        <v>1225019760.06</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>197998279.3</v>
@@ -3005,10 +3005,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1582898137.74</v>
+        <v>1582899862.13</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236977519.78</v>
+        <v>236977906.37</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>51757451.41</v>
@@ -3020,16 +3020,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5234100.12</v>
+        <v>5234100.38</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6970414.35</v>
+        <v>6970414.7</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>339794141.16</v>
+        <v>339794528.36</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3916156197964661</v>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1838986062.34</v>
+        <v>1838988685.01</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>306596831.13</v>
@@ -3063,10 +3063,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2463892552.37</v>
+        <v>2463895175.04</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>385281823.88</v>
+        <v>385282514.13</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>76961502.72</v>
@@ -3078,16 +3078,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>10618452.96</v>
+        <v>10618454.87</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>18123463.36</v>
+        <v>18123466.62</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>558883941.76</v>
+        <v>558884637.1799999</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0.40067966485108</v>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1909375228.94</v>
+        <v>1909382742.4</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>376107142.6</v>
@@ -3121,10 +3121,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2709894677.23</v>
+        <v>2709902190.69</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>383374912.02</v>
+        <v>383378240.99</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>102191529.21</v>
@@ -3136,16 +3136,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>12010632.74</v>
+        <v>12010667.4</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>22113712.06</v>
+        <v>22113775.87</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>605770778.11</v>
+        <v>605774205.54</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0.442865215754716</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1124614656.91</v>
+        <v>1124667809.74</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>250093696.52</v>
@@ -3179,10 +3179,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1556232869.44</v>
+        <v>1556286022.27</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>215815448.71</v>
+        <v>215835789.84</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>65852392.81</v>
@@ -3194,16 +3194,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>3872565.43</v>
+        <v>3872669.67</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>5477836.24</v>
+        <v>5477983.7</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>337176174.67</v>
+        <v>337196767.5</v>
       </c>
       <c r="R47" s="10" t="n">
         <v>0.4207679702437824</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1314880248.45</v>
+        <v>1315050738.51</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>251713084.28</v>
@@ -3237,10 +3237,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>1713202616.99</v>
+        <v>1713373107.05</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>242185034.56</v>
+        <v>242225186.59</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>62840730.8</v>
@@ -3252,16 +3252,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>4582887.65</v>
+        <v>4582960.79</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>5976548.88</v>
+        <v>5976644.26</v>
       </c>
       <c r="P48" s="9" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>349167324.45</v>
+        <v>349207645</v>
       </c>
       <c r="R48" s="10" t="n">
         <v>0.4544083188194561</v>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>1345609096.19</v>
+        <v>1345743299.59</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>255216837.43</v>
@@ -3295,10 +3295,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>1765961932.02</v>
+        <v>1766096135.42</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>244360019</v>
+        <v>244405204.6</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>63158844.13</v>
@@ -3310,16 +3310,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="9" t="n">
-        <v>5331782.94</v>
+        <v>5332063.8</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>6161808.03</v>
+        <v>6162132.61</v>
       </c>
       <c r="P49" s="9" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>355867926.29</v>
+        <v>355913717.33</v>
       </c>
       <c r="R49" s="10" t="n">
         <v>0.4715622688002217</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>1272473677.89</v>
+        <v>1272621523.83</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>251070477.59</v>
@@ -3353,10 +3353,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>1722363855.64</v>
+        <v>1722511701.58</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>250878435.62</v>
+        <v>250930724.7</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>57612870.57</v>
@@ -3368,16 +3368,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="9" t="n">
-        <v>5176317.14</v>
+        <v>5176625.29</v>
       </c>
       <c r="O50" s="9" t="n">
-        <v>6615435.36</v>
+        <v>6615829.18</v>
       </c>
       <c r="P50" s="9" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>364512204.13</v>
+        <v>364565195.19</v>
       </c>
       <c r="R50" s="10" t="n">
         <v>0.5184969295746537</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>1424366772.25</v>
+        <v>1424679587.67</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>287468135.92</v>
@@ -3411,10 +3411,10 @@
         <v>28011807</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>1926649173.68</v>
+        <v>1926961989.1</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>254225570.01</v>
+        <v>254328905.52</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>59780017.61</v>
@@ -3426,16 +3426,16 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="9" t="n">
-        <v>5693509.01</v>
+        <v>5694203.48</v>
       </c>
       <c r="O51" s="9" t="n">
-        <v>8128260.43</v>
+        <v>8129251.89</v>
       </c>
       <c r="P51" s="9" t="n">
         <v>13969238.87</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>369327847.69</v>
+        <v>369432869.12</v>
       </c>
       <c r="R51" s="10" t="n">
         <v>0.5173698555705437</v>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>2085015517.59</v>
+        <v>2085636839.91</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>438830798.95</v>
@@ -3469,10 +3469,10 @@
         <v>20465067</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>2873985415.65</v>
+        <v>2874606737.97</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>406416243.2</v>
+        <v>406621366.14</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>92879457.39</v>
@@ -3484,23 +3484,77 @@
         <v>15738266.69</v>
       </c>
       <c r="N52" s="9" t="n">
-        <v>8697713.74</v>
+        <v>8698935.67</v>
       </c>
       <c r="O52" s="9" t="n">
-        <v>25802247.09</v>
+        <v>25805872.02</v>
       </c>
       <c r="P52" s="9" t="n">
         <v>10232009.27</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>588632447.84</v>
+        <v>588842417.65</v>
       </c>
       <c r="R52" s="10" t="n">
         <v>0.4928123695831447</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>2214587588.52</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>590872240.37</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>88600562.34999999</v>
+      </c>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n">
+        <v>47959130.31</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>181516613</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>67156727</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>3190692861.55</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>396415830.19</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>126606680.82</v>
+      </c>
+      <c r="L53" s="9" t="n">
+        <v>22293136.54</v>
+      </c>
+      <c r="M53" s="9" t="n"/>
+      <c r="N53" s="9" t="n">
+        <v>9367056.460000001</v>
+      </c>
+      <c r="O53" s="9" t="n">
+        <v>35452610.41</v>
+      </c>
+      <c r="P53" s="9" t="n">
+        <v>33049467.84</v>
+      </c>
+      <c r="Q53" s="9" t="n">
+        <v>623184782.26</v>
+      </c>
+      <c r="R53" s="10" t="n">
+        <v>0.4799759022140718</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R52"/>
+  <autoFilter ref="A2:R53"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3516,7 +3570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6375,8 +6429,59 @@
         <v>974687583</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3170000000</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>592211008.3099999</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>88600562.34999999</v>
+      </c>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n">
+        <v>47959130.31</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>185536555</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>67547059</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>4151854314.97</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>879992000</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>126810450.73</v>
+      </c>
+      <c r="L53" s="9" t="n">
+        <v>22293136.54</v>
+      </c>
+      <c r="M53" s="9" t="n"/>
+      <c r="N53" s="9" t="n">
+        <v>13001876.55</v>
+      </c>
+      <c r="O53" s="9" t="n">
+        <v>50299564.84</v>
+      </c>
+      <c r="P53" s="9" t="n">
+        <v>33184209.53</v>
+      </c>
+      <c r="Q53" s="9" t="n">
+        <v>1125581238.19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:Q52"/>
+  <autoFilter ref="A2:Q53"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -6391,7 +6496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7877,7 +7982,7 @@
         <v>10158090</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>0.6379</v>
+        <v>0.6378</v>
       </c>
       <c r="I35" s="11" t="n">
         <v>0.4234000000000001</v>
@@ -8393,7 +8498,7 @@
         <v>11226252</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>0.6766</v>
+        <v>0.6765000000000001</v>
       </c>
       <c r="I47" s="11" t="n">
         <v>0.4061</v>
@@ -8436,7 +8541,7 @@
         <v>13207850</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>0.6995</v>
+        <v>0.6994</v>
       </c>
       <c r="I48" s="11" t="n">
         <v>0.4791</v>
@@ -8479,7 +8584,7 @@
         <v>11477871</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>0.7086</v>
+        <v>0.7084999999999999</v>
       </c>
       <c r="I49" s="11" t="n">
         <v>0.4597</v>
@@ -8522,7 +8627,7 @@
         <v>12724485</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.6546</v>
       </c>
       <c r="I50" s="11" t="n">
         <v>0.4323</v>
@@ -8565,7 +8670,7 @@
         <v>15736949</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>0.7066</v>
+        <v>0.7064</v>
       </c>
       <c r="I51" s="11" t="n">
         <v>0.5035000000000001</v>
@@ -8608,7 +8713,7 @@
         <v>38042084</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>0.649</v>
+        <v>0.6487999999999999</v>
       </c>
       <c r="I52" s="11" t="n">
         <v>0.4738</v>
@@ -8626,15 +8731,54 @@
         <v>0.302</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>1526545200</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>42862000.8</v>
+      </c>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n">
+        <v>298615538.59</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>46953298.28</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>47830508</v>
+      </c>
+      <c r="H53" s="11" t="n">
+        <v>0.6893</v>
+      </c>
+      <c r="I53" s="11" t="n">
+        <v>0.4838</v>
+      </c>
+      <c r="J53" s="11" t="n"/>
+      <c r="K53" s="11" t="n">
+        <v>0.5054</v>
+      </c>
+      <c r="L53" s="11" t="n">
+        <v>0.9790000000000001</v>
+      </c>
+      <c r="M53" s="11" t="n">
+        <v>0.2635</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M52"/>
+  <autoFilter ref="A2:M53"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -8665,7 +8809,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-21. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -505,7 +505,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Contracts traded  (one-sided, $1 face)</t>
+          <t>Taker Volume  (contracts, one-sided, $1 face)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1226362956.81</v>
+        <v>1436291212.47</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1404325051.39</v>
+        <v>1614253307.05</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>290715570.41</v>
+        <v>299227228.99</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>524811.64</v>
+        <v>466111.76</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>9360263.75</v>
+        <v>8313323.71</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>354058552.43</v>
+        <v>361464571.1</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1019800702.49</v>
+        <v>1205571433.13</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1203205612</v>
+        <v>1388976342.64</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>223747522.24</v>
+        <v>231812202.33</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>516297.55</v>
+        <v>458019.1</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>9237365.98</v>
+        <v>8194673.86</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>289059291.55</v>
+        <v>296023001.07</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>766411149.46</v>
+        <v>889406809.65</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>882453696.5</v>
+        <v>1005449356.69</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>197403208.75</v>
+        <v>202393041.66</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -758,16 +758,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>374709.46</v>
+        <v>334880.88</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5399345.73</v>
+        <v>4825438.94</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>239492546.32</v>
+        <v>243868643.86</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>983766835.9400001</v>
+        <v>1155122773.3</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1168404984.96</v>
+        <v>1339760922.32</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>236065236.83</v>
+        <v>243083730.79</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>324588.34</v>
+        <v>288784.6</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7358538.5</v>
+        <v>6546854.26</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>305861948.24</v>
+        <v>312032954.22</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1097592214.3</v>
+        <v>1292325892.67</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1302672251.88</v>
+        <v>1497405930.25</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>250951862.97</v>
+        <v>259386245.31</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>709927.33</v>
+        <v>631739.51</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7693355.22</v>
+        <v>6846047.82</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>328055876.78</v>
+        <v>335564763.9</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1011527784.84</v>
+        <v>1187470480.24</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1233700904.35</v>
+        <v>1409643599.75</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>229526393.68</v>
+        <v>236784485.26</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1255743.57</v>
+        <v>1121124.6</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>8409730.25</v>
+        <v>7508185.34</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>309201324.16</v>
+        <v>315423251.85</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>961948549.76</v>
+        <v>1139472600.21</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1145555711.3</v>
+        <v>1323079761.75</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>214891003.65</v>
+        <v>224391932.61</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>814775.3</v>
+        <v>727221.0699999999</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6850517.26</v>
+        <v>6114373.5</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>281208141.41</v>
+        <v>289885372.39</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1073052479.18</v>
+        <v>1265084691.76</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1277718376.66</v>
+        <v>1469750589.24</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>240126698.78</v>
+        <v>247904300.21</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2353400.76</v>
+        <v>2089370.81</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7569917.55</v>
+        <v>6720642.34</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>313750494.97</v>
+        <v>320414791.25</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>960779939.2</v>
+        <v>1136156308.74</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1185453256.32</v>
+        <v>1360829625.86</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>212552972.89</v>
+        <v>220224867.55</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2490170.74</v>
+        <v>2216238.86</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8929352.02</v>
+        <v>7947076.32</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>296187836.34</v>
+        <v>302603523.43</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>686517234.2</v>
+        <v>817335136</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>813428925.23</v>
+        <v>944246827.03</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>150993587.7</v>
+        <v>157384944.68</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1897058.49</v>
+        <v>1682384.8</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3485516.09</v>
+        <v>3091090.4</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>196258122.18</v>
+        <v>202040379.78</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>970917726.73</v>
+        <v>1149010810.82</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1130474380.97</v>
+        <v>1308567465.06</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>227542692.71</v>
+        <v>235935015.83</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,16 +1222,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2642020.14</v>
+        <v>2341917.81</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5513109.2</v>
+        <v>4886884.99</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>286540370.5</v>
+        <v>294006367.08</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1042733507.13</v>
+        <v>1239522017.27</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1244217697.2</v>
+        <v>1441006207.34</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>230883959.56</v>
+        <v>240227545.57</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2865666.55</v>
+        <v>2540876.53</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>7026074.43</v>
+        <v>6229750.5</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>305688771.98</v>
+        <v>313911244.04</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1046533320.81</v>
+        <v>1228237582.97</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1268580420.62</v>
+        <v>1450284682.78</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238383791.66</v>
+        <v>245766950.44</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3737712.41</v>
+        <v>3332864.81</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>7838302.01</v>
+        <v>6989302.03</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>315850542.88</v>
+        <v>321979854.09</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1026533540.76</v>
+        <v>1206694582.99</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1228677419.79</v>
+        <v>1408838462.02</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>246157420.46</v>
+        <v>254177958.98</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3558662.26</v>
+        <v>3170561.57</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>7537351.75</v>
+        <v>6715343.04</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>315577488.63</v>
+        <v>322387917.75</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1275238563.42</v>
+        <v>1502784885.58</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1517960040.67</v>
+        <v>1745506362.83</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>295677291.2</v>
+        <v>307040468.04</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4271132.75</v>
+        <v>3811143.19</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>9581183.539999999</v>
+        <v>8549315.720000001</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>378773603.37</v>
+        <v>388644922.83</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1123214947.24</v>
+        <v>1333524682.78</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1375390108.57</v>
+        <v>1585699844.11</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>251892996.64</v>
+        <v>261226724.51</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3520550.35</v>
+        <v>3122211.65</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>11255917.87</v>
+        <v>9982347.77</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>341112421.7</v>
+        <v>348774240.77</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>780519684.51</v>
+        <v>918409295.78</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>941936530.04</v>
+        <v>1079826141.31</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>182891236.98</v>
+        <v>188477035.9</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2893238.68</v>
+        <v>2573290.38</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4978972.16</v>
+        <v>4428373.38</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>240375290.76</v>
+        <v>245090542.6</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>925228616.4400001</v>
+        <v>1097888712.22</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1103232000.26</v>
+        <v>1275892096.04</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>208940405.61</v>
+        <v>215918640.68</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3099140.15</v>
+        <v>2738069.66</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>6218653.61</v>
+        <v>5494139.01</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>270758709.38</v>
+        <v>276651359.36</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1099268146.55</v>
+        <v>1303187541.17</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1314568440.37</v>
+        <v>1518487834.99</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>244623589.59</v>
+        <v>252864781.27</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3671184.83</v>
+        <v>3247080.99</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>7710541.88</v>
+        <v>6819802.08</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>319477737.01</v>
+        <v>326404085.04</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>967600829.9299999</v>
+        <v>1144724149.08</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1190921835.51</v>
+        <v>1368045154.66</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>210535313.9</v>
+        <v>217696505.83</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3281802.63</v>
+        <v>2916877.12</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>7536306.42</v>
+        <v>6698294.28</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>283818303.62</v>
+        <v>289776557.9</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1003092587.3</v>
+        <v>1190738004.6</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1198249275.36</v>
+        <v>1385894692.66</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>222089714.94</v>
+        <v>229729503.14</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3891012.63</v>
+        <v>3441497</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>6335893.6</v>
+        <v>5603929.09</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>281021116.1</v>
+        <v>287479424.16</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1362288839.85</v>
+        <v>1612355750.21</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1634505594.97</v>
+        <v>1884572505.33</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>306763353.05</v>
+        <v>316887393.13</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>6136471.87</v>
+        <v>5435365.88</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>10270564.89</v>
+        <v>9097129.279999999</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>388022521.31</v>
+        <v>396272019.79</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1156904574.94</v>
+        <v>1377194770.15</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1409404542.59</v>
+        <v>1629694737.8</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>247799030.55</v>
+        <v>256709061.04</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3795223.48</v>
+        <v>3355926.66</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>9929359.369999999</v>
+        <v>8780036.82</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>325996838.17</v>
+        <v>333318249.3</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>870311652.5700001</v>
+        <v>1037097767.79</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1039415864.94</v>
+        <v>1206201980.16</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>193435927.08</v>
+        <v>200202084.89</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3256065.33</v>
+        <v>2871147.64</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5684209.25</v>
+        <v>5012247.1</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>245278013.29</v>
+        <v>250987291.26</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1002271713.67</v>
+        <v>1198842915.31</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1209609121.63</v>
+        <v>1406180323.27</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>217002066.51</v>
+        <v>225000637.9</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2934141.59</v>
+        <v>2585282.48</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6937706.54</v>
+        <v>6112837.63</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>280974319.72</v>
+        <v>287799163.09</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1105968178.49</v>
+        <v>1317392590.05</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1351823078.14</v>
+        <v>1563247489.7</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>242485269.66</v>
+        <v>251063889.23</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2693260.53</v>
+        <v>2381326.04</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>8764081.130000001</v>
+        <v>7749021.8</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>322799090.32</v>
+        <v>330050716.07</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>932849708.41</v>
+        <v>1110051660.15</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1136797522.86</v>
+        <v>1313999474.6</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>196525951</v>
+        <v>203729999.45</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2927930.48</v>
+        <v>2592783.58</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6577853.44</v>
+        <v>5824916.44</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>259480076.28</v>
+        <v>265596040.83</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1162035394.15</v>
+        <v>1383849280.61</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1354871878.22</v>
+        <v>1576685764.68</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>252354442.13</v>
+        <v>261336616.92</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>4229209.57</v>
+        <v>3726726.16</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4541696.97</v>
+        <v>4002086.12</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>311967067.3</v>
+        <v>319907147.83</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1440011463.71</v>
+        <v>1727299533.05</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1740068129.74</v>
+        <v>2027356199.08</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>284720110.8</v>
+        <v>296354688.53</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>4067082.35</v>
+        <v>3587884.98</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5978504.09</v>
+        <v>5274096.57</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>375590886.1</v>
+        <v>386041858.94</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1319736758.13</v>
+        <v>1572726221.5</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1579499842.25</v>
+        <v>1832489305.62</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>283379052.83</v>
+        <v>293607638.86</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3050964.21</v>
+        <v>2694875.52</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>7438402.73</v>
+        <v>6570240.77</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>363619784.29</v>
+        <v>372624119.67</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1097010773.18</v>
+        <v>1305393622.02</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1283051799.29</v>
+        <v>1491434648.13</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>243430627.18</v>
+        <v>251860988.55</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1660629.78</v>
+        <v>1463492.63</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>7202063.73</v>
+        <v>6347090.32</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>302148212.22</v>
+        <v>309526463.02</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1142137766.09</v>
+        <v>1368369925.8</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143033.33</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1366028880.04</v>
+        <v>1592261039.75</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>239662388.39</v>
+        <v>248806135.95</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.03</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1298507.66</v>
+        <v>1142560.11</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>9234258.84</v>
+        <v>8125247.26</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>307455529.63</v>
+        <v>315334318.06</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174721986673</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1192859316.47</v>
+        <v>1428040946.31</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482292.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1436516323.14</v>
+        <v>1671697952.98</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>253633253.61</v>
+        <v>263139103.74</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009606.34</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2145314.55</v>
+        <v>1891007.99</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>6745131.44</v>
+        <v>5945560.5</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>327988101.8</v>
+        <v>336440074.43</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918139984984</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1226946284.86</v>
+        <v>1456208465.75</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1494286575.73</v>
+        <v>1723548756.62</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>272960332.59</v>
+        <v>282236552.84</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2511839.25</v>
+        <v>2226974.22</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>7248299.5</v>
+        <v>6426277.53</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>361202556.02</v>
+        <v>369371889.28</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1348640208.39</v>
+        <v>1613187384.9</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563894</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1622960353.14</v>
+        <v>1887507529.65</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>278441295</v>
+        <v>289612211.1</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969403.31</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2307534.73</v>
+        <v>2038733.84</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>8088523.91</v>
+        <v>7146305.18</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>361828260.43</v>
+        <v>371788156.91</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320960096582</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1778328115.67</v>
+        <v>2119622306.57</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439695.17</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2122391177.73</v>
+        <v>2463685368.63</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>364516044.18</v>
+        <v>378506228.95</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814559.69</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3919085.64</v>
+        <v>3468831.5</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>6647148.87</v>
+        <v>5883474.22</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>465535046.46</v>
+        <v>478311302.43</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201375328469</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1364426641.21</v>
+        <v>1628363240.71</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1651196427.81</v>
+        <v>1915133027.31</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>283725983.4</v>
+        <v>294597583.2</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4917248.96</v>
+        <v>4346486.72</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>7352675.72</v>
+        <v>6499225.01</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>374623697.77</v>
+        <v>384071084.61</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1038079761.61</v>
+        <v>1241343575.09</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184348327.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1347456478.4</v>
+        <v>1550720291.88</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>218490363.17</v>
+        <v>227090737.31</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663233.49</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3629112.95</v>
+        <v>3230018.51</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4592111</v>
+        <v>4087115.43</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>316840160.6</v>
+        <v>324536444.73</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156022523452979</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1143696049.56</v>
+        <v>1377183390.82</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233679.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1422178469.17</v>
+        <v>1655665810.43</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>228261114.03</v>
+        <v>238172777.86</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723993.31</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>3388661.07</v>
+        <v>2993006.14</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>5521934.41</v>
+        <v>4877201.72</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>314044894.68</v>
+        <v>322916170.91</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586814200401954</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1339531864.58</v>
+        <v>1613722602.08</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803300.35</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1715105770.18</v>
+        <v>1989296507.68</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>269969322.97</v>
+        <v>282618229.62</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467972.27</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2886712.04</v>
+        <v>2562076.36</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>7560653.61</v>
+        <v>6710392.86</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>389862157.98</v>
+        <v>401336168.19</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.3748043859905762</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1172397330.73</v>
+        <v>1427762935.73</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>221857126.57</v>
@@ -2947,10 +2947,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1562182321.79</v>
+        <v>1817547926.79</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>220144842.45</v>
+        <v>232863017.83</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>61180264.16</v>
@@ -2962,16 +2962,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2632938.73</v>
+        <v>2342310.48</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>7180755.21</v>
+        <v>6388131.25</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>332030452.52</v>
+        <v>343665375.71</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.3738082799669966</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1225019760.06</v>
+        <v>1480854495.23</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>197998279.3</v>
@@ -3005,10 +3005,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1582899862.13</v>
+        <v>1838734597.3</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>236977906.37</v>
+        <v>248376276.39</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>51757451.41</v>
@@ -3020,16 +3020,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>5234100.38</v>
+        <v>4638581.75</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6970414.7</v>
+        <v>6177343.96</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>339794528.36</v>
+        <v>349804309.01</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3916156197964661</v>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1838988685.01</v>
+        <v>2194891335.65</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>306596831.13</v>
@@ -3063,10 +3063,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2463895175.04</v>
+        <v>2819797825.68</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>385282514.13</v>
+        <v>400038602.04</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>76961502.72</v>
@@ -3078,16 +3078,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>10618454.87</v>
+        <v>9471678.58</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>18123466.62</v>
+        <v>16166160.97</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>558884637.1799999</v>
+        <v>570536643.16</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0.40067966485108</v>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1909382742.4</v>
+        <v>2305299214.24</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>376107142.6</v>
@@ -3121,10 +3121,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>2709902190.69</v>
+        <v>3105818662.53</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>383378240.99</v>
+        <v>402169103.4</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>102191529.21</v>
@@ -3136,16 +3136,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>12010667.4</v>
+        <v>10742331.73</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>22113775.87</v>
+        <v>19778544.22</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>605774205.54</v>
+        <v>620961500.63</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0.442865215754716</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1124667809.74</v>
+        <v>1370755778.1</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>250093696.52</v>
@@ -3179,10 +3179,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1556286022.27</v>
+        <v>1802373990.63</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>215835789.84</v>
+        <v>227511230.16</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>65852392.81</v>
@@ -3194,16 +3194,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>3872669.67</v>
+        <v>3449564.96</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>5477983.7</v>
+        <v>4879491.98</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>337196767.5</v>
+        <v>347850611.4</v>
       </c>
       <c r="R47" s="10" t="n">
         <v>0.4207679702437824</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1315050738.51</v>
+        <v>1605866475.56</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>251713084.28</v>
@@ -3237,10 +3237,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>1713373107.05</v>
+        <v>2004188844.1</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>242225186.59</v>
+        <v>256669523.34</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>62840730.8</v>
@@ -3252,16 +3252,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>4582960.79</v>
+        <v>4066667.4</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>5976644.26</v>
+        <v>5303345.47</v>
       </c>
       <c r="P48" s="9" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>349207645</v>
+        <v>362462389.56</v>
       </c>
       <c r="R48" s="10" t="n">
         <v>0.4544083188194561</v>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>1345743299.59</v>
+        <v>1642708321.87</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>255216837.43</v>
@@ -3295,10 +3295,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>1766096135.42</v>
+        <v>2063061157.7</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>244405204.6</v>
+        <v>257252804.75</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>63158844.13</v>
@@ -3310,16 +3310,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="9" t="n">
-        <v>5332063.8</v>
+        <v>4712177.07</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>6162132.61</v>
+        <v>5445745.05</v>
       </c>
       <c r="P49" s="9" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>355913717.33</v>
+        <v>367425043.19</v>
       </c>
       <c r="R49" s="10" t="n">
         <v>0.4715622688002217</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>1272621523.83</v>
+        <v>1539510329.86</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>251070477.59</v>
@@ -3353,10 +3353,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>1722511701.58</v>
+        <v>1989400507.61</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>250930724.7</v>
+        <v>263408298.27</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>57612870.57</v>
@@ -3368,16 +3368,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="9" t="n">
-        <v>5176625.29</v>
+        <v>4619968.46</v>
       </c>
       <c r="O50" s="9" t="n">
-        <v>6615829.18</v>
+        <v>5904410.78</v>
       </c>
       <c r="P50" s="9" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>364565195.19</v>
+        <v>375774693.53</v>
       </c>
       <c r="R50" s="10" t="n">
         <v>0.5184969295746537</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>1424679587.67</v>
+        <v>1765206715.63</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>287468135.92</v>
@@ -3411,10 +3411,10 @@
         <v>28011807</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>1926961989.1</v>
+        <v>2267489117.06</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>254328905.52</v>
+        <v>281262904.2</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>59780017.61</v>
@@ -3426,16 +3426,16 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="9" t="n">
-        <v>5694203.48</v>
+        <v>5175358.52</v>
       </c>
       <c r="O51" s="9" t="n">
-        <v>8129251.89</v>
+        <v>7388529.97</v>
       </c>
       <c r="P51" s="9" t="n">
         <v>13969238.87</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>369432869.12</v>
+        <v>395107300.93</v>
       </c>
       <c r="R51" s="10" t="n">
         <v>0.5173698555705437</v>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>2085636839.91</v>
+        <v>2536929451.93</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>438830798.95</v>
@@ -3469,10 +3469,10 @@
         <v>20465067</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>2874606737.97</v>
+        <v>3325899349.99</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>406621366.14</v>
+        <v>439508240.97</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>92879457.39</v>
@@ -3484,16 +3484,16 @@
         <v>15738266.69</v>
       </c>
       <c r="N52" s="9" t="n">
-        <v>8698935.67</v>
+        <v>7897917.47</v>
       </c>
       <c r="O52" s="9" t="n">
-        <v>25805872.02</v>
+        <v>23429607.39</v>
       </c>
       <c r="P52" s="9" t="n">
         <v>10232009.27</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>588842417.65</v>
+        <v>618552009.65</v>
       </c>
       <c r="R52" s="10" t="n">
         <v>0.4928123695831447</v>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>2214587588.52</v>
+        <v>2708237290.11</v>
       </c>
       <c r="C53" s="6" t="n">
         <v>590872240.37</v>
@@ -3514,7 +3514,9 @@
       <c r="D53" s="6" t="n">
         <v>88600562.34999999</v>
       </c>
-      <c r="E53" s="6" t="n"/>
+      <c r="E53" s="6" t="n">
+        <v>183536981</v>
+      </c>
       <c r="F53" s="6" t="n">
         <v>47959130.31</v>
       </c>
@@ -3525,10 +3527,10 @@
         <v>67156727</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>3190692861.55</v>
+        <v>3867879544.14</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>396415830.19</v>
+        <v>422369249.13</v>
       </c>
       <c r="K53" s="9" t="n">
         <v>126606680.82</v>
@@ -3536,21 +3538,23 @@
       <c r="L53" s="9" t="n">
         <v>22293136.54</v>
       </c>
-      <c r="M53" s="9" t="n"/>
+      <c r="M53" s="9" t="n">
+        <v>34860196.13</v>
+      </c>
       <c r="N53" s="9" t="n">
-        <v>9367056.460000001</v>
+        <v>8425248.460000001</v>
       </c>
       <c r="O53" s="9" t="n">
-        <v>35452610.41</v>
+        <v>31888037.89</v>
       </c>
       <c r="P53" s="9" t="n">
         <v>33049467.84</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>623184782.26</v>
+        <v>679492016.8099999</v>
       </c>
       <c r="R53" s="10" t="n">
-        <v>0.4799759022140718</v>
+        <v>0.516687833119383</v>
       </c>
     </row>
   </sheetData>
@@ -3595,7 +3599,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Contracts traded  (one-sided, $1 face)</t>
+          <t>Taker Volume  (contracts, one-sided, $1 face)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -3720,7 +3724,7 @@
         <v>1589915312.44</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>391416000</v>
+        <v>282423000</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>51252892</v>
@@ -3730,16 +3734,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>597732.41</v>
+        <v>451391.81</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>10763477.26</v>
+        <v>8128295.13</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2079977.15</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>456546255.58</v>
+        <v>344771732.85</v>
       </c>
     </row>
     <row r="4">
@@ -3771,7 +3775,7 @@
         <v>1425882342.19</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>344224000</v>
+        <v>248372000</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51599931.62</v>
@@ -3781,16 +3785,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>621241.21</v>
+        <v>472485.7</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>11260037.98</v>
+        <v>8563834.51</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3993660.15</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>412183842.84</v>
+        <v>313486883.86</v>
       </c>
     </row>
     <row r="5">
@@ -3822,7 +3826,7 @@
         <v>945257982.33</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>229325360</v>
+        <v>165467830</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>32367279.06</v>
@@ -3832,16 +3836,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>398141.79</v>
+        <v>302668.26</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>5884200.74</v>
+        <v>4473182.21</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4439328.3</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>272579713.29</v>
+        <v>207215691.23</v>
       </c>
     </row>
     <row r="6">
@@ -3875,7 +3879,7 @@
         <v>1337472266.44</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>319240000</v>
+        <v>230345000</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>48161416.36</v>
@@ -3887,16 +3891,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>362287.47</v>
+        <v>278001.58</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>8323241.01</v>
+        <v>6386845.64</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8118311.67</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>390784413.02</v>
+        <v>299868731.77</v>
       </c>
     </row>
     <row r="7">
@@ -3930,7 +3934,7 @@
         <v>1508462724.71</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>360880000</v>
+        <v>260390000</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>48492980.6</v>
@@ -3942,16 +3946,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>822533.66</v>
+        <v>630447.04</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>9005629.640000001</v>
+        <v>6902541.21</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>13080537.68</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>440136137.2</v>
+        <v>337350962.14</v>
       </c>
     </row>
     <row r="8">
@@ -3985,7 +3989,7 @@
         <v>1404494465.02</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>327568000</v>
+        <v>236354000</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50721504.22</v>
@@ -3997,16 +4001,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1460046.62</v>
+        <v>1125323.01</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>9946253.73</v>
+        <v>7666021.07</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>12037420</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>409276921.85</v>
+        <v>315447965.57</v>
       </c>
     </row>
     <row r="9">
@@ -4040,7 +4044,7 @@
         <v>1345716396.68</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>322016000</v>
+        <v>232348000</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>45150709.09</v>
@@ -4052,16 +4056,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>962433.0699999999</v>
+        <v>735948.33</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>8208439.79</v>
+        <v>6276787.15</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8928506.67</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>390209556.44</v>
+        <v>298383419.06</v>
       </c>
     </row>
     <row r="10">
@@ -4095,7 +4099,7 @@
         <v>1495901158.14</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>358104000</v>
+        <v>258387000</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44119482.44</v>
@@ -4107,16 +4111,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2778971.06</v>
+        <v>2122262.71</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>9002713.9</v>
+        <v>6875251.15</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11733055.02</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>433750822.73</v>
+        <v>331249651.63</v>
       </c>
     </row>
     <row r="11">
@@ -4150,7 +4154,7 @@
         <v>1395900552.75</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>324792000</v>
+        <v>234351000</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48633763.9</v>
@@ -4162,16 +4166,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2932449.05</v>
+        <v>2264663.99</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>10626534.78</v>
+        <v>8206632.14</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17177521.22</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>410713156.22</v>
+        <v>317184468.51</v>
       </c>
     </row>
     <row r="12">
@@ -4205,7 +4209,7 @@
         <v>989849374.5</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>239180160</v>
+        <v>172578480</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28257376.93</v>
@@ -4217,16 +4221,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>2270517.48</v>
+        <v>1729027.12</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>4301543.57</v>
+        <v>3275678.59</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5899079.07</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>285838858.06</v>
+        <v>217669822.71</v>
       </c>
     </row>
     <row r="13">
@@ -4260,7 +4264,7 @@
         <v>1343154413.9</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>327568000</v>
+        <v>236354000</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32891944.15</v>
@@ -4272,16 +4276,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>3012908.88</v>
+        <v>2287482.11</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>6389321.75</v>
+        <v>4850946.3</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>9798821.01</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>388240565.14</v>
+        <v>294762762.91</v>
       </c>
     </row>
     <row r="14">
@@ -4315,7 +4319,7 @@
         <v>1504161748.55</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>360880000</v>
+        <v>260390000</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44498190.03</v>
@@ -4327,16 +4331,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>3398429.19</v>
+        <v>2597579.3</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>8427781.550000001</v>
+        <v>6441749.92</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11851028.97</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>438258374.61</v>
+        <v>334981493.09</v>
       </c>
     </row>
     <row r="15">
@@ -4370,7 +4374,7 @@
         <v>1443671258.72</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>338672000</v>
+        <v>244366000</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47657304.2</v>
@@ -4382,16 +4386,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>4351229.76</v>
+        <v>3337764.47</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>9198423.59</v>
+        <v>7055975.69</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11585255.98</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>418444696.08</v>
+        <v>320982782.89</v>
       </c>
     </row>
     <row r="16">
@@ -4425,7 +4429,7 @@
         <v>1403857232.44</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>333120000</v>
+        <v>240360000</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>45100146.59</v>
@@ -4437,16 +4441,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3990201.72</v>
+        <v>3045353.89</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>8569320.26</v>
+        <v>6540173.82</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>6068522.46</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>404295736.12</v>
+        <v>308561741.85</v>
       </c>
     </row>
     <row r="17">
@@ -4480,7 +4484,7 @@
         <v>1743817609.09</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>416400000</v>
+        <v>300450000</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>49047089.99</v>
@@ -4492,16 +4496,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4926149.54</v>
+        <v>3750318.72</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>11163433.78</v>
+        <v>8498815.23</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11193826.09</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>501862732.34</v>
+        <v>382072282.96</v>
       </c>
     </row>
     <row r="18">
@@ -4535,7 +4539,7 @@
         <v>1653362788.96</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>388640000</v>
+        <v>280420000</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>57064827.84</v>
@@ -4547,16 +4551,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>4126757.68</v>
+        <v>3162643.13</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>13312891.88</v>
+        <v>10202664.99</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11617145.57</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>480660247.37</v>
+        <v>368365905.94</v>
       </c>
     </row>
     <row r="19">
@@ -4590,7 +4594,7 @@
         <v>1089384247.07</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>257168640</v>
+        <v>185557920</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>37038769.64</v>
@@ -4602,16 +4606,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>3288970.22</v>
+        <v>2521701.95</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>5772252.5</v>
+        <v>4425671.08</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5588473.52</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>316027555.06</v>
+        <v>242302985.39</v>
       </c>
     </row>
     <row r="20">
@@ -4645,7 +4649,7 @@
         <v>1340192319.16</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>322016000</v>
+        <v>232348000</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38155857.92</v>
@@ -4657,16 +4661,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>3635012.06</v>
+        <v>2765248.19</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>7401482.81</v>
+        <v>5630500.44</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6942822.13</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>385786786.29</v>
+        <v>293478040.05</v>
       </c>
     </row>
     <row r="21">
@@ -4700,7 +4704,7 @@
         <v>1587465380.89</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>380312000</v>
+        <v>274411000</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44959266.73</v>
@@ -4712,16 +4716,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>4356201.81</v>
+        <v>3317581.3</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>9258759.859999999</v>
+        <v>7051254.73</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10509589.79</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>457786942.94</v>
+        <v>348639817.3</v>
       </c>
     </row>
     <row r="22">
@@ -4755,7 +4759,7 @@
         <v>1415070801.07</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>330344000</v>
+        <v>238357000</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44531856.81</v>
@@ -4767,16 +4771,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>3953306.49</v>
+        <v>3028055.84</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>9255640.52</v>
+        <v>7089406.4</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11732475.1</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>406240612.16</v>
+        <v>311162127.39</v>
       </c>
     </row>
     <row r="23">
@@ -4810,7 +4814,7 @@
         <v>1458033835.64</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>349776000</v>
+        <v>252378000</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35238750.52</v>
@@ -4822,16 +4826,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>4682007.62</v>
+        <v>3538290.77</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>8063191.77</v>
+        <v>6093522.11</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3733039.67</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>411461171.27</v>
+        <v>310949784.75</v>
       </c>
     </row>
     <row r="24">
@@ -4865,7 +4869,7 @@
         <v>1954426235.36</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>466368000</v>
+        <v>336504000</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43368591.4</v>
@@ -4877,16 +4881,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>7290541.98</v>
+        <v>5508799.46</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>12558859.76</v>
+        <v>9489588.029999999</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9679849.300000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>551227496.37</v>
+        <v>416512482.13</v>
       </c>
     </row>
     <row r="25">
@@ -4920,7 +4924,7 @@
         <v>1734605071.38</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>410848000</v>
+        <v>296444000</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45347988.13</v>
@@ -4932,16 +4936,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>4660735.14</v>
+        <v>3539329.41</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>12573164.11</v>
+        <v>9547972.210000001</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10164913.41</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>492714566.97</v>
+        <v>374163969.34</v>
       </c>
     </row>
     <row r="26">
@@ -4975,7 +4979,7 @@
         <v>1291826561.79</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>310912000</v>
+        <v>224336000</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31546614.61</v>
@@ -4987,16 +4991,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>3901201.2</v>
+        <v>2947278.16</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>7274515.54</v>
+        <v>5495748.53</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5301039.25</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>365240331.65</v>
+        <v>275931641.59</v>
       </c>
     </row>
     <row r="27">
@@ -5030,7 +5034,7 @@
         <v>1529950067.26</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>366432000</v>
+        <v>264396000</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38758367.74</v>
@@ -5042,16 +5046,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>3577476.75</v>
+        <v>2710122.36</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>8872272.810000001</v>
+        <v>6721202.28</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7686001.99</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>433305882.68</v>
+        <v>328251457.74</v>
       </c>
     </row>
     <row r="28">
@@ -5085,7 +5089,7 @@
         <v>1668694671.32</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>394192000</v>
+        <v>284426000</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47966998.93</v>
@@ -5097,16 +5101,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>3227798.28</v>
+        <v>2463077.86</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>11010694.22</v>
+        <v>8402073.109999999</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10719319.3</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>477548344.21</v>
+        <v>364409002.67</v>
       </c>
     </row>
     <row r="29">
@@ -5140,7 +5144,7 @@
         <v>1396519155.63</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>330344000</v>
+        <v>238357000</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33561811.06</v>
@@ -5152,16 +5156,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>3640235.79</v>
+        <v>2768346.1</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>8615263.130000001</v>
+        <v>6551781.66</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>10035145.32</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>396311386.54</v>
+        <v>301389015.37</v>
       </c>
     </row>
     <row r="30">
@@ -5195,7 +5199,7 @@
         <v>1686858008.05</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>413624000</v>
+        <v>298447000</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30240724.05</v>
@@ -5207,16 +5211,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>5188369.11</v>
+        <v>3903667.61</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>6157754.61</v>
+        <v>4633021.8</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>6248721.69</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>476497589.52</v>
+        <v>358511155.2</v>
       </c>
     </row>
     <row r="31">
@@ -5250,7 +5254,7 @@
         <v>2232774110.14</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>535768000</v>
+        <v>386579000</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46829617.02</v>
@@ -5262,16 +5266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>5320843.96</v>
+        <v>4034210.31</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>8220245.64</v>
+        <v>6232507.47</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>12259956.04</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>630508778.4299999</v>
+        <v>478045406.6</v>
       </c>
     </row>
     <row r="32">
@@ -5305,7 +5309,7 @@
         <v>1962302275.15</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>471920000</v>
+        <v>340510000</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>46033156.99</v>
@@ -5317,16 +5321,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>3750171.98</v>
+        <v>2840827.03</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>9584871.42</v>
+        <v>7260723.51</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14340728.19</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>555274713.02</v>
+        <v>420631220.16</v>
       </c>
     </row>
     <row r="33">
@@ -5360,7 +5364,7 @@
         <v>1589670533.29</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>388640000</v>
+        <v>280420000</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36835334.14</v>
@@ -5372,16 +5376,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1997237.73</v>
+        <v>1505004.13</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>9135804.35</v>
+        <v>6884219.7</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>5454763.56</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>450235674.48</v>
+        <v>339271856.24</v>
       </c>
     </row>
     <row r="34">
@@ -5415,7 +5419,7 @@
         <v>1747242420.22</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>421952000</v>
+        <v>304456000</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33675810.27</v>
@@ -5427,16 +5431,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1629230.19</v>
+        <v>1230182.01</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>12075528.88</v>
+        <v>9117863.470000001</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8660771.18</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>493416336.83</v>
+        <v>372563623.24</v>
       </c>
     </row>
     <row r="35">
@@ -5470,7 +5474,7 @@
         <v>1826702297.86</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>438608000</v>
+        <v>316474000</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39150985.29</v>
@@ -5482,16 +5486,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>2654002.85</v>
+        <v>2011590.11</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>8744699.619999999</v>
+        <v>6628007.69</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>12178807.65</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>515971489.35</v>
+        <v>391078384.69</v>
       </c>
     </row>
     <row r="36">
@@ -5525,7 +5529,7 @@
         <v>1810647593.14</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>427504000</v>
+        <v>308462000</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47297561.25</v>
@@ -5537,16 +5541,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2976367.39</v>
+        <v>2277021.45</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>9004772.539999999</v>
+        <v>6888954.74</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13771335.88</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>518615563.81</v>
+        <v>396758400.07</v>
       </c>
     </row>
     <row r="37">
@@ -5580,7 +5584,7 @@
         <v>2048778203.86</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>491352000</v>
+        <v>354531000</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>50100849.41</v>
@@ -5592,16 +5596,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2924361.97</v>
+        <v>2216249.49</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>10890933.57</v>
+        <v>8253775.1</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>6213562.76</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>578858479.9</v>
+        <v>438692208.95</v>
       </c>
     </row>
     <row r="38">
@@ -5635,7 +5639,7 @@
         <v>2636849792.74</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>635704000</v>
+        <v>458687000</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46914612.74</v>
@@ -5647,16 +5651,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>5017312.78</v>
+        <v>3794757.46</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>8967927.640000001</v>
+        <v>6782736.47</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9944728.02</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>740455156.33</v>
+        <v>560030409.85</v>
       </c>
     </row>
     <row r="39">
@@ -5690,7 +5694,7 @@
         <v>2060377632.24</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>491352000</v>
+        <v>354531000</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38188228.54</v>
@@ -5702,16 +5706,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>6168118.49</v>
+        <v>4688276.87</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>9921976.369999999</v>
+        <v>7541517.29</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16230447.81</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>586372836.21</v>
+        <v>445691535.5</v>
       </c>
     </row>
     <row r="40">
@@ -5745,7 +5749,7 @@
         <v>1673241744.18</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>377536000</v>
+        <v>272408000</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52881481.78</v>
@@ -5757,16 +5761,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>4415441.67</v>
+        <v>3423659.48</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>6245638.64</v>
+        <v>4842763.54</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18624740.64</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>478693836.95</v>
+        <v>371171179.66</v>
       </c>
     </row>
     <row r="41">
@@ -5800,7 +5804,7 @@
         <v>1842478717.46</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>433056000</v>
+        <v>312468000</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45961726.06</v>
@@ -5812,16 +5816,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>4351982.42</v>
+        <v>3324030.98</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>7636551.78</v>
+        <v>5832775.1</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17374100.29</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>522515427.2</v>
+        <v>399095699.07</v>
       </c>
     </row>
     <row r="42">
@@ -5855,7 +5859,7 @@
         <v>2170024151.17</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>496904000</v>
+        <v>358537000</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59745247.93</v>
@@ -5867,16 +5871,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>3633037.73</v>
+        <v>2804785.63</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>10234418.62</v>
+        <v>7901197.96</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26976320.04</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>620799252.3099999</v>
+        <v>479270779.57</v>
       </c>
     </row>
     <row r="43">
@@ -5910,7 +5914,7 @@
         <v>2036573149.79</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>455264000</v>
+        <v>328492000</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>61536534.58</v>
@@ -5922,16 +5926,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>3481497.74</v>
+        <v>2691076.88</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>10499973.87</v>
+        <v>8116115.28</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22991971.37</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>572363033.64</v>
+        <v>442416754.19</v>
       </c>
     </row>
     <row r="44">
@@ -5965,7 +5969,7 @@
         <v>2069120435.98</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>471920000</v>
+        <v>340510000</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>52316511.19</v>
@@ -5977,16 +5981,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>6862714.94</v>
+        <v>5267877.13</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>10044385.59</v>
+        <v>7710154.01</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>19960813.73</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>582374864.5599999</v>
+        <v>447035795.17</v>
       </c>
     </row>
     <row r="45">
@@ -6020,7 +6024,7 @@
         <v>3001875093.93</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>657912000</v>
+        <v>474711000</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>77234060.05</v>
@@ -6032,16 +6036,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>13102229.99</v>
+        <v>10116256.82</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>23213259.91</v>
+        <v>17923002.35</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>16489733.2</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>840187962.88</v>
+        <v>648710732.15</v>
       </c>
     </row>
     <row r="46">
@@ -6075,7 +6079,7 @@
         <v>3366086979.97</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>710656000</v>
+        <v>512768000</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>102432751.1</v>
@@ -6087,16 +6091,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>15054396.62</v>
+        <v>11742697.69</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>28527338.1</v>
+        <v>22251832.18</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>33092919.58</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>943145523.76</v>
+        <v>735670318.91</v>
       </c>
     </row>
     <row r="47">
@@ -6130,7 +6134,7 @@
         <v>2022018189.85</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>438608000</v>
+        <v>316474000</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>66197336.17</v>
@@ -6142,16 +6146,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>4999078.62</v>
+        <v>3893481.28</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>8292543.38</v>
+        <v>6458562.64</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>25513319.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>565533786.64</v>
+        <v>440460208.57</v>
       </c>
     </row>
     <row r="48">
@@ -6185,7 +6189,7 @@
         <v>2322854768.65</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>530216000</v>
+        <v>382573000</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>63291974.74</v>
@@ -6197,16 +6201,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>6235831.63</v>
+        <v>4771502.6</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>9200187.15</v>
+        <v>7039753.4</v>
       </c>
       <c r="P48" s="9" t="n">
         <v>17669329.8</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>644172370.01</v>
+        <v>492904607.24</v>
       </c>
     </row>
     <row r="49">
@@ -6240,7 +6244,7 @@
         <v>2421901799.74</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>549648000</v>
+        <v>396594000</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>63886790.88</v>
@@ -6252,16 +6256,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="9" t="n">
-        <v>7320858.3</v>
+        <v>5605245.48</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>9689080.130000001</v>
+        <v>7418484.33</v>
       </c>
       <c r="P49" s="9" t="n">
         <v>16498863.67</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>670121544.05</v>
+        <v>513081335.43</v>
       </c>
     </row>
     <row r="50">
@@ -6295,7 +6299,7 @@
         <v>2185552507.22</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>480248000</v>
+        <v>346519000</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>57936471.2</v>
@@ -6307,16 +6311,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="9" t="n">
-        <v>6701161.1</v>
+        <v>5163079.85</v>
       </c>
       <c r="O50" s="9" t="n">
-        <v>9458314.16</v>
+        <v>7287398.49</v>
       </c>
       <c r="P50" s="9" t="n">
         <v>13379834.23</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>598794217.22</v>
+        <v>461356220.3</v>
       </c>
     </row>
     <row r="51">
@@ -6350,7 +6354,7 @@
         <v>2598617595.62</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>580184000</v>
+        <v>418627000</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>60104622.44</v>
@@ -6362,16 +6366,16 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="9" t="n">
-        <v>8030044.83</v>
+        <v>6127856.36</v>
       </c>
       <c r="O51" s="9" t="n">
-        <v>12531036.67</v>
+        <v>9562635.619999999</v>
       </c>
       <c r="P51" s="9" t="n">
         <v>14189280.7</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>702570236.41</v>
+        <v>536142646.88</v>
       </c>
     </row>
     <row r="52">
@@ -6405,7 +6409,7 @@
         <v>3604346415.18</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>780056000</v>
+        <v>562843000</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>93075890.23999999</v>
@@ -6417,16 +6421,16 @@
         <v>15738266.69</v>
       </c>
       <c r="N52" s="9" t="n">
-        <v>11483767.21</v>
+        <v>8796087.1</v>
       </c>
       <c r="O52" s="9" t="n">
-        <v>35108423.63</v>
+        <v>26891589.36</v>
       </c>
       <c r="P52" s="9" t="n">
         <v>10358724.77</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>974687583</v>
+        <v>746570068.63</v>
       </c>
     </row>
     <row r="53">
@@ -6444,7 +6448,9 @@
       <c r="D53" s="6" t="n">
         <v>88600562.34999999</v>
       </c>
-      <c r="E53" s="6" t="n"/>
+      <c r="E53" s="6" t="n">
+        <v>183536981</v>
+      </c>
       <c r="F53" s="6" t="n">
         <v>47959130.31</v>
       </c>
@@ -6455,10 +6461,10 @@
         <v>67547059</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>4151854314.97</v>
+        <v>4335391295.97</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>879992000</v>
+        <v>634951000</v>
       </c>
       <c r="K53" s="9" t="n">
         <v>126810450.73</v>
@@ -6466,18 +6472,20 @@
       <c r="L53" s="9" t="n">
         <v>22293136.54</v>
       </c>
-      <c r="M53" s="9" t="n"/>
+      <c r="M53" s="9" t="n">
+        <v>34860196.13</v>
+      </c>
       <c r="N53" s="9" t="n">
-        <v>13001876.55</v>
+        <v>9962692.99</v>
       </c>
       <c r="O53" s="9" t="n">
-        <v>50299564.84</v>
+        <v>38542061.2</v>
       </c>
       <c r="P53" s="9" t="n">
         <v>33184209.53</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>1125581238.19</v>
+        <v>900603747.12</v>
       </c>
     </row>
   </sheetData>
@@ -6600,7 +6608,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>678999600</v>
+        <v>888864000</v>
       </c>
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="6" t="n">
@@ -6616,7 +6624,7 @@
         <v>15122319</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>0.5537</v>
+        <v>0.6189</v>
       </c>
       <c r="I3" s="11" t="n"/>
       <c r="J3" s="11" t="n">
@@ -6639,7 +6647,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>597134400</v>
+        <v>781696000</v>
       </c>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n">
@@ -6655,7 +6663,7 @@
         <v>13414300</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.5855</v>
+        <v>0.6484000000000001</v>
       </c>
       <c r="I4" s="11" t="n"/>
       <c r="J4" s="11" t="n">
@@ -6678,7 +6686,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>397816716</v>
+        <v>520773440</v>
       </c>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n">
@@ -6694,7 +6702,7 @@
         <v>5593903</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.5191</v>
+        <v>0.5855</v>
       </c>
       <c r="I5" s="11" t="n"/>
       <c r="J5" s="11" t="n">
@@ -6717,7 +6725,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>553794000</v>
+        <v>724960000</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>7074510.67</v>
@@ -6735,7 +6743,7 @@
         <v>10388004</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.5629</v>
+        <v>0.6275999999999999</v>
       </c>
       <c r="I6" s="11" t="n">
         <v>0.3931</v>
@@ -6760,7 +6768,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>626028000</v>
+        <v>819520000</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>6375222.34</v>
@@ -6778,7 +6786,7 @@
         <v>11554341</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.5704</v>
+        <v>0.6341</v>
       </c>
       <c r="I7" s="11" t="n">
         <v>0.3082</v>
@@ -6803,7 +6811,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>568240800</v>
+        <v>743872000</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>5520981.46</v>
@@ -6821,7 +6829,7 @@
         <v>11900005</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.5618</v>
+        <v>0.6264</v>
       </c>
       <c r="I8" s="11" t="n">
         <v>0.3006</v>
@@ -6846,7 +6854,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>558609600</v>
+        <v>731264000</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>5566119.94</v>
@@ -6864,7 +6872,7 @@
         <v>9881154</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.5807</v>
+        <v>0.6418</v>
       </c>
       <c r="I9" s="11" t="n">
         <v>0.3517</v>
@@ -6889,7 +6897,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>621212400</v>
+        <v>813216000</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>6866983.28</v>
@@ -6907,7 +6915,7 @@
         <v>12561820</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.5789</v>
+        <v>0.6428</v>
       </c>
       <c r="I10" s="11" t="n">
         <v>0.3298</v>
@@ -6932,7 +6940,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>563425200</v>
+        <v>737568000</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>5930919.66</v>
@@ -6950,7 +6958,7 @@
         <v>12447288</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.5864</v>
+        <v>0.6492</v>
       </c>
       <c r="I11" s="11" t="n">
         <v>0.3287</v>
@@ -6975,7 +6983,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>414912096</v>
+        <v>543152640</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>5863027.8</v>
@@ -6993,7 +7001,7 @@
         <v>5158036</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.6043999999999999</v>
+        <v>0.6645</v>
       </c>
       <c r="I12" s="11" t="n">
         <v>0.3621</v>
@@ -7018,7 +7026,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>568240800</v>
+        <v>743872000</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>6978018.66</v>
@@ -7036,7 +7044,7 @@
         <v>9937864</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.5853</v>
+        <v>0.6474</v>
       </c>
       <c r="I13" s="11" t="n">
         <v>0.3335</v>
@@ -7061,7 +7069,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>626028000</v>
+        <v>819520000</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>7314178.95</v>
@@ -7079,7 +7087,7 @@
         <v>11483868</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.6004</v>
+        <v>0.6612</v>
       </c>
       <c r="I14" s="11" t="n">
         <v>0.3297</v>
@@ -7104,7 +7112,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>587503200</v>
+        <v>769088000</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>6610607.24</v>
@@ -7122,7 +7130,7 @@
         <v>11876717</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.5614</v>
+        <v>0.6262</v>
       </c>
       <c r="I15" s="11" t="n">
         <v>0.3308</v>
@@ -7147,7 +7155,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>577872000</v>
+        <v>756480000</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>8484995.99</v>
@@ -7165,7 +7173,7 @@
         <v>10105691</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.5629</v>
+        <v>0.6269</v>
       </c>
       <c r="I16" s="11" t="n">
         <v>0.3907</v>
@@ -7190,7 +7198,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>722340000</v>
+        <v>945600000</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>10516524.95</v>
@@ -7208,7 +7216,7 @@
         <v>15529922</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.5664</v>
+        <v>0.6292</v>
       </c>
       <c r="I17" s="11" t="n">
         <v>0.3994</v>
@@ -7233,7 +7241,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>674184000</v>
+        <v>882560000</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>6805807.23</v>
@@ -7251,7 +7259,7 @@
         <v>16183161</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.6002000000000001</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="I18" s="11" t="n">
         <v>0.3354</v>
@@ -7276,7 +7284,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>446117184</v>
+        <v>584002560</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>6013077.75</v>
@@ -7294,7 +7302,7 @@
         <v>5512796</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.5716</v>
+        <v>0.6359</v>
       </c>
       <c r="I19" s="11" t="n">
         <v>0.3486</v>
@@ -7319,7 +7327,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>558609600</v>
+        <v>731264000</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>7131623.62</v>
@@ -7337,7 +7345,7 @@
         <v>9370589</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.6038</v>
+        <v>0.6661</v>
       </c>
       <c r="I20" s="11" t="n">
         <v>0.344</v>
@@ -7362,7 +7370,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>659737200</v>
+        <v>863648000</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>7503694.94</v>
@@ -7380,7 +7388,7 @@
         <v>12363246</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.6002000000000001</v>
+        <v>0.6627</v>
       </c>
       <c r="I21" s="11" t="n">
         <v>0.3256</v>
@@ -7405,7 +7413,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>573056400</v>
+        <v>750176000</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>5474050.14</v>
@@ -7423,7 +7431,7 @@
         <v>9845111</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.6553</v>
       </c>
       <c r="I22" s="11" t="n">
         <v>0.2813</v>
@@ -7448,7 +7456,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>606765600</v>
+        <v>794304000</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>7108192.79</v>
@@ -7466,7 +7474,7 @@
         <v>9562382</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.6049</v>
+        <v>0.6670999999999999</v>
       </c>
       <c r="I23" s="11" t="n">
         <v>0.3146</v>
@@ -7491,7 +7499,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>809020800</v>
+        <v>1059072000</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>13287188.62</v>
@@ -7509,7 +7517,7 @@
         <v>16160186</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.5939</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="I24" s="11" t="n">
         <v>0.3856</v>
@@ -7534,7 +7542,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>712708800</v>
+        <v>932992000</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>9660178.35</v>
@@ -7552,7 +7560,7 @@
         <v>15568073</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.616</v>
+        <v>0.6775</v>
       </c>
       <c r="I25" s="11" t="n">
         <v>0.3765</v>
@@ -7577,7 +7585,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>539347200</v>
+        <v>706048000</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>7897337.67</v>
@@ -7595,7 +7603,7 @@
         <v>7232750</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.6197</v>
+        <v>0.6808</v>
       </c>
       <c r="I26" s="11" t="n">
         <v>0.3647</v>
@@ -7620,7 +7628,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>635659200</v>
+        <v>832128000</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>9927373.289999999</v>
@@ -7638,7 +7646,7 @@
         <v>11383349</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.6342</v>
+        <v>0.6940999999999999</v>
       </c>
       <c r="I27" s="11" t="n">
         <v>0.3861</v>
@@ -7663,7 +7671,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>683815200</v>
+        <v>895168000</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>8425863.65</v>
@@ -7681,7 +7689,7 @@
         <v>13381960</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>0.6183</v>
+        <v>0.6795</v>
       </c>
       <c r="I28" s="11" t="n">
         <v>0.3211</v>
@@ -7706,7 +7714,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>573056400</v>
+        <v>750176000</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>6513031.07</v>
@@ -7724,7 +7732,7 @@
         <v>9008514</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0.6143</v>
+        <v>0.6758</v>
       </c>
       <c r="I29" s="11" t="n">
         <v>0.3433</v>
@@ -7749,7 +7757,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>717524400</v>
+        <v>939296000</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>10978365.44</v>
@@ -7767,7 +7775,7 @@
         <v>7506867</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>0.6175</v>
+        <v>0.6788</v>
       </c>
       <c r="I30" s="11" t="n">
         <v>0.3898</v>
@@ -7792,7 +7800,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>929410800</v>
+        <v>1216672000</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>13135089.02</v>
@@ -7810,7 +7818,7 @@
         <v>11160815</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.6454000000000001</v>
+        <v>0.7044</v>
       </c>
       <c r="I31" s="11" t="n">
         <v>0.3762</v>
@@ -7835,7 +7843,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>818652000</v>
+        <v>1071680000</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>9473243.35</v>
@@ -7853,7 +7861,7 @@
         <v>12728635</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>0.6203</v>
+        <v>0.6814</v>
       </c>
       <c r="I32" s="11" t="n">
         <v>0.3658</v>
@@ -7878,7 +7886,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>674184000</v>
+        <v>882560000</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>10680115.83</v>
@@ -7896,7 +7904,7 @@
         <v>9774024</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.6146</v>
+        <v>0.6761</v>
       </c>
       <c r="I33" s="11" t="n">
         <v>0.4301</v>
@@ -7921,7 +7929,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>731971200</v>
+        <v>958208000</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>14236899.75</v>
@@ -7939,7 +7947,7 @@
         <v>12995978</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.6409</v>
+        <v>0.7003</v>
       </c>
       <c r="I34" s="11" t="n">
         <v>0.474</v>
@@ -7964,7 +7972,7 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>760864800</v>
+        <v>996032000</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>11377652.1</v>
@@ -7982,7 +7990,7 @@
         <v>10158090</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>0.6378</v>
+        <v>0.6975</v>
       </c>
       <c r="I35" s="11" t="n">
         <v>0.4234000000000001</v>
@@ -8007,7 +8015,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>741602400</v>
+        <v>970816000</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>9775548.310000001</v>
@@ -8025,7 +8033,7 @@
         <v>8471978</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>0.6043999999999999</v>
+        <v>0.6667000000000001</v>
       </c>
       <c r="I36" s="11" t="n">
         <v>0.3584000000000001</v>
@@ -8050,7 +8058,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>852361200</v>
+        <v>1115808000</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>12490106.43</v>
@@ -8068,7 +8076,7 @@
         <v>11868618</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>0.632</v>
+        <v>0.6917</v>
       </c>
       <c r="I37" s="11" t="n">
         <v>0.3806</v>
@@ -8093,7 +8101,7 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>1102772400</v>
+        <v>1443616000</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>18169819.03</v>
@@ -8111,7 +8119,7 @@
         <v>10824093</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>0.6201</v>
+        <v>0.6811</v>
       </c>
       <c r="I38" s="11" t="n">
         <v>0.3624</v>
@@ -8136,7 +8144,7 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>852361200</v>
+        <v>1115808000</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>10625376.42</v>
@@ -8154,7 +8162,7 @@
         <v>12319196</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>0.6247</v>
+        <v>0.6851999999999999</v>
       </c>
       <c r="I39" s="11" t="n">
         <v>0.3315</v>
@@ -8179,7 +8187,7 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>654921600</v>
+        <v>857344000</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>10495613.05</v>
@@ -8197,7 +8205,7 @@
         <v>7061846</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>0.6309</v>
+        <v>0.6907</v>
       </c>
       <c r="I40" s="11" t="n">
         <v>0.3536</v>
@@ -8222,7 +8230,7 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>751233600</v>
+        <v>983424000</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>12213347.32</v>
@@ -8240,7 +8248,7 @@
         <v>9247924</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.7141</v>
       </c>
       <c r="I41" s="11" t="n">
         <v>0.4061999999999999</v>
@@ -8265,7 +8273,7 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>861992400</v>
+        <v>1128416000</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>13331547.8</v>
@@ -8283,7 +8291,7 @@
         <v>15189926</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>0.6435</v>
+        <v>0.6993</v>
       </c>
       <c r="I42" s="11" t="n">
         <v>0.3605</v>
@@ -8308,7 +8316,7 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>789758400</v>
+        <v>1033856000</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>10973579.3</v>
@@ -8326,7 +8334,7 @@
         <v>13411796</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>0.6736</v>
+        <v>0.7241</v>
       </c>
       <c r="I43" s="11" t="n">
         <v>0.3466</v>
@@ -8351,7 +8359,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>818652000</v>
+        <v>1071680000</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>14687824.44</v>
@@ -8369,7 +8377,7 @@
         <v>12049458</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>0.6683</v>
+        <v>0.7237</v>
       </c>
       <c r="I44" s="11" t="n">
         <v>0.4026</v>
@@ -8394,7 +8402,7 @@
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>1141297200</v>
+        <v>1494048000</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>25784306.09</v>
@@ -8412,7 +8420,7 @@
         <v>21875177</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>0.6206</v>
+        <v>0.6807</v>
       </c>
       <c r="I45" s="11" t="n">
         <v>0.3898</v>
@@ -8437,7 +8445,7 @@
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>1232793600</v>
+        <v>1613824000</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>30527478.39</v>
@@ -8455,7 +8463,7 @@
         <v>24436069</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>0.6456999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="I46" s="11" t="n">
         <v>0.4415</v>
@@ -8480,7 +8488,7 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>760864800</v>
+        <v>996032000</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>14529335.06</v>
@@ -8498,7 +8506,7 @@
         <v>11226252</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>0.6765000000000001</v>
+        <v>0.7265999999999999</v>
       </c>
       <c r="I47" s="11" t="n">
         <v>0.4061</v>
@@ -8523,7 +8531,7 @@
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>919779600</v>
+        <v>1204064000</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>16723415.34</v>
@@ -8541,7 +8549,7 @@
         <v>13207850</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>0.6994</v>
+        <v>0.7498</v>
       </c>
       <c r="I48" s="11" t="n">
         <v>0.4791</v>
@@ -8566,7 +8574,7 @@
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>953488800</v>
+        <v>1248192000</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>19750670.59</v>
@@ -8584,7 +8592,7 @@
         <v>11477871</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7598</v>
       </c>
       <c r="I49" s="11" t="n">
         <v>0.4597</v>
@@ -8609,7 +8617,7 @@
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>833098800</v>
+        <v>1090592000</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>19265583.23</v>
@@ -8627,7 +8635,7 @@
         <v>12724485</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>0.6546</v>
+        <v>0.7084</v>
       </c>
       <c r="I50" s="11" t="n">
         <v>0.4323</v>
@@ -8652,7 +8660,7 @@
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>1006460400</v>
+        <v>1317536000</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>25326363.49</v>
@@ -8670,7 +8678,7 @@
         <v>15736949</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>0.7064</v>
+        <v>0.7464</v>
       </c>
       <c r="I51" s="11" t="n">
         <v>0.5035000000000001</v>
@@ -8695,7 +8703,7 @@
         </is>
       </c>
       <c r="B52" s="6" t="n">
-        <v>1353183600</v>
+        <v>1771424000</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>41469933.99</v>
@@ -8713,7 +8721,7 @@
         <v>38042084</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>0.6487999999999999</v>
+        <v>0.6983</v>
       </c>
       <c r="I52" s="11" t="n">
         <v>0.4738</v>
@@ -8738,12 +8746,14 @@
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>1526545200</v>
+        <v>1998368000</v>
       </c>
       <c r="C53" s="6" t="n">
         <v>42862000.8</v>
       </c>
-      <c r="D53" s="6" t="n"/>
+      <c r="D53" s="6" t="n">
+        <v>128207646</v>
+      </c>
       <c r="E53" s="6" t="n">
         <v>298615538.59</v>
       </c>
@@ -8754,12 +8764,14 @@
         <v>47830508</v>
       </c>
       <c r="H53" s="11" t="n">
-        <v>0.6893</v>
+        <v>0.7379000000000001</v>
       </c>
       <c r="I53" s="11" t="n">
         <v>0.4838</v>
       </c>
-      <c r="J53" s="11" t="n"/>
+      <c r="J53" s="11" t="n">
+        <v>0.6984999999999999</v>
+      </c>
       <c r="K53" s="11" t="n">
         <v>0.5054</v>
       </c>
@@ -8793,7 +8805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -8809,7 +8821,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-21. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-22. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>
@@ -8819,122 +8831,164 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>One comparable metric: contracts traded, one-sided (a buy matched with a</t>
+          <t>One comparable metric: TAKER VOLUME - contracts traded, one-sided (a buy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sell counts once), each a $1-max-payout instrument. 'Notional $' re-weights</t>
+          <t>matched with a sell counts once - the taker's fill, not the maker's resting</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>each contract by its traded price (~ the dollars that changed hands).</t>
+          <t>order), each a $1-max-payout instrument. This is the metric every one of</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>these venues reports as its own 'volume' under CFTC Part 16.01 (Kalshi's own</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>TAB 'Sports volume'  - each venue's sports book only. Apples-to-apples on sports.</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>API calls it 'taker volume' outright). 'Notional $' re-weights each contract</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Kalshi = single-leg sports + its sports parlay engine.</t>
+          <t>by its traded price (~ the dollars that changed hands, roughly 1/3 of the</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Polymarket US / Crypto.com / Rothera = sports filtered out of a wider book.</t>
+          <t>taker-volume figure). Every venue re-verified against its live source as of</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Novig / DKeX / UDX = sports-only exchanges (their sports IS their whole book).</t>
+          <t>2026-09-22: independently recomputed totals matched the committed figures exactly</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>for all seven venues (see VOLUME_METHODOLOGY.md for the audit detail).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>TAB 'Total exchange'  - each venue's WHOLE book, every category (sports, crypto,</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  politics, economics, ...). Apples-to-apples on total platform activity.</t>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>TAB 'Sports volume'  - each venue's sports book only. Apples-to-apples on sports.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Kalshi total from DeFi Rate (last ~2 days projected). Polymarket = all QCX.</t>
+          <t xml:space="preserve">  Kalshi = single-leg sports + its sports parlay engine.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Crypto.com = the whole Nadex/CDNA book (events + fx/commodity/crypto binaries).</t>
+          <t xml:space="preserve">  Polymarket US / Crypto.com / Rothera = sports filtered out of a wider book.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Rothera = sports + its US-macro / elections markets.</t>
+          <t xml:space="preserve">  Novig / DKeX / UDX = sports-only exchanges (their sports IS their whole book).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Novig / DKeX / UDX total == their sports figure (sports-only exchanges).</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TAB 'Total exchange'  - each venue's WHOLE book, every category (sports, crypto,</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>TAB 'Parlay share'  - per-venue combo/parlay volume and % of that venue's sports book.</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  politics, economics, ...). Apples-to-apples on total platform activity.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Kalshi total from DeFi Rate (last ~2 days projected). Polymarket = all QCX.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UDX and Crypto.com have no usable price column - their Notional $ is estimated</t>
+          <t xml:space="preserve">  Crypto.com = the whole Nadex/CDNA book (events + fx/commodity/crypto binaries).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rothera = sports + its US-macro / elections markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Novig / DKeX / UDX total == their sports figure (sports-only exchanges).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>TAB 'Parlay share'  - per-venue combo/parlay volume and % of that venue's sports book.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>UDX and Crypto.com have no usable price column - their Notional $ is estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>with the day's contract-weighted average price across the venues that report one.</t>
         </is>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:R54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1436291212.47</v>
+        <v>1436292122.83</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1614253307.05</v>
+        <v>1614254217.41</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>299227228.99</v>
+        <v>299227422.63</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -650,16 +650,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>466111.76</v>
+        <v>466111.75</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>8313323.71</v>
+        <v>8313323.47</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>361464571.1</v>
+        <v>361464764.48</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1205571433.13</v>
+        <v>1205571579.51</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1388976342.64</v>
+        <v>1388976489.02</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>231812202.33</v>
+        <v>231812319.19</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -704,16 +704,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>458019.1</v>
+        <v>458019.24</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>8194673.86</v>
+        <v>8194676.3</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>296023001.07</v>
+        <v>296023120.51</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>889406809.65</v>
+        <v>889406923.05</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>1005449356.69</v>
+        <v>1005449470.09</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>202393041.66</v>
+        <v>202393069.54</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -761,13 +761,13 @@
         <v>334880.88</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>4825438.94</v>
+        <v>4825438.95</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>243868643.86</v>
+        <v>243868671.75</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1155122773.3</v>
+        <v>1155123713.37</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1339760922.32</v>
+        <v>1339761862.39</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>243083730.79</v>
+        <v>243084344.13</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -816,16 +816,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>288784.6</v>
+        <v>288784.97</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>6546854.26</v>
+        <v>6546862.73</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>312032954.22</v>
+        <v>312033576.4</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1292325892.67</v>
+        <v>1292326682.44</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>125055737.8</v>
@@ -859,10 +859,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1497405930.25</v>
+        <v>1497406720.02</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>259386245.31</v>
+        <v>259386594.51</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>47948549.82</v>
@@ -874,16 +874,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>631739.51</v>
+        <v>631739.84</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>6846047.82</v>
+        <v>6846051.41</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>335564763.9</v>
+        <v>335565117.02</v>
       </c>
       <c r="R7" s="10" t="n">
         <v>0.1036604405692761</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1187470480.24</v>
+        <v>1187470733.41</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1409643599.75</v>
+        <v>1409643852.92</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>236784485.26</v>
+        <v>236784575.48</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -932,16 +932,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1121124.6</v>
+        <v>1121124.72</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>7508185.34</v>
+        <v>7508186.16</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>315423251.85</v>
+        <v>315423343.02</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1139472600.21</v>
+        <v>1139472955.19</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1323079761.75</v>
+        <v>1323080116.73</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>224391932.61</v>
+        <v>224392076.92</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>727221.0699999999</v>
+        <v>727221.24</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6114373.5</v>
+        <v>6114374.94</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>289885372.39</v>
+        <v>289885518.3</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1265084691.76</v>
+        <v>1265085721.25</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1469750589.24</v>
+        <v>1469751618.73</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>247904300.21</v>
+        <v>247904360.5</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2089370.81</v>
+        <v>2089369.71</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>6720642.34</v>
+        <v>6720638.8</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>320414791.25</v>
+        <v>320414846.89</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1136156308.74</v>
+        <v>1136156511.32</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>126075255.12</v>
@@ -1091,10 +1091,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1360829625.86</v>
+        <v>1360829828.44</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>220224867.55</v>
+        <v>220224910.2</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>48533344.05</v>
@@ -1106,16 +1106,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>2216238.86</v>
+        <v>2216238.84</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>7947076.32</v>
+        <v>7947076.26</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>302603523.43</v>
+        <v>302603566</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>0.1174147553025735</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>817335136</v>
+        <v>817335185.02</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>944246827.03</v>
+        <v>944246876.05</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>157384944.68</v>
+        <v>157384965.37</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1164,16 +1164,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1682384.8</v>
+        <v>1682384.89</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3091090.4</v>
+        <v>3091090.56</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>202040379.78</v>
+        <v>202040400.72</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1149010810.82</v>
+        <v>1149010908.63</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1308567465.06</v>
+        <v>1308567562.87</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>235935015.83</v>
+        <v>235935037.53</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,7 +1222,7 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2341917.81</v>
+        <v>2341917.8</v>
       </c>
       <c r="O13" s="9" t="n">
         <v>4886884.99</v>
@@ -1231,7 +1231,7 @@
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>294006367.08</v>
+        <v>294006388.77</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1239522017.27</v>
+        <v>1239522251.9</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>114182203.82</v>
@@ -1265,10 +1265,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>1441006207.34</v>
+        <v>1441006441.97</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>240227545.57</v>
+        <v>240227594.84</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>44020201.24</v>
@@ -1280,16 +1280,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2540876.53</v>
+        <v>2540876.52</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>6229750.5</v>
+        <v>6229750.46</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>313911244.04</v>
+        <v>313911293.25</v>
       </c>
       <c r="R14" s="10" t="n">
         <v>0.1369006174109096</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1228237582.97</v>
+        <v>1228237800.68</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1450284682.78</v>
+        <v>1450284900.49</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>245766950.44</v>
+        <v>245766996.16</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3332864.81</v>
+        <v>3332864.79</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>6989302.03</v>
+        <v>6989301.97</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>321979854.09</v>
+        <v>321979899.72</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1206694582.99</v>
+        <v>1206694864.16</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1408838462.02</v>
+        <v>1408838743.19</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>254177958.98</v>
+        <v>254178044.65</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1396,16 +1396,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>3170561.57</v>
+        <v>3170561.79</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>6715343.04</v>
+        <v>6715343.49</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>322387917.75</v>
+        <v>322388004.09</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1502784885.58</v>
+        <v>1502784943.2</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1745506362.83</v>
+        <v>1745506420.45</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>307040468.04</v>
+        <v>307040479.14</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>3811143.19</v>
+        <v>3811143.17</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>8549315.720000001</v>
+        <v>8549315.68</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>388644922.83</v>
+        <v>388644933.88</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1333524682.78</v>
+        <v>1333524743.97</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1585699844.11</v>
+        <v>1585699905.3</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>261226724.51</v>
+        <v>261226753.68</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3122211.65</v>
+        <v>3122211.8</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>9982347.77</v>
+        <v>9982348.24</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>348774240.77</v>
+        <v>348774270.56</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>918409295.78</v>
+        <v>918409296.78</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,7 +1555,7 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>1079826141.31</v>
+        <v>1079826142.31</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>188477035.9</v>
@@ -1579,7 +1579,7 @@
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>245090542.6</v>
+        <v>245090542.59</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>1097888712.22</v>
+        <v>1097888772.79</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1275892096.04</v>
+        <v>1275892156.61</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>215918640.68</v>
+        <v>215918663.38</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1628,16 +1628,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>2738069.66</v>
+        <v>2738069.76</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>5494139.01</v>
+        <v>5494139.2</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>276651359.36</v>
+        <v>276651382.35</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1303187541.17</v>
+        <v>1303187747.18</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1518487834.99</v>
+        <v>1518488041</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>252864781.27</v>
+        <v>252864878.23</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3247080.99</v>
+        <v>3247081.53</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>6819802.08</v>
+        <v>6819803.22</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>326404085.04</v>
+        <v>326404183.68</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>1144724149.08</v>
+        <v>1144724408.04</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1368045154.66</v>
+        <v>1368045413.62</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>217696505.83</v>
+        <v>217696605.58</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>2916877.12</v>
+        <v>2916877.59</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>6698294.28</v>
+        <v>6698295.35</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>289776557.9</v>
+        <v>289776659.19</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1190738004.6</v>
+        <v>1190738823.27</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1385894692.66</v>
+        <v>1385895511.33</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>229729503.14</v>
+        <v>229729887.06</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1802,16 +1802,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>3441497</v>
+        <v>3441499.65</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>5603929.09</v>
+        <v>5603933.4</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>287479424.16</v>
+        <v>287479815.04</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1612355750.21</v>
+        <v>1612356752.76</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1884572505.33</v>
+        <v>1884573507.88</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>316887393.13</v>
+        <v>316887749.18</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1860,16 +1860,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>5435365.88</v>
+        <v>5435367.94</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>9097129.279999999</v>
+        <v>9097132.75</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>396272019.79</v>
+        <v>396272381.37</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1377194770.15</v>
+        <v>1377195069</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1629694737.8</v>
+        <v>1629695036.65</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>256709061.04</v>
+        <v>256709125.58</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1918,16 +1918,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>3355926.66</v>
+        <v>3355926.7</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>8780036.82</v>
+        <v>8780036.91</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>333318249.3</v>
+        <v>333318313.97</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>1037097767.79</v>
+        <v>1037097872.4</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1206201980.16</v>
+        <v>1206202084.77</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>200202084.89</v>
+        <v>200202110.31</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>2871147.64</v>
+        <v>2871147.68</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5012247.1</v>
+        <v>5012247.17</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>250987291.26</v>
+        <v>250987316.8</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1198842915.31</v>
+        <v>1198843168.33</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1406180323.27</v>
+        <v>1406180576.29</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>225000637.9</v>
+        <v>225000720.51</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2585282.48</v>
+        <v>2585282.76</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6112837.63</v>
+        <v>6112838.31</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>287799163.09</v>
+        <v>287799246.66</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1317392590.05</v>
+        <v>1317392628.7</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1563247489.7</v>
+        <v>1563247528.35</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>251063889.23</v>
+        <v>251063900.56</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2381326.04</v>
+        <v>2381326.06</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>7749021.8</v>
+        <v>7749021.88</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>330050716.07</v>
+        <v>330050727.5</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>1110051660.15</v>
+        <v>1110052118.66</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1313999474.6</v>
+        <v>1313999933.11</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>203729999.45</v>
+        <v>203730159.16</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2150,16 +2150,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>2592783.58</v>
+        <v>2592784.26</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>5824916.44</v>
+        <v>5824917.96</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>265596040.83</v>
+        <v>265596202.74</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1383849280.61</v>
+        <v>1383850302.96</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1576685764.68</v>
+        <v>1576686787.03</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>261336616.92</v>
+        <v>261337111.85</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>3726726.16</v>
+        <v>3726729.59</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4002086.12</v>
+        <v>4002089.8</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>319907147.83</v>
+        <v>319907649.87</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1727299533.05</v>
+        <v>1727299894.36</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>2027356199.08</v>
+        <v>2027356560.39</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>296354688.53</v>
+        <v>296354868.5</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>3587884.98</v>
+        <v>3587886.04</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5274096.57</v>
+        <v>5274098.12</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>386041858.94</v>
+        <v>386042041.52</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1572726221.5</v>
+        <v>1572729725.12</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1832489305.62</v>
+        <v>1832492809.24</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>293607638.86</v>
+        <v>293610191.83</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>2694875.52</v>
+        <v>2694889.17</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>6570240.77</v>
+        <v>6570274.05</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>372624119.67</v>
+        <v>372626719.57</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1305393622.02</v>
+        <v>1305394516.16</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1491434648.13</v>
+        <v>1491435542.27</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>251860988.55</v>
+        <v>251861529.04</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1463492.63</v>
+        <v>1463494.35</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>6347090.32</v>
+        <v>6347097.78</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>309526463.02</v>
+        <v>309527012.7</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1368369925.8</v>
+        <v>1368370592.51</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>111143033.33</v>
+        <v>111143043.36</v>
       </c>
       <c r="D34" s="6" t="n">
         <v>30033982.35</v>
@@ -2425,13 +2425,13 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1592261039.75</v>
+        <v>1592261716.49</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>248806135.95</v>
+        <v>248806529.96</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>33583851.03</v>
+        <v>33583851.98</v>
       </c>
       <c r="L34" s="9" t="n">
         <v>8422284.43</v>
@@ -2440,19 +2440,19 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1142560.11</v>
+        <v>1142561.09</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>8125247.26</v>
+        <v>8125254.18</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>315334318.06</v>
+        <v>315334720.92</v>
       </c>
       <c r="R34" s="10" t="n">
-        <v>0.3414174721986673</v>
+        <v>0.3414174701179286</v>
       </c>
     </row>
     <row r="35">
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1428040946.31</v>
+        <v>1428042977.49</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>132482292.68</v>
+        <v>132482297.68</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>26868942.32</v>
@@ -2483,13 +2483,13 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1671697952.98</v>
+        <v>1671699989.16</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>263139103.74</v>
+        <v>263139824.94</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>39009606.34</v>
+        <v>39009607.96</v>
       </c>
       <c r="L35" s="9" t="n">
         <v>6948205.54</v>
@@ -2498,19 +2498,19 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>1891007.99</v>
+        <v>1891009.8</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>5945560.5</v>
+        <v>5945566.16</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>336440074.43</v>
+        <v>336440804.72</v>
       </c>
       <c r="R35" s="10" t="n">
-        <v>0.3444918139984984</v>
+        <v>0.3444918130280069</v>
       </c>
     </row>
     <row r="36">
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1456208465.75</v>
+        <v>1456209168.75</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1723548756.62</v>
+        <v>1723549459.62</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>282236552.84</v>
+        <v>282236867.89</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2226974.22</v>
+        <v>2226975.24</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>6426277.53</v>
+        <v>6426280.46</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>369371889.28</v>
+        <v>369372208.27</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1613187384.9</v>
+        <v>1613188023.44</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>161563894</v>
+        <v>161563899.02</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>32818984.23</v>
@@ -2599,13 +2599,13 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1887507529.65</v>
+        <v>1887508173.21</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>289612211.1</v>
+        <v>289612509.79</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>49969403.31</v>
+        <v>49969404.96</v>
       </c>
       <c r="L37" s="9" t="n">
         <v>10372615.86</v>
@@ -2614,19 +2614,19 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2038733.84</v>
+        <v>2038734.82</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>7146305.18</v>
+        <v>7146308.6</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>371788156.91</v>
+        <v>371788461.65</v>
       </c>
       <c r="R37" s="10" t="n">
-        <v>0.3158320960096582</v>
+        <v>0.3158320949670745</v>
       </c>
     </row>
     <row r="38">
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>2119622306.57</v>
+        <v>2119622380.67</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>172439695.17</v>
+        <v>172439724.32</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>50137129.16</v>
@@ -2657,13 +2657,13 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2463685368.63</v>
+        <v>2463685471.88</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>378506228.95</v>
+        <v>378506261.85</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>46814559.69</v>
+        <v>46814572.08</v>
       </c>
       <c r="L38" s="9" t="n">
         <v>18023125.75</v>
@@ -2672,19 +2672,19 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3468831.5</v>
+        <v>3468831.68</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>5883474.22</v>
+        <v>5883474.53</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>478311302.43</v>
+        <v>478311348.23</v>
       </c>
       <c r="R38" s="10" t="n">
-        <v>0.3730201375328469</v>
+        <v>0.3730201312691256</v>
       </c>
     </row>
     <row r="39">
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1628363240.71</v>
+        <v>1628363765.23</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1915133027.31</v>
+        <v>1915133551.83</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>294597583.2</v>
+        <v>294597889.86</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2730,16 +2730,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>4346486.72</v>
+        <v>4346489.07</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>6499225.01</v>
+        <v>6499228.51</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>384071084.61</v>
+        <v>384071397.12</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1241343575.09</v>
+        <v>1241344552.98</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>184348327.32</v>
+        <v>184349276.32</v>
       </c>
       <c r="D40" s="6" t="n">
         <v>29680306.46</v>
@@ -2773,13 +2773,13 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1550720291.88</v>
+        <v>1550722218.77</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>227090737.31</v>
+        <v>227091122.61</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>52663233.49</v>
+        <v>52663679.72</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>10696701.66</v>
@@ -2788,19 +2788,19 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3230018.51</v>
+        <v>3230022.87</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4087115.43</v>
+        <v>4087120.95</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>324536444.73</v>
+        <v>324537286.14</v>
       </c>
       <c r="R40" s="10" t="n">
-        <v>0.3156022523452979</v>
+        <v>0.3156021020167954</v>
       </c>
     </row>
     <row r="41">
@@ -2810,10 +2810,10 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1377183390.82</v>
+        <v>1377183618.16</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>155233679.84</v>
+        <v>155233923.84</v>
       </c>
       <c r="D41" s="6" t="n">
         <v>30068575.81</v>
@@ -2831,13 +2831,13 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1655665810.43</v>
+        <v>1655666281.77</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>238172777.86</v>
+        <v>238172838.96</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>45723993.31</v>
+        <v>45723994.53</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>8900667.25</v>
@@ -2846,19 +2846,19 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>2993006.14</v>
+        <v>2993005.86</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>4877201.72</v>
+        <v>4877201.27</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>322916170.91</v>
+        <v>322916232.49</v>
       </c>
       <c r="R41" s="10" t="n">
-        <v>0.3586814200401954</v>
+        <v>0.3586813700389345</v>
       </c>
     </row>
     <row r="42">
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1613722602.08</v>
+        <v>1613722990.15</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>202803300.35</v>
+        <v>202803340.18</v>
       </c>
       <c r="D42" s="6" t="n">
         <v>36982193.7</v>
@@ -2889,13 +2889,13 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1989296507.68</v>
+        <v>1989296935.58</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>282618229.62</v>
+        <v>282618324.75</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>59467972.27</v>
+        <v>59467977.05</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>13379956.09</v>
@@ -2904,19 +2904,19 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2562076.36</v>
+        <v>2562076.45</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>6710392.86</v>
+        <v>6710393.09</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>401336168.19</v>
+        <v>401336268.42</v>
       </c>
       <c r="R42" s="10" t="n">
-        <v>0.3748043859905762</v>
+        <v>0.374804382581988</v>
       </c>
     </row>
     <row r="43">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1427762935.73</v>
+        <v>1427764963.66</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>221857126.57</v>
+        <v>221859292.06</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>31660988.96</v>
@@ -2947,13 +2947,13 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1817547926.79</v>
+        <v>1817552120.21</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>232863017.83</v>
+        <v>232864303.05</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>61180264.16</v>
+        <v>61180817.13</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>8080178.7</v>
@@ -2962,19 +2962,19 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>2342310.48</v>
+        <v>2342317.79</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>6388131.25</v>
+        <v>6388151.19</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>343665375.71</v>
+        <v>343667241.14</v>
       </c>
       <c r="R43" s="10" t="n">
-        <v>0.3738082799669966</v>
+        <v>0.373808055436679</v>
       </c>
     </row>
     <row r="44">
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1480854495.23</v>
+        <v>1480854986.26</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>197998279.3</v>
+        <v>197999210.33</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>36482666.67</v>
@@ -3005,13 +3005,13 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1838734597.3</v>
+        <v>1838736019.36</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>248376276.39</v>
+        <v>248376608.58</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>51757451.41</v>
+        <v>51757760.82</v>
       </c>
       <c r="L44" s="9" t="n">
         <v>11549732.06</v>
@@ -3020,19 +3020,19 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>4638581.75</v>
+        <v>4638586.82</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6177343.96</v>
+        <v>6177350.73</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>349804309.01</v>
+        <v>349804962.45</v>
       </c>
       <c r="R44" s="10" t="n">
-        <v>0.3916156197964661</v>
+        <v>0.3916154766095744</v>
       </c>
     </row>
     <row r="45">
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>2194891335.65</v>
+        <v>2194895532.88</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>306596831.13</v>
+        <v>306596858.33</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>66142107.86</v>
@@ -3063,13 +3063,13 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2819797825.68</v>
+        <v>2819802050.11</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>400038602.04</v>
+        <v>400042110.09</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>76961502.72</v>
+        <v>76961510.28</v>
       </c>
       <c r="L45" s="9" t="n">
         <v>23893066.65</v>
@@ -3078,19 +3078,19 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>9471678.58</v>
+        <v>9471724.84</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>16166160.97</v>
+        <v>16166239.91</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>570536643.16</v>
+        <v>570540283.96</v>
       </c>
       <c r="R45" s="10" t="n">
-        <v>0.40067966485108</v>
+        <v>0.4006796632230236</v>
       </c>
     </row>
     <row r="46">
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>2305299214.24</v>
+        <v>2305300284.2</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>376107142.6</v>
+        <v>376108161.46</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>69142299.48</v>
@@ -3121,13 +3121,13 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>3105818662.53</v>
+        <v>3105820751.35</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>402169103.4</v>
+        <v>402169408.03</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>102191529.21</v>
+        <v>102191987.48</v>
       </c>
       <c r="L46" s="9" t="n">
         <v>23371135.67</v>
@@ -3136,19 +3136,19 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>10742331.73</v>
+        <v>10742338.01</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>19778544.22</v>
+        <v>19778555.78</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>620961500.63</v>
+        <v>620962281.38</v>
       </c>
       <c r="R46" s="10" t="n">
-        <v>0.442865215754716</v>
+        <v>0.442865097926909</v>
       </c>
     </row>
     <row r="47">
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1370755778.1</v>
+        <v>1370761394.41</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>250093696.52</v>
@@ -3179,10 +3179,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1802373990.63</v>
+        <v>1802379606.94</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>227511230.16</v>
+        <v>227514205.72</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>65852392.81</v>
@@ -3194,16 +3194,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>3449564.96</v>
+        <v>3449584.18</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>4879491.98</v>
+        <v>4879519.17</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>347850611.4</v>
+        <v>347853633.36</v>
       </c>
       <c r="R47" s="10" t="n">
         <v>0.4207679702437824</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1605866475.56</v>
+        <v>1605871041.63</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>251713084.28</v>
@@ -3237,10 +3237,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>2004188844.1</v>
+        <v>2004193410.17</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>256669523.34</v>
+        <v>256671760.57</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>62840730.8</v>
@@ -3252,16 +3252,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>4066667.4</v>
+        <v>4066683.65</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>5303345.47</v>
+        <v>5303366.67</v>
       </c>
       <c r="P48" s="9" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>362462389.56</v>
+        <v>362464664.24</v>
       </c>
       <c r="R48" s="10" t="n">
         <v>0.4544083188194561</v>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>1642708321.87</v>
+        <v>1642713225.95</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>255216837.43</v>
@@ -3295,10 +3295,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>2063061157.7</v>
+        <v>2063066061.78</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>257252804.75</v>
+        <v>257254032.32</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>63158844.13</v>
@@ -3310,16 +3310,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="9" t="n">
-        <v>4712177.07</v>
+        <v>4712181.75</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>5445745.05</v>
+        <v>5445750.45</v>
       </c>
       <c r="P49" s="9" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>367425043.19</v>
+        <v>367426280.83</v>
       </c>
       <c r="R49" s="10" t="n">
         <v>0.4715622688002217</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>1539510329.86</v>
+        <v>1539518945.56</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>251070477.59</v>
@@ -3353,10 +3353,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>1989400507.61</v>
+        <v>1989409123.31</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>263408298.27</v>
+        <v>263411374.68</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>57612870.57</v>
@@ -3368,16 +3368,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="9" t="n">
-        <v>4619968.46</v>
+        <v>4619986.79</v>
       </c>
       <c r="O50" s="9" t="n">
-        <v>5904410.78</v>
+        <v>5904434.21</v>
       </c>
       <c r="P50" s="9" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>375774693.53</v>
+        <v>375777811.7</v>
       </c>
       <c r="R50" s="10" t="n">
         <v>0.5184969295746537</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>1765206715.63</v>
+        <v>1765217564.19</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>287468135.92</v>
@@ -3411,10 +3411,10 @@
         <v>28011807</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>2267489117.06</v>
+        <v>2267499965.62</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>281262904.2</v>
+        <v>281267417.73</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>59780017.61</v>
@@ -3426,16 +3426,16 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="9" t="n">
-        <v>5175358.52</v>
+        <v>5175394.01</v>
       </c>
       <c r="O51" s="9" t="n">
-        <v>7388529.97</v>
+        <v>7388580.63</v>
       </c>
       <c r="P51" s="9" t="n">
         <v>13969238.87</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>395107300.93</v>
+        <v>395111900.61</v>
       </c>
       <c r="R51" s="10" t="n">
         <v>0.5173698555705437</v>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>2536929451.93</v>
+        <v>2536959580.32</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>438830798.95</v>
@@ -3469,10 +3469,10 @@
         <v>20465067</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>3325899349.99</v>
+        <v>3325929478.38</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>439508240.97</v>
+        <v>439519159.74</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>92879457.39</v>
@@ -3484,16 +3484,16 @@
         <v>15738266.69</v>
       </c>
       <c r="N52" s="9" t="n">
-        <v>7897917.47</v>
+        <v>7897988.96</v>
       </c>
       <c r="O52" s="9" t="n">
-        <v>23429607.39</v>
+        <v>23429819.47</v>
       </c>
       <c r="P52" s="9" t="n">
         <v>10232009.27</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>618552009.65</v>
+        <v>618563211.99</v>
       </c>
       <c r="R52" s="10" t="n">
         <v>0.4928123695831447</v>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>2708237290.11</v>
+        <v>2708461835.86</v>
       </c>
       <c r="C53" s="6" t="n">
         <v>590872240.37</v>
@@ -3527,10 +3527,10 @@
         <v>67156727</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>3867879544.14</v>
+        <v>3868104089.89</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>422369249.13</v>
+        <v>422460535.68</v>
       </c>
       <c r="K53" s="9" t="n">
         <v>126606680.82</v>
@@ -3542,23 +3542,81 @@
         <v>34860196.13</v>
       </c>
       <c r="N53" s="9" t="n">
-        <v>8425248.460000001</v>
+        <v>8425931.73</v>
       </c>
       <c r="O53" s="9" t="n">
-        <v>31888037.89</v>
+        <v>31890623.95</v>
       </c>
       <c r="P53" s="9" t="n">
         <v>33049467.84</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>679492016.8099999</v>
+        <v>679586572.6900001</v>
       </c>
       <c r="R53" s="10" t="n">
         <v>0.516687833119383</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1282885006.91</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>284348309.59</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>32474571.36</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>57588278</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>7363404.4</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>34662824</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>57503053</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>1756825447.26</v>
+      </c>
+      <c r="J54" s="8" t="n">
+        <v>213890258.88</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>74184906.98999999</v>
+      </c>
+      <c r="L54" s="9" t="n">
+        <v>11013728.59</v>
+      </c>
+      <c r="M54" s="9" t="n">
+        <v>11903181.4</v>
+      </c>
+      <c r="N54" s="9" t="n">
+        <v>1456753.47</v>
+      </c>
+      <c r="O54" s="9" t="n">
+        <v>6857587.4</v>
+      </c>
+      <c r="P54" s="9" t="n">
+        <v>28258572.47</v>
+      </c>
+      <c r="Q54" s="9" t="n">
+        <v>347564989.2</v>
+      </c>
+      <c r="R54" s="10" t="n">
+        <v>0.4317620090381182</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R53"/>
+  <autoFilter ref="A2:R54"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3574,7 +3632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6488,8 +6546,63 @@
         <v>900603747.12</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1450000000</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>286563759.1</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>32474571.36</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>57588278</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>7363404.4</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>39019322</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>58055983</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>1931065317.86</v>
+      </c>
+      <c r="J54" s="8" t="n">
+        <v>290435000</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>74503258.86</v>
+      </c>
+      <c r="L54" s="9" t="n">
+        <v>11013728.59</v>
+      </c>
+      <c r="M54" s="9" t="n">
+        <v>11903181.4</v>
+      </c>
+      <c r="N54" s="9" t="n">
+        <v>1626674.13</v>
+      </c>
+      <c r="O54" s="9" t="n">
+        <v>8619888.029999999</v>
+      </c>
+      <c r="P54" s="9" t="n">
+        <v>28496322.82</v>
+      </c>
+      <c r="Q54" s="9" t="n">
+        <v>426598053.83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:Q53"/>
+  <autoFilter ref="A2:Q54"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -6504,7 +6617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8721,7 +8834,7 @@
         <v>38042084</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>0.6983</v>
+        <v>0.6981999999999999</v>
       </c>
       <c r="I52" s="11" t="n">
         <v>0.4738</v>
@@ -8764,7 +8877,7 @@
         <v>47830508</v>
       </c>
       <c r="H53" s="11" t="n">
-        <v>0.7379000000000001</v>
+        <v>0.7378</v>
       </c>
       <c r="I53" s="11" t="n">
         <v>0.4838</v>
@@ -8782,15 +8895,58 @@
         <v>0.2635</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="12" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>914080000</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>14268394.25</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>36623329</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>110402683.25</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>6763656.95</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>11731471</v>
+      </c>
+      <c r="H54" s="11" t="n">
+        <v>0.7125</v>
+      </c>
+      <c r="I54" s="11" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="J54" s="11" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="K54" s="11" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="L54" s="11" t="n">
+        <v>0.9186</v>
+      </c>
+      <c r="M54" s="11" t="n">
+        <v>0.3384</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~3M-trade sample scaled to the daily total; ~62% of Kalshi's sports book by contracts, ~18% by $ (parlay legs are many and cheap). Not folded into the Sports tab's blended Combo % (sample-based, moves less day to day). Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M53"/>
+  <autoFilter ref="A2:M54"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1436292122.83</v>
+        <v>1436292162.39</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>133399888.66</v>
@@ -637,10 +637,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>1614254217.41</v>
+        <v>1614254256.97</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>299227422.63</v>
+        <v>299227432.12</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>50986272.22</v>
@@ -653,13 +653,13 @@
         <v>466111.75</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>8313323.47</v>
+        <v>8313323.49</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>361464764.48</v>
+        <v>361464773.99</v>
       </c>
       <c r="R3" s="10" t="n">
         <v>0.08714584215412201</v>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1205571579.51</v>
+        <v>1205571594.9</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>134065934.54</v>
@@ -691,10 +691,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1388976489.02</v>
+        <v>1388976504.41</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>231812319.19</v>
+        <v>231812323.09</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>51144509.72</v>
@@ -707,13 +707,13 @@
         <v>458019.24</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>8194676.3</v>
+        <v>8194676.32</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>296023120.51</v>
+        <v>296023124.43</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0.07635377691307524</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>889406923.05</v>
+        <v>889407055.26</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>85344135.09999999</v>
@@ -745,10 +745,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>1005449470.09</v>
+        <v>1005449602.3</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>202393069.54</v>
+        <v>202393103.87</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>31777180.84</v>
@@ -761,13 +761,13 @@
         <v>334880.88</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>4825438.95</v>
+        <v>4825438.99</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>243868671.75</v>
+        <v>243868706.13</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0.05231046649197771</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1155123713.37</v>
+        <v>1155123727.99</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>120394335.41</v>
@@ -801,10 +801,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>1339761862.39</v>
+        <v>1339761877.01</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>243084344.13</v>
+        <v>243084347.93</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>47471997.74</v>
@@ -825,7 +825,7 @@
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>312033576.4</v>
+        <v>312033580.21</v>
       </c>
       <c r="R6" s="10" t="n">
         <v>0.1040882840699126</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1187470733.41</v>
+        <v>1187470758.41</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>141146850.05</v>
@@ -917,10 +917,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1409643852.92</v>
+        <v>1409643877.92</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>236784575.48</v>
+        <v>236784582.23</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>50551741.94</v>
@@ -935,13 +935,13 @@
         <v>1121124.72</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>7508186.16</v>
+        <v>7508186.19</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>315423343.02</v>
+        <v>315423349.8</v>
       </c>
       <c r="R8" s="10" t="n">
         <v>0.09320593928966855</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1139472955.19</v>
+        <v>1139473267.71</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>117925601.54</v>
@@ -975,10 +975,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1323080116.73</v>
+        <v>1323080429.25</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>224392076.92</v>
+        <v>224392150.4</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>44939973.52</v>
@@ -990,16 +990,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>727221.24</v>
+        <v>727221.26</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>6114374.94</v>
+        <v>6114375.05</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>289885518.3</v>
+        <v>289885591.9</v>
       </c>
       <c r="R9" s="10" t="n">
         <v>0.100308786205459</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1265085721.25</v>
+        <v>1265085762.5</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>119094679.49</v>
@@ -1033,10 +1033,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1469751618.73</v>
+        <v>1469751659.98</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>247904360.5</v>
+        <v>247904369.99</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>44015511.37</v>
@@ -1048,16 +1048,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2089369.71</v>
+        <v>2089369.72</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>6720638.8</v>
+        <v>6720638.81</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>320414846.89</v>
+        <v>320414856.4</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>0.1305164739611011</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>817335185.02</v>
+        <v>817335188.77</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>76773291.01000001</v>
@@ -1149,10 +1149,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>944246876.05</v>
+        <v>944246879.8</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>157384965.37</v>
+        <v>157384966.27</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>28141958.88</v>
@@ -1173,7 +1173,7 @@
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>202040400.72</v>
+        <v>202040401.62</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>0.1320471995718654</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1149010908.63</v>
+        <v>1149010960.88</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>86060025.34</v>
@@ -1207,10 +1207,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1308567562.87</v>
+        <v>1308567615.12</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>235935037.53</v>
+        <v>235935049.43</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>32573678.23</v>
@@ -1222,7 +1222,7 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>2341917.8</v>
+        <v>2341917.81</v>
       </c>
       <c r="O13" s="9" t="n">
         <v>4886884.99</v>
@@ -1231,7 +1231,7 @@
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>294006388.77</v>
+        <v>294006400.68</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>0.1581581529884586</v>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1228237800.68</v>
+        <v>1228238414.69</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>130618679.53</v>
@@ -1323,10 +1323,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1450284900.49</v>
+        <v>1450285514.5</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>245766996.16</v>
+        <v>245767139.67</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>47519466.33</v>
@@ -1338,16 +1338,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>3332864.79</v>
+        <v>3332864.86</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>6989301.97</v>
+        <v>6989302.13</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>321979899.72</v>
+        <v>321980043.47</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>0.1338434618903201</v>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>1206694864.16</v>
+        <v>1206694960.17</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>122512075.89</v>
@@ -1381,10 +1381,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1408838743.19</v>
+        <v>1408838839.2</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>254178044.65</v>
+        <v>254178066.65</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>44967846.15</v>
@@ -1405,7 +1405,7 @@
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>322388004.09</v>
+        <v>322388026.09</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>0.1467243571212392</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>1502784943.2</v>
+        <v>1502785449.02</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>135215397.14</v>
@@ -1439,10 +1439,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1745506420.45</v>
+        <v>1745506926.27</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>307040479.14</v>
+        <v>307040581.16</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>48968794.7</v>
@@ -1454,16 +1454,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>3811143.17</v>
+        <v>3811143.06</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>8549315.68</v>
+        <v>8549315.439999999</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>388644933.88</v>
+        <v>388645035.55</v>
       </c>
       <c r="R17" s="10" t="n">
         <v>0.1671310595982739</v>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1333524743.97</v>
+        <v>1333524845.97</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>146617403.12</v>
@@ -1497,10 +1497,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1585699905.3</v>
+        <v>1585700007.3</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>261226753.68</v>
+        <v>261226775.88</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>56978627.74</v>
@@ -1512,16 +1512,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>3122211.8</v>
+        <v>3122211.79</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>9982348.24</v>
+        <v>9982348.23</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>348774270.56</v>
+        <v>348774292.75</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0.1404248555660547</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>918409296.78</v>
+        <v>918409350.51</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>100434174.96</v>
@@ -1555,10 +1555,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>1079826142.31</v>
+        <v>1079826196.04</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>188477035.9</v>
+        <v>188477047.25</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>36933011.94</v>
@@ -1570,16 +1570,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>2573290.38</v>
+        <v>2573290.37</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>4428373.38</v>
+        <v>4428373.36</v>
       </c>
       <c r="P19" s="9" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>245090542.59</v>
+        <v>245090553.91</v>
       </c>
       <c r="R19" s="10" t="n">
         <v>0.1248997633733931</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>1097888772.79</v>
+        <v>1097888803.57</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>104121932.82</v>
@@ -1613,10 +1613,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>1275892156.61</v>
+        <v>1275892187.39</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>215918663.38</v>
+        <v>215918670.38</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>38002578.37</v>
@@ -1631,13 +1631,13 @@
         <v>2738069.76</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>5494139.2</v>
+        <v>5494139.21</v>
       </c>
       <c r="P20" s="9" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>276651382.35</v>
+        <v>276651389.36</v>
       </c>
       <c r="R20" s="10" t="n">
         <v>0.178213812300984</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>1303187747.18</v>
+        <v>1303187878.18</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>122677612.96</v>
@@ -1671,10 +1671,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>1518488041</v>
+        <v>1518488172</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>252864878.23</v>
+        <v>252864908.46</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>44708007.56</v>
@@ -1686,16 +1686,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>3247081.53</v>
+        <v>3247081.55</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>6819803.22</v>
+        <v>6819803.26</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>326404183.68</v>
+        <v>326404213.98</v>
       </c>
       <c r="R21" s="10" t="n">
         <v>0.2003579150386557</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>1144724408.04</v>
+        <v>1144724469.81</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>132905659.86</v>
@@ -1729,10 +1729,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1368045413.62</v>
+        <v>1368045475.39</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>217696605.58</v>
+        <v>217696608.67</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>44439935.08</v>
@@ -1744,16 +1744,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>2916877.59</v>
+        <v>2916877.49</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>6698295.35</v>
+        <v>6698295.11</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>289776659.19</v>
+        <v>289776661.94</v>
       </c>
       <c r="R22" s="10" t="n">
         <v>0.180964978836361</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1190738823.27</v>
+        <v>1190738828.17</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>118302722.67</v>
@@ -1787,10 +1787,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1385895511.33</v>
+        <v>1385895516.23</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>229729887.06</v>
+        <v>229729888.28</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>35142057.4</v>
@@ -1811,7 +1811,7 @@
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>287479815.04</v>
+        <v>287479816.26</v>
       </c>
       <c r="R23" s="10" t="n">
         <v>0.316619068118602</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1612356752.76</v>
+        <v>1612356910.58</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>146513108.49</v>
@@ -1845,10 +1845,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1884573507.88</v>
+        <v>1884573665.7</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>316887749.18</v>
+        <v>316887782.33</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>43271898.85</v>
@@ -1863,13 +1863,13 @@
         <v>5435367.94</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>9097132.75</v>
+        <v>9097132.74</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>396272381.37</v>
+        <v>396272414.52</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>0.3069045894333504</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1377195069</v>
+        <v>1377195148.12</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>144797057.56</v>
@@ -1903,10 +1903,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1629695036.65</v>
+        <v>1629695115.77</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>256709125.58</v>
+        <v>256709142.39</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>45249277.15</v>
@@ -1921,13 +1921,13 @@
         <v>3355926.7</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>8780036.91</v>
+        <v>8780036.93</v>
       </c>
       <c r="P25" s="9" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>333318313.97</v>
+        <v>333318330.8</v>
       </c>
       <c r="R25" s="10" t="n">
         <v>0.2790295913221863</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>1037097872.4</v>
+        <v>1037097877.06</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>97537800.47</v>
@@ -1961,10 +1961,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1206202084.77</v>
+        <v>1206202089.43</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>200202110.31</v>
+        <v>200202111.47</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>31464287.45</v>
@@ -1976,16 +1976,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>2871147.68</v>
+        <v>2871147.69</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>5012247.17</v>
+        <v>5012247.18</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>250987316.8</v>
+        <v>250987317.96</v>
       </c>
       <c r="R26" s="10" t="n">
         <v>0.2509415863550032</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1198843168.33</v>
+        <v>1198843206.56</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>122103455.85</v>
@@ -2019,10 +2019,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>1406180576.29</v>
+        <v>1406180614.52</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>225000720.51</v>
+        <v>225000729.91</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>38650744.49</v>
@@ -2034,16 +2034,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>2585282.76</v>
+        <v>2585282.78</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>6112838.31</v>
+        <v>6112838.34</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>287799246.66</v>
+        <v>287799256.11</v>
       </c>
       <c r="R27" s="10" t="n">
         <v>0.2836514946154119</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1317392628.7</v>
+        <v>1317393138.59</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>146265225.05</v>
@@ -2077,10 +2077,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1563247528.35</v>
+        <v>1563248038.24</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>251063900.56</v>
+        <v>251064022.53</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>47820263.66</v>
@@ -2092,16 +2092,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>2381326.06</v>
+        <v>2381326.17</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>7749021.88</v>
+        <v>7749022.23</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>330050727.5</v>
+        <v>330050849.92</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0.2603327878455701</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>1110052118.66</v>
+        <v>1110052220.96</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>110832888.3</v>
@@ -2135,10 +2135,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1313999933.11</v>
+        <v>1314000035.41</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>203730159.16</v>
+        <v>203730180.25</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>33469362.8</v>
@@ -2153,13 +2153,13 @@
         <v>2592784.26</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>5824917.96</v>
+        <v>5824917.97</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>265596202.74</v>
+        <v>265596223.84</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0.2711837542671093</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1383850302.96</v>
+        <v>1383850370.5</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>97591814.65000001</v>
@@ -2193,10 +2193,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1576686787.03</v>
+        <v>1576686854.57</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>261337111.85</v>
+        <v>261337127.97</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>30161405.65</v>
@@ -2208,16 +2208,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>3726729.59</v>
+        <v>3726729.62</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>4002089.8</v>
+        <v>4002089.83</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>319907649.87</v>
+        <v>319907666.05</v>
       </c>
       <c r="R30" s="10" t="n">
         <v>0.3089090135319407</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1727299894.36</v>
+        <v>1727300829.21</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>164444551.54</v>
@@ -2251,10 +2251,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>2027356560.39</v>
+        <v>2027357495.24</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>296354868.5</v>
+        <v>296355095.24</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>46737225.01</v>
@@ -2266,16 +2266,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>3587886.04</v>
+        <v>3587886.5</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>5274098.12</v>
+        <v>5274098.8</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>386042041.52</v>
+        <v>386042269.41</v>
       </c>
       <c r="R31" s="10" t="n">
         <v>0.3202852257171364</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1572729725.12</v>
+        <v>1572729833.31</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>152797571.95</v>
@@ -2309,10 +2309,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>1832492809.24</v>
+        <v>1832492917.43</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>293610191.83</v>
+        <v>293610220.36</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>45961937.88</v>
@@ -2324,16 +2324,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>2694889.17</v>
+        <v>2694889.22</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>6570274.05</v>
+        <v>6570274.16</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>372626719.57</v>
+        <v>372626748.27</v>
       </c>
       <c r="R32" s="10" t="n">
         <v>0.3068596818867773</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>1305394516.16</v>
+        <v>1305394551.41</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>112904481.21</v>
@@ -2367,10 +2367,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>1491435542.27</v>
+        <v>1491435577.52</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>251861529.04</v>
+        <v>251861538.55</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>36710222.03</v>
@@ -2382,16 +2382,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>1463494.35</v>
+        <v>1463494.36</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>6347097.78</v>
+        <v>6347097.83</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>309527012.7</v>
+        <v>309527022.27</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0.2945849325840212</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1368370592.51</v>
+        <v>1368370792.51</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>111143043.36</v>
@@ -2425,10 +2425,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1592261716.49</v>
+        <v>1592261916.49</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>248806529.96</v>
+        <v>248806579.96</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>33583851.98</v>
@@ -2440,16 +2440,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>1142561.09</v>
+        <v>1142561.12</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>8125254.18</v>
+        <v>8125254.46</v>
       </c>
       <c r="P34" s="9" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>315334720.92</v>
+        <v>315334771.23</v>
       </c>
       <c r="R34" s="10" t="n">
         <v>0.3414174701179286</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1428042977.49</v>
+        <v>1428043055.58</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>132482297.68</v>
@@ -2483,10 +2483,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1671699989.16</v>
+        <v>1671700067.25</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>263139824.94</v>
+        <v>263139844.38</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>39009607.96</v>
@@ -2498,16 +2498,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>1891009.8</v>
+        <v>1891009.82</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>5945566.16</v>
+        <v>5945566.23</v>
       </c>
       <c r="P35" s="9" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>336440804.72</v>
+        <v>336440824.25</v>
       </c>
       <c r="R35" s="10" t="n">
         <v>0.3444918130280069</v>
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1456209168.75</v>
+        <v>1456209337.79</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>147816672.25</v>
@@ -2541,10 +2541,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>1723549459.62</v>
+        <v>1723549628.66</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>282236867.89</v>
+        <v>282236903.03</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>47162206.4</v>
@@ -2556,16 +2556,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>2226975.24</v>
+        <v>2226975.23</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>6426280.46</v>
+        <v>6426280.44</v>
       </c>
       <c r="P36" s="9" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>369372208.27</v>
+        <v>369372243.38</v>
       </c>
       <c r="R36" s="10" t="n">
         <v>0.3000842795719814</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1613188023.44</v>
+        <v>1613188231.2</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>161563899.02</v>
@@ -2599,10 +2599,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>1887508173.21</v>
+        <v>1887508380.97</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>289612509.79</v>
+        <v>289612568.54</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>49969404.96</v>
@@ -2614,16 +2614,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>2038734.82</v>
+        <v>2038734.92</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>7146308.6</v>
+        <v>7146308.95</v>
       </c>
       <c r="P37" s="9" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>371788461.65</v>
+        <v>371788520.85</v>
       </c>
       <c r="R37" s="10" t="n">
         <v>0.3158320949670745</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>2119622380.67</v>
+        <v>2119622643.15</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>172439724.32</v>
@@ -2657,10 +2657,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>2463685471.88</v>
+        <v>2463685734.36</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>378506261.85</v>
+        <v>378506324.78</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>46814572.08</v>
@@ -2672,16 +2672,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>3468831.68</v>
+        <v>3468831.77</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>5883474.53</v>
+        <v>5883474.68</v>
       </c>
       <c r="P38" s="9" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>478311348.23</v>
+        <v>478311411.4</v>
       </c>
       <c r="R38" s="10" t="n">
         <v>0.3730201312691256</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1628363765.23</v>
+        <v>1628363784.63</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>131412975.25</v>
@@ -2715,10 +2715,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>1915133551.83</v>
+        <v>1915133571.23</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>294597889.86</v>
+        <v>294597893.84</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>38038258.86</v>
@@ -2733,13 +2733,13 @@
         <v>4346489.07</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>6499228.51</v>
+        <v>6499228.52</v>
       </c>
       <c r="P39" s="9" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>384071397.12</v>
+        <v>384071401.1</v>
       </c>
       <c r="R39" s="10" t="n">
         <v>0.3654745795652588</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1241344552.98</v>
+        <v>1241345314.98</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>184349276.32</v>
@@ -2773,10 +2773,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1550722218.77</v>
+        <v>1550722980.77</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>227091122.61</v>
+        <v>227091307.62</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>52663679.72</v>
@@ -2788,16 +2788,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>3230022.87</v>
+        <v>3230023.13</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4087120.95</v>
+        <v>4087121.28</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>324537286.14</v>
+        <v>324537471.74</v>
       </c>
       <c r="R40" s="10" t="n">
         <v>0.3156021020167954</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1377183618.16</v>
+        <v>1377183724.71</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>155233923.84</v>
@@ -2831,10 +2831,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>1655666281.77</v>
+        <v>1655666388.32</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>238172838.96</v>
+        <v>238172864.89</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>45723994.53</v>
@@ -2846,16 +2846,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>2993005.86</v>
+        <v>2993005.91</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>4877201.27</v>
+        <v>4877201.34</v>
       </c>
       <c r="P41" s="9" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>322916232.49</v>
+        <v>322916258.55</v>
       </c>
       <c r="R41" s="10" t="n">
         <v>0.3586813700389345</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1613722990.15</v>
+        <v>1613723248.67</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>202803340.18</v>
@@ -2889,10 +2889,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1989296935.58</v>
+        <v>1989297194.1</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>282618324.75</v>
+        <v>282618381.96</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>59467977.05</v>
@@ -2904,16 +2904,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>2562076.45</v>
+        <v>2562076.48</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>6710393.09</v>
+        <v>6710393.18</v>
       </c>
       <c r="P42" s="9" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>401336268.42</v>
+        <v>401336325.75</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>0.374804382581988</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1427764963.66</v>
+        <v>1427764971.75</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>221859292.06</v>
@@ -2947,10 +2947,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1817552120.21</v>
+        <v>1817552128.3</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>232864303.05</v>
+        <v>232864304.72</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>61180817.13</v>
@@ -2971,7 +2971,7 @@
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>343667241.14</v>
+        <v>343667242.82</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>0.373808055436679</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1480854986.26</v>
+        <v>1480855814.27</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>197999210.33</v>
@@ -3005,10 +3005,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>1838736019.36</v>
+        <v>1838736847.37</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>248376608.58</v>
+        <v>248376796.92</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>51757760.82</v>
@@ -3020,16 +3020,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>4638586.82</v>
+        <v>4638587.25</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6177350.73</v>
+        <v>6177351.29</v>
       </c>
       <c r="P44" s="9" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>349804962.45</v>
+        <v>349805151.77</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>0.3916154766095744</v>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>2194895532.88</v>
+        <v>2194895684.57</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>306596858.33</v>
@@ -3063,10 +3063,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>2819802050.11</v>
+        <v>2819802201.8</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>400042110.09</v>
+        <v>400042153.69</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>76961510.28</v>
@@ -3078,16 +3078,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>9471724.84</v>
+        <v>9471725.060000001</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>16166239.91</v>
+        <v>16166240.29</v>
       </c>
       <c r="P45" s="9" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>570540283.96</v>
+        <v>570540328.17</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>0.4006796632230236</v>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>2305300284.2</v>
+        <v>2305300426.84</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>376108161.46</v>
@@ -3121,10 +3121,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>3105820751.35</v>
+        <v>3105820893.99</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>402169408.03</v>
+        <v>402169448.09</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>102191987.48</v>
@@ -3136,16 +3136,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="9" t="n">
-        <v>10742338.01</v>
+        <v>10742338.22</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>19778555.78</v>
+        <v>19778556.17</v>
       </c>
       <c r="P46" s="9" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>620962281.38</v>
+        <v>620962322.04</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0.442865097926909</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1370761394.41</v>
+        <v>1370761427</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>250093696.52</v>
@@ -3179,10 +3179,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>1802379606.94</v>
+        <v>1802379639.53</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>227514205.72</v>
+        <v>227514212.35</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>65852392.81</v>
@@ -3197,13 +3197,13 @@
         <v>3449584.18</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>4879519.17</v>
+        <v>4879519.18</v>
       </c>
       <c r="P47" s="9" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>347853633.36</v>
+        <v>347853640</v>
       </c>
       <c r="R47" s="10" t="n">
         <v>0.4207679702437824</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1605871041.63</v>
+        <v>1605872176.31</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>251713084.28</v>
@@ -3237,10 +3237,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>2004193410.17</v>
+        <v>2004194544.85</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>256671760.57</v>
+        <v>256671847.89</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>62840730.8</v>
@@ -3252,16 +3252,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>4066683.65</v>
+        <v>4066682.29</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>5303366.67</v>
+        <v>5303364.9</v>
       </c>
       <c r="P48" s="9" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>362464664.24</v>
+        <v>362464748.43</v>
       </c>
       <c r="R48" s="10" t="n">
         <v>0.4544083188194561</v>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>1642713225.95</v>
+        <v>1642713234.62</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>255216837.43</v>
@@ -3295,10 +3295,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>2063066061.78</v>
+        <v>2063066070.45</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>257254032.32</v>
+        <v>257254035.39</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>63158844.13</v>
@@ -3310,16 +3310,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="9" t="n">
-        <v>4712181.75</v>
+        <v>4712181.77</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>5445750.45</v>
+        <v>5445750.47</v>
       </c>
       <c r="P49" s="9" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>367426280.83</v>
+        <v>367426283.95</v>
       </c>
       <c r="R49" s="10" t="n">
         <v>0.4715622688002217</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>1539518945.56</v>
+        <v>1539518961.44</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>251070477.59</v>
@@ -3353,10 +3353,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>1989409123.31</v>
+        <v>1989409139.19</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>263411374.68</v>
+        <v>263411379.44</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>57612870.57</v>
@@ -3368,16 +3368,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="9" t="n">
-        <v>4619986.79</v>
+        <v>4619986.81</v>
       </c>
       <c r="O50" s="9" t="n">
-        <v>5904434.21</v>
+        <v>5904434.23</v>
       </c>
       <c r="P50" s="9" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>375777811.7</v>
+        <v>375777816.51</v>
       </c>
       <c r="R50" s="10" t="n">
         <v>0.5184969295746537</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>1765217564.19</v>
+        <v>1765217644.62</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>287468135.92</v>
@@ -3411,10 +3411,10 @@
         <v>28011807</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>2267499965.62</v>
+        <v>2267500046.05</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>281267417.73</v>
+        <v>281267439.22</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>59780017.61</v>
@@ -3426,16 +3426,16 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="9" t="n">
-        <v>5175394.01</v>
+        <v>5175394.11</v>
       </c>
       <c r="O51" s="9" t="n">
-        <v>7388580.63</v>
+        <v>7388580.77</v>
       </c>
       <c r="P51" s="9" t="n">
         <v>13969238.87</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>395111900.61</v>
+        <v>395111922.35</v>
       </c>
       <c r="R51" s="10" t="n">
         <v>0.5173698555705437</v>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>2536959580.32</v>
+        <v>2536960277.95</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>438830798.95</v>
@@ -3469,10 +3469,10 @@
         <v>20465067</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>3325929478.38</v>
+        <v>3325930176.01</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>439519159.74</v>
+        <v>439519440.63</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>92879457.39</v>
@@ -3484,16 +3484,16 @@
         <v>15738266.69</v>
       </c>
       <c r="N52" s="9" t="n">
-        <v>7897988.96</v>
+        <v>7897990.99</v>
       </c>
       <c r="O52" s="9" t="n">
-        <v>23429819.47</v>
+        <v>23429825.5</v>
       </c>
       <c r="P52" s="9" t="n">
         <v>10232009.27</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>618563211.99</v>
+        <v>618563500.9400001</v>
       </c>
       <c r="R52" s="10" t="n">
         <v>0.4928123695831447</v>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>2708461835.86</v>
+        <v>2708471971.18</v>
       </c>
       <c r="C53" s="6" t="n">
         <v>590872240.37</v>
@@ -3527,10 +3527,10 @@
         <v>67156727</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>3868104089.89</v>
+        <v>3868114225.21</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>422460535.68</v>
+        <v>422463870.59</v>
       </c>
       <c r="K53" s="9" t="n">
         <v>126606680.82</v>
@@ -3542,16 +3542,16 @@
         <v>34860196.13</v>
       </c>
       <c r="N53" s="9" t="n">
-        <v>8425931.73</v>
+        <v>8425952.220000001</v>
       </c>
       <c r="O53" s="9" t="n">
-        <v>31890623.95</v>
+        <v>31890701.48</v>
       </c>
       <c r="P53" s="9" t="n">
         <v>33049467.84</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>679586572.6900001</v>
+        <v>679590005.62</v>
       </c>
       <c r="R53" s="10" t="n">
         <v>0.516687833119383</v>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>1282885006.91</v>
+        <v>1282986326.04</v>
       </c>
       <c r="C54" s="6" t="n">
         <v>284348309.59</v>
@@ -3585,10 +3585,10 @@
         <v>57503053</v>
       </c>
       <c r="I54" s="7" t="n">
-        <v>1756825447.26</v>
+        <v>1756926766.39</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>213890258.88</v>
+        <v>213932273.92</v>
       </c>
       <c r="K54" s="9" t="n">
         <v>74184906.98999999</v>
@@ -3600,16 +3600,16 @@
         <v>11903181.4</v>
       </c>
       <c r="N54" s="9" t="n">
-        <v>1456753.47</v>
+        <v>1456847.81</v>
       </c>
       <c r="O54" s="9" t="n">
-        <v>6857587.4</v>
+        <v>6858031.48</v>
       </c>
       <c r="P54" s="9" t="n">
         <v>28258572.47</v>
       </c>
       <c r="Q54" s="9" t="n">
-        <v>347564989.2</v>
+        <v>347607542.66</v>
       </c>
       <c r="R54" s="10" t="n">
         <v>0.4317620090381182</v>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R54"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>889407055.26</v>
+        <v>889407458.1799999</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>85344135.09999999</v>
@@ -796,10 +796,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>1005449602.3</v>
+        <v>1005450005.22</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>202393103.87</v>
+        <v>202393160.48</v>
       </c>
       <c r="K5" s="12" t="n">
         <v>31777180.84</v>
@@ -809,16 +809,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>334880.88</v>
+        <v>334880.82</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>4825438.99</v>
+        <v>4825438.16</v>
       </c>
       <c r="P5" s="12" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>243868706.13</v>
+        <v>243868761.85</v>
       </c>
       <c r="R5" s="13" t="n">
         <v>0.05231046649197771</v>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1292326682.44</v>
+        <v>1292327073.33</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>125055737.8</v>
@@ -910,10 +910,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>1497406720.02</v>
+        <v>1497407110.91</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>259386594.51</v>
+        <v>259386650.04</v>
       </c>
       <c r="K7" s="12" t="n">
         <v>47948549.82</v>
@@ -925,16 +925,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>631739.84</v>
+        <v>631739.78</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>6846051.41</v>
+        <v>6846050.74</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>335565117.02</v>
+        <v>335565171.82</v>
       </c>
       <c r="R7" s="13" t="n">
         <v>0.1036604405692761</v>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1265085762.5</v>
+        <v>1265085795.24</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>119094679.49</v>
@@ -1084,10 +1084,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1469751659.98</v>
+        <v>1469751692.72</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>247904369.99</v>
+        <v>247904374.76</v>
       </c>
       <c r="K10" s="12" t="n">
         <v>44015511.37</v>
@@ -1099,16 +1099,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>2089369.72</v>
+        <v>2089369.7</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>6720638.81</v>
+        <v>6720638.76</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>320414856.4</v>
+        <v>320414861.1</v>
       </c>
       <c r="R10" s="13" t="n">
         <v>0.1305164739611011</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>1136156511.32</v>
+        <v>1136156655.83</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>126075255.12</v>
@@ -1142,10 +1142,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1360829828.44</v>
+        <v>1360829972.95</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>220224910.2</v>
+        <v>220224924.32</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>48533344.05</v>
@@ -1157,16 +1157,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2216238.84</v>
+        <v>2216238.7</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>7947076.26</v>
+        <v>7947075.77</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>302603566</v>
+        <v>302603579.49</v>
       </c>
       <c r="R11" s="13" t="n">
         <v>0.1174147553025735</v>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>817335188.77</v>
+        <v>817336492.33</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>76773291.01000001</v>
@@ -1200,10 +1200,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>944246879.8</v>
+        <v>944248183.36</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>157384966.27</v>
+        <v>157385033.16</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>28141958.88</v>
@@ -1215,16 +1215,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>1682384.89</v>
+        <v>1682383.08</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>3091090.56</v>
+        <v>3091087.24</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>202040401.62</v>
+        <v>202040463.38</v>
       </c>
       <c r="R12" s="13" t="n">
         <v>0.1320471995718654</v>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>1149010960.88</v>
+        <v>1149011433.47</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>86060025.34</v>
@@ -1258,10 +1258,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>1308567615.12</v>
+        <v>1308568087.71</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>235935049.43</v>
+        <v>235935054.26</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>32573678.23</v>
@@ -1273,16 +1273,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2341917.81</v>
+        <v>2341916.98</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>4886884.99</v>
+        <v>4886883.27</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>294006400.68</v>
+        <v>294006402.95</v>
       </c>
       <c r="R13" s="13" t="n">
         <v>0.1581581529884586</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>1239522251.9</v>
+        <v>1239522366.62</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>114182203.82</v>
@@ -1316,10 +1316,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>1441006441.97</v>
+        <v>1441006556.69</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>240227594.84</v>
+        <v>240227611.38</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>44020201.24</v>
@@ -1331,16 +1331,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2540876.52</v>
+        <v>2540876.44</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>6229750.46</v>
+        <v>6229750.29</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>313911293.25</v>
+        <v>313911309.55</v>
       </c>
       <c r="R14" s="13" t="n">
         <v>0.1369006174109096</v>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>1228238414.69</v>
+        <v>1228238448.25</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>130618679.53</v>
@@ -1374,10 +1374,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>1450285514.5</v>
+        <v>1450285548.06</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>245767139.67</v>
+        <v>245767143.36</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>47519466.33</v>
@@ -1389,16 +1389,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3332864.86</v>
+        <v>3332864.82</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>6989302.13</v>
+        <v>6989302.05</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>321980043.47</v>
+        <v>321980047.03</v>
       </c>
       <c r="R15" s="13" t="n">
         <v>0.1338434618903201</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>1206694960.17</v>
+        <v>1206695041.43</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>122512075.89</v>
@@ -1432,10 +1432,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>1408838839.2</v>
+        <v>1408838920.46</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>254178066.65</v>
+        <v>254178075.43</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>44967846.15</v>
@@ -1447,16 +1447,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>3170561.79</v>
+        <v>3170561.69</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>6715343.49</v>
+        <v>6715343.28</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>322388026.09</v>
+        <v>322388034.56</v>
       </c>
       <c r="R16" s="13" t="n">
         <v>0.1467243571212392</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1502785449.02</v>
+        <v>1502785584.78</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>135215397.14</v>
@@ -1490,10 +1490,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>1745506926.27</v>
+        <v>1745507062.03</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>307040581.16</v>
+        <v>307040594.98</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>48968794.7</v>
@@ -1505,16 +1505,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>3811143.06</v>
+        <v>3811142.9</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>8549315.439999999</v>
+        <v>8549315.07</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>388645035.55</v>
+        <v>388645048.83</v>
       </c>
       <c r="R17" s="13" t="n">
         <v>0.1671310595982739</v>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>1333524845.97</v>
+        <v>1333525136.35</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>146617403.12</v>
@@ -1548,10 +1548,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>1585700007.3</v>
+        <v>1585700297.68</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>261226775.88</v>
+        <v>261226803.09</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>56978627.74</v>
@@ -1563,16 +1563,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>3122211.79</v>
+        <v>3122211.45</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>9982348.23</v>
+        <v>9982347.140000001</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>348774292.75</v>
+        <v>348774318.53</v>
       </c>
       <c r="R18" s="13" t="n">
         <v>0.1404248555660547</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>918409350.51</v>
+        <v>918409510.1900001</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>100434174.96</v>
@@ -1606,10 +1606,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>1079826196.04</v>
+        <v>1079826355.72</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>188477047.25</v>
+        <v>188477064.19</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>36933011.94</v>
@@ -1621,16 +1621,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2573290.37</v>
+        <v>2573290.16</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>4428373.36</v>
+        <v>4428373.01</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>245090553.91</v>
+        <v>245090570.29</v>
       </c>
       <c r="R19" s="13" t="n">
         <v>0.1248997633733931</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>1097888803.57</v>
+        <v>1097888884.61</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>104121932.82</v>
@@ -1664,10 +1664,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>1275892187.39</v>
+        <v>1275892268.43</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>215918670.38</v>
+        <v>215918680.99</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>38002578.37</v>
@@ -1679,16 +1679,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2738069.76</v>
+        <v>2738069.69</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>5494139.21</v>
+        <v>5494139.07</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>276651389.36</v>
+        <v>276651399.76</v>
       </c>
       <c r="R20" s="13" t="n">
         <v>0.178213812300984</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>1144724469.81</v>
+        <v>1144724477.06</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>132905659.86</v>
@@ -1780,10 +1780,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>1368045475.39</v>
+        <v>1368045482.64</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>217696608.67</v>
+        <v>217696609.62</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>44439935.08</v>
@@ -1795,16 +1795,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>2916877.49</v>
+        <v>2916877.48</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>6698295.11</v>
+        <v>6698295.1</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>289776661.94</v>
+        <v>289776662.87</v>
       </c>
       <c r="R22" s="13" t="n">
         <v>0.180964978836361</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>1612356910.58</v>
+        <v>1612356965.58</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>146513108.49</v>
@@ -1896,10 +1896,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>1884573665.7</v>
+        <v>1884573720.7</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>316887782.33</v>
+        <v>316887786.18</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>43271898.85</v>
@@ -1911,16 +1911,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>5435367.94</v>
+        <v>5435367.83</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>9097132.74</v>
+        <v>9097132.560000001</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>396272414.52</v>
+        <v>396272418.07</v>
       </c>
       <c r="R24" s="13" t="n">
         <v>0.3069045894333504</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>1377195148.12</v>
+        <v>1377198087.71</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>144797057.56</v>
@@ -1954,10 +1954,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>1629695115.77</v>
+        <v>1629698055.36</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>256709142.39</v>
+        <v>256709219.93</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>45249277.15</v>
@@ -1969,16 +1969,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>3355926.7</v>
+        <v>3355921.23</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>8780036.93</v>
+        <v>8780022.609999999</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>333318330.8</v>
+        <v>333318388.56</v>
       </c>
       <c r="R25" s="13" t="n">
         <v>0.2790295913221863</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>1037097877.06</v>
+        <v>1037097889.06</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>97537800.47</v>
@@ -2012,10 +2012,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>1206202089.43</v>
+        <v>1206202101.43</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>200202111.47</v>
+        <v>200202112.91</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>31464287.45</v>
@@ -2027,16 +2027,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2871147.69</v>
+        <v>2871147.67</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>5012247.18</v>
+        <v>5012247.15</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>250987317.96</v>
+        <v>250987319.37</v>
       </c>
       <c r="R26" s="13" t="n">
         <v>0.2509415863550032</v>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>1198843206.56</v>
+        <v>1198843512.26</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>122103455.85</v>
@@ -2070,10 +2070,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>1406180614.52</v>
+        <v>1406180920.22</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>225000729.91</v>
+        <v>225000762.3</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>38650744.49</v>
@@ -2085,16 +2085,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>2585282.78</v>
+        <v>2585282.5</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>6112838.34</v>
+        <v>6112837.68</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>287799256.11</v>
+        <v>287799287.56</v>
       </c>
       <c r="R27" s="13" t="n">
         <v>0.2836514946154119</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>1317393138.59</v>
+        <v>1317393645.95</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>146265225.05</v>
@@ -2128,10 +2128,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>1563248038.24</v>
+        <v>1563248545.6</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>251064022.53</v>
+        <v>251064051.1</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>47820263.66</v>
@@ -2143,16 +2143,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2381326.17</v>
+        <v>2381325.58</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>7749022.23</v>
+        <v>7749020.32</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>330050849.92</v>
+        <v>330050876.01</v>
       </c>
       <c r="R28" s="13" t="n">
         <v>0.2603327878455701</v>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>1110052220.96</v>
+        <v>1110052739.17</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>110832888.3</v>
@@ -2186,10 +2186,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>1314000035.41</v>
+        <v>1314000553.62</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>203730180.25</v>
+        <v>203730236.92</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>33469362.8</v>
@@ -2201,16 +2201,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2592784.26</v>
+        <v>2592783.78</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>5824917.97</v>
+        <v>5824916.88</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>265596223.84</v>
+        <v>265596278.94</v>
       </c>
       <c r="R29" s="13" t="n">
         <v>0.2711837542671093</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>1383850370.5</v>
+        <v>1383850888.58</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>97591814.65000001</v>
@@ -2244,10 +2244,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>1576686854.57</v>
+        <v>1576687372.65</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>261337127.97</v>
+        <v>261337138.2</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>30161405.65</v>
@@ -2259,16 +2259,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>3726729.62</v>
+        <v>3726728.49</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>4002089.83</v>
+        <v>4002088.62</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>319907666.05</v>
+        <v>319907673.93</v>
       </c>
       <c r="R30" s="13" t="n">
         <v>0.3089090135319407</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>1727300829.21</v>
+        <v>1727301123.18</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>164444551.54</v>
@@ -2302,10 +2302,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>2027357495.24</v>
+        <v>2027357789.21</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>296355095.24</v>
+        <v>296355126.47</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>46737225.01</v>
@@ -2317,16 +2317,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>3587886.5</v>
+        <v>3587886.27</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>5274098.8</v>
+        <v>5274098.46</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>386042269.41</v>
+        <v>386042300.05</v>
       </c>
       <c r="R31" s="13" t="n">
         <v>0.3202852257171364</v>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>1572729833.31</v>
+        <v>1572730064.88</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>152797571.95</v>
@@ -2360,10 +2360,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>1832492917.43</v>
+        <v>1832493149</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>293610220.36</v>
+        <v>293610230.38</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>45961937.88</v>
@@ -2375,16 +2375,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>2694889.22</v>
+        <v>2694888.95</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>6570274.16</v>
+        <v>6570273.49</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>372626748.27</v>
+        <v>372626757.34</v>
       </c>
       <c r="R32" s="13" t="n">
         <v>0.3068596818867773</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>1305394551.41</v>
+        <v>1305395045.82</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>112904481.21</v>
@@ -2418,10 +2418,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>1491435577.52</v>
+        <v>1491436071.93</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>251861538.55</v>
+        <v>251861545.1</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>36710222.03</v>
@@ -2433,16 +2433,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1463494.36</v>
+        <v>1463493.89</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>6347097.83</v>
+        <v>6347095.81</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>309527022.27</v>
+        <v>309527026.33</v>
       </c>
       <c r="R33" s="13" t="n">
         <v>0.2945849325840212</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>1368370792.51</v>
+        <v>1368371108.65</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>111143043.36</v>
@@ -2476,10 +2476,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>1592261916.49</v>
+        <v>1592262232.63</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>248806579.96</v>
+        <v>248806601.45</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>33583851.98</v>
@@ -2491,16 +2491,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1142561.12</v>
+        <v>1142560.97</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>8125254.46</v>
+        <v>8125253.37</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>315334771.23</v>
+        <v>315334791.48</v>
       </c>
       <c r="R34" s="13" t="n">
         <v>0.3414174701179286</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>1428043055.58</v>
+        <v>1428043055.62</v>
       </c>
       <c r="C35" s="9" t="n">
         <v>132482297.68</v>
@@ -2534,7 +2534,7 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>1671700067.25</v>
+        <v>1671700067.29</v>
       </c>
       <c r="J35" s="11" t="n">
         <v>263139844.38</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>1456209337.79</v>
+        <v>1456209531.34</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>147816672.25</v>
@@ -2592,10 +2592,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>1723549628.66</v>
+        <v>1723549822.21</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>282236903.03</v>
+        <v>282236923.65</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>47162206.4</v>
@@ -2607,16 +2607,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>2226975.23</v>
+        <v>2226975.1</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>6426280.44</v>
+        <v>6426280.07</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>369372243.38</v>
+        <v>369372263.5</v>
       </c>
       <c r="R36" s="13" t="n">
         <v>0.3000842795719814</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>1613188231.2</v>
+        <v>1613188273.98</v>
       </c>
       <c r="C37" s="9" t="n">
         <v>161563899.02</v>
@@ -2650,10 +2650,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>1887508380.97</v>
+        <v>1887508423.75</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>289612568.54</v>
+        <v>289612573.24</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>49969404.96</v>
@@ -2665,16 +2665,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2038734.92</v>
+        <v>2038734.9</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>7146308.95</v>
+        <v>7146308.88</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>371788520.85</v>
+        <v>371788525.46</v>
       </c>
       <c r="R37" s="13" t="n">
         <v>0.3158320949670745</v>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>2119622643.15</v>
+        <v>2119622813.3</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>172439724.32</v>
@@ -2708,10 +2708,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>2463685734.36</v>
+        <v>2463685904.51</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>378506324.78</v>
+        <v>378506344.87</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>46814572.08</v>
@@ -2723,16 +2723,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>3468831.77</v>
+        <v>3468831.68</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>5883474.68</v>
+        <v>5883474.52</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>478311411.4</v>
+        <v>478311431.23</v>
       </c>
       <c r="R38" s="13" t="n">
         <v>0.3730201312691256</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>1628363784.63</v>
+        <v>1628364067.09</v>
       </c>
       <c r="C39" s="9" t="n">
         <v>131412975.25</v>
@@ -2766,10 +2766,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>1915133571.23</v>
+        <v>1915133853.69</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>294597893.84</v>
+        <v>294597919.64</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>38038258.86</v>
@@ -2781,16 +2781,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>4346489.07</v>
+        <v>4346488.71</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>6499228.52</v>
+        <v>6499227.98</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>384071401.1</v>
+        <v>384071426.01</v>
       </c>
       <c r="R39" s="13" t="n">
         <v>0.3654745795652588</v>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>1241345314.98</v>
+        <v>1241345745.98</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>184349276.32</v>
@@ -2824,10 +2824,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>1550722980.77</v>
+        <v>1550723411.77</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>227091307.62</v>
+        <v>227091326.94</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>52663679.72</v>
@@ -2839,16 +2839,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>3230023.13</v>
+        <v>3230022.41</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>4087121.28</v>
+        <v>4087120.37</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>324537471.74</v>
+        <v>324537489.43</v>
       </c>
       <c r="R40" s="13" t="n">
         <v>0.3156021020167954</v>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>1377183724.71</v>
+        <v>1377184264.3</v>
       </c>
       <c r="C41" s="9" t="n">
         <v>155233923.84</v>
@@ -2882,10 +2882,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>1655666388.32</v>
+        <v>1655666927.91</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>238172864.89</v>
+        <v>238172870.89</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>45723994.53</v>
@@ -2897,16 +2897,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>2993005.91</v>
+        <v>2993004.97</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>4877201.34</v>
+        <v>4877199.81</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>322916258.55</v>
+        <v>322916262.07</v>
       </c>
       <c r="R41" s="13" t="n">
         <v>0.3586813700389345</v>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>1613723248.67</v>
+        <v>1613724249.38</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>202803340.18</v>
@@ -2940,10 +2940,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>1989297194.1</v>
+        <v>1989298194.81</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>282618381.96</v>
+        <v>282618397.06</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>59467977.05</v>
@@ -2955,16 +2955,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>2562076.48</v>
+        <v>2562075.26</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>6710393.18</v>
+        <v>6710389.98</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>401336325.75</v>
+        <v>401336336.44</v>
       </c>
       <c r="R42" s="13" t="n">
         <v>0.374804382581988</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>1427764971.75</v>
+        <v>1427764995.74</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>221859292.06</v>
@@ -2998,10 +2998,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>1817552128.3</v>
+        <v>1817552152.29</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>232864304.72</v>
+        <v>232864307.21</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>61180817.13</v>
@@ -3013,16 +3013,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>2342317.79</v>
+        <v>2342317.78</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>6388151.19</v>
+        <v>6388151.15</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>343667242.82</v>
+        <v>343667245.25</v>
       </c>
       <c r="R43" s="13" t="n">
         <v>0.373808055436679</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>1480855814.27</v>
+        <v>1480855923.19</v>
       </c>
       <c r="C44" s="9" t="n">
         <v>197999210.33</v>
@@ -3056,10 +3056,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>1838736847.37</v>
+        <v>1838736956.29</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>248376796.92</v>
+        <v>248376802.14</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>51757760.82</v>
@@ -3071,16 +3071,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>4638587.25</v>
+        <v>4638587.03</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>6177351.29</v>
+        <v>6177351.01</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>349805151.77</v>
+        <v>349805156.5</v>
       </c>
       <c r="R44" s="13" t="n">
         <v>0.3916154766095744</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>2194895684.57</v>
+        <v>2194897379.12</v>
       </c>
       <c r="C45" s="9" t="n">
         <v>306596858.33</v>
@@ -3114,10 +3114,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>2819802201.8</v>
+        <v>2819803896.35</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>400042153.69</v>
+        <v>400042269.7</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>76961510.28</v>
@@ -3129,16 +3129,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>9471725.060000001</v>
+        <v>9471721.119999999</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>16166240.29</v>
+        <v>16166233.56</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>570540328.17</v>
+        <v>570540433.51</v>
       </c>
       <c r="R45" s="13" t="n">
         <v>0.4006796632230236</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>2305300426.84</v>
+        <v>2305301030.26</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>376108161.46</v>
@@ -3172,10 +3172,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>3105820893.99</v>
+        <v>3105821497.41</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>402169448.09</v>
+        <v>402169619.78</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>102191987.48</v>
@@ -3187,16 +3187,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>10742338.22</v>
+        <v>10742339.15</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>19778556.17</v>
+        <v>19778557.88</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>620962322.04</v>
+        <v>620962496.37</v>
       </c>
       <c r="R46" s="13" t="n">
         <v>0.442865097926909</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>1370761427</v>
+        <v>1370763829.29</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>250093696.52</v>
@@ -3230,10 +3230,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>1802379639.53</v>
+        <v>1802382041.82</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>227514212.35</v>
+        <v>227514873.45</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>65852392.81</v>
@@ -3245,16 +3245,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>3449584.18</v>
+        <v>3449586.19</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>4879519.18</v>
+        <v>4879522.01</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>347853640</v>
+        <v>347854305.94</v>
       </c>
       <c r="R47" s="13" t="n">
         <v>0.4207679702437824</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>1605872176.31</v>
+        <v>1605872697.74</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>251713084.28</v>
@@ -3288,10 +3288,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>2004194544.85</v>
+        <v>2004195066.28</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>256671847.89</v>
+        <v>256672009.65</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>62840730.8</v>
@@ -3303,16 +3303,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>4066682.29</v>
+        <v>4066683.07</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>5303364.9</v>
+        <v>5303365.91</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>362464748.43</v>
+        <v>362464911.98</v>
       </c>
       <c r="R48" s="13" t="n">
         <v>0.4544083188194561</v>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>1642713234.62</v>
+        <v>1642715400.81</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>255216837.43</v>
@@ -3346,10 +3346,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>2063066070.45</v>
+        <v>2063068236.64</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>257254035.39</v>
+        <v>257254199.7</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>63158844.13</v>
@@ -3361,16 +3361,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>4712181.77</v>
+        <v>4712178.84</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>5445750.47</v>
+        <v>5445747.1</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>367426283.95</v>
+        <v>367426441.96</v>
       </c>
       <c r="R49" s="13" t="n">
         <v>0.4715622688002217</v>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>1539518961.44</v>
+        <v>1539523365.13</v>
       </c>
       <c r="C50" s="9" t="n">
         <v>251070477.59</v>
@@ -3404,10 +3404,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>1989409139.19</v>
+        <v>1989413542.88</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>263411379.44</v>
+        <v>263412066.47</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>57612870.57</v>
@@ -3419,16 +3419,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>4619986.81</v>
+        <v>4619984.98</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>5904434.23</v>
+        <v>5904431.89</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>375777816.51</v>
+        <v>375778499.36</v>
       </c>
       <c r="R50" s="13" t="n">
         <v>0.5184969295746537</v>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>1765217644.62</v>
+        <v>1765220467.91</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>287468135.92</v>
@@ -3462,10 +3462,10 @@
         <v>28011807</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>2267500046.05</v>
+        <v>2267502869.34</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>281267439.22</v>
+        <v>281268960.17</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>59780017.61</v>
@@ -3477,16 +3477,16 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>5175394.11</v>
+        <v>5175408.03</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>7388580.77</v>
+        <v>7388600.65</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>13969238.87</v>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>395111922.35</v>
+        <v>395113477.09</v>
       </c>
       <c r="R51" s="13" t="n">
         <v>0.5173698555705437</v>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>2536960277.95</v>
+        <v>2536966421.09</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>438830798.95</v>
@@ -3520,10 +3520,10 @@
         <v>20465067</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>3325930176.01</v>
+        <v>3325936319.15</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>439519440.63</v>
+        <v>439522907.93</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>92879457.39</v>
@@ -3535,16 +3535,16 @@
         <v>15738266.69</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>7897990.99</v>
+        <v>7898022.26</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>23429825.5</v>
+        <v>23429918.26</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>10232009.27</v>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>618563500.9400001</v>
+        <v>618567092.27</v>
       </c>
       <c r="R52" s="13" t="n">
         <v>0.4928123695831447</v>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>2708471971.18</v>
+        <v>2708525121.57</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>590872240.37</v>
@@ -3578,10 +3578,10 @@
         <v>67156727</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>3868114225.21</v>
+        <v>3868167375.6</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>422463870.59</v>
+        <v>422490043.31</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>126606680.82</v>
@@ -3593,16 +3593,16 @@
         <v>34860196.13</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>8425952.220000001</v>
+        <v>8426174.109999999</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>31890701.48</v>
+        <v>31891541.28</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>33049467.84</v>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>679590005.62</v>
+        <v>679617240.03</v>
       </c>
       <c r="R53" s="13" t="n">
         <v>0.516687833119383</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>1282986326.04</v>
+        <v>1283305639.66</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>284348309.59</v>
@@ -3636,10 +3636,10 @@
         <v>57503053</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>1756926766.39</v>
+        <v>1757246080.01</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>213932273.92</v>
+        <v>214042401.28</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>74184906.98999999</v>
@@ -3651,23 +3651,65 @@
         <v>11903181.4</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1456847.81</v>
+        <v>1457049.37</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>6858031.48</v>
+        <v>6858980.32</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>28258572.47</v>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>347607542.66</v>
+        <v>347718820.42</v>
       </c>
       <c r="R54" s="13" t="n">
         <v>0.4317620090381182</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>1348587780.22</v>
+      </c>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="9" t="n"/>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="9" t="n">
+        <v>32458365</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>29175511</v>
+      </c>
+      <c r="I55" s="10" t="n">
+        <v>1410221656.22</v>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>230206095.55</v>
+      </c>
+      <c r="K55" s="12" t="n"/>
+      <c r="L55" s="12" t="n"/>
+      <c r="M55" s="12" t="n"/>
+      <c r="N55" s="12" t="n"/>
+      <c r="O55" s="12" t="n">
+        <v>5735465.78</v>
+      </c>
+      <c r="P55" s="12" t="n">
+        <v>13247763.43</v>
+      </c>
+      <c r="Q55" s="12" t="n">
+        <v>249189324.76</v>
+      </c>
+      <c r="R55" s="13" t="n">
+        <v>0.3459</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R54"/>
+  <autoFilter ref="A2:R55"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3683,7 +3725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6652,8 +6694,47 @@
         <v>426598053.83</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>1561065779.67</v>
+      </c>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="9" t="n"/>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="9" t="n">
+        <v>36689522</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>29709360</v>
+      </c>
+      <c r="I55" s="10" t="n">
+        <v>1627464661.67</v>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>312681475.67</v>
+      </c>
+      <c r="K55" s="12" t="n"/>
+      <c r="L55" s="12" t="n"/>
+      <c r="M55" s="12" t="n"/>
+      <c r="N55" s="12" t="n"/>
+      <c r="O55" s="12" t="n">
+        <v>7521757.01</v>
+      </c>
+      <c r="P55" s="12" t="n">
+        <v>13444987.69</v>
+      </c>
+      <c r="Q55" s="12" t="n">
+        <v>333648220.37</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:Q54"/>
+  <autoFilter ref="A2:Q55"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -6668,7 +6749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8971,7 +9052,7 @@
         <v>11731471</v>
       </c>
       <c r="H54" s="14" t="n">
-        <v>0.7125</v>
+        <v>0.7123</v>
       </c>
       <c r="I54" s="14" t="n">
         <v>0.4394</v>
@@ -8989,15 +9070,42 @@
         <v>0.3384</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="15" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="n">
+        <v>984095867.5</v>
+      </c>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="9" t="n"/>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="9" t="n">
+        <v>11228218</v>
+      </c>
+      <c r="H55" s="14" t="n">
+        <v>0.7297</v>
+      </c>
+      <c r="I55" s="14" t="n"/>
+      <c r="J55" s="14" t="n"/>
+      <c r="K55" s="14" t="n"/>
+      <c r="L55" s="14" t="n"/>
+      <c r="M55" s="14" t="n">
+        <v>0.3459</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~5M-trade sample (refreshed weekly) scaled to the daily total; ~70% of Kalshi's sports book by contracts, ~24% by $ (parlay legs are many and cheap - this sample-based split can move noticeably week to week, see VOLUME_METHODOLOGY.md). Not folded into the Sports tab's blended Combo %. Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M54"/>
+  <autoFilter ref="A2:M55"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>1205571594.9</v>
+        <v>1205571609.59</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>134065934.54</v>
@@ -742,10 +742,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>1388976504.41</v>
+        <v>1388976519.1</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>231812323.09</v>
+        <v>231812328.01</v>
       </c>
       <c r="K4" s="12" t="n">
         <v>51144509.72</v>
@@ -758,13 +758,13 @@
         <v>458019.24</v>
       </c>
       <c r="O4" s="12" t="n">
-        <v>8194676.32</v>
+        <v>8194676.37</v>
       </c>
       <c r="P4" s="12" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="12" t="n">
-        <v>296023124.43</v>
+        <v>296023129.4</v>
       </c>
       <c r="R4" s="13" t="n">
         <v>0.07635377691307524</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>889407458.1799999</v>
+        <v>889407805.64</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>85344135.09999999</v>
@@ -796,10 +796,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>1005450005.22</v>
+        <v>1005450352.68</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>202393160.48</v>
+        <v>202393301.41</v>
       </c>
       <c r="K5" s="12" t="n">
         <v>31777180.84</v>
@@ -809,16 +809,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>334880.82</v>
+        <v>334880.9</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>4825438.16</v>
+        <v>4825439.31</v>
       </c>
       <c r="P5" s="12" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>243868761.85</v>
+        <v>243868904</v>
       </c>
       <c r="R5" s="13" t="n">
         <v>0.05231046649197771</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1155123727.99</v>
+        <v>1155123729.11</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>120394335.41</v>
@@ -852,10 +852,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>1339761877.01</v>
+        <v>1339761878.13</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>243084347.93</v>
+        <v>243084348.72</v>
       </c>
       <c r="K6" s="12" t="n">
         <v>47471997.74</v>
@@ -870,13 +870,13 @@
         <v>288784.97</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>6546862.73</v>
+        <v>6546862.75</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>312033580.21</v>
+        <v>312033581.01</v>
       </c>
       <c r="R6" s="13" t="n">
         <v>0.1040882840699126</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1187470758.41</v>
+        <v>1187470769</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>141146850.05</v>
@@ -968,10 +968,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>1409643877.92</v>
+        <v>1409643888.51</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>236784582.23</v>
+        <v>236784587.05</v>
       </c>
       <c r="K8" s="12" t="n">
         <v>50551741.94</v>
@@ -983,16 +983,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>1121124.72</v>
+        <v>1121124.73</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>7508186.19</v>
+        <v>7508186.25</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>315423349.8</v>
+        <v>315423354.69</v>
       </c>
       <c r="R8" s="13" t="n">
         <v>0.09320593928966855</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1139473267.71</v>
+        <v>1139473490.06</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>117925601.54</v>
@@ -1026,10 +1026,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>1323080429.25</v>
+        <v>1323080651.6</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>224392150.4</v>
+        <v>224392246.56</v>
       </c>
       <c r="K9" s="12" t="n">
         <v>44939973.52</v>
@@ -1041,16 +1041,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>727221.26</v>
+        <v>727221.38</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>6114375.05</v>
+        <v>6114376.07</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>289885591.9</v>
+        <v>289885689.21</v>
       </c>
       <c r="R9" s="13" t="n">
         <v>0.100308786205459</v>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1265085795.24</v>
+        <v>1265085796.78</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>119094679.49</v>
@@ -1084,10 +1084,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1469751692.72</v>
+        <v>1469751694.26</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>247904374.76</v>
+        <v>247904375.33</v>
       </c>
       <c r="K10" s="12" t="n">
         <v>44015511.37</v>
@@ -1102,13 +1102,13 @@
         <v>2089369.7</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>6720638.76</v>
+        <v>6720638.77</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>320414861.1</v>
+        <v>320414861.68</v>
       </c>
       <c r="R10" s="13" t="n">
         <v>0.1305164739611011</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>1136156655.83</v>
+        <v>1136156661.83</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>126075255.12</v>
@@ -1142,10 +1142,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1360829972.95</v>
+        <v>1360829978.95</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>220224924.32</v>
+        <v>220224928.76</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>48533344.05</v>
@@ -1157,16 +1157,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2216238.7</v>
+        <v>2216238.72</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>7947075.77</v>
+        <v>7947075.85</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>302603579.49</v>
+        <v>302603584.04</v>
       </c>
       <c r="R11" s="13" t="n">
         <v>0.1174147553025735</v>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>817336492.33</v>
+        <v>817336493.87</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>76773291.01000001</v>
@@ -1200,10 +1200,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>944248183.36</v>
+        <v>944248184.9</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>157385033.16</v>
+        <v>157385033.81</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>28141958.88</v>
@@ -1218,13 +1218,13 @@
         <v>1682383.08</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>3091087.24</v>
+        <v>3091087.25</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>202040463.38</v>
+        <v>202040464.04</v>
       </c>
       <c r="R12" s="13" t="n">
         <v>0.1320471995718654</v>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>1149011433.47</v>
+        <v>1149011447.63</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>86060025.34</v>
@@ -1258,10 +1258,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>1308568087.71</v>
+        <v>1308568101.87</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>235935054.26</v>
+        <v>235935058.79</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>32573678.23</v>
@@ -1273,16 +1273,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2341916.98</v>
+        <v>2341916.99</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>4886883.27</v>
+        <v>4886883.29</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>294006402.95</v>
+        <v>294006407.52</v>
       </c>
       <c r="R13" s="13" t="n">
         <v>0.1581581529884586</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>1239522366.62</v>
+        <v>1239522404.62</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>114182203.82</v>
@@ -1316,10 +1316,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>1441006556.69</v>
+        <v>1441006594.69</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>240227611.38</v>
+        <v>240227632.66</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>44020201.24</v>
@@ -1331,16 +1331,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2540876.44</v>
+        <v>2540876.55</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>6229750.29</v>
+        <v>6229750.55</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>313911309.55</v>
+        <v>313911331.2</v>
       </c>
       <c r="R14" s="13" t="n">
         <v>0.1369006174109096</v>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>1228238448.25</v>
+        <v>1228238872.6</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>130618679.53</v>
@@ -1374,10 +1374,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>1450285548.06</v>
+        <v>1450285972.41</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>245767143.36</v>
+        <v>245767270.26</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>47519466.33</v>
@@ -1389,16 +1389,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3332864.82</v>
+        <v>3332865.17</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>6989302.05</v>
+        <v>6989302.78</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>321980047.03</v>
+        <v>321980175.02</v>
       </c>
       <c r="R15" s="13" t="n">
         <v>0.1338434618903201</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1502785584.78</v>
+        <v>1502785784.78</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>135215397.14</v>
@@ -1490,10 +1490,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>1745507062.03</v>
+        <v>1745507262.03</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>307040594.98</v>
+        <v>307040656.98</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>48968794.7</v>
@@ -1505,16 +1505,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>3811142.9</v>
+        <v>3811143.08</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>8549315.07</v>
+        <v>8549315.470000001</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>388645048.83</v>
+        <v>388645111.4</v>
       </c>
       <c r="R17" s="13" t="n">
         <v>0.1671310595982739</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>918409510.1900001</v>
+        <v>918409517.5599999</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>100434174.96</v>
@@ -1606,10 +1606,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>1079826355.72</v>
+        <v>1079826363.09</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>188477064.19</v>
+        <v>188477067.06</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>36933011.94</v>
@@ -1621,16 +1621,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2573290.16</v>
+        <v>2573290.17</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>4428373.01</v>
+        <v>4428373.03</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>245090570.29</v>
+        <v>245090573.19</v>
       </c>
       <c r="R19" s="13" t="n">
         <v>0.1248997633733931</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>1612356965.58</v>
+        <v>1612356969.85</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>146513108.49</v>
@@ -1896,10 +1896,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>1884573720.7</v>
+        <v>1884573724.97</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>316887786.18</v>
+        <v>316887788.1</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>43271898.85</v>
@@ -1911,16 +1911,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>5435367.83</v>
+        <v>5435367.85</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>9097132.560000001</v>
+        <v>9097132.59</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>396272418.07</v>
+        <v>396272420.03</v>
       </c>
       <c r="R24" s="13" t="n">
         <v>0.3069045894333504</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>1037097889.06</v>
+        <v>1037097908.91</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>97537800.47</v>
@@ -2012,10 +2012,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>1206202101.43</v>
+        <v>1206202121.28</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>200202112.91</v>
+        <v>200202122.82</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>31464287.45</v>
@@ -2027,16 +2027,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2871147.67</v>
+        <v>2871147.74</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>5012247.15</v>
+        <v>5012247.27</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>250987319.37</v>
+        <v>250987329.46</v>
       </c>
       <c r="R26" s="13" t="n">
         <v>0.2509415863550032</v>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>1110052739.17</v>
+        <v>1110052759.17</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>110832888.3</v>
@@ -2186,10 +2186,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>1314000553.62</v>
+        <v>1314000573.62</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>203730236.92</v>
+        <v>203730249.52</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>33469362.8</v>
@@ -2201,16 +2201,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2592783.78</v>
+        <v>2592783.86</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>5824916.88</v>
+        <v>5824917.07</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>265596278.94</v>
+        <v>265596291.82</v>
       </c>
       <c r="R29" s="13" t="n">
         <v>0.2711837542671093</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>1383850888.58</v>
+        <v>1383850891.57</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>97591814.65000001</v>
@@ -2244,10 +2244,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>1576687372.65</v>
+        <v>1576687375.64</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>261337138.2</v>
+        <v>261337140.13</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>30161405.65</v>
@@ -2259,16 +2259,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>3726728.49</v>
+        <v>3726728.5</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>4002088.62</v>
+        <v>4002088.63</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>319907673.93</v>
+        <v>319907675.9</v>
       </c>
       <c r="R30" s="13" t="n">
         <v>0.3089090135319407</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>1727301123.18</v>
+        <v>1727301335.46</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>164444551.54</v>
@@ -2302,10 +2302,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>2027357789.21</v>
+        <v>2027358001.49</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>296355126.47</v>
+        <v>296355202.27</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>46737225.01</v>
@@ -2317,16 +2317,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>3587886.27</v>
+        <v>3587886.61</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>5274098.46</v>
+        <v>5274098.95</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>386042300.05</v>
+        <v>386042376.69</v>
       </c>
       <c r="R31" s="13" t="n">
         <v>0.3202852257171364</v>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>1572730064.88</v>
+        <v>1572730499.58</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>152797571.95</v>
@@ -2360,10 +2360,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>1832493149</v>
+        <v>1832493583.7</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>293610230.38</v>
+        <v>293610505.67</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>45961937.88</v>
@@ -2375,16 +2375,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>2694888.95</v>
+        <v>2694890.33</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>6570273.49</v>
+        <v>6570276.87</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>372626757.34</v>
+        <v>372627037.4</v>
       </c>
       <c r="R32" s="13" t="n">
         <v>0.3068596818867773</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>1305395045.82</v>
+        <v>1305395286.57</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>112904481.21</v>
@@ -2418,10 +2418,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>1491436071.93</v>
+        <v>1491436312.68</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>251861545.1</v>
+        <v>251861625.92</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>36710222.03</v>
@@ -2433,16 +2433,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1463493.89</v>
+        <v>1463494.04</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>6347095.81</v>
+        <v>6347096.46</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>309527026.33</v>
+        <v>309527107.95</v>
       </c>
       <c r="R33" s="13" t="n">
         <v>0.2945849325840212</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>1368371108.65</v>
+        <v>1368371266.63</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>111143043.36</v>
@@ -2476,10 +2476,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>1592262232.63</v>
+        <v>1592262390.61</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>248806601.45</v>
+        <v>248806714.42</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>33583851.98</v>
@@ -2491,16 +2491,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1142560.97</v>
+        <v>1142561.28</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>8125253.37</v>
+        <v>8125255.54</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>315334791.48</v>
+        <v>315334906.92</v>
       </c>
       <c r="R34" s="13" t="n">
         <v>0.3414174701179286</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>1428043055.62</v>
+        <v>1428043073.62</v>
       </c>
       <c r="C35" s="9" t="n">
         <v>132482297.68</v>
@@ -2534,10 +2534,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>1671700067.29</v>
+        <v>1671700085.29</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>263139844.38</v>
+        <v>263139850.5</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>39009607.96</v>
@@ -2549,16 +2549,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1891009.82</v>
+        <v>1891009.83</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>5945566.23</v>
+        <v>5945566.27</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>336440824.25</v>
+        <v>336440830.42</v>
       </c>
       <c r="R35" s="13" t="n">
         <v>0.3444918130280069</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>1456209531.34</v>
+        <v>1456209531.4</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>147816672.25</v>
@@ -2592,10 +2592,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>1723549822.21</v>
+        <v>1723549822.27</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>282236923.65</v>
+        <v>282236923.69</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>47162206.4</v>
@@ -2616,7 +2616,7 @@
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>369372263.5</v>
+        <v>369372263.54</v>
       </c>
       <c r="R36" s="13" t="n">
         <v>0.3000842795719814</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>1613188273.98</v>
+        <v>1613188561.89</v>
       </c>
       <c r="C37" s="9" t="n">
         <v>161563899.02</v>
@@ -2650,10 +2650,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>1887508423.75</v>
+        <v>1887508711.66</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>289612573.24</v>
+        <v>289612674.85</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>49969404.96</v>
@@ -2665,16 +2665,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2038734.9</v>
+        <v>2038735.15</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>7146308.88</v>
+        <v>7146309.77</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>371788525.46</v>
+        <v>371788628.2</v>
       </c>
       <c r="R37" s="13" t="n">
         <v>0.3158320949670745</v>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>1241345745.98</v>
+        <v>1241345775.67</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>184349276.32</v>
@@ -2824,10 +2824,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>1550723411.77</v>
+        <v>1550723441.46</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>227091326.94</v>
+        <v>227091341.22</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>52663679.72</v>
@@ -2839,16 +2839,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>3230022.41</v>
+        <v>3230022.49</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>4087120.37</v>
+        <v>4087120.47</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>324537489.43</v>
+        <v>324537503.89</v>
       </c>
       <c r="R40" s="13" t="n">
         <v>0.3156021020167954</v>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>1613724249.38</v>
+        <v>1613725261.67</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>202803340.18</v>
@@ -2940,10 +2940,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>1989298194.81</v>
+        <v>1989299207.1</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>282618397.06</v>
+        <v>282618786.05</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>59467977.05</v>
@@ -2955,16 +2955,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>2562075.26</v>
+        <v>2562076.47</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>6710389.98</v>
+        <v>6710393.15</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>401336336.44</v>
+        <v>401336729.8</v>
       </c>
       <c r="R42" s="13" t="n">
         <v>0.374804382581988</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>1427764995.74</v>
+        <v>1427764997.47</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>221859292.06</v>
@@ -2998,10 +2998,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>1817552152.29</v>
+        <v>1817552154.02</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>232864307.21</v>
+        <v>232864307.92</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>61180817.13</v>
@@ -3016,13 +3016,13 @@
         <v>2342317.78</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>6388151.15</v>
+        <v>6388151.16</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>343667245.25</v>
+        <v>343667245.97</v>
       </c>
       <c r="R43" s="13" t="n">
         <v>0.373808055436679</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>2194897379.12</v>
+        <v>2194897929.17</v>
       </c>
       <c r="C45" s="9" t="n">
         <v>306596858.33</v>
@@ -3114,10 +3114,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>2819803896.35</v>
+        <v>2819804446.4</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>400042269.7</v>
+        <v>400042773.75</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>76961510.28</v>
@@ -3129,16 +3129,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>9471721.119999999</v>
+        <v>9471727.939999999</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>16166233.56</v>
+        <v>16166245.21</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>570540433.51</v>
+        <v>570540956.04</v>
       </c>
       <c r="R45" s="13" t="n">
         <v>0.4006796632230236</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>2305301030.26</v>
+        <v>2305301035.29</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>376108161.46</v>
@@ -3172,10 +3172,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>3105821497.41</v>
+        <v>3105821502.44</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>402169619.78</v>
+        <v>402169623.74</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>102191987.48</v>
@@ -3187,16 +3187,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>10742339.15</v>
+        <v>10742339.2</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>19778557.88</v>
+        <v>19778557.98</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>620962496.37</v>
+        <v>620962500.48</v>
       </c>
       <c r="R46" s="13" t="n">
         <v>0.442865097926909</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>1370763829.29</v>
+        <v>1370763912.37</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>250093696.52</v>
@@ -3230,10 +3230,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>1802382041.82</v>
+        <v>1802382124.9</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>227514873.45</v>
+        <v>227514915.57</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>65852392.81</v>
@@ -3245,16 +3245,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>3449586.19</v>
+        <v>3449586.46</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>4879522.01</v>
+        <v>4879522.39</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>347854305.94</v>
+        <v>347854348.7</v>
       </c>
       <c r="R47" s="13" t="n">
         <v>0.4207679702437824</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>1605872697.74</v>
+        <v>1605872968.06</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>251713084.28</v>
@@ -3288,10 +3288,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>2004195066.28</v>
+        <v>2004195336.6</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>256672009.65</v>
+        <v>256672087.31</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>62840730.8</v>
@@ -3303,16 +3303,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>4066683.07</v>
+        <v>4066683.4</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>5303365.91</v>
+        <v>5303366.35</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>362464911.98</v>
+        <v>362464990.41</v>
       </c>
       <c r="R48" s="13" t="n">
         <v>0.4544083188194561</v>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>1642715400.81</v>
+        <v>1642715866.58</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>255216837.43</v>
@@ -3346,10 +3346,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>2063068236.64</v>
+        <v>2063068702.41</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>257254199.7</v>
+        <v>257254303.6</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>63158844.13</v>
@@ -3361,16 +3361,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>4712178.84</v>
+        <v>4712179.12</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>5445747.1</v>
+        <v>5445747.42</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>367426441.96</v>
+        <v>367426546.46</v>
       </c>
       <c r="R49" s="13" t="n">
         <v>0.4715622688002217</v>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>1539523365.13</v>
+        <v>1539525034.58</v>
       </c>
       <c r="C50" s="9" t="n">
         <v>251070477.59</v>
@@ -3404,10 +3404,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>1989413542.88</v>
+        <v>1989415212.33</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>263412066.47</v>
+        <v>263413432.68</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>57612870.57</v>
@@ -3419,16 +3419,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>4619984.98</v>
+        <v>4619998.27</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>5904431.89</v>
+        <v>5904448.88</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>375778499.36</v>
+        <v>375779895.85</v>
       </c>
       <c r="R50" s="13" t="n">
         <v>0.5184969295746537</v>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>1765220467.91</v>
+        <v>1765221425.51</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>287468135.92</v>
@@ -3462,10 +3462,10 @@
         <v>28011807</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>2267502869.34</v>
+        <v>2267503826.94</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>281268960.17</v>
+        <v>281269263.53</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>59780017.61</v>
@@ -3477,16 +3477,16 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>5175408.03</v>
+        <v>5175409.88</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>7388600.65</v>
+        <v>7388603.28</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>13969238.87</v>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>395113477.09</v>
+        <v>395113784.93</v>
       </c>
       <c r="R51" s="13" t="n">
         <v>0.5173698555705437</v>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>2536966421.09</v>
+        <v>2536967708.16</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>438830798.95</v>
@@ -3520,10 +3520,10 @@
         <v>20465067</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>3325936319.15</v>
+        <v>3325937606.22</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>439522907.93</v>
+        <v>439523241.63</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>92879457.39</v>
@@ -3535,16 +3535,16 @@
         <v>15738266.69</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>7898022.26</v>
+        <v>7898023.53</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>23429918.26</v>
+        <v>23429922.02</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>10232009.27</v>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>618567092.27</v>
+        <v>618567431</v>
       </c>
       <c r="R52" s="13" t="n">
         <v>0.4928123695831447</v>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>2708525121.57</v>
+        <v>2708549732.51</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>590872240.37</v>
@@ -3578,10 +3578,10 @@
         <v>67156727</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>3868167375.6</v>
+        <v>3868191986.54</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>422490043.31</v>
+        <v>422501262.49</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>126606680.82</v>
@@ -3593,16 +3593,16 @@
         <v>34860196.13</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>8426174.109999999</v>
+        <v>8426264.99</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>31891541.28</v>
+        <v>31891885.25</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>33049467.84</v>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>679617240.03</v>
+        <v>679628894.05</v>
       </c>
       <c r="R53" s="13" t="n">
         <v>0.516687833119383</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>1283305639.66</v>
+        <v>1283393131.72</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>284348309.59</v>
@@ -3636,10 +3636,10 @@
         <v>57503053</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>1757246080.01</v>
+        <v>1757333572.07</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>214042401.28</v>
+        <v>214071162.53</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>74184906.98999999</v>
@@ -3651,16 +3651,16 @@
         <v>11903181.4</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1457049.37</v>
+        <v>1457098.52</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>6858980.32</v>
+        <v>6859211.67</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>28258572.47</v>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>347718820.42</v>
+        <v>347747862.16</v>
       </c>
       <c r="R54" s="13" t="n">
         <v>0.4317620090381182</v>
@@ -3673,12 +3673,20 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>1348587780.22</v>
-      </c>
-      <c r="C55" s="9" t="n"/>
-      <c r="D55" s="9" t="n"/>
-      <c r="E55" s="9" t="n"/>
-      <c r="F55" s="9" t="n"/>
+        <v>1534738131.47</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>305249223.57</v>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>41722458.11</v>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>37510457</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>15961471.65</v>
+      </c>
       <c r="G55" s="9" t="n">
         <v>32458365</v>
       </c>
@@ -3686,26 +3694,34 @@
         <v>29175511</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>1410221656.22</v>
+        <v>1996815617.8</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>230206095.55</v>
-      </c>
-      <c r="K55" s="12" t="n"/>
-      <c r="L55" s="12" t="n"/>
-      <c r="M55" s="12" t="n"/>
-      <c r="N55" s="12" t="n"/>
+        <v>255002702.23</v>
+      </c>
+      <c r="K55" s="12" t="n">
+        <v>60959047.28</v>
+      </c>
+      <c r="L55" s="12" t="n">
+        <v>11132266.45</v>
+      </c>
+      <c r="M55" s="12" t="n">
+        <v>8988100.75</v>
+      </c>
+      <c r="N55" s="12" t="n">
+        <v>2861748.64</v>
+      </c>
       <c r="O55" s="12" t="n">
-        <v>5735465.78</v>
+        <v>5819493.59</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>13247763.43</v>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>249189324.76</v>
+        <v>358011122.37</v>
       </c>
       <c r="R55" s="13" t="n">
-        <v>0.3459</v>
+        <v>0.5085823534173731</v>
       </c>
     </row>
   </sheetData>
@@ -6701,12 +6717,20 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>1561065779.67</v>
-      </c>
-      <c r="C55" s="9" t="n"/>
-      <c r="D55" s="9" t="n"/>
-      <c r="E55" s="9" t="n"/>
-      <c r="F55" s="9" t="n"/>
+        <v>1800000000</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>308120133.5</v>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>41722458.11</v>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>37510457</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>15961471.65</v>
+      </c>
       <c r="G55" s="9" t="n">
         <v>36689522</v>
       </c>
@@ -6714,23 +6738,31 @@
         <v>29709360</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>1627464661.67</v>
+        <v>2269713402.26</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>312681475.67</v>
-      </c>
-      <c r="K55" s="12" t="n"/>
-      <c r="L55" s="12" t="n"/>
-      <c r="M55" s="12" t="n"/>
-      <c r="N55" s="12" t="n"/>
+        <v>360540000</v>
+      </c>
+      <c r="K55" s="12" t="n">
+        <v>61476075.38</v>
+      </c>
+      <c r="L55" s="12" t="n">
+        <v>11132266.45</v>
+      </c>
+      <c r="M55" s="12" t="n">
+        <v>8988100.75</v>
+      </c>
+      <c r="N55" s="12" t="n">
+        <v>3279903.2</v>
+      </c>
       <c r="O55" s="12" t="n">
-        <v>7521757.01</v>
+        <v>7539284.8</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>13444987.69</v>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>333648220.37</v>
+        <v>466400618.26</v>
       </c>
     </row>
   </sheetData>
@@ -9052,7 +9084,7 @@
         <v>11731471</v>
       </c>
       <c r="H54" s="14" t="n">
-        <v>0.7123</v>
+        <v>0.7121999999999999</v>
       </c>
       <c r="I54" s="14" t="n">
         <v>0.4394</v>
@@ -9077,22 +9109,38 @@
         </is>
       </c>
       <c r="B55" s="9" t="n">
-        <v>984095867.5</v>
-      </c>
-      <c r="C55" s="9" t="n"/>
-      <c r="D55" s="9" t="n"/>
-      <c r="E55" s="9" t="n"/>
-      <c r="F55" s="9" t="n"/>
+        <v>1134720000</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>19045498.4</v>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>22905214</v>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>151961620.57</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>15035317.6</v>
+      </c>
       <c r="G55" s="9" t="n">
         <v>11228218</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>0.7297</v>
-      </c>
-      <c r="I55" s="14" t="n"/>
-      <c r="J55" s="14" t="n"/>
-      <c r="K55" s="14" t="n"/>
-      <c r="L55" s="14" t="n"/>
+        <v>0.7393999999999999</v>
+      </c>
+      <c r="I55" s="14" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="J55" s="14" t="n">
+        <v>0.6106</v>
+      </c>
+      <c r="K55" s="14" t="n">
+        <v>0.4978</v>
+      </c>
+      <c r="L55" s="14" t="n">
+        <v>0.9420000000000001</v>
+      </c>
       <c r="M55" s="14" t="n">
         <v>0.3459</v>
       </c>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -9396,7 +9396,7 @@
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>Volume-weighted avg. from Kalshi's own trade feed - the sports figure prices each series off its exact per-trade VWAP; the whole-exchange total uses a ~5M-trade sample of the public feed, refreshed weekly.</t>
+          <t>Volume-weighted avg. from Kalshi's own trade feed - the sports figure prices each series off its exact per-trade VWAP; the whole-exchange total uses a ~5M-trade sample of the public feed, refreshed weekly. Separately: the whole-exchange CONTRACT COUNT (not this price) comes from DeFi Rate, who display it abbreviated (e.g. "$2.09B") - about +/-0.3% built-in rounding vs. the exact per-market figures the other six venues give us.</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R55"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>1436292162.39</v>
+        <v>1436292621.39</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>133399888.66</v>
@@ -688,10 +688,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>1614254256.97</v>
+        <v>1614254715.97</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>299227432.12</v>
+        <v>299227596.16</v>
       </c>
       <c r="K3" s="12" t="n">
         <v>50986272.22</v>
@@ -701,16 +701,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>466111.75</v>
+        <v>466111.83</v>
       </c>
       <c r="O3" s="12" t="n">
-        <v>8313323.49</v>
+        <v>8313324.93</v>
       </c>
       <c r="P3" s="12" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="12" t="n">
-        <v>361464773.99</v>
+        <v>361464939.55</v>
       </c>
       <c r="R3" s="13" t="n">
         <v>0.08714584215412201</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>1205571609.59</v>
+        <v>1205571755.95</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>134065934.54</v>
@@ -742,10 +742,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>1388976519.1</v>
+        <v>1388976665.46</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>231812328.01</v>
+        <v>231812362.42</v>
       </c>
       <c r="K4" s="12" t="n">
         <v>51144509.72</v>
@@ -755,16 +755,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>458019.24</v>
+        <v>458019.25</v>
       </c>
       <c r="O4" s="12" t="n">
-        <v>8194676.37</v>
+        <v>8194676.46</v>
       </c>
       <c r="P4" s="12" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="12" t="n">
-        <v>296023129.4</v>
+        <v>296023163.91</v>
       </c>
       <c r="R4" s="13" t="n">
         <v>0.07635377691307524</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>889407805.64</v>
+        <v>889408055.46</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>85344135.09999999</v>
@@ -796,10 +796,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>1005450352.68</v>
+        <v>1005450602.5</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>202393301.41</v>
+        <v>202393360.57</v>
       </c>
       <c r="K5" s="12" t="n">
         <v>31777180.84</v>
@@ -812,13 +812,13 @@
         <v>334880.9</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>4825439.31</v>
+        <v>4825439.28</v>
       </c>
       <c r="P5" s="12" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>243868904</v>
+        <v>243868963.13</v>
       </c>
       <c r="R5" s="13" t="n">
         <v>0.05231046649197771</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1155123729.11</v>
+        <v>1155124034.98</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>120394335.41</v>
@@ -852,10 +852,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>1339761878.13</v>
+        <v>1339762184</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>243084348.72</v>
+        <v>243084458.1</v>
       </c>
       <c r="K6" s="12" t="n">
         <v>47471997.74</v>
@@ -867,16 +867,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>288784.97</v>
+        <v>288785.01</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>6546862.75</v>
+        <v>6546863.56</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>312033581.01</v>
+        <v>312033691.24</v>
       </c>
       <c r="R6" s="13" t="n">
         <v>0.1040882840699126</v>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1292327073.33</v>
+        <v>1292327121.89</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>125055737.8</v>
@@ -910,10 +910,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>1497407110.91</v>
+        <v>1497407159.47</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>259386650.04</v>
+        <v>259386661.65</v>
       </c>
       <c r="K7" s="12" t="n">
         <v>47948549.82</v>
@@ -928,13 +928,13 @@
         <v>631739.78</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>6846050.74</v>
+        <v>6846050.76</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>335565171.82</v>
+        <v>335565183.45</v>
       </c>
       <c r="R7" s="13" t="n">
         <v>0.1036604405692761</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1187470769</v>
+        <v>1187471131.96</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>141146850.05</v>
@@ -968,10 +968,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>1409643888.51</v>
+        <v>1409644251.47</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>236784587.05</v>
+        <v>236784644.97</v>
       </c>
       <c r="K8" s="12" t="n">
         <v>50551741.94</v>
@@ -983,16 +983,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>1121124.73</v>
+        <v>1121124.65</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>7508186.25</v>
+        <v>7508185.68</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>315423354.69</v>
+        <v>315423411.95</v>
       </c>
       <c r="R8" s="13" t="n">
         <v>0.09320593928966855</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1139473490.06</v>
+        <v>1139473853.53</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>117925601.54</v>
@@ -1026,10 +1026,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>1323080651.6</v>
+        <v>1323081015.07</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>224392246.56</v>
+        <v>224392328.29</v>
       </c>
       <c r="K9" s="12" t="n">
         <v>44939973.52</v>
@@ -1044,13 +1044,13 @@
         <v>727221.38</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>6114376.07</v>
+        <v>6114376.12</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>289885689.21</v>
+        <v>289885770.99</v>
       </c>
       <c r="R9" s="13" t="n">
         <v>0.100308786205459</v>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1265085796.78</v>
+        <v>1265086031.78</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>119094679.49</v>
@@ -1084,10 +1084,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1469751694.26</v>
+        <v>1469751929.26</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>247904375.33</v>
+        <v>247904404.68</v>
       </c>
       <c r="K10" s="12" t="n">
         <v>44015511.37</v>
@@ -1099,16 +1099,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>2089369.7</v>
+        <v>2089369.56</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>6720638.77</v>
+        <v>6720638.29</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>320414861.68</v>
+        <v>320414890.41</v>
       </c>
       <c r="R10" s="13" t="n">
         <v>0.1305164739611011</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>1136156661.83</v>
+        <v>1136156873.5</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>126075255.12</v>
@@ -1142,10 +1142,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1360829978.95</v>
+        <v>1360830190.62</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>220224928.76</v>
+        <v>220224960.28</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>48533344.05</v>
@@ -1157,16 +1157,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2216238.72</v>
+        <v>2216238.61</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>7947075.85</v>
+        <v>7947075.43</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>302603584.04</v>
+        <v>302603615.02</v>
       </c>
       <c r="R11" s="13" t="n">
         <v>0.1174147553025735</v>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>817336493.87</v>
+        <v>817337625.74</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>76773291.01000001</v>
@@ -1200,10 +1200,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>944248184.9</v>
+        <v>944249316.77</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>157385033.81</v>
+        <v>157385713.38</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>28141958.88</v>
@@ -1215,16 +1215,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>1682383.08</v>
+        <v>1682386.81</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>3091087.25</v>
+        <v>3091094.1</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>202040464.04</v>
+        <v>202041154.19</v>
       </c>
       <c r="R12" s="13" t="n">
         <v>0.1320471995718654</v>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>1149011447.63</v>
+        <v>1149011828.88</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>86060025.34</v>
@@ -1258,10 +1258,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>1308568101.87</v>
+        <v>1308568483.12</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>235935058.79</v>
+        <v>235935104.97</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>32573678.23</v>
@@ -1273,16 +1273,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2341916.99</v>
+        <v>2341916.67</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>4886883.29</v>
+        <v>4886882.62</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>294006407.52</v>
+        <v>294006452.7</v>
       </c>
       <c r="R13" s="13" t="n">
         <v>0.1581581529884586</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>1239522404.62</v>
+        <v>1239523185.61</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>114182203.82</v>
@@ -1316,10 +1316,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>1441006594.69</v>
+        <v>1441007375.68</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>240227632.66</v>
+        <v>240227738.39</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>44020201.24</v>
@@ -1331,16 +1331,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2540876.55</v>
+        <v>2540876.02</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>6229750.55</v>
+        <v>6229749.24</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>313911331.2</v>
+        <v>313911435.08</v>
       </c>
       <c r="R14" s="13" t="n">
         <v>0.1369006174109096</v>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>1228238872.6</v>
+        <v>1228242328.29</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>130618679.53</v>
@@ -1374,10 +1374,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>1450285972.41</v>
+        <v>1450289428.1</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>245767270.26</v>
+        <v>245769284.68</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>47519466.33</v>
@@ -1389,16 +1389,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3332865.17</v>
+        <v>3332878.51</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>6989302.78</v>
+        <v>6989330.75</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>321980175.02</v>
+        <v>321982230.74</v>
       </c>
       <c r="R15" s="13" t="n">
         <v>0.1338434618903201</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>1206695041.43</v>
+        <v>1206695871.54</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>122512075.89</v>
@@ -1432,10 +1432,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>1408838920.46</v>
+        <v>1408839750.57</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>254178075.43</v>
+        <v>254178401.9</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>44967846.15</v>
@@ -1447,16 +1447,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>3170561.69</v>
+        <v>3170563.08</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>6715343.28</v>
+        <v>6715346.22</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>322388034.56</v>
+        <v>322388365.35</v>
       </c>
       <c r="R16" s="13" t="n">
         <v>0.1467243571212392</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1502785784.78</v>
+        <v>1502785997.89</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>135215397.14</v>
@@ -1490,10 +1490,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>1745507262.03</v>
+        <v>1745507475.14</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>307040656.98</v>
+        <v>307040803.3</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>48968794.7</v>
@@ -1505,16 +1505,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>3811143.08</v>
+        <v>3811144.08</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>8549315.470000001</v>
+        <v>8549317.710000001</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>388645111.4</v>
+        <v>388645260.97</v>
       </c>
       <c r="R17" s="13" t="n">
         <v>0.1671310595982739</v>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>1333525136.35</v>
+        <v>1333526172.18</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>146617403.12</v>
@@ -1548,10 +1548,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>1585700297.68</v>
+        <v>1585701333.51</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>261226803.09</v>
+        <v>261227195.29</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>56978627.74</v>
@@ -1563,16 +1563,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>3122211.45</v>
+        <v>3122212.98</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>9982347.140000001</v>
+        <v>9982352.029999999</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>348774318.53</v>
+        <v>348774717.14</v>
       </c>
       <c r="R18" s="13" t="n">
         <v>0.1404248555660547</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>918409517.5599999</v>
+        <v>918409554.3099999</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>100434174.96</v>
@@ -1606,10 +1606,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>1079826363.09</v>
+        <v>1079826399.84</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>188477067.06</v>
+        <v>188477086.68</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>36933011.94</v>
@@ -1621,16 +1621,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2573290.17</v>
+        <v>2573290.3</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>4428373.03</v>
+        <v>4428373.24</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>245090573.19</v>
+        <v>245090593.14</v>
       </c>
       <c r="R19" s="13" t="n">
         <v>0.1248997633733931</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>1097888884.61</v>
+        <v>1097889067.26</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>104121932.82</v>
@@ -1664,10 +1664,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>1275892268.43</v>
+        <v>1275892451.08</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>215918680.99</v>
+        <v>215918800.59</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>38002578.37</v>
@@ -1679,16 +1679,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2738069.69</v>
+        <v>2738070.51</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>5494139.07</v>
+        <v>5494140.7</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>276651399.76</v>
+        <v>276651521.81</v>
       </c>
       <c r="R20" s="13" t="n">
         <v>0.178213812300984</v>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>1303187878.18</v>
+        <v>1303188544</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>122677612.96</v>
@@ -1722,10 +1722,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>1518488172</v>
+        <v>1518488837.82</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>252864908.46</v>
+        <v>252865081.71</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>44708007.56</v>
@@ -1737,16 +1737,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>3247081.55</v>
+        <v>3247081.86</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>6819803.26</v>
+        <v>6819803.91</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>326404213.98</v>
+        <v>326404388.19</v>
       </c>
       <c r="R21" s="13" t="n">
         <v>0.2003579150386557</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>1144724477.06</v>
+        <v>1144725375.7</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>132905659.86</v>
@@ -1780,10 +1780,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>1368045482.64</v>
+        <v>1368046381.28</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>217696609.62</v>
+        <v>217697235.87</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>44439935.08</v>
@@ -1795,16 +1795,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>2916877.48</v>
+        <v>2916882.02</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>6698295.1</v>
+        <v>6698305.52</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>289776662.87</v>
+        <v>289777304.08</v>
       </c>
       <c r="R22" s="13" t="n">
         <v>0.180964978836361</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>1190738828.17</v>
+        <v>1190739704.81</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>118302722.67</v>
@@ -1838,10 +1838,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>1385895516.23</v>
+        <v>1385896392.87</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>229729888.28</v>
+        <v>229729929.14</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>35142057.4</v>
@@ -1853,16 +1853,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>3441499.65</v>
+        <v>3441497.91</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>5603933.4</v>
+        <v>5603930.56</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>287479816.26</v>
+        <v>287479852.54</v>
       </c>
       <c r="R23" s="13" t="n">
         <v>0.316619068118602</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>1612356969.85</v>
+        <v>1612357613.17</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>146513108.49</v>
@@ -1896,10 +1896,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>1884573724.97</v>
+        <v>1884574368.29</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>316887788.1</v>
+        <v>316887970.26</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>43271898.85</v>
@@ -1911,16 +1911,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>5435367.85</v>
+        <v>5435368.52</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>9097132.59</v>
+        <v>9097133.699999999</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>396272420.03</v>
+        <v>396272603.98</v>
       </c>
       <c r="R24" s="13" t="n">
         <v>0.3069045894333504</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>1377198087.71</v>
+        <v>1377198322.04</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>144797057.56</v>
@@ -1954,10 +1954,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>1629698055.36</v>
+        <v>1629698289.69</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>256709219.93</v>
+        <v>256709383.42</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>45249277.15</v>
@@ -1969,16 +1969,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>3355921.23</v>
+        <v>3355922.44</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>8780022.609999999</v>
+        <v>8780025.77</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>333318388.56</v>
+        <v>333318556.41</v>
       </c>
       <c r="R25" s="13" t="n">
         <v>0.2790295913221863</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>1037097908.91</v>
+        <v>1037098040.96</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>97537800.47</v>
@@ -2012,10 +2012,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>1206202121.28</v>
+        <v>1206202253.33</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>200202122.82</v>
+        <v>200202208.98</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>31464287.45</v>
@@ -2027,16 +2027,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2871147.74</v>
+        <v>2871148.43</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>5012247.27</v>
+        <v>5012248.48</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>250987329.46</v>
+        <v>250987417.53</v>
       </c>
       <c r="R26" s="13" t="n">
         <v>0.2509415863550032</v>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>1198843512.26</v>
+        <v>1198843920.19</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>122103455.85</v>
@@ -2070,10 +2070,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>1406180920.22</v>
+        <v>1406181328.15</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>225000762.3</v>
+        <v>225001046.75</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>38650744.49</v>
@@ -2085,16 +2085,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>2585282.5</v>
+        <v>2585284.36</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>6112837.68</v>
+        <v>6112842.08</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>287799287.56</v>
+        <v>287799578.27</v>
       </c>
       <c r="R27" s="13" t="n">
         <v>0.2836514946154119</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>1317393645.95</v>
+        <v>1317395129.74</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>146265225.05</v>
@@ -2128,10 +2128,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>1563248545.6</v>
+        <v>1563250029.39</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>251064051.1</v>
+        <v>251064490.35</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>47820263.66</v>
@@ -2143,16 +2143,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2381325.58</v>
+        <v>2381326.52</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>7749020.32</v>
+        <v>7749023.37</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>330050876.01</v>
+        <v>330051319.25</v>
       </c>
       <c r="R28" s="13" t="n">
         <v>0.2603327878455701</v>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>1110052759.17</v>
+        <v>1110053544.41</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>110832888.3</v>
@@ -2186,10 +2186,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>1314000573.62</v>
+        <v>1314001358.86</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>203730249.52</v>
+        <v>203730972.4</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>33469362.8</v>
@@ -2201,16 +2201,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2592783.86</v>
+        <v>2592789.55</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>5824917.07</v>
+        <v>5824929.85</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>265596291.82</v>
+        <v>265597033.16</v>
       </c>
       <c r="R29" s="13" t="n">
         <v>0.2711837542671093</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>1383850891.57</v>
+        <v>1383851572.15</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>97591814.65000001</v>
@@ -2244,10 +2244,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>1576687375.64</v>
+        <v>1576688056.22</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>261337140.13</v>
+        <v>261337426.72</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>30161405.65</v>
@@ -2259,16 +2259,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>3726728.5</v>
+        <v>3726730.27</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>4002088.63</v>
+        <v>4002090.54</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>319907675.9</v>
+        <v>319907966.16</v>
       </c>
       <c r="R30" s="13" t="n">
         <v>0.3089090135319407</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>1727301335.46</v>
+        <v>1727302472.59</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>164444551.54</v>
@@ -2302,10 +2302,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>2027358001.49</v>
+        <v>2027359138.62</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>296355202.27</v>
+        <v>296355396.99</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>46737225.01</v>
@@ -2317,16 +2317,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>3587886.61</v>
+        <v>3587886.4</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>5274098.95</v>
+        <v>5274098.65</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>386042376.69</v>
+        <v>386042570.89</v>
       </c>
       <c r="R31" s="13" t="n">
         <v>0.3202852257171364</v>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>1572730499.58</v>
+        <v>1572731510.28</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>152797571.95</v>
@@ -2360,10 +2360,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>1832493583.7</v>
+        <v>1832494594.4</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>293610505.67</v>
+        <v>293610919.59</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>45961937.88</v>
@@ -2375,16 +2375,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>2694890.33</v>
+        <v>2694891.88</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>6570276.87</v>
+        <v>6570280.64</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>372627037.4</v>
+        <v>372627456.63</v>
       </c>
       <c r="R32" s="13" t="n">
         <v>0.3068596818867773</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>1305395286.57</v>
+        <v>1305396310.28</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>112904481.21</v>
@@ -2418,10 +2418,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>1491436312.68</v>
+        <v>1491437336.39</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>251861625.92</v>
+        <v>251861790.32</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>36710222.03</v>
@@ -2433,16 +2433,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1463494.04</v>
+        <v>1463493.81</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>6347096.46</v>
+        <v>6347095.45</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>309527107.95</v>
+        <v>309527271.11</v>
       </c>
       <c r="R33" s="13" t="n">
         <v>0.2945849325840212</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>1368371266.63</v>
+        <v>1368372123.09</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>111143043.36</v>
@@ -2476,10 +2476,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>1592262390.61</v>
+        <v>1592263247.07</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>248806714.42</v>
+        <v>248807139.54</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>33583851.98</v>
@@ -2491,16 +2491,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1142561.28</v>
+        <v>1142562.23</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>8125255.54</v>
+        <v>8125262.32</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>315334906.92</v>
+        <v>315335339.78</v>
       </c>
       <c r="R34" s="13" t="n">
         <v>0.3414174701179286</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>1428043073.62</v>
+        <v>1428045019.9</v>
       </c>
       <c r="C35" s="9" t="n">
         <v>132482297.68</v>
@@ -2534,10 +2534,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>1671700085.29</v>
+        <v>1671702031.57</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>263139850.5</v>
+        <v>263140323.07</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>39009607.96</v>
@@ -2549,16 +2549,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1891009.83</v>
+        <v>1891010.3</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>5945566.27</v>
+        <v>5945567.74</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>336440830.42</v>
+        <v>336441304.92</v>
       </c>
       <c r="R35" s="13" t="n">
         <v>0.3444918130280069</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>1456209531.4</v>
+        <v>1456210004.04</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>147816672.25</v>
@@ -2592,10 +2592,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>1723549822.27</v>
+        <v>1723550294.91</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>282236923.69</v>
+        <v>282237032.95</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>47162206.4</v>
@@ -2607,16 +2607,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>2226975.1</v>
+        <v>2226975.15</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>6426280.07</v>
+        <v>6426280.21</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>369372263.54</v>
+        <v>369372372.99</v>
       </c>
       <c r="R36" s="13" t="n">
         <v>0.3000842795719814</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>1613188561.89</v>
+        <v>1613188890.89</v>
       </c>
       <c r="C37" s="9" t="n">
         <v>161563899.02</v>
@@ -2650,10 +2650,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>1887508711.66</v>
+        <v>1887509040.66</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>289612674.85</v>
+        <v>289612789</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>49969404.96</v>
@@ -2665,16 +2665,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2038735.15</v>
+        <v>2038735.43</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>7146309.77</v>
+        <v>7146310.74</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>371788628.2</v>
+        <v>371788743.6</v>
       </c>
       <c r="R37" s="13" t="n">
         <v>0.3158320949670745</v>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>2119622813.3</v>
+        <v>2119623767.07</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>172439724.32</v>
@@ -2708,10 +2708,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>2463685904.51</v>
+        <v>2463686858.28</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>378506344.87</v>
+        <v>378506521.91</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>46814572.08</v>
@@ -2723,16 +2723,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>3468831.68</v>
+        <v>3468831.62</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>5883474.52</v>
+        <v>5883474.42</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>478311431.23</v>
+        <v>478311608.11</v>
       </c>
       <c r="R38" s="13" t="n">
         <v>0.3730201312691256</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>1628364067.09</v>
+        <v>1628364635.61</v>
       </c>
       <c r="C39" s="9" t="n">
         <v>131412975.25</v>
@@ -2766,10 +2766,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>1915133853.69</v>
+        <v>1915134422.21</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>294597919.64</v>
+        <v>294598078.01</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>38038258.86</v>
@@ -2781,16 +2781,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>4346488.71</v>
+        <v>4346489.23</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>6499227.98</v>
+        <v>6499228.75</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>384071426.01</v>
+        <v>384071585.67</v>
       </c>
       <c r="R39" s="13" t="n">
         <v>0.3654745795652588</v>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>1241345775.67</v>
+        <v>1241347558.43</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>184349276.32</v>
@@ -2824,10 +2824,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>1550723441.46</v>
+        <v>1550725224.22</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>227091341.22</v>
+        <v>227091796.61</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>52663679.72</v>
@@ -2839,16 +2839,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>3230022.49</v>
+        <v>3230023.33</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>4087120.47</v>
+        <v>4087121.53</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>324537503.89</v>
+        <v>324537961.18</v>
       </c>
       <c r="R40" s="13" t="n">
         <v>0.3156021020167954</v>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>1377184264.3</v>
+        <v>1377185238.28</v>
       </c>
       <c r="C41" s="9" t="n">
         <v>155233923.84</v>
@@ -2882,10 +2882,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>1655666927.91</v>
+        <v>1655667901.89</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>238172870.89</v>
+        <v>238172998.14</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>45723994.53</v>
@@ -2897,16 +2897,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>2993004.97</v>
+        <v>2993004.37</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>4877199.81</v>
+        <v>4877198.84</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>322916262.07</v>
+        <v>322916387.75</v>
       </c>
       <c r="R41" s="13" t="n">
         <v>0.3586813700389345</v>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>1613725261.67</v>
+        <v>1613727443.3</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>202803340.18</v>
@@ -2940,10 +2940,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>1989299207.1</v>
+        <v>1989301388.73</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>282618786.05</v>
+        <v>282619919.71</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>59467977.05</v>
@@ -2955,16 +2955,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>2562076.47</v>
+        <v>2562081</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>6710393.15</v>
+        <v>6710405.02</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>401336729.8</v>
+        <v>401337879.86</v>
       </c>
       <c r="R42" s="13" t="n">
         <v>0.374804382581988</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>1427764997.47</v>
+        <v>1427767508.54</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>221859292.06</v>
@@ -2998,10 +2998,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>1817552154.02</v>
+        <v>1817554665.09</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>232864307.92</v>
+        <v>232864597.97</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>61180817.13</v>
@@ -3013,16 +3013,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>2342317.78</v>
+        <v>2342316.49</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>6388151.16</v>
+        <v>6388147.64</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>343667245.97</v>
+        <v>343667531.21</v>
       </c>
       <c r="R43" s="13" t="n">
         <v>0.373808055436679</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>1480855923.19</v>
+        <v>1480856540.2</v>
       </c>
       <c r="C44" s="9" t="n">
         <v>197999210.33</v>
@@ -3056,10 +3056,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>1838736956.29</v>
+        <v>1838737573.3</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>248376802.14</v>
+        <v>248377086.17</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>51757760.82</v>
@@ -3071,16 +3071,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>4638587.03</v>
+        <v>4638589.31</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>6177351.01</v>
+        <v>6177354.04</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>349805156.5</v>
+        <v>349805445.85</v>
       </c>
       <c r="R44" s="13" t="n">
         <v>0.3916154766095744</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>2194897929.17</v>
+        <v>2194898084.1</v>
       </c>
       <c r="C45" s="9" t="n">
         <v>306596858.33</v>
@@ -3114,10 +3114,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>2819804446.4</v>
+        <v>2819804601.33</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>400042773.75</v>
+        <v>400042798.38</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>76961510.28</v>
@@ -3129,16 +3129,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>9471727.939999999</v>
+        <v>9471727.83</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>16166245.21</v>
+        <v>16166245.01</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>570540956.04</v>
+        <v>570540980.35</v>
       </c>
       <c r="R45" s="13" t="n">
         <v>0.4006796632230236</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>2305301035.29</v>
+        <v>2305302998.69</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>376108161.46</v>
@@ -3172,10 +3172,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>3105821502.44</v>
+        <v>3105823465.84</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>402169623.74</v>
+        <v>402170465.57</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>102191987.48</v>
@@ -3187,16 +3187,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>10742339.2</v>
+        <v>10742347.38</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>19778557.98</v>
+        <v>19778573.03</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>620962500.48</v>
+        <v>620963365.53</v>
       </c>
       <c r="R46" s="13" t="n">
         <v>0.442865097926909</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>1370763912.37</v>
+        <v>1370766145.9</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>250093696.52</v>
@@ -3230,10 +3230,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>1802382124.9</v>
+        <v>1802384358.43</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>227514915.57</v>
+        <v>227515236.98</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>65852392.81</v>
@@ -3245,16 +3245,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>3449586.46</v>
+        <v>3449585.34</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>4879522.39</v>
+        <v>4879520.81</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>347854348.7</v>
+        <v>347854667.42</v>
       </c>
       <c r="R47" s="13" t="n">
         <v>0.4207679702437824</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>1605872968.06</v>
+        <v>1605877489.48</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>251713084.28</v>
@@ -3288,10 +3288,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>2004195336.6</v>
+        <v>2004199858.02</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>256672087.31</v>
+        <v>256672802.22</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>62840730.8</v>
@@ -3303,16 +3303,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>4066683.4</v>
+        <v>4066682.22</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>5303366.35</v>
+        <v>5303364.8</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>362464990.41</v>
+        <v>362465702.59</v>
       </c>
       <c r="R48" s="13" t="n">
         <v>0.4544083188194561</v>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>1642715866.58</v>
+        <v>1642728228.17</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>255216837.43</v>
@@ -3346,10 +3346,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>2063068702.41</v>
+        <v>2063081064</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>257254303.6</v>
+        <v>257255722.56</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>63158844.13</v>
@@ -3361,16 +3361,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>4712179.12</v>
+        <v>4712168.8</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>5445747.42</v>
+        <v>5445735.49</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>367426546.46</v>
+        <v>367427943.17</v>
       </c>
       <c r="R49" s="13" t="n">
         <v>0.4715622688002217</v>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>1539525034.58</v>
+        <v>1539527367.68</v>
       </c>
       <c r="C50" s="9" t="n">
         <v>251070477.59</v>
@@ -3404,10 +3404,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>1989415212.33</v>
+        <v>1989417545.43</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>263413432.68</v>
+        <v>263414357.19</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>57612870.57</v>
@@ -3419,16 +3419,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>4619998.27</v>
+        <v>4620004.39</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>5904448.88</v>
+        <v>5904456.7</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>375779895.85</v>
+        <v>375780834.3</v>
       </c>
       <c r="R50" s="13" t="n">
         <v>0.5184969295746537</v>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>1765221425.51</v>
+        <v>1765226970.96</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>287468135.92</v>
@@ -3462,10 +3462,10 @@
         <v>28011807</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>2267503826.94</v>
+        <v>2267509372.39</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>281269263.53</v>
+        <v>281270702.01</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>59780017.61</v>
@@ -3477,16 +3477,16 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>5175409.88</v>
+        <v>5175416.27</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>7388603.28</v>
+        <v>7388612.4</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>13969238.87</v>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>395113784.93</v>
+        <v>395115238.92</v>
       </c>
       <c r="R51" s="13" t="n">
         <v>0.5173698555705437</v>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>2536967708.16</v>
+        <v>2536972715.09</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>438830798.95</v>
@@ -3520,10 +3520,10 @@
         <v>20465067</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>3325937606.22</v>
+        <v>3325942613.15</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>439523241.63</v>
+        <v>439525707.94</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>92879457.39</v>
@@ -3535,16 +3535,16 @@
         <v>15738266.69</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>7898023.53</v>
+        <v>7898044.17</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>23429922.02</v>
+        <v>23429983.27</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>10232009.27</v>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>618567431</v>
+        <v>618569979.2</v>
       </c>
       <c r="R52" s="13" t="n">
         <v>0.4928123695831447</v>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>2708549732.51</v>
+        <v>2708586376.88</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>590872240.37</v>
@@ -3578,10 +3578,10 @@
         <v>67156727</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>3868191986.54</v>
+        <v>3868228630.91</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>422501262.49</v>
+        <v>422517352.17</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>126606680.82</v>
@@ -3593,16 +3593,16 @@
         <v>34860196.13</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>8426264.99</v>
+        <v>8426392.189999999</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>31891885.25</v>
+        <v>31892366.7</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>33049467.84</v>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>679628894.05</v>
+        <v>679645592.39</v>
       </c>
       <c r="R53" s="13" t="n">
         <v>0.516687833119383</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>1283393131.72</v>
+        <v>1283525018.76</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>284348309.59</v>
@@ -3636,10 +3636,10 @@
         <v>57503053</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>1757333572.07</v>
+        <v>1757465459.11</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>214071162.53</v>
+        <v>214119217.9</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>74184906.98999999</v>
@@ -3651,16 +3651,16 @@
         <v>11903181.4</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1457098.52</v>
+        <v>1457192.76</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>6859211.67</v>
+        <v>6859655.34</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>28258572.47</v>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>347747862.16</v>
+        <v>347796455.46</v>
       </c>
       <c r="R54" s="13" t="n">
         <v>0.4317620090381182</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>1534738131.47</v>
+        <v>1535157957.92</v>
       </c>
       <c r="C55" s="9" t="n">
         <v>305249223.57</v>
@@ -3694,10 +3694,10 @@
         <v>29175511</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>1996815617.8</v>
+        <v>1997235444.25</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>255002702.23</v>
+        <v>255149280.35</v>
       </c>
       <c r="K55" s="12" t="n">
         <v>60959047.28</v>
@@ -3709,23 +3709,81 @@
         <v>8988100.75</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>2861748.64</v>
+        <v>2862332.67</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>5819493.59</v>
+        <v>5820681.24</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>13247763.43</v>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>358011122.37</v>
+        <v>358159472.17</v>
       </c>
       <c r="R55" s="13" t="n">
         <v>0.5085823534173731</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>1511966851.24</v>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>295641521.04</v>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>43306685.92</v>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>43505922</v>
+      </c>
+      <c r="F56" s="9" t="n">
+        <v>15775991.06</v>
+      </c>
+      <c r="G56" s="9" t="n">
+        <v>30628983</v>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>26518877</v>
+      </c>
+      <c r="I56" s="10" t="n">
+        <v>1967344831.26</v>
+      </c>
+      <c r="J56" s="11" t="n">
+        <v>238952486.21</v>
+      </c>
+      <c r="K56" s="12" t="n">
+        <v>65905215.47</v>
+      </c>
+      <c r="L56" s="12" t="n">
+        <v>11606516.79</v>
+      </c>
+      <c r="M56" s="12" t="n">
+        <v>10595274.38</v>
+      </c>
+      <c r="N56" s="12" t="n">
+        <v>2794338.95</v>
+      </c>
+      <c r="O56" s="12" t="n">
+        <v>5425190.71</v>
+      </c>
+      <c r="P56" s="12" t="n">
+        <v>13188992.45</v>
+      </c>
+      <c r="Q56" s="12" t="n">
+        <v>348468014.96</v>
+      </c>
+      <c r="R56" s="13" t="n">
+        <v>0.5057931637222076</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R55"/>
+  <autoFilter ref="A2:R56"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3741,7 +3799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6765,8 +6823,63 @@
         <v>466400618.26</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>1810000000</v>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>300394808.78</v>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>43306685.92</v>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>43505922</v>
+      </c>
+      <c r="F56" s="9" t="n">
+        <v>15775991.06</v>
+      </c>
+      <c r="G56" s="9" t="n">
+        <v>34777194</v>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>27236488</v>
+      </c>
+      <c r="I56" s="10" t="n">
+        <v>2274997089.76</v>
+      </c>
+      <c r="J56" s="11" t="n">
+        <v>362543000</v>
+      </c>
+      <c r="K56" s="12" t="n">
+        <v>67333022.11</v>
+      </c>
+      <c r="L56" s="12" t="n">
+        <v>11606516.79</v>
+      </c>
+      <c r="M56" s="12" t="n">
+        <v>10595274.38</v>
+      </c>
+      <c r="N56" s="12" t="n">
+        <v>3301438.49</v>
+      </c>
+      <c r="O56" s="12" t="n">
+        <v>7277816.43</v>
+      </c>
+      <c r="P56" s="12" t="n">
+        <v>13431117.34</v>
+      </c>
+      <c r="Q56" s="12" t="n">
+        <v>476088185.54</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:Q55"/>
+  <autoFilter ref="A2:Q56"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -6781,7 +6894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9127,7 +9240,7 @@
         <v>11228218</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7392</v>
       </c>
       <c r="I55" s="14" t="n">
         <v>0.4565</v>
@@ -9145,15 +9258,58 @@
         <v>0.3459</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="15" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="n">
+        <v>1141024000</v>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>19363934.86</v>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>25803264</v>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>145934787.29</v>
+      </c>
+      <c r="F56" s="9" t="n">
+        <v>13745564.92</v>
+      </c>
+      <c r="G56" s="9" t="n">
+        <v>12075182</v>
+      </c>
+      <c r="H56" s="14" t="n">
+        <v>0.7547</v>
+      </c>
+      <c r="I56" s="14" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="J56" s="14" t="n">
+        <v>0.5931000000000001</v>
+      </c>
+      <c r="K56" s="14" t="n">
+        <v>0.4936</v>
+      </c>
+      <c r="L56" s="14" t="n">
+        <v>0.8713</v>
+      </c>
+      <c r="M56" s="14" t="n">
+        <v>0.3942</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~5M-trade sample (refreshed weekly) scaled to the daily total; ~70% of Kalshi's sports book by contracts, ~24% by $ (parlay legs are many and cheap - this sample-based split can move noticeably week to week, see VOLUME_METHODOLOGY.md). Not folded into the Sports tab's blended Combo %. Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M55"/>
+  <autoFilter ref="A2:M56"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -9186,7 +9342,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-23. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-24. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9401,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-23: independently recomputed totals matched the committed figures exactly</t>
+          <t>2026-09-24: independently recomputed totals matched the committed figures exactly</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1292327121.89</v>
+        <v>1292327356.14</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>125055737.8</v>
@@ -910,10 +910,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>1497407159.47</v>
+        <v>1497407393.72</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>259386661.65</v>
+        <v>259386671.02</v>
       </c>
       <c r="K7" s="12" t="n">
         <v>47948549.82</v>
@@ -925,16 +925,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>631739.78</v>
+        <v>631739.7</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>6846050.76</v>
+        <v>6846049.86</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>335565183.45</v>
+        <v>335565191.84</v>
       </c>
       <c r="R7" s="13" t="n">
         <v>0.1036604405692761</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>1136156873.5</v>
+        <v>1136156904.5</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>126075255.12</v>
@@ -1142,10 +1142,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1360830190.62</v>
+        <v>1360830221.62</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>220224960.28</v>
+        <v>220224961.52</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>48533344.05</v>
@@ -1157,16 +1157,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2216238.61</v>
+        <v>2216238.56</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>7947075.43</v>
+        <v>7947075.28</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>302603615.02</v>
+        <v>302603616.06</v>
       </c>
       <c r="R11" s="13" t="n">
         <v>0.1174147553025735</v>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>1149011828.88</v>
+        <v>1149011866.88</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>86060025.34</v>
@@ -1258,10 +1258,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>1308568483.12</v>
+        <v>1308568521.12</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>235935104.97</v>
+        <v>235935106.49</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>32573678.23</v>
@@ -1273,16 +1273,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2341916.67</v>
+        <v>2341916.61</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>4886882.62</v>
+        <v>4886882.5</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>294006452.7</v>
+        <v>294006454.05</v>
       </c>
       <c r="R13" s="13" t="n">
         <v>0.1581581529884586</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>1206695871.54</v>
+        <v>1206696194.55</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>122512075.89</v>
@@ -1432,10 +1432,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>1408839750.57</v>
+        <v>1408840073.58</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>254178401.9</v>
+        <v>254178415.92</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>44967846.15</v>
@@ -1447,16 +1447,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>3170563.08</v>
+        <v>3170562.47</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>6715346.22</v>
+        <v>6715344.93</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>322388365.35</v>
+        <v>322388377.48</v>
       </c>
       <c r="R16" s="13" t="n">
         <v>0.1467243571212392</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>918409554.3099999</v>
+        <v>918410309.3099999</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>100434174.96</v>
@@ -1606,10 +1606,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>1079826399.84</v>
+        <v>1079827154.84</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>188477086.68</v>
+        <v>188477135.16</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>36933011.94</v>
@@ -1621,16 +1621,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2573290.3</v>
+        <v>2573288.97</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>4428373.24</v>
+        <v>4428370.95</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>245090593.14</v>
+        <v>245090638.01</v>
       </c>
       <c r="R19" s="13" t="n">
         <v>0.1248997633733931</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>1037098040.96</v>
+        <v>1037098071.66</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>97537800.47</v>
@@ -2012,10 +2012,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>1206202253.33</v>
+        <v>1206202284.03</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>200202208.98</v>
+        <v>200202210.51</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>31464287.45</v>
@@ -2027,16 +2027,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2871148.43</v>
+        <v>2871148.38</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>5012248.48</v>
+        <v>5012248.38</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>250987417.53</v>
+        <v>250987418.9</v>
       </c>
       <c r="R26" s="13" t="n">
         <v>0.2509415863550032</v>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>1198843920.19</v>
+        <v>1198844154.44</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>122103455.85</v>
@@ -2070,10 +2070,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>1406181328.15</v>
+        <v>1406181562.4</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>225001046.75</v>
+        <v>225001056.12</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>38650744.49</v>
@@ -2085,16 +2085,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>2585284.36</v>
+        <v>2585284</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>6112842.08</v>
+        <v>6112841.24</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>287799578.27</v>
+        <v>287799586.44</v>
       </c>
       <c r="R27" s="13" t="n">
         <v>0.2836514946154119</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>1383851572.15</v>
+        <v>1383852603.56</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>97591814.65000001</v>
@@ -2244,10 +2244,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>1576688056.22</v>
+        <v>1576689087.63</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>261337426.72</v>
+        <v>261337478.29</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>30161405.65</v>
@@ -2259,16 +2259,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>3726730.27</v>
+        <v>3726728.39</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>4002090.54</v>
+        <v>4002088.52</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>319907966.16</v>
+        <v>319908013.83</v>
       </c>
       <c r="R30" s="13" t="n">
         <v>0.3089090135319407</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>1368372123.09</v>
+        <v>1368372194.09</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>111143043.36</v>
@@ -2476,10 +2476,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>1592263247.07</v>
+        <v>1592263318.07</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>248807139.54</v>
+        <v>248807143.09</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>33583851.98</v>
@@ -2491,16 +2491,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1142562.23</v>
+        <v>1142562.19</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>8125262.32</v>
+        <v>8125262.04</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>315335339.78</v>
+        <v>315335343.01</v>
       </c>
       <c r="R34" s="13" t="n">
         <v>0.3414174701179286</v>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>1241347558.43</v>
+        <v>1241347559.43</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>184349276.32</v>
@@ -2824,10 +2824,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>1550725224.22</v>
+        <v>1550725225.22</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>227091796.61</v>
+        <v>227091796.66</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>52663679.72</v>
@@ -2848,7 +2848,7 @@
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>324537961.18</v>
+        <v>324537961.23</v>
       </c>
       <c r="R40" s="13" t="n">
         <v>0.3156021020167954</v>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>1377185238.28</v>
+        <v>1377185483.03</v>
       </c>
       <c r="C41" s="9" t="n">
         <v>155233923.84</v>
@@ -2882,10 +2882,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>1655667901.89</v>
+        <v>1655668146.64</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>238172998.14</v>
+        <v>238173010.37</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>45723994.53</v>
@@ -2897,16 +2897,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>2993004.37</v>
+        <v>2993004.03</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>4877198.84</v>
+        <v>4877198.29</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>322916387.75</v>
+        <v>322916399.09</v>
       </c>
       <c r="R41" s="13" t="n">
         <v>0.3586813700389345</v>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>1613727443.3</v>
+        <v>1613727498.3</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>202803340.18</v>
@@ -2940,10 +2940,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>1989301388.73</v>
+        <v>1989301443.73</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>282619919.71</v>
+        <v>282619922.46</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>59467977.05</v>
@@ -2955,16 +2955,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>2562081</v>
+        <v>2562080.95</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>6710405.02</v>
+        <v>6710404.87</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>401337879.86</v>
+        <v>401337882.41</v>
       </c>
       <c r="R42" s="13" t="n">
         <v>0.374804382581988</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>1427767508.54</v>
+        <v>1427767698.38</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>221859292.06</v>
@@ -2998,10 +2998,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>1817554665.09</v>
+        <v>1817554854.93</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>232864597.97</v>
+        <v>232864613.03</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>61180817.13</v>
@@ -3013,16 +3013,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>2342316.49</v>
+        <v>2342316.34</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>6388147.64</v>
+        <v>6388147.24</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>343667531.21</v>
+        <v>343667545.72</v>
       </c>
       <c r="R43" s="13" t="n">
         <v>0.373808055436679</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>2305302998.69</v>
+        <v>2305303001.33</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>376108161.46</v>
@@ -3172,10 +3172,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>3105823465.84</v>
+        <v>3105823468.48</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>402170465.57</v>
+        <v>402170466.87</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>102191987.48</v>
@@ -3187,16 +3187,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>10742347.38</v>
+        <v>10742347.39</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>19778573.03</v>
+        <v>19778573.05</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>620963365.53</v>
+        <v>620963366.87</v>
       </c>
       <c r="R46" s="13" t="n">
         <v>0.442865097926909</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>1370766145.9</v>
+        <v>1370766149.59</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>250093696.52</v>
@@ -3230,10 +3230,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>1802384358.43</v>
+        <v>1802384362.12</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>227515236.98</v>
+        <v>227515238.9</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>65852392.81</v>
@@ -3245,16 +3245,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>3449585.34</v>
+        <v>3449585.35</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>4879520.81</v>
+        <v>4879520.83</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>347854667.42</v>
+        <v>347854669.37</v>
       </c>
       <c r="R47" s="13" t="n">
         <v>0.4207679702437824</v>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>1539527367.68</v>
+        <v>1539527391.1</v>
       </c>
       <c r="C50" s="9" t="n">
         <v>251070477.59</v>
@@ -3404,10 +3404,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>1989417545.43</v>
+        <v>1989417568.85</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>263414357.19</v>
+        <v>263414358.13</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>57612870.57</v>
@@ -3419,16 +3419,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>4620004.39</v>
+        <v>4620004.35</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>5904456.7</v>
+        <v>5904456.65</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>375780834.3</v>
+        <v>375780835.14</v>
       </c>
       <c r="R50" s="13" t="n">
         <v>0.5184969295746537</v>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>1765226970.96</v>
+        <v>1765226971.96</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>287468135.92</v>
@@ -3462,10 +3462,10 @@
         <v>28011807</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>2267509372.39</v>
+        <v>2267509373.39</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>281270702.01</v>
+        <v>281270702.06</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>59780017.61</v>
@@ -3486,7 +3486,7 @@
         <v>13969238.87</v>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>395115238.92</v>
+        <v>395115238.97</v>
       </c>
       <c r="R51" s="13" t="n">
         <v>0.5173698555705437</v>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>2536972715.09</v>
+        <v>2536973279.67</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>438830798.95</v>
@@ -3520,10 +3520,10 @@
         <v>20465067</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>3325942613.15</v>
+        <v>3325943177.73</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>439525707.94</v>
+        <v>439525764.58</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>92879457.39</v>
@@ -3535,16 +3535,16 @@
         <v>15738266.69</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>7898044.17</v>
+        <v>7898043.52</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>23429983.27</v>
+        <v>23429981.34</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>10232009.27</v>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>618569979.2</v>
+        <v>618570033.26</v>
       </c>
       <c r="R52" s="13" t="n">
         <v>0.4928123695831447</v>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>2708586376.88</v>
+        <v>2708587899.26</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>590872240.37</v>
@@ -3578,10 +3578,10 @@
         <v>67156727</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>3868228630.91</v>
+        <v>3868230153.29</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>422517352.17</v>
+        <v>422517915.65</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>126606680.82</v>
@@ -3593,16 +3593,16 @@
         <v>34860196.13</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>8426392.189999999</v>
+        <v>8426396.09</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>31892366.7</v>
+        <v>31892381.46</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>33049467.84</v>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>679645592.39</v>
+        <v>679646174.54</v>
       </c>
       <c r="R53" s="13" t="n">
         <v>0.516687833119383</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>1283525018.76</v>
+        <v>1283530595.17</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>284348309.59</v>
@@ -3636,10 +3636,10 @@
         <v>57503053</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>1757465459.11</v>
+        <v>1757471035.52</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>214119217.9</v>
+        <v>214120689.6</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>74184906.98999999</v>
@@ -3651,16 +3651,16 @@
         <v>11903181.4</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1457192.76</v>
+        <v>1457194.34</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>6859655.34</v>
+        <v>6859662.78</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>28258572.47</v>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>347796455.46</v>
+        <v>347797936.17</v>
       </c>
       <c r="R54" s="13" t="n">
         <v>0.4317620090381182</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>1535157957.92</v>
+        <v>1535178463.85</v>
       </c>
       <c r="C55" s="9" t="n">
         <v>305249223.57</v>
@@ -3694,10 +3694,10 @@
         <v>29175511</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>1997235444.25</v>
+        <v>1997255950.18</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>255149280.35</v>
+        <v>255155773.76</v>
       </c>
       <c r="K55" s="12" t="n">
         <v>60959047.28</v>
@@ -3709,16 +3709,16 @@
         <v>8988100.75</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>2862332.67</v>
+        <v>2862355.73</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>5820681.24</v>
+        <v>5820728.14</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>13247763.43</v>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>358159472.17</v>
+        <v>358166035.54</v>
       </c>
       <c r="R55" s="13" t="n">
         <v>0.5085823534173731</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>1511966851.24</v>
+        <v>1512027740.49</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>295641521.04</v>
@@ -3752,10 +3752,10 @@
         <v>26518877</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>1967344831.26</v>
+        <v>1967405720.51</v>
       </c>
       <c r="J56" s="11" t="n">
-        <v>238952486.21</v>
+        <v>238971190.68</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>65905215.47</v>
@@ -3767,16 +3767,16 @@
         <v>10595274.38</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>2794338.95</v>
+        <v>2794403.99</v>
       </c>
       <c r="O56" s="12" t="n">
-        <v>5425190.71</v>
+        <v>5425316.98</v>
       </c>
       <c r="P56" s="12" t="n">
         <v>13188992.45</v>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>348468014.96</v>
+        <v>348486910.74</v>
       </c>
       <c r="R56" s="13" t="n">
         <v>0.5057931637222076</v>
@@ -9240,7 +9240,7 @@
         <v>11228218</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>0.7392</v>
+        <v>0.7391</v>
       </c>
       <c r="I55" s="14" t="n">
         <v>0.4565</v>
@@ -9283,7 +9283,7 @@
         <v>12075182</v>
       </c>
       <c r="H56" s="14" t="n">
-        <v>0.7547</v>
+        <v>0.7545999999999999</v>
       </c>
       <c r="I56" s="14" t="n">
         <v>0.4471</v>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>1436292621.39</v>
+        <v>1436294422.68</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>133399888.66</v>
@@ -688,10 +688,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>1614254715.97</v>
+        <v>1614256517.26</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>299227596.16</v>
+        <v>299227836.4</v>
       </c>
       <c r="K3" s="12" t="n">
         <v>50986272.22</v>
@@ -701,16 +701,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>466111.83</v>
+        <v>466111.61</v>
       </c>
       <c r="O3" s="12" t="n">
-        <v>8313324.93</v>
+        <v>8313321.09</v>
       </c>
       <c r="P3" s="12" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="12" t="n">
-        <v>361464939.55</v>
+        <v>361465175.73</v>
       </c>
       <c r="R3" s="13" t="n">
         <v>0.08714584215412201</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>1205571755.95</v>
+        <v>1205571891.8</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>134065934.54</v>
@@ -742,10 +742,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>1388976665.46</v>
+        <v>1388976801.31</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>231812362.42</v>
+        <v>231812429.71</v>
       </c>
       <c r="K4" s="12" t="n">
         <v>51144509.72</v>
@@ -755,16 +755,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>458019.25</v>
+        <v>458019.31</v>
       </c>
       <c r="O4" s="12" t="n">
-        <v>8194676.46</v>
+        <v>8194677.56</v>
       </c>
       <c r="P4" s="12" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="12" t="n">
-        <v>296023163.91</v>
+        <v>296023232.35</v>
       </c>
       <c r="R4" s="13" t="n">
         <v>0.07635377691307524</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>889408055.46</v>
+        <v>889408107.8099999</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>85344135.09999999</v>
@@ -796,10 +796,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>1005450602.5</v>
+        <v>1005450654.85</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>202393360.57</v>
+        <v>202393372.63</v>
       </c>
       <c r="K5" s="12" t="n">
         <v>31777180.84</v>
@@ -812,13 +812,13 @@
         <v>334880.9</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>4825439.28</v>
+        <v>4825439.27</v>
       </c>
       <c r="P5" s="12" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>243868963.13</v>
+        <v>243868975.18</v>
       </c>
       <c r="R5" s="13" t="n">
         <v>0.05231046649197771</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1155124034.98</v>
+        <v>1155124680.95</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>120394335.41</v>
@@ -852,10 +852,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>1339762184</v>
+        <v>1339762829.97</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>243084458.1</v>
+        <v>243084529.44</v>
       </c>
       <c r="K6" s="12" t="n">
         <v>47471997.74</v>
@@ -867,16 +867,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>288785.01</v>
+        <v>288784.93</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>6546863.56</v>
+        <v>6546861.87</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>312033691.24</v>
+        <v>312033760.81</v>
       </c>
       <c r="R6" s="13" t="n">
         <v>0.1040882840699126</v>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1292327356.14</v>
+        <v>1292327849.45</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>125055737.8</v>
@@ -910,10 +910,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>1497407393.72</v>
+        <v>1497407887.03</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>259386671.02</v>
+        <v>259386804.98</v>
       </c>
       <c r="K7" s="12" t="n">
         <v>47948549.82</v>
@@ -925,16 +925,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>631739.7</v>
+        <v>631739.74</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>6846049.86</v>
+        <v>6846050.35</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>335565191.84</v>
+        <v>335565326.33</v>
       </c>
       <c r="R7" s="13" t="n">
         <v>0.1036604405692761</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1187471131.96</v>
+        <v>1187471723.31</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>141146850.05</v>
@@ -968,10 +968,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>1409644251.47</v>
+        <v>1409644842.82</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>236784644.97</v>
+        <v>236784791.23</v>
       </c>
       <c r="K8" s="12" t="n">
         <v>50551741.94</v>
@@ -983,16 +983,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>1121124.65</v>
+        <v>1121124.7</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>7508185.68</v>
+        <v>7508186.02</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>315423411.95</v>
+        <v>315423558.61</v>
       </c>
       <c r="R8" s="13" t="n">
         <v>0.09320593928966855</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1139473853.53</v>
+        <v>1139474985.35</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>117925601.54</v>
@@ -1026,10 +1026,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>1323081015.07</v>
+        <v>1323082146.89</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>224392328.29</v>
+        <v>224392495.43</v>
       </c>
       <c r="K9" s="12" t="n">
         <v>44939973.52</v>
@@ -1041,16 +1041,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>727221.38</v>
+        <v>727221.1800000001</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>6114376.12</v>
+        <v>6114374.37</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>289885770.99</v>
+        <v>289885936.18</v>
       </c>
       <c r="R9" s="13" t="n">
         <v>0.100308786205459</v>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1265086031.78</v>
+        <v>1265087276.75</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>119094679.49</v>
@@ -1084,10 +1084,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1469751929.26</v>
+        <v>1469753174.23</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>247904404.68</v>
+        <v>247904714.4</v>
       </c>
       <c r="K10" s="12" t="n">
         <v>44015511.37</v>
@@ -1099,16 +1099,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>2089369.56</v>
+        <v>2089369.81</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>6720638.29</v>
+        <v>6720639.12</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>320414890.41</v>
+        <v>320415201.21</v>
       </c>
       <c r="R10" s="13" t="n">
         <v>0.1305164739611011</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>1136156904.5</v>
+        <v>1136158985.39</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>126075255.12</v>
@@ -1142,10 +1142,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1360830221.62</v>
+        <v>1360832302.51</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>220224961.52</v>
+        <v>220224994.41</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>48533344.05</v>
@@ -1157,16 +1157,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2216238.56</v>
+        <v>2216235.31</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>7947075.28</v>
+        <v>7947063.6</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>302603616.06</v>
+        <v>302603634.01</v>
       </c>
       <c r="R11" s="13" t="n">
         <v>0.1174147553025735</v>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>817337625.74</v>
+        <v>817338101.49</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>76773291.01000001</v>
@@ -1200,10 +1200,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>944249316.77</v>
+        <v>944249792.52</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>157385713.38</v>
+        <v>157385850.49</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>28141958.88</v>
@@ -1215,16 +1215,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>1682386.81</v>
+        <v>1682387.12</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>3091094.1</v>
+        <v>3091094.65</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>202041154.19</v>
+        <v>202041292.16</v>
       </c>
       <c r="R12" s="13" t="n">
         <v>0.1320471995718654</v>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>1149011866.88</v>
+        <v>1149012354.1</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>86060025.34</v>
@@ -1258,10 +1258,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>1308568521.12</v>
+        <v>1308569008.34</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>235935106.49</v>
+        <v>235935235.65</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>32573678.23</v>
@@ -1273,16 +1273,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2341916.61</v>
+        <v>2341916.77</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>4886882.5</v>
+        <v>4886882.83</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>294006454.05</v>
+        <v>294006583.7</v>
       </c>
       <c r="R13" s="13" t="n">
         <v>0.1581581529884586</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>1239523185.61</v>
+        <v>1239523499.17</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>114182203.82</v>
@@ -1316,10 +1316,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>1441007375.68</v>
+        <v>1441007689.24</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>240227738.39</v>
+        <v>240227776</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>44020201.24</v>
@@ -1331,16 +1331,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2540876.02</v>
+        <v>2540875.76</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>6229749.24</v>
+        <v>6229748.61</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>313911435.08</v>
+        <v>313911471.81</v>
       </c>
       <c r="R14" s="13" t="n">
         <v>0.1369006174109096</v>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>1228242328.29</v>
+        <v>1228242998.85</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>130618679.53</v>
@@ -1374,10 +1374,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>1450289428.1</v>
+        <v>1450290098.66</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>245769284.68</v>
+        <v>245769332.65</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>47519466.33</v>
@@ -1389,16 +1389,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3332878.51</v>
+        <v>3332877.43</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>6989330.75</v>
+        <v>6989328.49</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>321982230.74</v>
+        <v>321982275.37</v>
       </c>
       <c r="R15" s="13" t="n">
         <v>0.1338434618903201</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>1206696194.55</v>
+        <v>1206696239.55</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>122512075.89</v>
@@ -1432,10 +1432,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>1408840073.58</v>
+        <v>1408840118.58</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>254178415.92</v>
+        <v>254178452.67</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>44967846.15</v>
@@ -1447,16 +1447,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>3170562.47</v>
+        <v>3170562.74</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>6715344.93</v>
+        <v>6715345.5</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>322388377.48</v>
+        <v>322388415.06</v>
       </c>
       <c r="R16" s="13" t="n">
         <v>0.1467243571212392</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1502785997.89</v>
+        <v>1502787360.73</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>135215397.14</v>
@@ -1490,10 +1490,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>1745507475.14</v>
+        <v>1745508837.98</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>307040803.3</v>
+        <v>307041496.45</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>48968794.7</v>
@@ -1505,16 +1505,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>3811144.08</v>
+        <v>3811148.02</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>8549317.710000001</v>
+        <v>8549326.57</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>388645260.97</v>
+        <v>388645966.92</v>
       </c>
       <c r="R17" s="13" t="n">
         <v>0.1671310595982739</v>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>1333526172.18</v>
+        <v>1333526538.74</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>146617403.12</v>
@@ -1548,10 +1548,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>1585701333.51</v>
+        <v>1585701700.07</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>261227195.29</v>
+        <v>261227409.04</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>56978627.74</v>
@@ -1563,16 +1563,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>3122212.98</v>
+        <v>3122214.22</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>9982352.029999999</v>
+        <v>9982355.99</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>348774717.14</v>
+        <v>348774936.09</v>
       </c>
       <c r="R18" s="13" t="n">
         <v>0.1404248555660547</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>918410309.3099999</v>
+        <v>918410591.3099999</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>100434174.96</v>
@@ -1606,10 +1606,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>1079827154.84</v>
+        <v>1079827436.84</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>188477135.16</v>
+        <v>188477182.67</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>36933011.94</v>
@@ -1621,16 +1621,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2573288.97</v>
+        <v>2573288.79</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>4428370.95</v>
+        <v>4428370.65</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>245090638.01</v>
+        <v>245090685.03</v>
       </c>
       <c r="R19" s="13" t="n">
         <v>0.1248997633733931</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>1097889067.26</v>
+        <v>1097889138.04</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>104121932.82</v>
@@ -1664,10 +1664,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>1275892451.08</v>
+        <v>1275892521.86</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>215918800.59</v>
+        <v>215918844.49</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>38002578.37</v>
@@ -1679,16 +1679,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2738070.51</v>
+        <v>2738070.8</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>5494140.7</v>
+        <v>5494141.29</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>276651521.81</v>
+        <v>276651566.59</v>
       </c>
       <c r="R20" s="13" t="n">
         <v>0.178213812300984</v>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>1303188544</v>
+        <v>1303188690.82</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>122677612.96</v>
@@ -1722,10 +1722,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>1518488837.82</v>
+        <v>1518488984.64</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>252865081.71</v>
+        <v>252865125.83</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>44708007.56</v>
@@ -1737,16 +1737,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>3247081.86</v>
+        <v>3247081.99</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>6819803.91</v>
+        <v>6819804.18</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>326404388.19</v>
+        <v>326404432.71</v>
       </c>
       <c r="R21" s="13" t="n">
         <v>0.2003579150386557</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>1144725375.7</v>
+        <v>1144725862.47</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>132905659.86</v>
@@ -1780,10 +1780,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>1368046381.28</v>
+        <v>1368046868.05</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>217697235.87</v>
+        <v>217697316.57</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>44439935.08</v>
@@ -1795,16 +1795,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>2916882.02</v>
+        <v>2916881.79</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>6698305.52</v>
+        <v>6698304.98</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>289777304.08</v>
+        <v>289777384.01</v>
       </c>
       <c r="R22" s="13" t="n">
         <v>0.180964978836361</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>1190739704.81</v>
+        <v>1190739981.82</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>118302722.67</v>
@@ -1838,10 +1838,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>1385896392.87</v>
+        <v>1385896669.88</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>229729929.14</v>
+        <v>229730034.6</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>35142057.4</v>
@@ -1853,16 +1853,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>3441497.91</v>
+        <v>3441498.5</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>5603930.56</v>
+        <v>5603931.53</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>287479852.54</v>
+        <v>287479959.56</v>
       </c>
       <c r="R23" s="13" t="n">
         <v>0.316619068118602</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>1612357613.17</v>
+        <v>1612357829</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>146513108.49</v>
@@ -1896,10 +1896,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>1884574368.29</v>
+        <v>1884574584.12</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>316887970.26</v>
+        <v>316888023.07</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>43271898.85</v>
@@ -1911,16 +1911,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>5435368.52</v>
+        <v>5435368.62</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>9097133.699999999</v>
+        <v>9097133.880000001</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>396272603.98</v>
+        <v>396272657.07</v>
       </c>
       <c r="R24" s="13" t="n">
         <v>0.3069045894333504</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>1377198322.04</v>
+        <v>1377198457.04</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>144797057.56</v>
@@ -1954,10 +1954,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>1629698289.69</v>
+        <v>1629698424.69</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>256709383.42</v>
+        <v>256709471.12</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>45249277.15</v>
@@ -1969,16 +1969,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>3355922.44</v>
+        <v>3355923.07</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>8780025.77</v>
+        <v>8780027.42</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>333318556.41</v>
+        <v>333318646.38</v>
       </c>
       <c r="R25" s="13" t="n">
         <v>0.2790295913221863</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>1037098071.66</v>
+        <v>1037098603.03</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>97537800.47</v>
@@ -2012,10 +2012,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>1206202284.03</v>
+        <v>1206202815.4</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>200202210.51</v>
+        <v>200202273.18</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>31464287.45</v>
@@ -2027,16 +2027,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2871148.38</v>
+        <v>2871147.81</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>5012248.38</v>
+        <v>5012247.4</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>250987418.9</v>
+        <v>250987480.02</v>
       </c>
       <c r="R26" s="13" t="n">
         <v>0.2509415863550032</v>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>1198844154.44</v>
+        <v>1198844540.56</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>122103455.85</v>
@@ -2070,10 +2070,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>1406181562.4</v>
+        <v>1406181948.52</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>225001056.12</v>
+        <v>225001261.48</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>38650744.49</v>
@@ -2085,16 +2085,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>2585284</v>
+        <v>2585285.17</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>6112841.24</v>
+        <v>6112844</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>287799586.44</v>
+        <v>287799795.74</v>
       </c>
       <c r="R27" s="13" t="n">
         <v>0.2836514946154119</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>1317395129.74</v>
+        <v>1317396437.76</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>146265225.05</v>
@@ -2128,10 +2128,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>1563250029.39</v>
+        <v>1563251337.41</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>251064490.35</v>
+        <v>251064591.28</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>47820263.66</v>
@@ -2143,16 +2143,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2381326.52</v>
+        <v>2381325.22</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>7749023.37</v>
+        <v>7749019.13</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>330051319.25</v>
+        <v>330051414.63</v>
       </c>
       <c r="R28" s="13" t="n">
         <v>0.2603327878455701</v>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>1110053544.41</v>
+        <v>1110053782.77</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>110832888.3</v>
@@ -2186,10 +2186,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>1314001358.86</v>
+        <v>1314001597.22</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>203730972.4</v>
+        <v>203731026.81</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>33469362.8</v>
@@ -2201,16 +2201,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2592789.55</v>
+        <v>2592789.61</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>5824929.85</v>
+        <v>5824929.99</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>265597033.16</v>
+        <v>265597087.78</v>
       </c>
       <c r="R29" s="13" t="n">
         <v>0.2711837542671093</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>1383852603.56</v>
+        <v>1383852822.06</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>97591814.65000001</v>
@@ -2244,10 +2244,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>1576689087.63</v>
+        <v>1576689306.13</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>261337478.29</v>
+        <v>261337617.55</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>30161405.65</v>
@@ -2259,16 +2259,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>3726728.39</v>
+        <v>3726729.53</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>4002088.52</v>
+        <v>4002089.73</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>319908013.83</v>
+        <v>319908155.44</v>
       </c>
       <c r="R30" s="13" t="n">
         <v>0.3089090135319407</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>1727302472.59</v>
+        <v>1727303212.09</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>164444551.54</v>
@@ -2302,10 +2302,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>2027359138.62</v>
+        <v>2027359878.12</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>296355396.99</v>
+        <v>296355691.66</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>46737225.01</v>
@@ -2317,16 +2317,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>3587886.4</v>
+        <v>3587887.86</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>5274098.65</v>
+        <v>5274100.8</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>386042570.89</v>
+        <v>386042869.18</v>
       </c>
       <c r="R31" s="13" t="n">
         <v>0.3202852257171364</v>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>1572731510.28</v>
+        <v>1572732281.16</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>152797571.95</v>
@@ -2360,10 +2360,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>1832494594.4</v>
+        <v>1832495365.28</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>293610919.59</v>
+        <v>293611101.73</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>45961937.88</v>
@@ -2375,16 +2375,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>2694891.88</v>
+        <v>2694892.07</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>6570280.64</v>
+        <v>6570281.1</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>372627456.63</v>
+        <v>372627639.42</v>
       </c>
       <c r="R32" s="13" t="n">
         <v>0.3068596818867773</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>1305396310.28</v>
+        <v>1305396982.46</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>112904481.21</v>
@@ -2418,10 +2418,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>1491437336.39</v>
+        <v>1491438008.57</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>251861790.32</v>
+        <v>251861980.64</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>36710222.03</v>
@@ -2433,16 +2433,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1463493.81</v>
+        <v>1463494.06</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>6347095.45</v>
+        <v>6347096.52</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>309527271.11</v>
+        <v>309527462.74</v>
       </c>
       <c r="R33" s="13" t="n">
         <v>0.2945849325840212</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>1368372194.09</v>
+        <v>1368373322.94</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>111143043.36</v>
@@ -2476,10 +2476,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>1592263318.07</v>
+        <v>1592264446.92</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>248807143.09</v>
+        <v>248807322.63</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>33583851.98</v>
@@ -2491,16 +2491,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1142562.19</v>
+        <v>1142562.03</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>8125262.04</v>
+        <v>8125260.87</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>315335343.01</v>
+        <v>315335521.22</v>
       </c>
       <c r="R34" s="13" t="n">
         <v>0.3414174701179286</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>1428045019.9</v>
+        <v>1428047926.82</v>
       </c>
       <c r="C35" s="9" t="n">
         <v>132482297.68</v>
@@ -2534,10 +2534,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>1671702031.57</v>
+        <v>1671704938.49</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>263140323.07</v>
+        <v>263141431.55</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>39009607.96</v>
@@ -2549,16 +2549,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1891010.3</v>
+        <v>1891013.31</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>5945567.74</v>
+        <v>5945577.21</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>336441304.92</v>
+        <v>336442425.89</v>
       </c>
       <c r="R35" s="13" t="n">
         <v>0.3444918130280069</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>1456210004.04</v>
+        <v>1456211256.51</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>147816672.25</v>
@@ -2592,10 +2592,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>1723550294.91</v>
+        <v>1723551547.38</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>282237032.95</v>
+        <v>282237396.18</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>47162206.4</v>
@@ -2607,16 +2607,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>2226975.15</v>
+        <v>2226975.74</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>6426280.21</v>
+        <v>6426281.9</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>369372372.99</v>
+        <v>369372738.5</v>
       </c>
       <c r="R36" s="13" t="n">
         <v>0.3000842795719814</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>1613188890.89</v>
+        <v>1613189866.64</v>
       </c>
       <c r="C37" s="9" t="n">
         <v>161563899.02</v>
@@ -2650,10 +2650,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>1887509040.66</v>
+        <v>1887510016.41</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>289612789</v>
+        <v>289612974.35</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>49969404.96</v>
@@ -2665,16 +2665,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2038735.43</v>
+        <v>2038735.39</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>7146310.74</v>
+        <v>7146310.6</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>371788743.6</v>
+        <v>371788928.78</v>
       </c>
       <c r="R37" s="13" t="n">
         <v>0.3158320949670745</v>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>2119623767.07</v>
+        <v>2119624401.22</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>172439724.32</v>
@@ -2708,10 +2708,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>2463686858.28</v>
+        <v>2463687492.43</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>378506521.91</v>
+        <v>378506823.26</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>46814572.08</v>
@@ -2723,16 +2723,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>3468831.62</v>
+        <v>3468832.93</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>5883474.42</v>
+        <v>5883476.66</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>478311608.11</v>
+        <v>478311913.01</v>
       </c>
       <c r="R38" s="13" t="n">
         <v>0.3730201312691256</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>1628364635.61</v>
+        <v>1628366714.66</v>
       </c>
       <c r="C39" s="9" t="n">
         <v>131412975.25</v>
@@ -2766,10 +2766,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>1915134422.21</v>
+        <v>1915136501.26</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>294598078.01</v>
+        <v>294598291.66</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>38038258.86</v>
@@ -2781,16 +2781,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>4346489.23</v>
+        <v>4346486.86</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>6499228.75</v>
+        <v>6499225.21</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>384071585.67</v>
+        <v>384071793.41</v>
       </c>
       <c r="R39" s="13" t="n">
         <v>0.3654745795652588</v>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>1241347559.43</v>
+        <v>1241351270.68</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>184349276.32</v>
@@ -2824,10 +2824,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>1550725225.22</v>
+        <v>1550728936.47</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>227091796.66</v>
+        <v>227092279.77</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>52663679.72</v>
@@ -2839,16 +2839,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>3230023.33</v>
+        <v>3230020.34</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>4087121.53</v>
+        <v>4087117.75</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>324537961.23</v>
+        <v>324538437.56</v>
       </c>
       <c r="R40" s="13" t="n">
         <v>0.3156021020167954</v>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>1377185483.03</v>
+        <v>1377185796.22</v>
       </c>
       <c r="C41" s="9" t="n">
         <v>155233923.84</v>
@@ -2882,10 +2882,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>1655668146.64</v>
+        <v>1655668459.83</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>238173010.37</v>
+        <v>238173086.57</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>45723994.53</v>
@@ -2897,16 +2897,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>2993004.03</v>
+        <v>2993004.18</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>4877198.29</v>
+        <v>4877198.52</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>322916399.09</v>
+        <v>322916475.67</v>
       </c>
       <c r="R41" s="13" t="n">
         <v>0.3586813700389345</v>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>1613727498.3</v>
+        <v>1613729081.42</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>202803340.18</v>
@@ -2940,10 +2940,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>1989301443.73</v>
+        <v>1989303026.85</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>282619922.46</v>
+        <v>282620157.94</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>59467977.05</v>
@@ -2955,16 +2955,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>2562080.95</v>
+        <v>2562080.4</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>6710404.87</v>
+        <v>6710403.44</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>401337882.41</v>
+        <v>401338115.91</v>
       </c>
       <c r="R42" s="13" t="n">
         <v>0.374804382581988</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>1427767698.38</v>
+        <v>1427768237.52</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>221859292.06</v>
@@ -2998,10 +2998,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>1817554854.93</v>
+        <v>1817555394.07</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>232864613.03</v>
+        <v>232864673.99</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>61180817.13</v>
@@ -3013,16 +3013,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>2342316.34</v>
+        <v>2342316.06</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>6388147.24</v>
+        <v>6388146.46</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>343667545.72</v>
+        <v>343667605.62</v>
       </c>
       <c r="R43" s="13" t="n">
         <v>0.373808055436679</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>1480856540.2</v>
+        <v>1480857025.54</v>
       </c>
       <c r="C44" s="9" t="n">
         <v>197999210.33</v>
@@ -3056,10 +3056,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>1838737573.3</v>
+        <v>1838738058.64</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>248377086.17</v>
+        <v>248377231.89</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>51757760.82</v>
@@ -3071,16 +3071,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>4638589.31</v>
+        <v>4638590.04</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>6177354.04</v>
+        <v>6177355.02</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>349805445.85</v>
+        <v>349805593.27</v>
       </c>
       <c r="R44" s="13" t="n">
         <v>0.3916154766095744</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>2194898084.1</v>
+        <v>2194901222.62</v>
       </c>
       <c r="C45" s="9" t="n">
         <v>306596858.33</v>
@@ -3114,10 +3114,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>2819804601.33</v>
+        <v>2819807739.85</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>400042798.38</v>
+        <v>400043357.62</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>76961510.28</v>
@@ -3129,16 +3129,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>9471727.83</v>
+        <v>9471726.51</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>16166245.01</v>
+        <v>16166242.77</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>570540980.35</v>
+        <v>570541536.03</v>
       </c>
       <c r="R45" s="13" t="n">
         <v>0.4006796632230236</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>2305303001.33</v>
+        <v>2305304666.68</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>376108161.46</v>
@@ -3172,10 +3172,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>3105823468.48</v>
+        <v>3105825133.83</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>402170466.87</v>
+        <v>402170958.18</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>102191987.48</v>
@@ -3187,16 +3187,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>10742347.39</v>
+        <v>10742350.27</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>19778573.05</v>
+        <v>19778578.36</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>620963366.87</v>
+        <v>620963866.37</v>
       </c>
       <c r="R46" s="13" t="n">
         <v>0.442865097926909</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>1370766149.59</v>
+        <v>1370768389.55</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>250093696.52</v>
@@ -3230,10 +3230,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>1802384362.12</v>
+        <v>1802386602.08</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>227515238.9</v>
+        <v>227515592.59</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>65852392.81</v>
@@ -3245,16 +3245,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>3449585.35</v>
+        <v>3449584.56</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>4879520.83</v>
+        <v>4879519.7</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>347854669.37</v>
+        <v>347855021.14</v>
       </c>
       <c r="R47" s="13" t="n">
         <v>0.4207679702437824</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>1605877489.48</v>
+        <v>1605879118.04</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>251713084.28</v>
@@ -3288,10 +3288,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>2004199858.02</v>
+        <v>2004201486.58</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>256672802.22</v>
+        <v>256673126.18</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>62840730.8</v>
@@ -3303,16 +3303,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>4066682.22</v>
+        <v>4066682.56</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>5303364.8</v>
+        <v>5303365.24</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>362465702.59</v>
+        <v>362466027.33</v>
       </c>
       <c r="R48" s="13" t="n">
         <v>0.4544083188194561</v>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>1642728228.17</v>
+        <v>1642729965.66</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>255216837.43</v>
@@ -3346,10 +3346,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>2063081064</v>
+        <v>2063082801.49</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>257255722.56</v>
+        <v>257256125.15</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>63158844.13</v>
@@ -3361,16 +3361,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>4712168.8</v>
+        <v>4712170.03</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>5445735.49</v>
+        <v>5445736.91</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>367427943.17</v>
+        <v>367428348.4</v>
       </c>
       <c r="R49" s="13" t="n">
         <v>0.4715622688002217</v>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>1539527391.1</v>
+        <v>1539533856.72</v>
       </c>
       <c r="C50" s="9" t="n">
         <v>251070477.59</v>
@@ -3404,10 +3404,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>1989417568.85</v>
+        <v>1989424034.47</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>263414358.13</v>
+        <v>263415121.24</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>57612870.57</v>
@@ -3419,16 +3419,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>4620004.35</v>
+        <v>4619998.55</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>5904456.65</v>
+        <v>5904449.24</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>375780835.14</v>
+        <v>375781585.05</v>
       </c>
       <c r="R50" s="13" t="n">
         <v>0.5184969295746537</v>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>1765226971.96</v>
+        <v>1765229484.66</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>287468135.92</v>
@@ -3462,10 +3462,10 @@
         <v>28011807</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>2267509373.39</v>
+        <v>2267511886.09</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>281270702.06</v>
+        <v>281271724.46</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>59780017.61</v>
@@ -3477,16 +3477,16 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>5175416.27</v>
+        <v>5175424.17</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>7388612.4</v>
+        <v>7388623.69</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>13969238.87</v>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>395115238.97</v>
+        <v>395116280.57</v>
       </c>
       <c r="R51" s="13" t="n">
         <v>0.5173698555705437</v>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>2536973279.67</v>
+        <v>2536976230.19</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>438830798.95</v>
@@ -3520,10 +3520,10 @@
         <v>20465067</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>3325943177.73</v>
+        <v>3325946128.25</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>439525764.58</v>
+        <v>439526979.36</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>92879457.39</v>
@@ -3535,16 +3535,16 @@
         <v>15738266.69</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>7898043.52</v>
+        <v>7898052.48</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>23429981.34</v>
+        <v>23430007.91</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>10232009.27</v>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>618570033.26</v>
+        <v>618571283.5700001</v>
       </c>
       <c r="R52" s="13" t="n">
         <v>0.4928123695831447</v>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>2708587899.26</v>
+        <v>2708635757.64</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>590872240.37</v>
@@ -3578,10 +3578,10 @@
         <v>67156727</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>3868230153.29</v>
+        <v>3868278011.67</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>422517915.65</v>
+        <v>422537502.95</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>126606680.82</v>
@@ -3593,16 +3593,16 @@
         <v>34860196.13</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>8426396.09</v>
+        <v>8426543.43</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>31892381.46</v>
+        <v>31892939.09</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>33049467.84</v>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>679646174.54</v>
+        <v>679666466.8</v>
       </c>
       <c r="R53" s="13" t="n">
         <v>0.516687833119383</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>1283530595.17</v>
+        <v>1283611509.5</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>284348309.59</v>
@@ -3636,10 +3636,10 @@
         <v>57503053</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>1757471035.52</v>
+        <v>1757551949.85</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>214120689.6</v>
+        <v>214152399.99</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>74184906.98999999</v>
@@ -3651,16 +3651,16 @@
         <v>11903181.4</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1457194.34</v>
+        <v>1457261.72</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>6859662.78</v>
+        <v>6859979.96</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>28258572.47</v>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>347797936.17</v>
+        <v>347830031.12</v>
       </c>
       <c r="R54" s="13" t="n">
         <v>0.4317620090381182</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>1535178463.85</v>
+        <v>1535404703.37</v>
       </c>
       <c r="C55" s="9" t="n">
         <v>305249223.57</v>
@@ -3694,10 +3694,10 @@
         <v>29175511</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>1997255950.18</v>
+        <v>1997482189.7</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>255155773.76</v>
+        <v>255239214.43</v>
       </c>
       <c r="K55" s="12" t="n">
         <v>60959047.28</v>
@@ -3709,16 +3709,16 @@
         <v>8988100.75</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>2862355.73</v>
+        <v>2862706.8</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>5820728.14</v>
+        <v>5821442.06</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>13247763.43</v>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>358166035.54</v>
+        <v>358250541.2</v>
       </c>
       <c r="R55" s="13" t="n">
         <v>0.5085823534173731</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>1512027740.49</v>
+        <v>1512506709.74</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>295641521.04</v>
@@ -3752,10 +3752,10 @@
         <v>26518877</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>1967405720.51</v>
+        <v>1967884689.76</v>
       </c>
       <c r="J56" s="11" t="n">
-        <v>238971190.68</v>
+        <v>239141141.44</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>65905215.47</v>
@@ -3767,23 +3767,81 @@
         <v>10595274.38</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>2794403.99</v>
+        <v>2795102.78</v>
       </c>
       <c r="O56" s="12" t="n">
-        <v>5425316.98</v>
+        <v>5426673.67</v>
       </c>
       <c r="P56" s="12" t="n">
         <v>13188992.45</v>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>348486910.74</v>
+        <v>348658916.98</v>
       </c>
       <c r="R56" s="13" t="n">
         <v>0.5057931637222076</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>1709598911.47</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>307512657.17</v>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>57758660.58</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>70970611</v>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>17889394.25</v>
+      </c>
+      <c r="G57" s="9" t="n">
+        <v>35583543</v>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>27882416</v>
+      </c>
+      <c r="I57" s="10" t="n">
+        <v>2227196193.47</v>
+      </c>
+      <c r="J57" s="11" t="n">
+        <v>279891859.28</v>
+      </c>
+      <c r="K57" s="12" t="n">
+        <v>59383053.97</v>
+      </c>
+      <c r="L57" s="12" t="n">
+        <v>14390406.83</v>
+      </c>
+      <c r="M57" s="12" t="n">
+        <v>15136999.32</v>
+      </c>
+      <c r="N57" s="12" t="n">
+        <v>3154835.61</v>
+      </c>
+      <c r="O57" s="12" t="n">
+        <v>6275239.23</v>
+      </c>
+      <c r="P57" s="12" t="n">
+        <v>14538750.58</v>
+      </c>
+      <c r="Q57" s="12" t="n">
+        <v>392771144.82</v>
+      </c>
+      <c r="R57" s="13" t="n">
+        <v>0.5643242205108819</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R56"/>
+  <autoFilter ref="A2:R57"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3799,7 +3857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q56"/>
+  <dimension ref="A1:Q57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6878,8 +6936,63 @@
         <v>476088185.54</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>1990000000</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>317516647.48</v>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>57758660.58</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>70970611</v>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>17889394.25</v>
+      </c>
+      <c r="G57" s="9" t="n">
+        <v>38935764</v>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>28435594</v>
+      </c>
+      <c r="I57" s="10" t="n">
+        <v>2521506671.31</v>
+      </c>
+      <c r="J57" s="11" t="n">
+        <v>398597000</v>
+      </c>
+      <c r="K57" s="12" t="n">
+        <v>62879914.17</v>
+      </c>
+      <c r="L57" s="12" t="n">
+        <v>14390406.83</v>
+      </c>
+      <c r="M57" s="12" t="n">
+        <v>15136999.32</v>
+      </c>
+      <c r="N57" s="12" t="n">
+        <v>3671096.05</v>
+      </c>
+      <c r="O57" s="12" t="n">
+        <v>7990037.42</v>
+      </c>
+      <c r="P57" s="12" t="n">
+        <v>14774827.07</v>
+      </c>
+      <c r="Q57" s="12" t="n">
+        <v>517440280.86</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:Q56"/>
+  <autoFilter ref="A2:Q57"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -6894,7 +7007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9197,7 +9310,7 @@
         <v>11731471</v>
       </c>
       <c r="H54" s="14" t="n">
-        <v>0.7121999999999999</v>
+        <v>0.7121</v>
       </c>
       <c r="I54" s="14" t="n">
         <v>0.4394</v>
@@ -9240,7 +9353,7 @@
         <v>11228218</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>0.7391</v>
+        <v>0.7390000000000001</v>
       </c>
       <c r="I55" s="14" t="n">
         <v>0.4565</v>
@@ -9283,7 +9396,7 @@
         <v>12075182</v>
       </c>
       <c r="H56" s="14" t="n">
-        <v>0.7545999999999999</v>
+        <v>0.7544</v>
       </c>
       <c r="I56" s="14" t="n">
         <v>0.4471</v>
@@ -9301,15 +9414,58 @@
         <v>0.3942</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="15" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>1254496000</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>24158138.18</v>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>45672309</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>176995832.08</v>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>15317858.15</v>
+      </c>
+      <c r="G57" s="9" t="n">
+        <v>14205984</v>
+      </c>
+      <c r="H57" s="14" t="n">
+        <v>0.7338</v>
+      </c>
+      <c r="I57" s="14" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="J57" s="14" t="n">
+        <v>0.6435</v>
+      </c>
+      <c r="K57" s="14" t="n">
+        <v>0.5756</v>
+      </c>
+      <c r="L57" s="14" t="n">
+        <v>0.8563</v>
+      </c>
+      <c r="M57" s="14" t="n">
+        <v>0.3992</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~5M-trade sample (refreshed weekly) scaled to the daily total; ~70% of Kalshi's sports book by contracts, ~24% by $ (parlay legs are many and cheap - this sample-based split can move noticeably week to week, see VOLUME_METHODOLOGY.md). Not folded into the Sports tab's blended Combo %. Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M56"/>
+  <autoFilter ref="A2:M57"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -9342,7 +9498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-24. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-25. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>
@@ -9401,7 +9557,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-24: independently recomputed totals matched the committed figures exactly</t>
+          <t>2026-09-25: independently recomputed totals matched the committed figures exactly</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>2194901222.62</v>
+        <v>2194901522.62</v>
       </c>
       <c r="C45" s="9" t="n">
         <v>306596858.33</v>
@@ -3114,10 +3114,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>2819807739.85</v>
+        <v>2819808039.85</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>400043357.62</v>
+        <v>400043378.62</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>76961510.28</v>
@@ -3129,16 +3129,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>9471726.51</v>
+        <v>9471725.82</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>16166242.77</v>
+        <v>16166241.59</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>570541536.03</v>
+        <v>570541555.16</v>
       </c>
       <c r="R45" s="13" t="n">
         <v>0.4006796632230236</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>2305304666.68</v>
+        <v>2305304670.88</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>376108161.46</v>
@@ -3172,10 +3172,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>3105825133.83</v>
+        <v>3105825138.03</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>402170958.18</v>
+        <v>402170960.82</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>102191987.48</v>
@@ -3187,16 +3187,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>10742350.27</v>
+        <v>10742350.31</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>19778578.36</v>
+        <v>19778578.42</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>620963866.37</v>
+        <v>620963869.1</v>
       </c>
       <c r="R46" s="13" t="n">
         <v>0.442865097926909</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>1370768389.55</v>
+        <v>1370769366.33</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>250093696.52</v>
@@ -3230,10 +3230,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>1802386602.08</v>
+        <v>1802387578.86</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>227515592.59</v>
+        <v>227516369.28</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>65852392.81</v>
@@ -3245,16 +3245,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>3449584.56</v>
+        <v>3449590.53</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>4879519.7</v>
+        <v>4879528.15</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>347855021.14</v>
+        <v>347855812.25</v>
       </c>
       <c r="R47" s="13" t="n">
         <v>0.4207679702437824</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>1605879118.04</v>
+        <v>1605879745.64</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>251713084.28</v>
@@ -3288,10 +3288,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>2004201486.58</v>
+        <v>2004202114.18</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>256673126.18</v>
+        <v>256673244.82</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>62840730.8</v>
@@ -3303,16 +3303,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>4066682.56</v>
+        <v>4066682.62</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>5303365.24</v>
+        <v>5303365.32</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>362466027.33</v>
+        <v>362466146.11</v>
       </c>
       <c r="R48" s="13" t="n">
         <v>0.4544083188194561</v>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>1642729965.66</v>
+        <v>1642730315.78</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>255216837.43</v>
@@ -3346,10 +3346,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>2063082801.49</v>
+        <v>2063083151.61</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>257256125.15</v>
+        <v>257256387.77</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>63158844.13</v>
@@ -3361,16 +3361,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>4712170.03</v>
+        <v>4712172.67</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>5445736.91</v>
+        <v>5445739.96</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>367428348.4</v>
+        <v>367428616.72</v>
       </c>
       <c r="R49" s="13" t="n">
         <v>0.4715622688002217</v>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>1539533856.72</v>
+        <v>1539534414.04</v>
       </c>
       <c r="C50" s="9" t="n">
         <v>251070477.59</v>
@@ -3404,10 +3404,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>1989424034.47</v>
+        <v>1989424591.79</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>263415121.24</v>
+        <v>263415298.6</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>57612870.57</v>
@@ -3419,16 +3419,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>4619998.55</v>
+        <v>4619999.46</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>5904449.24</v>
+        <v>5904450.4</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>375781585.05</v>
+        <v>375781764.49</v>
       </c>
       <c r="R50" s="13" t="n">
         <v>0.5184969295746537</v>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>1765229484.66</v>
+        <v>1765229549.34</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>287468135.92</v>
@@ -3462,10 +3462,10 @@
         <v>28011807</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>2267511886.09</v>
+        <v>2267511950.77</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>281271724.46</v>
+        <v>281271753.48</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>59780017.61</v>
@@ -3477,16 +3477,16 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>5175424.17</v>
+        <v>5175424.41</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>7388623.69</v>
+        <v>7388624.04</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>13969238.87</v>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>395116280.57</v>
+        <v>395116310.17</v>
       </c>
       <c r="R51" s="13" t="n">
         <v>0.5173698555705437</v>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>2536976230.19</v>
+        <v>2536976369.49</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>438830798.95</v>
@@ -3520,10 +3520,10 @@
         <v>20465067</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>3325946128.25</v>
+        <v>3325946267.55</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>439526979.36</v>
+        <v>439527064.48</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>92879457.39</v>
@@ -3535,16 +3535,16 @@
         <v>15738266.69</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>7898052.48</v>
+        <v>7898053.28</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>23430007.91</v>
+        <v>23430010.28</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>10232009.27</v>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>618571283.5700001</v>
+        <v>618571371.85</v>
       </c>
       <c r="R52" s="13" t="n">
         <v>0.4928123695831447</v>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>2708635757.64</v>
+        <v>2708647150.05</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>590872240.37</v>
@@ -3578,10 +3578,10 @@
         <v>67156727</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>3868278011.67</v>
+        <v>3868289404.08</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>422537502.95</v>
+        <v>422542604.24</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>126606680.82</v>
@@ -3593,16 +3593,16 @@
         <v>34860196.13</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>8426543.43</v>
+        <v>8426584.279999999</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>31892939.09</v>
+        <v>31893093.71</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>33049467.84</v>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>679666466.8</v>
+        <v>679671763.5599999</v>
       </c>
       <c r="R53" s="13" t="n">
         <v>0.516687833119383</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>1283611509.5</v>
+        <v>1283623267.06</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>284348309.59</v>
@@ -3636,10 +3636,10 @@
         <v>57503053</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>1757551949.85</v>
+        <v>1757563707.41</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>214152399.99</v>
+        <v>214156360.82</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>74184906.98999999</v>
@@ -3651,16 +3651,16 @@
         <v>11903181.4</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1457261.72</v>
+        <v>1457268.74</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>6859979.96</v>
+        <v>6860012.97</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>28258572.47</v>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>347830031.12</v>
+        <v>347834031.98</v>
       </c>
       <c r="R54" s="13" t="n">
         <v>0.4317620090381182</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>1535404703.37</v>
+        <v>1535430421.94</v>
       </c>
       <c r="C55" s="9" t="n">
         <v>305249223.57</v>
@@ -3694,10 +3694,10 @@
         <v>29175511</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>1997482189.7</v>
+        <v>1997507908.27</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>255239214.43</v>
+        <v>255248246.6</v>
       </c>
       <c r="K55" s="12" t="n">
         <v>60959047.28</v>
@@ -3709,16 +3709,16 @@
         <v>8988100.75</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>2862706.8</v>
+        <v>2862743</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>5821442.06</v>
+        <v>5821515.66</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>13247763.43</v>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>358250541.2</v>
+        <v>358259683.16</v>
       </c>
       <c r="R55" s="13" t="n">
         <v>0.5085823534173731</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>1512506709.74</v>
+        <v>1512540167.24</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>295641521.04</v>
@@ -3752,10 +3752,10 @@
         <v>26518877</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>1967884689.76</v>
+        <v>1967918147.26</v>
       </c>
       <c r="J56" s="11" t="n">
-        <v>239141141.44</v>
+        <v>239153273.21</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>65905215.47</v>
@@ -3767,16 +3767,16 @@
         <v>10595274.38</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>2795102.78</v>
+        <v>2795153.71</v>
       </c>
       <c r="O56" s="12" t="n">
-        <v>5426673.67</v>
+        <v>5426772.57</v>
       </c>
       <c r="P56" s="12" t="n">
         <v>13188992.45</v>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>348658916.98</v>
+        <v>348671198.58</v>
       </c>
       <c r="R56" s="13" t="n">
         <v>0.5057931637222076</v>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>1709598911.47</v>
+        <v>1709684300.95</v>
       </c>
       <c r="C57" s="9" t="n">
         <v>307512657.17</v>
@@ -3810,10 +3810,10 @@
         <v>27882416</v>
       </c>
       <c r="I57" s="10" t="n">
-        <v>2227196193.47</v>
+        <v>2227281582.95</v>
       </c>
       <c r="J57" s="11" t="n">
-        <v>279891859.28</v>
+        <v>279924142</v>
       </c>
       <c r="K57" s="12" t="n">
         <v>59383053.97</v>
@@ -3825,16 +3825,16 @@
         <v>15136999.32</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>3154835.61</v>
+        <v>3154977.36</v>
       </c>
       <c r="O57" s="12" t="n">
-        <v>6275239.23</v>
+        <v>6275521.17</v>
       </c>
       <c r="P57" s="12" t="n">
         <v>14538750.58</v>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>392771144.82</v>
+        <v>392803851.23</v>
       </c>
       <c r="R57" s="13" t="n">
         <v>0.5643242205108819</v>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R57"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>1436294422.68</v>
+        <v>1436294771.91</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>133399888.66</v>
@@ -688,10 +688,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>1614256517.26</v>
+        <v>1614256866.49</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>299227836.4</v>
+        <v>299227931.95</v>
       </c>
       <c r="K3" s="12" t="n">
         <v>50986272.22</v>
@@ -701,16 +701,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>466111.61</v>
+        <v>466111.64</v>
       </c>
       <c r="O3" s="12" t="n">
-        <v>8313321.09</v>
+        <v>8313321.5</v>
       </c>
       <c r="P3" s="12" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="12" t="n">
-        <v>361465175.73</v>
+        <v>361465271.71</v>
       </c>
       <c r="R3" s="13" t="n">
         <v>0.08714584215412201</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>1205571891.8</v>
+        <v>1205572527.37</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>134065934.54</v>
@@ -742,10 +742,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>1388976801.31</v>
+        <v>1388977436.88</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>231812429.71</v>
+        <v>231812469.95</v>
       </c>
       <c r="K4" s="12" t="n">
         <v>51144509.72</v>
@@ -755,16 +755,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>458019.31</v>
+        <v>458019.15</v>
       </c>
       <c r="O4" s="12" t="n">
-        <v>8194677.56</v>
+        <v>8194674.84</v>
       </c>
       <c r="P4" s="12" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="12" t="n">
-        <v>296023232.35</v>
+        <v>296023269.73</v>
       </c>
       <c r="R4" s="13" t="n">
         <v>0.07635377691307524</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>889408107.8099999</v>
+        <v>889408207.3200001</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>85344135.09999999</v>
@@ -796,10 +796,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>1005450654.85</v>
+        <v>1005450754.36</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>202393372.63</v>
+        <v>202393402.47</v>
       </c>
       <c r="K5" s="12" t="n">
         <v>31777180.84</v>
@@ -809,16 +809,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>334880.9</v>
+        <v>334880.91</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>4825439.27</v>
+        <v>4825439.38</v>
       </c>
       <c r="P5" s="12" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>243868975.18</v>
+        <v>243869005.14</v>
       </c>
       <c r="R5" s="13" t="n">
         <v>0.05231046649197771</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1155124680.95</v>
+        <v>1155124761.9</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>120394335.41</v>
@@ -852,10 +852,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>1339762829.97</v>
+        <v>1339762910.92</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>243084529.44</v>
+        <v>243084553.51</v>
       </c>
       <c r="K6" s="12" t="n">
         <v>47471997.74</v>
@@ -867,16 +867,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>288784.93</v>
+        <v>288784.94</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>6546861.87</v>
+        <v>6546861.98</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>312033760.81</v>
+        <v>312033785</v>
       </c>
       <c r="R6" s="13" t="n">
         <v>0.1040882840699126</v>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1292327849.45</v>
+        <v>1292327864.05</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>125055737.8</v>
@@ -910,10 +910,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>1497407887.03</v>
+        <v>1497407901.63</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>259386804.98</v>
+        <v>259386809.75</v>
       </c>
       <c r="K7" s="12" t="n">
         <v>47948549.82</v>
@@ -925,16 +925,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>631739.74</v>
+        <v>631739.75</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>6846050.35</v>
+        <v>6846050.38</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>335565326.33</v>
+        <v>335565331.13</v>
       </c>
       <c r="R7" s="13" t="n">
         <v>0.1036604405692761</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1187471723.31</v>
+        <v>1187473379.22</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>141146850.05</v>
@@ -968,10 +968,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>1409644842.82</v>
+        <v>1409646498.73</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>236784791.23</v>
+        <v>236785396.63</v>
       </c>
       <c r="K8" s="12" t="n">
         <v>50551741.94</v>
@@ -983,16 +983,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>1121124.7</v>
+        <v>1121125.56</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>7508186.02</v>
+        <v>7508191.76</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>315423558.61</v>
+        <v>315424170.61</v>
       </c>
       <c r="R8" s="13" t="n">
         <v>0.09320593928966855</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1139474985.35</v>
+        <v>1139475102.86</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>117925601.54</v>
@@ -1026,10 +1026,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>1323082146.89</v>
+        <v>1323082264.4</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>224392495.43</v>
+        <v>224392529.9</v>
       </c>
       <c r="K9" s="12" t="n">
         <v>44939973.52</v>
@@ -1041,16 +1041,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>727221.1800000001</v>
+        <v>727221.2</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>6114374.37</v>
+        <v>6114374.56</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>289885936.18</v>
+        <v>289885970.86</v>
       </c>
       <c r="R9" s="13" t="n">
         <v>0.100308786205459</v>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1265087276.75</v>
+        <v>1265087404.75</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>119094679.49</v>
@@ -1084,10 +1084,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1469753174.23</v>
+        <v>1469753302.23</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>247904714.4</v>
+        <v>247904750.22</v>
       </c>
       <c r="K10" s="12" t="n">
         <v>44015511.37</v>
@@ -1099,16 +1099,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>2089369.81</v>
+        <v>2089369.87</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>6720639.12</v>
+        <v>6720639.29</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>320415201.21</v>
+        <v>320415237.26</v>
       </c>
       <c r="R10" s="13" t="n">
         <v>0.1305164739611011</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>1136158985.39</v>
+        <v>1136159290.18</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>126075255.12</v>
@@ -1142,10 +1142,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1360832302.51</v>
+        <v>1360832607.3</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>220224994.41</v>
+        <v>220225082.75</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>48533344.05</v>
@@ -1157,16 +1157,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2216235.31</v>
+        <v>2216235.46</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>7947063.6</v>
+        <v>7947064.16</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>302603634.01</v>
+        <v>302603723.07</v>
       </c>
       <c r="R11" s="13" t="n">
         <v>0.1174147553025735</v>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>817338101.49</v>
+        <v>817338212.49</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>76773291.01000001</v>
@@ -1200,10 +1200,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>944249792.52</v>
+        <v>944249903.52</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>157385850.49</v>
+        <v>157385884.62</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>28141958.88</v>
@@ -1215,16 +1215,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>1682387.12</v>
+        <v>1682387.2</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>3091094.65</v>
+        <v>3091094.82</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>202041292.16</v>
+        <v>202041326.54</v>
       </c>
       <c r="R12" s="13" t="n">
         <v>0.1320471995718654</v>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>1149012354.1</v>
+        <v>1149012503.87</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>86060025.34</v>
@@ -1258,10 +1258,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>1308569008.34</v>
+        <v>1308569158.11</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>235935235.65</v>
+        <v>235935265.58</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>32573678.23</v>
@@ -1273,16 +1273,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2341916.77</v>
+        <v>2341916.74</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>4886882.83</v>
+        <v>4886882.77</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>294006583.7</v>
+        <v>294006613.54</v>
       </c>
       <c r="R13" s="13" t="n">
         <v>0.1581581529884586</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>1239523499.17</v>
+        <v>1239523612.46</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>114182203.82</v>
@@ -1316,10 +1316,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>1441007689.24</v>
+        <v>1441007802.53</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>240227776</v>
+        <v>240227808.84</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>44020201.24</v>
@@ -1331,16 +1331,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2540875.76</v>
+        <v>2540875.83</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>6229748.61</v>
+        <v>6229748.78</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>313911471.81</v>
+        <v>313911504.89</v>
       </c>
       <c r="R14" s="13" t="n">
         <v>0.1369006174109096</v>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>1228242998.85</v>
+        <v>1228243450.84</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>130618679.53</v>
@@ -1374,10 +1374,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>1450290098.66</v>
+        <v>1450290550.65</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>245769332.65</v>
+        <v>245769484.31</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>47519466.33</v>
@@ -1389,16 +1389,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3332877.43</v>
+        <v>3332877.98</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>6989328.49</v>
+        <v>6989329.64</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>321982275.37</v>
+        <v>321982428.73</v>
       </c>
       <c r="R15" s="13" t="n">
         <v>0.1338434618903201</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>1206696239.55</v>
+        <v>1206697605.93</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>122512075.89</v>
@@ -1432,10 +1432,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>1408840118.58</v>
+        <v>1408841484.96</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>254178452.67</v>
+        <v>254178821.71</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>44967846.15</v>
@@ -1447,16 +1447,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>3170562.74</v>
+        <v>3170563.31</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>6715345.5</v>
+        <v>6715346.71</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>322388415.06</v>
+        <v>322388785.89</v>
       </c>
       <c r="R16" s="13" t="n">
         <v>0.1467243571212392</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1502787360.73</v>
+        <v>1502787564.29</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>135215397.14</v>
@@ -1490,10 +1490,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>1745508837.98</v>
+        <v>1745509041.54</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>307041496.45</v>
+        <v>307041589.03</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>48968794.7</v>
@@ -1505,16 +1505,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>3811148.02</v>
+        <v>3811148.5</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>8549326.57</v>
+        <v>8549327.640000001</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>388645966.92</v>
+        <v>388646061.05</v>
       </c>
       <c r="R17" s="13" t="n">
         <v>0.1671310595982739</v>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>1333526538.74</v>
+        <v>1333527107.48</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>146617403.12</v>
@@ -1548,10 +1548,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>1585701700.07</v>
+        <v>1585702268.81</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>261227409.04</v>
+        <v>261227630.36</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>56978627.74</v>
@@ -1563,16 +1563,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>3122214.22</v>
+        <v>3122215.12</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>9982355.99</v>
+        <v>9982358.85</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>348774936.09</v>
+        <v>348775161.17</v>
       </c>
       <c r="R18" s="13" t="n">
         <v>0.1404248555660547</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>918410591.3099999</v>
+        <v>918411728.12</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>100434174.96</v>
@@ -1606,10 +1606,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>1079827436.84</v>
+        <v>1079828573.65</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>188477182.67</v>
+        <v>188477283.51</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>36933011.94</v>
@@ -1621,16 +1621,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2573288.79</v>
+        <v>2573287.09</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>4428370.65</v>
+        <v>4428367.72</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>245090685.03</v>
+        <v>245090781.25</v>
       </c>
       <c r="R19" s="13" t="n">
         <v>0.1248997633733931</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>1097889138.04</v>
+        <v>1097889577.89</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>104121932.82</v>
@@ -1664,10 +1664,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>1275892521.86</v>
+        <v>1275892961.71</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>215918844.49</v>
+        <v>215918898.02</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>38002578.37</v>
@@ -1679,16 +1679,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2738070.8</v>
+        <v>2738070.37</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>5494141.29</v>
+        <v>5494140.43</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>276651566.59</v>
+        <v>276651618.83</v>
       </c>
       <c r="R20" s="13" t="n">
         <v>0.178213812300984</v>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>1303188690.82</v>
+        <v>1303188695.5</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>122677612.96</v>
@@ -1722,10 +1722,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>1518488984.64</v>
+        <v>1518488989.32</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>252865125.83</v>
+        <v>252865126.02</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>44708007.56</v>
@@ -1737,16 +1737,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>3247081.99</v>
+        <v>3247081.98</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>6819804.18</v>
+        <v>6819804.17</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>326404432.71</v>
+        <v>326404432.87</v>
       </c>
       <c r="R21" s="13" t="n">
         <v>0.2003579150386557</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>1144725862.47</v>
+        <v>1144727968.93</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>132905659.86</v>
@@ -1780,10 +1780,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>1368046868.05</v>
+        <v>1368048974.51</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>217697316.57</v>
+        <v>217697884.64</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>44439935.08</v>
@@ -1795,16 +1795,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>2916881.79</v>
+        <v>2916883.05</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>6698304.98</v>
+        <v>6698307.9</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>289777384.01</v>
+        <v>289777956.26</v>
       </c>
       <c r="R22" s="13" t="n">
         <v>0.180964978836361</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>1190739981.82</v>
+        <v>1190740247.18</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>118302722.67</v>
@@ -1838,10 +1838,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>1385896669.88</v>
+        <v>1385896935.24</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>229730034.6</v>
+        <v>229730116.3</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>35142057.4</v>
@@ -1853,16 +1853,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>3441498.5</v>
+        <v>3441498.83</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>5603931.53</v>
+        <v>5603932.07</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>287479959.56</v>
+        <v>287480042.13</v>
       </c>
       <c r="R23" s="13" t="n">
         <v>0.316619068118602</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>1612357829</v>
+        <v>1612359282.76</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>146513108.49</v>
@@ -1896,10 +1896,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>1884574584.12</v>
+        <v>1884576037.88</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>316888023.07</v>
+        <v>316888609.73</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>43271898.85</v>
@@ -1911,16 +1911,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>5435368.62</v>
+        <v>5435372.62</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>9097133.880000001</v>
+        <v>9097140.58</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>396272657.07</v>
+        <v>396273254.43</v>
       </c>
       <c r="R24" s="13" t="n">
         <v>0.3069045894333504</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>1377198457.04</v>
+        <v>1377199116.99</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>144797057.56</v>
@@ -1954,10 +1954,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>1629698424.69</v>
+        <v>1629699084.64</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>256709471.12</v>
+        <v>256709602.36</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>45249277.15</v>
@@ -1969,16 +1969,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>3355923.07</v>
+        <v>3355923.03</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>8780027.42</v>
+        <v>8780027.310000001</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>333318646.38</v>
+        <v>333318777.48</v>
       </c>
       <c r="R25" s="13" t="n">
         <v>0.2790295913221863</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>1037098603.03</v>
+        <v>1037098946.29</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>97537800.47</v>
@@ -2012,10 +2012,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>1206202815.4</v>
+        <v>1206203158.66</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>200202273.18</v>
+        <v>200202376.65</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>31464287.45</v>
@@ -2027,16 +2027,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2871147.81</v>
+        <v>2871148.19</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>5012247.4</v>
+        <v>5012248.06</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>250987480.02</v>
+        <v>250987584.53</v>
       </c>
       <c r="R26" s="13" t="n">
         <v>0.2509415863550032</v>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>1198844540.56</v>
+        <v>1198844632.54</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>122103455.85</v>
@@ -2070,10 +2070,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>1406181948.52</v>
+        <v>1406182040.5</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>225001261.48</v>
+        <v>225001300.69</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>38650744.49</v>
@@ -2085,16 +2085,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>2585285.17</v>
+        <v>2585285.36</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>6112844</v>
+        <v>6112844.45</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>287799795.74</v>
+        <v>287799835.58</v>
       </c>
       <c r="R27" s="13" t="n">
         <v>0.2836514946154119</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>1317396437.76</v>
+        <v>1317396516.11</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>146265225.05</v>
@@ -2128,10 +2128,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>1563251337.41</v>
+        <v>1563251415.76</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>251064591.28</v>
+        <v>251064623.63</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>47820263.66</v>
@@ -2143,16 +2143,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2381325.22</v>
+        <v>2381325.33</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>7749019.13</v>
+        <v>7749019.51</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>330051414.63</v>
+        <v>330051447.48</v>
       </c>
       <c r="R28" s="13" t="n">
         <v>0.2603327878455701</v>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>1110053782.77</v>
+        <v>1110054121.36</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>110832888.3</v>
@@ -2186,10 +2186,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>1314001597.22</v>
+        <v>1314001935.81</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>203731026.81</v>
+        <v>203731171.93</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>33469362.8</v>
@@ -2201,16 +2201,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2592789.61</v>
+        <v>2592790.39</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>5824929.99</v>
+        <v>5824931.73</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>265597087.78</v>
+        <v>265597235.41</v>
       </c>
       <c r="R29" s="13" t="n">
         <v>0.2711837542671093</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>1383852822.06</v>
+        <v>1383853189.28</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>97591814.65000001</v>
@@ -2244,10 +2244,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>1576689306.13</v>
+        <v>1576689673.35</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>261337617.55</v>
+        <v>261337732.09</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>30161405.65</v>
@@ -2259,16 +2259,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>3726729.53</v>
+        <v>3726730</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>4002089.73</v>
+        <v>4002090.25</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>319908155.44</v>
+        <v>319908270.97</v>
       </c>
       <c r="R30" s="13" t="n">
         <v>0.3089090135319407</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>1727303212.09</v>
+        <v>1727303217.17</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>164444551.54</v>
@@ -2302,10 +2302,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>2027359878.12</v>
+        <v>2027359883.2</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>296355691.66</v>
+        <v>296355693.73</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>46737225.01</v>
@@ -2317,16 +2317,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>3587887.86</v>
+        <v>3587887.87</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>5274100.8</v>
+        <v>5274100.81</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>386042869.18</v>
+        <v>386042871.27</v>
       </c>
       <c r="R31" s="13" t="n">
         <v>0.3202852257171364</v>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>1572732281.16</v>
+        <v>1572732698.76</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>152797571.95</v>
@@ -2360,10 +2360,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>1832495365.28</v>
+        <v>1832495782.88</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>293611101.73</v>
+        <v>293611128.13</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>45961937.88</v>
@@ -2375,16 +2375,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>2694892.07</v>
+        <v>2694891.63</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>6570281.1</v>
+        <v>6570280.04</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>372627639.42</v>
+        <v>372627664.33</v>
       </c>
       <c r="R32" s="13" t="n">
         <v>0.3068596818867773</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>1305396982.46</v>
+        <v>1305397293.87</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>112904481.21</v>
@@ -2418,10 +2418,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>1491438008.57</v>
+        <v>1491438319.98</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>251861980.64</v>
+        <v>251862125.19</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>36710222.03</v>
@@ -2433,16 +2433,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1463494.06</v>
+        <v>1463494.44</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>6347096.52</v>
+        <v>6347098.2</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>309527462.74</v>
+        <v>309527609.36</v>
       </c>
       <c r="R33" s="13" t="n">
         <v>0.2945849325840212</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>1368373322.94</v>
+        <v>1368373799.62</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>111143043.36</v>
@@ -2476,10 +2476,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>1592264446.92</v>
+        <v>1592264923.6</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>248807322.63</v>
+        <v>248807408.73</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>33583851.98</v>
@@ -2491,16 +2491,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1142562.03</v>
+        <v>1142562</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>8125260.87</v>
+        <v>8125260.65</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>315335521.22</v>
+        <v>315335607.07</v>
       </c>
       <c r="R34" s="13" t="n">
         <v>0.3414174701179286</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>1428047926.82</v>
+        <v>1428048707.96</v>
       </c>
       <c r="C35" s="9" t="n">
         <v>132482297.68</v>
@@ -2534,10 +2534,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>1671704938.49</v>
+        <v>1671705719.63</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>263141431.55</v>
+        <v>263141611.94</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>39009607.96</v>
@@ -2549,16 +2549,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1891013.31</v>
+        <v>1891013.44</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>5945577.21</v>
+        <v>5945577.63</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>336442425.89</v>
+        <v>336442606.83</v>
       </c>
       <c r="R35" s="13" t="n">
         <v>0.3444918130280069</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>1456211256.51</v>
+        <v>1456212603.34</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>147816672.25</v>
@@ -2592,10 +2592,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>1723551547.38</v>
+        <v>1723552894.21</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>282237396.18</v>
+        <v>282237551.49</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>47162206.4</v>
@@ -2607,16 +2607,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>2226975.74</v>
+        <v>2226974.92</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>6426281.9</v>
+        <v>6426279.52</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>369372738.5</v>
+        <v>369372890.61</v>
       </c>
       <c r="R36" s="13" t="n">
         <v>0.3000842795719814</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>1613189866.64</v>
+        <v>1613190917.55</v>
       </c>
       <c r="C37" s="9" t="n">
         <v>161563899.02</v>
@@ -2650,10 +2650,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>1887510016.41</v>
+        <v>1887511067.32</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>289612974.35</v>
+        <v>289613127.27</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>49969404.96</v>
@@ -2665,16 +2665,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2038735.39</v>
+        <v>2038735.08</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>7146310.6</v>
+        <v>7146309.54</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>371788928.78</v>
+        <v>371789080.33</v>
       </c>
       <c r="R37" s="13" t="n">
         <v>0.3158320949670745</v>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>2119624401.22</v>
+        <v>2119627585.85</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>172439724.32</v>
@@ -2708,10 +2708,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>2463687492.43</v>
+        <v>2463690677.06</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>378506823.26</v>
+        <v>378507471.37</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>46814572.08</v>
@@ -2723,16 +2723,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>3468832.93</v>
+        <v>3468833.15</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>5883476.66</v>
+        <v>5883477.03</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>478311913.01</v>
+        <v>478312561.72</v>
       </c>
       <c r="R38" s="13" t="n">
         <v>0.3730201312691256</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>1628366714.66</v>
+        <v>1628367827.22</v>
       </c>
       <c r="C39" s="9" t="n">
         <v>131412975.25</v>
@@ -2766,10 +2766,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>1915136501.26</v>
+        <v>1915137613.82</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>294598291.66</v>
+        <v>294598352.82</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>38038258.86</v>
@@ -2781,16 +2781,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>4346486.86</v>
+        <v>4346484.97</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>6499225.21</v>
+        <v>6499222.39</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>384071793.41</v>
+        <v>384071849.86</v>
       </c>
       <c r="R39" s="13" t="n">
         <v>0.3654745795652588</v>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>1241351270.68</v>
+        <v>1241351285.48</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>184349276.32</v>
@@ -2824,10 +2824,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>1550728936.47</v>
+        <v>1550728951.27</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>227092279.77</v>
+        <v>227092283.63</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>52663679.72</v>
@@ -2839,7 +2839,7 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>3230020.34</v>
+        <v>3230020.35</v>
       </c>
       <c r="O40" s="12" t="n">
         <v>4087117.75</v>
@@ -2848,7 +2848,7 @@
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>324538437.56</v>
+        <v>324538441.44</v>
       </c>
       <c r="R40" s="13" t="n">
         <v>0.3156021020167954</v>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>1377185796.22</v>
+        <v>1377185820.93</v>
       </c>
       <c r="C41" s="9" t="n">
         <v>155233923.84</v>
@@ -2882,10 +2882,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>1655668459.83</v>
+        <v>1655668484.54</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>238173086.57</v>
+        <v>238173101.15</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>45723994.53</v>
@@ -2897,16 +2897,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>2993004.18</v>
+        <v>2993004.27</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>4877198.52</v>
+        <v>4877198.67</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>322916475.67</v>
+        <v>322916490.49</v>
       </c>
       <c r="R41" s="13" t="n">
         <v>0.3586813700389345</v>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>1613729081.42</v>
+        <v>1613729395.82</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>202803340.18</v>
@@ -2940,10 +2940,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>1989303026.85</v>
+        <v>1989303341.25</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>282620157.94</v>
+        <v>282620294.98</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>59467977.05</v>
@@ -2955,16 +2955,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>2562080.4</v>
+        <v>2562080.88</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>6710403.44</v>
+        <v>6710404.7</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>401338115.91</v>
+        <v>401338254.69</v>
       </c>
       <c r="R42" s="13" t="n">
         <v>0.374804382581988</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>1427768237.52</v>
+        <v>1427769414.83</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>221859292.06</v>
@@ -2998,10 +2998,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>1817555394.07</v>
+        <v>1817556571.38</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>232864673.99</v>
+        <v>232864797.19</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>61180817.13</v>
@@ -3013,16 +3013,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>2342316.06</v>
+        <v>2342315.36</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>6388146.46</v>
+        <v>6388144.56</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>343667605.62</v>
+        <v>343667726.23</v>
       </c>
       <c r="R43" s="13" t="n">
         <v>0.373808055436679</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>1480857025.54</v>
+        <v>1480857719.21</v>
       </c>
       <c r="C44" s="9" t="n">
         <v>197999210.33</v>
@@ -3056,10 +3056,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>1838738058.64</v>
+        <v>1838738752.31</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>248377231.89</v>
+        <v>248377324.62</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>51757760.82</v>
@@ -3071,16 +3071,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>4638590.04</v>
+        <v>4638589.51</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>6177355.02</v>
+        <v>6177354.3</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>349805593.27</v>
+        <v>349805684.75</v>
       </c>
       <c r="R44" s="13" t="n">
         <v>0.3916154766095744</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>2194901522.62</v>
+        <v>2194903494.81</v>
       </c>
       <c r="C45" s="9" t="n">
         <v>306596858.33</v>
@@ -3114,10 +3114,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>2819808039.85</v>
+        <v>2819810012.04</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>400043378.62</v>
+        <v>400044786.19</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>76961510.28</v>
@@ -3129,16 +3129,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>9471725.82</v>
+        <v>9471743.35</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>16166241.59</v>
+        <v>16166271.51</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>570541555.16</v>
+        <v>570543010.1799999</v>
       </c>
       <c r="R45" s="13" t="n">
         <v>0.4006796632230236</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>2305304670.88</v>
+        <v>2305305174.13</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>376108161.46</v>
@@ -3172,10 +3172,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>3105825138.03</v>
+        <v>3105825641.28</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>402170960.82</v>
+        <v>402171072.7</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>102191987.48</v>
@@ -3187,16 +3187,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>10742350.31</v>
+        <v>10742350.51</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>19778578.42</v>
+        <v>19778578.79</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>620963869.1</v>
+        <v>620963981.5599999</v>
       </c>
       <c r="R46" s="13" t="n">
         <v>0.442865097926909</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>1370769366.33</v>
+        <v>1370776453.14</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>250093696.52</v>
@@ -3230,10 +3230,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>1802387578.86</v>
+        <v>1802394665.67</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>227516369.28</v>
+        <v>227517050.14</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>65852392.81</v>
@@ -3245,16 +3245,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>3449590.53</v>
+        <v>3449583.55</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>4879528.15</v>
+        <v>4879518.28</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>347855812.25</v>
+        <v>347856476.26</v>
       </c>
       <c r="R47" s="13" t="n">
         <v>0.4207679702437824</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>1605879745.64</v>
+        <v>1605881206.51</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>251713084.28</v>
@@ -3288,10 +3288,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>2004202114.18</v>
+        <v>2004203575.05</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>256673244.82</v>
+        <v>256674056.92</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>62840730.8</v>
@@ -3303,16 +3303,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>4066682.62</v>
+        <v>4066688.93</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>5303365.32</v>
+        <v>5303373.55</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>362466146.11</v>
+        <v>362466972.75</v>
       </c>
       <c r="R48" s="13" t="n">
         <v>0.4544083188194561</v>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>1642730315.78</v>
+        <v>1642734154.13</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>255216837.43</v>
@@ -3346,10 +3346,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>2063083151.61</v>
+        <v>2063086989.96</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>257256387.77</v>
+        <v>257258915.45</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>63158844.13</v>
@@ -3361,16 +3361,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>4712172.67</v>
+        <v>4712196.99</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>5445739.96</v>
+        <v>5445768.07</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>367428616.72</v>
+        <v>367431196.83</v>
       </c>
       <c r="R49" s="13" t="n">
         <v>0.4715622688002217</v>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>1539534414.04</v>
+        <v>1539536354.08</v>
       </c>
       <c r="C50" s="9" t="n">
         <v>251070477.59</v>
@@ -3404,10 +3404,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>1989424591.79</v>
+        <v>1989426531.83</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>263415298.6</v>
+        <v>263416069.75</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>57612870.57</v>
@@ -3419,16 +3419,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>4619999.46</v>
+        <v>4620004.58</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>5904450.4</v>
+        <v>5904456.95</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>375781764.49</v>
+        <v>375782547.3</v>
       </c>
       <c r="R50" s="13" t="n">
         <v>0.5184969295746537</v>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>1765229549.34</v>
+        <v>1765234997.97</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>287468135.92</v>
@@ -3462,10 +3462,10 @@
         <v>28011807</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>2267511950.77</v>
+        <v>2267517399.4</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>281271753.48</v>
+        <v>281272806.25</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>59780017.61</v>
@@ -3477,16 +3477,16 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>5175424.41</v>
+        <v>5175425.81</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>7388624.04</v>
+        <v>7388626.03</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>13969238.87</v>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>395116310.17</v>
+        <v>395117366.33</v>
       </c>
       <c r="R51" s="13" t="n">
         <v>0.5173698555705437</v>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>2536976369.49</v>
+        <v>2536981423.09</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>438830798.95</v>
@@ -3520,10 +3520,10 @@
         <v>20465067</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>3325946267.55</v>
+        <v>3325951321.15</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>439527064.48</v>
+        <v>439530027.01</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>92879457.39</v>
@@ -3535,16 +3535,16 @@
         <v>15738266.69</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>7898053.28</v>
+        <v>7898080.48</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>23430010.28</v>
+        <v>23430090.98</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>10232009.27</v>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>618571371.85</v>
+        <v>618574442.29</v>
       </c>
       <c r="R52" s="13" t="n">
         <v>0.4928123695831447</v>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>2708647150.05</v>
+        <v>2708733441.6</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>590872240.37</v>
@@ -3578,10 +3578,10 @@
         <v>67156727</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>3868289404.08</v>
+        <v>3868375695.63</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>422542604.24</v>
+        <v>422579475.21</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>126606680.82</v>
@@ -3593,16 +3593,16 @@
         <v>34860196.13</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>8426584.279999999</v>
+        <v>8426870.4</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>31893093.71</v>
+        <v>31894176.62</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>33049467.84</v>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>679671763.5599999</v>
+        <v>679710003.5599999</v>
       </c>
       <c r="R53" s="13" t="n">
         <v>0.516687833119383</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>1283623267.06</v>
+        <v>1283735583.29</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>284348309.59</v>
@@ -3636,10 +3636,10 @@
         <v>57503053</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>1757563707.41</v>
+        <v>1757676023.64</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>214156360.82</v>
+        <v>214204504.66</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>74184906.98999999</v>
@@ -3651,16 +3651,16 @@
         <v>11903181.4</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1457268.74</v>
+        <v>1457379.96</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>6860012.97</v>
+        <v>6860536.57</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>28258572.47</v>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>347834031.98</v>
+        <v>347882810.64</v>
       </c>
       <c r="R54" s="13" t="n">
         <v>0.4317620090381182</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>1535430421.94</v>
+        <v>1535588631.95</v>
       </c>
       <c r="C55" s="9" t="n">
         <v>305249223.57</v>
@@ -3694,10 +3694,10 @@
         <v>29175511</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>1997507908.27</v>
+        <v>1997666118.28</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>255248246.6</v>
+        <v>255313286.41</v>
       </c>
       <c r="K55" s="12" t="n">
         <v>60959047.28</v>
@@ -3709,16 +3709,16 @@
         <v>8988100.75</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>2862743</v>
+        <v>2863043.22</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>5821515.66</v>
+        <v>5822126.18</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>13247763.43</v>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>358259683.16</v>
+        <v>358325633.73</v>
       </c>
       <c r="R55" s="13" t="n">
         <v>0.5085823534173731</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>1512540167.24</v>
+        <v>1512773796.63</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>295641521.04</v>
@@ -3752,10 +3752,10 @@
         <v>26518877</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>1967918147.26</v>
+        <v>1968151776.65</v>
       </c>
       <c r="J56" s="11" t="n">
-        <v>239153273.21</v>
+        <v>239242977.1</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>65905215.47</v>
@@ -3767,16 +3767,16 @@
         <v>10595274.38</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>2795153.71</v>
+        <v>2795550.3</v>
       </c>
       <c r="O56" s="12" t="n">
-        <v>5426772.57</v>
+        <v>5427542.54</v>
       </c>
       <c r="P56" s="12" t="n">
         <v>13188992.45</v>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>348671198.58</v>
+        <v>348762069.02</v>
       </c>
       <c r="R56" s="13" t="n">
         <v>0.5057931637222076</v>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>1709684300.95</v>
+        <v>1710113978.33</v>
       </c>
       <c r="C57" s="9" t="n">
         <v>307512657.17</v>
@@ -3810,10 +3810,10 @@
         <v>27882416</v>
       </c>
       <c r="I57" s="10" t="n">
-        <v>2227281582.95</v>
+        <v>2227711260.33</v>
       </c>
       <c r="J57" s="11" t="n">
-        <v>279924142</v>
+        <v>280098666.51</v>
       </c>
       <c r="K57" s="12" t="n">
         <v>59383053.97</v>
@@ -3825,23 +3825,81 @@
         <v>15136999.32</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>3154977.36</v>
+        <v>3155789.83</v>
       </c>
       <c r="O57" s="12" t="n">
-        <v>6275521.17</v>
+        <v>6277137.26</v>
       </c>
       <c r="P57" s="12" t="n">
         <v>14538750.58</v>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>392803851.23</v>
+        <v>392980804.3</v>
       </c>
       <c r="R57" s="13" t="n">
         <v>0.5643242205108819</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>1665920736.64</v>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>360408853.21</v>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>58314497.01</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>63533336</v>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>24820892.38</v>
+      </c>
+      <c r="G58" s="9" t="n">
+        <v>52104017</v>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>38681934</v>
+      </c>
+      <c r="I58" s="10" t="n">
+        <v>2263784266.24</v>
+      </c>
+      <c r="J58" s="11" t="n">
+        <v>272476635.13</v>
+      </c>
+      <c r="K58" s="12" t="n">
+        <v>71309977.62</v>
+      </c>
+      <c r="L58" s="12" t="n">
+        <v>17694898.39</v>
+      </c>
+      <c r="M58" s="12" t="n">
+        <v>15006248.84</v>
+      </c>
+      <c r="N58" s="12" t="n">
+        <v>4491345.03</v>
+      </c>
+      <c r="O58" s="12" t="n">
+        <v>9428231.439999999</v>
+      </c>
+      <c r="P58" s="12" t="n">
+        <v>19224841.85</v>
+      </c>
+      <c r="Q58" s="12" t="n">
+        <v>409632178.3</v>
+      </c>
+      <c r="R58" s="13" t="n">
+        <v>0.5560789475916204</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R57"/>
+  <autoFilter ref="A2:R58"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3857,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:Q58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6991,8 +7049,63 @@
         <v>517440280.86</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>1932135780.79</v>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>373857348.69</v>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>58314497.01</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>63533336</v>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>24820892.38</v>
+      </c>
+      <c r="G58" s="9" t="n">
+        <v>56377186</v>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>39460452</v>
+      </c>
+      <c r="I58" s="10" t="n">
+        <v>2548499492.87</v>
+      </c>
+      <c r="J58" s="11" t="n">
+        <v>387006796.89</v>
+      </c>
+      <c r="K58" s="12" t="n">
+        <v>76475302.37</v>
+      </c>
+      <c r="L58" s="12" t="n">
+        <v>17694898.39</v>
+      </c>
+      <c r="M58" s="12" t="n">
+        <v>15006248.84</v>
+      </c>
+      <c r="N58" s="12" t="n">
+        <v>5188299.08</v>
+      </c>
+      <c r="O58" s="12" t="n">
+        <v>11784495.81</v>
+      </c>
+      <c r="P58" s="12" t="n">
+        <v>19555570.12</v>
+      </c>
+      <c r="Q58" s="12" t="n">
+        <v>532711611.51</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:Q57"/>
+  <autoFilter ref="A2:Q58"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -7007,7 +7120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9267,7 +9380,7 @@
         <v>47830508</v>
       </c>
       <c r="H53" s="14" t="n">
-        <v>0.7378</v>
+        <v>0.7376999999999999</v>
       </c>
       <c r="I53" s="14" t="n">
         <v>0.4838</v>
@@ -9310,7 +9423,7 @@
         <v>11731471</v>
       </c>
       <c r="H54" s="14" t="n">
-        <v>0.7121</v>
+        <v>0.7120000000000001</v>
       </c>
       <c r="I54" s="14" t="n">
         <v>0.4394</v>
@@ -9353,7 +9466,7 @@
         <v>11228218</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>0.7390000000000001</v>
+        <v>0.7389</v>
       </c>
       <c r="I55" s="14" t="n">
         <v>0.4565</v>
@@ -9396,7 +9509,7 @@
         <v>12075182</v>
       </c>
       <c r="H56" s="14" t="n">
-        <v>0.7544</v>
+        <v>0.7543000000000001</v>
       </c>
       <c r="I56" s="14" t="n">
         <v>0.4471</v>
@@ -9439,7 +9552,7 @@
         <v>14205984</v>
       </c>
       <c r="H57" s="14" t="n">
-        <v>0.7338</v>
+        <v>0.7336</v>
       </c>
       <c r="I57" s="14" t="n">
         <v>0.4183</v>
@@ -9457,15 +9570,58 @@
         <v>0.3992</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="15" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="n">
+        <v>1218018396.21</v>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>23632292.97</v>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>37662641</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>209113970.95</v>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>22369104.94</v>
+      </c>
+      <c r="G58" s="9" t="n">
+        <v>18174499</v>
+      </c>
+      <c r="H58" s="14" t="n">
+        <v>0.7311</v>
+      </c>
+      <c r="I58" s="14" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="J58" s="14" t="n">
+        <v>0.5928</v>
+      </c>
+      <c r="K58" s="14" t="n">
+        <v>0.5802</v>
+      </c>
+      <c r="L58" s="14" t="n">
+        <v>0.9012</v>
+      </c>
+      <c r="M58" s="14" t="n">
+        <v>0.3488</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~5M-trade sample (refreshed weekly) scaled to the daily total; ~70% of Kalshi's sports book by contracts, ~24% by $ (parlay legs are many and cheap - this sample-based split can move noticeably week to week, see VOLUME_METHODOLOGY.md). Not folded into the Sports tab's blended Combo %. Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M57"/>
+  <autoFilter ref="A2:M58"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -9498,7 +9654,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-25. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-26. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9713,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-25: independently recomputed totals matched the committed figures exactly</t>
+          <t>2026-09-26: independently recomputed totals matched the committed figures exactly</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$58</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$58</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R58"/>
+  <dimension ref="A1:R59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>1436294771.91</v>
+        <v>1436295792.28</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>133399888.66</v>
@@ -688,10 +688,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>1614256866.49</v>
+        <v>1614257886.86</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>299227931.95</v>
+        <v>299227977.2</v>
       </c>
       <c r="K3" s="12" t="n">
         <v>50986272.22</v>
@@ -701,16 +701,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>466111.64</v>
+        <v>466111.4</v>
       </c>
       <c r="O3" s="12" t="n">
-        <v>8313321.5</v>
+        <v>8313317.18</v>
       </c>
       <c r="P3" s="12" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="12" t="n">
-        <v>361465271.71</v>
+        <v>361465312.4</v>
       </c>
       <c r="R3" s="13" t="n">
         <v>0.08714584215412201</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>1205572527.37</v>
+        <v>1205572764.67</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>134065934.54</v>
@@ -742,10 +742,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>1388977436.88</v>
+        <v>1388977674.18</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>231812469.95</v>
+        <v>231812487.87</v>
       </c>
       <c r="K4" s="12" t="n">
         <v>51144509.72</v>
@@ -755,16 +755,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>458019.15</v>
+        <v>458019.1</v>
       </c>
       <c r="O4" s="12" t="n">
-        <v>8194674.84</v>
+        <v>8194673.91</v>
       </c>
       <c r="P4" s="12" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="12" t="n">
-        <v>296023269.73</v>
+        <v>296023286.66</v>
       </c>
       <c r="R4" s="13" t="n">
         <v>0.07635377691307524</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>889408207.3200001</v>
+        <v>889409108.64</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>85344135.09999999</v>
@@ -796,10 +796,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>1005450754.36</v>
+        <v>1005451655.68</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>202393402.47</v>
+        <v>202393699.12</v>
       </c>
       <c r="K5" s="12" t="n">
         <v>31777180.84</v>
@@ -809,16 +809,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>334880.91</v>
+        <v>334881.02</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>4825439.38</v>
+        <v>4825440.96</v>
       </c>
       <c r="P5" s="12" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>243869005.14</v>
+        <v>243869303.48</v>
       </c>
       <c r="R5" s="13" t="n">
         <v>0.05231046649197771</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1155124761.9</v>
+        <v>1155125148.83</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>120394335.41</v>
@@ -852,10 +852,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>1339762910.92</v>
+        <v>1339763297.85</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>243084553.51</v>
+        <v>243084633.11</v>
       </c>
       <c r="K6" s="12" t="n">
         <v>47471997.74</v>
@@ -867,16 +867,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>288784.94</v>
+        <v>288784.93</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>6546861.98</v>
+        <v>6546861.75</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>312033785</v>
+        <v>312033864.36</v>
       </c>
       <c r="R6" s="13" t="n">
         <v>0.1040882840699126</v>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1292327864.05</v>
+        <v>1292328358.91</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>125055737.8</v>
@@ -910,10 +910,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>1497407901.63</v>
+        <v>1497408396.49</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>259386809.75</v>
+        <v>259386991.34</v>
       </c>
       <c r="K7" s="12" t="n">
         <v>47948549.82</v>
@@ -925,16 +925,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>631739.75</v>
+        <v>631739.88</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>6846050.38</v>
+        <v>6846051.85</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>335565331.13</v>
+        <v>335565514.33</v>
       </c>
       <c r="R7" s="13" t="n">
         <v>0.1036604405692761</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1187473379.22</v>
+        <v>1187474069.69</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>141146850.05</v>
@@ -968,10 +968,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>1409646498.73</v>
+        <v>1409647189.2</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>236785396.63</v>
+        <v>236785600.64</v>
       </c>
       <c r="K8" s="12" t="n">
         <v>50551741.94</v>
@@ -983,16 +983,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>1121125.56</v>
+        <v>1121125.74</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>7508191.76</v>
+        <v>7508192.98</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>315424170.61</v>
+        <v>315424376.01</v>
       </c>
       <c r="R8" s="13" t="n">
         <v>0.09320593928966855</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1139475102.86</v>
+        <v>1139475798.9</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>117925601.54</v>
@@ -1026,10 +1026,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>1323082264.4</v>
+        <v>1323082960.44</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>224392529.9</v>
+        <v>224392735.83</v>
       </c>
       <c r="K9" s="12" t="n">
         <v>44939973.52</v>
@@ -1041,16 +1041,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>727221.2</v>
+        <v>727221.34</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>6114374.56</v>
+        <v>6114375.72</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>289885970.86</v>
+        <v>289886178.08</v>
       </c>
       <c r="R9" s="13" t="n">
         <v>0.100308786205459</v>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1265087404.75</v>
+        <v>1265087780.96</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>119094679.49</v>
@@ -1084,10 +1084,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1469753302.23</v>
+        <v>1469753678.44</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>247904750.22</v>
+        <v>247904802.27</v>
       </c>
       <c r="K10" s="12" t="n">
         <v>44015511.37</v>
@@ -1099,16 +1099,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>2089369.87</v>
+        <v>2089369.66</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>6720639.29</v>
+        <v>6720638.65</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>320415237.26</v>
+        <v>320415288.46</v>
       </c>
       <c r="R10" s="13" t="n">
         <v>0.1305164739611011</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>1136159290.18</v>
+        <v>1136159801.99</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>126075255.12</v>
@@ -1142,10 +1142,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1360832607.3</v>
+        <v>1360833119.11</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>220225082.75</v>
+        <v>220225203.26</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>48533344.05</v>
@@ -1157,16 +1157,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2216235.46</v>
+        <v>2216235.51</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>7947064.16</v>
+        <v>7947064.34</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>302603723.07</v>
+        <v>302603843.81</v>
       </c>
       <c r="R11" s="13" t="n">
         <v>0.1174147553025735</v>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>817338212.49</v>
+        <v>817339664.7</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>76773291.01000001</v>
@@ -1200,10 +1200,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>944249903.52</v>
+        <v>944251355.73</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>157385884.62</v>
+        <v>157386020.55</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>28141958.88</v>
@@ -1215,16 +1215,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>1682387.2</v>
+        <v>1682385.71</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>3091094.82</v>
+        <v>3091092.08</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>202041326.54</v>
+        <v>202041458.24</v>
       </c>
       <c r="R12" s="13" t="n">
         <v>0.1320471995718654</v>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>1149012503.87</v>
+        <v>1149012874.56</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>86060025.34</v>
@@ -1258,10 +1258,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>1308569158.11</v>
+        <v>1308569528.8</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>235935265.58</v>
+        <v>235935409.08</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>32573678.23</v>
@@ -1273,16 +1273,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2341916.74</v>
+        <v>2341917.23</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>4886882.77</v>
+        <v>4886883.79</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>294006613.54</v>
+        <v>294006758.56</v>
       </c>
       <c r="R13" s="13" t="n">
         <v>0.1581581529884586</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>1239523612.46</v>
+        <v>1239523834.71</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>114182203.82</v>
@@ -1316,10 +1316,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>1441007802.53</v>
+        <v>1441008024.78</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>240227808.84</v>
+        <v>240227831.74</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>44020201.24</v>
@@ -1331,16 +1331,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2540875.83</v>
+        <v>2540875.62</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>6229748.78</v>
+        <v>6229748.25</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>313911504.89</v>
+        <v>313911527.05</v>
       </c>
       <c r="R14" s="13" t="n">
         <v>0.1369006174109096</v>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>1228243450.84</v>
+        <v>1228244144.28</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>130618679.53</v>
@@ -1374,10 +1374,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>1450290550.65</v>
+        <v>1450291244.09</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>245769484.31</v>
+        <v>245769708.98</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>47519466.33</v>
@@ -1389,16 +1389,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3332877.98</v>
+        <v>3332878.74</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>6989329.64</v>
+        <v>6989331.23</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>321982428.73</v>
+        <v>321982655.74</v>
       </c>
       <c r="R15" s="13" t="n">
         <v>0.1338434618903201</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>1206697605.93</v>
+        <v>1206699121.9</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>122512075.89</v>
@@ -1432,10 +1432,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>1408841484.96</v>
+        <v>1408843000.93</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>254178821.71</v>
+        <v>254179037.12</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>44967846.15</v>
@@ -1447,16 +1447,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>3170563.31</v>
+        <v>3170561.97</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>6715346.71</v>
+        <v>6715343.88</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>322388785.89</v>
+        <v>322388997.14</v>
       </c>
       <c r="R16" s="13" t="n">
         <v>0.1467243571212392</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1502787564.29</v>
+        <v>1502787686.94</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>135215397.14</v>
@@ -1490,10 +1490,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>1745509041.54</v>
+        <v>1745509164.19</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>307041589.03</v>
+        <v>307041600.92</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>48968794.7</v>
@@ -1505,16 +1505,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>3811148.5</v>
+        <v>3811148.35</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>8549327.640000001</v>
+        <v>8549327.289999999</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>388646061.05</v>
+        <v>388646072.44</v>
       </c>
       <c r="R17" s="13" t="n">
         <v>0.1671310595982739</v>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>1333527107.48</v>
+        <v>1333527779.09</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>146617403.12</v>
@@ -1548,10 +1548,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>1585702268.81</v>
+        <v>1585702940.42</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>261227630.36</v>
+        <v>261227786.79</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>56978627.74</v>
@@ -1563,16 +1563,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>3122215.12</v>
+        <v>3122215.2</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>9982358.85</v>
+        <v>9982359.109999999</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>348775161.17</v>
+        <v>348775317.94</v>
       </c>
       <c r="R18" s="13" t="n">
         <v>0.1404248555660547</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>918411728.12</v>
+        <v>918412109.84</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>100434174.96</v>
@@ -1606,10 +1606,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>1079828573.65</v>
+        <v>1079828955.37</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>188477283.51</v>
+        <v>188477360.65</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>36933011.94</v>
@@ -1621,16 +1621,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2573287.09</v>
+        <v>2573286.99</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>4428367.72</v>
+        <v>4428367.54</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>245090781.25</v>
+        <v>245090858.11</v>
       </c>
       <c r="R19" s="13" t="n">
         <v>0.1248997633733931</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>1097889577.89</v>
+        <v>1097890036.06</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>104121932.82</v>
@@ -1664,10 +1664,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>1275892961.71</v>
+        <v>1275893419.88</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>215918898.02</v>
+        <v>215919005.71</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>38002578.37</v>
@@ -1679,16 +1679,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2738070.37</v>
+        <v>2738070.46</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>5494140.43</v>
+        <v>5494140.6</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>276651618.83</v>
+        <v>276651726.78</v>
       </c>
       <c r="R20" s="13" t="n">
         <v>0.178213812300984</v>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>1303188695.5</v>
+        <v>1303189628.44</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>122677612.96</v>
@@ -1722,10 +1722,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>1518488989.32</v>
+        <v>1518489922.26</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>252865126.02</v>
+        <v>252865351.51</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>44708007.56</v>
@@ -1737,16 +1737,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>3247081.98</v>
+        <v>3247082.24</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>6819804.17</v>
+        <v>6819804.71</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>326404432.87</v>
+        <v>326404659.15</v>
       </c>
       <c r="R21" s="13" t="n">
         <v>0.2003579150386557</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>1144727968.93</v>
+        <v>1144728531.05</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>132905659.86</v>
@@ -1780,10 +1780,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>1368048974.51</v>
+        <v>1368049536.63</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>217697884.64</v>
+        <v>217697987.56</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>44439935.08</v>
@@ -1795,16 +1795,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>2916883.05</v>
+        <v>2916882.89</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>6698307.9</v>
+        <v>6698307.51</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>289777956.26</v>
+        <v>289778058.63</v>
       </c>
       <c r="R22" s="13" t="n">
         <v>0.180964978836361</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>1190740247.18</v>
+        <v>1190740925.2</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>118302722.67</v>
@@ -1838,10 +1838,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>1385896935.24</v>
+        <v>1385897613.26</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>229730116.3</v>
+        <v>229730310.82</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>35142057.4</v>
@@ -1853,16 +1853,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>3441498.83</v>
+        <v>3441499.5</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>5603932.07</v>
+        <v>5603933.15</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>287480042.13</v>
+        <v>287480238.4</v>
       </c>
       <c r="R23" s="13" t="n">
         <v>0.316619068118602</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>1612359282.76</v>
+        <v>1612360798.46</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>146513108.49</v>
@@ -1896,10 +1896,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>1884576037.88</v>
+        <v>1884577553.58</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>316888609.73</v>
+        <v>316889282.95</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>43271898.85</v>
@@ -1911,16 +1911,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>5435372.62</v>
+        <v>5435377.67</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>9097140.58</v>
+        <v>9097149.02</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>396273254.43</v>
+        <v>396273941.14</v>
       </c>
       <c r="R24" s="13" t="n">
         <v>0.3069045894333504</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>1377199116.99</v>
+        <v>1377200237.42</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>144797057.56</v>
@@ -1954,10 +1954,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>1629699084.64</v>
+        <v>1629700205.07</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>256709602.36</v>
+        <v>256709764.62</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>45249277.15</v>
@@ -1969,16 +1969,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>3355923.03</v>
+        <v>3355922.33</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>8780027.310000001</v>
+        <v>8780025.48</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>333318777.48</v>
+        <v>333318937.21</v>
       </c>
       <c r="R25" s="13" t="n">
         <v>0.2790295913221863</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>1037098946.29</v>
+        <v>1037100841.91</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>97537800.47</v>
@@ -2012,10 +2012,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>1206203158.66</v>
+        <v>1206205054.28</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>200202376.65</v>
+        <v>200202872.35</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>31464287.45</v>
@@ -2027,16 +2027,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2871148.19</v>
+        <v>2871149.39</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>5012248.06</v>
+        <v>5012250.14</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>250987584.53</v>
+        <v>250988083.51</v>
       </c>
       <c r="R26" s="13" t="n">
         <v>0.2509415863550032</v>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>1198844632.54</v>
+        <v>1198845133.86</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>122103455.85</v>
@@ -2070,10 +2070,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>1406182040.5</v>
+        <v>1406182541.82</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>225001300.69</v>
+        <v>225001532.23</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>38650744.49</v>
@@ -2085,16 +2085,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>2585285.36</v>
+        <v>2585286.55</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>6112844.45</v>
+        <v>6112847.28</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>287799835.58</v>
+        <v>287800071.14</v>
       </c>
       <c r="R27" s="13" t="n">
         <v>0.2836514946154119</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>1317396516.11</v>
+        <v>1317397401.7</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>146265225.05</v>
@@ -2128,10 +2128,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>1563251415.76</v>
+        <v>1563252301.35</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>251064623.63</v>
+        <v>251064654.32</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>47820263.66</v>
@@ -2143,16 +2143,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2381325.33</v>
+        <v>2381324.17</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>7749019.51</v>
+        <v>7749015.73</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>330051447.48</v>
+        <v>330051473.22</v>
       </c>
       <c r="R28" s="13" t="n">
         <v>0.2603327878455701</v>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>1110054121.36</v>
+        <v>1110056285</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>110832888.3</v>
@@ -2186,10 +2186,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>1314001935.81</v>
+        <v>1314004099.45</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>203731171.93</v>
+        <v>203731801.93</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>33469362.8</v>
@@ -2201,16 +2201,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2592790.39</v>
+        <v>2592792.33</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>5824931.73</v>
+        <v>5824936.09</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>265597235.41</v>
+        <v>265597871.71</v>
       </c>
       <c r="R29" s="13" t="n">
         <v>0.2711837542671093</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>1383853189.28</v>
+        <v>1383854919.42</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>97591814.65000001</v>
@@ -2244,10 +2244,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>1576689673.35</v>
+        <v>1576691403.49</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>261337732.09</v>
+        <v>261338260.77</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>30161405.65</v>
@@ -2259,16 +2259,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>3726730</v>
+        <v>3726732.12</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>4002090.25</v>
+        <v>4002092.52</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>319908270.97</v>
+        <v>319908804.05</v>
       </c>
       <c r="R30" s="13" t="n">
         <v>0.3089090135319407</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>1727303217.17</v>
+        <v>1727304757.71</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>164444551.54</v>
@@ -2302,10 +2302,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>2027359883.2</v>
+        <v>2027361423.74</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>296355693.73</v>
+        <v>296356558.27</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>46737225.01</v>
@@ -2317,16 +2317,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>3587887.87</v>
+        <v>3587893.31</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>5274100.81</v>
+        <v>5274108.8</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>386042871.27</v>
+        <v>386043749.23</v>
       </c>
       <c r="R31" s="13" t="n">
         <v>0.3202852257171364</v>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>1572732698.76</v>
+        <v>1572733613.27</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>152797571.95</v>
@@ -2360,10 +2360,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>1832495782.88</v>
+        <v>1832496697.39</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>293611128.13</v>
+        <v>293611516.58</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>45961937.88</v>
@@ -2375,16 +2375,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>2694891.63</v>
+        <v>2694893.14</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>6570280.04</v>
+        <v>6570283.7</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>372627664.33</v>
+        <v>372628057.94</v>
       </c>
       <c r="R32" s="13" t="n">
         <v>0.3068596818867773</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>1305397293.87</v>
+        <v>1305397812.21</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>112904481.21</v>
@@ -2418,10 +2418,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>1491438319.98</v>
+        <v>1491438838.32</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>251862125.19</v>
+        <v>251862289.97</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>36710222.03</v>
@@ -2433,16 +2433,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1463494.44</v>
+        <v>1463494.72</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>6347098.2</v>
+        <v>6347099.4</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>309527609.36</v>
+        <v>309527775.62</v>
       </c>
       <c r="R33" s="13" t="n">
         <v>0.2945849325840212</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>1368373799.62</v>
+        <v>1368375339.29</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>111143043.36</v>
@@ -2476,10 +2476,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>1592264923.6</v>
+        <v>1592266463.27</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>248807408.73</v>
+        <v>248807952.13</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>33583851.98</v>
@@ -2491,16 +2491,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1142562</v>
+        <v>1142562.89</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>8125260.65</v>
+        <v>8125266.98</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>315335607.07</v>
+        <v>315336157.69</v>
       </c>
       <c r="R34" s="13" t="n">
         <v>0.3414174701179286</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>1428048707.96</v>
+        <v>1428051682</v>
       </c>
       <c r="C35" s="9" t="n">
         <v>132482297.68</v>
@@ -2534,10 +2534,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>1671705719.63</v>
+        <v>1671708693.67</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>263141611.94</v>
+        <v>263142566.91</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>39009607.96</v>
@@ -2549,16 +2549,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1891013.44</v>
+        <v>1891015.49</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>5945577.63</v>
+        <v>5945584.08</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>336442606.83</v>
+        <v>336443570.3</v>
       </c>
       <c r="R35" s="13" t="n">
         <v>0.3444918130280069</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>1456212603.34</v>
+        <v>1456214318.01</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>147816672.25</v>
@@ -2592,10 +2592,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>1723552894.21</v>
+        <v>1723554608.88</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>282237551.49</v>
+        <v>282237847.46</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>47162206.4</v>
@@ -2607,16 +2607,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>2226974.92</v>
+        <v>2226974.47</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>6426279.52</v>
+        <v>6426278.25</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>369372890.61</v>
+        <v>369373184.86</v>
       </c>
       <c r="R36" s="13" t="n">
         <v>0.3000842795719814</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>1613190917.55</v>
+        <v>1613194101.81</v>
       </c>
       <c r="C37" s="9" t="n">
         <v>161563899.02</v>
@@ -2650,10 +2650,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>1887511067.32</v>
+        <v>1887514251.58</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>289613127.27</v>
+        <v>289614305.49</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>49969404.96</v>
@@ -2665,16 +2665,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2038735.08</v>
+        <v>2038738.18</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>7146309.54</v>
+        <v>7146320.4</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>371789080.33</v>
+        <v>371790272.51</v>
       </c>
       <c r="R37" s="13" t="n">
         <v>0.3158320949670745</v>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>2119627585.85</v>
+        <v>2119628604.63</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>172439724.32</v>
@@ -2708,10 +2708,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>2463690677.06</v>
+        <v>2463691695.84</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>378507471.37</v>
+        <v>378507754.92</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>46814572.08</v>
@@ -2723,16 +2723,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>3468833.15</v>
+        <v>3468833.79</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>5883477.03</v>
+        <v>5883478.11</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>478312561.72</v>
+        <v>478312846.98</v>
       </c>
       <c r="R38" s="13" t="n">
         <v>0.3730201312691256</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>1628367827.22</v>
+        <v>1628369842.15</v>
       </c>
       <c r="C39" s="9" t="n">
         <v>131412975.25</v>
@@ -2766,10 +2766,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>1915137613.82</v>
+        <v>1915139628.75</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>294598352.82</v>
+        <v>294598802.65</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>38038258.86</v>
@@ -2781,16 +2781,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>4346484.97</v>
+        <v>4346485.51</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>6499222.39</v>
+        <v>6499223.19</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>384071849.86</v>
+        <v>384072301.02</v>
       </c>
       <c r="R39" s="13" t="n">
         <v>0.3654745795652588</v>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>1241351285.48</v>
+        <v>1241352326.93</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>184349276.32</v>
@@ -2824,10 +2824,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>1550728951.27</v>
+        <v>1550729992.72</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>227092283.63</v>
+        <v>227092584.15</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>52663679.72</v>
@@ -2839,16 +2839,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>3230020.35</v>
+        <v>3230021.19</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>4087117.75</v>
+        <v>4087118.82</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>324538441.44</v>
+        <v>324538743.87</v>
       </c>
       <c r="R40" s="13" t="n">
         <v>0.3156021020167954</v>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>1377185820.93</v>
+        <v>1377187834</v>
       </c>
       <c r="C41" s="9" t="n">
         <v>155233923.84</v>
@@ -2882,10 +2882,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>1655668484.54</v>
+        <v>1655670497.61</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>238173101.15</v>
+        <v>238173667.92</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>45723994.53</v>
@@ -2897,16 +2897,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>2993004.27</v>
+        <v>2993005.93</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>4877198.67</v>
+        <v>4877201.37</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>322916490.49</v>
+        <v>322917061.61</v>
       </c>
       <c r="R41" s="13" t="n">
         <v>0.3586813700389345</v>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>1613729395.82</v>
+        <v>1613732093.25</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>202803340.18</v>
@@ -2940,10 +2940,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>1989303341.25</v>
+        <v>1989306038.68</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>282620294.98</v>
+        <v>282621363.68</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>59467977.05</v>
@@ -2955,16 +2955,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>2562080.88</v>
+        <v>2562084.31</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>6710404.7</v>
+        <v>6710413.67</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>401338254.69</v>
+        <v>401339335.79</v>
       </c>
       <c r="R42" s="13" t="n">
         <v>0.374804382581988</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>1427769414.83</v>
+        <v>1427769682.62</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>221859292.06</v>
@@ -2998,10 +2998,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>1817556571.38</v>
+        <v>1817556839.17</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>232864797.19</v>
+        <v>232864866.28</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>61180817.13</v>
@@ -3013,16 +3013,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>2342315.36</v>
+        <v>2342315.49</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>6388144.56</v>
+        <v>6388144.92</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>343667726.23</v>
+        <v>343667795.8</v>
       </c>
       <c r="R43" s="13" t="n">
         <v>0.373808055436679</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>1480857719.21</v>
+        <v>1480859068.44</v>
       </c>
       <c r="C44" s="9" t="n">
         <v>197999210.33</v>
@@ -3056,10 +3056,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>1838738752.31</v>
+        <v>1838740101.54</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>248377324.62</v>
+        <v>248377543.4</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>51757760.82</v>
@@ -3071,16 +3071,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>4638589.51</v>
+        <v>4638588.99</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>6177354.3</v>
+        <v>6177353.61</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>349805684.75</v>
+        <v>349805902.32</v>
       </c>
       <c r="R44" s="13" t="n">
         <v>0.3916154766095744</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>2194903494.81</v>
+        <v>2194912326.15</v>
       </c>
       <c r="C45" s="9" t="n">
         <v>306596858.33</v>
@@ -3114,10 +3114,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>2819810012.04</v>
+        <v>2819818843.38</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>400044786.19</v>
+        <v>400046324.34</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>76961510.28</v>
@@ -3129,16 +3129,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>9471743.35</v>
+        <v>9471739.029999999</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>16166271.51</v>
+        <v>16166264.13</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>570543010.1799999</v>
+        <v>570544536.63</v>
       </c>
       <c r="R45" s="13" t="n">
         <v>0.4006796632230236</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>2305305174.13</v>
+        <v>2305308624.95</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>376108161.46</v>
@@ -3172,10 +3172,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>3105825641.28</v>
+        <v>3105829092.1</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>402171072.7</v>
+        <v>402172569.81</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>102191987.48</v>
@@ -3187,16 +3187,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>10742350.51</v>
+        <v>10742365.2</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>19778578.79</v>
+        <v>19778605.83</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>620963981.5599999</v>
+        <v>620965520.4</v>
       </c>
       <c r="R46" s="13" t="n">
         <v>0.442865097926909</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>1370776453.14</v>
+        <v>1370778519.76</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>250093696.52</v>
@@ -3230,10 +3230,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>1802394665.67</v>
+        <v>1802396732.29</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>227517050.14</v>
+        <v>227518110.47</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>65852392.81</v>
@@ -3245,16 +3245,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>3449583.55</v>
+        <v>3449590.27</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>4879518.28</v>
+        <v>4879527.79</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>347856476.26</v>
+        <v>347857552.82</v>
       </c>
       <c r="R47" s="13" t="n">
         <v>0.4207679702437824</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>1605881206.51</v>
+        <v>1605884435.15</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>251713084.28</v>
@@ -3288,10 +3288,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>2004203575.05</v>
+        <v>2004206803.69</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>256674056.92</v>
+        <v>256675473</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>62840730.8</v>
@@ -3303,16 +3303,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>4066688.93</v>
+        <v>4066698.51</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>5303373.55</v>
+        <v>5303386.05</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>362466972.75</v>
+        <v>362468410.91</v>
       </c>
       <c r="R48" s="13" t="n">
         <v>0.4544083188194561</v>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>1642734154.13</v>
+        <v>1642735755.29</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>255216837.43</v>
@@ -3346,10 +3346,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>2063086989.96</v>
+        <v>2063088591.12</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>257258915.45</v>
+        <v>257259436.56</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>63158844.13</v>
@@ -3361,16 +3361,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>4712196.99</v>
+        <v>4712200.1</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>5445768.07</v>
+        <v>5445771.66</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>367431196.83</v>
+        <v>367431724.65</v>
       </c>
       <c r="R49" s="13" t="n">
         <v>0.4715622688002217</v>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>1539536354.08</v>
+        <v>1539540787.28</v>
       </c>
       <c r="C50" s="9" t="n">
         <v>251070477.59</v>
@@ -3404,10 +3404,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>1989426531.83</v>
+        <v>1989430965.03</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>263416069.75</v>
+        <v>263417937.47</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>57612870.57</v>
@@ -3419,16 +3419,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>4620004.58</v>
+        <v>4620017.62</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>5904456.95</v>
+        <v>5904473.6</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>375782547.3</v>
+        <v>375784444.71</v>
       </c>
       <c r="R50" s="13" t="n">
         <v>0.5184969295746537</v>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>1765234997.97</v>
+        <v>1765237511.48</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>287468135.92</v>
@@ -3462,10 +3462,10 @@
         <v>28011807</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>2267517399.4</v>
+        <v>2267519912.91</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>281272806.25</v>
+        <v>281273971.44</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>59780017.61</v>
@@ -3477,16 +3477,16 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>5175425.81</v>
+        <v>5175435.65</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>7388626.03</v>
+        <v>7388640.08</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>13969238.87</v>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>395117366.33</v>
+        <v>395118555.41</v>
       </c>
       <c r="R51" s="13" t="n">
         <v>0.5173698555705437</v>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>2536981423.09</v>
+        <v>2536994712.59</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>438830798.95</v>
@@ -3520,10 +3520,10 @@
         <v>20465067</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>3325951321.15</v>
+        <v>3325964610.65</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>439530027.01</v>
+        <v>439535999</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>92879457.39</v>
@@ -3535,16 +3535,16 @@
         <v>15738266.69</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>7898080.48</v>
+        <v>7898127.56</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>23430090.98</v>
+        <v>23430230.63</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>10232009.27</v>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>618574442.29</v>
+        <v>618580601.01</v>
       </c>
       <c r="R52" s="13" t="n">
         <v>0.4928123695831447</v>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>2708733441.6</v>
+        <v>2708842734.56</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>590872240.37</v>
@@ -3578,10 +3578,10 @@
         <v>67156727</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>3868375695.63</v>
+        <v>3868484988.59</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>422579475.21</v>
+        <v>422626460.96</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>126606680.82</v>
@@ -3593,16 +3593,16 @@
         <v>34860196.13</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>8426870.4</v>
+        <v>8427236.539999999</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>31894176.62</v>
+        <v>31895562.4</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>33049467.84</v>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>679710003.5599999</v>
+        <v>679758741.23</v>
       </c>
       <c r="R53" s="13" t="n">
         <v>0.516687833119383</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>1283735583.29</v>
+        <v>1283918446.65</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>284348309.59</v>
@@ -3636,10 +3636,10 @@
         <v>57503053</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>1757676023.64</v>
+        <v>1757858887</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>214204504.66</v>
+        <v>214282784.22</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>74184906.98999999</v>
@@ -3651,16 +3651,16 @@
         <v>11903181.4</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1457379.96</v>
+        <v>1457560.58</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>6860536.57</v>
+        <v>6861386.8</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>28258572.47</v>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>347882810.64</v>
+        <v>347962121.04</v>
       </c>
       <c r="R54" s="13" t="n">
         <v>0.4317620090381182</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>1535588631.95</v>
+        <v>1535864084.85</v>
       </c>
       <c r="C55" s="9" t="n">
         <v>305249223.57</v>
@@ -3694,10 +3694,10 @@
         <v>29175511</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>1997666118.28</v>
+        <v>1997941571.18</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>255313286.41</v>
+        <v>255430233.77</v>
       </c>
       <c r="K55" s="12" t="n">
         <v>60959047.28</v>
@@ -3709,16 +3709,16 @@
         <v>8988100.75</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>2863043.22</v>
+        <v>2863596.19</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>5822126.18</v>
+        <v>5823250.66</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>13247763.43</v>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>358325633.73</v>
+        <v>358444258.53</v>
       </c>
       <c r="R55" s="13" t="n">
         <v>0.5085823534173731</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>1512773796.63</v>
+        <v>1513097400.13</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>295641521.04</v>
@@ -3752,10 +3752,10 @@
         <v>26518877</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>1968151776.65</v>
+        <v>1968475380.15</v>
       </c>
       <c r="J56" s="11" t="n">
-        <v>239242977.1</v>
+        <v>239381356</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>65905215.47</v>
@@ -3767,16 +3767,16 @@
         <v>10595274.38</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>2795550.3</v>
+        <v>2796215.42</v>
       </c>
       <c r="O56" s="12" t="n">
-        <v>5427542.54</v>
+        <v>5428833.87</v>
       </c>
       <c r="P56" s="12" t="n">
         <v>13188992.45</v>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>348762069.02</v>
+        <v>348902404.38</v>
       </c>
       <c r="R56" s="13" t="n">
         <v>0.5057931637222076</v>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>1710113978.33</v>
+        <v>1710538291.44</v>
       </c>
       <c r="C57" s="9" t="n">
         <v>307512657.17</v>
@@ -3810,10 +3810,10 @@
         <v>27882416</v>
       </c>
       <c r="I57" s="10" t="n">
-        <v>2227711260.33</v>
+        <v>2228135573.44</v>
       </c>
       <c r="J57" s="11" t="n">
-        <v>280098666.51</v>
+        <v>280271339.54</v>
       </c>
       <c r="K57" s="12" t="n">
         <v>59383053.97</v>
@@ -3825,16 +3825,16 @@
         <v>15136999.32</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>3155789.83</v>
+        <v>3156594.54</v>
       </c>
       <c r="O57" s="12" t="n">
-        <v>6277137.26</v>
+        <v>6278737.89</v>
       </c>
       <c r="P57" s="12" t="n">
         <v>14538750.58</v>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>392980804.3</v>
+        <v>393155882.67</v>
       </c>
       <c r="R57" s="13" t="n">
         <v>0.5643242205108819</v>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>1665920736.64</v>
+        <v>1669847493.13</v>
       </c>
       <c r="C58" s="9" t="n">
         <v>360408853.21</v>
@@ -3868,10 +3868,10 @@
         <v>38681934</v>
       </c>
       <c r="I58" s="10" t="n">
-        <v>2263784266.24</v>
+        <v>2267711022.73</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>272476635.13</v>
+        <v>273081236.1</v>
       </c>
       <c r="K58" s="12" t="n">
         <v>71309977.62</v>
@@ -3883,23 +3883,81 @@
         <v>15006248.84</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>4491345.03</v>
+        <v>4490144.69</v>
       </c>
       <c r="O58" s="12" t="n">
-        <v>9428231.439999999</v>
+        <v>9425711.689999999</v>
       </c>
       <c r="P58" s="12" t="n">
         <v>19224841.85</v>
       </c>
       <c r="Q58" s="12" t="n">
-        <v>409632178.3</v>
+        <v>410233059.18</v>
       </c>
       <c r="R58" s="13" t="n">
         <v>0.5560789475916204</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>2349332801.23</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>470702992.36</v>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>90645710.43000001</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>137323871</v>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>52115164.6</v>
+      </c>
+      <c r="G59" s="9" t="n">
+        <v>127461751</v>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>20443443</v>
+      </c>
+      <c r="I59" s="10" t="n">
+        <v>3248025733.62</v>
+      </c>
+      <c r="J59" s="11" t="n">
+        <v>376772420.49</v>
+      </c>
+      <c r="K59" s="12" t="n">
+        <v>82082024.87</v>
+      </c>
+      <c r="L59" s="12" t="n">
+        <v>28532332.02</v>
+      </c>
+      <c r="M59" s="12" t="n">
+        <v>33934101.63</v>
+      </c>
+      <c r="N59" s="12" t="n">
+        <v>9030969.970000001</v>
+      </c>
+      <c r="O59" s="12" t="n">
+        <v>22087683.21</v>
+      </c>
+      <c r="P59" s="12" t="n">
+        <v>10406677.63</v>
+      </c>
+      <c r="Q59" s="12" t="n">
+        <v>562846209.8200001</v>
+      </c>
+      <c r="R59" s="13" t="n">
+        <v>0.52815090628141</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R58"/>
+  <autoFilter ref="A2:R59"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3915,7 +3973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7056,7 +7114,7 @@
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>1932135780.79</v>
+        <v>1936461735.07</v>
       </c>
       <c r="C58" s="9" t="n">
         <v>373857348.69</v>
@@ -7077,10 +7135,10 @@
         <v>39460452</v>
       </c>
       <c r="I58" s="10" t="n">
-        <v>2548499492.87</v>
+        <v>2552825447.15</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>387006796.89</v>
+        <v>387873285.53</v>
       </c>
       <c r="K58" s="12" t="n">
         <v>76475302.37</v>
@@ -7092,20 +7150,75 @@
         <v>15006248.84</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>5188299.08</v>
+        <v>5187919.85</v>
       </c>
       <c r="O58" s="12" t="n">
-        <v>11784495.81</v>
+        <v>11783634.44</v>
       </c>
       <c r="P58" s="12" t="n">
         <v>19555570.12</v>
       </c>
       <c r="Q58" s="12" t="n">
-        <v>532711611.51</v>
+        <v>533576859.54</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>2724436268.13</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>486438716.83</v>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>90645710.43000001</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>137323871</v>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>52115164.6</v>
+      </c>
+      <c r="G59" s="9" t="n">
+        <v>131571145</v>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>20822242</v>
+      </c>
+      <c r="I59" s="10" t="n">
+        <v>3643353117.99</v>
+      </c>
+      <c r="J59" s="11" t="n">
+        <v>545704584.51</v>
+      </c>
+      <c r="K59" s="12" t="n">
+        <v>88438958.8</v>
+      </c>
+      <c r="L59" s="12" t="n">
+        <v>28532332.02</v>
+      </c>
+      <c r="M59" s="12" t="n">
+        <v>33934101.63</v>
+      </c>
+      <c r="N59" s="12" t="n">
+        <v>10651651.36</v>
+      </c>
+      <c r="O59" s="12" t="n">
+        <v>26891404.37</v>
+      </c>
+      <c r="P59" s="12" t="n">
+        <v>10500226.58</v>
+      </c>
+      <c r="Q59" s="12" t="n">
+        <v>744653259.26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q58"/>
+  <autoFilter ref="A2:Q59"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -7120,7 +7233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9423,7 +9536,7 @@
         <v>11731471</v>
       </c>
       <c r="H54" s="14" t="n">
-        <v>0.7120000000000001</v>
+        <v>0.7119</v>
       </c>
       <c r="I54" s="14" t="n">
         <v>0.4394</v>
@@ -9466,7 +9579,7 @@
         <v>11228218</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>0.7389</v>
+        <v>0.7387999999999999</v>
       </c>
       <c r="I55" s="14" t="n">
         <v>0.4565</v>
@@ -9509,7 +9622,7 @@
         <v>12075182</v>
       </c>
       <c r="H56" s="14" t="n">
-        <v>0.7543000000000001</v>
+        <v>0.7541</v>
       </c>
       <c r="I56" s="14" t="n">
         <v>0.4471</v>
@@ -9552,7 +9665,7 @@
         <v>14205984</v>
       </c>
       <c r="H57" s="14" t="n">
-        <v>0.7336</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="I57" s="14" t="n">
         <v>0.4183</v>
@@ -9577,7 +9690,7 @@
         </is>
       </c>
       <c r="B58" s="9" t="n">
-        <v>1218018396.21</v>
+        <v>1220745477.79</v>
       </c>
       <c r="C58" s="9" t="n">
         <v>23632292.97</v>
@@ -9613,15 +9726,58 @@
         <v>0.3488</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="15" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>1717484623.43</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>36857669.38</v>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>81078999</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>269760987.47</v>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>49593779.55</v>
+      </c>
+      <c r="G59" s="9" t="n">
+        <v>26557480</v>
+      </c>
+      <c r="H59" s="14" t="n">
+        <v>0.7311</v>
+      </c>
+      <c r="I59" s="14" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v>0.5904</v>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v>0.5731000000000001</v>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v>0.9516</v>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v>0.2084</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~5M-trade sample (refreshed weekly) scaled to the daily total; ~70% of Kalshi's sports book by contracts, ~24% by $ (parlay legs are many and cheap - this sample-based split can move noticeably week to week, see VOLUME_METHODOLOGY.md). Not folded into the Sports tab's blended Combo %. Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M58"/>
+  <autoFilter ref="A2:M59"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -9654,7 +9810,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-26. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-27. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9869,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-26: independently recomputed totals matched the committed figures exactly</t>
+          <t>2026-09-27: independently recomputed totals matched the committed figures exactly</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sports volume'!$A$2:$R$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Total exchange'!$A$2:$Q$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Parlay share'!$A$2:$M$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>1436295792.28</v>
+        <v>1436296608.54</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>133399888.66</v>
@@ -688,10 +688,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>1614257886.86</v>
+        <v>1614258703.12</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>299227977.2</v>
+        <v>299228267.62</v>
       </c>
       <c r="K3" s="12" t="n">
         <v>50986272.22</v>
@@ -701,16 +701,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>466111.4</v>
+        <v>466111.54</v>
       </c>
       <c r="O3" s="12" t="n">
-        <v>8313317.18</v>
+        <v>8313319.71</v>
       </c>
       <c r="P3" s="12" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="12" t="n">
-        <v>361465312.4</v>
+        <v>361465605.5</v>
       </c>
       <c r="R3" s="13" t="n">
         <v>0.08714584215412201</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>1205572764.67</v>
+        <v>1205574861.38</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>134065934.54</v>
@@ -742,10 +742,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>1388977674.18</v>
+        <v>1388979770.89</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>231812487.87</v>
+        <v>231812830.09</v>
       </c>
       <c r="K4" s="12" t="n">
         <v>51144509.72</v>
@@ -755,16 +755,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>458019.1</v>
+        <v>458018.94</v>
       </c>
       <c r="O4" s="12" t="n">
-        <v>8194673.91</v>
+        <v>8194670.93</v>
       </c>
       <c r="P4" s="12" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="12" t="n">
-        <v>296023286.66</v>
+        <v>296023625.73</v>
       </c>
       <c r="R4" s="13" t="n">
         <v>0.07635377691307524</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>889409108.64</v>
+        <v>889409896.5700001</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>85344135.09999999</v>
@@ -796,10 +796,10 @@
         <v>9061437</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>1005451655.68</v>
+        <v>1005452443.61</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>202393699.12</v>
+        <v>202393986.66</v>
       </c>
       <c r="K5" s="12" t="n">
         <v>31777180.84</v>
@@ -809,16 +809,16 @@
         <v>165403.4</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>334881.02</v>
+        <v>334881.15</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>4825440.96</v>
+        <v>4825442.91</v>
       </c>
       <c r="P5" s="12" t="n">
         <v>4372698.14</v>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>243869303.48</v>
+        <v>243869593.1</v>
       </c>
       <c r="R5" s="13" t="n">
         <v>0.05231046649197771</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1155125148.83</v>
+        <v>1155126136.17</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>120394335.41</v>
@@ -852,10 +852,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>1339763297.85</v>
+        <v>1339764285.19</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>243084633.11</v>
+        <v>243084975.15</v>
       </c>
       <c r="K6" s="12" t="n">
         <v>47471997.74</v>
@@ -867,16 +867,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>288784.93</v>
+        <v>288785.03</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>6546861.75</v>
+        <v>6546864.16</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>312033864.36</v>
+        <v>312034208.91</v>
       </c>
       <c r="R6" s="13" t="n">
         <v>0.1040882840699126</v>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1292328358.91</v>
+        <v>1292332471.96</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>125055737.8</v>
@@ -910,10 +910,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>1497408396.49</v>
+        <v>1497412509.54</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>259386991.34</v>
+        <v>259388974.55</v>
       </c>
       <c r="K7" s="12" t="n">
         <v>47948549.82</v>
@@ -925,16 +925,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>631739.88</v>
+        <v>631741.9300000001</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>6846051.85</v>
+        <v>6846074</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>335565514.33</v>
+        <v>335567521.74</v>
       </c>
       <c r="R7" s="13" t="n">
         <v>0.1036604405692761</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1187474069.69</v>
+        <v>1187476681.79</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>141146850.05</v>
@@ -968,10 +968,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>1409647189.2</v>
+        <v>1409649801.3</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>236785600.64</v>
+        <v>236786492.22</v>
       </c>
       <c r="K8" s="12" t="n">
         <v>50551741.94</v>
@@ -983,16 +983,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>1121125.74</v>
+        <v>1121126.86</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>7508192.98</v>
+        <v>7508200.49</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>315424376.01</v>
+        <v>315425276.23</v>
       </c>
       <c r="R8" s="13" t="n">
         <v>0.09320593928966855</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1139475798.9</v>
+        <v>1139507899.4</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>117925601.54</v>
@@ -1026,10 +1026,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>1323082960.44</v>
+        <v>1323115060.94</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>224392735.83</v>
+        <v>224409184.84</v>
       </c>
       <c r="K9" s="12" t="n">
         <v>44939973.52</v>
@@ -1041,16 +1041,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>727221.34</v>
+        <v>727245.53</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>6114375.72</v>
+        <v>6114579.11</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>289886178.08</v>
+        <v>289902854.68</v>
       </c>
       <c r="R9" s="13" t="n">
         <v>0.100308786205459</v>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1265087780.96</v>
+        <v>1265100760.99</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>119094679.49</v>
@@ -1084,10 +1084,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1469753678.44</v>
+        <v>1469766658.47</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>247904802.27</v>
+        <v>247911615.74</v>
       </c>
       <c r="K10" s="12" t="n">
         <v>44015511.37</v>
@@ -1099,16 +1099,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>2089369.66</v>
+        <v>2089396.38</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>6720638.65</v>
+        <v>6720724.56</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>320415288.46</v>
+        <v>320422214.56</v>
       </c>
       <c r="R10" s="13" t="n">
         <v>0.1305164739611011</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>1136159801.99</v>
+        <v>1136186134.46</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>126075255.12</v>
@@ -1142,10 +1142,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1360833119.11</v>
+        <v>1360859451.58</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>220225203.26</v>
+        <v>220239170.28</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>48533344.05</v>
@@ -1157,16 +1157,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2216235.51</v>
+        <v>2216296.98</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>7947064.34</v>
+        <v>7947284.77</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>302603843.81</v>
+        <v>302618092.73</v>
       </c>
       <c r="R11" s="13" t="n">
         <v>0.1174147553025735</v>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>817339664.7</v>
+        <v>817343221.84</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>76773291.01000001</v>
@@ -1200,10 +1200,10 @@
         <v>11323712</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>944251355.73</v>
+        <v>944254912.87</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>157386020.55</v>
+        <v>157387106.03</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>28141958.88</v>
@@ -1215,16 +1215,16 @@
         <v>146839.93</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>1682385.71</v>
+        <v>1682388.48</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>3091092.08</v>
+        <v>3091097.16</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>5809820.01</v>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>202041458.24</v>
+        <v>202042551.57</v>
       </c>
       <c r="R12" s="13" t="n">
         <v>0.1320471995718654</v>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>1149012874.56</v>
+        <v>1149014388.96</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>86060025.34</v>
@@ -1258,10 +1258,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>1308569528.8</v>
+        <v>1308571043.2</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>235935409.08</v>
+        <v>235935835.7</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>32573678.23</v>
@@ -1273,16 +1273,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2341917.23</v>
+        <v>2341917.94</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>4886883.79</v>
+        <v>4886885.27</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>294006758.56</v>
+        <v>294007187.35</v>
       </c>
       <c r="R13" s="13" t="n">
         <v>0.1581581529884586</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>1239523834.71</v>
+        <v>1239561801.33</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>114182203.82</v>
@@ -1316,10 +1316,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>1441008024.78</v>
+        <v>1441045991.4</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>240227831.74</v>
+        <v>240248616.98</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>44020201.24</v>
@@ -1331,16 +1331,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2540875.62</v>
+        <v>2540979.82</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>6229748.25</v>
+        <v>6230003.74</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>313911527.05</v>
+        <v>313932671.99</v>
       </c>
       <c r="R14" s="13" t="n">
         <v>0.1369006174109096</v>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>1228244144.28</v>
+        <v>1228257030</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>130618679.53</v>
@@ -1374,10 +1374,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>1450291244.09</v>
+        <v>1450304129.81</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>245769708.98</v>
+        <v>245776338.47</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>47519466.33</v>
@@ -1389,16 +1389,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3332878.74</v>
+        <v>3332919.04</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>6989331.23</v>
+        <v>6989415.74</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>321982655.74</v>
+        <v>321989410.05</v>
       </c>
       <c r="R15" s="13" t="n">
         <v>0.1338434618903201</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>1206699121.9</v>
+        <v>1206704453.72</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>122512075.89</v>
@@ -1432,10 +1432,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>1408843000.93</v>
+        <v>1408848332.75</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>254179037.12</v>
+        <v>254182820.52</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>44967846.15</v>
@@ -1447,16 +1447,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>3170561.97</v>
+        <v>3170587.98</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>6715343.88</v>
+        <v>6715398.97</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>322388997.14</v>
+        <v>322392861.63</v>
       </c>
       <c r="R16" s="13" t="n">
         <v>0.1467243571212392</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1502787686.94</v>
+        <v>1502791049.02</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>135215397.14</v>
@@ -1490,10 +1490,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>1745509164.19</v>
+        <v>1745512526.27</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>307041600.92</v>
+        <v>307043241.84</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>48968794.7</v>
@@ -1505,16 +1505,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>3811148.35</v>
+        <v>3811157.38</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>8549327.289999999</v>
+        <v>8549347.57</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>388646072.44</v>
+        <v>388647742.67</v>
       </c>
       <c r="R17" s="13" t="n">
         <v>0.1671310595982739</v>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>1333527779.09</v>
+        <v>1333531452.65</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>146617403.12</v>
@@ -1548,10 +1548,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>1585702940.42</v>
+        <v>1585706613.98</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>261227786.79</v>
+        <v>261229831.82</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>56978627.74</v>
@@ -1563,16 +1563,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>3122215.2</v>
+        <v>3122226.7</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>9982359.109999999</v>
+        <v>9982395.9</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>348775317.94</v>
+        <v>348777411.26</v>
       </c>
       <c r="R18" s="13" t="n">
         <v>0.1404248555660547</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>918412109.84</v>
+        <v>918415716.47</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>100434174.96</v>
@@ -1606,10 +1606,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>1079828955.37</v>
+        <v>1079832562</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>188477360.65</v>
+        <v>188478240.81</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>36933011.94</v>
@@ -1621,16 +1621,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2573286.99</v>
+        <v>2573287.65</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>4428367.54</v>
+        <v>4428368.69</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>245090858.11</v>
+        <v>245091740.08</v>
       </c>
       <c r="R19" s="13" t="n">
         <v>0.1248997633733931</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>1097890036.06</v>
+        <v>1097891897.95</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>104121932.82</v>
@@ -1664,10 +1664,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>1275893419.88</v>
+        <v>1275895281.77</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>215919005.71</v>
+        <v>215920037.01</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>38002578.37</v>
@@ -1679,16 +1679,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2738070.46</v>
+        <v>2738076.86</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>5494140.6</v>
+        <v>5494153.45</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>276651726.78</v>
+        <v>276652777.33</v>
       </c>
       <c r="R20" s="13" t="n">
         <v>0.178213812300984</v>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>1303189628.44</v>
+        <v>1303192514.01</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>122677612.96</v>
@@ -1722,10 +1722,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>1518489922.26</v>
+        <v>1518492807.83</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>252865351.51</v>
+        <v>252866845.84</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>44708007.56</v>
@@ -1737,16 +1737,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>3247082.24</v>
+        <v>3247091.21</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>6819804.71</v>
+        <v>6819823.55</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>326404659.15</v>
+        <v>326406181.3</v>
       </c>
       <c r="R21" s="13" t="n">
         <v>0.2003579150386557</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>1144728531.05</v>
+        <v>1144731478.31</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>132905659.86</v>
@@ -1780,10 +1780,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>1368049536.63</v>
+        <v>1368052483.89</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>217697987.56</v>
+        <v>217699072.82</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>44439935.08</v>
@@ -1795,16 +1795,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>2916882.89</v>
+        <v>2916887.69</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>6698307.51</v>
+        <v>6698318.53</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>11601612.35</v>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>289778058.63</v>
+        <v>289779159.71</v>
       </c>
       <c r="R22" s="13" t="n">
         <v>0.180964978836361</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>1190740925.2</v>
+        <v>1190742685.65</v>
       </c>
       <c r="C23" s="9" t="n">
         <v>118302722.67</v>
@@ -1838,10 +1838,10 @@
         <v>9456461</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>1385897613.26</v>
+        <v>1385899373.71</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>229730310.82</v>
+        <v>229731063.86</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>35142057.4</v>
@@ -1853,16 +1853,16 @@
         <v>577229.27</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>3441499.5</v>
+        <v>3441504.29</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>5603933.15</v>
+        <v>5603940.96</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>3594255.85</v>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>287480238.4</v>
+        <v>287481004.04</v>
       </c>
       <c r="R23" s="13" t="n">
         <v>0.316619068118602</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>1612360798.46</v>
+        <v>1612364188</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>146513108.49</v>
@@ -1896,10 +1896,10 @@
         <v>21014051</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>1884577553.58</v>
+        <v>1884580943.12</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>316889282.95</v>
+        <v>316890022.54</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>43271898.85</v>
@@ -1911,16 +1911,16 @@
         <v>545961.96</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>5435377.67</v>
+        <v>5435378.05</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>9097149.02</v>
+        <v>9097149.66</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>9618578.710000001</v>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>396273941.14</v>
+        <v>396274681.76</v>
       </c>
       <c r="R24" s="13" t="n">
         <v>0.3069045894333504</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>1377200237.42</v>
+        <v>1377204127.54</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>144797057.56</v>
@@ -1954,10 +1954,10 @@
         <v>21174047</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>1629700205.07</v>
+        <v>1629704095.19</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>256709764.62</v>
+        <v>256710518.8</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>45249277.15</v>
@@ -1969,16 +1969,16 @@
         <v>678289.72</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>3355922.33</v>
+        <v>3355921.9</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>8780025.48</v>
+        <v>8780024.35</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>10104181.45</v>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>333318937.21</v>
+        <v>333319689.83</v>
       </c>
       <c r="R25" s="13" t="n">
         <v>0.2790295913221863</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>1037100841.91</v>
+        <v>1037106357.48</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>97537800.47</v>
@@ -2012,10 +2012,10 @@
         <v>11503296</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>1206205054.28</v>
+        <v>1206210569.85</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>200202872.35</v>
+        <v>200204990.8</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>31464287.45</v>
@@ -2027,16 +2027,16 @@
         <v>240533.84</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2871149.39</v>
+        <v>2871160.85</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>5012250.14</v>
+        <v>5012270.16</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>5132563.13</v>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>250988083.51</v>
+        <v>250990233.44</v>
       </c>
       <c r="R26" s="13" t="n">
         <v>0.2509415863550032</v>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>1198845133.86</v>
+        <v>1198848502.39</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>122103455.85</v>
@@ -2070,10 +2070,10 @@
         <v>16332836</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>1406182541.82</v>
+        <v>1406185910.35</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>225001532.23</v>
+        <v>225002416.17</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>38650744.49</v>
@@ -2085,16 +2085,16 @@
         <v>345067.73</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>2585286.55</v>
+        <v>2585288.36</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>6112847.28</v>
+        <v>6112851.54</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>7469897.21</v>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>287800071.14</v>
+        <v>287800961.14</v>
       </c>
       <c r="R27" s="13" t="n">
         <v>0.2836514946154119</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>1317397401.7</v>
+        <v>1317399208.05</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>146265225.05</v>
@@ -2128,10 +2128,10 @@
         <v>22808657</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>1563252301.35</v>
+        <v>1563254107.7</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>251064654.32</v>
+        <v>251065348.5</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>47820263.66</v>
@@ -2143,16 +2143,16 @@
         <v>1170559.87</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2381324.17</v>
+        <v>2381326.5</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>7749015.73</v>
+        <v>7749023.3</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>10604681.86</v>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>330051473.22</v>
+        <v>330052177.3</v>
       </c>
       <c r="R28" s="13" t="n">
         <v>0.2603327878455701</v>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>1110056285</v>
+        <v>1110059016.52</v>
       </c>
       <c r="C29" s="9" t="n">
         <v>110832888.3</v>
@@ -2186,10 +2186,10 @@
         <v>22948569</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>1314004099.45</v>
+        <v>1314006830.97</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>203731801.93</v>
+        <v>203733115.18</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>33469362.8</v>
@@ -2201,16 +2201,16 @@
         <v>3504492.28</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2592792.33</v>
+        <v>2592800</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>5824936.09</v>
+        <v>5824953.33</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>9864047.33</v>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>265597871.71</v>
+        <v>265599209.87</v>
       </c>
       <c r="R29" s="13" t="n">
         <v>0.2711837542671093</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>1383854919.42</v>
+        <v>1383858654.76</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>97591814.65000001</v>
@@ -2244,10 +2244,10 @@
         <v>14181446</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>1576691403.49</v>
+        <v>1576695138.83</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>261338260.77</v>
+        <v>261340857.92</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>30161405.65</v>
@@ -2259,16 +2259,16 @@
         <v>5547393.25</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>3726732.12</v>
+        <v>3726754.08</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>4002092.52</v>
+        <v>4002116.1</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>5642292.92</v>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>319908804.05</v>
+        <v>319911446.73</v>
       </c>
       <c r="R30" s="13" t="n">
         <v>0.3089090135319407</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>1727304757.71</v>
+        <v>1727308138.95</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>164444551.54</v>
@@ -2302,10 +2302,10 @@
         <v>25879178</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>2027361423.74</v>
+        <v>2027364804.98</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>296356558.27</v>
+        <v>296357454.33</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>46737225.01</v>
@@ -2317,16 +2317,16 @@
         <v>10477277.08</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>3587893.31</v>
+        <v>3587895.7</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>5274108.8</v>
+        <v>5274112.33</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>11977848.09</v>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>386043749.23</v>
+        <v>386044651.22</v>
       </c>
       <c r="R31" s="13" t="n">
         <v>0.3202852257171364</v>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>1572733613.27</v>
+        <v>1572739280.16</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>152797571.95</v>
@@ -2360,10 +2360,10 @@
         <v>30594436</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>1832496697.39</v>
+        <v>1832502364.28</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>293611516.58</v>
+        <v>293613646.9</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>45961937.88</v>
@@ -2375,16 +2375,16 @@
         <v>1721674.99</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>2694893.14</v>
+        <v>2694900.39</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>6570283.7</v>
+        <v>6570301.39</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>14143642.2</v>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>372628057.94</v>
+        <v>372630213.2</v>
       </c>
       <c r="R32" s="13" t="n">
         <v>0.3068596818867773</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>1305397812.21</v>
+        <v>1305404155.84</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>112904481.21</v>
@@ -2418,10 +2418,10 @@
         <v>10653135</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>1491438838.32</v>
+        <v>1491445181.95</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>251862289.97</v>
+        <v>251865223.34</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>36710222.03</v>
@@ -2433,16 +2433,16 @@
         <v>7580.34</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1463494.72</v>
+        <v>1463502.56</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>6347099.4</v>
+        <v>6347133.41</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>4972134.8</v>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>309527775.62</v>
+        <v>309530750.85</v>
       </c>
       <c r="R33" s="13" t="n">
         <v>0.2945849325840212</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>1368375339.29</v>
+        <v>1368379960.81</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>111143043.36</v>
@@ -2476,10 +2476,10 @@
         <v>17975675</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>1592266463.27</v>
+        <v>1592271084.79</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>248807952.13</v>
+        <v>248809182.28</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>33583851.98</v>
@@ -2491,16 +2491,16 @@
         <v>7000711.88</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1142562.89</v>
+        <v>1142564.06</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>8125266.98</v>
+        <v>8125275.34</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>8253527.4</v>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>315336157.69</v>
+        <v>315337397.37</v>
       </c>
       <c r="R34" s="13" t="n">
         <v>0.3414174701179286</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>1428051682</v>
+        <v>1428055849.67</v>
       </c>
       <c r="C35" s="9" t="n">
         <v>132482297.68</v>
@@ -2534,10 +2534,10 @@
         <v>24222748</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>1671708693.67</v>
+        <v>1671712861.34</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>263142566.91</v>
+        <v>263143751.55</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>39009607.96</v>
@@ -2549,16 +2549,16 @@
         <v>7686788.4</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1891015.49</v>
+        <v>1891017.48</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>5945584.08</v>
+        <v>5945590.33</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>11819801.92</v>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>336443570.3</v>
+        <v>336444763.19</v>
       </c>
       <c r="R35" s="13" t="n">
         <v>0.3444918130280069</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>1456214318.01</v>
+        <v>1456218816.48</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>147816672.25</v>
@@ -2592,10 +2592,10 @@
         <v>27056266</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>1723554608.88</v>
+        <v>1723559107.35</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>282237847.46</v>
+        <v>282240802.83</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>47162206.4</v>
@@ -2607,16 +2607,16 @@
         <v>8799940.630000001</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>2226974.47</v>
+        <v>2226986.77</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>6426278.25</v>
+        <v>6426313.73</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>13258351.53</v>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>369373184.86</v>
+        <v>369376188</v>
       </c>
       <c r="R36" s="13" t="n">
         <v>0.3000842795719814</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>1613194101.81</v>
+        <v>1613198157.16</v>
       </c>
       <c r="C37" s="9" t="n">
         <v>161563899.02</v>
@@ -2650,10 +2650,10 @@
         <v>12713214</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>1887514251.58</v>
+        <v>1887518306.93</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>289614305.49</v>
+        <v>289616003.94</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>49969404.96</v>
@@ -2665,16 +2665,16 @@
         <v>7004156.33</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2038738.18</v>
+        <v>2038743.24</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>7146320.4</v>
+        <v>7146338.13</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>5644731.29</v>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>371790272.51</v>
+        <v>371791993.75</v>
       </c>
       <c r="R37" s="13" t="n">
         <v>0.3158320949670745</v>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>2119628604.63</v>
+        <v>2119633503.56</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>172439724.32</v>
@@ -2708,10 +2708,10 @@
         <v>20531449</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>2463691695.84</v>
+        <v>2463696594.77</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>378507754.92</v>
+        <v>378509198.02</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>46814572.08</v>
@@ -2723,16 +2723,16 @@
         <v>15883449.41</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>3468833.79</v>
+        <v>3468837.43</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>5883478.11</v>
+        <v>5883484.28</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>9731632.92</v>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>478312846.98</v>
+        <v>478314299.89</v>
       </c>
       <c r="R38" s="13" t="n">
         <v>0.3730201312691256</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>1628369842.15</v>
+        <v>1628372409.48</v>
       </c>
       <c r="C39" s="9" t="n">
         <v>131412975.25</v>
@@ -2766,10 +2766,10 @@
         <v>33293997</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>1915139628.75</v>
+        <v>1915142196.08</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>294598802.65</v>
+        <v>294599924.59</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>38038258.86</v>
@@ -2781,16 +2781,16 @@
         <v>11501420.69</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>4346485.51</v>
+        <v>4346492.58</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>6499223.19</v>
+        <v>6499233.76</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>16077465.82</v>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>384072301.02</v>
+        <v>384073440.6</v>
       </c>
       <c r="R39" s="13" t="n">
         <v>0.3654745795652588</v>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>1241352326.93</v>
+        <v>1241356784.44</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>184349276.32</v>
@@ -2824,10 +2824,10 @@
         <v>36648697</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>1550729992.72</v>
+        <v>1550734450.23</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>227092584.15</v>
+        <v>227094989.49</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>52663679.72</v>
@@ -2839,16 +2839,16 @@
         <v>8293832.56</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>3230021.19</v>
+        <v>3230036.18</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>4087118.82</v>
+        <v>4087137.79</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>18474805.77</v>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>324538743.87</v>
+        <v>324541183.17</v>
       </c>
       <c r="R40" s="13" t="n">
         <v>0.3156021020167954</v>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>1377187834</v>
+        <v>1377194732.21</v>
       </c>
       <c r="C41" s="9" t="n">
         <v>155233923.84</v>
@@ -2882,10 +2882,10 @@
         <v>35555460</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>1655670497.61</v>
+        <v>1655677395.82</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>238173667.92</v>
+        <v>238175771.74</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>45723994.53</v>
@@ -2897,16 +2897,16 @@
         <v>5234399.4</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>2993005.93</v>
+        <v>2993013.13</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>4877201.37</v>
+        <v>4877213.11</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>17014125.22</v>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>322917061.61</v>
+        <v>322919184.38</v>
       </c>
       <c r="R41" s="13" t="n">
         <v>0.3586813700389345</v>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>1613732093.25</v>
+        <v>1613742416.79</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>202803340.18</v>
@@ -2940,10 +2940,10 @@
         <v>55348498</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>1989306038.68</v>
+        <v>1989316362.22</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>282621363.68</v>
+        <v>282626477.96</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>59467977.05</v>
@@ -2955,16 +2955,16 @@
         <v>9926271.91</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>2562084.31</v>
+        <v>2562104.12</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>6710413.67</v>
+        <v>6710465.56</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>26671269.08</v>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>401339335.79</v>
+        <v>401344521.77</v>
       </c>
       <c r="R42" s="13" t="n">
         <v>0.374804382581988</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>1427769682.62</v>
+        <v>1427774475.26</v>
       </c>
       <c r="C43" s="9" t="n">
         <v>221859292.06</v>
@@ -2998,10 +2998,10 @@
         <v>48290841</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>1817556839.17</v>
+        <v>1817561631.81</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>232864866.28</v>
+        <v>232868177.22</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>61180817.13</v>
@@ -3013,16 +3013,16 @@
         <v>10508877.38</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>2342315.49</v>
+        <v>2342332.31</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>6388144.92</v>
+        <v>6388190.78</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>22302595.9</v>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>343667795.8</v>
+        <v>343671169.42</v>
       </c>
       <c r="R43" s="13" t="n">
         <v>0.373808055436679</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>1480859068.44</v>
+        <v>1480866077.45</v>
       </c>
       <c r="C44" s="9" t="n">
         <v>197999210.33</v>
@@ -3056,10 +3056,10 @@
         <v>37871164</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>1838740101.54</v>
+        <v>1838747110.55</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>248377543.4</v>
+        <v>248381276.77</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>51757760.82</v>
@@ -3071,16 +3071,16 @@
         <v>9720707.050000001</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>4638588.99</v>
+        <v>4638621.83</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>6177353.61</v>
+        <v>6177397.34</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>17584216.39</v>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>349805902.32</v>
+        <v>349809712.26</v>
       </c>
       <c r="R44" s="13" t="n">
         <v>0.3916154766095744</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>2194912326.15</v>
+        <v>2194917003.33</v>
       </c>
       <c r="C45" s="9" t="n">
         <v>306596858.33</v>
@@ -3114,10 +3114,10 @@
         <v>32146387</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>2819818843.38</v>
+        <v>2819823520.56</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>400046324.34</v>
+        <v>400047238.8</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>76961510.28</v>
@@ -3129,16 +3129,16 @@
         <v>28343613.08</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>9471739.029999999</v>
+        <v>9471738.470000001</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>16166264.13</v>
+        <v>16166263.18</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>15662019.12</v>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>570544536.63</v>
+        <v>570545449.59</v>
       </c>
       <c r="R45" s="13" t="n">
         <v>0.4006796632230236</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>2305308624.95</v>
+        <v>2305318227.24</v>
       </c>
       <c r="C46" s="9" t="n">
         <v>376108161.46</v>
@@ -3172,10 +3172,10 @@
         <v>64959415</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>3105829092.1</v>
+        <v>3105838694.39</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>402172569.81</v>
+        <v>402178371.6</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>102191987.48</v>
@@ -3187,16 +3187,16 @@
         <v>30010982.69</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>10742365.2</v>
+        <v>10742435.82</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>19778605.83</v>
+        <v>19778735.87</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>32697873.72</v>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>620965520.4</v>
+        <v>620971522.85</v>
       </c>
       <c r="R46" s="13" t="n">
         <v>0.442865097926909</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>1370778519.76</v>
+        <v>1370779911.2</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>250093696.52</v>
@@ -3230,10 +3230,10 @@
         <v>52052630</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>1802396732.29</v>
+        <v>1802398123.73</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>227518110.47</v>
+        <v>227518737.89</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>65852392.81</v>
@@ -3245,16 +3245,16 @@
         <v>10674494.15</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>3449590.27</v>
+        <v>3449593.92</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>4879527.79</v>
+        <v>4879532.95</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>24234422.43</v>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>347857552.82</v>
+        <v>347858189.04</v>
       </c>
       <c r="R47" s="13" t="n">
         <v>0.4207679702437824</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>1605884435.15</v>
+        <v>1605889446.8</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>251713084.28</v>
@@ -3288,10 +3288,10 @@
         <v>33130642</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>2004206803.69</v>
+        <v>2004211815.34</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>256675473</v>
+        <v>256678027.89</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>62840730.8</v>
@@ -3303,16 +3303,16 @@
         <v>7847120.41</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>4066698.51</v>
+        <v>4066717.5</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>5303386.05</v>
+        <v>5303410.81</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>16023075.86</v>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>362468410.91</v>
+        <v>362471009.55</v>
       </c>
       <c r="R48" s="13" t="n">
         <v>0.4544083188194561</v>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>1642735755.29</v>
+        <v>1642741004.82</v>
       </c>
       <c r="C49" s="9" t="n">
         <v>255216837.43</v>
@@ -3346,10 +3346,10 @@
         <v>28557666</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>2063088591.12</v>
+        <v>2063093840.65</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>257259436.56</v>
+        <v>257261306.54</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>63158844.13</v>
@@ -3361,16 +3361,16 @@
         <v>10739760.3</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>4712200.1</v>
+        <v>4712212.44</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>5445771.66</v>
+        <v>5445785.92</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>13777521.12</v>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>367431724.65</v>
+        <v>367433621.21</v>
       </c>
       <c r="R49" s="13" t="n">
         <v>0.4715622688002217</v>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>1539540787.28</v>
+        <v>1539548198.35</v>
       </c>
       <c r="C50" s="9" t="n">
         <v>251070477.59</v>
@@ -3404,10 +3404,10 @@
         <v>26540371</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>1989430965.03</v>
+        <v>1989438376.1</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>263417937.47</v>
+        <v>263421455.43</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>57612870.57</v>
@@ -3419,16 +3419,16 @@
         <v>15892369.91</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>4620017.62</v>
+        <v>4620044.41</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>5904473.6</v>
+        <v>5904507.84</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>13158708.92</v>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>375784444.71</v>
+        <v>375788023.7</v>
       </c>
       <c r="R50" s="13" t="n">
         <v>0.5184969295746537</v>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>1765237511.48</v>
+        <v>1765241756.34</v>
       </c>
       <c r="C51" s="9" t="n">
         <v>287468135.92</v>
@@ -3462,10 +3462,10 @@
         <v>28011807</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>2267519912.91</v>
+        <v>2267524157.77</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>281273971.44</v>
+        <v>281275433.1</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>59780017.61</v>
@@ -3477,16 +3477,16 @@
         <v>13923546.06</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>5175435.65</v>
+        <v>5175445.42</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>7388640.08</v>
+        <v>7388654.02</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>13969238.87</v>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>395118555.41</v>
+        <v>395120040.78</v>
       </c>
       <c r="R51" s="13" t="n">
         <v>0.5173698555705437</v>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>2536994712.59</v>
+        <v>2536997584.3</v>
       </c>
       <c r="C52" s="9" t="n">
         <v>438830798.95</v>
@@ -3520,10 +3520,10 @@
         <v>20465067</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>3325964610.65</v>
+        <v>3325967482.36</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>439535999</v>
+        <v>439537471.45</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>92879457.39</v>
@@ -3535,16 +3535,16 @@
         <v>15738266.69</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>7898127.56</v>
+        <v>7898140.18</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>23430230.63</v>
+        <v>23430268.07</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>10232009.27</v>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>618580601.01</v>
+        <v>618582123.52</v>
       </c>
       <c r="R52" s="13" t="n">
         <v>0.4928123695831447</v>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>2708842734.56</v>
+        <v>2708860229.71</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>590872240.37</v>
@@ -3578,10 +3578,10 @@
         <v>67156727</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>3868484988.59</v>
+        <v>3868502483.74</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>422626460.96</v>
+        <v>422632774.73</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>126606680.82</v>
@@ -3593,16 +3593,16 @@
         <v>34860196.13</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>8427236.539999999</v>
+        <v>8427279.23</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>31895562.4</v>
+        <v>31895724</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>33049467.84</v>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>679758741.23</v>
+        <v>679765259.29</v>
       </c>
       <c r="R53" s="13" t="n">
         <v>0.516687833119383</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>1283918446.65</v>
+        <v>1284040098.14</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>284348309.59</v>
@@ -3636,10 +3636,10 @@
         <v>57503053</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>1757858887</v>
+        <v>1757980538.49</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>214282784.22</v>
+        <v>214334321.19</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>74184906.98999999</v>
@@ -3651,16 +3651,16 @@
         <v>11903181.4</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1457560.58</v>
+        <v>1457678.4</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>6861386.8</v>
+        <v>6861941.43</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>28258572.47</v>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>347962121.04</v>
+        <v>348014330.46</v>
       </c>
       <c r="R54" s="13" t="n">
         <v>0.4317620090381182</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>1535864084.85</v>
+        <v>1536281102.71</v>
       </c>
       <c r="C55" s="9" t="n">
         <v>305249223.57</v>
@@ -3694,10 +3694,10 @@
         <v>29175511</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>1997941571.18</v>
+        <v>1998358589.04</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>255430233.77</v>
+        <v>255581901.18</v>
       </c>
       <c r="K55" s="12" t="n">
         <v>60959047.28</v>
@@ -3709,16 +3709,16 @@
         <v>8988100.75</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>2863596.19</v>
+        <v>2864225.27</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>5823250.66</v>
+        <v>5824529.92</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>13247763.43</v>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>358444258.53</v>
+        <v>358597834.28</v>
       </c>
       <c r="R55" s="13" t="n">
         <v>0.5085823534173731</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>1513097400.13</v>
+        <v>1516357209.48</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>295641521.04</v>
@@ -3752,10 +3752,10 @@
         <v>26518877</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>1968475380.15</v>
+        <v>1971735189.5</v>
       </c>
       <c r="J56" s="11" t="n">
-        <v>239381356</v>
+        <v>240624799.9</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>65905215.47</v>
@@ -3767,16 +3767,16 @@
         <v>10595274.38</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>2796215.42</v>
+        <v>2801669.77</v>
       </c>
       <c r="O56" s="12" t="n">
-        <v>5428833.87</v>
+        <v>5439423.46</v>
       </c>
       <c r="P56" s="12" t="n">
         <v>13188992.45</v>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>348902404.38</v>
+        <v>350161892.22</v>
       </c>
       <c r="R56" s="13" t="n">
         <v>0.5057931637222076</v>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>1710538291.44</v>
+        <v>1739639289.71</v>
       </c>
       <c r="C57" s="9" t="n">
         <v>307512657.17</v>
@@ -3810,10 +3810,10 @@
         <v>27882416</v>
       </c>
       <c r="I57" s="10" t="n">
-        <v>2228135573.44</v>
+        <v>2257236571.71</v>
       </c>
       <c r="J57" s="11" t="n">
-        <v>280271339.54</v>
+        <v>292536631.12</v>
       </c>
       <c r="K57" s="12" t="n">
         <v>59383053.97</v>
@@ -3825,16 +3825,16 @@
         <v>15136999.32</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>3156594.54</v>
+        <v>3214476.69</v>
       </c>
       <c r="O57" s="12" t="n">
-        <v>6278737.89</v>
+        <v>6393870.47</v>
       </c>
       <c r="P57" s="12" t="n">
         <v>14538750.58</v>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>393155882.67</v>
+        <v>405594188.99</v>
       </c>
       <c r="R57" s="13" t="n">
         <v>0.5643242205108819</v>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>1669847493.13</v>
+        <v>1799604576.25</v>
       </c>
       <c r="C58" s="9" t="n">
         <v>360408853.21</v>
@@ -3868,10 +3868,10 @@
         <v>38681934</v>
       </c>
       <c r="I58" s="10" t="n">
-        <v>2267711022.73</v>
+        <v>2397468105.85</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>273081236.1</v>
+        <v>295984175.58</v>
       </c>
       <c r="K58" s="12" t="n">
         <v>71309977.62</v>
@@ -3883,16 +3883,16 @@
         <v>15006248.84</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>4490144.69</v>
+        <v>4484044.1</v>
       </c>
       <c r="O58" s="12" t="n">
-        <v>9425711.689999999</v>
+        <v>9412905.33</v>
       </c>
       <c r="P58" s="12" t="n">
         <v>19224841.85</v>
       </c>
       <c r="Q58" s="12" t="n">
-        <v>410233059.18</v>
+        <v>433117091.71</v>
       </c>
       <c r="R58" s="13" t="n">
         <v>0.5560789475916204</v>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>2349332801.23</v>
+        <v>2499705071.41</v>
       </c>
       <c r="C59" s="9" t="n">
         <v>470702992.36</v>
@@ -3926,10 +3926,10 @@
         <v>20443443</v>
       </c>
       <c r="I59" s="10" t="n">
-        <v>3248025733.62</v>
+        <v>3398398003.8</v>
       </c>
       <c r="J59" s="11" t="n">
-        <v>376772420.49</v>
+        <v>402855964.25</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>82082024.87</v>
@@ -3941,23 +3941,77 @@
         <v>33934101.63</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>9030969.970000001</v>
+        <v>9031386.5</v>
       </c>
       <c r="O59" s="12" t="n">
-        <v>22087683.21</v>
+        <v>22088701.93</v>
       </c>
       <c r="P59" s="12" t="n">
         <v>10406677.63</v>
       </c>
       <c r="Q59" s="12" t="n">
-        <v>562846209.8200001</v>
+        <v>588931188.83</v>
       </c>
       <c r="R59" s="13" t="n">
         <v>0.52815090628141</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n">
+        <v>2647422716.28</v>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>745141871.74</v>
+      </c>
+      <c r="D60" s="9" t="n"/>
+      <c r="E60" s="9" t="n">
+        <v>196562591</v>
+      </c>
+      <c r="F60" s="9" t="n">
+        <v>52529461.52</v>
+      </c>
+      <c r="G60" s="9" t="n">
+        <v>139971003</v>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>68138881</v>
+      </c>
+      <c r="I60" s="10" t="n">
+        <v>3849766524.54</v>
+      </c>
+      <c r="J60" s="11" t="n">
+        <v>435159946.87</v>
+      </c>
+      <c r="K60" s="12" t="n">
+        <v>120161766.31</v>
+      </c>
+      <c r="L60" s="12" t="n"/>
+      <c r="M60" s="12" t="n">
+        <v>38122461.88</v>
+      </c>
+      <c r="N60" s="12" t="n">
+        <v>9008807.619999999</v>
+      </c>
+      <c r="O60" s="12" t="n">
+        <v>24005040.26</v>
+      </c>
+      <c r="P60" s="12" t="n">
+        <v>33777300.2</v>
+      </c>
+      <c r="Q60" s="12" t="n">
+        <v>660235323.14</v>
+      </c>
+      <c r="R60" s="13" t="n">
+        <v>0.6145082904966043</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R59"/>
+  <autoFilter ref="A2:R60"/>
   <mergeCells count="3">
     <mergeCell ref="R1"/>
     <mergeCell ref="B1:I1"/>
@@ -3973,7 +4027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7114,7 +7168,7 @@
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>1936461735.07</v>
+        <v>2081161721</v>
       </c>
       <c r="C58" s="9" t="n">
         <v>373857348.69</v>
@@ -7135,10 +7189,10 @@
         <v>39460452</v>
       </c>
       <c r="I58" s="10" t="n">
-        <v>2552825447.15</v>
+        <v>2697525433.08</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>387873285.53</v>
+        <v>416856692.72</v>
       </c>
       <c r="K58" s="12" t="n">
         <v>76475302.37</v>
@@ -7150,16 +7204,16 @@
         <v>15006248.84</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>5187919.85</v>
+        <v>5175957.32</v>
       </c>
       <c r="O58" s="12" t="n">
-        <v>11783634.44</v>
+        <v>11756463.22</v>
       </c>
       <c r="P58" s="12" t="n">
         <v>19555570.12</v>
       </c>
       <c r="Q58" s="12" t="n">
-        <v>533576859.54</v>
+        <v>562521132.98</v>
       </c>
     </row>
     <row r="59">
@@ -7169,7 +7223,7 @@
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>2724436268.13</v>
+        <v>2890796443.32</v>
       </c>
       <c r="C59" s="9" t="n">
         <v>486438716.83</v>
@@ -7190,10 +7244,10 @@
         <v>20822242</v>
       </c>
       <c r="I59" s="10" t="n">
-        <v>3643353117.99</v>
+        <v>3809713293.18</v>
       </c>
       <c r="J59" s="11" t="n">
-        <v>545704584.51</v>
+        <v>579026527.6</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>88438958.8</v>
@@ -7205,20 +7259,71 @@
         <v>33934101.63</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>10651651.36</v>
+        <v>10641879.77</v>
       </c>
       <c r="O59" s="12" t="n">
-        <v>26891404.37</v>
+        <v>26866734.79</v>
       </c>
       <c r="P59" s="12" t="n">
         <v>10500226.58</v>
       </c>
       <c r="Q59" s="12" t="n">
-        <v>744653259.26</v>
+        <v>777940761.1900001</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n">
+        <v>3061625253.21</v>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>759849421.62</v>
+      </c>
+      <c r="D60" s="9" t="n"/>
+      <c r="E60" s="9" t="n">
+        <v>196562591</v>
+      </c>
+      <c r="F60" s="9" t="n">
+        <v>52529461.52</v>
+      </c>
+      <c r="G60" s="9" t="n">
+        <v>144490541</v>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>68576188</v>
+      </c>
+      <c r="I60" s="10" t="n">
+        <v>4283633456.35</v>
+      </c>
+      <c r="J60" s="11" t="n">
+        <v>613243538.22</v>
+      </c>
+      <c r="K60" s="12" t="n">
+        <v>126269139.95</v>
+      </c>
+      <c r="L60" s="12" t="n"/>
+      <c r="M60" s="12" t="n">
+        <v>38122461.88</v>
+      </c>
+      <c r="N60" s="12" t="n">
+        <v>10431657.68</v>
+      </c>
+      <c r="O60" s="12" t="n">
+        <v>28693914.19</v>
+      </c>
+      <c r="P60" s="12" t="n">
+        <v>33912349.21</v>
+      </c>
+      <c r="Q60" s="12" t="n">
+        <v>850673061.13</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q59"/>
+  <autoFilter ref="A2:Q60"/>
   <mergeCells count="2">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:Q1"/>
@@ -7233,7 +7338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7601,7 +7706,7 @@
         <v>9881154</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>0.6418</v>
+        <v>0.6417</v>
       </c>
       <c r="I9" s="14" t="n">
         <v>0.3517</v>
@@ -7816,7 +7921,7 @@
         <v>11483868</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>0.6612</v>
+        <v>0.6611</v>
       </c>
       <c r="I14" s="14" t="n">
         <v>0.3297</v>
@@ -8676,7 +8781,7 @@
         <v>12995978</v>
       </c>
       <c r="H34" s="14" t="n">
-        <v>0.7003</v>
+        <v>0.7001999999999999</v>
       </c>
       <c r="I34" s="14" t="n">
         <v>0.474</v>
@@ -9579,7 +9684,7 @@
         <v>11228218</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>0.7387999999999999</v>
+        <v>0.7386</v>
       </c>
       <c r="I55" s="14" t="n">
         <v>0.4565</v>
@@ -9622,7 +9727,7 @@
         <v>12075182</v>
       </c>
       <c r="H56" s="14" t="n">
-        <v>0.7541</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="I56" s="14" t="n">
         <v>0.4471</v>
@@ -9665,7 +9770,7 @@
         <v>14205984</v>
       </c>
       <c r="H57" s="14" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.7211</v>
       </c>
       <c r="I57" s="14" t="n">
         <v>0.4183</v>
@@ -9690,7 +9795,7 @@
         </is>
       </c>
       <c r="B58" s="9" t="n">
-        <v>1220745477.79</v>
+        <v>1311964348.92</v>
       </c>
       <c r="C58" s="9" t="n">
         <v>23632292.97</v>
@@ -9708,7 +9813,7 @@
         <v>18174499</v>
       </c>
       <c r="H58" s="14" t="n">
-        <v>0.7311</v>
+        <v>0.7290000000000001</v>
       </c>
       <c r="I58" s="14" t="n">
         <v>0.4053</v>
@@ -9733,7 +9838,7 @@
         </is>
       </c>
       <c r="B59" s="9" t="n">
-        <v>1717484623.43</v>
+        <v>1822358077.87</v>
       </c>
       <c r="C59" s="9" t="n">
         <v>36857669.38</v>
@@ -9751,7 +9856,7 @@
         <v>26557480</v>
       </c>
       <c r="H59" s="14" t="n">
-        <v>0.7311</v>
+        <v>0.7290000000000001</v>
       </c>
       <c r="I59" s="14" t="n">
         <v>0.4066</v>
@@ -9769,15 +9874,54 @@
         <v>0.2084</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="15" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>1930048559.62</v>
+      </c>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="9" t="n">
+        <v>135605251</v>
+      </c>
+      <c r="E60" s="9" t="n">
+        <v>468819494.82</v>
+      </c>
+      <c r="F60" s="9" t="n">
+        <v>50715643.98</v>
+      </c>
+      <c r="G60" s="9" t="n">
+        <v>41811319</v>
+      </c>
+      <c r="H60" s="14" t="n">
+        <v>0.7290000000000001</v>
+      </c>
+      <c r="I60" s="14" t="n"/>
+      <c r="J60" s="14" t="n">
+        <v>0.6899</v>
+      </c>
+      <c r="K60" s="14" t="n">
+        <v>0.6292</v>
+      </c>
+      <c r="L60" s="14" t="n">
+        <v>0.9655</v>
+      </c>
+      <c r="M60" s="14" t="n">
+        <v>0.2987</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
         <is>
           <t>Combo % = parlay volume / that venue's sports book. Kalshi's parlay is its KXMVE multi-event engine (leg-checked ~100% sports legs despite the 'cross-category' name), from a ~5M-trade sample (refreshed weekly) scaled to the daily total; ~70% of Kalshi's sports book by contracts, ~24% by $ (parlay legs are many and cheap - this sample-based split can move noticeably week to week, see VOLUME_METHODOLOGY.md). Not folded into the Sports tab's blended Combo %. Rothera runs no on-exchange parlay product.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M59"/>
+  <autoFilter ref="A2:M60"/>
   <mergeCells count="2">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B1:G1"/>
@@ -9810,7 +9954,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-27. Full detail: VOLUME_METHODOLOGY.md</t>
+          <t>Generated 2026-09-28. Full detail: VOLUME_METHODOLOGY.md</t>
         </is>
       </c>
     </row>
@@ -9869,7 +10013,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-27: independently recomputed totals matched the committed figures exactly</t>
+          <t>2026-09-28: independently recomputed totals matched the committed figures exactly</t>
         </is>
       </c>
     </row>

--- a/unified_sports_volume.xlsx
+++ b/unified_sports_volume.xlsx
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>1436296608.54</v>
+        <v>1436297224.82</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>133399888.66</v>
@@ -688,10 +688,10 @@
         <v>4370899</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>1614258703.12</v>
+        <v>1614259319.4</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>299228267.62</v>
+        <v>299228541.18</v>
       </c>
       <c r="K3" s="12" t="n">
         <v>50986272.22</v>
@@ -701,16 +701,16 @@
         <v>436176.76</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>466111.54</v>
+        <v>466111.72</v>
       </c>
       <c r="O3" s="12" t="n">
-        <v>8313319.71</v>
+        <v>8313322.91</v>
       </c>
       <c r="P3" s="12" t="n">
         <v>2035457.65</v>
       </c>
       <c r="Q3" s="12" t="n">
-        <v>361465605.5</v>
+        <v>361465882.44</v>
       </c>
       <c r="R3" s="13" t="n">
         <v>0.08714584215412201</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>1205574861.38</v>
+        <v>1205575132.45</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>134065934.54</v>
@@ -742,10 +742,10 @@
         <v>7690938</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>1388979770.89</v>
+        <v>1388980041.96</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>231812830.09</v>
+        <v>231812848.89</v>
       </c>
       <c r="K4" s="12" t="n">
         <v>51144509.72</v>
@@ -755,16 +755,16 @@
         <v>484971.88</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>458018.94</v>
+        <v>458018.87</v>
       </c>
       <c r="O4" s="12" t="n">
-        <v>8194670.93</v>
+        <v>8194669.82</v>
       </c>
       <c r="P4" s="12" t="n">
         <v>3928624.18</v>
       </c>
       <c r="Q4" s="12" t="n">
-        <v>296023625.73</v>
+        <v>296023643.36</v>
       </c>
       <c r="R4" s="13" t="n">
         <v>0.07635377691307524</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1155126136.17</v>
+        <v>1155126256.17</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>120394335.41</v>
@@ -852,10 +852,10 @@
         <v>16424385</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>1339764285.19</v>
+        <v>1339764405.19</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>243084975.15</v>
+        <v>243084981.15</v>
       </c>
       <c r="K6" s="12" t="n">
         <v>47471997.74</v>
@@ -867,16 +867,16 @@
         <v>222905.14</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>288785.03</v>
+        <v>288785.01</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>6546864.16</v>
+        <v>6546863.69</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>8062430.32</v>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>312034208.91</v>
+        <v>312034214.42</v>
       </c>
       <c r="R6" s="13" t="n">
         <v>0.1040882840699126</v>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1292332471.96</v>
+        <v>1292332574.87</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>125055737.8</v>
@@ -910,10 +910,10 @@
         <v>25367258</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>1497412509.54</v>
+        <v>1497412612.45</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>259388974.55</v>
+        <v>259388996.86</v>
       </c>
       <c r="K7" s="12" t="n">
         <v>47948549.82</v>
@@ -925,16 +925,16 @@
         <v>292548.17</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>631741.9300000001</v>
+        <v>631741.92</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>6846074</v>
+        <v>6846073.99</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>12897725.83</v>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>335567521.74</v>
+        <v>335567544.03</v>
       </c>
       <c r="R7" s="13" t="n">
         <v>0.1036604405692761</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1187476681.79</v>
+        <v>1187476835.25</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>141146850.05</v>
@@ -968,10 +968,10 @@
         <v>23442413</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>1409649801.3</v>
+        <v>1409649954.76</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>236786492.22</v>
+        <v>236786512.05</v>
       </c>
       <c r="K8" s="12" t="n">
         <v>50551741.94</v>
@@ -983,16 +983,16 @@
         <v>314539.43</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>1121126.86</v>
+        <v>1121126.81</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>7508200.49</v>
+        <v>7508200.14</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>11914017.45</v>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>315425276.23</v>
+        <v>315425295.65</v>
       </c>
       <c r="R8" s="13" t="n">
         <v>0.09320593928966855</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1139507899.4</v>
+        <v>1139508307.31</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>117925601.54</v>
@@ -1026,10 +1026,10 @@
         <v>18014225</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>1323115060.94</v>
+        <v>1323115468.85</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>224409184.84</v>
+        <v>224409187.74</v>
       </c>
       <c r="K9" s="12" t="n">
         <v>44939973.52</v>
@@ -1041,16 +1041,16 @@
         <v>280061.26</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>727245.53</v>
+        <v>727245.3</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>6114579.11</v>
+        <v>6114577.24</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>8768403.85</v>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>289902854.68</v>
+        <v>289902855.49</v>
       </c>
       <c r="R9" s="13" t="n">
         <v>0.100308786205459</v>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1265100760.99</v>
+        <v>1265101167.02</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>119094679.49</v>
@@ -1084,10 +1084,10 @@
         <v>23158725</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>1469766658.47</v>
+        <v>1469767064.5</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>247911615.74</v>
+        <v>247911651.56</v>
       </c>
       <c r="K10" s="12" t="n">
         <v>44015511.37</v>
@@ -1099,16 +1099,16 @@
         <v>545929.65</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>2089396.38</v>
+        <v>2089396.02</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>6720724.56</v>
+        <v>6720723.43</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>11672366.2</v>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>320422214.56</v>
+        <v>320422248.89</v>
       </c>
       <c r="R10" s="13" t="n">
         <v>0.1305164739611011</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>1136186134.46</v>
+        <v>1136186555.06</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>126075255.12</v>
@@ -1142,10 +1142,10 @@
         <v>33913543</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1360859451.58</v>
+        <v>1360859872.18</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>220239170.28</v>
+        <v>220239177.9</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>48533344.05</v>
@@ -1157,16 +1157,16 @@
         <v>391311.2</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2216296.98</v>
+        <v>2216296.33</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>7947284.77</v>
+        <v>7947282.43</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>17131109.38</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>302618092.73</v>
+        <v>302618097.36</v>
       </c>
       <c r="R11" s="13" t="n">
         <v>0.1174147553025735</v>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>1149014388.96</v>
+        <v>1149015333.9</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>86060025.34</v>
@@ -1258,10 +1258,10 @@
         <v>19659153</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>1308571043.2</v>
+        <v>1308571988.14</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>235935835.7</v>
+        <v>235935874.64</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>32573678.23</v>
@@ -1273,16 +1273,16 @@
         <v>342568.77</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2341917.94</v>
+        <v>2341916.52</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>4886885.27</v>
+        <v>4886882.31</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>9689300.880000001</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>294007187.35</v>
+        <v>294007221.92</v>
       </c>
       <c r="R13" s="13" t="n">
         <v>0.1581581529884586</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>1239561801.33</v>
+        <v>1239562071.33</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>114182203.82</v>
@@ -1316,10 +1316,10 @@
         <v>23900271</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>1441045991.4</v>
+        <v>1441046261.4</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>240248616.98</v>
+        <v>240248736.03</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>44020201.24</v>
@@ -1331,16 +1331,16 @@
         <v>463531.04</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2540979.82</v>
+        <v>2540980.32</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>6230003.74</v>
+        <v>6230004.97</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>11689925.33</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>313932671.99</v>
+        <v>313932792.77</v>
       </c>
       <c r="R14" s="13" t="n">
         <v>0.1369006174109096</v>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>1228257030</v>
+        <v>1228257038</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>130618679.53</v>
@@ -1374,10 +1374,10 @@
         <v>24114127</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>1450304129.81</v>
+        <v>1450304137.81</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>245776338.47</v>
+        <v>245776342.07</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>47519466.33</v>
@@ -1389,16 +1389,16 @@
         <v>401500.01</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3332919.04</v>
+        <v>3332919.06</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>6989415.74</v>
+        <v>6989415.78</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>11390787.92</v>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>321989410.05</v>
+        <v>321989413.71</v>
       </c>
       <c r="R15" s="13" t="n">
         <v>0.1338434618903201</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>1206704453.72</v>
+        <v>1206705231.25</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>122512075.89</v>
@@ -1432,10 +1432,10 @@
         <v>13420824</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>1408848332.75</v>
+        <v>1408849110.28</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>254182820.52</v>
+        <v>254183195.13</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>44967846.15</v>
@@ -1447,16 +1447,16 @@
         <v>598777.14</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>3170587.98</v>
+        <v>3170589.98</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>6715398.97</v>
+        <v>6715403.19</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>5908662.92</v>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>322392861.63</v>
+        <v>322393242.46</v>
       </c>
       <c r="R16" s="13" t="n">
         <v>0.1467243571212392</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>1502791049.02</v>
+        <v>1502791231.77</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>135215397.14</v>
@@ -1490,10 +1490,10 @@
         <v>23624339</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>1745512526.27</v>
+        <v>1745512709.02</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>307043241.84</v>
+        <v>307043338.65</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>48968794.7</v>
@@ -1505,16 +1505,16 @@
         <v>899431.51</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>3811157.38</v>
+        <v>3811157.95</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>8549347.57</v>
+        <v>8549348.84</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>11142968.25</v>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>388647742.67</v>
+        <v>388647841.32</v>
       </c>
       <c r="R17" s="13" t="n">
         <v>0.1671310595982739</v>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>1333531452.65</v>
+        <v>1333531484.65</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>146617403.12</v>
@@ -1548,10 +1548,10 @@
         <v>24327302</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>1585706613.98</v>
+        <v>1585706645.98</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>261229831.82</v>
+        <v>261229833.33</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>56978627.74</v>
@@ -1563,16 +1563,16 @@
         <v>644960.33</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>3122226.7</v>
+        <v>3122226.65</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>9982395.9</v>
+        <v>9982395.74</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>11565704.7</v>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>348777411.26</v>
+        <v>348777412.56</v>
       </c>
       <c r="R18" s="13" t="n">
         <v>0.1404248555660547</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>918415716.47</v>
+        <v>918415786.73</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>100434174.96</v>
@@ -1606,10 +1606,10 @@
         <v>11675481</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>1079832562</v>
+        <v>1079832632.26</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>188478240.81</v>
+        <v>188478271.36</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>36933011.94</v>
@@ -1621,16 +1621,16 @@
         <v>587784.12</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2573287.65</v>
+        <v>2573287.81</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>4428368.69</v>
+        <v>4428368.96</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>5508381.8</v>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>245091740.08</v>
+        <v>245091771.06</v>
       </c>
       <c r="R19" s="13" t="n">
         <v>0.1248997633733931</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>1097891897.95</v>
+        <v>1097892298.54</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>104121932.82</v>
@@ -1664,10 +1664,10 @@
         <v>14628870</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>1275895281.77</v>
+        <v>1275895682.36</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>215920037.01</v>
+        <v>215920066.53</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>38002578.37</v>
@@ -1679,16 +1679,16 @@
         <v>262338.04</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2738076.86</v>
+        <v>2738076.27</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>5494153.45</v>
+        <v>5494152.27</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>6862320.27</v>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>276652777.33</v>
+        <v>276652805.09</v>
       </c>
       <c r="R20" s="13" t="n">
         <v>0.178213812300984</v>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>1303192514.01</v>
+        <v>1303192525.68</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>122677612.96</v>
@@ -1722,10 +1722,10 @@
         <v>21296436</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>1518492807.83</v>
+        <v>1518492819.5</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>252866845.84</v>
+        <v>252866852.55</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>44708007.56</v>
@@ -1737,16 +1737,16 @@
         <v>691813.04</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>3247091.21</v>
+        <v>3247091.25</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>6819823.55</v>
+        <v>6819823.64</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>10373288.39</v>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>326406181.3</v>
+        <v>326406188.14</v>
       </c>
       <c r="R21" s="13" t="n">
         <v>0.2003579150386557</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>1144731478.31</v>
+        <v>1144731493.31</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>132905659.86</v>
@@ -1780,10 +1780,10 @@
         <v>24665675</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>1368052483.89</v>
+        <v>1368052498.89</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>217699072.82</v>
+        <v>217699074.32</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>44439935.08</v>
@@ -1795,16 +1795,16 @@
         <v>426029.96</v>
       </c>
       <c r="N22" s="